--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822D5758-B91C-454F-9A57-6A849E902056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0439226-990F-4699-8CC5-D5D5B639E6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="309">
   <si>
     <t>#</t>
   </si>
@@ -131,12 +131,6 @@
     <t>SSPH</t>
   </si>
   <si>
-    <t>SSPH/Bol.982/2026</t>
-  </si>
-  <si>
-    <t>Narcolaboratorio</t>
-  </si>
-  <si>
     <t>Cuautepec</t>
   </si>
   <si>
@@ -257,9 +251,6 @@
     <t>Tizayuca</t>
   </si>
   <si>
-    <t>Exigen liberación de persona</t>
-  </si>
-  <si>
     <t>Canal del Pueblo</t>
   </si>
   <si>
@@ -275,54 +266,18 @@
     <t>Aldo Falcón</t>
   </si>
   <si>
-    <t>Turismo</t>
-  </si>
-  <si>
-    <t>Hacienda</t>
-  </si>
-  <si>
-    <t>RTVH</t>
-  </si>
-  <si>
-    <t>SSH/Bol.176/2026</t>
-  </si>
-  <si>
-    <t>Cultura/Bol.710/2026</t>
-  </si>
-  <si>
     <t>Saderh</t>
   </si>
   <si>
     <t>Eulalio Larrieta agradece a Jair Martínez de la SEGOBH, porque esta al pendiente de lo que se necesite y los reportes.</t>
   </si>
   <si>
-    <t>Eulalio Larrieta agradece a Edith Balderas de la Secretaria de Educación Pública.</t>
-  </si>
-  <si>
-    <t>UPLAPH/Bol.156/2026</t>
-  </si>
-  <si>
     <t>Nidia</t>
   </si>
   <si>
-    <t>Taller regional recoge necesidades de tres municipios para orientar el desarrollo de Tula</t>
-  </si>
-  <si>
-    <t>Ordenamiento Territorial</t>
-  </si>
-  <si>
     <t>Neutro</t>
   </si>
   <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>Los diferentes retos de movilidad, infraestructura, servicios y crecimiento urbano de Axapusco, Tepeapulco, Tetepango y Tlahuelilpan fueron abordados durante el taller de elaboración del Programa Regional de Desarrollo Urbano y Ordenamiento Territorial en Tula, como parte de la política de planeación estratégica que impulsa el gobernador Julio Menchaca Salazar. El encuentro realizado a cargo de la Unidad de Planeación y Prospectiva de Hidalgo al frente del encargado del despacho, Onésimo Serrano Rivera, como parte de los trabajos que darán a conocer las condiciones de la región y definir las prioridades con base a las experiencias y quienes viven en ella. De esta forma, los habitantes, autoridades y dependencias compartieron problemáticas, oportunidades y proyectos que pueden contribuir a mejorar la conexión entre los municipios para ordenar orden el crecimiento urbano y fortalecer los servicios que utiliza la población.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ycSPSNTAVbFNKVnG__BLd9cUyod570Ph/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -332,298 +287,45 @@
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Onésimo Serrano Rivera</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Marlene López García, Teresa Olivares Reyna, y Ajacuba, Zitlaly Jazmín Zúñiga, Enrique Estrada Corres</t>
-  </si>
-  <si>
-    <t>Andrés Torres Andrés en respuesta a un radioescucha señala que Radio y Televisión de Hidalgo enfrenta nuevamente subejercicio presupuestario por cuarto o quinto año consecutivo. Asegura que aunque se asignó un presupuesto de 14 millones de pesos para abrir dos estaciones en 2026, no habrá incremento por mala administración. Critica que las prioridades de la gestión están en actividades superficiales, como relaciones públicas, en lugar del trabajo real. Comenta que la transmisión del 15 de septiembre no se realizó correctamente, pues fue realizada por otra empresa que cortó la señal sin avisarles y los dejó hablando solos. Señala la falta de reuniones y de seguimiento en el uso del presupuesto para los proyectos asignados, expresando su preocupación por la situación actual.</t>
-  </si>
-  <si>
-    <t>Mal Desempeño</t>
-  </si>
-  <si>
     <t>Negativo</t>
   </si>
   <si>
-    <t>Andrés Torres: si me preguntan sobre este tema de las estaciones, lo que decían, allá en Ixmiquilpan, pues hay una, otra vez subejercicio, ¿no?
-Así es.
-Por cuarto o quinto año consecutivo, Radio y Televisión de Hidalgo tendrá subejercicio, ¿no?
-Que es decir, el escaso, el escasísimo presupuesto que se da para la operación de Radio y Televisión, ni es, lo hemos sabido ejercer, no es que no lo hayamos tenido.
-En este año había 14, 2026, 14 millones de pesos para abrir dos estaciones.
-Radio Tenango y Radio, este, en Pachuca en AM.
-Eso es un hecho, no habrá en el 2026 otra vez, este, el incremento en las estaciones, ¿por qué? Pues por la mala administración.
-¿Por qué? Porque los que hicieron el proyecto quién sabe a dónde están.
-¿Por qué? Porque todos los temas son más urgentes, ¿no?, como tener su carro, tener tu gasolina, estar haciendo relaciones públicas, pero del trabajo, nada.
-Del trabajo, nada.
-Aquí solo importa quedar bien y estar parado ahí en los eventos diciendo que uno trabaja, pero nada más, nada, aunque la cámara esté apagada, ¿no?, como pasó en el informe.
-Como pasó, por supuesto, ¿no?
-Que fue un gran fraude, ¿no?, porque pues nada más fueron a pararse ahí, poner la cámara, pero no estaban transmitiendo.
-¿Qué pasó el día 15 de diciembre, el 15 de septiembre, ¿no?
-La, la transmisión era parte de otra empresa, cuando nos cortaron la señal, cuando se acabó la transmisión, nos dejaron hablando solos, ¿no?
-Entonces, aquí hay un gran, aquí hay una gran desfase, ¿no? Y hay que decirlo, ¿no?
-Ese dinero del presupuesto estaba aprobado por el Congreso para el 2026.
-Que era el proyecto para la estación en AM en Pachuca, que era el proyecto para la estación de Tenango de Doria, ¿dónde estamos en octubre, eh?
-Una sola junta, una sola reunión al respecto, no tuvimos.
-No había.
-Y estamos hablando del décimo mes de aquí.
-¿Dónde están?
-¿Quién lo marcó? ¿Quién lo marcó? ¿Por qué lo aprobamos?
-¿Se redireccionó ese dinero o es su ejercicio simple y puro?
-A eso me refiero y gracias por sus comentarios, no estoy enojado, estoy preocupado, ¿no?
-o.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1qZlYmaSu7-TiGz0tWXIabCot8dPNwZxK/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Andrés Torres dice estar preocupado por la situación en Radio y Televisión de Hidalgo. Comenta que, a pesar de estar en octubre, hay un subejercicio presupuestario continuo desde hace varios años bajo la dirección de Alan Austin y Carlos Barra. Señala que no se han podido gastar los fondos asignados y plantea preguntas sobre la falta de agua y papel en los baños, así como cortes de servicios. También critica que las plazas vacantes no se reponen y que siempre falta equipo y recursos para realizar coberturas o estrategias. Advierte que este problema de subejercicio continuará en los próximos años, lo que indica una mala administración en la institución y falta de conocimiento en la gestión de los recursos.</t>
-  </si>
-  <si>
-    <t>No, no estoy enojado, estoy preocupado, estoy preocupado porque veo que se pasa el tiempo, ya estamos en octubre y otra vez subejercicio, en los cuatro, los casi tres años de ala casi año que lleva todos los años es decir no nos podemos ni gastar el presupuesto el escaso presupuesto que se da ni ese nos podemos gastar lo que uno nos explica es porque no hay agua en los baños porque no hay papel en los baños porque nos cortan la luz nos cortan el agua porque si una persona es despedida o renuncia no se repone en la plaza porque si queremos no se hace algún tipo de cobertura no tenemos equipo porque si queremos hacer algún tipo de estrategia siempre hay el tema de que no hay recurso no hay recurso a eso me refiero 2022, 2023 2024, 2025 y 2026 vamos a tener subejercicio en realidad, que dicen ya 5 años seguidos, los 20 de septiembre entiendo porque nosotros entramos hasta septiembre, ¿no? aquí nosotros llegamos en septiembre ok digamos la administración ha entendido pero subejercicio es decir, ni siquiera podemos hemos sabido aplicar el recurso que se nos ha dado eso habla de una pésima es una administración que la gente que está al frente del área administrativa del reto de Cíndalo tiene ni idea de lo que está haciendo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1QT8ctzEi0fFP5WqK9-zITbx9GbJzshZo/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Carlos Barra Moulain</t>
-  </si>
-  <si>
-    <t>Esta noche del lunes, la comunidad de San Gabriel fue blanco de una doble jornada violenta que incluyó la ejecución a balazos de un hombre dentro de un vehículo y un posterior enfrentamiento armado contra la policía municipal. De acuerdo con fuentes policiales, los hechos comenzaron en un camino de terracería situada a espaldas de la parroquia del poblado de San Gabriel, donde vecinos alertaron sobre ráfagas de armas de fuego. Al arribar, las corporaciones de emergencia hallaron el cuerpo similar de un masculino con múltiples disparos dentro de un automóvil blanco. La zona fue acordonada por peritos de la Procuraduría General de Justicia del Estado de Hidalgo para el levantamiento de indicios. Minutos después, los ocupantes de otro vehículo realizaban detonaciones al aire, lo que motivó la intervención de patrullas municipales. Al notar la presencia de los uniformados, los civiles armados dispararon directamente contra los policías, lo que desató un intercambio de fuego y una persecución. La persecución concluyó cuando los agresores abandonaron el auto en el que se desplazaban y se dieron a la fuga a pie, internándose entre la maleza. La unidad quedó asegurada por las autoridades sin que se reportaran personas detenidas.</t>
-  </si>
-  <si>
-    <t>Ejecuciones</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1vGeRFpBEkV-5SWUr4IR9awt2kl4wZ05X/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1926/2026</t>
-  </si>
-  <si>
-    <t>Talento hidalguense destaca en las Olimpiadas Mexicanas de Informática 2026</t>
-  </si>
-  <si>
-    <t>Olimpiada de informática</t>
-  </si>
-  <si>
-    <t>También hay información de la Secretaría de Educación Pública de Hidalgo respecto a las actividades que están realizando. En este caso, eh el tema es la Olimpiada Mexicana de Informática y la Olimpiada Mexicana de Informática para primaria y secundaria, en donde se obtuvieron una medalla de plata, una de bronce y dos menciones honoríficas. Además, eh la entidad Hidalgo fue sede nacional de ambas competencias en las que participaron representantes de 25 delegaciones de diferentes partes del país. Estos resultados se se señala a través de comunicado oficial eh reflejan el talento y la preparación de las y los estudiantes hidalguenses en programación, algoritmos y resolución de problemas, así como las acciones emprendidas para identificar, formar e impulsar las habilidades tecnológicas de niñas, niños y jóvenes en los 84 municipios de Hidalgo. Eh se señala que bajo el liderazgo del gobernador Julio Menchaca Salazar y del secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, la Secretaría Pública estatal impulsa estrategias para planear las eh ampliar las oportunidades de aprendizaje, innovación y desarrollo de competencias digitales con el propósito de acercar la tecnología a las distintas regiones de la entidad. En la Olimpiada Mexicana de Informática, Juan José Pérez Domínguez, estudiante de la Escuela Preparatoria Doctor Alberto Zoebisch de Pachuca, obtuvo medalla de plata en la categoría de bachillerato; en la Olimpiada eh eh Mexicana de Informática para primaria y secundaria, específicamente eh Iker Daniel Pérez Domínguez, alumno del centro educativo Calmecac también en Pachuca, consiguió medalla de bronce en la categoría de secundaria. También José Alberto Lorenzana Cortés, del Colegio Antares de Tulancingo, y Maxel Uriel Quijano Sánchez, de la Escuela Niños Héroes de Chapultepec de Tetepango, Hidalgo, este reciben mención honorífica por su desempeño. La estrategia estatal contempló una convocatoria abierta a estudiantes de primaria, secundaria y bachillerato de la entidad a fin de brindar oportunidades de participación sin distinción de región o plantel educativo. Como parte de este proceso de febrero a septiembre de este año, las y los estudiantes seleccionados recibieron 8 meses de capacitación eh organizados en cuatro fases progresivas para fortalecer sus conocimientos y desarrollar las habilidades necesarias para competir. La realización de ambas olimpiadas en Hidalgo posiciona la entidad como sede del talento tecnológico juvenil del país y permitió visibilizar las capacidades de las nuevas generaciones en áreas estratégicas como el desarrollo científico y digital.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/138lb9tDLxYny7pMi3x0KxQ-w5UCCzwN6/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Natividad Castrejón</t>
-  </si>
-  <si>
     <t>Saderh/Bol.83/2026</t>
   </si>
   <si>
-    <t>Nueva olla de agua reactivará la actividad pecuaria en Zempoala</t>
-  </si>
-  <si>
     <t>Captación De Agua</t>
   </si>
   <si>
     <t>Zempoala</t>
   </si>
   <si>
-    <t>La actividad pecuaria de San Pedro Tlaquilpan ahora contará con mayor disponibilidad de agua durante la temporada de estiaje, con la inauguración de una olla de captación, almacenamiento y aprovechamiento hídrico cuya capacidad supera los 3.2 millones de litros. El titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Napoleón González Pérez, encabezó la entrega de esta infraestructura que fue construida con una inversión de 2.435.459 pesos, como parte de las acciones impulsadas por el gobierno de Julio Menchaca Salazar para fortalecer el sector agropecuario. La obra permitirá almacenar hasta 3.243.000 litros de agua y facilitar su conducción mediante 80 metros lineales construidos para el ingreso de recursos, además de líneas de conducción y trabajos complementarios de conservación. Con esta infraestructura se busca reactivar y dar continuidad a las actividades ganaderas de la región al contar con una fuente de abastecimiento que contribuya a enfrentar los periodos de escasez de lluvias y favorezca la producción pecuaria. Durante la inauguración acompañaron al titular de la SADER, el presidente municipal de Zempoala, Francisco Sinue Ramírez, autoridades locales y productores beneficiados, en tanto que para garantizar la transparencia y la correcta administración de la obra, se integró un comité conformado por habitantes de la comunidad. Esta acción se suma a las 148 ollas de captación que han sido construidas durante la presente administración estatal Que han estado orientadas a fortalecer la disponibilidad de agua, respaldar a las familias productoras Y a contribuir a la continuidad de las actividades agropecuarias aquí en el estado de Hidalgo Y de verdad que esas ollas de captación son fundamentales para, sobre todo, insisto, para espacios donde no llueve mucho Y cada gotita, de veras, que la atesoran</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zb_Dhb8wwqHZSzx6gxa9-X1DbMP1hyXw/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Napoleón González Pérez</t>
   </si>
   <si>
-    <t>Julio Menchaca, Sinuhe Ramírez Oviedo</t>
-  </si>
-  <si>
-    <t>Segobh/CBPEH/Bol.SN-A/2026</t>
-  </si>
-  <si>
-    <t>Se está reportando el hallazgo de 5 cuerpos de se considera igual número de personas que fueron localizadas en una fosa clandestina ubicada en la localidad de Texas, entre el municipio de Atotonilco de Tula. Vaya que ha sido todo un tema Atotonilco de Tula en meses recientes. Esto fue informado por la Comisión de Búsqueda de Personas en el Estado de Hidalgo. El hallazgo se hizo en esta fosa en los límites entre la entidad y el Estado de México. Y ocurrió este hallazgo durante un operativo realizado como parte de los trabajos de búsqueda que mantiene la comisión con apoyo de la Procuraduría General de Justicia del Estado de Hidalgo. De acuerdo con la información oficial, las labores de búsqueda de la comisión eh de búsqueda de personas permitieron localizar el sitio donde se encontraban los cuerpos. Posteriormente, personal de la Procuraduría de Justicia que estuvo a cargo del procesamiento del lugar, lo que permitió recuperar los restos de 5 personas que habían sido inhumadas ilegalmente. Hasta el momento, las autoridades no han informado la identidad de las personas localizadas por lo que continúan los trabajos para lograr su identificación plena. Tiene por momentos eh que se da a conocer esta información. De hecho, también se señala que las autoridades realizarán las acciones necesarias dentro de sus atribuciones para avanzar en la identificación de los cuerpos y posteriormente llevar a cabo su restitución a los familiares a quien correspondan. De hecho, tanto la Comisión de Búsqueda de Personas de Hidalgo como la propia Procuraduría Estatal mantienen coordinación durante el proceso y señalaron que permanecerán abiertos los canales de comunicación con familiares, colectivos, organizaciones y asociaciones dedicadas a la búsqueda de personas. El hallazgo se suma a las labores de búsqueda que se están haciendo en el estado de Hidalgo.</t>
-  </si>
-  <si>
     <t>CBPEH</t>
   </si>
   <si>
-    <t>Fosa clandestina</t>
-  </si>
-  <si>
-    <t>Atotonilco de Tula</t>
-  </si>
-  <si>
-    <t>Se está reportando el hallazgo de cinco cuerpos de... se considera igual número de personas que fueron localizados en una fosa clandestina ubicada en la localidad de Texas, centro del municipio de Atotonilco de Tula. Vaya que ha sido todo un tema Atotonilco de Tula en meses recientes. Esto fue informado por la Comisión de Búsqueda de Personas en el estado de Hidalgo. El hallazgo se hizo en esta fosa, en los límites entre la entidad y el estado de México. Y ocurrió este hallazgo durante un operativo realizado como parte de los trabajos de búsqueda que mantiene la Comisión con apoyo de la Procuraduría General de Justicia del Estado de Hidalgo. De acuerdo con la información oficial, las labores de búsqueda de la Comisión de Búsqueda de Personas permitieron localizar el sitio donde se encontraban los cuerpos. Posteriormente, personas de la Procuraduría de Justicia estuvo a cargo del procesamiento del lugar, lo que permitió recuperar los restos de cinco personas que habían sido inhumadas ilegalmente. Hasta el momento, las autoridades no han informado la identidad de las personas localizadas por lo que continúan los trabajos para lograr su identificación plena. Tiene momentos en que se da a conocer esta información. De hecho, también se señala que las autoridades realizarán las acciones necesarias dentro de sus atribuciones para avanzar en la identificación de los cuerpos y posiblemente llevar a cabo su restitución a los familiares a quien correspondan. De hecho, tanto la Comisión de Búsqueda de Personas de Hidalgo como la propia Procuraduría Estatal mantienen coordinación durante el proceso y señalaron que permanecerán abiertos los canales de comunicación con familiares, colectivos, organizaciones y asociaciones dedicadas a la búsqueda de personas. El hallazgo se suma a las labores de búsqueda que están haciendo en el estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1OGwHvcxAFpYEZwfkrFvx354jFaLFAEwu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>rocuraduría General de Justicia del Estado de Hidalgo</t>
-  </si>
-  <si>
     <t>Congreso</t>
   </si>
   <si>
-    <t>Traumatismo craneoencefálico fue la causa de muerte del réferi Gerardo Germán Pineda, conocido en el ámbito de la lucha libre como ‘El Búho’, quien falleció tras recibir un martinete durante una función en Mineral de la Reforma, realizada el pasado 6 de octubre. De acuerdo con los resultados de la autopsia, el impacto contra la lona desencadenó un edema cerebral y una hemorragia subaracnoidea, lesiones que derivaron en la muerte del referí. Los resultados del estudio médico fueron ingresados en la carpeta de investigación 12-2026-12673. Los hechos ocurrieron durante un enfrentamiento en el cuadrilátero, cuando presuntamente surgió una discusión entre Pineda y el luchador Hijo de Fishman, quien le aplicó la maniobra que terminó con consecuencias fatales. Tras el fallecimiento del réferi, el luchador fue detenido y señalado por el delito de homicidio doloso; posteriormente recuperó su libertad luego de que se alcanzara un acuerdo con la familia de la víctima. Como parte de ese convenio, se estableció un acuerdo reparatorio de daños que consistió en el pago de 585 mil 525 pesos a familiares del réferi, con lo que se desestimó el caso y los cargos penales.</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>Traumatismo encefálico fue la causa de muerte. De hecho, falleció tras recibir un martinete durante esta función de lucha libre que les estoy comentando y me ha dado la reforma realizada el pasado 6 de octubre, la semana pasada. De acuerdo con resultados de la autopsia, el impacto contra la lona desencadenó un edema cerebral y una hemorragia subaracnoidea, lesiones que derivaron en la muerte del réferi. ya hubo un sangrado, un traumatismo en la cabeza los resultados del estudio médico fueron ingresados en la carpeta de investigación 12-2026-12673 los hechos ocurrieron como le comentaba durante este enfrentamiento en el cuadrilátero cuando presuntamente surgió una discusión entre Pineda y el luchador hijo de Frischmann quien le aplicó la maniobra que terminó con consecuencias fatales tras el fallecimiento del réferi el luchador fue detenido y señalado por el delito de homicidio doloso posteriormente recuperó la libertad luego de que se alcanzara un acuerdo con la familia de la víctima. Como parte de ese convenio se estableció un acuerdo reparatorio de daños que consiste en el pago de 585 mil 525 pesos a familiares del réferi, con lo que se desestimó el caso y los cargos penales.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ITs-KqTVUDRlRysKJyuIetbJ_QW-dFWF/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Ultra Noticias</t>
   </si>
   <si>
-    <t>Con corte al 30 de septiembre del 2026, el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública reportó una disminución de 30.1% en los homicidios dolosos que se han registrado en el estado de Hidalgo con un total de 160 casos de enero a septiembre. Los datos corresponden a lo presentado durante la conferencia de prensa matutina a cargo del Gobierno Federal realizada el martes 13 de octubre. Se señaló que de enero a agosto del 2026 la entidad registró 149 homicidios dolosos, el 1.3% del total nacional, en comparación con los 160 casos reportados hasta septiembre, se tuvo un incremento de 11 homicidios hasta el noveno mes. Además, el estado de Hidalgo se ubicó en la posición número 14 entre las entidades con menos registros de homicidios dolosos. Se informó que el promedio diario de homicidios dolosos en México disminuyó más de 52% entre septiembre del 2024 y septiembre del 2026, al pasar de 89.9 a 42.2 casos diarios. Esto significa que en septiembre de este año se registraron 47.7 homicidios dolosos menos por día que en el mismo mes del 2024. La secretaria ejecutiva del Sistema, Marcela Figueroa Franco, detalló que siete entidades concentraron 50% de los homicidios dolosos registrados en el país: Baja California y Guanajuato representaron 8.5% cada uno, Chihuahua 7.8%, Sinaloa 7.7%, el Estado de México 6.4%, Guerrero 5.7% y Morelos 5.2%. Las entidades que destacaron por la reducción de este delito fueron San Luis Potosí, con una disminución de 78.6%, Nayarit 69.5% y Quintana Roo de 59.7%.</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
-    <t>Con corte, al 30 de septiembre del 2026, el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública reportó una disminución de 30.1% en los homicidios dolosos que se han registrado en el estado de Hidalgo con un total de 160 casos de enero a septiembre. Los datos corresponden a lo presentado durante la conferencia de prensa matutina a cargo del gobierno federal realizada el martes 13 de octubre. Se señaló que de enero a agosto del 2026 la entidad registró 149 homicidios dolosos, el 1.3% del total nacional en comparación con los 160 casos reportados hasta septiembre. Se tuvo un incremento de 11 homicidios hasta el noveno mes. Además, el Estado de Hidalgo se ubicó en la posición número 14 entre las entidades con menos registros de homicidios dolosos. Se informó que el promedio diario de homicidios dolosos en México disminuyó más de 52% entre septiembre del 2024 y septiembre del 2026, al pasar de 89.9 a 42.2 casos diarios. Esto significa que en septiembre de este año se registraron 47.7 homicidios dolosos menos por día que en el mismo mes del 2024. La secretaria ejecutiva del sistema, Marcela Figueroa Franco, detalló que siete entidades concentraron 50% de los homicidios dolosos registrados en el país. Baja California y Guanajuato representaron 8.5% cada uno. Chihuahua 7.8%, Sinaloa 7.7%, el Estado de México 6.4%, Guerrero 5.7% y Morelos 5.2%. Las entidades que destacaron por la reducción de este delito fueron San Luis Potosí con una disminución de 78.6%, Nayarit 69.5% y Quintana Roo de 59.7%.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1PHjwZDc7uL4S4BJN_XmHW906pQXATGQ3/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Marcela Figueroa Franco</t>
-  </si>
-  <si>
-    <t>Tulancingo</t>
-  </si>
-  <si>
-    <t>Hidalgo sumaría una nueva instancia municipal dedicada a la protección de niñas, niños y adolescentes, luego de que Ixmiquilpan pusiera en funcionamiento su Procuraduría Municipal de Protección para este sector de la población. La nueva dependencia brindará orientación, acompañamiento integral y asesoría jurídica, psicológica y de trabajo social a menores y sus familias ante situaciones que pongan en riesgo sus derechos. La procuraduría contará inicialmente con un equipo integrado por un abogado, una psicóloga y una trabajadora social, proyectándose la incorporación de un médico general en los próximos días. Esta área trabajará de manera coordinada con el Sistema Municipal DIF, autoridades educativas, dependencias municipales y seguridad pública para dar seguimiento a los casos canalizados. Esta instalación responde a las reformas a la Ley de los Derechos de Niñas, Niños y Adolescentes en el estado de Hidalgo, las cuales establecen que los 84 municipios deberán contar con una instancia de protección antes del 10 de diciembre de 2026.</t>
-  </si>
-  <si>
     <t>DIFH</t>
   </si>
   <si>
-    <t>Procuraduría municipal del menor</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Hidalgo estaría sumando una nueva instancia municipal dedicada a la protección de niñas, niños y adolescentes. Luego de que Miquel Pan, pues, de alguna forma pusiera en funcionamiento esta Procuraduría Municipal de Protección para este sector de la población. De hecho, la nueva dependencia estaría brindando orientación y acompañamiento a menores y sus familias también. además de atender situaciones en las que puedan estar en riesgo sus derechos con apoyo jurídico, psicológico y también de trabajo social. Y pues la Procuraduría estaría contando inicialmente con un equipo integrado por el abogado, una psicóloga y también una trabajadora social, mientras que en los próximos días se prevé la incorporación de un médico general para fortalecer los servicios. y pues el área estaría trabajando de manera coordinada con el sistema municipal de disciplina, también autoridades educativas, dependencias municipales y seguridad pública, con la finalidad de dar seguimiento integral a los casos que sean canalizados. De hecho, la instalación de la Procuraduría responde a las reformas a la ley, precisamente los derechos de niñas, niños y adolescentes en el estado de Hidalgo, pues que establece que los 84 municipios deberán contar con instancias de protección antes del 10 de diciembre del 2026 entonces pues bien, ya se suma una más en Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1D69kj7WG_vRNGNKy7ovYZnMwxei83ssg/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Daniel Martínez: esto último acerca de las evaluaciones que hacen de recaudación, calificaciones, etcétera, etcétera, etcétera. Entiendo que está en un quizás en uno de los espacios más delicados, todos tienen su su complejidad, pero más delicados en el manejo de los recursos financieros, este materiales y el más importante que es el humano, pero esta última parte de tenemos buenas calificaciones, no hemos pedido deuda, etcétera, etcétera. Eh entiendo que es la explicación y o justificación de que le vamos a meter 7,000 millones de pesos a tres proyectos, pero no dejamos abandonados y al resto de la infraestructura del estado de Hidalgo. Ánimas que así sea. **Izza Hernández:** Así es, porque sí era alguna de las preguntas, pero bueno, pues ahí está también lo que responden al respecto y serán 7,000 millones de pesos en estos tres proyectos. **Daniel Martínez:** Dicen por acá, "Muchas inversiones para Pachuca y Tulancingo, ¿para cuándo habrá una inversión millonaria?", consideran, pues parece que que nunca, es lo que nos escriben por acá por WhatsApp, por ejemplo. **Daniel Martínez: te parafraseo hoy, es por lo menos el distribuidor vial Pueblos Unidos, por lo menos ya tiene nombre.</t>
-  </si>
-  <si>
-    <t>Obras De Infraestructura</t>
-  </si>
-  <si>
-    <t>Todo último acerca de las evaluaciones que hacen de recaudación, calificaciones, etcétera, etcétera. Entiendo que están quizá en uno de los espacios más delicados, todos tienen su complejidad, pero más delicados en el manejo de los recursos financieros, materiales y el más importante que es el humano. Pero esta última parte de tenemos buenas calificaciones, no hemos pedido deuda, etcétera, etcétera. Entiendo que es la explicación y o justificación de que le vamos a meter 7 mil millones de pesos a tres proyectos, pero no dejamos abandonados al resto de la infraestructura del Estado Hidalgo. Ánimas que así sea. Así es, porque si era alguna de las preguntas, pero bueno, pues ahí está también lo que responden al respecto y serán 7 mil millones de pesos en estos tres proyectos. Dicen por acá muchas inversiones para Pachuca y Tulancingo. ¿Para cuándo habrá una inversión millonaria? Consideran, pues parece que nunca. Es lo que dicen por acá por WhatsApp, por ejemplo. Bueno, 8 de la mañana con 59 minutos de parafraseo. Oye, es por lo menos el distribuidor vial Pueblos Unidos, por lo menos ya tiene nombre. Pausa, la hora en punto. Vamos y venimos, estamos en Ultra Noticias Hidalgo</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1l7-YauniBKFP73He31T7itvIRuf4MREg/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Hacienda/Bol.014/2026</t>
-  </si>
-  <si>
-    <t>El gobierno del estado de Hidalgo ha destinado en coordinación con la Federación 10,200 millones de pesos para poder atender los daños provocados por las lluvias registradas en octubre del 2025. Así lo informó la secretaria de Hacienda estatal, estamos hablando de María Esther Ramírez Vargas, durante la comparecencia ante el Congreso local. El total de recursos alrededor de 2,400 millones de pesos corresponden a obras de infraestructura, mientras que otros 2,100 millones fueron dirigidos a apoyos para habitantes de 236 comunidades, estas ubicadas en 28 municipios afectados por estas precipitaciones. Y bueno, la funcionaria señaló también que pues de alguna forma se contemplan 5,700 millones de pesos para la reconstrucción de puentes, además también una bolsa de 800 millones destinada a cerca de 300 obras que todavía pues se encuentran en proceso de validación o contratación y de acuerdo con lo expuesto ante los legisladores, se prevé que los procedimientos relacionados con estas obras queden concluidos antes de finalizar el 2026, todo esto como parte de las acciones para poder recuperar la infraestructura dañada y atender también a las zonas que resultaron afectadas por las lluvias. De hecho, la funcionaria señaló también que alrededor de 300 obras se, bueno, que implican una inversión de 800 millones de pesos continúan en proceso de validación y contratación también, así lo informó María Esther Ramírez Vargas, quien es secretaria de Hacienda estatal. Explicó también que pues la reconstrucción contempló una bolsa total de 10,200 millones de pesos para poder atender los daños registrados en 236 comunidades de 28 municipios de la entidad. De ese monto, 4,500 millones corresponden a recursos estatales y el resto a las aportaciones de la Federación. De hecho, de la inversión estatal 2,400 millones de pesos se destinaron a infraestructura, mientras que 2,100 millones pues se asignaron a los eh apoyos precisamente en especie. Y Ramírez Vargas agregó también que los trabajos de reconstrucción continúan y que la aplicación también de los recursos para las obras pues están a cargo de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible porque es la ejecutora del gasto. Entonces pues de esta manera, Daniel es como pues dan a conocer cuánto se estaría o se estima pues a la reconstrucción tras la lluvia en el 2025, ya un año, por cierto, de esto.</t>
-  </si>
-  <si>
-    <t>El gobierno del estado de Hidalgo ha destinado en coordinación con la Federación 10.200 millones de pesos para poder atender los daños provocados por las lluvias registradas en octubre del 2025. Así lo informó la Secretaría de Hacienda Estatal, estamos hablando de María Esther Ramírez Vargas, durante la comparecencia ante el Congreso Local. Y pues el total de recursos, alrededor de 2.400 millones de pesos, corresponden a obras de infraestructura, mientras que otros 2.100 millones fueron dirigidos a apoyos para habitantes de 236 comunidades, estas ubicadas en 28 municipios afectados por estas precipitaciones. Y, bueno, la funcionaria señaló también que, pues, de alguna forma se contemplan 5.700 millones de pesos para la reconstrucción de puentes, además también una bolsa de 800 millones destinada a cerca de 300 obras que todavía se encuentran en proceso de validación o contratación. Y de acuerdo con lo expuesto ante los legisladores, se prevé que los procedimientos relacionados con estas obras pues queden concluidos antes de finalizar el 2026. Todo esto como parte de las acciones para poder recuperar la infraestructura dañada y atender también a las zonas que resultaron afectadas por las lluvias De hecho la funcionaria se también que alrededor de 300 obras que implican una inversión de 800 millones de pesos, continúan en proceso de validación y contratación también, así lo informó María Esther Ramírez Vargas, quien es secretaria de Hacienda Estatal. Explicó también que la reconstrucción contempló una bolsa total de 10.200 millones de pesos para poder atender los daños registrados en 236 comunidades de 28 municipios de la entidad. De ese monto, 4.500 millones corresponden a recursos estatales y el resto a las aportaciones de la Federación. De hecho, de la inversión estatal, 2.400 millones de pesos se destinaron a infraestructura, mientras que 2.100 millones se asignaron a los apoyos precisamente en especie. Ramírez Vargas agregó también que los trabajos de reconstrucción continúan y que la aplicación también de los recursos para las obras, pues están a cargo de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, porque es la ejecutora del gasto. Entonces, pues de esa manera, Daniel, es como pues dan a conocer cuánto se estaría o se destina a la reconstrucción tras la lluvia en el 2025, ya un año por cierto de esto.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1-GGsFJcATTc7HN_Vd0NXMPZ0YiVzUbp2/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Congreso Local, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible.</t>
-  </si>
-  <si>
-    <t>María Esther Ramírez Vargas</t>
-  </si>
-  <si>
-    <t>Diálogo abierto y atención directa con la ciudadanía en la Mesa de Seguridad de Tenango de Doria</t>
-  </si>
-  <si>
-    <t>Mesa de seguridad</t>
-  </si>
-  <si>
-    <t>Como parte de las políticas de cercanía y diálogo permanente que impulsa el gobernador Julio Menchaca Salazar, el Gabinete de Seguridad se constituyó en el municipio de Tenango de Doria con autoridades federales y estatales para revisar la situación de las comunidades, fortalecer la coordinación y establecer acuerdos en beneficio de las familias de la región. El secretario de Gobierno, Guillermo Olivares Reyna, mantuvo un diálogo directo con la población en un espacio abierto donde las personas pudieron expresar con toda libertad sus planteamientos y compartir los asuntos que consideran prioritarios para sus comunidades. "Venimos para atenderles, para que ustedes nos digan: por favor, pongan atención aquí porque nos afecta de esta forma o de esta manera la situación que hoy les estoy narrando. Es cómo podemos generar las condiciones de convivencia armónica y gobernabilidad". El secretario insistió en que el gobierno de Julio Menchaca no espera que surjan problemas y que estos lleguen a constituir una crisis, una confrontación entre comunidades o entre familias. Dijo: "Venimos aquí por ustedes para conocer con toda anticipación qué es lo que debe atenderse, ese es el propósito", expresó Guillermo Olivares. Entre los asuntos prioritarios de la región, se dijo, se encuentra la tala ilegal, una problemática que requiere la intervención coordinada de las autoridades para proteger los recursos forestales y prevenir actividades que afecten el patrimonio natural de la comunidad. En ese sentido, se destacó la importancia de mantener el trabajo conjunto entre instancias federales y estatales, así como municipales, para fortalecer la vigilancia en las zonas forestales y darle seguimiento a todos los reportes con el propósito de prevenir y combatir la extracción ilegal de madera, así como preservar pues los bosques de esa región. En las mesas también se realizan espacios abiertos para facilitar el acercamiento de la ciudadanía con autoridades, además de revisar los temas sociales, se permite conocer de primera mano lo que ocurre en cada región y dar seguimiento a los asuntos expuestos por sus habitantes. Durante el encuentro, se tomó nota de los planteamientos de la población que se recibieron y que se dará seguimiento, todo ello en coordinación con las instancias correspondientes para construir respuestas y mantener la comunicación con las personas, con las comunidades. Trabajo conjunto en los tres órdenes de gobierno permite revisar las problemáticas de la región y establecer acuerdos para fortalecer la prevención y la atención a las demandas de la ciudadanía. Dice el secretario Guillermo Olivares durante esta mesa de seguridad que se estableció, que se constituyó ayer en...</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1muY8ozo62oBGlkV764OGahb1ushwErd5/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Guillermo Olivares Reyna</t>
   </si>
   <si>
     <t>Julio Menchaca</t>
   </si>
   <si>
-    <t>SSH/Bol.177/2026</t>
-  </si>
-  <si>
-    <t>Hidalgo fortalece la atención a la infancia desde sus primeros años de vida</t>
-  </si>
-  <si>
-    <t>Capacitación médica</t>
-  </si>
-  <si>
-    <t>Para fortalecer el desarrollo infantil temprano es una prioridad para el gobierno del estado de Hidalgo, encarcelado por el gobernador Julio Menchaca Salazar, que impulsa la capacitación del personal de salud para mejorar el acompañamiento y la atención integral de niñas y niños desde sus primeros años de vida. Como esta estrategia, la Secretaría de Salud de Estatal, Vanessa Escalante Arroyo, encarceló el curso-taller, el personal de salud como agente de cambio en el desarrollo infantil temprano, Cada momento cuenta impartido por la Fundación Televisa a estudiantes de medicina del Instituto Educativo y Cultural de Hidalgo en Tizayuca. Durante esta jornada, la titular de la Secretaría destacó que las experiencias de atención que reciben niñas y niños en esta etapa pueden influir significativamente en su bienestar futuro. Por ello, llamó a los participantes a ejercer su labor con sensibilidad, compromiso y una visión integral.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/12D6G_RPe-znTQzdCWJErNnWLIjLw7mqy/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
-    <t>Andrés Torres señala que hay un subejercicio, que se habían previsto 14 millones de pesos para Radio y Televisión Hidalgo en 2026 con el fin de abrir dos estaciones, una en Tenango de Doria y otra en Pachuca. Sin embargo, debido a errores, conflictos de interés y falta de conocimiento del personal administrativo, no se podrán abrir estas estaciones. Hay preocupación sobre el destino de esos fondos, y se ha discutido esta situación con el secretario de gobierno, Guillermo Olivares. Cuestiona la capacidad de quienes dirigen los proyectos, como Alan Austin y Carlos Barra, ya que no tienen experiencia en medios de comunicación. Critica la falta de profesionalismo en la propuesta de crear una agencia informativa por alguien que nunca ha trabajado en ese sector. Señala que una agencia informativa debe operar todos los días y las 24 horas, pero el actual director parece más interesado en relaciones públicas y favores personales que en la gestión efectiva de la información. Plantea que la falta de habilidades y experiencia de los líderes está causando el fracaso de proyectos importantes en la radio y televisión pública. Asimismo, destaca la necesidad de tener personas capacitadas al mando para que las iniciativas tengan éxito. A pesar de las amenazas de despido que pueda recibir, expresa que no teme y critica abiertamente la situación actual, cuestionando si los responsables entienden el descontrol en el que se encuentran. Asegura que es necesario realizar ajustes significativos para mejorar la situación en Radio y Televisión Hidalgo.</t>
-  </si>
-  <si>
-    <t>No hombre, lo que falta, otro año con subejercicio, ¿no?
-Para el 2026, estaba presupuestado para Radio y Televisión de Hidalgo, varios millones de pesos, creo que eran 7, 8 millones de pesos, 7 millones, no, eran 14 millones de pesos, para abrir dos estaciones, una en Tenango de Doria y una en Pachuca. Incluso ese asunto, yo aquí lo comenté desde el 2025. Está el proyecto para hacer una radiodifusora en amplitud modulada para Pachuca. Debido a las pifias, a los intereses encontrados, al desconocimiento del personal administrativo en Radio y Televisión de Hidalgo y, por supuesto, a los intereses personales de los directores, como Alan Austria y como Carlos Barra, no tendremos otra vez este año estaciones, ¿no? Y este dinero, pues o se hará su ejercicio o vaya usted a saber a dónde quedó. Este es un asunto que yo ya platiqué con el propio secretario de Gobierno, Guillermo Olivares, me externó su preocupación, ¿no?
-Pero bueno, pues entonces este... este es ahí donde uno dice, pues no que iban a cambiar, no que íbamos a hacer también, también estaba proyectado, se hizo un anuncio como un platillo de una agencia de noticias, ¿no?
-Pero ¿cómo alguien que es un neófito en materia informativa puede proponer una agencia informativa? Como alguien que nunca en su vida ha trabajado en los medios de comunicación, aunque diga lo que diga para quebrarla y hacerle este canelas, no es ser reportero, ni es ser editor, ni es ser ninguno de los eh pues perfiles que en la prensa conocemos, jefe de información, editor general, este corrector incluso, ¿no? ¿Cómo puede hablar de hacer una agencia informativa si nunca ha trabajado en una? Si nunca ha conocido una.
-Si no sabe que las agencias informativas trabajan los 365 días, las 24 horas del día. Cuando tenemos un director que con trabajos viene un ratito y siempre está en el café y siempre está haciendo relaciones públicas y pidiéndole favores a los secretarios. Pregunte a la secretaria de turismo, ¿no?
-El director general pidiéndole plazas, pasos amigos, ¿no? Entonces es cuando uno dice, porque estamos en estas condiciones y porque permiten que personas así nos dirijan, nos conduzcan, estén al frente de proyectos, por eso los proyectos fracasan, porque ponen verdaderos neófitos, neófitos, ignoran al frente de proyectos muy importantes, pues la radio y la televisión pública, así de simple, ¿no? Pero... pues ¿qué hace uno?
-No sabe. y te amenazan y te dicen que te mandan a correr como si me diera miedo, ¿no? Como si les tuviera miedo, ¿no? Por favor, o sea. De verdad, o sea, esto ya es, esto ya se descontroló, ¿no? ¿Qué no se dan cuenta que esto ya se descontroló, que hay que hacer verdaderamente un ajuste?
-Pero bueno.
----.
----</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/13FNWqMzAKHvSw915GF-66F1XNy3shx6n/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna, Alan Austria</t>
-  </si>
-  <si>
-    <t>Hoy tenemos comparecencia, a las 10 de la mañana asiste el secretario de Economía a cargo del ingeniero Carlos Henkel Escorza, más tarde a las 16 horas la Contraloría a cargo del director doctor Álvaro Bardales Ramírez.</t>
-  </si>
-  <si>
-    <t>Hoy tenemos comparecencia a las 10 de la mañana, asiste la Secretaría de Economía a cargo del ingeniero Carlos Henkel Escoza. Más tarde a las 16 horas, la Contraloría a cargo del doctor Álvaro Bardales Ramírez.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JVmb-4n90RpEbdqJ64Ok_914VAsoQvbk/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Álvaro Bardales</t>
   </si>
   <si>
@@ -633,87 +335,15 @@
     <t>Sedeco</t>
   </si>
   <si>
-    <t>Hoy tenemos comparecencia a las 10 de la mañana, asiste la Secretaría de Economía a cargo del ingeniero Carlos Hengel Escoza. Más tarde a las 16 horas, la Contraloría a cargo del doctor Álvaro Bardales Ramírez.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1N6aiRgTekOWEUOuewKPnfMlAqK2O6viu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Hidalgo vive un momento histórico: finanzas sólidas e inversión récord</t>
-  </si>
-  <si>
-    <t>Ayer compareció ante el Congreso del Estado la titular de la Secretaría de Hacienda y Crédito... la Hacienda de nuestro estado, ¿no? Hacienda y Crédito Público es la Federal. En el marco de la glosa del cuarto informe, la Secretaria de Hacienda, María Esther Ramírez Vargas, compareció ante la Sexagésima Sexta Legislatura del Congreso del Estado Libre y Soberano de Hidalgo para informar los resultados alcanzados en materia de fortalecimiento fiscal, inversión pública, transparencia financiera y saneamiento de la deuda heredada bajo el liderazgo del gobernador Julio Menchaca Salazar, eh quien consolida como un referente nacional el manejo responsable de las finanzas públicas. Durante su exposición, destacó que los ingresos... María Esther Ramírez Vargas destacó que los ingresos propios del Estado crecieron 96% en los últimos cuatro años, pasaron de 4,916 millones de pesos en 2021 a 9,636 millones al cierre del 2025. Es decir, sin aumentar tasas de los impuestos ya vigentes, este resultado pues es gracias a la modernización de los procesos tributarios, la ampliación de la base de contribuyentes y el fortalecimiento de los mecanismos de fiscalización. De la misma manera, dicen, la participación de los ingresos propios dentro del total de los ingresos estatales pasó de 9% a 13% en el mismo periodo, lo que fortalece la autonomía financiera de nuestro estado. La Secretaria informó que Hidalgo ocupó el primer lugar nacional en crecimiento de los recursos vinculados al Fondo General de Participación, esto durante el segundo trimestre del 2026. Registramos un incremento de 8% respecto al mismo periodo del año anterior. Destacó que Hidalgo mantiene el primer lugar en el tablero global de eficiencia recaudatoria del Servicio de Administración Tributaria, el SAT, después de haber ocupado el lugar 26 en término de la administración anterior. Entre los resultados relevantes de esta administración hacendaria, sobresale la generación de 3,650 millones de pesos en rendimientos financieros, producto de una gestión eficiente de disponibilidad y de optimización de las condiciones bancarias para la inversión de recursos públicos, fortaleciendo la liquidez estatal sin recurrir al endeudamiento. En materia de deuda pública, se destacó una reducción del 42% respecto al saldo heredado al inicio de la administración, todo ello mediante la liquidación anticipada de dos créditos y la liberación de más de 300 millones de pesos anuales que hoy se destinan a obra pública y programas sociales. Gracias a esta estrategia, Hidalgo se mantiene entre las cinco entidades con menor nivel de endeudamiento del país y es la única administración en los últimos 23 años que no contrató deuda pública ni a corto ni a largo plazo... este en ninguno de los... participaciones federales. Dice la Secretaria de Hacienda: "Este desempeño fue reconocido por las agencias calificadoras Fitch Ratings, Moody's, Local SP Global y HR Ratings, que ubican a Hidalgo en un rango Doble A consolidado entre las cuatro entidades federativas mejor evaluadas del país. Además, durante la comparecencia de ayer ante los diputados locales, se destacó que en los últimos 26 años Hidalgo no había alcanzado calificaciones crediticias tan altas, reflejo de la disciplina fiscal, el fortalecimiento de los ingresos propios, financieros y la transparencia en el ejercicio de los recursos públicos". También se destacó que entre el 2022 y el 2026, el Presupuesto de Egresos del Estado creció 37% y pasó de 54,892 millones de pesos a 75,343 millones. Este fortalecimiento presupuestal permitió destinar más de 45,500 millones de pesos a 4,800 proyectos de infraestructura, programas sociales y beneficio para los 84 municipios de nuestro estado. Tan solo en el presente año se realizó una inversión histórica superior a 4,600 millones de pesos para la ejecución de más de 300... de 232 obras con alcance en todas las localidades, fortaleciendo la conectividad regional, la infraestructura hidráulica, la movilidad y el desarrollo equilibrado de las distintas regiones de Hidalgo. En el ámbito social, se registra un incremento histórico, pues en el 2026 fueron destinados casi 5,000 millones de pesos a programas sociales y bienestar, cifra que multiplica por cinco lo ejercido al final de la administración anterior. De recursos, eh dice, de estos recursos, más de 2,600 millones de pesos fueron dirigidos a la atención de personas migrantes, mujeres, niñas, niños y adolescentes, juventudes, personas adultas mayores, pueblos originarios, personas con discapacidad y población LGBTTTIQ+. Asimismo, alcanzó el primer lugar nacional en el índice de calidad de la información del sistema de recursos federales transferidos de la Secretaría de Hacienda y Crédito Público, con un cumplimiento del 100% y mantiene por tercer año consecutivo el segundo lugar nacional en el índice de la modernización catastral de la SEDATU, entre resultados, y esto refleja una administración comprometida con la transparencia, la rendición de cuentas y el uso eficiente de los recursos públicos. Dice la Secretaria Esther Ramírez: "Con disciplina fiscal, eficiencia recaudatoria, transparencia y responsabilidad financiera, Hidalgo se consolidó como un referente nacional en materia hacendaria. Los resultados alcanzados permiten la capacidad del Estado para impulsar el desarrollo nacional en materia hacendaria, atraer inversión y generar bienestar para las..."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1i7r6QlOO6hEcD2CA8PyWJG-qpV_xrm5T/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Seguimos fuera del aire y no tenemos noticias de cuándo volverá la señal de la estación en Jacala de Ledezma, operando en el 91.1 de frecuencia modulada. Este problema se debe a cuestiones de proveedores y fallos técnicos. A pesar de nuestros esfuerzos por reportar la situación, esto parece no ser prioridad para el área administrativa, que está ocupada con auditorías, demandas y otros asuntos que no están relacionados con nuestro trabajo. Esto genera frustración entre los empleados, quienes también comentan sobre el ambiente laboral lleno de acosos y preocupaciones constantes. Existen dificultades diarias y a menudo se nos culpa por problemas como la falta de energía eléctrica. Por otro lado, el área administrativa no se encarga de cosas simples, como el pago de servicios esenciales, lo que requiere que se les envíen recordatorios continuos. Este tipo de gestión ocasiona una pérdida de tiempo y recursos. A pesar de que presumen ser profesionales, muchos no están a la altura de sus responsabilidades. Además, se menciona que el periodismo en Hidalgo ha cambiado, pero en realidad no se ve una mejora significativa. La comunicación se centra más en relaciones públicas que en el ejercicio periodístico real. El liderazgo dentro de la institución también se cuestiona. Hay líderes que no tienen experiencia en periodismo ni en el funcionamiento de una agencia informativa. A menudo están más preocupados por hacer relaciones públicas y solicitar favores de otros secretarios que en impulsar un trabajo efectivo. Esto lleva a que proyectos importantes fracasen porque son dirigidos por personas inexpertas. La situación ha alcanzado un punto crítico y se plantea la necesidad de realizar ajustes genuinos. La obligación de la radio y la televisión pública es informar a la población y mantener operativas sus plataformas. Sin embargo, el funcionamiento actual parece más enfocado en el beneficio personal de algunos empleados, y la programación se revisa para determinar cuántos programas son originales y cuántos son repetidos, lo que muestra una falta de innovación. Finalmente, se reporta que hay dificultades para cumplir con la programación adecuada. Los programas se repiten habitualmente y se cuentan como producciones propias, lo que evidencia un problema en la calidad y autenticidad de la producción de contenido. Así, la situación general dentro de la estación y el ambiente laboral se perciben caóticos, y la falta de dirección y profesionalismo se destacan como factores que afectan gravemente a la institución.</t>
-  </si>
-  <si>
-    <t>Andrés Torres: ...seguimos fuera del aire y el de yo no lo veo para cuándo, le soy muy honesto, no sé cuándo vaya a volver este, nuestra señal allá en el 1010 de amplitud modulada, eh no, no es el 1010, es el 91.1 de amplitud de frecuencia modulada allá en Jacala de Ledezma. Bueno, es una cuestión ahí de proveedores, de cuestiones de ingeniería, de cuestiones técnicas, pues nosotros hacemos el reporte, ¿no?, insistimos, pero pues usted sabe que en el área administrativa vive a otra, a otra este, a otra velocidad, están este, están entre auditorías, entre demandas, entre este despidos, entre acosamientos, entre este diferentes cuestiones que no tiene nada que ver con el trabajo, ahí están entretenidos mientras pues seguimos fuera del aire, ¿no? Y ya estamos a punto de cumplir un mes ahora y se terminó el 91.1 de frecuencia modulada, la voz de la Sierra Gorda. Y esto uno uno no se explica, ¿no?, pues no que iban a mejorar, no que todos éramos profesionales, no que todo el mundo sabía muchísimo, pues aquí solamente se habla de acoso, solamente se habla de terrorismo, solamente se habla de excesos, solamente se habla de demandas, todos los días ese es el ir y venir de Radio y Televisión de Hidalgo de trabajo, nada, pero de este problemas todos los días y si dices algo "te voy a correr", ¿no? y si se va la luz, "te voy a correr", ¿no? Tu culpa. Porque es tu culpa que se vaya la luz, ¿no? Cuando las áreas administrativas no pueden hacer un documento para pagar 40 pesos de agua desde agosto, imagínese usted, ¿no? Les tienen que mandar tres o cuatro avisos para decir, oye, ¿ya pagaste el agua, eh? Oye, ¿hay que pagar la luz, eh? no, no tienen toda la vida haciéndolo y pues se olvida, ¿no? y cada mes hay que gastar papel, tiempo, este personal para recordarle a la gente qué tiene que hacer, si se dicen profesionales, ¿no? cambiaron el periodo, a mí me presumieron en una junta, "yo cambié el periodo de Hidalgo, no, la transversalidad por Dios", ¿no? No tiene ni la menor idea de lo que está haciendo, puras relaciones públicas, ¿no? Pidiendo a diestra y siniestra todos los secretarios apoyos, ¿no? Pero de trabajo nadita, ¿no? El periodismo pues menos, no lo conocen de veras, canelas, ¿no? No, más bien ni de lejos, pero bueno, podemos decir que cambió el periodismo en Hidalgo. Otro cambio de periodismo, no tiene, porque estamos cumpliendo con el propósito de la radio y la televisión pública. Tenemos la obligación de cumplir con este propósito, que es informar a la población, tener las estaciones y la televisión a punto y bueno, pues aquí todo el mundo está jalando para para su beneficio, ¿no? Así es. Porque pues revisa las programaciones, ¿no? Revisa las programaciones, vamos a ver cuántas programaciones, cuántos programas son hechos producidos aquí en Radio y Televisión y cuántos son de fuera. Vea cuántas programas se repiten, ¿no? Se repiten diariamente, ¿no? Es decir, los registran como si fueran producciones propias, eso es estafar, eso es mentir, ¿no? Eso es faltarle al propósito y a la responsabilidad que tenemos aquí en Radio y Televisión estatal y por supuesto en la televisión, ¿no? Y le dices, "Oiga, hay que arreglar la estación, hay que ¡uh! hasta Jacala, ¿no? que lo puedes hacer por teléfono, ¿no?</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nVBBWCsmBEFwJ_f48yy15cI_hRrdwrxb/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Alan Austria</t>
-  </si>
-  <si>
-    <t>En Cuautepec, se descubrió otro túnel usado para sacar hidrocarburo de los ductos de Pemex. La Guardia Nacional, el gobierno del Estado de Hidalgo y la Policía Municipal realizaron un operativo que resultó en varias detenciones. El robo de hidrocarburo es un problema serio en la zona de Cuautepec y Santiago Tulantepec, donde hay operativos diarios.</t>
-  </si>
-  <si>
-    <t>En Cuautepec, la cosa estuvo complicadísima, otro túnel, localizaron otro túnel a través del cual estaban vaciando o sacando combustible, los ductos de Pemex, gente detenida, un operativo entre la Guardia Nacional y el gobierno del Estado de Hidalgo, por supuesto, policía municipal, y vaya que es un azote este asunto, es un tema muy complicado, el robo de hidrocarburos en toda esta zona de Cuautepec, Lucan, Santiago Tulantepec. también. Bueno, todos los días hay operativos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1yFryQvmhrwxOEoRanxnPSoUwMX5uqy2t/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Ayer hubo manifestación por parte de trabajadores del IMSS. Hoy se espera una marcha por parte de familiares de personas desaparecidas, esto se realizará de la Plaza Juárez hasta la Comisión de Búsqueda de Personas del Estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Andrés Torres informa que a Secretaría de Salud ha iniciado una campaña de vacunación estatal contra el covid y la influenza. Se invita a las personas a acudir a los centros de salud, clínicas y hospitales más cercanos, donde las vacunas son gratuitas. La meta es aplicar más de un millón y medio de vacunas antes de que comience el invierno, que empieza entre el 20 y el 25 de diciembre. Se prioriza la vacunación de niños menores de 5 años, adultos mayores y personas con enfermedades crónicas. También se recuerda la importancia de recibir el refuerzo contra el covid. Si alguien presenta síntomas como dolor de cabeza, congestión nasal o fiebre, debe ir de inmediato a su centro de salud, ya que no se recomienda la automedicación.</t>
-  </si>
-  <si>
-    <t>Tenemos campaña ya de vacunación en la Secretaría de Salud. Nos recuerda que el pasado lunes inició la campaña estatal de vacunación contra el COVID, contra la influenza. Por favor, acérquese a los centros de salud más cercanos a su domicilio, a las clínicas, a los hospitales. Las vacunas son gratis. Hay el propósito, la meta de aplicar más de un millón y medio de vacunas para esta temporada invernal y que antes de que se declare el invierno, el invierno entrará hasta los últimos días de diciembre, así del 20 al 25 de diciembre, entra el invierno, pero la Secretaría de Salud ya está trabajando para que una vez que esta temporada llegue, bueno, pues se hayan aplicado las vacunas, principalmente niños menores de 5 años, adultos mayores, personas con enfermedades crónico-degenerativas. Es muy importante que estén vacunados, hay que ponerse la fuerza de COVID a los balcones. Así es, y muy importante ir a vacunarse y es completamente gratuita. Además hay que recordar, si por favor presenta algún síntoma como dolor de cabeza, escurrimiento nasal, temperatura alta, inmediatamente acudir a su centro de salud. No es recomendable automedicar.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1O46hL8eWNxZIUFsg2K0IusBJ47U-kz-M/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Yazmin Leonardo</t>
   </si>
   <si>
     <t>Enlace Hidalgo2</t>
   </si>
   <si>
-    <t>Dos de la tarde con 51 minutos, estamos cerrando por acá con la información. Hidalgo destaca a nivel nacional en la Olimpiada Mexicana de Informática y la Olimpiada Mexicana de Informática para Primaria y Secundaria 2026, al obtener una medalla de plata, una de bronce y dos menciones honoríficas. Además, la entidad fue sede nacional de ambas competencias en las que participaron representantes de 25 delegaciones del país. Estos resultados reflejan el talento y la preparación de las y los estudiantes hidalguenses en programación, algoritmos y resolución de problemas, así como las acciones emprendidas para identificar, formar e impulsar las habilidades tecnológicas de niñas, niños y jóvenes de los 84 municipios. Y pues bueno, bajo el liderazgo del gobernador Julio Menchaca y del secretario de Educación, Natividad Castrejón, la Secretaría de Educación Pública de Hidalgo impulsa estrategias para ampliar oportunidades de aprendizaje, innovación y desarrollo de competencias digitales con el propósito de acercar la tecnología en las distintas regiones de la entidad. En la Olimpiada Mexicana de Informática, Juan José Pérez Domínguez, estudiante de la Escuela Preparatoria Doctor Alberto Zoević de Pachuca, obtuvo medalla de plata en la categoría de bachillerato, mientras que en la Olimpiada Mexicana de Informática para Primaria y Secundaria, Íker Daniel Pérez Domínguez, alumno del Centro Educativo Calmecac, también de Pachuca, consiguió medalla de bronce en la categoría de secundaria. Asimismo, Jorge Alberto Lorenzana Cortés, del Colegio Antares aquí de Tulancingo, y Maxel Uriel Quijano Sánchez, de la Escuela Niños Héroes de Chapultepec, del municipio de Tezontepec de Aldama, recibieron mención honorífica por su desempeño. La estrategia estatal contempló una convocatoria abierta a estudiantes de primaria, secundaria y bachillerato de la entidad a fin de brindar oportunidades de participación sin distinción de región o plantel educativo. Como parte de este proceso, de febrero a septiembre del 2026, las y los estudiantes seleccionados recibieron ocho meses de capacitación organizados en cuatro fases progresivas para fortalecer sus conocimientos y desarrollar las habilidades necesarias para competir. La realización de ambas olimpiadas en Hidalgo posicionó a la entidad como una sede del talento tecnológico juvenil del país y permitió visibilizar las capacidades de las nuevas generaciones en áreas estratégicas para el desarrollo científico digital, así que enhorabuena para estos jóvenes medallistas de las Olimpiadas Mexicanas de Informática, tanto de primaria como de secundaria y de preparatoria.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1PXiDEb4YmSWJEqPd5xhm6FRg7tECeZFH/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Natividad Castrejón</t>
   </si>
   <si>
-    <t>En el estado de Hidalgo, tras una solicitud de familiares de personas desaparecidas, la Comisión de Búsqueda de Personas localizó una fosa clandestina con los restos de cinco personas en la región comprendida entre Atotonilco de Tula, Tula y Atitalaquia. Luis Piña Sánchez, director de acciones de búsqueda, informó que los cuerpos presentaban un nivel avanzado de descomposición. Las autoridades se encuentran realizando los trabajos periciales y ministeriales correspondientes para lograr la identificación de las víctimas, mientras los familiares permanecen a la espera de los resultados.</t>
-  </si>
-  <si>
-    <t>Por la mañana le platicábamos sobre este este hallazgo de una pues de una fosa clandestina aquí en el estado de Hidalgo y pues resulta que pues obviamente esto se derivó del trabajo, del trabajo entre entre autoridades y pues sobre todo solicitudes, solicitudes de los padres de familia de personas desaparecidas quienes llevaron a la Comisión de Búsqueda de Personas del Estado de Hidalgo a realizar labores en la región de Tula, donde fue localizada esta fosa clandestina con restos humanos que presuntamente corresponderían a cinco a cinco personas. Le comparto con información de El Universal que Luis Piña Sánchez, director de acciones de búsqueda de la dependencia, informó que el hallazgo ocurrió durante las labores que realizaba el personal de la comisión sin que se tratara de una llamada anónima. El funcionario explicó que acudieron a ese punto tras una solicitud de familiares de personas desaparecidas, aunque evitó revelar detalles sobre la información que recibieron porque dijo no solicitaron algunas familiares, así nos lo pidieron. Las acciones sorprendieron eh de comprendieron, mejor dicho, en las zonas de Atotonilco de Tula, Tula y Atitalaquia, sin embargo, el funcionario no confirmó si las personas localizadas corresponden a casos de eh pues desapariciones previamente denunciadas, ni tampoco confirmó si cuentan con ficha de búsqueda. Lo que dijo el único comentario que podemos hacer es que en estas acciones que realiza la Comisión de Búsqueda fue que se localizó esta fosa y ahorita está la Comisión de Búsqueda junto con personal de la Fiscalía haciendo los asuntos periciales y ministeriales correspondientes. Esto eh obviamente las familias están a la espera de que se logren identificar los cuerpos y pues son momentos obviamente de de incertidumbres, ¿no? Porque pues ya los cuerpos presentaban eh pues cierto cierto nivel de descomposición, mejor dicho, avanzado nivel de descomposición y pues son momentos de incertidumbre que viven los familiares, esperando por un lado que pues dar con los restos de de su persona desaparecida y por otro lado pues con la esperanza de que no sean y que continúen con vida, pero bueno, así es este tema y estaremos dándole seguimiento a la información.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1U21wUv8bL8pMm4N3DyuRF9wMLLvb7A_4/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El Universal Hidalgo</t>
-  </si>
-  <si>
-    <t>Luis Piña Sánchez</t>
-  </si>
-  <si>
-    <t>Entrevista vía telefónica, el notario Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios del Estado de Hidalgo: Recordó que septiembre y octubre son considerados los meses del testamento en la entidad, periodo en el cual se promueven acciones pro bono e incentivos económicos para fomentar la cultura de la legalidad y la planeación patrimonial. Explicó que el trámite testamentario es un acto personalísimo, libre y revocable que inicia con una entrevista personalizada con el notario, reiterando que la institución cuenta con 94 notarías operando en el estado. Asimismo, detalló las tarifas preferenciales vigentes para la campaña, las cuales contemplan un costo de $950 pesos más IVA para adultos mayores de 60 años, $2,500 pesos más IVA para personas menores de dicha edad, y un costo reducido de $500 pesos más IVA para elementos de seguridad pública, bomberos y paramédicos.</t>
-  </si>
-  <si>
     <t>OCSAD</t>
   </si>
   <si>
@@ -723,121 +353,9 @@
     <t>Testamento</t>
   </si>
   <si>
-    <t>Locutor David Cárdenas: Gracias, David. Continúa con nosotros. Saludamos en esta oportunidad al licenciado Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios en el Estado de Hidalgo. Presidente, gracias por tomar la llamada. Buena tarde.
-Pedro Luis Noble Monterrubio: Hola, David, muchas gracias por la oportunidad de comunicación y pues a las ordenes como siempre.
-Locutor David Cárdenas: El mes de septiembre habíamos comentado al inicio de este mes hemos tenido hoy charlas en torno a la actividad notarial y que adquiere relevancia, no solamente que es su trabajo diario, sino están acudiendo, lo ha destacado mucho el gobernador del estado de Hidalgo, Julio Menchaca Salazar, a las rutas de la transformación, y en el mes de septiembre octubre, desde luego se lleva a cabo la tarea también por parte de ustedes de brindar apoyo a la ciudadanía en el mes del testamento, ya concluyó septiembre, estamos a mitad de octubre. Cuéntenos, sabemos, por pláticas con ustedes, notarias y notarios, que la cultura del testamento ha venido creciendo y esto también tiene que ver mucho con las facilidades que ustedes le otorgan en septiembre octubre. Cuéntenos.
-Pedro Luis Noble Monterrubio: Claro, David. Efectivamente, septiembre y octubre para Hidalgo son meses del testamento y el gobernador Menchaca nos ha pedido, nos ha invitado a ejercer acciones pro bono. Pro bono es una palabra que proviene del que significa el pro bien, y el pro bien es dar una atención especial, manejar un honorario reducido y dar atención, consulta gratuita a las personas, la consulta y el honorario que ya para el otorgamiento del testamento hay unos honorarios reducidos para aquellos que tenemos más de 60 años, $950 pesos más IVA, y personas con menor edad, $2,500 pesos. Y algo importante, una una promoción especial dirigida a los elementos que forman parte de las fuerzas operativas de seguridad pública, policía bancaria industrial, policía de investigación, mando coordinado, es decir, policías municipales que tienen mando coordinado con Secretaría de Seguridad Pública, bomberos y paramédicos de Cruz Roja Mexicana hay un honorario reducido de $500 pesos por testamento. Entonces, la invitación donde habría de aprovechar aquí estos grandes micrófonos de ese gran auditorio, pues invitar a la ciudadanía a que acudan con su notario más próximo, que otorguen testamento, que si ya lo hicieron y si se les ofreciera platicar con el notario para reformarlo, es decir, revocarlo, modificarlo, lo pueden hacer por supuesto. Es fortalecer la cultura de la legalidad, la cultura de la planeación patrimonial y sobre todo de fortalecer la confianza en la institución y sobre todo que las familias tengan después del fallecimiento del autor de la herencia, del dueño de los bienes, pues se tengan esa la confianza de que fue lo que quiso que se hiciera el testador, la persona que trabajó tantos años.
-Locutor David Cárdenas: En distintos momentos estoy charlando con el licenciado Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios y titular de la Notaría 18 en Pachuca. Nos ha comentado usted que el tema de realizar un testamento es un asunto personalísimo, así lo subrayan. pudiera si alguna persona requiere tener alguien que lo asesore, lo acompañe, lo podría hacer bajo su propio criterio, pero ustedes no influyen en la toma de decisiones, ¿cierto?
-Pedro Luis Noble Monterrubio: Es correcto, David. El testamento es un acto personalísimo, libre y revocable. ¿Qué significa? Que solamente la persona interesada debe estar presente con el notario para que le dé sus ideas, le platique sus inquietudes, sus intereses, de cómo quiere dejar su testamento y que se haga en completa libertad. Eso el notario se encarga de proveer ese espacio de libertad plena. A menos de que, por ejemplo, una persona que no supiera leer ni escribir, pues se tiene que asistir de un testigo de identidad, de asistencia, como dice el Código Civil, para que firme a su ruego y encargo, o también un tipo, algún tipo de ayuda, ¿no? Una persona que tuviese una discapacidad visual, por ejemplo, lo mismo. Ahí el propio código señala cómo y de qué manera es que se pueden dar esas ayudas a la persona testadora, pero de entrada es un acto personalísimo y si alguna persona tiene que platicar algo especial, algo muy íntimo de las personas, porque platicar que hay que manejarlo, el testador tiene la plena libertad de decir al notario, "notario, quiero platicar con usted en privado."
-Locutor David Cárdenas: Correcto. Bien, esto, todo esto tiene que ver porque en ocasiones, y ya ha ido cambiando, pero íbamos a la notaría y pensábamos pues que era un costo muy elevado, que no teníamos conocimiento de las leyes. Las notarias y los notarios tienen la posibilidad de irnos asesorando, de irnos orientando y de irnos dando paso a paso. En ese terreno, comentaba usted hace unos días, personas que tengan alguna discapacidad tienen ayuda, pero también ustedes pueden acudir cuando hay una persona que se encuentra enferma, ¿estoy en lo cierto?
-Pedro Luis Noble Monterrubio: Es correcto. También se da un servicio especial, por llamarlo de esa manera, a personas que no pueden trasladarse a la oficina y directamente al notario pedirles que asistan al hospital o al domicilio por alguna circunstancia de movilidad. El notario hará constar esas circunstancias en su instrumento y que sienta la ciudadanía de que siempre van a tener la orientación adecuada a través de un notario. De ahí la invitación a que vayan con su notario, su notaría más próxima a su domicilio, a la notaría notario de confianza y pidan una entrevista previa para que le platiquen al notario, le expongan sus proyectos, sus planes de plan patrimonial en materia testamentaria, y el notario va a tomar ya el concepto y después puede hacer que ahí mismo redacte el testamento o bien se agenda ya para la redacción y lectura del mismo.
-Locutor David Cárdenas: Dos preguntas, licenciado Pedro Luis Noble Monterrubio, ¿cuántas notarías existen en el estado de Hidalgo y por otro lado nos puede reiterar de nueva cuenta los costos de recuperación, me decía usted para personas de 60 y más, para personas que tengan otra edad, otro segmento y para los elementos de seguridad?
-Pedro Luis Noble Monterrubio: Somos 94 notarías que estamos operando en Hidalgo. Y yo yo les invitaría a que en cualquier buscador de internet tengan la posibilidad de usted poner Colegio de Notarios Hidalgo y ahí va a desplegar la pantalla, el directorio en dónde estamos en todo el territorio de Hidalgo. Y repito los honorarios reducidos para este mes de octubre, personas de más de 60 años, $950 pesos más IVA; personas de menos de esa edad, $2,500 pesos más IVA; y para elementos de las fuerzas operativas de seguridad pública, bomberos y paramédicos de Cruz Roja Mexicana, un honorario reducido de $500 pesos por testamento más IVA, por supuesto.
-Locutor David Cárdenas: Pues le agradezco como siempre haber hecho contacto con nosotros, tomar la llamada y, desde luego, sabemos que el Colegio de Notarios tiene en fe pública, son baluarte de la sociedad y sobre todo lo que siempre nos han comentado, cuando ya no estemos no dejemos problemas a la familia, ¿algo que desea agregar?
-Pedro Luis Noble Monterrubio: Pues David, reiterar la invitación a que aprovechemos ese mes de octubre a que revisemos lo que tengamos ya testamento otorgado o bien que pensemos en un testamento, que con confianza nos acerquemos a la notaría más próxima y pidamos una entrevista con el notario y ahí les habremos de atender con el profesionalismo, con la discreción y sobre todo con la seguridad que va a encontrar un consejo oportuno y prudente para hacer su testamento.
-Locutor David Cárdenas:: Gracias, presidente del Colegio de Notarios, licenciado Pedro Luis Noble Monterrubio, titular de la Notaría 18 en Pachuca. Gracias, mil. Buena tarde.
-Pedro Luis Noble Monterrubio: Gracias, David. Muchas gracias, David Astorga.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nE56kXPOzWyS0w-oMzjQoczzWf8HFrkF/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Colegio de Notarios del Estado de Hidalgo, Secretaría de Seguridad Pública</t>
-  </si>
-  <si>
     <t>Pedro Luis Noble Monterrubio</t>
   </si>
   <si>
-    <t>Durante su comparecencia ante el Congreso local, la secretaria de Hacienda, María Esther Ramírez Vargas, informó que las finanzas públicas de Hidalgo se han fortalecido mediante la planeación estratégica, la disciplina financiera y el robustecimiento de los ingresos propios, los cuales aumentaron un 96% al pasar de $4,916 millones de pesos en 2021 a más de $9,636 millones al cierre de 2025 sin incrementar impuestos. Asimismo, destacó que estas acciones, sumadas a la reducción del 42% de la deuda heredada y a la disminución de la dependencia de participaciones federales, han permitido que agencias calificadoras como Fitch Ratings y Moody's Local ubiquen al estado en el rango AA por su solvencia, liquidez y disciplina financiera.</t>
-  </si>
-  <si>
-    <t>Continuamos esta tarde la información Hidalgo fortaleció sus finanzas públicas, elevó sus ingresos propios y redujo 42% la deuda heredada, resultados que colocan al estado entre los cuatro mejores evaluados del país, esto de acuerdo con las calificaciones crediticias reportadas por la Secretaría de Hacienda Estatal. Durante su comparecencia ante el Congreso local, María Esther Ramírez Vargas informó que Fitch Ratings y Moody's Local ubican al estado en el rango AA, reflejo de indicadores de solvencia, liquidez y disciplina financiera. Son tres puntos que hay que destacar: la solvencia, la liquidez y la disciplina financiera. Precisamente en torno a la disciplina financiera, María Esther Ramírez destacó que desde el inicio de esta administración hubo algo que fue fundamental, desde luego, en la instrucción del gobernador Julio Menchaca Salazar, llevar a cabo una política financiera sana. Eso fue lo que destacó María Esther Ramírez. 
-María Esther Ramírez Vargas: Desde el inicio de esta administración, la instrucción del gobernador Julio Menchaca Salazar fue clara: ordenar las finanzas, planear estratégicamente y mantener la disciplina financiera. Redoblar esfuerzos para robustecer los ingresos propios ha sido fundamental para consolidar la autonomía financiera del estado de Hidalgo. Reducir la dependencia de las participaciones federales y asegurar la sostenibilidad fiscal, con ello, fortalecer la capacidad de respuesta institucional frente a las demandas de las familias hidalguenses mediante un sistema tributario más eficiente, equitativo y cercano al contribuyente. Hoy informo a esta soberanía que, sin incrementar los impuestos existentes, logramos que los ingresos propios crecieran un 96%, al pasar de $4,916 millones de pesos en 2021 a más de $9,636 millones de pesos al cierre del ejercicio fiscal 2025. Y aquí es importante destacar que este crecimiento se logró mediante la implementación de estrategias de administración tributaria, modernización de procesos, la ampliación de la base de contribuyentes y de combate a la evasión y a la elusión fiscal.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14H8vpT9MaW4DwwBjAl01Gqz8aRuVBMTn/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Congreso de Hidalgo</t>
-  </si>
-  <si>
-    <t>Este martes dieron inicio las operaciones de la Procuraduría Municipal de Protección a Niñas, Niños y Adolescentes en Ixmiquilpan, bajo la titularidad de la licenciada Erika Poblete Acosta. La instancia, presentada durante la conferencia semanal del gobierno local, tiene como objetivo brindar atención y protección a los derechos de este sector de la población con un equipo conformado por un médico, un psicólogo y un abogado, además de ofrecer atención psicológica, médica y legal en las oficinas ubicadas en la presidencia municipal, a un costado de Seguridad Pública.</t>
-  </si>
-  <si>
-    <t>inicia operaciones la Procuraduría Municipal de Protección a Niñas, Niños y Adolescentes en Ixmiquilpan. Nancy Aranda, tienes la información. 
-Este martes inició operaciones la Procuraduría Municipal de Protección a Niñas, Niños y Adolescentes en Ixmiquilpan, área que estará enfocada en la atención y protección de los derechos de este sector de la población. Durante la conferencia semanal del gobierno local fue presentada la licenciada Erika Poblete Acosta, quien estará al frente de esta instancia municipal, que contará además con personal especializado para atender los asuntos relacionados con la niñez y adolescencia. Como parte de su equipo de trabajo, la procuraduría dispondrá de atención psicológica y médica, además de personal que participará en la atención de los casos que presenten. En este sentido, Poblete Acosta informó que al inicio de operaciones se cuenta con un médico, un psicólogo y un abogado. Las oficinas se encuentran ubicadas en la presidencia municipal, a un costado de las instalaciones de Seguridad Pública Municipal.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1cH-PYs5tICV-N4MwkMFBDcPnvJWJekEW/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Erika Poblete Acosta</t>
-  </si>
-  <si>
-    <t>Entrevista vía telefónica, el notario Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios del Estado de Hidalgo: Detalló el proceso para la elaboración de testamentos en el marco de la campaña del "Mes del Testamento" (septiembre-octubre). Explicó que el trámite comienza con una entrevista previa de aproximadamente 20 minutos para definir los deseos del testador, seguida del otorgamiento formal que toma cerca de hora y media. Asimismo, recordó que durante esta temporada se mantienen honorarios reducidos (como $950$ pesos más IVA para adultos mayores de 60 años y una promoción especial de $500$ pesos más IVA para elementos de seguridad pública, bomberos y paramédicos) con el fin de fomentar la cultura de la planeación patrimonial y brindar certeza jurídica a las familias hidalguenses sin representar un obstáculo de tiempo o recursos.</t>
-  </si>
-  <si>
-    <t>Locutor Juan Carlos Santamaría: Vuelve a en Pachuca, son las 9 de la mañana con 44 minutos, y tengo el gusto de saludar a Pedro Luis Noble Monterrubio, notario notario de de Pachuca, notario del estado de Hidalgo, presidente del Colegio de Notarios del estado de Hidalgo. Y muy buen día, pues octubre sigue siendo mes de del testamento, y le pediría que pues fuéramos muy prácticos, si me permite el término para comentarle, compartirle a la población que ahora nos está escuchando, que le estará escuchando, a partir de que toma la la decisión de establecer su testamento, cuáles son los los pasos a seguir. Muy buen día, Pedro Luis Noble Monterrubio. 
-Pedro Luis Noble Monterrubio: Estimado Juan Carlos, muy buenos días para ti y para esa gran audiencia de NQ. Bueno, pues el primer punto muy puntual es tener una entrevista con el notario previa, una una reunión, una consulta y explicar al notario cuál es nuestro deseo como testadores, para que los bienes de los que somos dueños, cómo queremos transmitirlos para después de la muerte. Entonces, de esa manera es como como como se tiene el primer contacto, se elabora el testamento, se designan herederos, también puede haber legatarios y se designa al albacea. Y entonces, en esa plática con el notario, el notario interpreta la voluntad del testador, sus deseos, sus necesidades, y plasma el notario en el documento llamado testamento, es una escritura pública de testamento, la voluntad para que sus bienes se distribuyan para después de la muerte. Y este es el el el efecto más importante de tener la libertad de testamentar, de dejar establecida esa voluntad para designar herederos, sucesores y que se respete la voluntad de cada quien a través de la cláusula correspondiente que el notario hará de redactar, estimado Juan Carlos. 
-Locutor Juan Carlos Santamaría: Y a partir de que se toma esta decisión, este proceso que nos comenta aproximadamente cuánto tiempo implica, notario? 
-Pedro Luis Noble Monterrubio: Mira, para para la entrevista seguramente 20 minutos serían suficientes y para el otorgamiento de testamento empleamos aproximadamente hora y media, dependiendo si se trata de un testamento extenso o con legados. Bueno, eso incluso eso ya no entra en la campaña mes del testamento, que comprende para Hidalgo septiembre-octubre. Un un un testamento que entra en la campaña es de designación de herederos universales. De herencia, nombro e instituyo como legítimos herederos, como mi copra como mis herederos a 1, 2 y 3, o o o nada más a uno, o a y decimos en qué proporciones: partes iguales al hijo 1, el el el el 50%, al hijo 2 el 25 y a la hija 3 el 25%. Esa es la herencia universal y yo creo que se va a emplear aproximadamente una hora y media cuando mucho el proceso del otorgamiento de testamento, estimado Juan Carlos. 
-Locutor Juan Carlos Santamaría: Es decir, en unas en un tiempo de un solo día queda queda este trámite establecido, notario? 
-Pedro Luis Noble Monterrubio: Es correcto, es correcto. Lo recomendable es hacer una cita previa, por eso ir limitando continua a que estemos en la en la en la cercanía del notario o de la notaria para explicar cuál es su deseo, el notario se forma una idea, redacta el documento y una parte importante que no vamos a pedir que el legislador que el notario va a saber ahí si la persona requiere algún apoyo, alguna ayuda, es decir, si fuese una persona que no sabe leer y escribir, bueno, designamos a un testigo de asistencia, como dice la ley. Por eso es importante la entrevista previa. 
-Locutor Juan Carlos Santamaría: Muy bien, en todas las notarías de la entidad en su calidad de presidente del Colegio de Notarios, hay esta posibilidad de agendar previamente la cita? 
-Pedro Luis Noble Monterrubio: Es correcto, por eso la invitación a que se acerque la ciudadanía, el interesado, la interesada a su notaría más próxima con su notario de confianza, con su notaria de cabecera y de pedirle unos minutos para explicarle lo que lo que es nuestra intención como testadores, y entonces ya se agenda la la la la la la diligencia del acto del testamento, ¿por qué? Porque la ley exige una solemnidad especial para el testamento, formalidades especiales que dice el código civil, bueno, eso lo observamos en cada notaría, independientemente de la de la toma de firma, de las toma de credenciales, de las identificaciones, todo eso que que se hace en ese contexto, en un solo contexto es en donde se desarrolla este testamento, mi estimado Juan Carlos. 
-Locutor Juan Carlos Santamaría: Muy bien, notario, bien, pues con lo que nos explica dejamos fuera el asunto del tiempo como un obstáculo para para poder realizar este acto de testamentar, puesto que es realmente poco desde que se hace la cita y que se lleva a cabo el trámite. Por otra parte, nos habla acerca de los la promoción de septiembre y octubre como meses del testamento en Hidalgo, ¿en qué consiste, notario? 
-Pedro Luis Noble Monterrubio: Sí, Juan Carlos, es invitar a la ciudadanía a fortalecer la cultura de la legalidad, la cultura del testamento, la cultura de la planeación patrimonial, y que acudamos en estos meses a las notarías que hacemos eco de la invitación del gobernador Julio Menchaca de hacer acciones pro bono. Esto que significa en latín, el pro bono es hacer el bien pro bien. Y entonces una de estas acciones es manejar honorarios reducidos y, por ejemplo, tenemos los montos que hemos convenido desde el año 2022, adultos mayores de más de 60 años, un honorario reducido de 950 pesos mas IVA, y los menores de esa edad 2,500 pesos. Y algo importante, una una promoción especial dirigida a los elementos que forman parte de las fuerzas operativas de seguridad pública, de policía bancaria industrial, de policía de investigación, de mando coordinado, estos son los policías municipales que tienen mando coordinado con con Secretaría de Seguridad Pública, cuerpo de bomberos y paramédicos de Cruz Roja Mexicana, una promoción del del honorario reducido por 500 pesos mas IVA, y esta se extiende hasta el mes de diciembre, por aquí su segundo año consecutivo que tenemos esa campaña de invitación al público de esos servidores públicos, ¿no? Que nos que tanto nos ayuda. 
-Locutor Juan Carlos Santamaría:: Muy bien, notario, pues muchísimas gracias por esta información que nos deja claro que testamentar no nos implica una inversión mayor ni en tiempo ni en recursos y sí nos implica una tranquilidad hacia el futuro para nuestras familias. Muchas gracias, ¿algo que desea agregar? 
-Pedro Luis Noble Monterrubio: Es invitar al público a esa gran audiencia de NQ a que se acerquen con su notario, su notaria, y pues que tomen en cuenta que el testamento es un medio para disponer de los bienes, una vez ocurrido el fallecimiento de cada uno de nosotros. 
-Locutor Juan Carlos Santamaría: Bien, pues muchas gracias, Pedro Luis Noble Monterrubio, notario y presidente del Colegio de Notarios del Estado de Hidalgo, muy buen día. 
-Pedro Luis Noble Monterrubio: Estimado Juan Carlos, muchas gracias por la oportunidad y un saludo a esta gran sesión. 
-Locutor Juan Carlos Santamaría:: Muchas gracias. Hasta pronto. Buenos días.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1vo3lBKpxDyVIEzAGkR0ax2X5BDN69kug/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Secturh/Bol.168/2026</t>
-  </si>
-  <si>
-    <t>Hidalgo consolida su crecimiento turístico con más visitantes, inversión y promoción</t>
-  </si>
-  <si>
-    <t>Continuamos en Pachuca y bueno, en este calendario de comparecencias, tocó el turno también ya a la Secretaria de Turismo, y como parte de este ejercicio de rendición de cuentas ante el Congreso del Estado, la titular del ramo, Elizabeth Quintanar Gómez, presentó los principales resultados alcanzados durante la presente administración con una política turística que coloca al sector como una herramienta para generar desarrollo regional, fortalecer las economías locales y mejorar el bienestar de las familias hidalguenses. Durante su comparecencia, la titular de la Secretaría de Turismo destacó que Hidalgo vive una transformación en su actividad turística basada en sostenibilidad, innovación e inclusión comunitaria, con una visión que busca que los beneficios derivados de la llegada de visitantes alcancen a un mayor número de comunidades y prestadores de servicios. Entre los principales indicadores, informó que Hidalgo es referente nacional y ocupa el primer lugar en crecimiento de servicios turísticos, con un incremento de 20.9% respecto al primer año de la actual administración, y esto de acuerdo con cifras del Instituto Nacional de Estadística, Geografía e Informática, el INEGI. Además, informó que la entidad pasó de 4.8 millones de visitantes en 2022 a más de 6.5 millones en 2026, lo que representa un incremento de 36%. Durante este periodo, la actividad turística generó una derrama económica superior a los 14,000 millones de pesos, con una ocupación hotelera promedio anual de 53.8%. Resultado de ello, la recaudación del impuesto sobre hospedaje ha incrementado un 55.5% al pasar de poco más de 14 millones de pesos en 2022 a 22 millones de pesos en 2025, acumulando en estos 4 años más de 74 millones de pesos. El incremento en la cifra de personas que visitan el estado ha requerido importantes acciones y estrategias para que todas y todos disfruten su paso por la entidad. Es por ello que de septiembre de 2022 a septiembre de 2026 se ejercieron 51 millones de pesos en 18 obras de infraestructura turística, incluidos programas de señalización carretera. Entre las acciones realizadas destacan la rehabilitación de espacios turísticos en Mineral del Chico, la construcción del arco de bienvenida de Real del Monte, el andador turístico La Escondida en Villa de Tezontepec, los andadores del Centro Histórico de Calnali y la segunda etapa del Centro Gastronómico y Turístico de Santiago de Anaya, espacio destinado a brindar mejores condiciones a cocineras y cocineros tradicionales, preservar los alveres de la cocina hidalguense y consolidar al Valle del Mezquital como un referente del turismo gastronómico. Como parte de la estrategia estatal para ampliar las oportunidades de desarrollo, la Secretaría de Turismo impulsó el turismo comunitario como una vía para que las propias localidades participen en las decisiones sobre el aprovechamiento de su patrimonio natural y cultural, al tiempo que generan ingresos mediante sus tradiciones, sus artesanías, la gastronomía y sus conocimientos ancestrales. En este rubro, 25 experiencias de 21 municipios de Hidalgo fueron incorporadas a la Guía Nacional de Turismo Comunitario, generando oportunidades para más de 900 personas de distintas regiones de la entidad. Además, mediante las dos ediciones del Encuentro Estatal de Turismo Comunitario, Raíces de Hidalgo, se reunieron 60 experiencias y 91 expositores de 87 comunidades pertenecientes a 19 municipios, con la apertura también de canales de comercialización directa entre las comunidades y los operadores turísticos. La titular de la dependencia también resaltó el reconocimiento internacional de Omitlán de Juárez, distinguido con el sello Best Tourism Village, así como la visita de la Secretaría General de la ONU Turismo, Shaikha Nasser quien recorrió este municipio para reconocer su riqueza cultural y el trabajo desarrollado en materia de turismo comunitario. Y bien, es parte de lo que destacó en el contexto de su comparecencia la Secretaria de Turismo, Elizabeth Quintanar, quien también habló acerca del Festival Sabor a Hidalgo realizado en Zempoala con la presencia de 34 municipios reunidos ahí en Zempoala. La Secretaría de Turismo, la Secretaría de Turismo mantiene una estrategia permanente para posicionar la marca Hidalgo, tiene algo en México y el extranjero. Durante los 4 años de gobierno se realizaron 18 campañas de promoción turística con una inversión de 14 millones de pesos y, por supuesto, también destacó la participación de Hidalgo en la Feria Internacional de Turismo 2026 que tuvo lugar en Madrid, España. Otro resultado relevante fue la realización de la séptima edición del Tianguis Nacional de los Pueblos Mágicos en Pachuca durante noviembre de 2025; el encuentro reunió a los 177 Pueblos Mágicos del país, más de 3,000 prestadores de servicios turísticos y compradores nacionales e internacionales. Además, tenemos, por supuesto, en Hidalgo el primer pueblo mágico del país.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/16WyLuyuiYoKxlYwlr7aDHMbQes-wjIm7/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Congreso del Estado</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar</t>
-  </si>
-  <si>
-    <t>Shaikha Nasser</t>
-  </si>
-  <si>
-    <t>Locutor Juan Carlos Santamaría Y le comento que tocó ya el turno de su comparecencia a la Secretaria de Hacienda. Y bueno, en el marco de la glosa del cuarto informe del gobierno, la Secretaria de Hacienda, María Esther Ramírez Vargas, compareció ante la sexagésima sexta legislatura del Congreso del Estado para informar los resultados alcanzados en materia de fortalecimiento fiscal, inversión pública, transparencia financiera, financiera y saneamiento de la deuda heredada. Bajo el liderazgo del gobernador Julio Menchaca Salazar, Hidalgo se consolida como referente nacional en el manejo responsable de las finanzas públicas, destacó la funcionaria. Durante su exposición, puntualizó que los ingresos propios del Estado crecieron 96% en 4 años, al pasar de 4,916 millones de pesos en 2021 a más de 9,636 millones de pesos al cierre de 2025, esto sin aumentar tasas de los impuestos ya vigentes. Este resultado fue posible gracias a la modernización de los procesos tributarios, la ampliación de la base de contribuyentes y el fortalecimiento de los mecanismos de fiscalización. Asimismo, la participación de los ingresos propios dentro del total de ingresos estatales pasó de 9 a 13% en el mismo periodo, fortaleciendo la autonomía financiera de la entidad. La Secretaria de Hacienda informó que Hidalgo ocupó el primer lugar nacional en el crecimiento de los recursos vinculados al Fondo General de Participaciones durante el segundo trimestre de 2026, al registrar un incremento de 8% respecto al mismo periodo del año anterior. Asimismo, destacó que la entidad mantiene el primer lugar en el tablero global de eficiencia recaudatorio del Servicio de Administración Tributaria, el SAT, después de haber ocupado el lugar 26 al término de la administración anterior. Entre los resultados relevantes de la administración hacendaria, sobresale la generación de más de 3,650 millones de pesos en rendimientos financieros, producto de una gestión eficiente de disponibilidades y de la optimización de las condiciones bancarias para la inversión de recursos públicos, fortaleciendo la liquidez estatal sin recurrir al endeudamiento. Precisamente en materia de deuda pública, se destacó una reducción del 42% respecto al saldo heredado al inicio de la administración, mediante la liquidación anticipada de dos créditos y la liberación de más de 300 millones de pesos anuales que hoy se destinan a obra pública y programas sociales. Gracias a esta estrategia, Hidalgo se mantiene entre las cinco entidades con menor nivel de endeudamiento del país y es la única administración de los últimos 23 años que no ha contratado deuda de corto ni largo plazo ni ha solicitado adelantos de participaciones federales. En el contexto de su comparecencia, esto fue parte de lo que subrayó la Secretaria María Esther Ramírez Vargas. 
-María Esther Ramírez Vargas: Desde la Secretaría de Hacienda, continuamos generando las condiciones necesarias para impulsar más obras, acciones y proyectos orientados a elevar la calidad de vida de las familias hidalguenses. 
-Locutor Juan Carlos Santamaría: En esta comparecencia, también puntualizó que este desempeño ha sido reconocido, el desempeño financiero de Hidalgo ha sido reconocido por las agencias calificadoras Fitch Ratings, Moody's Global y HR Ratings, que ubican a Hidalgo en rango AA, consolidándolo entre las cuatro entidades federativas mejor evaluadas del país. Además, durante la comparecencia se destacó que en los últimos 26 años, Hidalgo no había alcanzado calificaciones crediticias tan altas, reflejo de la disciplina fiscal, el fortalecimiento de los ingresos propios, la liquidez financiera y la transparencia en el ejercicio de los recursos públicos. En la comparecencia también se destacó que entre 2022 y 2026, el presupuesto de egresos del Estado creció 37%, al pasar de 54,892 millones de pesos a 75,343 millones. Este fortalecimiento presupuestal permitió destinar más de 45,500 millones de pesos a 4,800 proyectos de infraestructura y programas sociales en beneficio de los 84 municipios de la entidad. Tan solo en 2026, se informó, se realiza una inversión histórica superior a los 4,600 millones de pesos para la ejecución de más de 232 obras con alcance en todos los municipios del estado, fortaleciendo la conectividad regional, la infraestructura hidráulica, la movilidad y el desarrollo equilibrado de las distintas regiones de Hidalgo. En el ámbito social, la inversión estatal registra un crecimiento histórico; para 2026 se destinan casi 5,000 millones de pesos a programas sociales y de bienestar, cifra que multiplica por cinco lo ejercido al final de la administración anterior. De estos recursos, más de 2,600 millones de pesos están dirigidos a la atención de personas migrantes, mujeres, niñas, niños y adolescentes, juventudes, personas adultas mayores, pueblos originarios, personas con discapacidad y población LGBTI+. Asimismo, Hidalgo alcanzó el primer lugar nacional en el índice de calidad de la información del Sistema de Recursos Federales Transferidos de la Secretaría de Hacienda y Crédito Público con un cumplimiento del 100% y mantiene por tercer año consecutivo el segundo lugar nacional en el índice de modernización catastral de la Sedatu. Estos resultados reflejan una administración comprometida con la transparencia, la rendición de cuentas y el uso eficiente de los recursos públicos, así lo puntualizó ante legisladores la Secretaria de Hacienda, María Esther Ramírez Vargas.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/11gAPXQbWJlebJUawIG7x-e2te-xdjX6i/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Comisión de Búqueda de Personas del Estado de Hidalgo localizó cinco cuerpos inhumados ilegalmente</t>
-  </si>
-  <si>
-    <t>La tarde de ayer, martes, personal de la Comisión de Búsqueda de Personas de Hidalgo y la y de la Procuraduría General de Justicia, realizaron una jornada de búsqueda de personas desaparecidas en un paraje del municipio de Atotonilco de Tula, donde se habría generado pues el hallazgo, el lamentable hallazgo de una fosa clandestina con cinco cadáveres ya en estado de descomposición. La noticia sobre este descubrimiento, obviamente este fue fue difundida y pues eh se comenzó a hacerse viral en la zona y pues bueno, en la mayoría, la mayoría de las personas solicitaban información detallada y aunque en principio se hablaba de dos cuerpos encontrados, los cuales indicaban que podrían corresponder a dos mujeres que fueron reportadas como desaparecidas, finalmente se confirmó que se trató de cinco cadáveres sin que hasta el momento se confirmen si son del sexo masculino o femenino. Fue esta madrugada, poco después de la de la 1:00 de la madrugada, cuando la comisión de búsqueda corroboró oficialmente la localización de esta fosa clandestina con cinco cuerpos que fueron inhumados ilegalmente. En el comunicado que se emitió, se destacó que la localización fue resultado de un operativo de búsqueda en conjunto con la Procuraduría General de Justicia del Estado. Asimismo, se reveló que luego del hallazgo el gobierno de Hidalgo pues expresó su compromiso para la identificación plena de las personas y la restitución inte- pues digna a sus familiares. El documento relata que los cuerpos de cinco personas fueron localizados en esta fosa clandestina, ubicada en la localidad de Texas, perteneciente al municipio de Atotonilco de Tula, ya casi en los límites con el Estado de México. Esto como resultado de los trabajos de búsqueda realizados de forma permanente por la Comisión de Búsqueda de Personas del Estado de Hidalgo y también se informó que el hallazgo derivó de las labores que realizan constantemente, incluso el titular señalaba que diario salen a distintos puntos a realizar búsquedas de personas. Estamos hablando de la Comisión de Búsqueda de Personas de Hidalgo y que el procesamiento del sitio pues corrió a cargo de la procuraduría y de esa manera se permitió recuperar los cinco cuerpos y también se refirió que hasta el momento las personas pues no han sido identificadas, pero se detalló que ya se realizan los trabajos correspondientes para lograr para lograr ello, que las víctimas sean identificadas y también pues se expresó la solidaridad con quienes buscan a una persona desaparecida. Así que bueno, pues toda toda una movilización, importante movimiento generó esta esta pues llamada, llamada fosa clandestina en allá en el municipio de Atotonilco de Tula.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Z9s0rObz1-zv3UrEWcU2Fhmce-FSL8WB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado, Gobierno de Hidalgo</t>
-  </si>
-  <si>
     <t>Iza</t>
   </si>
   <si>
@@ -847,293 +365,664 @@
     <t>Enfoque Regional Meridiano</t>
   </si>
   <si>
-    <t>Ha dado mucho de qué hablar el tema de la muerte del réferi allá en Mineral de la Reforma, incluso hoy hubo una conferencia de prensa; hoy se confirma que el traumatismo craneoencefálico fue la causa de muerte de Gerardo Germán Pineda, conocido en el ámbito de la lucha libre como «El Búho», quien falleció tras recibir un martinete durante una función en Mineral de la Reforma; el Hijo de Fishman fue el que le practicó esta llave.</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Ha dado mucho de qué hablar el tema de la muerte del réferi allá en Mineral de la Reforma, incluso hoy hubo una conferencia de prensa; hoy se confirma que el traumatismo craneoencefálico fue la causa de muerte de Gerardo Germán Pineda, conocido en el ámbito de la lucha libre como «El Búho», quien falleció tras recibir un martinete durante una función en Mineral de la Reforma; el Hijo de Fishman fue el que le practicó esta llave. De acuerdo con los resultados de la autopsia, el impacto contra la lona desencadenó un edema cerebral y una hemorragia, lesiones que derivaron en la muerte del réferi.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1cPdVn7XPTSLxrVh5kxGAqx-iyFah7yrt/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>En el municipio de Atotonilco de Tula. A través de un comunicado oficial emitido hoy, 14 de octubre, la Comisión de Búsqueda de Personas del Estado de Hidalgo informó sobre la localización de cinco cuerpos inhumados, enterrados de manera ilegal, en la localidad de Tejas, perteneciente al municipio de Atotonilco de Tula, en los límites con el Estado de México.</t>
-  </si>
-  <si>
-    <t>Vamos a la información que sucede en el municipio de Atotonilco de Tula. A través de un comunicado oficial emitido hoy, 14 de octubre, la Comisión de Búsqueda de Personas del Estado de Hidalgo informó sobre la localización de cinco cuerpos inhumados, enterrados, de manera ilegal en la localidad de Texas, perteneciente al municipio de Atotonilco de Tula, en los límites con el Estado de México. El hallazgo fue resultado de operativos de búsqueda permanentes coordinados por la Comisión en conjunto con la Procuraduría de Hidalgo, institución que estuvo a cargo del procesamiento del sitio y la recuperación de los restos. El gobierno de Hidalgo expresó su solidaridad con las familias que buscan a sus seres queridos y reafirmó el compromiso de llevar a cabo los trabajos necesarios para lograr la identificación plena de los cuerpos con apego a la dignidad humana, manteniendo comunicación directa con colectivos y organizaciones de búsqueda.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YYOaPNA4wNr1vT90hmVBp46DQpG05VFK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>GOBIERNO</t>
-  </si>
-  <si>
     <t>Vía telefónica notario Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios del Estado de Hidalgo con el tema: Octubre, igual que septiembre, mes del testamento.</t>
   </si>
   <si>
-    <t>Por ello, me da mucho gusto saludar en la vía telefónica al licenciado Pedro Luis Noble Monterrubio, él es presidente del Colegio de Notarios del Estado de Hidalgo. ¿Cómo está, licenciado Pedro Luis? Buena tarde. Muy bien, con el gusto de escucharles y saludar a su gran auditorio aquí en Supercero 100.5. Gracias, licenciado. Preguntarle sobre qué octubre es el mes del testamento, al igual que en septiembre, este tema tan importante, el testamento. Platícanos de ello, por favor. Con todo gusto Jesús, muchas gracias Platicarles que para Hidalgo Al igual que septiembre, octubre es el mes del testamento Y que de acuerdo con Atención a la invitación que nos hizo el gobernador Julio Menchaca De participar activamente Él menciona la acción pro bono Una acción pro bono es una acción para el bien Por bien Y bueno, pues por supuesto estamos en ese entendido de ayudar con la ciudadanía para mitigar riesgos cuando una persona fallece evitar conflictos sucesorios y mira si ahorita el público nos hace favor de de recordar en su mente algún concepto de alguna familia algún conocido que tenga un problema sucesorio pues vamos a ver de qué se trata el problema es otorgando testamento un testamento que se otorga nos permite disponer de los bienes para después de la muerte que uno llegue a experimentar y bueno pues entonces la invitación es al punto general de que se acerque con su notario su notaria más próxima de su domicilio de la notaria cabecera de confianza para que platiquen con él le den a conocer sus intenciones su voluntad para también fortalecer la cultura no solamente de la legalidad sino también de la planeación patrimonial que es tan importante y evitar conflictos a futuro es la indicación, el testamento recordemos don Jesús es un instrumento por el cual se definan a los herederos a quienes van a sucedernos en la propiedad de los bienes sea vía herencia o vía legado, la herencia comprende los bienes inmuebles y los bienes todo el latino y se maneja por por masa patrimonial lo que exista se va a repartir entre tantas personas o en una sola en estos porcentajes y ah se dice cu son y otra figura es el legado el legado espec el legado particular donde a cada persona se le dice qué terreno, qué departamento, qué casa qué tienda, qué bodega, qué trailer lo que se quiera disponer de los bienes Licenciado, ¿qué ventajas se tienen en este momento con esta oferta o con esta promoción o con este trabajo que ustedes están haciendo de poder llevar a cabo este trámite en el mes de octubre? ¿Qué ventaja tiene la ciudadanía? Sobre todo que tiene la posibilidad de establecer esa voluntad en un documento público en mi escritura que se llama Testamento para que todas las autoridades, para que todas las personas, la dependencia incluso, se entonga, se entere de cuál fue la voluntad del testador. Porque cuando una persona fallece sin hacer testamento, entonces abre la sucesión intertestamentaria llamada también legítima, porque los que tengan legítimo interés pueden concurrir todos a pedir la herencia. ¿Quiénes son los que tienen legítimo interés? Los parientes más cercanos. ¿Quiénes son los más cercanos? Obviamente los hijos. En línea descendente. Entonces la línea sube hacia los descendentes, los padres. No hay hijos, no hay papás, están los hermanos, si no están los sobrinos si no están los primos, ¿sí me explico? Sí, claro cuando en el testamento decimos quien sí exclusivamente quien sí la palabra exclusivamente excluye a los que no se hayan mencionado por supuesto, ¿no? eso es lo importante, evitar un conflicto a futuro la cultura de la legalidad también comprende evitar conflictos a futuro evitar pleitos y de esa manera, pues también de una u otra manera, se contribuye, contribuimos todos a que los tribunales, los juzgados, pues tengan el menor número de asuntos de litigio por falta de testamento, que es lo más importante. ¿En cuestión económica hay algún descuento, hay alguna facilidad para que la gente pueda hacer ese trámite, licenciado? Bueno, Jesús, efectivamente, qué buena pregunta. también es acción pro bono que nos ha invitado el señor gobernador es establecer honorarios reducidos personas que tenemos más de 60 años el honorario es de 950 pesos masiva personas de menos de 60 años 2500 pesos masiva y hay una promoci especial de atenci de orientaci de solidaridad social de atenci espec a los servidores que forman parte del cuerpo operativo de Secretaría de Seguridad Pública, de mando coordinado, estas son las policías municipales que están con la Seguridad Pública total, Policía Bancaria Industrial, con la Policía de Investigación, de Procuraduría con el cuerpo de bomberos y con paramédicos de Cruz Roja Mexiana. Y para ellos hay un honorario reducido de 500 pesos por semana. Realmente es algo simbólico y que sobre todo ayuda a la creación patrimonial de la familia. Esto es parte importante, licenciado, porque hemos visto que el Colegio de Notarios del Estado de Hidalgo está trabajando mucho de la mano del gobernador Julio Menchaca. Inclusive los hemos visto en las rutas de la transformación. hay buena relación, hay buen trabajo en beneficio de la gente, licenciado Mire, hacemos eco a la indicación del señor gobernador y bueno, pues nos sumamos a no solamente este programa a los que han actuado en BIF en materia de atención a la edad mayor en voluntad y paga para atención a igual, a quienes de una u otra manera tienen alguna algún pendiente, algún trámite alguna expectativa de riesgo por salud para que dispongan de esa voluntad. Para eso, yo no tengo nada más que decir, decidir en un acta notarial que la persona cuando se encuentra frente a una situación clínica que esté diagnosticada con menos de seis meses de vida, pues la persona decida no continuar con los tratamientos de obstinación médica. Ok. Es que no se sacrifica el patrimonio si hay un distante médico que dice hay expectativa de poca probabilidad de su prevencia bueno, se establece en un documento que se llama de voluntad citada la persona dispone a alguien de su confianza a su pareja, a su hermano a alguien de confianza que se respete esa voluntad y esa voluntad se hace en institucia pública igual y el notario le da aviso a la Secretaría de Salud a la Secretaría de Salud perdón, Secretaría de Salud a la Secretaría de Salud la Secretaría de Salud lleva el control nacional también de estos actos de voluntad insupada, de tal manera que una persona médico, tratante de cualquier hospital p o privado puede consultar a la Secretar de Salud y a la Secretar de Salud tal persona si es orgullosa de estar vean el documento de qu se trata y respeten su voluntad Excelente. Pues licenciado Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios del Estado de Hidalgo, invitar a la gente a que vaya a hacer su testamento, porque octubre, al igual que en septiembre, es el mes del testamento y es importante que la gente deje en orden todos sus documentos, licenciado. Es plenación patrimonial, es una cuestión de orden, Ahora, no es definitivo. El testamento tiene tres características importantes. Es personalísimo, es decir, solamente la persona interesada es quien lo va a dictar. El notario tiene que ver con quien subsine en su sala, nada más que es la persona interesada. Porque tiene que estar en plena libertad, porque el testamento es un acto libre. y además tiene formalidades pero además es revocar lo puede cambiar como en el momento y los términos que mejor le convengan o le acomoden al Cesaro con formación de SEO libre de SEO en el país o fuera de él, con un consul mexicano se puede revocar el con el propio notario o con otro notario pues estaremos muy al pendiente para ver cómo va esta campaña licenciado Dejen así que vemos que año con año se motiva más la ciudadanía eso lo vemos muy bien por parte de la de la cultura del testamento y rompemos un tabú, siempre pensábamos yo mismo cuando era muy joven pensábamos que el testamento era ya para los que estaban próximos a un deceso, no, no es cierto la ley permite que desde los 16 años y hoy con agrado vemos como jóvenes empresarios profesionistas jóvenes, adultos jóvenes algo de 30 y tantos y de 40 y tantos años ya tienen pensamiento cerrado, ¿por qué? porque se preocupan por tener un centro y aquí hago un paréntesis a través de este pensamiento también un hijo puede dejar un legado de alimentos para los papás con un joven empresario que tiene hijos pequeños también puede dejar instituido un legado de alimentos para los menores hijos licenciado, sin lugar a dudas hay muchos temas que platicar por parte del colegio de notarios tendremos una segunda oportunidad para seguir platicando yo le agradezco mucho por esta llamada y estamos al pendiente, gracias un abrazo gracias, él es Pedro Luis Noble Monterrubio presidente del colegio de notarios del estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rnV7JqmMkJzYQ8rrZRfTSJHTsUjuvXxY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>PGJEH , SSPH, SSH</t>
-  </si>
-  <si>
-    <t>Como parte del ejercicio de rendición de cuentas ante el Congreso del estado de Hidalgo, la secretaria de Turismo del Estado de Hidalgo, Elizabeth Quintanar Gómez, presentó los principales resultados alcanzados durante la presente administración, con una política turística ecabezada por el gobernador Julio Menchaca Salazar, que coloca al sector como una herramienta para generar desarrollo regional, fortalecer las economías locales y mejorar el bienestar de las familias hidalguenses.</t>
-  </si>
-  <si>
-    <t>Como parte del ejercicio de rendición de cuentas ante el Congreso del estado de Hidalgo, la secretaria de Turismo del Estado de Hidalgo, Elizabeth Quintanar Gómez, presentó los principales resultados alcanzados durante la presente administración, con una política turística ecabezada por el gobernador Julio Menchaca Salazar, que coloca al sector como una herramienta para generar desarrollo regional, fortalecer las economías locales y mejorar el bienestar de las familias hidalguenses.
-Durante su comparecencia, la titular de la Secretaría de Turismo destacó que Hidalgo vive una transformación en su actividad turística, basada en sostenibilidad, innovación e inclusión comunitaria, con una visión que busca que los beneficios derivados de la llegada de visitantes alcancen a un mayor número de comunidades y prestadores de servicios.
-Entre los principales indicadores, informó que Hidalgo es referente nacional y ocupa el primer lugar en crecimiento de servicios turísticos, con un incremento del 20.9% respecto al primer año de esta administración, de acuerdo a cifras del Instituto Nacional de Estadística, Geografía e Información (INEGI). 
-Además, informó que la entidad pasó de 4.8 millones de visitantes en 2022 a más de 6.5 millones en 2026, lo que representa un incremento de 36 por ciento. Durante este periodo, la actividad turística generó una derrama económica superior a los 14 mil millones de pesos, con una ocupación hotelera promedio anual de 53.8%.Resultado de ello la recaudación del Impuesto sobre Hospedaje ha incrementado un 55.5%, al pasar de poco más de 14 millones de pesos en 2022 a 22 millones en 2025, acumulando en estos cuatro años más de 74 millones de pesos. 
-El incremento en la cifra de personas que visitan el estado, ha requerido importantes acciones y estrategias para que, todas y todos disfruten su paso por la entidad, es por ello que, de septiembre de 2022 a septiembre de 2026 se ejercieron 51 millones de pesos en 18 obras de infraestructura turística, incluidos programas de señalización carretera.Entre las acciones realizadas destacan la rehabilitación de espacios turísticos en Mineral del Chico, la construcción del Arco de Bienvenida de Real del Monte, el Andador Turístico La Escondida en Villa de Tezontepec, los andadores del Centro Histórico de Calnali y la segunda etapa del Centro Gastronómico y Turístico de Santiago de Anaya, espacio destinado a brindar mejores condiciones a cocineras y cocineros tradicionales, preservar los saberes de la cocina hidalguense y consolidar al Valle del Mezquital como un referente del turismo gastronómico.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1f57QTR0bf9G0sW-NQs7kmPhBC4O7AC3C/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SSPH/Bol.983/2026</t>
-  </si>
-  <si>
-    <t>Una mujer de 40 años fue liberada y su expareja detenida durante un operativo de la policía estatal en Tulancingo. Según el reporte, la víctima fue amagada con una escopeta cuando dejaba a su hijo en la escuela en la colonia La Cañada y trasladada a un inmueble del barrio Otontepec. Al llegar los policías, el hombre presuntamente disparó contra ellos.La mujer fue puesta a salvo y el detenido, identificado con las iniciales S. R. P., de 43 años, quedó a disposición de las autoridades. En el operativo aseguraron una escopeta y dos rifles. Un policía resultó lesionado en una mano y una patrulla recibió un impacto de bala.</t>
-  </si>
-  <si>
-    <t>Rescate secuestro</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1j4ZtLHapf8maPbwAS39GYJdZ5mamBzrW/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Personal de salud y estudiantes de medicina recibieron capacitación en desarrollo infantil temprano, durante un curso-taller realizado en Tizayuca. La actividad fue encabezada por la secretaria de Salud de Hidalgo, Vanessa Escalante Arroyo, y estuvo dirigida a alumnos del Instituto Educativo y Cultural de Hidalgo. Fundación Televisa impartió la jornada enfocada en fortalecer la atención integral de niñas y niños desde sus primeros años.</t>
-  </si>
-  <si>
-    <t>Personal de salud y estudiantes de medicina recibieron capacitación en desarrollo infantil temprano, durante un curso-taller realizado en Tizayuca. La actividad fue encabezada por la secretaria de Salud de Hidalgo, Vanessa Escalante Arroyo, y estuvo dirigida a alumnos del Instituto Educativo y Cultural de Hidalgo. Fundación Televisa impartió la jornada enfocada en fortalecer la atención integral de niñas y niños desde sus primeros años.La capacitación destacó que consultas médicas, vacunación y visitas domiciliarias son oportunidades para orientar a las familias e identificar necesidades que favorezcan el desarrollo infantil. Quiero agradecerle a Fundación Televisa y a Hidalgo por el apoyo, por compartirnos estas herramientas, a todos quienes están aquí por esta capacitación y sobre todo por su magnitud de ayuda. Vemos nosotros en la Secretaría de Salud, en el servicio nacional que depende también de la Secretaría de Salud, un aliado y un compañero para seguir advancing por las causas físicas. Preocupados por la profesionalización de su gente y por algo que no se había dado antes, por darle la misma oportunidad a todas y a todos de estudiar sin importar de dónde vengamos. Hoy estamos trabajando para fortalecer los servicios de salud de Hidalgo. La capacitación es clave. Aprovechen a todas y a todos. Especialmente cuando se trata de acompañar a niñas y niños desde sus primeros años de vida.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1baKQVWaygXSSK5p9wuONs7ICHIJrvHe2/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Movilidad, infraestructura, servicios y crecimiento urbano, fueron algunos de los temas analizados por habitantes y autoridades de Ajacuba, Tetepango y Tlaxcoapan, durante un taller para elaborar el programa regional de desarrollo urbano y ordenamiento territorial de Tula.</t>
-  </si>
-  <si>
-    <t>Tula Tepeji</t>
-  </si>
-  <si>
-    <t>Movilidad, infraestructura, servicios y crecimiento urbano, fueron algunos de los temas analizados por habitantes y autoridades de Ajacuba, Tetepango y Tlaxcoapan, durante un taller para elaborar el programa regional de desarrollo urbano y ordenamiento territorial de Tula. La actividad fue organizada por la Unidad de Planeación y Prospectiva de Hidalgo, como parte de los trabajos para conocer las necesidades de la región y definir prioridades.La información recabada servirá para orientar decisiones sobre obras, movilidad, desarrollo económico y uso del territorio, así como para identificar asuntos que requieren coordinación entre municipios y el gobierno estatal. En el encuentro participaron las alcaldesas de Tlaxcoapan y Ajacuba, además del presidente municipal de Tetepango. Son ya las siete de la mañana con veintiocho minutos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bhEP2upUgZPiHqkxnMPvyAMT7xxOsa6s/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Unidad de Policía Cibernética alerta a compradores de bienes y servicios por Internet, para que no caigan en una nueva modalidad de fraude, que consiste en la comercialización ficticia de productos y servicios a través de Internet. Esto mediante ofertas engañosas, cuyo objetivo es obtener dinero o información personal de las víctimas sin entregar lo prometido.</t>
-  </si>
-  <si>
-    <t>UPC</t>
-  </si>
-  <si>
-    <t>Ciberseguridad</t>
-  </si>
-  <si>
-    <t>La Unidad de Policía Cibernética alerta a compradores de bienes y servicios por Internet, para que no caigan en una nueva modalidad de fraude, que consiste en la comercialización ficticia de productos y servicios a través de Internet. Esto mediante ofertas engañosas, cuyo objetivo es obtener dinero o información personal de las víctimas sin entregar lo prometido. La dependencia señala que los ciberdelincuentes utilizan las redes sociales, sitios web, grupos de compra-venta y aplicaciones de mensajería para difundir anuncios falsos y engañar a posibles compradores. La Policía Cibernética explica en un comunicado que los responsables utilizan fotografías atractivas, descripciones detalladas y perfiles que aparentan ser legítimos. El objetivo es generar confianza, y una vez que la persona muestra interés en la oferta, el supuesto vendedor solicita depósitos, anticipos o transferencias para apartar el producto, cubrir gastos de envío o confirmar la compra. Asegúrese de que la plataforma sea segura y no vaya a caer en una estafa. Siete de la mañana ya con 23 minutos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1XTUcKu_OpKYO29wIw1K9DipyaDw6v4pn/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Un grupo de personas se concentraron frente al Congreso del Estado, allá en Pachuca, para exigir la liberación de Macario y Lorenzo, habitantes de Julián Villagrán, Ixmiquilpan, a quienes consideran presos políticos. Los inconformes denunciaron presuntas irregularidades en el proceso relacionado con un conflicto agrario entre Julián Villagrán y Pueblo Nuevo. Aseguran que hay pruebas para desvirtuar las acusaciones y piden que ambos enfrenten su proceso en libertad.Estamos aquí, que ya resuelva este problema, dos años. Justamente la ley dice que ninguna persona debe estar detenida injustamente. Justamente dice la ley que ninguna persona debe estar detenida si no hay pruebas en su contra, si no hay pruebas para que esté detenido, debe ser liberado. La ley lo está marcando. Es una ley que desgraciadamente viola, viola hasta los derechos humanos, viola las garantías.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1r2Lo3NHFFKQ2TdUv9U3bqCM8HTn48bQ7/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La entidad pasó de cuatro punto nueve millones de visitantes en dos mil veintidós a más de seis punto cinco millones en lo que va de este dos mil veintiséis, con una derrama económica superior a los catorce mil millones de pesos y una ocupación hotelera promedio anual del cincuenta y tres punto nueve por ciento.</t>
-  </si>
-  <si>
-    <t>La entidad pasó de cuatro punto nueve millones de visitantes en dos mil veintidós a más de seis punto cinco millones en lo que va de este dos mil veintiséis, con una derrama económica superior a los catorce mil millones de pesos y una ocupación hotelera promedio anual del cincuenta y tres punto nueve por ciento. Esto lo destacó la secretaria de Turismo, Liz Quintanar.Hidalgo es referente nacional y ocupa el primer lugar en crecimiento de servicios turísticos, con un incremento del veinte punto nueve por ciento respecto al primer año de esta administración. Detrás de este indicador hay algo aún más importante, la confianza de quienes deciden invertir, emprender y apostar por el turismo en Hidalgo. Es decir, ahora más personas aprovechan la vocación turística de sus comunidades y valoran su patrimonio natural y cultural para convertirlo en una oportunidad de generar ingresos. Los resultados del trabajo realizado se reflejan en la llegada de visitantes. Pasamos de cuatro punto ocho millones en el dos mil veintidós a más de seis punto cinco millones de personas entre visitantes y turistas en lo que va del dos mil veintiséis. Un incremento del treinta y seis por ciento en estos cuatro años. En este periodo, la actividad turística ha generado una derrama económica superior a los catorce mil millones de pesos, con una ocupación hotelera promedio del cincuenta y tres punto ocho por ciento anual.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Mk0nBTkimWuQQqdz9JLoovsvGoOssJf-/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>EPH/Bol.1926/2026</t>
-  </si>
-  <si>
-    <t>Hidalgo obtuvo una medalla de plata, una de bronce y dos menciones honoríficas en la Olimpiada Mexicana de Informática en su edición para primaria y secundaria dos mil veintiséis, competencias de las que fue sede nacional y en las que participaron veinticinco delegaciones.Juan José Pérez Domínguez, de la preparatoria Alberto Zoebisch, ganó plata en bachillerato, mientras que Iker Daniel Pérez Domínguez, del centro educativo Calmécac, obtuvo bronce en secundaria. José Alberto Lorenzana Cortés, de Tulancingo, y Maxel Uziel Quijano Sánchez, de Tezontepec de Aldama, recibieron menciones honoríficas. Los estudiantes tuvieron ocho meses de capacitación en programación, algoritmos y resolución de problemas. Bueno, pues muchas felicidades. Son ya las siete con veintisiete minutos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1abB_zPhsgrS2tlQrCNvxbhTA1zxRT_qO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La secretaria de Cultura de Hidalgo, Neyda Naranjo Baltazar, compareció ante el Congreso del Estado como parte de la glosa del informe de actividades del gobernador Julio Menchaca Salazar, donde fue cuestionada sobre la tauromaquia, al señalar que la fiesta brava forma parte de expresiones históricas, literarias y comunitarias de México y de Hidalgo. En ese sentido, manifestó su postura a favor de los espectáculos sin sangre.</t>
-  </si>
-  <si>
-    <t>La secretaria de Cultura de Hidalgo, Neyda Naranjo Baltazar, compareció ante el Congreso del Estado como parte de la glosa del informe de actividades del gobernador Julio Menchaca Salazar, donde fue cuestionada sobre la tauromaquia, al señalar que la fiesta brava forma parte de expresiones históricas, literarias y comunitarias de México y de Hidalgo. En ese sentido, manifestó su postura a favor de los espectáculos sin sangre.Desde la Secretaría de Cultura estamos a favor de los espectáculos sin sangre, reconocemos como manifestación cultural porque finalmente eso es lo que representa, sin embargo, se ha enviado ya la contestación a esta soberanía y en espera de la propuesta que se había decidido, que es la consulta ciudadana para el seis de junio del dos mil veintisiete. Sin embargo, nos reiteramos a las órdenes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1W-SB-TvKsBUp8qTWOnhf-l2rSmmTZ0g3/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Neyda Naranjo</t>
   </si>
   <si>
-    <t>Ayer le platicábamos de esta información que le vamos a compartir de que ya iniciaron las campañas de vacunación en la región de Tula-Tepeji contra influenza, COVID-19 y virus del papiloma humano para prevenir enfermedades y complicaciones. Aquí está la información completa con nuestra compañera Claudia Alcántara.La vacunación por COVID-19 e influenza en la zona Tula-Tepeji comenzó con poca afluencia. Sin embargo, los ciudadanos que están asistiendo a inmunizarse a centros de salud nos señalaron que el propósito es prevenir un cuadro grave en caso de llegar a contagiarse de esos virus, además de inhibir la propagación de forma descontrolada como ocurrió en el dos mil veinte y dos mil veintiuno</t>
-  </si>
-  <si>
-    <t>- Ayer le platicábamos de esta información que le vamos a compartir de que ya iniciaron las campañas de vacunación en la región de Tula-Tepeji contra influenza, COVID-19 y virus del papiloma humano para prevenir enfermedades y complicaciones. Aquí está la información completa con nuestra compañera Claudia Alcántara.La vacunación por COVID-19 e influenza en la zona Tula-Tepeji comenzó con poca afluencia. Sin embargo, los ciudadanos que están asistiendo a inmunizarse a centros de salud nos señalaron que el propósito es prevenir un cuadro grave en caso de llegar a contagiarse de esos virus, además de inhibir la propagación de forma descontrolada como ocurrió en el dos mil veinte y dos mil veintiuno. Es bueno para que estén sanos y para prevenir las enfermedades que vengan. Sí, pues sobre todo empieza en esta época que empiezan los fríos y tiende la gente a enfermarse un poquito y es cuando empiezan estas campañas en lo personal. Sí, cada año me estoy vacunando también para cuidar a todos e invitar a que la gente no se raje y que vayan y que les pongan su vacuna. Es una responsabilidad de todos y es muy importante para que evitemos cualquier enfermedad. En estas fechas, ahorita que viene la temporada de frío y todo eso, pues para que no nos enfermemos. Expertos en salud y personal médico recomiendan la aplicación de vacunas ante la temporada invernal, en especial en grupos vulnerables como adultos mayores, infancias, embarazadas y personas con alguna comorbilidad. Mayores de sesenta años, embarazadas, niño menor de cinco años y pacientes con alguna comorbilidad como diabetes, obesidad, asma, problemas de corazón. Personal de salud, sí, todos tenemos que estar vacunados porque así nosotros brindamos salud a la población, entonces tenemos que inmunizarnos antes que la población. También llaman a que se mantengan medidas de higiene y uso de cubrebocas en espacios cerrados o aglomeraciones. Para Enfoque Regional informó, Claudia Alcántara.Son ya las siete de la mañana con once minutos y como dice el señor, no se raje, hay que vacunarse y hay que llevar, por supuesto, a niñas y niños y adultos mayores.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1GBs66NHaiAC8Vgodd1dHw6TsmvO2WYMc/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El secretario de gobierno de Hidalgo, Guillermo Olivares Reyna, informó que siete municipios de la entidad aún no cuentan con su atlas de riesgo. Mientras que otros 17 se encuentran en proceso de gestión para obtenerlo y 60 ya disponen de este documento fundamental para identificar las zonas vulnerables ante fenómenos naturales y otras emergencias.Y de los municipios hablábamos de que hay 17 municipios que no obstante les damos respaldo económico hasta un 40% del costo de estas herramientas pues están en estos momentos un año porque al final de cuentas suelten con el instrumento.</t>
-  </si>
-  <si>
-    <t>Atlas de Riesgos</t>
-  </si>
-  <si>
-    <t>El secretario de gobierno de Hidalgo, Guillermo Olivares Reyna, informó que siete municipios de la entidad aún no cuentan con su atlas de riesgo. Mientras que otros 17 se encuentran en proceso de gestión para obtenerlo y 60 ya disponen de este documento fundamental para identificar las zonas vulnerables ante fenómenos naturales y otras emergencias.Y de los municipios hablábamos de que hay 17 municipios que no obstante les damos respaldo económico hasta un 40% del costo de estas herramientas pues están en estos momentos un año porque al final de cuentas suelten con el instrumento. Los municipios económicamente no pueden condenarlos a estar castigados si tienen muchas funciones que hacer. Pero esto, les hemos dicho, es vital, es fundamental para la seguridad de todos los habitantes de su demarcación. Y bueno, pues no está por demás decir, si me permiten recorrer, qué municipios están en estos momentos tratando de contar con el instrumento. Cárdenas, Pacula, Francisco I. Madero, Pisaflores, Tlahuiltepa, San Salvador, Tasquillo, Tecozautla, Yahualica... El resto, o cuentan con su atlas de riesgo municipal o están actualizados. Esto se está cuidando porque pueden tener la realidad con el documento.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1NNhBTnNcq6CU8IIzCFaRbWG5NneB_uXc/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La secretaria de Hacienda de Hidalgo, María Esther Ramírez Vargas, informó ante el Congreso local que los ingresos propios del Estado crecieron 96% entre 2021 y 2025, sin aumentar las tasas de impuestos vigentes</t>
-  </si>
-  <si>
-    <t>La secretaria de Hacienda de Hidalgo, María Esther Ramírez Vargas, informó ante el Congreso local que los ingresos propios del Estado crecieron 96% entre 2021 y 2025, sin aumentar las tasas de impuestos vigentes. Durante la glosa del cuarto informe de gobierno, señaló que la deuda pública se redujo 42% respecto al saldo heredado y que la entidad no ha contratado nuevos créditos ni solicitado adelantos de participaciones. También destacó que el desempeño fiscal ha colocado en los primeros lugares al Estado de Hidalgo.Por primera vez, el Servicio de Administración Tributaria, SAT, otorgó a Hidalgo en el ejercicio 2025 y nuevamente en agosto de 2026 la más alta calificación en desempeño fiscal, posicionando a Hidalgo en el primer lugar del tablero global de eficiencia recaudatoria, después de haber ocupado el lugar número 26 al cierre de la administración anterior. Este avance refleja la eficacia recaudatoria, la eficiencia operativa y el cumplimiento normativo que consolidan a Hidalgo como un referente nacional en materia de auditoría fiscal.La funcionaria agregó del programa Circula Seguro, donde se ha recaudado más de 670 millones de pesos.El programa Circula Seguro 2026 permitió fortalecer recaudación estatal y destinar el 100% de los recursos obtenidos a infraestructura pública en los ochenta y cuatro municipios. En los primeros meses del ejercicio 2026 se recaudaron 673 millones de pesos y se regularizaron 405 mil 241 vehículos. De igual forma y como un hecho sin precedentes en la vida institucional del estado mantuvimos por segundo año consecutivo el impuesto sobre nómina participable. Esta acción permite devolver directamente a los municipios lo que efectivamente declararon y pagaron por este concepto.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1qk_uJWMRNU4e59I-Qe5fZZIBQ3Nud4xv/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Panorama Informativo</t>
-  </si>
-  <si>
-    <t>Radioescucha Solo para comentarle: el tráfico para la México a la altura del puente de Venta Prieta está tremendo y avanzando por una obra que ya lleva 45 días. Pues a ver cuándo lo abren ya, sí está complicado todo ese tráfico en esa zona.</t>
-  </si>
-  <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
-    <t>Radioescucha  Solo para comentarle: el tráfico para la México a la altura del puente de Venta Prieta está tremendo y avanzando por una obra que ya lleva 45 días. Pues a ver cuándo lo abren ya, sí está complicado todo ese tráfico en esa zona.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HZ-wuloGgJPhFyur1ZG7iENqaQC2mweZ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Radioescucha 9313. Señor Fidel, Licenciado, pues reportándome. Aquí en Ampliación Santa Julia, segunda sección, no cae agua. Más de una semana en la calle 18. Urgente, licenciado, por favor, nos encontramos sin agua</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bIZPJxpQnviTFRAqS9cdLZN4J45Ryptx/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Vía telefónica notario Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios del Estado de Hidalgo con el tema: Octubre, igual que septiembre, mes del testamento. Anunció que la campaña del Mes del Testamento se extenderá durante septiembre y octubre,</t>
-  </si>
-  <si>
-    <t>vamos a platicar con Pedro Luis Noble, presidente del Colegio de Notarios del Estado de Hidalgo, y el tema Mes del Testamento. Seguimos con septiembre Mes del Testamento en octubre, ¡qué importante es todo ello! Y lo mejor de tod... de toda esta situación, hay precios especiales para los adultos mayores, o sea, como para mí, y también para elementos de la Secretaría de Seguridad Pública. Entonces, creo que es muy importante platicarlo todo esto. ¿Cómo estás, mi estimado Pedro Luis Noble, en esta mañana de Panorama? Te dejo los micro... los micrófonos para que platiques al respecto, por favor.   Pedro Luis Noble: Muchas gracias, estimado Lalo. Agradezco... agradezco a este espacio de comunicación, a esa gran organización de radio y, bueno, pues decirles que septiembre y octubre son meses del testamento. Y... y así lo hemos hecho, así lo hemos acordado con el gobernador Menchaca, y también hemos hecho eco a su invitación de hacer acciones pro bono. ¿Qué significa acción pro bono? Hacer acciones para el bien, pro bono, pro bien.   Y una de esas es precisamente la de reducir honorarios notariales muy... muy... muy cómodos, y tenemos ahí un ejemplo: para el adulto mayor, el costo de honorario reducido es de 950 pesos más... más IVA. ¿Quiénes son? Las personas que tenemos más de 60 años. Para los más jóvenes, que tienen menos de esa edad, 2,500 pesos más... más IVA. Y para las fuerzas operativas de seguridad pública de Mando Coordinado, esto es las policías municipales que están coordinadas con... con Seguridad Pública estatal, la Policía de Investigación de Procuraduría, la Policía Bancaria Industrial, el cuerpo de bomberos y los médicos paramédicos de Cruz Roja Mexicana, tienen un... un honorario reducido de 500 pesos por otorgar testamento más el IVA, y esa promoción de para policías, para fuerza operativa, se prolonga hasta el mes de diciembre.   Entonces, pues aprovechar tus... tus micrófonos, estimado Lalo, para invitar a la ciudadanía a que se acerque con su notaría más próxima a su domicilio, con su notario de confianza, el notario de cabecera, de la familia, platicar con él una entrevista donde le digamos nuestro interés, nuestra intención para que los bienes que hemos podido formar o acumular a lo largo de años de trabajo, pues digamos a quién... a quién se los queremos heredar, a quién queremos establecer esa transmisión de patrimonio, esa transmisión de... de... de nuestros activos y, pues de esa manera, legar paz, tranquilidad, orden y, sobre todo, dejar establecido en el documento la voluntad libre y bien deliberada del... del testador, de la persona que desea disponer de sus bienes para después de la muerte.   Eulalio «Lalo» Larrieta: Esto es muy importante tenerlo. Y si algún... ¡algún notario se niega a hacer esto, ¿qué se hace? ¿Nos vamos a otro notario o qué hacemos? No lo sé, desconozco.   Pedro Luis Noble: Qué buena pregunta. Para empezar, mira, ningún notario puede negarse a dar servicio, ni para testamento, ni para compraventa, ni para donaciones, ni para constitución de sociedades, ni para una fe... de hecho, es a ver, hay un principio que se llama principio de rogación: el notario no puede negarse a dar el servicio a menos que lo que se está pidiendo sea contrario a derecho, que no vaya conforme a la ley, entonces sí el notario está legitimado para... para negar el servicio. Pero para las consultas, para las entrevistas de orientación, hay que ahora aprovechar para decir que son totalmente gratuitas. Si usted va a una notaría y pide entrevista con el notario para una consulta, tenga la certeza de que la consulta per se no le va a costar aquí en Hidalgo, es un... es un acuerdo que hemos tomado del Colegio. Y obviamente ya el servicio notarial pues depende de lo que se... se pida, ¿no? Y en materia testamentaria, pues aprovechar que estamos fomentando la cultura de la... del testamento, la cultura de la legalidad, la cultura de la planeación patrimonial, y una herramienta jurídica importantísima es el testamento.   Eulalio «Lalo» Larrieta: Yo... yo lo decía en cuestió... en cuestión del costo. En cuestión del costo, si alguien... si algún notario se niega a hacer ese descuento, ¿qué se hace?   Pedro Luis Noble: Mira, primero, pasar el dato al Colegio de Notarios. El teléfono... bueno, para que más... más fácil, podemos entrar a través de cualquier buscador de internet y poner «Colegio de Notarios de Hidalgo» y ahí aparece la página, ahí aparecen los números telefónicos, dirección del Colegio, y también van a encontrar las... oficinas, las direcciones de oficinas, teléfonos, correos electrónicos de las 94 notarías que hoy están operando en todo el territorio hidalguense.   Eulalio «Lalo» Larrieta: Perfecto, ¿y el número telefónico del Colegio de... de Notarios para que pues ahí se pueda comunicar también la gente?   Pedro Luis Noble: Sí, cómo no. Estoy abriendo porque el número no me lo sé de memoria, mi querido Lalo.   Eulalio «Lalo» Larrieta: Estoy en las mismas, a mí me preguntan mis números telefónicos y no me los sé de memoria tampoco, pero... Ya... a mi edad... a mi edad, pues imagínate, mi estimado...   Pedro Luis Noble: A la nuestra, mi querido Lalo. Ahorita te lo proporciono.   Eulalio «Lalo» Larrieta: De acuerdo.   Pedro Luis Noble: Y bueno, lo otro que te digo, el instrumento hoy más fácil es el... el de sumar el... el directorio del... del internet y pues ahí... ahí lo vamos a encontrar.   Eulalio «Lalo» Larrieta: Perfecto, en la página de internet del Colegio de Notarios ahí van a encontrar el número telefónico para la asesoría, ¿de acuerdo?   Pedro Luis Noble: Y de cualquier... y de todas las notarías del estado, ¿eh? Ah, perfecto, ahí tendrán ese directorio, eso es muy... muy importante. Te doy el número, te doy el número: 771 107 09 58. ¿Me permites repetirlo?   Eulalio «Lalo» Larrieta: Sí, adelante.   Pedro Luis Noble: 771 107 09 58.   Eulalio «Lalo» Larrieta: Perfecto. Ahí está por cualquier duda que tengan sobre los testamentos. Todavía en octubre tenemos el Mes del Testamento para que tengan esa oportunidad las personas adultas mayores, también las personas de los equipos de emergencia, policía industrial, también policía estatal, municipal, y paramédicos, bomberos...</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10DNEYWg-qeFSlXnj62DPqRdVz0vi4rZA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>PGJEH , SSPH</t>
-  </si>
-  <si>
-    <t>Pasando al panorama local, hoy por la madrugada, la Comisión de Búsqueda de Personas del Estado de Hidalgo informó que localizó cinco cuerpos inhumados ilegalmente. Estos cinco cuerpos fueron localizados en una fosa clandestina en la localidad de Texas, municipio de Atotonilco de Tula, en los límites del Estado de México, y esto fue como resultado de los trabajos de búsqueda realizados de forma permanente por la Comisión de Búsqueda de Personas del Estado de Hidalgo con apoyo de la Procuraduría General de Justicia del Estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1C_AD1G9UPYJvVriSN-07OJsL-aq6uV64/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Esther Ramírez Vargas , titular de la Secretaría de Hacienda de Hidalgo, compareció ante legisladores del Congreso del Estado de Hidalgo, destacó las finanzas sanas de la entidad.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/13SwxwyVQZW3gyX1n9WF0d5yk0JRMypPm/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Estudiantes hidalguenses destacaron en las Olimpiadas Mexicanas de Informática 2026, obtuvieron medallas de plata y bronce.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1eixbXxbtGvsv5Rx3TU7YSKeKw1koBJZ1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH) liberaron a una mujer de 40 años, presuntamente privada de la libertad por su expareja, y detuvieron al probable responsable, durante un operativo realizado en Tulancingo, tras recibir una denuncia ciudadana.De acuerdo con el reporte, los hechos ocurrieron alrededor de las 06:40 horas, cuando la mujer dejaba a su hijo en la escuela, en la colonia La Cañada</t>
-  </si>
-  <si>
-    <t>Elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH) liberaron a una mujer de 40 años, presuntamente privada de la libertad por su expareja, y detuvieron al probable responsable, durante un operativo realizado en Tulancingo, tras recibir una denuncia ciudadana.De acuerdo con el reporte, los hechos ocurrieron alrededor de las 06:40 horas, cuando la mujer dejaba a su hijo en la escuela, en la colonia La Cañada. Presuntamente, un hombre la amagó con una escopeta y la obligó a subir a un vehículo para trasladarla a un inmueble ubicado en el barrio Otontepec, en los límites con Acaxochitlán.Tras recibir el reporte, elementos de la Policía Estatal desplegaron acciones de búsqueda y localización que permitieron ubicar el domicilio. Al advertir la presencia de los uniformados, el presunto responsable ingresó al inmueble y habría realizado disparos contra los policías, por lo que se implementó una intervención táctica para controlar la situación y liberar a la mujer.Como resultado del operativo, la víctima fue puesta a salvo y se detuvo a un hombre identificado con las iniciales S. R. P., de 43 años. Además, los agentes aseguraron tres armas largas: una escopeta calibre 16 y dos rifles calibre .22.Durante la intervención, un elemento policial resultó lesionado en la mano izquierda y recibió atención médica. En tanto, una patrulla presentó un impacto de arma de fuego.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/17ibE0BcdKi4y-9WT7-3SJNVI8zlSNfjj/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Sebiso/Bol.690/2026</t>
-  </si>
-  <si>
-    <t>Con actividades que combinan aprendizaje, estimulación cognitiva y convivencia, los talleres de panadería del Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH), contribuyen a promover el desarrollo integral de este importante sector.De esa forma, a través de los Centros Gerontológicos Integrales y las Casas de Día se impulsó el taller de panadería como una actividad que combina el aprendizaje de técnicas culinarias con la estimulación cognitiva, el desarrollo de la motricidad fina y la convivencia social, pilares fundamentales para un envejecimiento saludable</t>
-  </si>
-  <si>
     <t>Bienestar</t>
   </si>
   <si>
-    <t>IAAMEH</t>
-  </si>
-  <si>
-    <t>Envejecimiento saludable</t>
-  </si>
-  <si>
-    <t>Con actividades que combinan aprendizaje, estimulación cognitiva y convivencia, los talleres de panadería del Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH), contribuyen a promover el desarrollo integral de este importante sector.De esa forma, a través de los Centros Gerontológicos Integrales y las Casas de Día se impulsó el taller de panadería como una actividad que combina el aprendizaje de técnicas culinarias con la estimulación cognitiva, el desarrollo de la motricidad fina y la convivencia social, pilares fundamentales para un envejecimiento saludable.A través de ellos, las y los usuarios fortalecen sus habilidades prácticas mediante la preparación de diversos productos de panadería, al tiempo que ejercitan la memoria, la concentración y la coordinación de movimientos. Además, estas actividades favorecen la autonomía, la participación y el intercambio de experiencias en un ambiente cálido, incluyente y participativo.En tanto, en el marco de la próxima celebración del Día de Muertos, las y los usuarios perfeccionan sus técnicas para elaborar el tradicional pan de muerto, un producto emblemático de la gastronomía mexicana que forma parte de las costumbres y expresiones culturales de las familias hidalguenses.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/19dx9Fd-FzU2u5_iZNjfEnhb93aXVTM6y/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Comento Eulalio Larrieta sobre la marcha de ayer. «Fue una manifestación limpia, tranquila, sin agresiones, sin insultos hacia... a la sociedad ni nada de ellos. Vinieron a pedir lo que querían, lo que necesitan. Sí sé que es del ámbito federal». Y lo dijo el secretario de Gobierno el pasado fin de semana:</t>
-  </si>
-  <si>
-    <t>Atención A Manifestantes</t>
-  </si>
-  <si>
-    <t>Comento Eulalio Larrieta sobre la marcha de ayer.  «Fue una manifestación limpia, tranquila, sin agresiones, sin insultos hacia... a la sociedad ni nada de ellos. Vinieron a pedir lo que querían, lo que necesitan. Sí sé que es del ámbito federal». Y lo dijo el secretario de Gobierno el pasado fin de semana: «Yo los escuché... yo... inclusive voy a hacer un recorrido con ellos, nada más visual, porque no puedo intervenir, porque es un ámbito federal. Sin embargo, en un ámbito... en una situación visual puedo acompañarlos y ver todas las situaciones que se presentan». Lo dijo en su momento el secretario de Gobierno Guillermo Olivares Reyna el pasado fin de semana. Sí, así lo comento: «O sea, con respeto los escucho, con respeto... si me permiten haré una visita nada más visual, no puedo intervenir, visual, que quede claro». Pues así está bien también, ¿no?   Eso es muy importante, y lo que hicieron ayer en esa manifestación, en verdad fue muy bien, fue pues agradable para mí. Que no hubo desmanes, no hubo pintas, no hubo  quebraron vidrios, no agredieron a negocios ni nada.Entonces, sí llama la atención, ¿no? Fue muy respetuosa.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1uaaqOwSHNeCt1L5rO_QLVxrljVGX-U0u/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Eulalio Larrieta agradece a Edith Balderas de la Secretaría de Educación Pública.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1rGitVvI9XqkSl8aR8b44eDS8bEX78a7g/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Edith Balderas</t>
-  </si>
-  <si>
-    <t>Eulalio Larrieta agradece a Jair Martínez de la Secretaría de Gobierno.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1lPROTZG7Nq9398BvETy06_wJlf02zbTy/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Jair Martínez</t>
   </si>
   <si>
-    <t>Eulalio Larrieta agradece a Cristian Yahir Castañeda de la movilidad de transporte.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1EesCMymOrcdJWgoX30WhoS9qBF0AmjnQ/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Cristian Yahir Castañeda</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1J1XTH5ODaGCoF1-JmDGjyJYBkjfOZcTE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Paola García, Sarahi Pineda</t>
+    <t>Un trabajador de la construcción fue localizado sin vida al interior de una vivienda del fraccionamiento Fuentes de Tizayuca luego de que presuntamente sufriera un accidente mientras realizaba sus labores. De acuerdo con los primeros reportes, la propietaria del inmueble encontró al albañil y solicitó apoyo a través del número de emergencias 911. Al lugar acudieron paramédicos y elementos de la policía municipal tras revisar al trabajador los servicios de emergencia confirmados. La zona fue acordonada para preservar el lugar, en tanto que personal de la Procuraduría General de Justicia del Estado de Hidalgo inició el levantamiento de pruebas y testimoniales. El personal del Servicio Médico Forense realizó el levantamiento del cuerpo y lo trasladó al anfiteatro para practicarle la necropsia de ley. Las autoridades ministeriales investigan las circunstancias del fallecimiento para determinar si se trató de un accidente laboral o si existen otros factores relacionados con la muerte.</t>
+  </si>
+  <si>
+    <t>Jessenia Romero</t>
+  </si>
+  <si>
+    <t>Localización de cuerpo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iz4oebvE6nTW2uapNAyvNzPY8eGTtL7K/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Sedeco/Bol.284/2026</t>
+  </si>
+  <si>
+    <t>Sí, llama muchísimo la atención este dato que se está proporcionando, porque pues estamos hablando incluso de que sí ha habido aumento en el empleo informal, y pues incluso en las estadísticas que proporcionaban, un incremento del 1.7%. Entonces ahí hay un tema importante, ahí hay un punto que también se debe de revisar y pues lo que hemos estado platicando también, Daniel, que no solo es generar empleos, sino también que encuentren salarios dignos con prestaciones, porque pues esto también será indispensable. En con calidad laboral, no es únicamente los pesos y centavos, ¿eh?</t>
+  </si>
+  <si>
+    <t>Informalidad laboral</t>
+  </si>
+  <si>
+    <t>Sí, llama muchísimo la atención este dato que se está proporcionando, porque pues estamos hablando incluso de que sí ha habido aumento en el empleo informal, pues incluso en las estadísticas que proporcionaban, un incremento del 1.7%. Entonces, ahí hay un tema importante, ahí hay un punto que también se debe de revisar y pues lo que hemos estado platicando también, Daniel, que no solo es generar empleos, sino también que cuenten con salarios dignos, con prestaciones, porque pues esto también será indispensable. Y con calidad laboral, no es únicamente los pesos y centavos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SxDUqORBV_4vi-dB1xUC7lSyveB3zQ_F/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Un hombre de aproximadamente 45 años de edad, hasta el momento no identificado, fue localizado sin vida la tarde de este martes en el interior de una habitación que rentaba sobre la avenida Hidalgo, en la zona centro de la cabecera municipal de Epazoyucan. De acuerdo con los primeros reportes de las autoridades locales, la víctima no había sido vista por sus vecinos desde el pasado fin de semana. Fue a partir de que los vecinos percibieron un fuerte olor a gas, que los vecinos realizaron reporta a los cuerpos de seguridad pública y de atención a emergencias. Al sitio arribaron elementos de la Policía Municipal, quienes tras ingresar a la vivienda confirmaron el hallazgo del cuerpo y procedieron a resguardar y acordonar el área para preservar la escena. Personal de la Procuraduría General de Justicia del Estado de Hidalgo inició las investigaciones respectivas al caso, para establecer lo ocurrido y con ello señalar las responsabilidades legales.</t>
+  </si>
+  <si>
+    <t>Epazoyucan</t>
+  </si>
+  <si>
+    <t>Un hombre de aproximadamente 45 años de edad, hasta el momento no identificado, fue localizado sin vida la tarde de este martes en el interior de una habitación que rentaba sobre la avenida Hidalgo, en la zona centro de la cabecera municipal de Epazoyucan. De acuerdo con los primeros reportes de las autoridades locales, la víctima no había sido vista por sus vecinos desde el pasado fin de semana. El hecho fue a partir de que los vecinos percibieron un fuerte olor a gas, que pues ahora sí que los vecinos realizaron un reporte a los cuerpos de seguridad y de atención a emergencias y pues de ahí al sitio arribaron elementos de la policía municipal quienes tras ingresar a la vivienda confirmaron el hallazgo del cuerpo y procedieron a resguardar y acordonar también el área para preservar la escena. Y pues personal de la Procuraduría, que algo inició las investigaciones respectivas al caso para poder establecer lo ocurrido y con ello pues señalar también las responsabilidades legales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K9mv78ocyLZRF3MtNR4HHTuuaM8-NYXe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1929/2026</t>
+  </si>
+  <si>
+    <t>SEPH coordina estrategia de vacunación en escuelas</t>
+  </si>
+  <si>
+    <t>Básica</t>
+  </si>
+  <si>
+    <t>...pública de Hidalgo, que encabeza Natividad Castrojón Valdés, coordinó una campaña de vacunación contra la influenza y COVID-19 en escuelas de educación básica, en coordinación con instituciones del sector salud, esto con el objetivo de proteger a niñas, niños y personal educativo. Como parte de estas acciones, inició la jornada... ...el 70% al 31 de diciembre del 2026, Y del 100%, pues al concluir esta campaña, en todo caso, León Vite destacó la colaboración de las instituciones participantes, bien del Secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdés, con el bienestar de las comunidades escolares. Y pues esta jornada, en esta jornada estuvieron presentes la subdelegada del Issste en Hidalgo, María del Consuelo Cabrera Morales, y también el enlace de vinculación de la Subsecretaría de Educación Básica, Carlos García Contreras. Y pues en esa campaña las instituciones participantes están buscando ampliar la protección preventiva en las comunidades escolares de la entidad.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pMthwPJ-wlQjFPkg4GThY8ef8GrVwXIt/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón, María del Consuelo Cabrera Morales, Carlos García Contreras</t>
+  </si>
+  <si>
+    <t>Entrevista</t>
+  </si>
+  <si>
+    <t>SC/Bol.082/2026</t>
+  </si>
+  <si>
+    <t>Señala el contralor del estado de Hidalgo, Álvaro Bardales Ramírez, que hasta el momento se han presentado 97 denuncias penales en total por qué se le conoce a la "Estafa Siniestra" en el estado de Hidalgo por temas relacionados con presunta corrupción. Él puntualizó que se han presentado 42 denuncias hacia proveedores y exservidores públicos de 7 dependencias, 3 organismos y 10 municipios. El monto del presunto daño asciende a 2,400 millones de pesos, de los cuales se han recuperado 500 millones. A ellos se agrega que 228 millones de pesos corresponden a recursos en 13 municipios, mientras que otros 50 millones de pesos provienen de diversos organismos. Además de que 5 inmuebles fueron destinados a programas sociales con un valor de 201 millones de pesos. El funcionario estatal señaló que algunas de las denuncias presentadas ante la Procuraduría Estatal de Justicia han derivado en la detención de presidentes municipales por presuntos actos de corrupción. Bardales Ramírez destacó que se han incorporado al patrimonio del estado 435 inmuebles recuperados con un valor superior a 1,267 millones de pesos, que se han destinado a beneficiar a la ciudadanía mediante espacios sociales, entre ellos la casa de los adolescentes, centros culturales, parques y jardines, así como la nueva sede del Tribunal de Justicia Administrativa del Estado. Por otro lado, el contralor afirmó que Hidalgo ocupa el primer lugar en denuncias penales por hechos de corrupción y atribuyó ese posicionamiento al incremento de las denuncias presentadas.</t>
+  </si>
+  <si>
+    <t>Por cierto, que en temas que tienen que ver con recursos, en este caso públicos, señala el Contralor del Estado de Hidalgo, Eduardo Bardales Ramírez, que hasta el momento se han presentado 97 denuncias penales en tal porqué de que en la justicia del Estado de Hidalgo, por temas relacionados con presunta corrupción. Puntualizó que se han presentado 42 denuncias hacia proveedores y ex servidores públicos de 7 dependencias, 3 organismos y 10 municipios. El monto del presunto daño asciende a 2.400 millones de pesos, de los cuales se han recuperado 500 millones. A ellos se agrega que 228 millones de pesos corresponden a recursos en 13 municipios, mientras que otros 50 millones de pesos provienen de diversos organismos. Además de que 5 inmuebles fueron destinados a programas sociales con un valor de 201 millones de pesos. El funcionario estatal señaló que algunas de las denuncias presentadas ante la Procuraduría Estatal de Justicia han derivado en la detención de presidentes municipales por presuntos actos de corrupción. Ahí te hablan, Estafa Siniestra, ¿no? Bardales Ramírez destacó que se han incorporado al patrimonio del Estado 435 inmuebles recuperados con un valor superior a 1.267 millones de pesos que se han destinado a beneficiar a la ciudadanía mediante espacios sociales, entre ellos la Casa del Adolescente, Centros Culturales, Parques y Jardines, así como la nueva sede del Tribunal de Justicia Administrativa del Estado. La Casa del Adolescente ya existía, por cierto. Por otro lado, el contralor afirmó que Hidalgo ocupa el primer lugar en denuncias penales por hechos de corrupción y atribuyó este posicionamiento al incremento de las denuncias presentadas</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oXsMivhuPtMzmfias6XRajT2ehmiwnX-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Procuraduría Estatal de Justicia, Tribunal de Justicia Administrativa del Estado.</t>
+  </si>
+  <si>
+    <t>El 58.4 por ciento de los 130 proyectos de inversión que han llegado al Hidalgo en el actual periodo de gobierno de la entidad, ya están en operación, aseguró el titular de la Secretaría estatal de Desarrollo Económico (Sedecoh), Carlos Henkel Escorza. Lo anterior fue declarado durante su comparecencia ante integrantes del Congreso del Estado de Hidalgo, realizada el miércoles 14 de octubre, en el marco de la glosa por el Cuarto Informe de Gobierno de la actual administración estatal. El funcionario aseguró que los 130 proyectos de inversión privada están consolidados, con inversión por 147 mil millones de pesos, que el funcionario estatal calificó como histórica. Con ello se han creado más de 73 mil empleos directos y 117 mil indirectos, con impacto positivo a 37 municipios de las distintas regiones. En el desglose, Henkel Escorza señaló que de este total de proyectos, 76 ya están en operación, mientras que 28 siguen en construcción, y 26 proyectos en trámites y permisos. Mencionó que muchas de las empresas que se establecen, van desarrollando sus proyectos a corto, mediano y largo plazo, lo cual queda plasmado en su carta de intención, y cuando se hacen los anuncios de inversión quedan marcados los tiempos y en su mayoría los han cumplido. En otro momento de la comparecencia, Henkel Escorza, reconoció que uno de los principales retos de la entidad es reducir la informalidad laboral, al ubicarse entre los cinco estados del país con mayor registro en esta materia. Atribuyó esta problemática al descuido y al rezago estructural histórico, donde en el Estado de Hidalgo siete de cada diez personas ocupadas en Hidalgo se encuentran en el sector informal, de acuerdo a datos del Instituto Nacional de Estadística y Geografía (Inegi). Henkel Escorza aseguró que la dependencia combate la informalidad con la generación de fuentes de trabajo formales y estables al señalar que Hidalgo se consolida como referente nacional en dinamismo laboral ya que de septiembre de 2022 a julio de 2026, se generaron 39 mil 900 nuevos empleos formales. De este total, 23 mil 741 correspondieron a hombres, lo que representa el 59.5%, mientras que 16 mil 163 fueron ocupados por mujeres, es decir, el 40.5%. Además, indicó que la entidad cuenta con 296 mil 980 puestos de trabajo asegurados. En tanto, señaló que el número de trabajadores formales ha crecido 6.6%, mientras que el empleo informal registra un incremento de 1.7%. A lo largo de la actual administración, explicó, se ha impulsado la constitución y formalización de 223 sociedades mercantiles y cooperativas en 65 municipios, con una inversión de 31 millones de pesos, en beneficio directo de 21 mil 53 personas. Además, se destinó una bolsa de 20 millones de pesos para atender a cerca de 100 cooperativas, al cierre del último reporte se habían ejercido 12 millones de pesos para respaldar a 62 sociedades cooperativas de 24 municipios.</t>
+  </si>
+  <si>
+    <t>Le tocó al Secretario de Desarrollo Económico, donde por una parte su titular señala, ah han se han consolidado ya varios proyectos de los anunciados, pero por otra parte reconoce, eso sí, la limpia, de que está altísimo el comercio o las actividades económicas informales en el Estado de Hidalgo.
+**Izza Hernández:** Así es, estamos hablando que un 58.4% de los 130 proyectos de inversión que han llegado a Hidalgo en el actual periodo de gobierno de la entidad ya están en operación. Esto fue lo que dijo el titular de la Secretaría Estatal de Desarrollo Económico... comparecencia ante integrantes del Congreso del Estado de Hidalgo que se realizó el día de ayer miércoles en el marco de la glosa por el cuarto informe de gobierno de la actual administración estatal. El funcionario aseguró que los 130 proyectos de inversión privada están consolidados con inversión por 147,000 millones de pesos, que el funcionario estatal calificó como histórica. Con ellos se han creado más de 73,000 empleos directos y 117,000 indirectos con impacto positivo a 37 municipios de las distintas regiones. En el desglose, Henkel Escorza señaló que de este total de proyectos, 76 ya están en operación, mientras que 28...ya que de septiembre del 2022 a julio del 2026 se generaron 39,900 nuevos empleos formales. De este total, 23,741 correspondieron a hombres, lo que representa el 59.5%, mientras que 16,163 fueron ocupados por mujeres, es decir, 40.5%. Además, indicó que la entidad cuenta con 296,980 puestos de trabajo asegurados. En tanto, señaló que el número de trabajadores formales ha crecido 6.6%, mientras que el empleo informal también tuvo un aumento de 1.7%. A lo largo de la actual administración, explicó que se han impulsado la constitución y formalización de 223 sociedades mercantiles y cooperativas en 65 municipios. Además, se destinó una bolsa de 20 millones de pesos para atender a cerca de 100 cooperativas. Al cierre del último reporte, se habrían ejercido 12 millones de pesos para respaldar a 62 sociedades cooperativas de 24 municipios de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qzuJ-JsRm1qTdqQ9q9o25PaM2C6NN4r0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Con los nombres de sus seres queridos desaparecidos como consigna, familiares de personas no localizadas marcharon este miércoles en Pachuca para exigir avances en las labores de búsqueda y localización. La movilización, encabezada por el colectivo Madres Buscadoras, partió de Plaza Juárez y avanzó hacia las instalaciones de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH), donde las familias expusieron las dificultades que han enfrentado durante los procesos de búsqueda. “Carlos, escucha, tu madre está en la lucha”, “Luis, escucha, tu padre está en la lucha” y otras consignas fueron repetidas durante el recorrido, mientras madres, padres, hermanos y demás familiares recordaban los nombres de las personas cuyo paradero continúa sin conocerse. Durante la manifestación, algunas familias compartieron experiencias relacionadas con las jornadas de búsqueda realizadas en distintos puntos del estado y señalaron que existen zonas que requieren mayor atención, particularmente aquellas de difícil acceso. Entre las participantes estuvo la madre de Carlos Gabriel Elizalde Gutiérrez, desaparecido el 11 de marzo de 2026 en Zempoala, quien señaló que continúa participando en las labores para localizarlo y que hasta el momento no cuenta con información sobre su paradero. La mujer también cuestionó la efectividad reportada por la Comisión de Búsqueda y señaló que, desde su perspectiva, existen deficiencias y lentitud en algunas jornadas. Afirmó que las familias han proporcionado información sobre posibles puntos de interés y consideró necesario mantener las labores de campo. Respecto a las búsquedas realizadas en zonas de minas de Zempoala, explicó que en uno de los puntos fueron localizados nueve cuerpos que, según la información recibida por las familias, correspondían a restos arqueológicos antiguos. Las familias también destacaron la participación de la Procuraduría General de Justicia del Estado de Hidalgo en las inspecciones de algunos terrenos, particularmente en la recuperación y análisis de posibles restos e indicios. Durante la marcha, los familiares reiteraron que continuarán participando en las labores de búsqueda y solicitando que se atiendan los distintos casos de personas desaparecidas en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Búsqueda de personas</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ia_-OrcWeuIBq2d-cTzn_rDHqSdkC7Zh/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de nuestra entidad, Natividad Castrejón, no para, prácticamente recorre todo el estado constantemente visitando las escuelas, desde nivel preescolar hasta las superiores. Es de destacar el interés que hay por atender las demandas de las regiones en cuanto al tema educativo y pues es una constante la presencia del secretario en todas las regiones, en todas las escuelas de del estado.</t>
+  </si>
+  <si>
+    <t>Labor destacada</t>
+  </si>
+  <si>
+    <t>En nuestra entidad, Nativa de Castellón no para, prácticamente recorre todo el estado constantemente visitando las escuelas desde el nivel preescolar hasta las superiores, hasta las escuelas superiores, bueno pues, de destacarse el interés que hay por atender las demandas de las diferentes regiones en cuanto al tema educativo y pues es una constante, constante la presencia del secretario en todas las regiones, en todas las escuelas del Estado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1j-JpC2fPthBBdQnxhSSN6b9wfYjC-OsL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1928/2026</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón entregó nuevos espacios educativos en beneficio de estudiantes de Alfajayucan</t>
+  </si>
+  <si>
+    <t>Entrega de infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Alfajayucan</t>
+  </si>
+  <si>
+    <t>Con el propósito de fortalecer la infraestructura educativa con contar con espacios dignos para el aprendizaje, el Secretario de Educación Pública de Hidalgo, Natividad Cáceres Juan Valdés, encarzó la entrega de las nuevas instalaciones del Centro de Educación Media Superior a distancia en Alfajayucan, perteneciente al Colegio de Bachilleres del Estado de Hidalgo. Además, visitó la Secundaria Técnica Nº 8, donde habilitaron nuevas aulas. En estas instalaciones de Alfajayucan representan una inversión cercana a los 7.5 millones de pesos en beneficio directo de 202 estudiantes. El plantel cuenta con nuevas aulas didácticas, el taller de cómputo, módulos también de sanitarios, área administrativa y fachada institucional. Durante esta, don Adivete Castrejón destacó el trabajo coordinado entre el gobierno de Hidalgo, encabezado por el gobernador Julio Mecha Casalazar, y los gobiernos de Alfajayucan para dotar de la comunidad escolar con instalaciones propias educativas para sus actividades académicas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QuJz-Y-KnLUctV52sAIsPm8zf0X401UK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>CDMX</t>
+  </si>
+  <si>
+    <t>Hoy rinde su cuarto informe de actividades la titular del patronato DIF Hidalgo, Edita Vite Ramos a las 17:00 horas en el auditorio Gota de Plata.</t>
+  </si>
+  <si>
+    <t>Informe DIFH</t>
+  </si>
+  <si>
+    <t>Tenemos el cuarto informe de la Presidenta del Patronato DIF, Eda Vitte Ramos, el día de hoy a las 5 de la tarde en el Auditorio Gota de Plata, el informe de la Presidenta del Patronato. Mañana le estaremos dando puntual seguimiento, le vamos a platicar cómo estuvo este informe de la señora Eda Vitte, la Presidenta del Patronato DIF en nuestro Estado de Aldo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1e_VxzMyDCqOKaeShz8pjBgDy2N3ceMU9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Edda Vite</t>
+  </si>
+  <si>
+    <t>UPLAPH/Bol.157/2026</t>
+  </si>
+  <si>
+    <t>Rocket Revolution acerca la industria aeroespacial a Hidalgo</t>
+  </si>
+  <si>
+    <t>Impulso a ciencia y tecnología</t>
+  </si>
+  <si>
+    <t>La industria aeroespacial presentó oportunidades para el desarrollo científico, innovación y fomento del talento especializado en Hidalgo. En este contexto, la Universidad Politécnica de Pachuca fue sede del Rocket como parte de la Semana Mundial de Espacio México 2026, celebrada del 4 al 19 de octubre. Durante este encuentro, Coordinado General del Distrito de Innovación, Ciencia y Tecnología e Innovación, Alejandro Franco Segura, impartió conferencia potencial Hidalgo en la industria aeroespacial. Destacó las capacidades y oportunidades que tiene la entidad de integrarse a este sector como importancia del vínculo de talento de investigación y el desarrollo tecnológico de las necesidades industriales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pgljtXRv_de3FV152YWplQpJk7WeEcD9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Alejandro Franco Segura</t>
+  </si>
+  <si>
+    <t>Segobh/Bol.100/2026</t>
+  </si>
+  <si>
+    <t>Primera sentencia condenatoria por violencia vicaria</t>
+  </si>
+  <si>
+    <t>Mesas de acercamiento</t>
+  </si>
+  <si>
+    <t>Como resultado del seguimiento institucional a los planteamientos presentados en las mesas de acercamiento del Bienestar y la Paz por primera vez en Hidalgo se obtuvo la primera sentencia condenatoria por el delito de violencia familiar en su modalidad vicaria en agravio de una mujer del municipio de Cuautepec Recuerden ustedes que estas mesas de acercamiento de Bienestar y la Paz son encabezadas por el secretario de Gobierno, Guillermo Olivares Reina, por representantes de la Procuraduría General de Justicia, por ejemplo, como el encargado del despacho, don Francisco Fernández Hasbún, a veces también acude cuando le es posible su agenda, el secretario de Seguridad Pública, Salvador Crisneri, y autoridades de las Procuradurías de Justicia, de la Procuraduría de la Mujer y de otras instancias que tienen que ver con Defensoría. Luego de que se expusiera la situación durante estas mesas de acercamiento que se realizaron en aquella región de Cuautepec, de Tulancingo, la Secretar de Gobierno en coordinación con las instituciones competentes dieron seguimiento al caso a fin de que se recibiera la atención correspondiente La sentencia tiene un precedente importante para Hidalgo al tratarse del primer caso con una resolución condenatoria por violencia familiar que busca causar da a las mujeres a través de sus hijos e hijas. Esto es lo que se conoce como violencia vicaria, Cuando una pareja entra en conflicto y el varón busca perjudicar a su expareja vía los hijos, vía la familia. Este proceso también se reconoce la participación del Frente Nacional contra la Violencia Vicaria, organización que impulsa la visibilización y atención de esta forma de violencia y destacaron por supuesto el trabajo del agente del Ministerio Público y del juez que intervinieron en este caso, así como también se puso en el manifiesto la importancia de aplicar la perspectiva de género para garantizar el acceso a la justicia. Desde la Secretaría de Gobierno continuarán trabajando para que las mesas de acercamiento de bienestar y paz sigan siendo espacios abiertos de atención directa donde las personas puedan expresar sus situaciones y las instituciones correspondientes de seguimiento a los casos que ahí se presentan</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nDMibUvxvICeqbJbvV4pJK_DPCwwShPA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun, Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Hoy comparece Napoleón González, secretario de Agricultura y Salvador Cruz Neri, el secretario de Seguridad Pública</t>
+  </si>
+  <si>
+    <t>Para hablar a detalle, para responder preguntas, para explicar cuáles han sido los avances, los logros de estos años de trabajo y por supuesto también en particular del último año. Y bueno, hoy me comparecen a Jolén González, el Secretario de Agricultura y Salvador Cruz Ney, el Secretario de Seguridad. Van a ser dos comparecencias que de pensar muy interesantes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1F0gkhxSoPWw_F3Sr0-bDMFHfBgFLZPjw/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Hoy comparece Napoleón González, secretario de Agricultura y Salvador Cruz Neri, el secretario de Seguridad Pública.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19yiVCNjfUvyK04RsZGQG4G-lXFiUFY3q/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ayer tuve una reunión con el secretario del despacho del gobernador Julio Menchaca con don Alejandro Velázquez y estuvimos viendo el tema de resolver lo más pronto posible, junto con el secretario de gobierno Guillermo Olivares Reyna, la situación que tenemos en Jacala de Ledezma, donde casi ya llevamos un mes fuera del aire. Ayer tuvimos una reunión ex profeso para ver estos temas. Gracias de verdad por el apoyo, muy pronto vamos a estar nuevamente al aire allá en Jacala en el 91.1 de frecuencia modulada.</t>
+  </si>
+  <si>
+    <t>Radiodifusoras</t>
+  </si>
+  <si>
+    <t>Jacala</t>
+  </si>
+  <si>
+    <t>Ayer, como decía yo, tuve una reunión con el secretario del despacho del gobernador Julio Mechaca, con don Alejandro Velázquez. Estuvimos viendo el tema de resolver, lo más pronto posible, junto con el secretario de gobierno Guillermo Olivares Reina, pues la situación que tenemos en Jacala de Vélez, donde casi tenemos un mes fuera del aire. Ayer tuvimos una reunión en el profesor para ver estos temas. Gracias de verdad por el apoyo. Muy pronto, muy pronto vamos a estar nuevamente al aire allá en Jacala. en el 91.1 de frecuencia modulada</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Y9i8iws6MkUvVpxHFhGPiSzDWhRLe3ux/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La zona del municipio de Zapotlán está llamada a crecer exponencialmente en los próximos meses y años. Ya lo verá, Julio Menchaca anunció en su cuarto informe de gobierno a la carretera Pachuca-Ciudad de México, va a iniciar ahí, exactamente en el municipio de Zapotlán. En la comunidad de Acayuca y de ahí, pues vamos a iniciar con un importante sobre la México-Pachuca, se va a ampliar a ocho carriles. Y de ahí en adelante, vieneun importante desarrollo para toda esta zona de nuestro estado.</t>
+  </si>
+  <si>
+    <t>Gobernador</t>
+  </si>
+  <si>
+    <t>Ampliación carretera</t>
+  </si>
+  <si>
+    <t>Zapotlán</t>
+  </si>
+  <si>
+    <t>El proyecto de desarrollo para esta región, pues prácticamente ya conurbada con Pachuca, es muy ambicioso. La zona del municipio de Zapotlán está llamada a crecer exponencialmente en los próximos meses y años. Ya lo verá usted, la ampliación que el gobernador Julio Menchaca anunció en su cuarto informe de gobierno a la carretera Pachuca-Ciudad de México, Va a iniciar ahí exactamente En el municipio de Zapotlán En la comunidad de Acayuca Y de ahí pues vamos a iniciar con un puente Y una especie de libramiento Un retorno ahí Importante sobre la México Pachuca Se va a ampliar a 8 carriles Y bueno pues de ahí en adelante Así que bueno Viene un importante desarrollo Para toda esta zona de nuestro estado</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G7eFFxnIKiVE4OVew5qfwD6VwR595q9k/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/FN.36/2026</t>
+  </si>
+  <si>
+    <t>El gobernador del estado, Julio Menchaca Salazar, asistió a la Ciudad de México como invitado especial al segundo informe de actividades de la jefa de Gobierno, Clara Brugada. Ahí, se hace la declaratoria para que también municipios como Tula, Zapotlán, Tizayuca y Tepeji, se incluyan en esta zona metropolitana de la Ciudad de México. Comento el gobernador Julio Menchaca, acompañé a mi compañera Clara Brugada, perdón, a su entrega del segundo informe de gobierno. Los resultados confirman que con honestidad, cercanía y amor al pueblo, el segundo piso de la cuarta transformación se traduce en mejores condiciones de vida para las familias.</t>
+  </si>
+  <si>
+    <t>Asistencia a informe</t>
+  </si>
+  <si>
+    <t>Ayer el gobernador del estado viajó a la Ciudad de México, Julio Menchaca Salazar fue invitado, uno de los invitados especiales al segundo informe de actividades de la jefa de gobierno, pues ya se puede decir gobernadora, ¿no? Ya la Ciudad de México ya es un estado, ¿no? Ya no es un distrito federal, ahora sí ya es un estado, bueno, se quedó el tema de jefa de gobierno, Clara Brugada. Junto con otros gobernadores, otros mandatarios de Morena, Julio Menchaca fue invitado especial a este informe. Recuerden ustedes que a partir de que dio inicio la transformación, no solo en el estado de Hidalgo, sino en el país, hay una nueva concepción del proyecto de zona metropolitana de la Ciudad de México, que incluye ya otros estados, ya no solamente la Ciudad de México y el Estado de México, ahora incluye otras entidades, por supuesto, Hidalgo, Puebla, Tlaxcala, de este lado de acá, por supuesto Querétaro, Morelos y hay crecido en los últimos años. Recordarán ustedes que apenas este 2026 se reunió todo el consejo de la zona metropolitana de la Ciudad de México, fue una reunión muy importante, fue ahí en el Aeropuerto Internacional Felipe Ángeles y ahí se hizo la declaratoria para que más municipios de Hidalgo, porque en ese momento solamente Tizayuca pertenecía a la zona metropolitana de la Ciudad de México, ahí se hace la declaratoria para que también municipios como Tula, como Zapotlán, como Tolcayuca y me falta por ahí uno de aquel lado de Tula, que seguramente debe ser Tepeji, este se incluyan en esta zona metropolitana de la Ciudad de México, que lo que pretende, bueno, primero una coordinación, una coordinación entre entidades, entre estados para desarrollar un ordenado, con miras al natural crecimiento de la capital del país, un desarrollo que incluye, por supuesto, comunicaciones, es decir, carreteras, trenes, temas de bases aéreas como el Aeropuerto Internacional Felipe Ángeles, pero también otros asuntos que tienen que ver con la seguridad, con el tema de los recursos como el agua y, por supuesto, con la ubicación de los nuevos eh pues lugares o de los nuevos asentamientos humanos, es decir, donde va a vivir la gente, donde va a estar ubicada las nuevas zonas habitacionales con prospectiva, quiero decir prospectiva, es decir, a futuro de hasta 30 años. Se está trabajando intensamente con esta visión, Hidalgo forma parte fundamental de este proyecto y, bueno, pues ayer Julio Menchaca Salazar estuvo como invitado especial en este informe, Aldo Falcón. **Aldo Falcón:** Así es, dicho comento el gobernador Julio Menchaca, acompañé a mi compañera Clara Brugada, perdón, a su entrega del segundo informe de gobierno. Los resultados confirman que con honestidad, cercanía y amor al pueblo, el segundo piso de la cuarta transformación se traduce en mejores condiciones de vida para las familias.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18R02mD05uI8oMYz9Cgbl9Zrv2yaRv9Rj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Clara Brugada</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud Pública inició la campaña de vacunación invernal con dosis gratuitas contra el COVID-19 y la influenza estacional en todo el estado. Las vacunas son gratis, hay que ponerse la vacuna del COVID cada año, dos veces al año se recomienda la de influenza, por favor, primero niños, niñas menores de 5 años, es el sector de población uno de los más importantes para temas de salud, eh los adultos mayores, las personas que tienen enfermedades crónico-degenerativas.</t>
+  </si>
+  <si>
+    <t>Tenemos campaña de vacunación esta semana, la Secretaría de Salud Pública perdón, de Salud Pública, inició la campaña de vacunación invernal con dosis para el COVID y dosis para la, este, la influenza estacional por favor, si usted puede, si usted es su ánimo, acérquese a las clínicas a los centros de salud, a los hospitales más cercanos a su domicilio a su lugar de origen, a su comunidad las vacunas son gratis hay que ponerse la vacuna de COVID cada año, dos veces al año se recomienda la de influenza por favor, primero niños y niñas menores de 5 años es el sector de población uno de los más importantes para temas de salud los adultos mayores las personas que tienen enfermedades crónico-degenerativas pero las vacunas ya están disponibles, son totalmente gratuitas, más de un millón 500 mil dosis están listas Para ser aplicadas y totalmente Gratis nuevamente Hay que decirlo en todo el estado Por favor cuídense mucho Antes de que inicie el invierno Que estemos todos bien vacunados</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18KUo13ZlHSNg9wj9xx1m2eVvrj6nxdoU/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Locutor Jesús Riveros da salida a audio de radioescucha identificada como la doctora Leticia Guzmán quien reportó una grave fuga de agua potable con más de un mes de antigüedad ubicada en el fraccionamiento Mineral del Oro, específicamente entre las calles Maestranza y Mineral Paraíso, cerca de la explanada al sur de Pachuca. Señaló que a pesar de haber interpuesto más de 14 denuncias ante la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (CAASIM), las autoridades no han acudido a solucionar el problema que desperdicia miles de litros diarios, por lo que solicitó la intervención urgente del organismo.</t>
+  </si>
+  <si>
+    <t>Fuga De Agua</t>
+  </si>
+  <si>
+    <t>Muy negativo</t>
+  </si>
+  <si>
+    <t>Queridos locutores, dice: "Felicitito por su programa, gran labor, muchas gracias, porfa, ayúdennos a denunciar y pedir a CAASIM acá en Pachuca, no nos hacen caso, no han venido a dar solución, tenemos una gran fuga de agua potable de más de un mes, litros y litros están tirando diario, es la verdad que es una vergüenza que estos funcionarios, ya hicimos más de 14 denuncias y no las han atendido, esta gran fuga de agua potable, por favor CAASIM que venga a ayudar, está ubicada en colonia Fraccionamiento Mineral Oro, calle Maestranza y Mineral Paraíso, estamos frente cerca de la explanada al sur de Pachuca". Atentamente, doctora Leticia Guzmán de Pachuca.
+Doctora, pues muchas gracias por el reporte, con todo gusto lo vamos a canalizar a la CAASIM, esperando, esperando puedan brindarle la atención debida.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12AeXQH-FYrkMKA3xvDJ3R178eZOArJT_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Locutor Jesús Riveros da salida a audio de radioescucha que expresó su inconformidad sobre el costo de 3.4 millones de pesos destinado para la construcción de dos aulas equipadas con tecnología en un plantel escolar, cuestionando el destino de dicha inversión. En respuesta, Jesús Riveros explicó que se trata de espacios tipo laboratorios tecnológicos avanzados promovidos por la Secretaría de Educación Pública, los cuales justifican el monto debido a su alto nivel de equipamiento e innovación.</t>
+  </si>
+  <si>
+    <t>Infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Está muy bien que inviertan en hacer escuelas por el bien de toda la juventud o niños, pero 3.4 millones por dos aulas, mi pregunta es de qué las hicieron y qué tanto las les pusieron tanta tecnología para tantísimo dinero.   Gracias. Buenos días. Bueno, pues así sus reportes de audio. Sí, estas aulas, que son precisamente de laboratorios, de laboratorios tecnológicos y y pues que llevan obviamente una inversión fuerte en cuanto estamos hablando de tecnología, son esos estos centros de estudios que está promoviendo la Secretaría de Educación Pública y pues obviamente tiene toda la razón en cuestionarlo para saber precisamente cómo es que se se equipan estos laboratorios, que son de eh de última de última tecnología, por lo menos así lo ha referido la Secretaría de Educación Pública.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VeXuFG_2iLCRxrBfXN6sIFPzOiivSqBp/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Durante su comparecencia ante el Congreso, el titular de la Secretaría de Desarrollo Económico (Sedeco), Carlos Henkel Escorza, resaltó la consolidación de 130 proyectos de inversión para el estado de Hidalgo. El funcionario destacó que la entidad ha dejado atrás el rezago en infraestructura y conectividad para posicionarse como un competidor activo y un atractor de capitales a nivel nacional e internacional.</t>
+  </si>
+  <si>
+    <t>Muy positivo</t>
+  </si>
+  <si>
+    <t>También ayer durante su comparecencia Carlos Henkel Escorza, titular de la Sedeco, destaca 130 proyectos de inversión para el estado de Hidalgo. Durante su comparecencia, Carlos Henkel destacó y también, también dio a conocer en este sentido, Hidalgo está compitiendo, Hidalgo compite ya con las grandes marcas, con los grandes espacios para poder atraer recursos, traer capital y desde luego generar mayor desarrollo. 
+Carlos Henkel, titular de la Sedeco, destacó 130 proyectos de inversión, algo que llamó la atención y lo voy a destacar, sin duda. 
+Hace años se hablaba de Hidalgo, uno de los estados con pobres, eh no teníamos, no teníamos solución de energía, no había conectividad. México está inmerso en un tratado de libre comercio. México está participando en distintos momentos, en distintos escenarios. 
+Hidalgo no está participando, está compitiendo. Hidalgo es un competidor natural en el desarrollo de la República. 
+Una pausa de regreso.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1BWo9Ax4eoFPU22fCXR0j_aAiNPrMIDWx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Durante su comparecencia ante el Congreso de Hidalgo, el secretario de Contraloría, Álvaro Bardales Ramírez, informó sobre los avances en la fiscalización de recursos y la consolidación del complejo Hidalgo Honesto. El funcionario destacó la recuperación de cerca de 500 millones de pesos por desvíos y la incorporación de 435 inmuebles al patrimonio público con un valor superior a los 1,267 millones de pesos. Asimismo, detalló las auditorías e investigaciones realizadas para combatir la corrupción y garantizar la correcta aplicación del gasto en beneficio de la ciudadanía.</t>
+  </si>
+  <si>
+    <t>En más de la información, Álvaro Bardales, secretario de la Contraloría, compareció ayer ante el Congreso de Hidalgo y enfatizó avances en fiscalización y recuperación de recursos en la sesión antier de la Junta de Gobierno, Andrés Manuel López Paz que dio la bienvenida al secretario de Contraloría, Álvaro Bardales Ramírez, quien compareció ante el Congreso del Estado Libre y Soberano de Hidalgo como parte del procedimiento relativo al cuarto informe del Estado con guardan diversos ramos de la administración pública encabezada por el gobernador Menchaca Salazar.
+Es un mensaje y el coordinador recalcó que la transparencia, la honestidad y la rendición de cuentas son fundamentales para proteger los recursos públicos y fortalecer la confianza ciudadana. Álvaro Bardales señaló que desde el principio de este gobierno llegaron nuevas herramientas, la instrucción para que todo, todo recurso del Estado, producto del trabajo de las y los hidalguenses sea desde luego supervisado en todo momento.
+Álvaro Bardales señaló desde el principio de esta administración que el gobernador asumió el combate a la corrupción como una responsabilidad de Estado. Para cumplir con esa tarea, fortaleció a la Contraloría con infraestructura, personal, herramientas y recursos.
+Este respaldo nos obliga a trabajar con firmeza, a actuar con responsabilidad y entregar resultados que se revisen y expliquen. A 4 años de gobierno, contamos con una institución sólida y con mejores capacidades de fiscalización, control, investigación y prevención.
+El propósito es el mismo: cerrar espacios a la corrupción y evitar que vuelvan a repetirse las prácticas que dañaron el servicio público.
+Dentro de los logros más destacados, el funcionario informó los siguientes: la consolidación del complejo Hidalgo Honesto integrado por tres edificios especializados y laboratorios con 37 certificaciones para fortalecer la fiscalización de los recursos públicos y la calidad de las obras.
+También señaló Álvaro Bardales que en estas revisiones ha habido hallazgos y se ha dado seguimiento también para localizar, encontrar cuáles han sido las fallas.
+Bueno, mire, desde dinero que se extravió, se perdió, mal usado, edificios que se estaban rentando sin tener ninguna necesidad y sobre todo recursos que justamente se entregaron para obras en los municipios, 13 municipios de los cuales nunca llegaron esas obras.
+Álvaro Bardales en las revisiones y hallazgos detalló: "Las revisiones, auditorías e investigaciones permiten identificar irregularidades, obras inexistentes o deficientes, empresas utilizadas para simular operaciones, contrataciones sin sustento, personas que cobran sin cumplir sus funciones, duplicidad de plazas, sistemas tecnológicos que no responden a las necesidades institucionales, adquisiciones fuera de los procedimientos establecidos, conflictos de interés, simulación de servicios especializados y arrendamientos que imponen cargas innecesarias a las finanzas públicas.
+Ante cada hallazgo, nuestra obligación es investigar, documentar y actuar conforme a la ley. Con esa convicción trabajamos.
+Uno de los asuntos más graves que enfrentamos al iniciar esta administración es el desvío de recursos extraordinarios destinados a municipios, dependencias y organismos. Una auditoría de la Contraloría reveló que esos recursos fueron utilizados para obras y servicios simulados.
+La pérdida ascendió a 2,400 millones de pesos. Detrás de ese daño están las obras que no llegaron y los servicios que la población dejó de recibir."
+Obras que no llegaron, servicios que la población dejó de recibir, dinero que se extravió o ya más, lo menos, que en un momento determinado, alcaldes que se prestaron o que tomaron lo ajeno y yo a un lugar esto hallar.
+¿Qué es lo que se ha recuperado?
+Los ahorros superiores a 32 millones de pesos anuales, la recuperación de cerca de 500 millones de pesos vinculados con el desvío de recursos y la incorporación de 435 inmuebles al patrimonio público valuados en más de 1,267 millones de pesos.
+Pues imagínate toda esta cantidad de dinero que iba a beneficiar y que nunca llegaron.
+Esto fue lo que dijo Álvaro Bardales en torno a lo recuperado.
+A la fecha, logramos recuperar cerca de 500 millones de pesos, de ellos, 228 millones corresponden a recursos de 13 municipios, 50 millones provienen de diversos organismos y fueron destinados a programas sociales estatales, y cinco inmuebles con un valor aproximado de 201 millones de pesos se incorporaron al patrimonio público.
+Vigilamos asimismo el patrimonio público que se recuperó con 435 inmuebles con un valor superior a 1,267 millones de pesos, que hoy se transforman en sitios para beneficio de las familias hidalguenses.
+Pues se espera que no solamente quienes lo utilizaron, mal utilizaron, tengan esta responsabilidad, sino que instrumente también todos estos malos manejos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ycCaNvBSmkSewOfe32_fcfI4cp6cw8Mk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Andrés Velázquez Vázquez</t>
+  </si>
+  <si>
+    <t>En Hidalgo se logró la primera sentencia condenatoria por violencia vicaria tras el caso de una mujer de Cuautepec que expuso su situación en las mesas de acercamiento de Bienestar y Paz. El seguimiento institucional de la Secretaría de Gobernación y las instancias competentes permitió obtener este fallo histórico que busca causar daño a la madre a través de los hijos. En el proceso destacó la intervención del Frente Nacional Contra la Violencia Vicaria y la actuación con perspectiva de género por parte del Ministerio Público y el juez.</t>
+  </si>
+  <si>
+    <t>Vamos a dar la información de Hidalgo. Escuchar, atender y dar seguimiento permitió a Hidalgo lograr la primera sentencia por violencia vicaria. Una mujer expuso su caso en las mesas de acercamiento de Bienestar y Paz; el seguimiento institucional contribuyó a que llegara a una resolución judicial condenatoria. La atención directa a una mujer de Cuautepec derivó en la primera sentencia condenatoria en el estado por violencia familiar en su modalidad vicaria, un caso que coloca en el centro la importancia de escuchar, responder y dar seguimiento a las denuncias de violencia de género. La mujer expuso su situación durante las mesas de acercamiento de Bienestar y Paz; a partir del planteamiento, la Secretaría de Gobernación, en coordinación con las instituciones competentes, dio seguimiento para que recibiera la atención correspondiente. La violencia vicaria, le informo, busca causar daño a una mujer a través de sus hijas o hijos. La sentencia representa un precedente para la atención y el acceso a la justicia de quienes enfrentan esta forma de violencia. En el proceso también se reconoció la participación del Frente Nacional Contra la Violencia Vicaria, así como la actuación y el agente del Ministerio Público y el juez que intervinieron con énfasis en la aplicación de la perspectiva de género, dando seguimiento, atención se llegó a esta resolución.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zGrVqP1P7DXqaukAO6vFWY76Yg71iKVX/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Menchaca Salazar acompaña a Clara Brugada en Segundo Informe de Actividades</t>
+  </si>
+  <si>
+    <t>El día de ayer el gobernador de Hidalgo, Julio Menchaca Salazar, estuvo presente, acompañó a la titular del Poder Ejecutivo en la Ciudad de México, Clara Brugada, en su segundo informe de actividades. El mandatario hidalguense destacó que con resultados, honestidad, cercanía y amor se mejoran las condiciones de vida de las familias mexicanas, en respaldo a la transformación que se vive en otros rincones del país. El gobernador Julio Menchaca Salazar acompañó a la jefa de Gobierno de la Ciudad de México, Clara Brugada, en su segundo informe de actividades. En el marco de los trabajos de Hidalgo se destacó que con resultados, honestidad y cercanía se mejoran siempre las condiciones de vida de todas las personas, de las familias mexicanas. Fue todo lo que se dio a conocer..</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jch_-gyZr-A1tBX3Gq69QrzSd3XFHXkE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo</t>
+  </si>
+  <si>
+    <t>Cultura/Bol.715/2026</t>
+  </si>
+  <si>
+    <t>Con 21 funciones llegará Circuito Nacional de Artes Escénicas a Hidalgo</t>
+  </si>
+  <si>
+    <t>Evento Cultural</t>
+  </si>
+  <si>
+    <t>Y en otros temas, algo que había quedado pendiente, que quedó pendiente ayer y le compartía le adelantaba que a partir de este día 15, 15 de octubre se estará llevando a cabo en Hidalgo parte 21 funciones del Circuito Nacional de Artes Escénicas.
+21 puestas en escena en cinco foros alternativos se realizarán a partir de hoy, 15 de octubre, y hasta el 5 de diciembre el Circuito Nacional de Artes Escénicas en Espacios Independientes 2026. Para esta edición se presentarán en cuatro municipios de Hidalgo.
+Es iniciativa impulsada por la Secretaría de Cultura del Gobierno de México y operada a través del Instituto Nacional de Bellas Artes y Literatura promueve la circulación de montajes entre recintos independientes de distintas regiones del país. Los foros hidalguenses forman parte del circuito número 7.
+Entre las propuestas destacan Cocina Escénica, Resetario contra el olvido de la compañía Revolver Escena, que tendrá cuatro funciones en tres recintos, la mayor presencia de una obra en la cartelera estatal.
+La programación incluye el Foro Doble 9 y la Sala Siqueiros en Pachuca, el Foro Arlequín en Tulancingo, Xihui Espacio Cultural en Ciudad Sahagún y el Neuroforo Neurocarpa Artebus en el municipio de Apan.
+Las actividades, ya le decía, comienzan hoy jueves 15 de octubre a la 1 de la tarde en el Foro Doble 9 con medio en medio de la maleza.
+La obra llegará el día siguiente a mañana a la Sala Siqueiros, donde también se presentará No Concreto, los días 16 y 17 de este mes, mañana y el próximo sábado. Noviembre será el mes con más actividad al concentrar 14 de las 21 funciones anunciadas. Entre los títulos anunciados figuran 12 maneras de afilarse de afilarse los colmillos, Somos el enemigo y La extraordinaria historia del niño que se comió la servilleta de su sándwich.
+Otras dos obras ampliarán su presencia en el estado al presentarse en tres sedes cada una: Don Quijote y Siete Pecados, esta última con una propuesta escénica que incorpora títeres y también esto será en funciones vespertinas. Ya en su momento le estaremos compartiendo los detalles al respecto.
+La participación de los foros permite diversificar la oferta cultural en Hidalgo y acercar distintas expresiones teatrales a públicos de varios municipios. La Secretaría de Cultura Estatal apoyará la difusión de las actividades y la vinculación de los espacios con el circuito nacional.
+Así es que a partir de este día, hoy 15 de octubre, el Circuito Nacional de Artes Escénicas en Espacios Alternativos en el Estado de Hidalgo, en cuatro municipios del estado y hoy comienza</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zVkmfOvvluTK5Kkt9YSglseGvPx6oLYq/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Locutor Jesús Riveros: Y pues bueno, comentarle en esta oportunidad que eh pues con el propósito de fortalecer la infraestructura educativa y contar con espacios dignos para el aprendizaje, el secretario de Educación Pública de Hidalgo, Natividad Castrejon Valdez, encabezó la entrega de nuevas instalaciones del Centro de Educación Media Superior a Distancia (CEMSaD) en Alfajayucan, perteneciente al Colegio de Bachilleres del Estado de Hidalgo. Además, visitó la Secundaria Técnica número 8, donde se habilitaron dos nuevas aulas. 
+Las instalaciones de este CEMSaD Alfajayucan representaron una inversión cercana a los eh a los 7.5 millones de pesos en beneficio directo de 202 estudiantes. El plantel cuenta con nueve aulas didácticas, un taller de cómputo, módulo de sanitarios, área administrativa y fachada institucional. Durante el acto, Natividad Castrejón destacó el trabajo coordinado entre el gobierno de Hidalgo, encabezado por Julio Menchaca Salazar, y los gobiernos de Alfajayucan para dotar a la comunidad escolar pues de instalaciones propias y adecuadas para sus actividades académicas. Le comparto parte de lo que dijo. 
+Natividad Castrejón: Estudian mucho, pero denle mucha importancia al ABC de las emociones. Van a ser ustedes, jóvenes, la primera generación, junto con los que están en prepa y en primaria, van a ser la primera generación de jóvenes que recibieron alfabetización emocional. 
+Locutor Jesús Riveros: Dijo a nuestros a nuestras y nuestros estudiantes, les decimos este espacio es suyo, úsenlo para aprender, para descubrir sus talentos, para construir sus proyectos de vida y para convertirse en las y los agentes de transformación que Hidalgo necesita. Y pues bueno, por su parte el presidente municipal, Julio Agustín Cruz Tovar, reconoció el respaldo del gobierno estatal para mejorar las oportunidades educativas de las juventudes del municipio. Dijo que detrás de este logro está la perseverancia de una comunidad que reconoce el valor de la educación y trabaja por el futuro de sus hijas e hijos. En representación del alumnado, Daira Zúñiga Fuentes eh agradeció a las autoridades por atender las necesidades del plantel y señaló que las nuevas instalaciones representan mejores condiciones para aprender y mayores oportunidades para su futuro. 
+Durante su visita a la Secundaria Técnica número 8, el titular de la SEP entregó dos aulas didácticas en las que fueron invertidos 3.4 millones de pesos. El funcionario invitó a las y los jóvenes a participar en la estrategia ABC de las emociones y convertirse en prometores, en promotores, perdón, de la alfabetización emocional para favorecer su bienestar integral y contribuir a una convivencia escolar armónica. También le comparto parte de lo que se dijo en este evento. 
+Natividad Castrejón: Los queremos mucho, pero los queremos bien. Los queremos sanos, los queremos felices, los queremos plenos, hagan su proyecto de vida. Todos somos valiosos, todos tenemos mucho por qué florecer, todos tenemos competencias diferentes, aprendemos a diferentes ritmos, hagan de su Hidalgo bonito lo que decidan, háganlo desde el corazón y seguramente lo van a hacer bien y van a ser felices. 
+Locutor Jesús Riveros: Bueno, pues así la información, por supuesto que emite la Secretaría de Educación Pública en este evento, donde también estuvo el director general del COBAEH, Rubén López Valdez; la directora de Incorporación, Revalidación y Equivalencia de Educación Media Superior, María Guadalupe Solís Murcia; así como autoridades municipales, directivos docentes y miembros de la comunidad.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1p_mw7HszRseL51up7Tro9mYDWLJynB6J/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Julio Agustín Cruz Tovar, Rubén López Valdez</t>
+  </si>
+  <si>
+    <t>Complejo Hidalgo Honesto fortalece la vigilancia del dinero público y la calidad de las obras</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pKmdU4coST0do2eA_3NpoU_eVX2TdEzG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Julio Menchaca,</t>
+  </si>
+  <si>
+    <t>Presenta Carlos Henkel avances económicos en Hidalgo</t>
+  </si>
+  <si>
+    <t>Y que es lo que están informando las y los secretarios, los titulares de las oficinas del gobierno del Estado ante las y los diputados de la Sexagésima Sexta Legislatura local, pues aquí le damos seguimiento a eso que están informando y que bueno, se considera un ejercicio fundamental de transparencia, rendición de cuentas y consolidación de un gobierno abierto y cercano a la ciudadanía. Así lo destacó el secretario de Desarrollo Económico, Carlos Henkel Escorza, al comparecer ante las y los diputados de la Sexagésima Sexta Legislatura del Congreso del Estado para detallar los logros alcanzados durante el cuarto año de la administración que encabeza el gobernador Julio Menchaca Salazar.   Durante su intervención, el titular de la Sedeco enfatizó que Hidalgo ha dejado de ser solo una promesa de desarrollo para convertirse en el verdadero epicentro estratégico del sector industrial en México y el enlace natural de la nación con los mercados globales, distinción alcanzada gracias a su conectividad, certidumbre jurídica e infraestructura de vanguardia.   A cuatro años de administración, hemos consolidado 130 proyectos de inversión privada con un capital histórico superior a los 147,000 millones de pesos, proyectando más de 191,000 empleos directos e indirectos, extendiendo su impacto positivo a 37 municipios de distintas regiones, subrayó el funcionario estatal. El secretario destacó que el desarrollo económico hidalguense se encuentra alineado con la visión de impulso regional del gobierno federal que encabeza la presidenta Claudia Sheinbaum Pardo, como el polo de desarrollo económico para el Bienestar Reserva Zapotlán. Este proyecto emblemático se desarrollará sobre más de 910 hectáreas con una inversión privada estimada en 10,106 millones de pesos, distribuida en cinco etapas y la generación de más de 5,000 empleos, avanzando con la selección de Nafin como fiduciario y Consorcio Deguá como desarrollador.   El Valle de Plata, refirió, se ha posicionado como emblema industrial al comercializar 915,000 metros cuadrados de suelo, representando la captación de más de 15,700 millones de pesos de capital privado en el Parque Industrial Plata. Además, se ha destinado una inversión de 19.6 millones de pesos en nueve estudios estratégicos para vía de Tizayuca y Zapotlán de Juárez, 79 millones de pesos en la repavimentación y reconstrucción de vialidades internas en los parques de Tizayuca, Mineral de la Reforma y Tepeapulco, así como 64 millones de pesos destinados al desarrollo del nuevo Parque Industrial de Tepeapulco.   En economía sectorial y como fruto de la alianza entre gobierno, academia y el sector productivo, Hidalgo obtuvo la distinción histórica de ser el estado invitado de honor en la FAMEX 2027, la plataforma aeroespacial más importante de América Latina. En otro sector mencionó, con una inversión cercana a los 20 millones de pesos, se dignifican 12 centros de abasto, tras concluir seis en 2025 que fueron Almoloya, Emiliano Zapata, Xochimilco, Pachuca, Molango y Zimapán. En 2026 avanzan las obras en mercados de Agua Blanca, Axtopan, Huichapan, Mixquiahuala, San Bartolo Tutotepec y Singuilucan, beneficiando a 1,300 comerciantes y más de 691,000 habitantes.   El programa Impulso Nafin Más Hidalgo ha alcanzado una bolsa acumulada de 2,471 millones de pesos y se han colocado más de 1,665 millones de pesos en beneficio de 764 micro, pequeñas y medianas empresas de 60 municipios. Para 2026, informó Henkel Escorza, la aportación estatal de 35 millones de pesos se multiplicó 20 veces con Nafin para alcanzar un techo financiero de hasta 700 millones de pesos.   El titular de las políticas económicas del estado resaltó que a través de Hidalgo con Potencial se destinaron 35 millones de pesos para 665 micro, pequeñas y medianas empresas de 57 municipios, y con el programa Emprendiendo Paso a Paso se canalizaron 30 millones de pesos con apoyos directos de 25,000 pesos a 1,140 emprendedores de 58 municipios, priorizando su formalización ante el Servicio de Administración Tributaria (SAT).   Para impulsar la economía social se gestionó una bolsa de 20 millones de pesos para casi 100 cooperativas, de los cuales se han ejercido 12 millones de pesos para equipar a 62 sociedades de 24 municipios. En otro de los aspectos informados por el secretario de Desarrollo Económico, en el fomento al empleo se logró un acumulado de 165 millones de pesos para 4,114 becas entregadas en 82 municipios a través de los programas Transformando con la Juventud, Tu y tu Experiencia Transforma y por otra parte a través del programa Energía que Transforma se instalan 610 sistemas fotovoltaicos aislados y con 40 millones de pesos pues se está llevando luz por primera vez a 2,440 personas en 32 municipios, así lo resaltó el secretario Carlos Henkel.   Asimismo, con Energía para el Bienestar dijo se logró la entrega de 3,737 calentadores solares en 80 municipios para beneficiar a 14,948 personas con un esfuerzo compartido de 16 millones de pesos, 50% con la aportación del gobierno estatal y el otro 50% de las propias familias participantes. Concluyó su mensaje al resaltar que los datos y proyectos que hoy se presentan, dijo Carlos Henkel, demuestran que la transformación económica se mide en resultados, se mide en inversión que se concreta, infraestructura que se conecta, empleos que se generan, empresas que crecen, en jóvenes que encuentran una oportunidad, emprendedores que formalizan su actividad en cooperativas que desarrollan sus proyectos, en comunidades que reciben energía y familias que encuentran nuevas oportunidades para mejorar sus condiciones de vida, así lo puntualizó en su comparecencia el secretario de Desarrollo Económico del Gobierno del Estado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ELx7jALN1b5G3bN3J0mCo4q3wNI1IZY3/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso del Estado de Hidalgo,Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Claudia Sheinbaum,</t>
+  </si>
+  <si>
+    <t>La audiencia para dictar sentencia contra los tres responsables del triple feminicidio, dos homicidios dolosos y un aborto forzado cometidos en Santiago Tulantepec fue diferida debido a que uno de los acusados cambió de abogado y este no contaba con el expediente completo. Con esta suspensión, el proceso suma ya 36 audiencias y se reprogramó para el próximo 21 de octubre, mientras familiares, encabezados por Mónica Sepúlveda, exigen que los tres homicidios sean clasificados legalmente como feminicidios y se aplique perspectiva de género.</t>
+  </si>
+  <si>
+    <t>TSJEH</t>
+  </si>
+  <si>
+    <t>Proceso Por Feminicidio</t>
+  </si>
+  <si>
+    <t>Santiago Tulantepec</t>
+  </si>
+  <si>
+    <t>SSH/Bol.178/2026</t>
+  </si>
+  <si>
+    <t>SSH establece la ruta para fortalecer la atención segura y de calidad en 2027</t>
+  </si>
+  <si>
+    <t>Coordinación Interinstitucional</t>
+  </si>
+  <si>
+    <t>Por otra parte, le comento que pues se ha definido la ruta, las acciones a seguir por parte de autoridades de salud para 2027. En la tercera sesión ordinaria del Comité Estatal de Calidad en Salud se aprobaron los instrumentos de planeación que orientarán las acciones institucionales durante 2027. En la sesión se aprobaron el programa anual de trabajo, el plan estatal de capacitación en calidad, el plan estatal de supervisión en materia de calidad y seguridad del paciente, así como el calendario de reuniones que tendrá este comité para el próximo año. También se revisaron los avances de acuerdos previos, las acciones de higiene de manos y los resultados de las supervisiones realizadas por el Comando Estatal Interinstitucional del Sector Salud en Hidalgo.   Entre los temas prioritarios destacaron la prevención de infecciones asociadas a la atención sanitaria y el fortalecimiento de una cultura de seguridad del paciente. Como parte de los compromisos, las instituciones participarán en la Encuesta Nacional de Cultura de Seguridad del Paciente, entregarán sus planes de mejora de higiene de manos para 2027 y actualizarán la información de sus comités de calidad, asimismo se incorporará la Coordinación Estatal de Enfermería para ampliar los trabajos de supervisión y seguimiento. La reunión también dio continuidad a las acciones de reconocimiento a los avales ciudadanos y a la participación del sector salud en el Día Internacional de la Seguridad del Paciente, con énfasis en la colaboración social y la mejora de los servicios. En la reunión participaron representantes del ISSSTE, de los Servicios Públicos de Salud, del IMSS Bienestar, la Secretaría de Salud de Hidalgo, el Hospital del Niño DIF en la entidad, el Centro de Rehabilitación Infantil Teletón, también del Centro de Rehabilitación Integral de Hidalgo, la Unidad Especializada de Atención a la Mujer, el Colegio de Enfermeras y Parteras Hidalguenses, el Colegio Mexicano de Licenciados en Enfermería, filial Hidalgo, participaron en esta reunión en la que se definen líneas de trabajo hacia 2027 en una materia de de gran importancia como lo es la salud.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JAvb1kSMEHINl-Hv7T-PWq-JQE6Ll8m1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>ISSSTE, IMSS Bienestar, Hospital del Niño DIF, Centro de Rehabilitación Integral de Hidalgo</t>
+  </si>
+  <si>
+    <t>Durante el reporte sobre el Valle de México, se dio a conocer que el gobernador del estado, Julio Menchaca Salazar, estuvo presente para acompañar a Clara Brugada Molina, jefa de Gobierno de la Ciudad de México, en el marco de su segundo informe de actividades.</t>
+  </si>
+  <si>
+    <t>Y le sigo compartiendo información del Valle de México para comentarle que el gobernador del estado, Julio Menchaca Salazar, acompañó a la jefa de gobierno de la Ciudad de México, Clara Brugada Molina, en su segundo informe de actividades.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cvNKjJeCDflxUMMYBGiNo_4bQnb-6Tfb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Panorama Informativo Pachuca</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo (SEPH), que encabeza Natividad Castrejón Valdez coordina una campaña de vacunación contra la influenza y COVID-19 en escuelas de educación básica, en colaboración con instituciones del sector salud, con el objetivo de proteger a niñas, niños y personal educativo.</t>
+  </si>
+  <si>
+    <t>Nos vamos al estado de Hidalgo. 
+La Secretaría de Educación Pública de Hidalgo (SEPH), que encabeza Natividad Castrejón Valdez coordina una campaña de vacunación contra la influenza y COVID-19 en escuelas de educación básica, en colaboración con instituciones del sector salud, con el objetivo de proteger a niñas, niños y personal educativo.
+Como parte de estas acciones, inició una jornada en la Escuela Primaria Benito Torres Oropeza de Pachuca, en coordinación con la representación estatal del Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado (ISSSTE).
+En la estrategia participan el ISSSTE, IMSS Bienestar, IMSS ordinario, Petróleos Mexicanos (Pemex) y los Servicios de Salud de Hidalgo. La campaña se desarrolla del 12 de octubre de 2026 al 2 de abril de 2027, con módulos de vacunación en las entradas de los planteles de educación básica de la entidad.
+La meta es alcanzar una cobertura del 70 por ciento al 31 de diciembre de 2026 y del 100 por ciento al concluir la campaña.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Spt951E-MhIa5GqMnZuqqcNyZyeEm3_0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Miled 97.1 FM</t>
+  </si>
+  <si>
+    <t>María Antonieta Islas</t>
+  </si>
+  <si>
+    <t>Línea En Alta Tensión</t>
+  </si>
+  <si>
+    <t>Entrevista no cumplida</t>
+  </si>
+  <si>
+    <t>Canal 12 Huejutla</t>
+  </si>
+  <si>
+    <t>Selene Ortega</t>
+  </si>
+  <si>
+    <t>Contacto Informativo N</t>
+  </si>
+  <si>
+    <t>Y bueno, continuamos en contacto informativo y tenemos en la línea al licenciado Pedro Luis Noble Monterrubio, quien es presidente del Colegio de Notarios Públicos aquí en el estado de Hidalgo. Licenciado Pedro, muy buenas noches. Hola, excelente, muy buenas noches. Les saludo con toda la precia a usted y al comandante José de Bujutla y a todo este gran auditorio que generosamente nos escucha. escucha. Licenciado, usted presenta octubre, igual que septiembre, mes del testamento. Platíquenos para los que no conocemos, la audiencia que nos escucha y nos ve, ¿qué es un testamento? Muchas gracias. Bueno, pues en principio diré que el testamento es un un un acto jurídico, una disposición de las personas, por medio de la cual, ante notarios, el testamento público abierto, ante notario, dejamos establecida nuestra voluntad para que los bienes que nos pertenecen, nuestro patrimonio, sea transmitido a las personas que nosotros decidamos en forma libre. Y técnicamente se viene como el acto jurídico por medio del cual una persona dispone de esos bienes para después de la muerte. Es un acto personalísimo. Es decir, solamente ante la presencia del notario está el interesado o la interesada. Es un acto libre y para eso el notario, pues, es difícil hacer que no nota, no tiene conocimiento o no observa que hay algunos actos que sean contrarios a la voluntad del cesador, que no hay un flujo a esa libertad. Y también es un acto revocable de tal manera que cuando una persona dice el cesamento, su disposición, la puede cambiar en libertad cuando él diga y en donde también se disponga. Esos son los elementos del testamento, Selene. Ok, a ver, ¿quiénes podrían hacer un testamento y a partir de qué edad? Pregunta bien interesante. La ley hidalguense del Código Civil prevé que las personas que tengan 16 años cumplidos pueden otorgar testamento y no hay límite de edad para dejar de dictarlo. La única condición es de que estén en su cabal comprensión de lo que están dictando, de lo que están haciendo, y pues para eso el notario certifica lo que objetivamente aprecia con sus sentidos, la conducción que se da a una persona para disponer de sus bienes. ahora si puede intervenir otra persona con el estado por ejemplo para ayudarle ya el c nacional de procedimientos civiles familiares establece la la el apoyo y llama de ayudas en el C Civil ya tiene much a se prev que no pueda firmar y as lo dice tambi la ley del notariado quien no pueda firmar porque no conoce el idioma, porque esté fracturado, etcétera, se podrá apoyar de una persona que lo haga a su ruego y encargo. Lo mismo cuando hay personas que no conocen el idioma español, Hay una ayuda de intérprete que conoce la lengua originaria, la lengua materna, y se traduce al español. Y también puede ser la lengua extranjera, por supuesto. Y bueno, esa campaña es tendente a que las personas adquiramos el hábito, la cultura, primero de la legalidad, segundo de la planeación patrimonial con la cultura testamentaria. Y eso me parece también algo muy importante, porque si muchas personas ocupan, ocupamos, contratamos un seguro para cualquier efecto automotriz, de vida, de médico, etc., pues podamos también planear la disposición de lo que hemos logrado a lo largo de años y dispongamos de esos bienes para después de la muerte. decir a quién se van a transmitir vía herederos o vía legatarios De acuerdo a ver, ¿cuáles son los precios normales cuando uno llega a la notaría y qué descuentos se aplican? En este caso se aplicaron en el mes de septiembre pero en este mes de octubre que también es mes del testamento, ¿qué descuentos se van a aplicar? Sí, mire, traemos una, estamos haciendo eco a una invitación del señor gobernador que nos ha pedido repetidas ocasiones hacer acciones pro bono ¿Qué significa el pro bono? Proviene del latín es pro bien, hacer el bien, ayudar a la gente y en ese sentido desde el año dos mil veintidós estamos aplicando honorarios reducidos para las personas de más de sesenta años estamos teniendo un honorario reducido de 900 pesos masiva. Para las personas menores de 60 años, de 16 a 60 años, tiene un honorario reducido de 2.500 pesos masiva. Y para los servidores públicos que merecen todo nuestro respeto, los miembros de las Fuerzas de Seguridad Pública, de mando coordinado, que son las policías municipales coordinadas con Seguridad P estatal la polic bancaria industrial la polic de investigaci el cuerpo de bomberos y los param de Corja Mijana, estamos aplicando un honorario reducido de quinientos pesos por testamento, más el libro por la emisión del documento. Entonces, la invitación es a que aprovechen, que se acerquen a su notaría más próxima, que platiquen con el notario, con la notaria, lo escuchan también hay un huejut en la sierra en la la cuenca del golfo por supuesto también que se acercen con su notaria, con su notario que tengan esa entrevista para platicar y expresar sus intenciones su deseo, el notario con eso se forma una idea, se redacta y le da forma a la voluntad del cesador en una escritura que se llama Testamento Público Abierto y pues ahí se contendrá la voluntad de las personas que tengan a bien disponer de sus bienes para después de la muerte. Claro que sí, y denos un ejemplo, si las personas que ahorita nos están viendo y nos escuchan, ¿qué requisitos indispensables tiene que llevar ante el notario para iniciar este trámite de testamento? Claro que sí, a ver, lo primero es identificarse plenamente con el notario, llevar la credencial del lector o el pasaporte y decir al notario cuál es su intención respecto a los bienes porque, mire, y me voy a un caso muy muy muy concreto cuando una persona fallece y no deja testamento la ley establece que se deberá de aperturar la sucesión legítima o intestamentaria se llama legítima porque se llaman a todos los legítimos derechosos a acceder a la herencia. ¿Quiénes son? Dice la ley. Los hijos, los papás. Si no hay hijos, están los papás. Si no hay papás, están los hermanos. Si no hay hermanos, están los sobrinos. Si no están los sobrinos, están los primos. Es decir, la máxima en la ley dice que el pariente cercano excluye al pariente lejano. Y si una persona no hace testamento, ya se imaginará usted, pues van a llegar todos los parientes que crean con mejores derechos y por eso se llama legítima ahora, con el testamento uno responde, uno decide quién va a heredar en forma exclusiva de la herencia, quién va a ser parte si gusta le ponemos aquí un ejemplo pensando que una persona tiene cinco hijos y en el testamento va a decidir si los deja a todos en qu proporci partes iguales partes diferenciadas si de esos cinco hijos decide que nada m 12 a los herederos as lo habr decidido el pensador porque si no se hiciera entonces entran y están convocados los cinco hijos que son del autor de la herencia del difunto Ahora, si no se hace testamento, también estarían llamados los que aparezcan con calidad de hijos. Y entonces ahí se empieza a complicar la situación, ¿no? Claro que sí, depende de cada circunstancia, ¿no? Exactamente. Entonces, por esa razón es importante que la invitación que le hacemos a la ciudadanía, a este gran público, es el que acudan con su notario más cercano de la confianza y que le platiquen al notario en una entrevista, en una charla, cuál es su deseo, que pidan orientación. Porque además aquí, un punto importante, las notarias y los notarios no cobramos la consulta, la orientación. Ya el trabajo, el hacer el documento, bueno, pues ya dijimos los montos que están ahorita en promoción para fomentar esa cultura de la planeación patrimonial. Ok, bueno, este tema sin duda da para mucho porque de repente existen muchas dudas porque como lo comentamos hace un rato, depende de cada circunstancia que presente pues el que solicita el testamento. Bueno, le agradecemos precisamente por difundir octubre igual que septiembre, mes del testamento y pues ahí estamos a la orden, agradecemos algo más que quiera dar en algún mensaje final. Gracias, Elena, pues, invitar a la ciudadanía general para que se acerquen con su notaria, con su notario, notaria, ya sea en su lugar de origen, o incluso, yo sé que nos escuchan más allá del país, en cualquier parte del mundo donde haya un consul mexicano, habrá que sacar cita para que ante el consul mexicano se pueda otorgar testamento, modificarlo o revocarlo. Esa es la grandeza de esta institución llamada testamento, porque nos permite, repito, disponer de los bienes para después de la muerte, y que tenemos en Hidalgo 94 notarías que están operando, que en el país hay cerca de 4.500, y en el mundo, pues a través de los consulados mexicanos. Ok, le agradecemos, Lick, le enviamos saludos desde la Huasteca Hidalguense. Que usted esté muy bien. Bonita noche. Muchas gracias, Linné. Saludos a todas las amigas y amigos de la que ya vimos antes. Gracias. Buenas tardes. Buenas noches.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wnI33PmNh7A3imUHfi11peAIhsj76WPS/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Sebiso/Bol.692/2026</t>
+  </si>
+  <si>
+    <t>Al décimo mes de 2026, los apoyos de los programas Bienestar y Desarrollo, Madres Trabajadoras, Bienestar de Personas Artesanas y Xantolo han sido entregados por el gobierno de Hidalgo, a través de la Secretaría de Bienestar e Inclusión Social (Sebiso), en beneficio de cerca de 4 mil personas de las regiones Huasteca y Sierra Alta.El titular de la Sebiso, Ricardo Gómez Moreno, en Huejutla, encabezó la entrega de tarjetas correspondientes a la segunda etapa de los programas sociales.</t>
+  </si>
+  <si>
+    <t>Programas Del Pueblo</t>
+  </si>
+  <si>
+    <t>Al décimo mes de 2026, los apoyos de los programas Bienestar y Desarrollo, Madres Trabajadoras, Bienestar de Personas Artesanas y Xantolo han sido entregados por el gobierno de Hidalgo, a través de la Secretaría de Bienestar e Inclusión Social (Sebiso), en beneficio de cerca de 4 mil personas de las regiones Huasteca y Sierra Alta.El titular de la Sebiso, Ricardo Gómez Moreno,  en Huejutla, encabezó la entrega de tarjetas correspondientes a la segunda etapa de los programas sociales. En esta jornada fueron convocadas 502 personas beneficiarias de Bienestar y Desarrollo, 101 de Madres Trabajadoras y 154 de Bienestar de Personas Artesanas, quienes recibirán el apoyo económico correspondiente en los próximos días.Como parte de la gira, Ricardo Gómez Moreno también encabezó la distribución de paquetes del programa Xantolo, integrados por un kilogramo de cacao y otro de azúcar, para contribuir a la preservación de las tradiciones ancestrales de la Huasteca hidalguense.Los paquetes se distribuyeron en Huautla, con 800 unidades; Atlapexco, con 618; la comunidad de Tepetitla, en Yahualica, con 393, y la localidad de Coyula, en Calnali, con 380. En total, se entregaron 2 mil 191 paquetes para igual número de familias.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16avtRn3052izE8aAFfuYBIU-nf5je-65/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Por primera vez en Hidalgo, una persona fue sentenciada por violencia familiar en su modalidad vicaria, en agravio de una mujer de Cuautepec. El caso recibió seguimiento institucional luego de que la víctima expusiera su situación en las mesas de acercamiento de bienestar y paz. La Secretaría de Gobierno coordinó la atención con las instancias correspondientes. La resolución constituye un precedente para el Estado. El Frente Nacional contra Violencia Vicaria reconoció la actuación del Ministerio Público y del juez, así como la importancia de aplicar perspectiva de género para garantizar el acceso a la justicia. La Secretaría de Gobierno informó que continuará dando seguimiento a los casos planteados en estas mesas.</t>
+  </si>
+  <si>
+    <t>Por primera vez en Hidalgo, una persona fue sentenciada por violencia familiar en su modalidad vicaria en agravio de una mujer de Coautepec. El caso recibió seguimiento institucional luego de que la víctima expusiera su situación en las mesas de acercamiento de bienestar y paz. La secretaria de gobierno coordinó la atención con las instancias correspondientes. La resolución constituye un precedente para el Estado. El Frente Nacional contra Violencia Vicaria reconoció la actuación del Ministerio Público y del Juez, así como la importancia de aplicar perspectiva de género para garantizar el acceso a la justicia. La Secretaría de Gobierno informó que continuará dando seguimiento a los casos planteados en estas mesas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1v4VLXO3BULMM1GZwQpcBTHd1KS8b7stK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Vía telefónica secretario de educación pública Natividad Castrejón Valdéz con temas de educación</t>
+  </si>
+  <si>
+    <t>Impulso A La Educación</t>
+  </si>
+  <si>
+    <t>Bueno pues va a estar con nosotros y ya está con nosotros en la línea telefónica el secretario de educación pública Natividad Castrejón Valdéz. ¿Cómo estás secretario? Buenos días. Hola Cristian, muy buenos días, gracias y saludos a todo tu auditorio. Muchísimas gracias por aceptarnos esta llamada, por regalarnos estos minutos, porque nos da muchísimo gusto como siempre saludarlo y hoy vamos a poder platicar acerca de los logros que se han obtenido a lo largo de estos cuatro años y que a propósito de eso pues se viene ya la comparecencia porque estamos en un periodo de comparecencias entonces bueno pues eso es lo que nos gustaría saber secretario ¿Cuáles considera que fueron los principales logros educativos de Hidalgo durante el último año?
+Mira Cristian, creo que tenemos muchos motivos como sociedad porque la educación es un patrimonio común donde intervenimos todos de lo que hemos ido alcanzando. Si bien es cierto que yo debo presentar pues números muy concretos, estadísticas, referencias que puedan tener una comprobación en el proceso educativo, pues lo más importante es recordar que atrás de cada cifra hay un ser humano, hay una una persona concreta que tiene sus sueños, sus dificultades, sus metas, su proyecto de vida y que no podemos reducir a nadie a una calificación y que si sólo evaluamos un área entonces estamos mutilando a un ser humano completo. Eso lo digo porque es mi convicción que formamos personas integrales y entonces tenemos que revisar en todas las áreas que hemos alcanzado ¿No? Pero bueno empezamos con las estadísticas y luego con esa referencia ¿No? Porque no me gusta que las cifras oculten los rostros ¿No?
+Claro, claro, por supuesto, aparte es todo un mundo, no nada más es una sola cosa ¿No?
+Sí, es un sistema muy grande, muy complejo. Nosotros somos aproximadamente 950 mil personas que estamos dentro de algún proceso educativo desde inicial hasta superior, hasta posgrados e intervenimos 83 mil trabajadoras, trabajadores de la educación en todos los subsistemas tanto los que atendemos directamente como Estado, la Universidad Autónoma del Estado de Hidalgo y los organismos federalizados como el CONALEP, el CBTa, el tecnológico que si bien nos coordinamos las acciones ellos tienen una relación diferente a la nuestra con la federación y todo eso ¿No? Pero bueno damos información de todos. Mira Cristian, si pudiéramos resumir primero un dato muy muy claro, es que la Secretaría tiene diferentes indicadores que nos van retroalimentando como acá he estado ¿No? Nosotros en Hidalgo cuando inició el gobierno de Julio Menchaca recibimos una Secretaría que haciendo un esfuerzo llama eficiencia terminal completa, es decir, que un niño que entra primero de primaria logre terminar la universidad en un tiempo así de manera continua y completa ¿No? Ese es como el ideal de la escuela en México. Entonces de los niños que entraron en el 2005 y terminaron en el 2022 fueron 34. Si de cada 100 niños que se inscribieron en primero en el 2005, en el 2005 perdón, en el 22 logramos 34. Bueno en tres años, este año se sostuvo el número, logramos pasar de los que entraron en el 2008 y terminaron en el 2025 a 39. Ese es el número que resume todo el trabajo del sistema educativo. En 39 de cada 100 terminan la universidad y eso nos coloca en el octavo lugar nacional en resultados completos ¿No? Y luego ya en el camino tenemos que observar cuatro niveles en los cuales en tres nos va muy bien y en uno aún estamos muy lejos de sentirnos satisfechos. En los que nos va muy bien es en primaria y en secundaria donde prácticamente hay un trabajo de muchos años, por lo menos de tres décadas muy fuerte que ha permitido que primaria ya no sea un tema preocupante ni de algo, puesto que prácticamente el 100% de los niños que llegan a primaria termina su educación. Son casos muy atípicos cuando un niño sin causa justificada se da de baja ¿No? Porque muchos se dan de baja por migración, por algún problema específico, pero así que no tengamos una causa son muy pocos. La estadística reconoce que el 100% de los alumnos de primaria terminan y eso bueno pues ya es un tema superado ¿No? No hace que profundizar la parte formativa, eso se hace todos los días y se debe hacer todos los días, pero esa es la preocupación. Secundaria igual, secundaria hace 25 años los que de alguna manera participábamos en educación de diferentes maneras, nos pedían insistir mucho a las comunidades, a las madres y padres de familia que sus hijos fueran a la secundaria ¿No? Que fueran a la secundaria, que era importante que terminara la secundaria, porque en muchas regiones se hace un proceso cultural ¿No? Como decía Manuel ya terminó sexto, ya puede hacer las labores de la región, ya puede ayudar en la siembra, en el campo, ya puede ayudar en el oficio familiar, esto ya no requiere la secundaria, entonces fue un logro también que poco a poco toda la sociedad, sobre todo las mujeres y sobre todo en comunidades indígenas, fueran accediendo a la secundaria con mayor naturalidad y eso también ya se logró. Hoy día de cada 100 chicos que entran a secundaria, este año pasado, el ciclo que informaremos, bueno la estadística que tenemos del ciclo que informamos, se graduaron 94 de cada 100 que entraron a secundaria, ahí perdemos seis, siempre tratamos de ir por ellos, buscar a ver dónde están, pero esto nos colocó en el cuarto nivel nacional en eficiencia terminal de secundaria, perdón, en eficiencia terminal de secundaria, hasta ahí otra vez, palomita, vamos muy bien. Pero luego viene educación media y es ahí donde se empiezan a complicar los temas, educación media desde el 2012, la constitución la marca como el mínimo obligatorio que debe cruzar un ciudadano mexicano, un mexicano, sin embargo, de que se apruebe la ley en la constitución, a que se genere la infraestructura material y de docentes para hacerlo posible y que la sociedad lo asuma como una obligación del estado y de la familia y un derecho del joven, pues pasa mucho tiempo, entonces nosotros encontramos un sistema muy complicado en media y creo que ahí está nuestro mayor reto, nuestro mayor desafío, puesto que en el ciclo 2019-2022, que fue el ciclo que nos entregaron a nosotros terminando, también acordarnos que pasamos ahí la pandemia y eso también movió mucho la permanencia de algunos jóvenes, que tuvieron que salir a trabajar, migraron, en fin, sólo se graduaron 63% es decir, perdimos 37 chicos de cada 100 que ingresaron a la prepa, esto nos colocó en el lugar número 30 en el país, o sea, nos fuimos hasta los últimos lugares en eficiencia de educación media. Y bueno, tres años después, con todo el esfuerzo de la sociedad, de los alumnos de papás, del gobierno, tratando de crear un andamiaje que motiva a los chicos a estar en la prepa y por eso las tabletas, los uniformes, los libros y una actividad en otras áreas, como la parte de Steam, concursos y participación de muchas áreas del arte, de la cultura, tener motivados a los jóvenes a que encuentran sentido a la permanencia en la prepa, logramos graduar el año pasado 75.6 de cada 100, es decir, hemos crecido 12.4 puntos porcentuales en eficiencia en la prepa, esto nos dice que perdemos, bueno, por una parte ingresaron seis mil alumnos más, o sea, pasamos de 33 mil a 39 mil chicos que se gradúan, son seis mil vidas, esos 12 puntos implican por año seis mil chicos que sí terminan su prepa, que ya es una cantidad considerable, pero estamos realmente ahí en el promedio nacional, el promedio nacional es de 76, entonces estamos a un punto y avanzamos siete lugares, nos colocamos en el lugar número 23, entonces fíjate, los primeros cinco lugares en primaria, el cuarto lugar en secundaria, y hoy estamos en 23, en el lugar 23 en prepa, por eso creo que ahí está nuestro mayor desafío. Por eso pues estamos ahorita construyendo 12 preparatorias nuevas, anteriormente abrimos cinco, hoy hay preparatorias en los 84 municipios, pero el tema no es de cobertura, fundamentalmente el problema, el tema es de que permanezcan los que llegan, y ahí tenemos que seguir reforzando el discurso, yo digo que es el mayor reto de este gobierno y del que sigue, que logremos que la familia, la sociedad, los jóvenes ya tengan muy grabado en su mente como parte de su desarrollo integral de personas que van a terminar la prepa, o sea, así como te dicen desde niño, tú tienes que ir a la escuela y tú tienes que estar en la secundaria, tenemos que lograr que todos podamos normalizar que terminar la preparatoria hoy en día, pues es un requisito indispensable, no solo por la parte legal, sino por las habilidades, capacidades, competencias, técnicas y humanas que el joven debe desarrollar para salir a un mundo con muchas oportunidades, pero también muy complejo, con sus propios problemas en este mundo digital y global necesitan hoy día la preparatoria, entonces creo que este gobierno todavía podemos avanzar, nuestra meta está en llegar los próximos dos años y este que terminó que aún no se mide, 25 y 26 aún no se mide porque van un año, hace como un año de retraso, creo que podemos llegar a superar el 80, 83% y quedará un reto todavía para el que siga, ahí está nuestra clave, el desafío. Y luego ya educación superior, otra vez las cosas se recomponen muy bien, porque de cada 100 chicos que llegaban a la universidad cuando llegamos nosotros, se estaban graduando 69.6, es decir, se perdían 30 chicos, este año que termina, logramos que se graduaran 84, que bueno, que permanecieran en la escuela, 84.5, es decir, subimos ahí 15 puntos porcentuales, que es un puntaje muy importante, ya tener arriba del 80% de que se gradúen, es altísimo en el país, esto nos colocó en el sexto lugar nacional, esos son los datos duros, Cristian, de qué es lo que voy a explicar, luego ya en los detalles de los programas, de las acciones, de qué estamos haciendo en cada nivel para fortalecerlo, pero en términos numéricos, así va la cosa.
+Que se dice, o se puede comentar, se puede compartir de manera muy fácil en algunos minutos, pero ha llevado un gran trabajo, porque como usted lo mencionaba, pues al inicio, cuando ustedes toman las riendas de la Secretaría de Educación Pública y cómo se deja, y ahora cómo la tienen ustedes, creo que ha sido un gran trabajo también, y estos números, a pesar de que de pronto, como usted lo menciona, a veces son 0.5, 0.7, pero son súper importantes, ya en el plano terrenal, en el plano hablando de las personas, de los estudiantes, creo que es muy importante, y más ahora, con todo lo que tiene nuestro entorno, creo que el trabajo se ha realizado, y el reto, pues es obviamente, como lo han hecho año con año, pues ir cambiando esas cifras y mejorarlo.
+Sí, ese es el reto de todos los días, tiene mucho que ver toda la comunidad, porque aprendemos en comunidad, pero en la parte cultural todavía nos falta esto que te enseñó de la educación media, todavía en muchos lugares no lo es necesario, sobre todo cuando tienen trabajos primarios, o sea, en nuestro estado es un estado muy disperso, somos el tercer estado más disperso en el país, el gobernador frecuentemente habla de las 4.800 comunidades que tenemos, menores de 5.000 habitantes, y las casi 2.500 menores de 500 habitantes, ahí suelen tener en lo local trabajos aparentemente muy sencillos, la artesanía, la gastronomía, el campo, oficios, y entonces ahí nos dicen, oye, ¿pero la prepa para qué? Pues ya vente a trabajar, el mismo muchacho, ya es joven, adolescente, fuerte, dice, no, no, no, pues yo me pongo a trabajar, o sea, ya sé hacer lo que voy a hacer, o lo que estoy haciendo, ya lo sé hacer, ¿no? Ya sé sembrar, ya sé hacer esto, ya sé hacer lo otro, ya, entonces ahí es donde el discurso tenemos que socializarlo más, porque la educación media no solo es para que aprendan más cosas del hacer, es donde terminamos de formar al ser humano, ¿no? O sea, en su parte de identidad, en su parte de acción lógica, en su parte de los vínculos que va a tener con el otro y con la sociedad, en su salud socioemocional, es decir, en todos esos resortes que van a ir definiendo su proyecto de vida, y el mejor lugar, pues es la escuela, y necesitamos enamorarlos de su escuela, ¿no? Que se sientan allí, que bien, que, aunque sea por los amigos, diga, bueno, pues por lo menos ahí tengo mis amigos y algo aprenderé ahí en el camino, ¿no? Pero bueno, eso me sirve de convivencia, le sirve de ver al otro, de compartir con el otro, porque con el otro construimos la paz en las comunidades, con el otro construimos la seguridad en nuestras sociedades, en fin, por ahí tenemos que seguir insistiendo todos, el Estado, los maestros, los papás, y ojalá que, y lo sé que lo vamos a lograr, sé que entre todos vamos a aumentar el nivel de eficiencia con los jóvenes, porque bueno, para el Estado está muy claro, y cuando digo Estado, me refiero a todas las instituciones del Estado, ¿no? Hoy los jóvenes requieren estar más tiempo en la escuela, para que tengan una formación completa, más integrados. Y así será.
+Secretario, muchas gracias por estas palabras que nos ha compartido, sin duda es un gran trabajo el que seguramente se ha realizado, y estaremos muy pendientes, pues ya en próximos días, que será la comparecencia, invitar también, por supuesto, a las papás, a las mamás, para que puedan seguirla a través de la página de Facebook de la SEP, y por supuesto del Congreso, porque hay muchos resultados muy importantes, y el trabajo que se ha realizado es súper importante también, que se conozca por parte de toda la población. Secretario, le agradecemos muchísimo este espacio.
+Gracias Cristian, te comento finalmente, perdone que esta semana anduve allá por tu región, estuve en Metztitlán, en Acaxochitlán, en Tecozautla, se canceló un evento en Atotonilco de Tula, regresaremos en unos días, pero mira, se abrió la Universidad Rosario Castellanos, ahí en Tecozautla, fue un gusto verlos, ya tienen una nueva universidad, naciente, pero empezaron 210 chicos a estudiar en esa nueva universidad, vamos a abrir, bueno, ya empezaron clases en una sede alterna, dos preparatorias en Margarita Maza, en Atotonilco de Tula, y una en Tula, ya están las licitaciones para iniciar las construcciones de los edificios, y vamos a empezar también en las próximas semanas los procesos internos de licitación, para construir un CAM, un Centro de Atención Múltiple en Tepeji, entonces es una región que por su crecimiento y su explosión demográfica, requiere que tengamos una respuesta más fuerte en diferentes temas, en el cuidado de los niños y otro en los chicos de prepa.
+Para que no haya pretexto, ¿no, secretario? Por todos lados. Que tengan la opción más cercana y que tengan ahí, por todos lados, se les aparezca una prepa a una universidad, así es, ese es mi lugar, ¿no? No, y además con los apoyos que se han dado, que también han sido parte fundamental, creo que ya no hay pretexto en estos tiempos para los papás, y a veces el tema era la economía, ahora creo que el gobierno ha estado muy de la mano con eso, entonces pues no hay pretexto para seguir estudiando.
+Les ayuda, les facilita la vida.
+Así es. Y gracias, Cristian, pues agradezco mucho la oportunidad y te mando un fuerte abrazo. Muchísimas gracias, secretario, pues aquí lo esperamos cuando ande por esta región, aquí tiene su casa, los micrófonos de Super Estéreo y de Enfoque Regional, cuando usted guste de pasadita saludarnos, aquí lo recibimos.
+Perfecto. Saludos.
+Gracias, secretario, que esté muy bien, hasta luego, buen día.
+El secretario de Educación Pública con nosotros en esta mañana a través de Enfoque Regional, que tendrá en próximos días su comparecencia, para que ustedes sigan estos resultados en esta comparecencia que hará la siguiente semana, bueno, pues pueden seguir la página de la Secretaría de Educación Pública de Hidalgo y también a través del Congreso esta transmisión que se hace en vivo y que es pública. Vamos rapidísimo a la pausa y volvemos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-v_wpqv5yhPSEP_Nx6oHev7jxYvE7RGc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Integrantes del Colectivo Madres Buscadoras de Hidalgo, se manifestaron en Plaza Juárez de Pachuca y posteriormente marcharon hacia la Comisión de Búsqueda de Personas de Hidalgo, para exigir avances en la localización de sus familiares, así lo refirió una de las madres buscadoras, quién desde el 24 de julio de 2025 se mantiene en la búsqueda de su hijo Cruz Giovanni Villegas Ruiz, de 31 años de edad.Giovanni desapareció en el municipio de Zempoala y de acuerdo con su mamá al encontrarse en compañía de otros amigos fue obligado a subir a un vehículo y desde entonces no ha sido localizado. Detalló además que su carpeta de investigación no ha presentado avances. «Vengo del colectivo de Madres Buscadoras de Hidalgo y pues yo busco este la ayuda para encontrar a mi hijo que desapareció el 24 de julio del 2025 en Santiago Tepeyahualco municipio de Zempoala.</t>
+  </si>
+  <si>
+    <t>Le comento que el colectivo Madres Buscadoras de Hidalgo realizó una marcha pacífica en Pachuca para exigir la localización de sus familiares. Voy contigo, Jack Servino  Integrantes del Colectivo Madres Buscadoras de Hidalgo, se manifestaron en Plaza Juárez  de Pachuca y posteriormente marcharon hacia la Comisión de Búsqueda de Personas de Hidalgo, para exigir avances en la localización de sus familiares, así lo refirió una de las madres buscadoras, quién desde el 24 de julio de 2025 se mantiene en la búsqueda de su hijo Cruz Giovanni Villegas Ruiz, de 31 años de edad.Giovanni desapareció en el municipio de Zempoala y de acuerdo con su mamá al encontrarse en compañía de otros amigos fue obligado a subir a un vehículo y desde entonces no ha sido localizado. Detalló además que su carpeta de investigación no ha presentado avances. «Vengo del colectivo de Madres Buscadoras de Hidalgo y pues yo busco este la ayuda para encontrar a mi hijo que desapareció el 24 de julio del 2025 en Santiago Tepeyahualco municipio de Zempoala.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NCubyLc4xizYx5LjTdLRvmdrgUrOICwh/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Hablando de comparecencias en el marco de la glosa del cuarto informe del gobernador Julio Menchaca Salazar, el secretario de la Contraloría Álvaro Bardales Ramírez destacó la consolidación del complejo Hidalgo honesto como una de las principales herramientas del estado para prevenir la corrupción,</t>
+  </si>
+  <si>
+    <t>Hablando de comparecencias en el marco de la glosa del cuarto informe del gobernador Julio Menchaca Salazar, el secretario de la Contraloría Álvaro Bardales Ramírez destacó la consolidación del complejo Hidalgo honesto como una de las principales herramientas del estado para prevenir la corrupción, fiscalizar los recursos públicos y verificar la calidad de las obras. A cuatro años de gobierno contamos con una institución sólida y con mejores capacidades de fiscalización, control, investigación y prevención. El propósito es el mismo, cerrar espacios a la corrupción y evitar que vuelvan a repetirse las prácticas que dañaron el servicio público. Las revisiones, auditorías e investigaciones permiten identificar irregularidades, obras inexistentes o deficientes, empresas utilizadas para simular operaciones, contrataciones sin sustento, personas que cobran sin cumplir sus funciones, duplicidad de plazas, sistemas tecnológicos que no responden a las necesidades institucionales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lAPH7mq5R0ys1ZsHnuzTSqc658er7Mzc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Otro tema que ha llamado la atención en Hidalgo es la prohibición de las corridas de toros, aquí en el estado sigue dando de qué hablar y durante la comparecencia de la secretaria de cultura Neyda Naranjo, el diputado Marco Antonio Mendoza Bustamante cuestionó a la funcionaria sobre este tema, el tauromachi es parte de la cultura hidalguense</t>
+  </si>
+  <si>
+    <t>Otro tema que ha llamado la atención en Hidalgo es la prohibición de las corridas de toros, aquí en el estado sigue dando de qué hablar y durante la comparecencia de la secretaria de cultura Neida Naranjo, el diputado Marco Antonio Mendoza Bustamante cuestionó a la funcionaria sobre este tema, el tauromachi es parte de la cultura hidalguense y si bien es un tema que genera debate público legítimo y posturas encontradas, también es innegable que ha formado parte de expresiones culturales, literarias, históricas y comunitarias de México y de manera particular de nuestra entidad, preguntarle cuál es la postura institucional de la secretaría de cultura del estado de Hidalgo frente a la tauromaquia, la fiesta brava y consecuentemente del gobierno del estado, la reconoce como una manifestación cultural con valor histórico, identitario y comunitario, considera que debe protegerse, regularse, discutirse o excluirse de la política cultural en el estado y qué criterios utiliza su dependencia para garantizar que este debate no se resuelva desde la censura o la descalificación, sino desde el diálogo informado, el respecto a la diversidad cultural y la responsabilidad pública, qué dijo la secretaria de cultura, dijo y dejó en claro que la información ya fue enviada al congreso de Hidalgo y que se está a favor de los espectáculos sin sangre, por el tema de tauromaquia ya ha sido enviada la contestación por parte de la secretaría de cultura como fue solicitada y decirle que desde la secretaría de cultura estamos a favor de los espectáculos sin sangre, reconocemos como manifestación cultural porque finalmente eso es lo que representa, sin embargo, se ha enviado ya la contestación a esta soberanía y en espera de la propuesta que se había decidido, que es la consulta ciudadana para el 6 de junio del 2026, sin embargo nos reiteramos a las órdenes diputados de poder trabajar de manera conjunta será una consulta que tendrán que llevar a cabo los taurinos y los antitaurinos, habrá gente que hará campaña a favor de la tauromaquia en Hidalgo y habrá quien diga que no, es todo un tema muy polémico por cierto que se va a llevar a cabo, que va a tomar mucha fuerza el próximo 2027 porque será justamente en junio cuando se lleve a cabo la consulta</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zQl0zbvdw3KsPdJ_4c3kvOM2vNHT1VvK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Marco Antonio Mendoza</t>
+  </si>
+  <si>
+    <t>Y también déjeme platicarle que Hidalgo suma 130 proyectos de inversión privada por más de 147 mil millones de pesos, con una proyección de 191 mil empleos directos e indirectos en 37 municipios. Así lo informó el secretario de Desarrollo Económico, Carlos Henkel Escorza, durante su comparecencia ante el Congreso Estatal. Entre los proyectos destacó el Polo de Desarrollo para el Bienestar, Reserva Zapotlán, que prevé una inversión de más de 10 mil millones de pesos y la creación de 5 mil empleos.</t>
+  </si>
+  <si>
+    <t>Y también déjeme platicarle que Hidalgo suma 130 proyectos de inversión privada por más de 147 mil millones de pesos, con una proyección de 191 mil empleos directos e indirectos en 37 municipios. Así lo informó el secretario de Desarrollo Económico, Carlos Henkel Escorza, durante su comparecencia ante el Congreso Estatal. Entre los proyectos destacó el Polo de Desarrollo para el Bienestar, Reserva Zapotlán, que prevé una inversión de más de 10 mil millones de pesos y la creación de 5 mil empleos. Henkel señaló que estos resultados reflejan el avance de la transformación económica de Hidalgo.Los resultados de esta visión son claros y medibles. A cuatro años de administración hemos consolidado 130 proyectos de inversión privada con un capital histórico superior a los 147 mil millones de pesos, proyectando más de 191 mil empleos directos e indirectos, extendiendo su impacto positivo a 37 municipios de nuestras distintas regiones. Esta confianza deposita a nuestro estado como un epicentro industrial donde la llegada de sectores estratégicos como el farmacéutico, automotriz, energías limpias, logístico, minero e industrial traduce el crecimiento económico en una plataforma de oportunidades incluyente, justa y sostenible para las familias hidalguenses. Uno de los proyectos emblemáticos que mejor representa esta transformación es el Polo de Desarrollo Económico para el Bienestar Reserva Zapotlán. Dimos seguimiento a su formalización mediante la selección del fiduciario y del Consorcio DEGUA como desarrollador, estimando una inversión de capital privado de 10 mil 106 millones de pesos distribuido en cinco etapas y la generación de más de 5 mil empleos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xWfyAXsHQSaqB0weas40fSO3gc1JtYMn/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La actividad pecuaria de San Pedro Tlaquilpan contará con mayor disponibilidad de agua durante la temporada de estiaje, con la inauguración de una olla de captación, almacenamiento y aprovechamiento hídrico, cuya capacidad supera los 3.2 millones de litros.El titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh), Napoleón González Pérez, encabezó la entrega de esta infraestructura, construida con una inversión de más de 2 millones de pesos,</t>
+  </si>
+  <si>
+    <t>La actividad pecuaria de San Pedro Tlaquilpan  contará con mayor disponibilidad de agua durante la temporada de estiaje, con la inauguración de una olla de captación, almacenamiento y aprovechamiento hídrico, cuya capacidad supera los 3.2 millones de litros.El titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh), Napoleón González Pérez, encabezó la entrega de esta infraestructura, construida con una inversión de más de 2 millones de pesos, La obra permitirá almacenar hasta 3 millones 243 mil litros de agua y facilitar su conducción mediante 80 metros lineales construidos para el ingreso del recurso, además de líneas de conducción y trabajos complementarios de conservación.Con esta infraestructura se busca reactivar y dar continuidad a las actividades ganaderas de la región, al contar con una fuente de abastecimiento que contribuya a enfrentar los periodos de escasez de lluvias y favorezca la producción pecuaria.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1W3--zS0v5Ku6PSzEe9w5Q8CYybdvjkXL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1t_RCXTdoA8B-pk8H7B687IWvtcapuBoO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Cristian Yahir Castañeda de movilidad y transporte.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SGBajPnGuHzSljE4H6v_nCAqdP8AyjsO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1c8yllRusOzj1zVQaHXEMfLJDYtLAfoTg/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Paola García , Sarahi Pineda</t>
+  </si>
+  <si>
+    <t>En respaldo a la transformación que se vive en otros rincones del país. El gobernador Julio Menchaca Salazar acompañó a la jefa de gobierno de la Ciudad de México, Clara Brugada, en su segundo informe de actividades, en el que el mandatario de Hidalgo destacó que con resultados, honestidad, cercanía y amor, se mejoran las condiciones de vida de las familias mexicanas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bsesuYpnqdho8CB1TwU_MuaWQd4Ch4Bo/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha dice: «Muy buenos días. En Panorama Informativo quiero hacer una denuncia por la falta de agua en la calle Arnulfo G. Farías, esquina con Magnolia. Ya llevamos tres días sin suministro de agua potable». Con mucho gusto, aquí la estamos pasando de una vez.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Nz3VjPQrybiqM5uVtGl_apgOP7WZVTXw/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha 0825. Luz, ¿cómo está, señora Luz? Dice: Muy buenos días, Lalo. Nos tomó desprevenidos la falta de agua en la colonia Nueva Francisco I. Madero, ya que no se notificó por parte de CAASIM». ¡Ah, caray! Pues vamos a checarlo. «Que nos envíen pipas</t>
+  </si>
+  <si>
+    <t>Radioescucha  0825. Luz, ¿cómo está, señora Luz? Dice: Muy buenos días, Lalo. Nos tomó desprevenidos la falta de agua en la colonia Nueva Francisco I. Madero, ya que no se notificó por parte de CAASIM». ¡Ah, caray! Pues vamos a checarlo. «Que nos envíen pipas</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Z352WcxpQqF6CUHKHmyOdHDauNeRBcPl/view?usp=drivesdk</t>
   </si>
 </sst>
 </file>
@@ -1838,8 +1727,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X60" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X60" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X49" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X49" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -2235,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -2309,31 +2198,31 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -2341,133 +2230,127 @@
         <v>33</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="C2" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S2" s="5">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>96</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U2" s="5"/>
       <c r="V2" s="5"/>
-      <c r="W2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>98</v>
-      </c>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="6">
+        <v>46310</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S3" s="3">
+        <v>38</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S3" s="3">
-        <v>140</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -2476,310 +2359,316 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S4" s="3">
+        <v>57</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S4" s="3">
-        <v>118</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="V4" s="3"/>
-      <c r="W4" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C5" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S5" s="3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U5" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
+      <c r="W5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C6" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S6" s="3">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="T6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="W6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="U6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S7" s="3">
+        <v>155</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="S7" s="3">
-        <v>104</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U7" s="3" t="s">
+      <c r="V7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="W7" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="C8" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>17</v>
@@ -2788,936 +2677,924 @@
         <v>18</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S8" s="3">
+        <v>150</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U8" s="3"/>
       <c r="V8" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S9" s="3">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
+      <c r="W9" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="C10" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S10" s="3">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U10" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="X10" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S11" s="3">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C12" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="S12" s="3">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U12" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C13" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="S13" s="3">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="X13" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S14" s="3">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>96</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="X14" s="3"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="C15" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S15" s="3">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>96</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="X15" s="3"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="M16" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S16" s="3">
+        <v>32</v>
+      </c>
+      <c r="T16" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S16" s="3">
-        <v>205</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>179</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="X16" s="3"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S17" s="3">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>184</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>191</v>
       </c>
       <c r="C18" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S18" s="3">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="C19" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="M19" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S19" s="3">
-        <v>384</v>
+        <v>72</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="W19" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="X19" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S20" s="3">
+        <v>56</v>
+      </c>
+      <c r="T20" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S20" s="3">
-        <v>228</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="W20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>194</v>
-      </c>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C21" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S21" s="3">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
@@ -3726,152 +3603,168 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C22" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
+      <c r="P22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="R22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="S22" s="3">
+        <v>71</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
+      <c r="W22" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="X22" s="3"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="C23" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S23" s="3">
-        <v>70</v>
+        <v>365</v>
       </c>
       <c r="T23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W23" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C24" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>33</v>
@@ -3880,755 +3773,725 @@
         <v>33</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S24" s="3">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>96</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U24" s="3"/>
       <c r="V24" s="3"/>
-      <c r="W24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>169</v>
-      </c>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="C25" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S25" s="3">
+        <v>43</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="W25" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="S25" s="3">
-        <v>144</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>225</v>
       </c>
       <c r="C26" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>213</v>
+        <v>23</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>213</v>
+        <v>23</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S26" s="3">
-        <v>492</v>
+        <v>188</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C27" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>220</v>
+        <v>151</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="Q27" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S27" s="3">
         <v>222</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S27" s="3">
-        <v>147</v>
-      </c>
       <c r="T27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U27" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V27" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="C28" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="P28" s="3"/>
       <c r="Q28" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S28" s="3">
-        <v>50</v>
+        <v>326</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U28" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="X28" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C29" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>213</v>
+        <v>97</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>213</v>
+        <v>5</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>215</v>
+        <v>32</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S29" s="3">
-        <v>505</v>
+        <v>427</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U29" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V29" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="C30" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="S30" s="3">
-        <v>341</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="V30" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="W30" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="X30" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="C31" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>34</v>
+        <v>248</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="S31" s="3">
-        <v>390</v>
+        <v>144</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="W31" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="X31" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="C32" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="R32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S32" s="3">
+        <v>17</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="S32" s="3">
-        <v>179</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C33" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S33" s="3">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U33" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
+      <c r="W33" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="X33" s="3"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="C34" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>17</v>
+        <v>262</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S34" s="3">
-        <v>53</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
       <c r="U34" s="3"/>
-      <c r="V34" s="3" t="s">
-        <v>254</v>
-      </c>
+      <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>24</v>
@@ -4637,157 +4500,149 @@
         <v>46309</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>15</v>
+        <v>263</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>214</v>
+        <v>102</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S35" s="3">
+        <v>691</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="S35" s="3">
-        <v>621</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>169</v>
-      </c>
+      <c r="X35" s="3"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="C36" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>22</v>
+        <v>255</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="S36" s="3">
-        <v>235</v>
+        <v>84</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>96</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="X36" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="X36" s="3"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>262</v>
+        <v>168</v>
       </c>
       <c r="C37" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>25</v>
@@ -4796,10 +4651,10 @@
         <v>26</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>17</v>
@@ -4808,52 +4663,56 @@
         <v>18</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>264</v>
+        <v>170</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S37" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
+      <c r="V37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="X37" s="3"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>25</v>
@@ -4862,108 +4721,112 @@
         <v>26</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S38" s="3">
-        <v>92</v>
+        <v>1147</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
+      <c r="V38" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="W38" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="X38" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
+        <v>14</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>46310</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>270</v>
+        <v>19</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S39" s="3">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
@@ -4972,34 +4835,34 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="C40" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>17</v>
@@ -5008,64 +4871,64 @@
         <v>18</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>275</v>
+        <v>32</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>104</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="R40" s="3"/>
       <c r="S40" s="3">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
+      <c r="W40" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="X40" s="3"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>17</v>
@@ -5074,54 +4937,56 @@
         <v>18</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S41" s="3">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U41" s="3"/>
-      <c r="V41" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>231</v>
+        <v>117</v>
       </c>
       <c r="C42" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>25</v>
@@ -5130,7 +4995,7 @@
         <v>26</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -5142,303 +5007,305 @@
         <v>18</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>19</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S42" s="3">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="s">
-        <v>236</v>
+        <v>96</v>
       </c>
       <c r="X42" s="3"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="C43" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>26</v>
+        <v>255</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S43" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
+      <c r="W43" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="X43" s="3"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>286</v>
+        <v>76</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>26</v>
+        <v>255</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>287</v>
+        <v>76</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S44" s="3">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="X44" s="3"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
+        <v>2</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="C45" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>290</v>
+        <v>42</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>26</v>
+        <v>255</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S45" s="3">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
+      <c r="W45" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="X45" s="3"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>293</v>
+        <v>45</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>26</v>
+        <v>255</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>294</v>
+        <v>44</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>295</v>
+        <v>45</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S46" s="3">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="s">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="X46" s="3"/>
     </row>
@@ -5447,19 +5314,19 @@
         <v>22</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="C47" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>25</v>
@@ -5468,110 +5335,112 @@
         <v>26</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="S47" s="3">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V47" s="3"/>
       <c r="W47" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="X47" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G48" s="3" t="s">
+      <c r="J48" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I48" s="3" t="s">
+      <c r="K48" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>302</v>
+        <v>39</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S48" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -5580,817 +5449,69 @@
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>18</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="S49" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>15</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q50" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="R50" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S50" s="3">
-        <v>391</v>
-      </c>
-      <c r="T50" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="W50" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="X50" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>14</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="R51" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S51" s="3">
-        <v>41</v>
-      </c>
-      <c r="T51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>13</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C52" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S52" s="3">
-        <v>9</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="X52" s="3"/>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
-        <v>12</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P53" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q53" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="R53" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S53" s="3">
-        <v>8</v>
-      </c>
-      <c r="T53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>11</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C54" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="S54" s="3">
-        <v>79</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>10</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C55" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q55" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="R55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="S55" s="3">
-        <v>72</v>
-      </c>
-      <c r="T55" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <v>9</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q56" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S56" s="3">
-        <v>86</v>
-      </c>
-      <c r="T56" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
-        <v>4</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S57" s="3">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="X57" s="3"/>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
-        <v>3</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S58" s="3">
-        <v>2</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="X58" s="3"/>
-    </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
-        <v>2</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="X59" s="3"/>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
-        <v>1</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S60" s="3">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="X60" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47E219C-80DA-4F72-9477-01DC6EBA56BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DD2A14-CA21-4C15-A67C-8104FD813A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="372">
   <si>
     <t>#</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Municipio</t>
   </si>
   <si>
-    <t>Súper Stéreo 100.5 FM</t>
-  </si>
-  <si>
     <t>Noticia</t>
   </si>
   <si>
@@ -101,15 +98,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Christian García</t>
-  </si>
-  <si>
-    <t>Enfoque Regional Matutino</t>
-  </si>
-  <si>
-    <t>Vacunación</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
@@ -122,9 +110,6 @@
     <t>Segobh</t>
   </si>
   <si>
-    <t>Acir 92.5 FM</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
@@ -134,27 +119,12 @@
     <t>Opinión</t>
   </si>
   <si>
-    <t>Abasto de agua</t>
-  </si>
-  <si>
-    <t>Eulalio Larrieta</t>
-  </si>
-  <si>
     <t>Boletín</t>
   </si>
   <si>
-    <t>Eulalio Larrieta agradece a Cristian Yahir Castañeda supervisor de la región Pachuca quien nos va atender los reportes que correspondan a la SEMOT</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
-    <t>Atención Ciudadana</t>
-  </si>
-  <si>
-    <t>Eulalio Larrieta agradece Paola García y Lic. Sarahi Pineda, por estar atentas a los mensajes de la ciudadanía y por atenderlos.</t>
-  </si>
-  <si>
     <t>NQ 90.1 FM</t>
   </si>
   <si>
@@ -209,9 +179,6 @@
     <t>Saderh</t>
   </si>
   <si>
-    <t>Eulalio Larrieta agradece a Jair Martínez de la SEGOBH, porque esta al pendiente de lo que se necesite y los reportes.</t>
-  </si>
-  <si>
     <t>DIFH</t>
   </si>
   <si>
@@ -221,57 +188,18 @@
     <t>OCSAD</t>
   </si>
   <si>
-    <t>Entrevista pautada</t>
-  </si>
-  <si>
-    <t>Testamento</t>
-  </si>
-  <si>
-    <t>Iza</t>
-  </si>
-  <si>
-    <t>Localización de cuerpo</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1929/2026</t>
-  </si>
-  <si>
     <t>SC/Bol.082/2026</t>
   </si>
   <si>
     <t>Informe DIFH</t>
   </si>
   <si>
-    <t>Zapotlán</t>
-  </si>
-  <si>
-    <t>Miled 97.1 FM</t>
-  </si>
-  <si>
-    <t>María Antonieta Islas</t>
-  </si>
-  <si>
-    <t>Línea En Alta Tensión</t>
-  </si>
-  <si>
     <t>DIFH/Bol.340/2026</t>
   </si>
   <si>
-    <t>Durante su comparecencia ante el Congreso del Estado en el marco del análisis del cuarto informe de gobierno, el titular de la Secretaría de Agricultura y Desarrollo Rural (SADERH), Napoleón González Pérez, destacó una inversión histórica de 721 millones de pesos destinada al campo durante 2026, beneficiando a más de 487,900 familias rurales. El funcionario subrayó los avances en programas de acompañamiento técnico, mecanización con la adquisición de tractores, certificación de 123 unidades de producción en inocuidad por el Senasica, y la atención fitosanitaria frente a problemáticas como el gusano barrenador. Asimismo, resaltó la asignación de más de 403.8 millones de pesos en infraestructura hidroagrícola para optimizar el aprovechamiento del agua en el estado.</t>
-  </si>
-  <si>
-    <t>Positiva</t>
-  </si>
-  <si>
     <t>Saderh/Bol.84/2026</t>
   </si>
   <si>
-    <t>Durante la presentación de su cuarto informe de actividades, la presidenta del Patronato del Sistema DIF Hidalgo, Edda Vite Ramos, destacó las acciones implementadas tras la suspensión del ejercicio anterior debido a la vaguada monzónica. Entre los logros resaltados se encuentran la entrega de despensas y cobijos mediante puentes aéreos, la incorporación del modelo Nacional Pilares con 113 centros activos, la entrega de becas a 2,968 usuarios con una inversión de 6,015,000 pesos, y la restitución del derecho a vivir en familia a 61 niñas, niños y adolescentes mediante adopciones agilizadas en coordinación con el Poder Judicial del Estado. Asimismo, subrayó el trabajo coordinado con el Congreso del Estado para la creación de Procuradurías Municipales de protección a la infancia.</t>
-  </si>
-  <si>
-    <t>Continuamos en la información en este inicio de fin de semana Edda Vite Ramos, presidenta del Patronato del Sistema DIF Hidalgo, presentó su cuarto informe de actividades. El acto contó con la presencia de Edda Vite Ramos, titular del Sistema Nacional DIF; el gobernador Julio Menchaca Salazar, a quienes Edda Vite agradeció su respaldo y colaboración. Este ejercicio de transparencia se ha realizado luego de que fue interrumpido en 2025 debido a las labores de apoyo brindadas por el organismo ante la emergencia ocasionada por la vaguada monzónica. Rosa María tiene la información. Durante su cuarto informe de actividades, la presidenta del Patronato del DIF Hidalgo, Edda Vite Ramos, informó sobre los proyectos que llevarán a cabo para el cierre de la actual administración, en donde destacó la rehabilitación y creación de nuevos espacios. Detalló que este año entrará en funcionamiento la nueva Casa Cuna, en donde fue rehabilitado el primer piso, se construyó el segundo piso y se invirtió en equipamiento; asimismo, fue remodelada totalmente la Casa del Niño y del Adolescente. Antes de concluir esta administración, precisó que se construirá el nuevo taller de órtesis y prótesis, así como tres bodegas. De igual manera, se ampliarán diferentes áreas del Centro de Rehabilitación Regional de Ixmiquilpan. Se construirán dos centros de atención infantil, uno en la colonia Matilde y otro en San Bartolo, en el municipio de Pachuca. Además, se construirá un edificio para incrementar los ingresos para seguir apoyando la asistencia social, aunque no brindó detalles de este proyecto. Por otra parte, subrayó que identificaron la necesidad de reformar la Ley de Asistencia Social con el fin de que niños, niñas y adolescentes se vieran protegidos, por lo que presentó al Congreso la reforma de la ley en octubre de 2025, que permite que las unidades de primer contacto de 51 municipios transiten a Procuraduría Municipal para atender la niñez y la adolescencia cuando sus derechos hayan sido violentados.</t>
-  </si>
-  <si>
     <t>SEPH/Bol.1930/2026</t>
   </si>
   <si>
@@ -281,106 +209,967 @@
     <t>Fomento A La Lectura</t>
   </si>
   <si>
-    <t>Informativa</t>
-  </si>
-  <si>
-    <t>Destaca Saderh inversión histórica de 721 mdp para el campo hidalguense</t>
-  </si>
-  <si>
-    <t>SSPH/Bol.985/2026</t>
-  </si>
-  <si>
-    <t>SSPH fortalece la seguridad en Hidalgo: más de 26 mil personas detenidas y 7 millones de litros de hidrocarburo incautados</t>
-  </si>
-  <si>
-    <t>Vía telefónica notario Pedro Luis Noble Monterrubio, presidente del Colegio de Notarios del Estado de Hidalgo con el tema: Octubre, igual que septiembre, mes del testamento</t>
-  </si>
-  <si>
-    <t>La Secretaría de Educación Pública de Hidalgo que reunió 5,932 libros durante la cuarta edición del Kilómetro del Libro. Los ejemplares fortalecerán bibliotecas de escuelas públicas de educación básica principalmente en comunidades alejadas y vulnerables. De los libros recaudados, 3,000 fueron donados por la Fundación Elena Poniatowska Amor y 2,932 por personal de distintas áreas de la dependencia. La iniciativa busca acercar la lectura a niñas, niños y jóvenes y apoyar el desarrollo de habilidades como la comprensión lectora y el pensamiento crítico que tanta falta hace hoy en día.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Educación Pública coordina una campaña de vacunación contra la influenza y COVID-19 en escuelas de educación básica de Hidalgo, esto en colaboración con instituciones del sector salud. Los módulos se instalarán en las entradas de los planteles y funcionarán del 12 de octubre al 2 de abril de 2027. La meta es alcanzar el 70% de cobertura al cierre de este año y llegar al 100% al concluir la campaña. En la estrategia participan el ISSSTE, el IMSS-Bienestar, el IMSS-Ordinario, Pemex y los Servicios de Salud de Hidalgo.</t>
-  </si>
-  <si>
-    <t>El cuerpo de una persona fue localizado en una obra en construcción ubicada entre tierras de cultivo en el municipio de Zapotlán de Juárez. De acuerdo con los reportes, estaba entre bloques de concreto y presentaba avanzado estado de descomposición. La identidad de la persona y las causas de su muerte no han sido confirmadas. Como señas de vestimenta, se informó que portaba tenis blancos, pantalón de mezclilla y una sudadera gris. Las autoridades realizarán las investigaciones correspondientes.</t>
-  </si>
-  <si>
-    <t>SSPH/Bol.984/2026</t>
-  </si>
-  <si>
-    <t>Estamos ya casi casi terminando, pero déjeme platicarles que la persecución de un tractocamión presuntamente relacionado con el robo de carga terminó con una persona detenida y el aseguramiento de la unidad, así como de dos semirremolques, esto lo informó la Secretaría de Seguridad Pública de Hidalgo.E</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>El secretario de la Contraloría de Hidalgo, Álvaro Bardales Ramírez, confirmó ante el Congreso del Estado que se han detenido a diez presidentes municipales que estaban en funciones por delitos vinculados a hechos de corrupción.Hoy Hidalgo es el primer lugar, desafortunadamente, en denuncias penales por hechos de corrupción. Presentamos cerca de cien denuncias contra quienes, con tolerancia, complicidad, desviaron recursos destinados a obras públicas y servicios esenciales. Se logró la detención de 25 personas, entre ellas un exsecretario, un exoficial mayor y diez presidentes municipales, diez alcaldes que se encontraban en funciones y fue a mitad de su periodo que por hechos de corrupción tuvieron que dejar el cargo que tenían.</t>
-  </si>
-  <si>
-    <t>La presidenta del Patronato del DIF Hidalgo, Edda Vite Ramos, presentó su cuarto informe de actividades con resultados en salud, alimentación, educación y atención cercana a grupos prioritarios. Entre las acciones destacó la puesta en marcha del Centro de Salud Mental Pilares con una inversión superior a 12 millones de pesos y el apoyo a más de 300 familias con integrantes con discapacidad para impulsar proyectos productivos.</t>
-  </si>
-  <si>
-    <t>SC/Bol.083/2026</t>
-  </si>
-  <si>
-    <t>La Contraloría de Hidalgo, Transparencia para el Pueblo y los súper agentes de la legalidad, ofrecen pláticas y talleres gratuitos para prevenir riesgos digitales entre niñas, niños y adolescentes. Las actividades están dirigidas a estudiantes, docentes y familias y además brindan herramientas para proteger datos personales, reconocer situaciones de ciberacoso o violencia digital y promover un uso responsable de Internet. También busca fortalecer el acompañamiento para detectar y atender a tiempo posibles riesgos en línea. Las comunidades escolares interesadas pueden solicitar estas actividades con las instituciones participantes.</t>
-  </si>
-  <si>
-    <t>Entornos digitales seguridad</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad Pública, Salvador Cruz Neri, habló sobre la fosa clandestina localizada en los límites de Hidalgo y Estado de México. La Fosa, la Comisión de Búsqueda de Personas del Estado de Hidalgo, todos los días hace, camina y hace acciones en busca de personas desaparecidas, ¿no? En coordinación con la Procuraduría del Estado. La información que yo tengo es que en un lugar denominado Texas, en la comunidad muy pegado en los límites con Estado de México, encontraron cinco cuerpos</t>
-  </si>
-  <si>
-    <t>Hidalgo</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun, jefe de despacho encargado de la Procuraduría General de Justicia, informó sobre la detención de Pedro N en el municipio de Tula. Hoy por la mañana, muy temprano, se detuvo una persona al nombre de Pedro N. Esa persona lo teníamos considerado en el escalón de la operatividad que llevaba el delincuente El H, ustedes recuerdan que fue detenido en Hidalgo, en un segundo plano. Creemos que con esta detención vamos a lograr tener mucho más tranquilidad en la zona de Tula-Tepeji y vamos a seguir deteniendo a cualquier criminal que haga daño o mueva la estructura en realidad.</t>
-  </si>
-  <si>
-    <t>Detención</t>
-  </si>
-  <si>
     <t>Tula</t>
   </si>
   <si>
-    <t>Como resultado de acciones a cargo de la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo, fue detenido un hombre de iniciales P. A. A., objetivo prioritario en la entidad. La detención de quien es ubicado como el brazo derecho de "El H", detenido anteriormente por la Procuraduría General de Justicia de Hidalgo, ocurrió en la localidad de Xochitlán de las Flores, municipio de Tula de Allende</t>
-  </si>
-  <si>
-    <t>Radioescucha 7723. Dice: «Muy buenos días, Lalo. Antes de todo, saludos cordiales. Por primera vez que te escribo solicitando tu valioso apoyo: hace tres meses CAASIM vino a revisar unas tomas de agua en el bulevar Paseos de Chavarria, en la segunda glorieta entrando por Sahagún, dejando inconcluso».</t>
-  </si>
-  <si>
-    <t>Panorama Informativo</t>
-  </si>
-  <si>
-    <t>Obra inconclusa</t>
-  </si>
-  <si>
-    <t>Negativa</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Radioescucha 6024. Dice: «Muy buenos días, licenciado. Soy el señor Badillo. Aquí en la colonia Real de Oriente no tenemos agua desde hace una semana».</t>
-  </si>
-  <si>
     <t>Abandono de obra</t>
   </si>
   <si>
-    <t>Radioescucha dice: «Lalo, un favor, reporto aquí que en la colonia CTM no cae agua desde hace cuatro días»</t>
-  </si>
-  <si>
-    <t>Radioescucha dice: Muy buenos días, señor Larrieta. Para saludar, Pedro Nieto. Solamente para solicitar el apoyo de CAASIM para ver si hay solución, porque no nos dan... no nos ha caído agua desde hace tres días en el barrio de San Clemente</t>
-  </si>
-  <si>
-    <t>Como resultado de acciones a cargo de la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo, fue detenido un hombre de iniciales P. A. A., objetivo prioritario en la entidad.La detención de quien es ubicado como el brazo derecho de “El H”, detenido anteriormente por la PGJEH, ocurrió en la localidad de Xochitlán de las Flores, municipio de Tula de Allende</t>
-  </si>
-  <si>
-    <t>En su comparecencia en el Congreso del Estado de Hidalgo, Salvador Cruz Neri, secretario de seguridad pública de Hidalgo, fue cuestionado por la diputada Karla Perales, sobre el reclutamiento de menores de edad en Hidalgo.</t>
-  </si>
-  <si>
-    <t>Con acciones de combate a la delincuencia, prevención y atención ciudadana, la Secretaría de Seguridad Pública de Hidalgo (SSPH) presentó los resultados de cuatro años de trabajo durante la comparecencia de su titular, Salvador Cruz Neri, ante el Congreso del Estado</t>
+    <t>Nidia</t>
+  </si>
+  <si>
+    <t>Canal del Pueblo</t>
+  </si>
+  <si>
+    <t>En esta agenda, en esta agenda 2026 de comparecencias ante el Congreso del Estado en la glosa del cuarto informe del gobernador Julio Menchaca tenemos por primera vez la comparecencia del oficial mayor, don Orlando Ángeles que, bueno pues, para algunos fue polémico, no yo lo vi en redes sociales, ahí hubo cierto borlote por decirlo así pero lo cierto es que se va a llevar una sorpresa porque si hay alguien que es de verdad meticuloso, metódico Que trae las cosas así De cuenta que usted le dice Orlando tal tema Parece que su cabeza Aquí está Van a ver ustedes Lo que va a ser esa comparecencia Esa primera comparecencia De un oficial mayor Ojalá que vayan bien preparados Los diputados porque lo que va a sobrar Es información y datos Ya lo verán ustedes Ojalá que los diputados Vayan bien preparados y puedan obtener y puedan generarnos información, porque eso es lo que sobra en la Oficialía Mayor de Información. Ya lo verán ustedes.</t>
+  </si>
+  <si>
+    <t>Andrés Torres</t>
+  </si>
+  <si>
+    <t>Vocales Radio</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor</t>
+  </si>
+  <si>
+    <t>Tv Local</t>
+  </si>
+  <si>
+    <t>Muy positivo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TFRM2xTBxc_ZuCj019XOnAz4gIhCJaQv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Segundos</t>
+  </si>
+  <si>
+    <t>Edgar Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Ayer fue muy polémico la comparecencia del secretario de seguridad pública, este porque bueno, los conocedores del tema de seguridad, pues dijeron, "No cuadran las cifras." Un ejemplo, ayer Don Salvador Cruz Neri dijo que eh solamente 80 de 84 municipios estaban dentro de este programa que se llama Mando Coordinado. De acuerdo a las cifras oficiales, pues están los 84 municipios dentro del Mando Coordinado. Entonces, esa es una de las contradicciones que existieron, pero ningún diputado se dio cuenta. Afortunadamente estaba yo y le preguntó, ¿no? ¿Lo escuchó usted aquí en las Vocales? A ver si no hay represalias luego porque dice que es muy enojón el secretario, ¿no?</t>
+  </si>
+  <si>
+    <t>Muy negativo</t>
+  </si>
+  <si>
+    <t>Ayer fue muy polémico la comparecencia del Secretario de Seguridad Pública, porque los conocedores del tema de seguridad, pues dijeron, no cuadran las cifras. Un ejemplo, ayer don Salvador Cruz Neri dijo que solamente 80 de 84 municipios estaban dentro de este programa que se llama el mando coordinado. De acuerdo a las cifras oficiales, estamos 84 municipios dentro del mando coordinado. Entonces esa es una de las contradicciones Que existieron, pero ningún diputado se dio cuenta Afortunadamente, ya le preguntó ¿No? ¿Lo escuchó usted aquí a las vocales? A ver si no hay represalia suelo Porque dicen que se murió enojado en el secretario Pero bueno, a ver Aldo Falcón Salvador Holguín, excelente día al equipo de vocales radio Andrés Torres, Aldo Falcón Un abrazo desde el Alto Mesquital Muy buenos días</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bOjRnDWm3xELYNJs6ANqjZeyZtCdlyFv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Andrés Torres en respuesta a Ana Lara que dice: "Qué semana de comparecencias, entre confesiones y sordera, las preguntas de familiares incómodos a las y los secretarios". Por ejemplo, Tania Meza, diputada local le preguntó a la secretaria de Cultura que ahí hay un, yo le diría, que ahí hay un conflicto de interés, porque doña Tania Meza también ha sido titular de Cultura, ¿no? Y este, le preguntó por el lazo sanguíneo que existe entre la titular de Cultura y su secretario particular y su particular, que son parientes, ¿no? Y este, obviamente le dijo, bueno, tiene un salario de 23,000 pesos, más una compensación de 30,000, pero pues en todo momento, a pesar de la insistencia de Tania Meza en la comparecencia, en todo momento la titular de Cultura evadió, evadió, evadió y nunca respondió.</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Nepotismo</t>
+  </si>
+  <si>
+    <t>De hecho nos escribió igual, Ana Lara dice ¿Qué semanas de comparecencias entre confesiones y sordera las preguntas de familiares incómodos a las y los secretarios? Por ejemplo, Tania Meza, diputada local, le preguntó a la secretaria de Cultura que ahí hay un, yo le diría que ahí hay un conflicto de interés porque doña Tania Meza también ha sido titular de Cultura, ¿no? Así es le preguntó por el lazo sanguíneo que existe entre la titular de Cultura y su secretaria particular. Y su particular, son parientes, ¿no? Y obviamente le dijo, bueno, tiene un salario de 23 mil pesos, más una compensación de 13 mil, pero en todo momento, a pesar de la insistencia de Tania Mesa en la comparecencia, en todo momento la titular de Cultura evadió, evadió, evadió y nunca la escondió.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1m3s7N6YaNQlZoKeK1A9uNN2pWaB8Llho/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Tania Meza Escorza</t>
+  </si>
+  <si>
+    <t>Ana Lara, muy buenos días, dice: "La señora Edavite ha trabajado bastante bien, debieron tomar el ejemplo las y los del gabinete", nos comenta.</t>
+  </si>
+  <si>
+    <t>Radioescucha</t>
+  </si>
+  <si>
+    <t>Positivo</t>
+  </si>
+  <si>
+    <t>Ana Lara, muy buenos días, dice la señora Edavite, ha trabajado bastante bien, debieron tomar el ejemplo las y los del gabinete.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T7IBixxz4O8_aEnOA_oylicsB3dba5Ur/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Edda Vite</t>
+  </si>
+  <si>
+    <t>Sobre el Informe de Edda Vite, titular DIFH comenta que el reconocimiento al trabajo del DIF fue a nivel nacional y recibió elogios de muchos ayuntamientos y del Sistema DIF Nacional. El informe de Edda Vite Ramos fue considerado muy completo, ya que antes el DIFH se enfocaba solo en cuestiones asistenciales. Actualmente, se involucra en temas más activos, como la salud, la educación, asuntos legales y la adopción, mostrando un enfoque más amplio y proactivo. Antes, los sistemas DIF eran vistos como meros apoyos asistenciales, pero ahora tienen una participación activa en la ayuda a los sectores más vulnerables. Un ejemplo destacado es la presidenta estatal del DIF, quien organizó ayuda y albergues durante emergencias, como las inundaciones en Metzitlán y Tulancingo. En el pasado, las estancias del DIF eran sólo figuras decorativas, pero hoy su papel es significativo y comparable al de una secretaría. Estas transformaciones en el DIFH marcan un cambio importante en su misión, posicionándose como una entidad que actúa y responde de manera más efectiva a las necesidades de la comunidad.</t>
+  </si>
+  <si>
+    <t>El reconocimiento fue prácticamente nacional, si usted revisa las redes sociales ayer, durante y después del informe de la señora David Ramos, bueno pues, reconocimiento prácticamente de todos los ayuntamientos, reconocimiento también, por supuesto, del sistema DIF nacional, y bueno, pues creo que ha sido un informe muy completo, y sobre todo, un informe, permítame decirlo, los temas del DIF, pues eran cuestiones asistenciales, hasta hace muy poco tiempo, hoy los informes del DIFH, lo acabo de leer, usted lo escuchó, tienen un sentido mucho más, yo le diría activo, por decirlo de alguna manera, porque hoy el DIF está involucrado en temas como la salud, como la educación, como los temas legales, temas muy importantes como el tema de la adopción y me parece que ya quedó atrás aquella pues sello que tenían los sistemas DIFH tanto municipales como estatales de ser solamente acompañamiento de ser solamente cuestiones meramente asistenciales hoy me parece que el DIF tiene una actitud o tiene una participación proactiva no nada m reactiva sino proactiva en la cuida de los sectores que m lo necesitan los sectores más desprotegidos de nuestro Estado. cuando usted había visto, por ejemplo, que una presidenta del DIF, una presidenta estatal del DIFH, estuviera al frente de la organización de temas de ayuda, incluso organización de albergues en caso de una emergencia, Que hemos tenido varias, ¿no? Recuerdo, por ejemplo, en el 99 Las inundaciones en Meztitlán, en Tulancingo Donde se vivieron circunstancias dificilísimas Yo estuve ahí, no me lo platicaron Yo estuve ahí, lo reporté para la Agencia Mexicana de Noticias En esos años, el corresponsal nacional Y las estancias del DIF eran meras figuras decorativas Yo lo vi, yo estuve ahí hoy el DIFH es una instancia proactiva, yo le diría al nivel de una secretaría, al nivel de una secretaría de estas que integran el esquema de la administración.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/169BhH7jucvMJevXuOkXKVBr7ji9LIUA1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ultra 102.9 FM</t>
+  </si>
+  <si>
+    <t>Un torso al parecer humano, fue localizado flotando sobre las aguas de la presa Endho, dentro del municipio de Tula de Allende. El reporte fue emitido por trabajadores que se encontraban en labores de retiro de lirio acuático dentro del cuerpo de agua; al percatarse de la presencia de los aparentes restos humanos, dieron aviso de inmediato a las autoridades. Tras ello, al sitio del hallazgo acudieron elementos de la Policía Municipal y de la Secretaría de Seguridad Pública de Hidalgo, quienes resguardaron el perímetro y solicitaron la intervención de la Procuraduría General de Justicia del Estado de Hidalgo. Personal pericial y agentes de investigación adscritos a la región se hicieron cargo de las maniobras para el rescate y recuperación del cuerpo, el cual fue trasladado por el Servicio Médico Forense para llevar a cabo los estudios que permitan determinar la causa de muerte e identificar a la víctima. En otros hechos, restos de una osamenta humana fueron localizados la mañana de este jueves en un predio del municipio de Zapotlán de Juárez, luego de que vecinos de la zona reportaran el hallazgo. Los restos se encontraban a un costado de un camino de terracería que conduce al municipio de Villa de Tezontepec. De manera preliminar, se presume que corresponderían a un hombre, aparentemente en situación de calle, cuyos restos habrían sido consumidos parcialmente por la fauna. El hallazgo fue reportado al Ministerio Público correspondiente, que tomó conocimiento de los hechos y se encargó de los protocolos para el levantamiento de los restos humanos, así como de las investigaciones encaminadas a establecer su identidad y determinar la causa de muerte.</t>
+  </si>
+  <si>
+    <t>Izza Hernández</t>
+  </si>
+  <si>
+    <t>Ultra Noticias1</t>
+  </si>
+  <si>
+    <t>Localización De Restos</t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>Resulta que un torso, al parecer humano, precisamente fue localizado flotando sobre las aguas de la Presa Endhó, dentro del municipio de Tula de Allende. De hecho, el reporte fue emitido por trabajadores que se encontraban en labores de retiro del hilo acuático, cuando se encontraron el cuerpo de agua, precisamente, y al percatarse de la presencia de los aparentes restos humanos, dieron aviso de inmediato a las autoridades y tras ello al sitio del hallazgo acudieron elementos de la policía municipal y de la Secretaría de Seguridad Pública de Hidalgo, quienes resguardaron el perímetro y solicitaron también la intervención de la Procuraduría General de Justicia del Estado de Hidalgo. Personal pericial y agentes de investigación adscritos a la región, que se hicieron cargo precisamente de las maniobras para el rescate y recuperación del cuerpo, el cual fue trasladado por el Servicio Médico Forense para poder llevar a cabo los estudios que pudieran permitir realizar los estudios para poder determinar la causa de la muerte, para poder identificar a la víctima también.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1q4NcQyQPk-F4Yd40440RRrwguMiSUgri/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Ultra Noticias</t>
+  </si>
+  <si>
+    <t>Seguridad Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Tres de los cinco cuerpos localizados en una fosa clandestina en Atotonilco de Tula ya fueron identificados por la División Científica de la Procuraduría General de Justicia de Hidalgo, de los cuales, dos fueron entregados a sus familiares, informó Francisco Fernández Hasbún, encargado de la dependencia. El funcionario precisó que las víctimas entregadas corresponden a un hombre y una mujer; mientras que continúan los trabajos para identificar los dos cadáveres restantes. Las cinco víctimas son mayores de edad y tenían fichas de búsqueda vigentes en la entidad. Fernández Hasbun agregó que la Comisión de Búsqueda de Personas del Estado de Hidalgo solicitó la intervención del Ministerio Público y del área de Servicios Periciales para efectuar los levantamientos y las pruebas genéticas. Sobre las investigaciones, aseguró que existen indicios importantes pero que se reservaría la información para no comprometer las indagatorias. Hasta ahora, no hay personas detenidas por estos hechos. No obstante, aseguró que, una vez concluido el procesamiento del sitio y las actividades periciales, proporcionaría más información sobre las condiciones en que fueron localizadas las víctimas y el tiempo que llevaban sin ser localizadas.</t>
+  </si>
+  <si>
+    <t>Fosa clandestina</t>
+  </si>
+  <si>
+    <t>Atotonilco de Tula</t>
+  </si>
+  <si>
+    <t>Tres de los cinco cuerpos localizados en una fosa clandestina en Atotonilco de Tula ya fueron identificados por la División Científica de la Procuraduría General de Justicia del Estado de Hidalgo, de los cuales dos fueron entregados a sus familiares, según informó Francisco Fernández Hasbun, el encargado de la dependencia. El funcionario precisó que las víctimas entregadas corresponden a un hombre y una mujer, mientras que continúan los trabajos para identificar los dos cadáveres restantes. Las cinco víctimas son mayores de edad y tenían ficha de búsqueda vigente en la entidad. Fernández Hasbun agregó que la Comisión de Búsqueda de Personas del Estado de Hidalgo solicitó la intervención del Ministerio Público y del Área de Servicios Periciales para efectuar los levantamientos y las pruebas genéticas. Sobre las investigaciones aseguró que existen indicios importantes, pero que se reservará la información para no comprometer las indagatorias. Hasta ahora no hay personas detenidas por estos hechos, no obstante, aseguró que una vez concluido el procesamiento del sitio y las actividades periciales proporcionaría más información sobre la condición en que fueron localizadas las víctimas y el tiempo también que llevaban sin ser localizadas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1a7Wp0cP8OPWqg0j1QfHFsEnEr6l4Aua4/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo, a través de la Dirección de Programas Curriculares y del Programa Estatal de Lectura y Escritura de Hidalgo, reunió 5.932 libros durante la cuarta edición del Kilómetro del Libro, iniciativa que está buscando fomentar el hábito de la lectura entre niñas, niños y jóvenes. De hecho, los ejemplares serían destinados a fortalecer la biblioteca o las bibliotecas de las escuelas públicas de educación básica, especialmente aquellas ubicadas en comunidades alejadas y en condiciones de vulnerabilidad con el propósito de ampliar el acceso y el asilo a los estudiantes de los libros y también al conocimiento. Del total recaudado, 3.000 libros fueron donados por la Fundación Elena Amor, de hecho mediante gestiones de la Dirección General de Desarrollo Curricular y también la Dirección de Programas Curriculares de la CEPIDALGO. Los 2.932 ejemplares restantes fueron aportados por personal de distintas áreas de la dependencia, pero sí al gobierno de Hidalgo encabezado por Julio Menchaca Salazar a través de la Secretaría de Educación Pública Estatal, dirigida por Natividad Castrejón Valdés. Impulsa acciones para promover la lectura y la escritura también como herramientas fundamentales para el aprendizaje y la formación integral de las y los estudiantes. La cuarta edición del kilómetro del libro, pues contó con la participación de distintos sectores para poder reunir materiales que pueden permitir acercar la lectura a más comunidades escolares y contribuir también al desarrollo de habilidades como comprensión lectora, la imaginación y el pensamiento crítico. Bien, es como reúne la CEPIRALGO 5.932 ejemplares en esta cuarta edición del kilómetro del libro.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12M4wX-WtD2fyA6DCJK6v74_EtDjSbIZH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Comunicado gubernamental</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>UPLAPH/Bol.159/2026</t>
+  </si>
+  <si>
+    <t>Daniel Martínez: Ojalá que también esa homologación llegue a los comunicados porque luego le digo un lenguaje oficialñol, que es darle vueltas a las cosas para decir concretamente de lo que se trata es la simplificación de los trámites para que no sea un laberinto burocrático, que tengas que acudir a realizar un trámite para pedir un servicio, abrir un negocio, solicitar alguna jornada de atención social, etc.</t>
+  </si>
+  <si>
+    <t>Daniel Martínez</t>
+  </si>
+  <si>
+    <t>Planeación</t>
+  </si>
+  <si>
+    <t>Comunicación gubernamental</t>
+  </si>
+  <si>
+    <t>Negativo</t>
+  </si>
+  <si>
+    <t>Ojalá que también esa homologación llegue a los comunicados porque luego le digo un lenguaje oficialñol, que es darle vueltas a las cosas para decir concretamente de lo que se trata es la simplificación de los trámites para que no sea un laberinto burocrático, que tengas que acudir a realizar un trámite para pedir un servicio, abrir un negocio, solicitar alguna jornada de atención social, etc.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tRfnKCJTEOEJTjRJ-qkMU7sitWPe7P4f/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La vaguada monzónica del año pasado afectó casi 27 mil hectáreas agrícolas en Hidalgo, para las cuales el gobierno del estado destinó 80 millones de pesos extraordinarios para atender exclusivamente a los 28 municipios con afectaciones, informó el titular de Saderh, Napoléon González Pérez.Consultar atlas El titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh) detalló que en total suman 140 millones de pesos, de los cuales 60 millones corresponden al fondo anual para atención de daños agropecuarios y 80 son los recursos extras por el fenómeno meteorológico. Durante su comparecencia ante el Congreso local indicó que con los recursos extraordinarios y los del fondo lograron apoyar casi 28 mil hectáreas, donde entregaron 5 mil pesos a productores con una hectárea, y menor cantidad a quienes tienen menos superficie, además de entregas de 4 mil pesos a productores pecuarios. “Se otorgaron más de 17 mil apoyos económicos directos para la recuperación agrícola y pecuaria, maquinaria pesada, lanchas, motores y equipo para facilitar las labores de rehabilitación y rescate, además de la apertura de ventanillas regionales”, recordó. También, dijo, en los demás programas y apoyos como Mujer Rural, Semillas, Fortalecimiento a la ganadería con los vientres ovinos, porcinos, sementales, terneras, dieron prioridad a los productores afectados por la vaguada en los 28 municipios, quienes cumplieron con las reglas de operación. En otro tema, dio a conocer que Hidalgo sumó mil 475 casos de gusano barrenador en ganado, de los cuales hasta el 14 de octubre 76 se mantienen activos; además mencionó que Saderh ha colaborado en la revisión de más de 47 mil animales. Agregó que participaron en la capacitación de más de 5 mil 100 productoras y productores, y más de 9 mil movilizaciones de ganado inspeccionados.</t>
+  </si>
+  <si>
+    <t>La vaguada monzónica del año pasado afectó casi 27 mil hectáreas agrícolas en el estado, para los cuales el gobierno del estado destinó 80 millones de pesos extraordinarios para atender exclusivamente a los 28 municipios con afectaciones, según informó el titular de SADER, Napoleón González Pérez. El titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo detalló que en total suman 140 millones de pesos, de los cuales 60 millones corresponden al Fondo Anual para Atención de Daños Agropecuarios y 80 son los recursos extras por el fenómeno meteorológico durante su comparecencia ante el Congreso local. Indicó que con los recursos extraordinarios y los del fondo lograron apoyar casi 28 mil hectáreas, donde entregaron 5 mil pesos a productores con una hectárea y menor cantidad a quienes tienen menos superficie, además de entregas de 4 mil pesos a productores pecuarios. Se otorgaron más de 17 mil apoyos económicos directos para la recuperación agrícola y pecuaria, maquinaria pesada, lanchas, motores y equipo para facilitar las labores de rehabilitación y rescate, además de la apertura de ventanillas regionales, según recordó. También dijo, en los demás programas y apoyos como Mujer Rural, Semilla, Fortalecimiento a la Ganadería con los vientres ovinos, Porcinos, Sementales, Terneras, dieron prioridad a los productores afectados por la vaguada en los 28 municipios. En otro tema dio a conocer que Hidalgo sumó 1.475 casos de Cusano Barrenador en ganado, de los cuales hasta el 14 de octubre de 76 se mantienen activos. Además mencionó que Sader ha colaborado en la revisión de más de 47 mil animales. Agregó que participaron en la capacitación más de 5 mil 100 productoras y productores y más de 9 mil movilizaciones de ganado inspeccionado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mH2D0kiF0_dkFqIb2lUV5ll0RZBTRY7r/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>Ocho servidores públicos de Hidalgo continúan cobrando dos sueldos, uno como docentes y otro por cargos en municipios, debido a que promovieron juicios de amparo o medios de impugnación contra los dictámenes de compatibilidad laboral que les impidieron mantener ambos empleos. Álvaro Bardales Ramírez, contralor estatal, informó que inicialmente detectaron alrededor de mil casos de personas con doble plaza en distintas dependencias y municipios, principalmente en los sectores educativo y de salud. De estos, cerca de 900 renunciaron a uno de sus puestos, mientras que permanecen vigentes 112 investigaciones. Claudia Guadalupe López Torres, directora general de Responsabilidades Administrativas de la Secretaría de Contraloría, explicó que los ocho inconformes argumentaron una presunta vulneración de sus derechos. Sin embargo, mediante visitas a centros educativos y revisiones de constancias laborales, la Contraloría determinó que no cumplían las condiciones de horarios y distancias para obtener un dictamen favorable que les permitiera conservar ambos empleos. Precisó que algunos obtuvieron suspensiones provisionales, por lo que la Contraloría está impedida para continuar las investigaciones hasta que se resuelva el fondo de los amparos. En otro caso, tras una resolución judicial, emitieron un nuevo dictamen negativo. Ninguno de estos ocho casos corresponde a personas que perciban más que el gobernador, aunque sí se detectaron 13 casos de remuneraciones superiores a la del titular del Ejecutivo estatal. Respecto a las sanciones, señaló que la Contraloría no tiene facultades para intervenir directamente en los municipios. En el ámbito estatal, indicó que corresponde a las secretarías involucradas revisar las dobles plazas y determinar las bajas, así como las responsabilidades de quienes autorizan los pagos de nómina. En otro tema, el contralor Álvaro Bardales informó que hay cuatro municipios con 487 millones de pesos por justificar, recurso que corresponde a la federación. Tepehuacán de Guerrero es el de mayor monto con 210 millones de pesos; le sigue Huichapan con 168 millones de pesos; Tepetitlán, 58 millones de pesos y Huehuetla, 51 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Claro, Bardales destacó en este caso el tema de las, los maestras, maestros que siguen todavía cobrando doble sueldo, doble salario por alguna circunstancia legal o por alguna cuestión que han logrado solventar y que están bajo revisión. Ese fue como que el gran tema. Lorena Rosas Pérez señala para el Universidad Hidalgo que ocho servidores públicos de la entidad continúan cobrando dos sueldos, uno como docentes y otro por cargos en municipios, debido a que promovieron juicios de amparo o medios de impugnación contra los dictámenes de compatibilidad laboral que les impidieron mantener ambos empleos. Álvaro Bardales Ramírez, Contralor Estatal, informó que inicialmente detectaron alrededor de mil casos de personas con doble plaza en distintos dependencias y municipios, principalmente en los sectores educativo y de salud. De estos, cerca de 900 renunciaron a uno de sus puestos, mientras que permanecen vigentes 112 investigaciones. Y es en cuatro casos donde sacaron algún amparo para poder seguir precisamente en sus labores. Claro, Guadalupe López Torres, directora general de responsabilidades administrativas de la Contraloría, explicó que los ocho inconformes argumentaron una presunta vulneración a sus derechos. Sin embargo mediante visitas a centros educativos y revisiones de constancias laborales la Contralor determinó que no cumplió las condiciones de horarios y distancias para obtener un dictamen favorable que les permitiera conservar ambos empleos Precisó que algunos obtuvieron suspensiones provisionales, por lo que la Contraloría está impedida para continuar las investigaciones hasta que se resuelvan los aparos de fondo. En otro caso, tras una resolución judicial, emitieron un nuevo dictamen negativo. Ninguno de estos ocho casos corresponde a personas que perciban más que el gobernador Aunque sí se detectaron trece casos de remuneraciones o sueldos más altos Que los del titular del Poder Ejecutivo del Estado de Hidalgo en este caso Respecto a las sanciones, señaló que la Contraloría no tiene facultades para intervenir directamente en los municipios En el ámbito estatal, indicó que corresponden a las secretarías involucradas revisar las dobles plazas Y determinar las bajas, así como las responsabilidades de quienes autorizan los pagos de nómina En otro tema, el contador Álvaro Bardales informó que hay cuatro municipios con 487 millones de pesos por justificar recursos que corresponden a la federación. Tepehuacán de Guerrero es el de mayor monto con 210 millones de pesos, 40% aproximadamente, que deben de justificar. Le siguen Huichapan con 168 millones de pesos, Tepetitlán con 58 millones y Huehuetla con 58 millones de pesos que les falta por justificar y que son recursos federales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lUDoSqn5XEinb8l8T8N82ctALXPa4n0o/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>El Universal Hidalgo</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales</t>
+  </si>
+  <si>
+    <t>El aseguramiento de aproximadamente 7 millones de litros de hidrocarburo extraído de manera ilegal de ductos de Petróleos Mexicanos, forma parte de resultados de seguridad presentados por el titular de la Secretaría de Seguridad Pública en Hidalgo, Salvador Cruz Neri. Esto durante la comparecencia ante el Congreso estatal. De hecho, el funcionario detalló que como parte de las acciones contra el robo de combustible durante los primeros 4 años de la actual administración, también fueron decomisados 1,588 vehículos relacionados con esta actividad; de hecho, fueron también 18 autotanques y más de 41,000 metros de manguera de alta presión. Y pues estas acciones se sumó también el desmantelamiento de 11 túneles localizados en distintos municipios, presuntamente utilizados para actividades vinculadas con la extracción ilegal de hidrocarburo. Además, 391 personas que fueron detenidas en flagrancia eh pues por hechos relacionados con este delito. En materia de combate de extorsión, Cruz Neri reportó también una disminución de 60.67% hecho esto en la incidencia de este delito y de acuerdo con las cifras expuestas ante los legisladores. Y respecto también a las atenciones realizadas por corporaciones estatales, informó que 26,536 personas fueron aseguradas por distintas faltas o posibles delitos. De ellas, 20,591 quedaron a disposición de un juez conciliador y 5,945 fueron presentadas ante el Ministerio Público; además también de 974 que ingresaron a un centro de reinserción social. Pero bien, el secretario también señaló que las quejas contra elementos policiales por presuntas violaciones a derechos humanos disminuyeron 23% y que 13 agentes fueron separados de sus cargos tras acreditarse como irregularidades. Y pues en cuanto a la infraestructura de vigilancia, informó sobre el proyecto de instalación de 5,100 cámaras conectadas al Centro de Comando, Control, Comunicaciones, Cómputo, Coordinación e Inteligencia, hablamos del C5i. Eh, asimismo también mencionó la adquisición de 18,000 cámaras con apoyo del sector empresarial pues que se estarían integrando al sistema una vez conectadas. Y pues finalmente Cruz Neri sostuvo que la percepción de inseguridad en Hidalgo se ubicó en 61.5%, todo esto por debajo del promedio nacional de 74%. De hecho también señaló que 80 de los 84 municipios del estado operaban bajo el esquema del mando coordinado. Entonces, pues es un todo, Daniel, y de alguna forma, sí, importante mencionar que lo que más destacó fue el reporte del decomiso de 7 millones de litros de huachicol.</t>
+  </si>
+  <si>
+    <t>El aseguramiento de aproximadamente 7 millones de litros de hidrocarburo extraído de manera ilegal de ductos de petróleos mexicanos formó parte de resultados de seguridad presentados por el titular de la Secretaría de Seguridad Pública en Hidalgo, Salvador Cruz Neri, esto durante la comparecencia ante el Congreso Estatal. De hecho, el funcionario detalló que, como parte de las acciones contra el robo de combustible durante los primeros cuatro años de la actual administración, También fueron decomisados 1.588 vehículos relacionados con esta actividad. De hecho, fueron también 18 autotanques y más de 41.000 metros de manguera de alta presión. Y pues estas acciones se sumó también el desmantelamiento de 11 túneles localizados en distintos municipios, presuntamente utilizados para actividades vinculadas con la extracción ilegal de hidrocarburo. Además, 391 personas que fueron detenidas en Florencia. pues por hechos relacionados con este delito. En materia de combate de extorsión, el Cruz Neri reportó también una disminución de 60.67% hecho esto en la incidencia de este delito y de acuerdo con las cifras expuestas ante los legisladores. Y respecto también a las detenciones realizadas por corporaciones estatales, informó que 26 personas fueron aseguradas por distintas faltas o posibles delitos De ellas 20 quedaron a disposición de un juez conciliador y 5 fueron presentados ante el Ministerio P además también de 974 que ingresaron a un centro de reinserción social. Pero bien, el secretario también señaló que las quejas contra elementos policiales por presuntas violaciones a derechos humanos disminuyeron 23% y que 13 agentes fueron separados de sus cargos tras acreditarse como irregularidades. Y pues, en cuanto a la infraestructura de vigilancia, informó sobre el proyecto de instalación de 5.100 cámaras conectadas al Centro de Comando, Control, Comunicación, Cómputo, Coordinación e Inteligencia, hablamos del C5I. Asimismo, también mencionó la adquisición de 18.000 cámaras con apoyo del sector empresarial, pues que se estarían integrando al sistema una vez conectadas. Y pues finalmente Kruzner sostuvo que la percepción de inseguridad en Hidalgo se ubicó en 61.5%, todo esto por debajo del promedio nacional de 74%. De hecho también señaló que 80 de los 84 municipios del estado operaban bajo el esquema del mando coordinado. Entonces, pues es un todo, Daniel, y de alguna forma sí, importante mencionar que lo que más destacó fue el reporte del decomiso de 7 millones de litros de huachicol</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lUDoSqn5XEinb8l8T8N82ctALXPa4n0o/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo avanza en la homologación y simplificación de trámites y servicios</t>
+  </si>
+  <si>
+    <t>Simplificación de trámites</t>
+  </si>
+  <si>
+    <t>Bueno, antes de irnos a la pausa, le comento que a través de un comunicado oficial, el gobierno del estado de Hidalgo señala que para facilitar la realización de trámites y mejorar la atención a la ciudadanía, el gobierno del estado, insisto, encabezado por Julio Menchaca Salazar, se incorporó al plan nacional de implementación del modelo nacional de homologación de trámites y servicios impulsado por la presidenta de México, Claudia Sheinbampardo. El encargado de despacho de la unidad de planeación y prospectiva de Hidalgo Nésimo Serrano Rivera Explicó que esta estrategia encabezada por la agencia de transformación digital y telecomunicaciones Permitirá avanzar de manera coordinada en la simplificación, homologación y digitalización de los servicios públicos</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zsi1FG2kLWtpBnHdQM9FI6B62bcenI_9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Onésimo Serrano Rivera</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Daniel Martínez sobre el informe de la presidenta del DIFH, Edda Vite destaca la importancia de brindar alimentación, refugio y protección a la población vulnerable, especialmente a niñas, niños y adolescentes. Sin embargo, destaca que la administración de Edda Vite Ramos en el DIF Hidalgo se ha enfocado en proteger los derechos e integridad de este grupo. Se han anunciado mejoras en los espacios de resguardo y se ha trabajado en la creación de procuradurías municipales para atender a niñas, niños y adolescentes. Estas procuradurías tienen como objetivo hacer la atención más rápida y directa. Izza Hernández coincide con Martínez en que este es un objetivo fundamental y subraya la importancia de estar atentos al proceso de atención a este sector de la población.</t>
+  </si>
+  <si>
+    <t>Reitero que sin quitar otras acciones de atención a población vulnerable, esto es, el que se les pueda dar alimentación, algún cobijo, algún resguardo, etcétera, etcétera, el sello fundamental que han tenido en esta administración que encabeza la señora David Ramos en el DIF Hidalgo ha sido la protección a los derechos y a la integridad de niñas, niñas y adolescentes. De ahí precisamente los anuncios que hace respecto a las mejoras de los espacios donde están a resguardo. y pues también el gran tema ha sido en los meses recientes, en el transcurso de este año particularmente, Isa, la conformación, la creación, la operación de las procuradurías y municipales de atención a niñas, niños y adolescentes justo para que la intención es de que la atención sea más ágil y directa para este sector de la población. Es correcto, Daniel, así como lo acabas de mencionar, de alguna forma pues ese es el objetivo. Entonces, pues bien, vamos a estar al pendiente de todo este proceso porque vaya que sí es importante, sobre todo si estamos hablando de atención directa a niñas, niños y adolescentes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1y-nVRKspOefY9X-9mPSZetYz_QSHgA04/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Este mismo año iniciará operaciones la nueva Casa Cuna a cargo del Sistema DIF Hidalgo, tras la rehabilitación del primer piso, la construcción del segundo nivel y su equipamiento. Lo anterior fue anunciado por Edda Vite Ramos, presidenta del organismo asistencial estatal, durante la presentación de su Cuarto Informe de Actividades. Agregó que se realizará la remodelación integral del Centro de Atención al Niño y al Adolescente, para que tenga condiciones para la atención digna de la población que lo requiere. También se construirá un nuevo taller de ortesis y prótesis, así como tres bodegas, dos de ellas en Pachuca, destinadas al archivo de concentración del sistema. Mientras que en Ixmiquilpan se construirá una más para resguardar en condiciones óptimas los insumos alimentarios destinados a 22 municipios de las regiones del Valle del Mezquital y la Sierra Gorda. Estas obras deberán estar listas antes de concluir la actual administración, incluyendo la ampliación de distintas áreas del Centro de Rehabilitación Regional de Ixmiquilpan. Además, se construirán dos centros de atención infantil, ubicados en la colonia Matilde y en San Bartolo, en Pachuca. También anunció la construcción de un edificio que dijo, permitirá incrementar los ingresos para continuar con las acciones de asistencia social. Vite Ramos señaló que se ampliará la cobertura del programa de alimentación que actualmente atiende a 150 mil estudiantes, con el objetivo de beneficiar a más de 190 mil priorizando a niñas y niños detectados con desnutrición, sobrepeso u obesidad. Se informó que durante la vaguada monzónica que afectó a 28 municipios, el DIFH coordinó la recepción, clasificación y distribución de apoyos alimentarios, ropa, cobijas y otros materiales, en colaboración con voluntarios de los distintos niveles de gobierno, la sociedad civil y la iniciativa privada. Desde diversos centros de acopio se organizó la distribución de 266 mil despensas para las comunidades afectadas y se recibió a 215 personas trasladadas a través de vuelos de rescate. De ellas, 49 eran niñas, niños y adolescentes, quienes recibieron atención, y se realizaron tres cirugías en el Hospital del Niño DIFH. A ello se suma la entrega de 94 mil 96 despensas destinadas a municipios afectados por la vaguada monzónica y a localidades con grados de marginación alta y muy alta.</t>
+  </si>
+  <si>
+    <t>Ayer la presidenta del sistema DIFIDA, Algoeda Vita y Ramos, presentó su cuarto informe de actividades y el sello particular que veo que ha existido en esta administración ha sido sobre todo los temas de protección a los derechos y a la integridad de niñas, niñas y adolescentes. Por ahí fue precisamente los anuncios que hizo la señora Vita y Ramos. Es correcto, este mismo año se ha iniciado operaciones la nueva Casa Cuna, es a cargo del sistema DIF tras la rehabilitación del primer piso, de hecho de construcción del segundo nivel y también su equipamiento. Pero bien, todo esto fue anunciado por el David Ramos, quien es presidente del organismo asistencial estatal, durante la presentación de su cuarto informe de actividades. De hecho, creo que están realizando la remodelación integral del centro de atención al niño y al adolescente para que tenga condiciones para la atención digna de la población que así lo requiere. También se va a construir un nuevo taller de ortesis, prótesis y también tres bodegas, dos de ellas en Pachuca destinadas al archivo de concentración del sistema, mientras que en Ixmiquilpan van a construir una más para poder resguardar en condiciones óptimas los insumos alimentarios destinados a 22 municipios de las regiones del Valle del Mezquital y de la Sierra Gorda. Estas obras deberán estar listas antes de concluir la actual administración, incluyendo la ampliación de distintas del Centro de Rehabilitación Regional de Ixmiquilpan Adem se van a construir dos centros de atención infantil estos ubicados en la colonia Matilde y en San Bartolo también en Pachuca pero bien, también anunció la construcción de un edificio que dijo pues estaría permitiendo incrementar los ingresos para poder continuar con las acciones de asistencia social, pero si Vite Ramos señaló que se estaría ampliando la cobertura del programa de alimentación que Actualmente, pues, atiende a 150 mil estudiantes con el objetivo de beneficiar a más de 190 mil, pues, priorizando de alguna forma niñas y niños, pues, detectados con desnutrición, sobrepeso u obesidad. De ellos se informó que durante la vaguada monzónica que afectó a 28 municipios, el DIFIDALGO coordinó la recepción, clasificación también y distribución de apoyos alimentarios, ropa, cobijas y otros materiales en colaboración con voluntarios de los distintos niveles de gobierno, la sociedad civil y también la iniciativa privada. Y pues desde diversos centros de acopio se organizó la distribución de 266 mil despensas para las comunidades afectadas y se recibió a 215 personas trasladadas a través de vuelos de rescate y pues de ellas 49 eran niñas, niños y adolescentes quienes recibieron la atención y se realizaron tres cirugías en el hospital del niño DIF Hidalgo. Entonces, a todo esto se suma también la entrega de 94.096 despensas destinadas a municipios afectados por la bárbara monzónica y también a las localidades con grados de marginación alta y muy alta.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Cw7mMhbVYqn0TzJsBFi41lmuze_Stx7f/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Segobh/Bol.100/2026</t>
+  </si>
+  <si>
+    <t>Una mujer de Cuautepec obtuvo una resolución judicial favorable en un caso de violencia vicaria, luego de que se dictara la primera sentencia condenatoria por este delito en Hidalgo, informó la Secretaría de Gobierno estatal. El caso llegó a las autoridades a través de las Mesas de Acercamiento de Bienestar y Paz, espacios en los que la víctima expuso su situación. A partir de ello, se dio seguimiento con las instancias correspondientes para avanzar en la atención del caso y el proceso de justicia. La violencia vicaria ocurre cuando una persona busca perjudicar a una mujer mediante sus hijas o hijos, utilizándolos como medio para ejercer daño o control. La sentencia constituye un antecedente judicial en Hidalgo para la atención de esta forma de violencia familiar. El Frente Nacional Contra Violencia Vicaria también intervino en el acompañamiento del caso y reconoció la actuación de la representación del Ministerio Público y del juez que participaron en el procedimiento. La organización subrayó la importancia de incorporar la perspectiva de género en la impartición de justicia. Por su parte, la Secretaría de Gobierno indicó que mantendrá las Mesas de Acercamiento como una vía para recibir planteamientos ciudadanos y canalizarlos ante las dependencias responsables de brindar atención.</t>
+  </si>
+  <si>
+    <t>Mesas de acercamiento</t>
+  </si>
+  <si>
+    <t>Cuautepec</t>
+  </si>
+  <si>
+    <t>Empezamos con un caso que fue relatado durante una de estas mesas de atención a la población, a la ciudadanía, realizadas hace algunos meses en Cuautepec. Estas mesas que encabeza Guillermo Olivares Reyna, secretario general de Gobierno, donde uno de los temas fue una mujer que tomó la palabra y que señaló estar, bueno, contó una serie de cuestiones complejas, complicadas, gravísimas en cuanto a violencia de género en principio, puntualizándose sobre todo en violencia vicaria, que es el tema acerca de ejercer violencia no permitiendo ver a tus hijos o hijas, influenciándolos para hablar de alguna forma de de la víctima, en este caso las mujeres. Hay sentencia y entiendo que es la primera que ocurre en el estado de Hidalgo, Izza. Es correcto, Daniel. Resulta que una mujer de Cuautepec obtuvo la resolución judicial favorable en un caso de violencia vicaria, luego de que se dictara la primera sentencia condenatoria por este delito en Hidalgo. Así lo informó la Secretaría de Gobierno estatal. Este caso llegó a las autoridades, todo esto a través de mesas de acercamiento del Bienestar y Paz, también espacios en los que la víctima expuso su situación. A partir de ello, de ello se dio seguimiento con las instancias correspondientes para poder avanzar en la atención del caso y el proceso de justicia. De hecho, la violencia vicaria ocurre, como ya lo adelantabas hace un momento, cuando una persona pues busca perjudicar a una mujer mediante sus hijas o hijos, utilizándolos como medio para poder ejercer daño o control. La sentencia de hecho constituye también un antecedente judicial en Hidalgo para la atención de esta forma de violencia familiar. Pero bien, el Frente Nacional Contra la Violencia Vicaria también intervino en el acompañamiento del caso y reconoció también la actuación de la representación del Ministerio Público y del juez que participaron en el procedimiento. De hecho, la organización subrayó la importancia de incorporar la perspectiva de género en la impartición de justicia, y por su parte, la Secretaría de Gobierno indicó, de hecho, que pues va a mantener las mesas de acercamiento como una vía para poder recibir planteamientos ciudadanos y también, obviamente, canalizarlos directamente ante las dependencias correspondientes para poder brindar atención. Esto fue lo que sucedió y sí, se da este primer caso en Hidalgo con sentencia por violencia vicaria y pues sucedió con un caso de Cuautepec.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oSV3rcre90BmJq7j68-Fhmx8r_LiobPQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Daniel Martínez: Entiendo que por cuestiones legales, así lo entendería, tú servidoras, este comunicado, este boletín oficial con el que se da a conocer esta sentencia no trae mayores datos, y lo entiendo perfectamente, acerca de la víctima y también de la persona que fue sentenciada, pero tampoco hay mayor información acerca de cuál es la sentencia que se está otorgando en cuanto a si se trata de, ahora sí que de sanción física, prisión o si hay una sanción o si hay alguna multa.</t>
+  </si>
+  <si>
+    <t>Entiendo que por cuestiones legales, así lo entendería tu servidor, Isa, este comunicado, este boletín oficial con el que se da a conocer esta sentencia no trae mayores datos, y lo entiendo perfectamente acerca de la víctima y también de la persona que fue sentenciada, pero tampoco hay mayor información acerca de cuál es la sentencia que se está otorgando en cuanto si se trata de, ahora sí que de sanción física, prisión, o si hay una sanción o hay alguna multa.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1k1eT4Llymr8AOt6ITcMmtZ-MEp0m4UHx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Hoy desde las 5:00 de la mañana, ha estado lloviendo mucho en la Sierra Otomí-Tepehua, lo que ha afectado las carreteras de la región en el Estado de Hidalgo. Ayer por la tarde, la Subsecretaría de Protección Civil ya había advertido sobre lluvias importantes, incluso torrenciales, especialmente en el norte del Estado. Esta región es un punto de conexión para la Huasteca hidalguense. Debido a estas condiciones, se han cerrado caminos en los municipios de Tenango de Doria, Huehuetla y San Bartolo Tutotepec. Metepec también ha sufrido algunos problemas, pero todavía se considera parte de la red vial. El nivel de los ríos en Huehuetla y San Bartolo Tutotepec ha aumentado significativamente. Además, se han suspendido las clases en las escuelas de Huehuetla, y se está monitoreando la situación en San Bartolo Tutotepec.</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Prevención De Riesgos</t>
+  </si>
+  <si>
+    <t>Otomí Tepehua</t>
+  </si>
+  <si>
+    <t>Desde aproximadamente las 5 de la mañana del día de hoy, esta llueve que te lleve en buena parte de la sierra Otomí- Tepehua, lo que evidentemente ha implicado afectaciones a las vías carreteras de esa región del estado de Hidalgo. Ayer por la tarde, la Subsecretaría de Protección Civil y Gestión de Riesgos del estado de Hidalgo ya había anticipado que se presentarían lluvias importantes, en algunos casos torrenciales, sobre todo en la zona norte del estado de Hidalgo. Habrá quien diga, más bien la Otomí- Tepehua es el oriente. Pues sí, pero está pegadito a la sierra alta y baja. Es punto de conducción precisamente para la huasteca Hidalguense. De ahí precisamente las afectaciones que están ocurriendo en este momento. Y precisamente como una forma de prevención es el cierre que se está estableciendo en los municipios, sobre todo de Tenango de Doria, Huehuetla y San Bartolo Tutotepec. Metepec está medianamente afectado, pero ahora sí que ahí empieza la red carretera correspondiente. El crecimiento de los ríos, sobre todo en la zona de Huehuetla, San Bartolo, Tutotepec Es bastante, bastante importante en este momento Se han suspendido clases, le comento y le confirmo en este momento Que se han suspendido clases en los planteles educativos de Huehuetla Específicamente, ahorita le cuento cómo está Le estoy checando San Bartolo, Tutotepec Y le cuento en un momentito más, ¿sale?</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zvyQRHpFjvkSeDBROnb15zfCQZWmaeds/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>comparecencia</t>
+  </si>
+  <si>
+    <t>El día de hoy también tenemos comparecencia en un minuto más la Secretaría de Salud, Vanesa Escalante, a las 10 de la mañana y horas más tarde, a las 16 horas, el licenciado Oscar Javier González de la Secretaría del Trabajo.</t>
+  </si>
+  <si>
+    <t>Aldo Falcón</t>
+  </si>
+  <si>
+    <t>STPSH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lgZsseQNSQMSnQ27FGpLUJamaB_hThgs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13qv-0ISri7aTwvjn_uSoGHP8IWpj4_Qk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Secretaría del Trabajo</t>
+  </si>
+  <si>
+    <t>Al comparecer ante los integrantes de la 66 Legislatura del Congreso del Estado, el titular de la Secretaría de Agricultura y Desarrollo Rural, Napoleón González Pérez, rindió un informe sobre el estado que guarda la administración pública en el sector primario, donde resaltó en ese sector primario donde resaltó que la gestión del gobernador Julio Menchaca pues ha sido fundamental para destinar una inversión al campo hidalguense que superó los 229 millones de pesos del 2022 a un techo histórico de 721 millones de pesos en el actual 2026, lo cual pues impactó de manera directa en beneficio o a beneficio de 487,900 familias rurales. Dice Don Napoleón que se destinó un importante rubro de 229 en ese rubro 229 millones de pesos, eh repito, del 2022 era lo que había para agricultura y en este 2026 pues ya se aplicaron 721 millones de pesos y, bueno, pues un importante eh beneficio para el sector agrícola en nuestro estado. Una de las comparecencias que fueron, me parece, más este participativas y bueno pues el tema de la agricultura sí creo que es algo que todos celebramos, ¿no?</t>
+  </si>
+  <si>
+    <t>Al comparecer ante los integrantes de la 66 legislatura del Congreso del Estado, el titular de la Secretaría de Agricultura y Desarrollo Rural, Napoleón González Pérez, rindió un informe sobre el Estado que guarda la Administración Pública en el sector primario, donde resaltó, en ese sector primario, donde resaltó que la visión del gobernador Julio Menchaca pues ha sido fundamental para destinar una inversión al campo hidalguense que superó los 229 millones de pesos del 2022 a un techo histórico de 721 millones de pesos en el actual 2026, lo cual pues impactó de manera directa en beneficio o a beneficio de 487 mil 900 familias rurales. Dice don Napoleón que se destinó un importante rubro de 229 millones de pesos Repito, del 2022 era lo que había para agricultura Y en este 2026 ya se aplicaron 721 millones de pesos Y bueno, pues un importante beneficio para el sector agrícola en nuestro estado pues una de las comparecencias que fueron me parecen más participativas y bueno pues el tema de la agricultura si creo que es algo que todos celebramos ¿no?</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yG6IDQDzzQqYxngJpU0Ab2_hnSVxbKzB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Por su parte, el gobernador Julio Menchaca comenta: "Felicito al equipo del DIF Hidalgo por su cuarto informe de actividades y, sobre todo, por el trabajo que realiza cada día por las familias hidalguenses, mi reconocimiento".</t>
+  </si>
+  <si>
+    <t>Gobernador</t>
+  </si>
+  <si>
+    <t>Por su parte, el gobernador Julio Menchaca comenta, felicito al equipo del DIF Hidalgo por su cuarto informe de actividades y sobre todo por el trabajo que realiza cada día por las familias hidalguenses, mi reconocimiento.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1O-TsQrmRtjBNEPcqv5ePJdpPIuL953Rb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Edda Vite presenta resultados de cuatro años de trabajo al frente del DIF Hidalgo</t>
+  </si>
+  <si>
+    <t>Ayer tuvimos un evento muy importante, la señora Edavite Ramos, presidenta del Patronato DIF Hidalgo, presentó el cuarto informe de actividades y en él destacó los principales resultados que fueron alcanzados en estos meses, en estos últimos 12 meses, primero el tema de eh pues lo que fue el último año y, por supuesto, en el resumen de toda la administración con trabajo hacia los grupos prioritarios, con acciones en materia de salud, alimentación, educación y, por supuesto, cercanía con la población. Siempre hay mucho que hacer, dijo la señora Edda Vite, proyectos por por concluir, programas por ampliar y acciones que motivan y que, por supuesto, nos ayudan a llegar a quienes más lo necesitan. Ese es nuestro compromiso y con amor lo asumimos, así expresó ante los hidalguenses beneficiados de los programas de asistencia social implementados durante su gestión, asociaciones de la sociedad civil, iniciativa privada e integrantes de la familia, de toda la familia hidalguense. Déjenme les digo que este evento tuvo verificativo en el Teatro Gota de Plata, allá en el Centro Cultural Hidalguense, ayer por la tarde, como invitado especial, por supuesto, el gobernador de nuestro estado, el licenciado Julio Menchaca y, por supuesto, también estuvo invitado especial, recibida ahí por muchos aplausos y muchos reconocimientos, Rocío García Pérez, que es titular del Sistema Nacional DIF y, bueno, junto con el gobernador y junto con la señora Edda Vite, bueno, pues estuvieron encabezando este evento. La señora Edavite agradeció el respaldo y colaboración del Sistema DIF Nacional, dijo, "Este ejercicio de transparencia se realiza luego de que fuera interrumpido en el 2025 debido a las labores de apoyo brindadas por el organismo ante la emergencia ocasionada por la vaguada monzónica". Recuerden que el año pasado, exactamente en estas fechas, la señora Edavite era quien estaba al frente de toda la organización de la ayuda que se concentraba en el aeropuerto Juan Guillermo Villasana, se habilitó un hangar para organizar toda la ayuda que llegaba vía donaciones o la ayuda del gobierno federal o la ayuda del gobierno del estado para distribuirla entre las personas que más lo necesitaban en los municipios más afectados por la vaguada monzónica, por este evento natural, fue necesario que se pospusiera, en este caso, pues ya se suspendió hasta este cuarto año la ceremonia o el evento de informe de la señora Edda Vite. Bueno, este año sí fue posible y, bueno, la señora Edavite destacó que en materia de salud, la entrega de apoyos de programas proyectos productivos denominado Hacia una vida mejor, del Centro de Rehabilitación Integral de Hidalgo, el CRIH, tuvo una inversión federal de 13 millones de pesos para beneficiar a más de 300 familias de 83 municipios y que cuentan con una persona, o en estas familias tienen personas con discapacidad permanente. El programa pues tiene como fin impulsar emprendimientos y fortalecer la economía. De la misma manera resaltó la puesta en marcha de Pilares, Centro de Salud Mental y Fortalecimiento Familiar, esto con una inversión de 12,291,127 pesos para contribuir a la atención de problemáticas como la depresión, la ansiedad y la y la ideación, así se denomina, ideación suicida, en concordancia con la Estrategia Nacional de Salud Mental. En el rubro de alimentación informó sobre la ampliación del programa Primeros 100 Días de Vida para incorporación a niños y niñas de 2 a 5 años con 11 meses que no están escolarizados, con una inversión federal de 169 millones de pesos. El programa registró 27,103 beneficiarios, Aldo Falcón, y la entrega de 175,198 canastas alimentarias. También recordó la reconoció la coordinación entre los gobiernos federales y estatales, así como la ciudadanía durante la contingencia provocada por la vaguada monzónica del 2025, que, bueno, pues obligó y que permitió entregar 94,096 despensas. De estas, 59 59,730 se destinaron a municipios afectados por el fenómeno climático y 34,366 a localidades con grados de marginación alto y muy alto. En educación destacó la incorporación del modelo nacional Pilares, que cuenta con 113 centros activos en nuestra entidad y ofrece espacios para el aprendizaje, el desarrollo de habilidades y la convivencia de niños, niñas y adolescentes, personas mayores y personas con discapacidad. A estas acciones se sumó la entrega de la beca Pilares a 2,968 usuarios mediante una inversión estatal de 6,15,000 pesos. Asimismo, resaltó las obras de infraestructura para atención infantil, la construcción del Centro de Asistencia Infantil Comunitario CAIC Colonias del Sur con 8,200,000 pesos, la rehabilitación y ampliación del CAIC Bomberos con 9,000,000 de pesos y la adquisición de un terreno para construir el CAIC Matilde, que tenía una inversión conjunta de 5,000,000 de 5,500,000 pesos. En el eje de cercanía, Edda Vite Ramos agradeció la colaboración de las dependencias estatales, la sociedad civil, la iniciativa privada y los siete sistemas y los los sistemas municipales DIF, cuya participación permite acercar los programas de asistencia social a la población de los 84 municipios de Hidalgo. Entre las acciones destacadas se encuentran las reuniones técnicas para el fortalecimiento de los sistemas municipales DIF orientadas a difundir los programas disponibles. De igual manera, reconoció la coordinación del Poder Judicial del Estado de Hidalgo que contribuyó para agilizar los procesos de adopción. Ese es un tema que de verdad destaca a nivel nacional y que ha sido motivo de reconocimiento en México hacia nuestro estado. Este modelo, nuevo modelo de adopción que permitió en la actual administración de Edda Vite Ramos en el Patronato del DIF que 61 niñas, niños y adolescentes bajo resguardo en los Centros de Asistencia Social del DIF encontraran un nuevo hogar. Como ustedes saben, el procedimiento, y eso era un tema de seguridad buscando garantizar las mejores condiciones para las niñas, los niños y los adolescentes, el procedimiento o el proceso de adopción en nuestro país, en el estado de Hidalgo no era la excepción, era muy complicado, era un marasmo de burocracia gracias a un programa implementado en Hidalgo que buscó no simplificar, no facilitar, sino tener rutas más accesibles apegadas a la ley, buscando siempre garantizar la seguridad de las niñas, los niños y los adolescentes se logró tener una digamos ruta segura ágil y muy muy apegada, totalmente apegada a la ley para el tema de la adopción. Finalmente la señora Edavite destacó el trabajo del Congreso del Estado de la 66 Legislatura para impulsar una reforma legal que permitió la creación de las procuradurías municipales de protección de niñas, niños y adolescentes con facultades para ejecutar medidas de protección ante posibles vulneraciones de los derechos de estos de estos sectores. Como resultado, el Sistema DIF Hidalgo refrenda su compromiso de fortalecer la asistencia social mediante el trabajo coordinado entre instituciones y sociedad con el objetivo de mejorar las condiciones de vida a quienes más lo necesitan</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-g7Xxvc9whtdNJ2L8PQLl85LScqB8UCj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso del Estado, Poder Judicial del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Rocío García Pérez, Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Andrés Torres menciona que han estado un mes fuera del aire en la estación de radio 91.1 FM (Jacala). Asegura que han hecho su parte en la producción de programas, pero los responsables de mantener las estaciones en funcionamiento no lo han logrado. Esto resulta en no cumplir las metas de transmisión. También destaca que han estado fuera del aire en varios lugares, como Huejutla y Jacala y esto se debe a la falta de esfuerzo de algunos trabajadores, quienes encuentran excusas para no trabajar, como la distancia, el clima o la falta de transporte y viáticos. A pesar de estos obstáculos, Andrés subraya que ellos producen más de 110 programas originales, en lugar de simplemente repetir contenido como ocurre en la televisión y en donde solo producen 2 programas. Critica a quienes falsifican firmas o cambian fechas, diciendo que no están engañando a nadie, y que al final la verdad siempre sale a la luz. Refiere que la falta de compromiso y seriedad en el trabajo diario es un gran obstáculo. Andrés también menciona que hay personas que hacen ruido y amenazan, lo que contribuye a un mal ambiente laboral. A pesar de estos desafíos, él y su equipo continúan esforzándose por hacer un buen trabajo. " Como esto que les estoy contando, pero bueno, pues con eso tenemos que luchar todos los días, todos los días, este la transversalidad es el principal este obstáculo de el trabajo, ¿no? Las ocurrencias, las locuras, las estridencias, ¿no? De un de un tipejo, ¿no? Que dice que sabe, pero lo único que hace es gritar y amenazar, lo cual también, pues por supuesto, este significa una falta en el tema laboral, pero bueno, así es, hay quien lo soporte, ¿no? A ver quién lo aguanta."</t>
+  </si>
+  <si>
+    <t>RTVH</t>
+  </si>
+  <si>
+    <t>Mal Desempeño</t>
+  </si>
+  <si>
+    <t>**Andrés Torres:** ...te decía que tenemos un mes fuera del aire allá en el 91.1 de frecuencia modulada. Pues nosotros ya hicimos lo que nos corresponde, ¿no? Y bueno, pues ya será cuestión de los responsables de tener las estaciones al aire y luego por eso no se cumplen las metas, ¿no? Luego por eso no, no se cumplen las metas, plantean metas de transmisiones este en algunas cuestiones este numéricas y luego te dicen, "¿Por qué no se cumplió la meta?" Porque estuvimos tres veces fuera del aire en Huejutla, porque estuvimos un mes fuera del aire en Jacala, ¿no? ¿Y por qué estamos fuera del aire? Pues alguien no quiere trabajar, ¿no? Alguien no se quiere, se le hace muy lejos ir a Huejutla a a trabajar, les da calor, les da frío, este no tienen vehículo, no les dan viáticos, no tienen ganas, ¿no? No tienen ganas de trabajar y entonces, pues afectan la labor de todos los que estamos, ¿no? Estamos de verdad, este, pues produciendo, ¿no? No mintiendo, sino, ¿verdad?, produciendo programas para radio, ¿no? No traemos, porque lo más sencillo sería poner las repeticiones, ¿no? Colgarnos de el trabajo ajeno, como hacen, por ejemplo, en el área de televisión, ¿no? Que se cuelgan de todo, ¿no? Y tienen dos programas propios, ¿no? Aquí en radio tenemos 100, más de 110 programas este que producimos aquí y que son nuestros y no mentimos, no engañamos a nadie y sobre todo, pues no estamos este pues haciendo cosas indebidas, ¿no? Como podría ser falsificando firmas, este cambiando fechas, ¿no? Y mintiendo y mintiendo y mintiendo sobre pues lo que supuestamente es el trabajo, pero pues al final no se refleja, ¿no? Y entonces al final nada se oculta bajo el sol y todo, todo sale a la luz, ¿no? Como esto que les estoy contando, pero bueno, pues con eso tenemos que luchar todos los días, todos los días, este la transversalidad es el principal este obstáculo de el trabajo, ¿no? Las ocurrencias, las locuras, las estridencias, ¿no? De un de un tipejo, ¿no? Que dice que sabe, pero lo único que hace es gritar y amenazar, lo cual también, pues por supuesto, este significa una falta en el tema laboral, pero bueno, así es, hay quien lo soporte, ¿no? A ver quién lo aguanta</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QprEzh7VXZ2NwHuL3pvq4sWgKcEVuV6d/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Hay que estar muy atentos en la región de Tula Tepeji. La Comisión Nacional del Agua, el Sistema Estatal de Protección Civil y las autoridades municipales están monitoreando de manera constante la presa Endhó y otros embalses en esta área. Existen varios lagos, incluyendo un lago artificial y lagos naturales. Las zonas residenciales importantes en Tepeji están siendo vigiladas, especialmente la presa Requena, para prevenir cualquier riesgo para la población.</t>
+  </si>
+  <si>
+    <t>Monitoreo De Presas</t>
+  </si>
+  <si>
+    <t>Tula Tepeji</t>
+  </si>
+  <si>
+    <t>Hay que estar muy pendientes allá en la región de Tula, Tepeji, bueno, pues la Comisión Nacional del Agua, el Sistema Estatal de Protección Civil, las autoridades municipales tienen un monitoreo permanente de la presa Endhó y de todos los embalses que están en esta región. Recuerden ustedes que hay varios lagos, hay un lago artificial y hay varios lagos naturales en la zona, hay zonas residenciales importantes, sobre todo en la zona de Tepeji, Y bueno, pues están siendo monitoreados estos embalses, la presa requena por supuesto, para evitar alguna situación que pudiera representar un riesgo para la población. El río Rosas, el río Tula, por supuesto todos los canales que componen o que integran este sistema hidráulico allá en la zona de Tula-Tepeji están siendo monitoreados. Esperamos que eleven sus niveles Y bueno pues también por supuesto Los márgenes de Arreotula seguramente Se van a elevar un poquito Con las lluvias</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1AW1mvIvG6cVec37TTs9sFapA9TQ4qdBZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Este fin de semana termina la feria San Francisco Pachuca 2026, con un gran cierre. Si planea asistir a los eventos en el Teatro del Pueblo o en el palenque, recuerde llevar paraguas y un suéter, ya que es posible que llueva. Sin embargo, esto no detendrá los eventos. El lunes se dará un informe sobre el saldo final de la feria, pero ya se sabe que se van a romper algunos récords de asistencia, lo que indica que ha sido un evento muy exitoso.</t>
+  </si>
+  <si>
+    <t>Turismo</t>
+  </si>
+  <si>
+    <t>OEEH</t>
+  </si>
+  <si>
+    <t>Feria Pachuca</t>
+  </si>
+  <si>
+    <t>Este fin de semana concluye la feria San Francisco Pachuca 2026. Va a haber un enorme, un gran cerrojazo para esta edición. Si usted tiene planeado este fin de semana disfrutar de los eventos del Teatro del Pueblo o del palenque o se halla en la feria, no olvide llevarse su parné, no olvide llevarse pues un suéter porque es probable que tengamos lluvia, pero eso no va a suspender, eso no nos va a detener para concluir con todo lo alto con estos eventos feriales. Ya le estaremos dando el lunes el reporte, el saldo final de cómo estuvo la edición 2026 de la Feria Pachuca San Francisco, pero se lo adelanto, se van a romper algunos récord de asistencia. Se van a este ya está confirmado algunos récord de asistencia, lo que pues habla de un un evento muy exitoso. El lunes, el lunes lo platicamos con calma.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1d5LdYuarFM2zBLWAXs2t5wiYFupTlial/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil del Estado de Hidalgo ha comunicado un pronóstico de lluvias fuertes debido al frente número 2 y su masa de aire polar. Estas lluvias se esperan del 15 al 18 de octubre, afectando principalmente durante el fin de semana. El viernes 16 de octubre se anticipan lluvias torrenciales que podrían alcanzar los 150 a 250 mm, lo que puede provocar inundaciones en áreas bajas, crecidas de ríos y arroyos, deslizamientos de tierra y desprendimiento de rocas. Andrés Torres hace un llamado a la población para que esté atenta a la información que se transmitirá por Radio y Televisión de Hidalgo y a las directrices que se compartirán en caso de alguna emergencia. Además, se recomienda que la ciudadanía esté informada a través de los gobiernos municipales sobre albergues y rutas de evacuación que se establecerán si es necesario. Indicó que durante el periodo de lluvias torrenciales, se aconseja a la población evitar acercarse a ríos y arroyos, ya que el nivel del agua puede aumentar rápidamente y sin previo aviso. La gente debe estar en comunicación con sus familias y seguir las recomendaciones de Protección Civil, que incluyen mantenerse informado por fuentes oficiales y evitar cruzar zonas inundadas. Advierte a quienes planean viajar a la Huasteca y la Sierra que reprogramen sus planes si es posible, ya que las condiciones climáticas serán peligrosas. La recomendación general es cuidarse y extremar precauciones, especialmente en la carretera.</t>
+  </si>
+  <si>
+    <t>Alerta Meteorológica</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil del Gobierno del Estado de Hidalgo, dependiente de la Secretaría de Gobierno, nos hace un llamado, nos hace un anuncio, también el gobernador de nuestro estado, Julio Menchaca Salazar, ya en redes sociales posteó esta información, Aldo Falcón. **Aldo Falcón:** Así es, Andrés, la Subsecretaría de Protección Civil y Gestión de Riesgos del Estado de Hidalgo da a conocer el pronóstico de lluvias fuertes en el estado de Hidalgo, debido al frente número 2 y su masa de aire polar ocasionará lluvias fuertes en el estado, acompañadas de descenso de temperatura y vientos intensos con posibles afectaciones. Esto es del período del 15 al 18 de octubre, prácticamente todo el fin de semana. Para este viernes 16 de octubre se esperan lluvias torrenciales de 150 a 250 mm en el estado de Hidalgo. Las posibles afectaciones serán inundaciones en zonas bajas, crecidas de ríos y arroyos, deslaves en zonas serranas y desprendimiento de rocas. **Andrés Torres:** Muy bien, vamos a insistir en este asunto. De acuerdo al pronóstico del clima para este fin de semana, esperamos lluvias torrenciales, lluvias torrenciales en la zona principalmente de la Huasteca y en la Sierra. Por favor, a todo nuestro auditorio, a toda la gente que nos esté escuchando, le solicitamos poner mucha atención, estar muy atentos a la señal de Radio y Televisión de Hidalgo, donde le estaremos dando seguimiento a las condiciones del clima y también, en caso de alguna contingencia, estaremos dando información para saber qué hacer, a dónde dirigirse en caso de que existiera algún problema. También, yo le recomiendo muchísimo estar pendiente de la información que a través de las presidencias municipales en todas estas regiones, la Huasteca, la Sierra, parte de la Sierra Alta de nuestro estado, vamos a generar, junto con las autoridades de nuestro estado, para identificar en su caso los albergues, las rutas de salida, las rutas de evacuación, en caso de ser necesario. Tenemos esta advertencia: lluvias torrenciales a partir de el 15 al 18 de octubre, es decir, en los próximos, a partir de ayer y hasta el próximo lunes, prácticamente tendremos esta condición del clima. Cuídese mucho, estén muy atentos a la señal de las Vocales Radio, de estar comunicados también con la familia, evite acercarse a ríos, arroyos, a cuerpos de agua, cualquier situación puede ser de riesgo porque las crecidas, la el nivel de los estos afluentes puede crecer de forma muy rápida y sin aviso, así que hay que estar muy atentos, por favor, cuídese mucho. **Aldo Falcón:** Así es, de hecho las recomendaciones es mantenerse informado a través de las fuentes oficiales, evitar cruces, ríos, arroyos en zonas inundadas, extremar precauciones en la carretera y seguir las indicaciones de Protección Civil. **Andrés Torres:** Así es, si usted tiene planeado viajar este fin de semana en la Huasteca y en la Sierra, por favor, cuídese mucho, reagende si es posible, no se exponga porque tendremos lluvias muy fuertes para este fin de semana.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JDeYO--XEgmVRCyZX27k5p5M0v4qRrvT/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radio y Televisión de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Andrés Torres: desafortunadamente ya tenemos un mes fuera del aire, allá en Zacualpan de Ledesma con nuestra estación 91.1 de frecuencia modulada. Tenemos problemas técnicos y bueno pues el área administrativa de Radio y Televisión de Hidalgo, ahí está pues tratando de resolver. Tenemos ya un mes esperando respuesta, también el área técnica pues está involucrada en este asunto. Mientras tanto, pues en redes sociales llegamos a la Sierra Gorda de nuestro estado.</t>
+  </si>
+  <si>
+    <t>Radiodifusoras</t>
+  </si>
+  <si>
+    <t>Desafortunadamente ya tenemos un mes fuera del aire, allá en Zacualpan de Ledesma con nuestra estación 91.1 de frecuencia modulada. Tenemos problemas técnicos y bueno pues el área administrativa de Radio y Televisión de Hidalgo, ahí está pues tratando de resolver. Tenemos ya un mes esperando respuesta, también el área técnica pues está involucrada en este asunto. Mientras tanto, pues en redes sociales llegamos a la Sierra Gorda de nuestro estado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1N2jlzuZKF0mncpvY9czh7zELDQLF2saL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Con la participación de alrededor de mil supervisores, docentes y padres de familia, el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, impartió la conferencia magistral "El papel de las madres, padres y personas tutoras en la formación de los hijos". Durante el evento, enmarcado en las acciones de la administración del gobernador Julio Menchaca Salazar, se destacó la creación de la Dirección General de Acompañamiento Socioemocional y Educativo para brindar herramientas a las familias. Asimismo, se enfatizó la importancia del afecto, la escucha activa y la colaboración entre el hogar y las escuelas para garantizar el desarrollo integral de la niñez hidalguense.</t>
+  </si>
+  <si>
+    <t>Jesús Riveros</t>
+  </si>
+  <si>
+    <t>Enlace Hidalgo2</t>
+  </si>
+  <si>
+    <t>Conferencia magistral</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fM6dYVeDfl2CjD3x95VFot5ZdjRNuWNw/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Tras el trágico suceso ocurrido la mañana del lunes en el exterior de las oficinas de Servicios Regionales de la SEP en Tulancingo, donde un trabajador perdió la vida a causa de disparos de arma de fuego, la Secretaría de Educación Pública de Hidalgo emitió un comunicado oficial. En el documento, la dependencia expresó sus condolencias a los familiares y compañeros de la víctima, y reiteró su disposición para colaborar plenamente con las autoridades ministeriales encargadas de las investigaciones correspondientes.</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Tulancingo</t>
+  </si>
+  <si>
+    <t>Retomando sobre el tema del lamentable suceso que se dio hoy por la mañana afuera de las oficinas de servicios regionales aquí en Tulancingo, de servicios regionales de la Secretaría de Educación Pública, este pues precisamente la la SEP emitió un comunicado, un pues sobre todo un un escrito que va dirigido a la sociedad en general y a la comunidad educativa que señala: "La Secretaría de Educación Pública de Hidalgo expresa su profundo pesar por el lamentable fallecimiento de un trabajador adscrito a servicios regionales de Tulancingo, ocurrido esta mañana al exterior de las oficinas de dicha subdirección. En estos momentos de dolor, extendemos nuestras más sinceras condolencias y respaldo a sus familiares, amistades, compañeras y compañeros de trabajo. La dependencia brinda acompañamiento institucional y colaboración con las autoridades competentes, quienes serán las encargadas de realizar las indagatorias correspondientes de este lamentable hecho. Por respeto a la víctima, a su familia y al debido proceso de investigación, la SEP se mantendrá atenta a la información oficial que determinen las instancias responsables. La Secretaría refrenda su solidaridad con la familia, comunidad educativa y manifiesta su confianza en que las autoridades darán seguimiento al caso hasta su esclarecimiento". Esto que lamentablemente, pues una de las noticias con la cual iniciamos la semana el día de hoy, muy muy lamentable, eh este este varón que fue por ahí ultimado con con un balazo en el pecho, hoy por la mañana afuera de las oficinas de servicios regionales. Descanse en paz y pues ya el tema está en las autoridades y por supuesto nuestras sinceras condolencias a sus a sus familiares. Un abrazo a ellos y pronta resignación.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15O5seBycnkDWEh3apNRGrq8sVk9k_uai/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>_ SEPH/Bol.1936/2026</t>
+  </si>
+  <si>
+    <t>Realiza SEPH Jornada Pedagógica Estatal de Educación Física</t>
+  </si>
+  <si>
+    <t>Irving Sánchez</t>
+  </si>
+  <si>
+    <t>Formación continua</t>
+  </si>
+  <si>
+    <t>Vamos ahora al tema educativo. La Secretaría de Educación Pública de Hidalgo realizó la jornada pedagógica estatal de educación física, con la participación de docentes especialistas en un espacio de formación e intercambio de experiencias para enriquecer la práctica pedagógica y contribuir al desarrollo integral de niñas, niños y adolescentes. En representación del secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, la subsecretaria de Educación Básica, Nancy Adriana León Vite, destacó la importancia de impulsar la formación continua de las y los educadores físicos, reconocer su contribución a la educación de las nuevas generaciones. Asimismo, agradeció a las y los docentes su compromiso con la actualización profesional y resaltó su labor en la promoción de hábitos saludables y la sana convivencia. El programa contempló cuatro conferencias relacionadas con los principios de Nueva Escuela Mexicana y los retos de educación física en las escuelas hidalguenses, además de un taller de elaboración de material didáctico basado en el trabajo académico desarrollado durante el ciclo escolar 2025-2026 para la subdirección de educación física. En el encuentro estuvieron presentes, en representación de Said Vargas Sáenz, secretario general de la Sección 15 del SNTE; Jorge Sánchez Lazcano, secretario de Organización; y el subdirector de educación física, Luis Enrique Sánchez Méndez. Que también la educación física es muy importante para el desarrollo de las y de los alumnos de cualquier nivel</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hDtQlI3k2J69LKx4XyPJV8qGS1dPc-Zx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón, Said Vargas Sáenz, Luis Enrique Sánchez Méndez</t>
+  </si>
+  <si>
+    <t>Durante la sesión en el Congreso del Estado de Hidalgo, el diputado Avelino Tovar Iglesias (Partido Verde Ecologista de México) presentó una iniciativa orientada a dignificar los centros de rehabilitación de adicciones, estableciendo protocolos de atención a crisis, rutas médicas claras y la regulación de espacios para menores de edad. Ante esto, la secretaria de Salud, Vanessa Escalante Arroyo, respondió de manera positiva a la propuesta de colaboración interinstitucional, reconociendo la atención en municipios como San Agustín Tlaxiaca y destacando la importancia del trabajo coordinado con los ayuntamientos y diversas secretarías para salvaguardar el bienestar y los derechos humanos de la juventud hidalguense.</t>
+  </si>
+  <si>
+    <t>Locutor David Cárdenas: En más de la información, construir puentes por la niñez coincide en el Congreso y la Secretaría de Salud en la ruta de atención y regulación de centros de rehabilitación. Avelino Tovar Iglesias llevó a la tribuna del Congreso del Estado de Hidalgo un tema prioritario: la atención integral a la niñez y la juventud que enfrenta problemas de adicciones. Le informo en un ejercicio de diálogo constructivo y absoluta responsabilidad institucional, el diputado Avelino Tovar Iglesias llevó a la tribuna del Congreso de Hidalgo un tema fundamental, un tema prioritario: la atención integral a la niñez y la juventud que enfrenta lamentablemente problemas de adicciones. El legislador planteó un puente de colaboración con la Secretaría de Salud para dignificar los espacios de apoyo y salvaguardar los derechos humanos de los usuarios. El Partido Verde Ecologista de México en Hidalgo, a través de la voz de Tovar Iglesias, reconoció el esfuerzo que la secretaria de Salud, Vanessa Escalante, realiza a través de las brigadas de verificación a tiempo que propuso sumar experiencia y voluntad para atender los retos que se viven en el terreno operativo. Entre los puntos fundamentales planteados a la dependencia destacan tres ejes de entendimiento mutuo. Escuchemos a Avelino Tovar.
+Diputado Avelino Tovar Iglesias: ...sabemos como aliado de estos temas. Y en mayo presenté una iniciativa para que los centros de rehabilitación de adicciones se pueda garantizar un trato digno, sin maltratos ni castigos y con protocolos para poder atender crisis y emergencias. Después de presentarla me senté a escuchar a quienes operan estos centros y cambió completamente la conversación porque hay cosas que desconocía, como por ejemplo que a los centros están llegando niñas y niños de 12, 13, 14, 15 años y no existe un lugar adecuado ni una ruta clara para canalizarlos. También que cuando una persona llega con una crisis de abstinencia, con convulsiones o con un brote psiquiátrico, no hay dónde estabilizarla antes de iniciar su tratamiento. Y los centros están pidiendo protocolos y una ruta médica. Y tercero, los centros que ya se registraron y se esfuerzan por cumplir, piden también algo justo. Quieren que la verificación llegue también a quienes operan en la clandestinidad y que no se le exija lo mismo a un grupo de ayuda mutua que a una clínica profesional. Y reconocemos lo que su secretaría ya hace, que es el operativo de verificación, y también pues le comento, la iniciativa que presenté no está cerrada y por eso le pregunto tres cosas, secretaria: primero, ¿cuál es hoy la ruta de atención para un adolescente de 14 años con una adicción que necesita internamiento y a dónde se le canaliza? Segundo, si contempla la Secretaría una unidad de desintoxicación o de toxicología en Hidalgo para poder estabilizar a una persona antes de canalizarla a un centro? Y tercera, si estaría usted en disposición para que podamos trabajar de manera conjunta y sus primeros entregables serían pues la plataforma pública, los protocolos de crisis y traslado y la ruta de atención a menor?
+Locutor David Cárdenas: En su oportunidad, la secretaria de Salud del Estado de Hidalgo, Vanessa Escalante Arroyo, respondió positivamente a esta invitación que hizo el diputado Avelino Tovar.
+Dra. Vanessa Escalante Arroyo (Secretaria de Salud): ...diputado, cuente con una servidora y con todas y todos los que integramos la Secretaría de Salud, porque estamos dispuestos precisamente sobre todo en atender estos temas críticos. Quiero comentarle precisamente que acabamos de acudir —y voy a citar el nombre del municipio— a San Agustín Tlaxiaca. Veíamos nosotros un foco en ese en ese lugar de atención por temas de uso de sustancias de algunos estudiantes menores precisamente de 15 años. Este tema se abordó incluso también con la Secretaría de Educación Pública y con la Secretaría de Seguridad Pública, de una forma en la que podamos actuar de manera integral por el cuidado de nuestras niñas, niños y adolescentes en el estado de Hidalgo. Y obviamente esto también entra en el marco de los derechos humanos de los jóvenes, pero sobre todo de la responsabilidad compartida que tenemos cada uno de nosotros y no hacer de un lado —porque tiene que trabajar en paralelo— las y los presidentes municipales. Ellos son claves en la conducción de estas políticas en materia de salud.
+Locutor David Cárdenas Con este intercambio cordial, ambas partes afirman que la salud mental y la protección de las nuevas generaciones en Hidalgo son una causa común que exige coordinación, empatía y trabajo en equipo. Continuamos en más de la información.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/192B_hCRzRdo9y2fhqiz2drp2Ihoci8xy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Avelino Tovar Iglesias</t>
+  </si>
+  <si>
+    <t>SSH/Bol.180/2026</t>
+  </si>
+  <si>
+    <t>Durante su comparecencia ante el Congreso del Estado de Hidalgo en el marco de la glosa del cuarto informe de gobierno, la secretaria de Salud, Vanessa Escalante Arroyo, destacó los avances en materia de infraestructura médica y prevención. Entre los proyectos principales, resaltó la construcción y equipamiento del nuevo Hospital General de Actopan —con una inversión superior a los 861 millones de pesos—, obra destinada a saldar una deuda histórica y beneficiar a 132,000 habitantes del Valle del Mezquital ampliando su capacidad a 60 camas y cuatro quirófanos. Asimismo, informó sobre inversiones en centros especializados como el CAPASITS y el centro contra adicciones en Tulancingo, bajo los principios de universalidad, transparencia y combate a la corrupción.</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>En este mismo marco, en el Congreso del Estado de Hidalgo, ha comparecido el día viernes la Secretaria de Salud, Vanessa Escalante, con ocasión del Congreso de Hidalgo y destacó avances en infraestructura médica y vacunación. En sesión ordinaria se llevó a cabo también esta comparecencia de la doctora Vanessa Escalante Arroyo, quien compareció ante el Congreso del Estado Libre y Soberano de Hidalgo como parte del procedimiento relativo al cuarto informe del Estado que guardan los diversos ramos de la administración. En esta materia, ya ha destacado la Secretaria de Salud los avances que se tienen en infraestructura médica, en construcción y equipamiento del Hospital General de Actopan, con una inversión superior a 861 millones de pesos para beneficiar a 132,000 habitantes del Valle del Mezquital. Escuchemos a la Secretaria de Salud, Vanessa Escalante.
+Dra. Vanessa Escalante Arroyo: Avanzamos hacia una salud pública centrada en la prevención y la atención universal, para que todas las personas reciban servicios médicos de calidad sin que su lugar de residencia o condición económica sean una barrera. Nuestro trabajo se sostiene en cuatro principios: presencia en territorio, especialmente donde existe mayor rezago social, uso suficiente del presupuesto, transparencia y combate a la corrupción. Un pueblo sano es un pueblo con futuro. Fortalecemos la infraestructura de salud, esto significa que acercamos diagnósticos oportunos y atención especializada. Por eso destinamos recursos a mejorar espacios y el equipo médico en distintas regiones de nuestro estado. Invertimos más de 15.8 millones de pesos en espacios de atención, incluidas las ampliaciones del Centro de Atención Integral contra las Adicciones de Tulancingo de Bravo y del Centro Ambulatorio para Prevención y Atención de SIDA e Infecciones de Transmisión Sexual (CAPASITS), para ampliar y mejorar sus servicios. La obra principal es el Hospital General de Actopan, con más de 506 millones de pesos destinados a su construcción y más de 355 millones para su equipamiento. Con ella, hemos atendido una deuda histórica: 132,000 habitantes del Valle del Mezquital, que comprenden a siete municipios, tendrán un impacto directo en su población, aumentando la infraestructura de 30 a 60 camas y con cuatro quirófanos que estarán funcionando como un nodo estratégico de descompresión sanitaria cuando tengan esta atención médica.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PxdbatLwOT_7viLffhbee-KmuvqRr4oe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>STPSH/Bol.89/2026</t>
+  </si>
+  <si>
+    <t>Durante la continuación de las comparecencias de la tarde, el locutor introdujo la intervención del titular de la Secretaría del Trabajo, destacando la importancia de la rendición de cuentas como un diálogo fundamental que enriquece la vida democrática y fortalece al Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Continuamos hoy también en esta tarde en las comparecencias y vamos a escuchar al titular de la Secretaría del Trabajo... [audio con interferencia] ...entendemos que la rendición de cuentas con la ciudadanía es un diálogo que enriquece la vida democrática de nuestra entidad y en consecuencia fortalece al Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1V4Wj06ODTcOzp2DCqgEHoYzsVvBbAWHe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Se dio a conocer el inicio de la segunda semana de comparecencias de las y los secretarios del gabinete del gobierno del estado de Hidalgo, correspondientes a las actividades de glosa en el marco del cuarto informe de gobierno presentado por el mandatario estatal Julio Menchaca Salazar.</t>
+  </si>
+  <si>
+    <t>Gobierno</t>
+  </si>
+  <si>
+    <t>Continuamos en la información del día de hoy. Se inicia la segunda semana de comparecencias de secretarios del gobierno del estado de Hidalgo, en el marco del cuarto informe de gobierno del mandatario Julio Menchaca Salazar.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yNq3-sNeYbVQKMDx-D5qJ6J8mZb-YRUL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Mediante enlace desde el notimóvil desde la colonia Media Sierra, frente a las oficinas de los Servicios Regionales de la SEP, René Aguilar informó sobre una agresión armada perpetrada en el exterior del inmueble. Los primeros reportes preliminares indicaban la presencia de una persona sin vida en el lugar. Debido a los protocolos de seguridad, la zona fue cercada por elementos policiales y autoridades estatales a la espera de la policía ministerial para realizar las diligencias e investigaciones correspondientes.</t>
+  </si>
+  <si>
+    <t>Lamentablemente se confirma, se confirma por ahí una agresión con arma de fuego en en las inmediaciones de las oficinas de servicios regionales de la SEP. René, estamos contigo, ¿estás en el lugar de los hechos?
+Así es, Jesús. Exactamente nos encontramos justamente aquí en la colonia Media Sierra, como bien lo mencionabas, frente a Servicios Regionales de la SEP, donde pues bueno, hace unos instantes se nos reportó precisamente esta situación de una balacera en donde está probablemente una persona sin vida, es lo que nos están indicando hasta este momento. Vamos a intentar recabar mayor información posible, sin embargo, pues es un poco complicado, ya que todo está cercado y pues las autoridades estatales pues no nos permiten directamente el acceso hasta que se vaya solucionando esta situación. Sin embargo, pues vamos a tratar de hacer también un un enlace en vivo vía Facebook, vía redes sociales para informar de la situación y estaremos al pendiente de toda la información que se pueda recabar.
+Sí, gracias, gracias René, sí, si está acordonado, quiere decir que efectivamente una persona ha fallecido y pues tendrá que llevarse a cabo el procedimiento de ley, eh que en estos casos se realiza, como lo es el acordonamiento, la toma de datos por parte de los primeros respondientes, policía municipal, policía estatal nos dices y obviamente el arribo de policía ministerial para llevar a cabo las diligencias correspondientes. Eh hasta el momento es lo que podemos, lo que podemos mencionar. Lo que salta la duda, René, no sé si tú alcanzas a percibir o si sabes, si te han comentado algo, si la agresión fue al interior de las oficinas o al exterior?
+Fue al exterior, Jesús, lo que nos mencionan este personas eh que hemos podido platicar con ellos, es al exterior eh de las oficinas de servicios regionales donde sucedió esta situación.
+Okay, gracias, gracias también por la aclaración, René.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Vwx3RhJy1JI9m8pJYFfO6dROdxo-K-df/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Mañanera</t>
+  </si>
+  <si>
+    <t>Durante la transmisión en directo desde la Sala del Pueblo del Ejecutivo estatal, el titular de comunicación, Edmundo Pineda, destacó la conmemoración del Día Mundial Contra el Cáncer de Mama este 19 de octubre. Asimismo, presentó materiales en video sobre las condiciones climáticas provocadas por las lluvias en la entidad, sirviendo de enlace entre las intervenciones del director del Sistema DIF Hidalgo, Ricardo Alvizo, y el subsecretario de Protección Civil y Gestión de Riesgos, Román Bernal Díaz.</t>
+  </si>
+  <si>
+    <t>Atención Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>Y justamente ahora está comenzando la participación de Román Bernal, subsecretario de Protección Civil. Los dejamos con la información que está brindando el funcionario estatal.
+Román Bernal Díaz: Al presentarse esta vaguada, se han tomado medidas de manera estratégica para coordinar la gestión del riesgo y prever la atención de emergencias. Se crearon 13 unidades regionales de protección civil para agilizar la reacción ante emergencias y facilitar el apoyo intermunicipal en caso de incidentes. Se brindó capacitación a través de visitas a los municipios y comunidades para la formación de brigadas comunitarias de protección civil, protocolos de evacuación y primeros auxilios. Estas acciones buscan fortalecer la percepción del riesgo y mejorar la preparación de la ciudadanía ante posibles emergencias. En 2026, principalmente en la Sierra Otomí-Tepehua, se realizaron actividades teóricas y prácticas de campo, incluyendo análisis de zonas susceptibles de deslizamiento de tierra y evaluación de laderas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VpRedmBj_WERxyMaSG7PJJV5sDFSLl2i/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Román Bernal Díaz</t>
+  </si>
+  <si>
+    <t>Mañanera de Hidalgo</t>
+  </si>
+  <si>
+    <t>Continuamos desde la Sala del Pueblo, en la sede del Ejecutivo estatal, en la transmisión en directo de la conferencia matutina semanal del gobierno del estado. Entre la culminación de la participación de Ricardo Alvizo, director general del Sistema DIF Hidalgo, y el inicio de lo que será la participación del subsecretario de Protección Civil y Gestión de Riesgos, Román Bernal Díaz, el titular de comunicación, Edmundo Pineda, ha hablado acerca, ha enfatizado acerca del Día Mundial Contra el Cáncer de Mama, que se conmemora justamente hoy, 19 de octubre, y también ha presentado información unos videos sobre condiciones que prevalecen por las lluvias en la entidad.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1S3Kra3D8J3Bciq_pHASCd9YX4sG_LQ2c/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo. Sistema DIF Hidalgo , Subsecretaría de Protección Civil y Gestión de Riesgos</t>
+  </si>
+  <si>
+    <t>Edmundo Pineda</t>
+  </si>
+  <si>
+    <t>Ricardo Alvizo Contreras, Román Bernal Díaz</t>
+  </si>
+  <si>
+    <t>Durante su participación en la conferencia matutina del gobierno estatal, Ricardo Alvizo Contreras, director del sistema DIF Hidalgo, detalló los avances informados previamente por la presidenta del patronato, Edda Vite Ramos. Alvizo Contreras destacó alianzas estratégicas como la realizada con la fundación Michou y Mau para el traslado gratuito de niños con quemaduras graves a Galveston, Texas, así como la atención a pacientes oncológicos mediante más de 68,000 quimioterapias y 46,000 atenciones de urgencia. Asimismo, resaltó que en los centros de rehabilitación integral se han brindado más de un millón de atenciones a personas con discapacidad, invirtiendo más de 60 millones de pesos en su remodelación y adquiriendo equipo tecnológico especializado como el robot LOCOMAT. En el eje alimentario, indicó que se han entregado más de 91 millones de desayunos a 150,000 niños diarios en los 84 municipios, con el objetivo de combatir la desnutrición, el sobrepeso y la obesidad mediante un presupuesto 100% estatal.</t>
+  </si>
+  <si>
+    <t>En.la cobertura de NQ en la conferencia matutina semanal del gobierno del estado. En este momento Ricardo Alvizo Contreras, director del sistema DIF Hidalgo, está refiriéndose al informe presentado por la presidenta del patronato de este sistema, Edda Vite Ramos, el pasado 15 de octubre. Vamos ahora a volvernos a enlazar para seguir escuchando la participación de Ricardo Alvizo Contreras, director del sistema DIF Hidalgo.
+Y alianzas que nos permiten garantizar la atención de los niños en algunas áreas en donde no se tiene en el estado, una de las más importantes que hemos hecho uso es la de Michou y Mau, en donde cualquier niño que sufra algún accidente por alguna quemadura ya muy profunda, podemos nosotros mediante esta alianza con Michou y Mau mandarlos a Galveston, Texas, para tener una atención de primera mano sin ningún costo. Ya hemos enviado algunas personas. Hemos tenido cerca de 46,000 atenciones en urgencia y, pues bueno, en lo que se refiere a los niños que desafortunadamente tienen una condición oncológica, la atención ha sido gratuita de igual forma y hemos dado más de 68,000 quimioterapias. La que sigue, por favor. En lo que se refiere a los centros de rehabilitación integral, contamos con uno en Pachuca, que es el que está sobre Bulevar Colosio y contamos con seis regionales en donde hemos atendido a cerca de 54,000 pacientes, pero el dato relevante aquí es que en estos cuatro años hemos dado más de 1 millón de atenciones en los siete centros. ¿Qué significa? Que el sistema DIF Hidalgo a través de los centros de rehabilitación somos quienes estamos atendiendo al mayor porcentaje de personas con alguna discapacidad en este estado. Los seis centros han sido prácticamente remodelados, actualizados en muchas áreas que post la pandemia habían sido muy deteriorados, en eso se hizo una inversión muy importante de más de 60 millones de pesos. De igual forma, y es importante mencionarlo, hemos entregado casi 10,000 ayudas técnicas a las personas que así lo han requerido. No ha habido una ayuda técnica que no haya llegado al sistema, ya sea por medio de una ruta de la transformación en donde el gobernador recibe esa petición o de manera directa, que no se haya atendido. Prácticamente podemos decir con mucho orgullo que todas las ayudas técnicas requeridas las hemos podido cubrir, esto ha necesitado una inversión de un poco más de 19 millones de pesos y de igual forma se ha buscado estar actualizado en todo lo que conlleva el equipamiento. Una de las últimas adquisiciones para el centro estatal que está aquí en Pachuca es el LOCOMAT, que es un robot y es especializado, único también en la zona centro, no hay ningún DIF en la zona centro que lo tenga y esto nos conllevó una inversión un poco mayor a los 18 millones de pesos, en donde pues bueno, quien ya tuvo oportunidad de conocerlo, pues saben perfectamente que es un aparato de última tecnología. La que sigue, por favor. En el segundo eje, que es el alimentario, como lo mencioné, se tuvo desde un inicio un análisis profundo de poder nosotros llegar principalmente a las regiones que más lo necesitaban. Se han entregado cerca de 91 millones de desayunos. Hoy en día se están atendiendo a 150,000 niños diarios en los 84 municipios, se tiene también una inversión estimada y lo comentó la presidenta en su informe, de buscar nosotros poder incrementar el año que viene para poder ser mucho más finos al momento de identificar y atacar los tres problemas que están sufriendo los niños, el de desnutrición, el de sobrepeso y el de obesidad. De igual forma, se tomó la decisión con un presupuesto 100% estatal de poder incrementar y fortalecer el programa de 100 días que atiende...
+Bien, continúa la participación de Ricardo Alvizo Contreras, director general del sistema DIF Hidalgo, dando a conocer los cuatro ejes o detallando los cuatro ejes sobre los que se orientó el informe, sobre los que se orienta la actividad en general de este sistema DIF Hidalgo y, por supuesto, en los que versó el informe presentado el pasado jueves por la presidenta del patronato del sistema DIF, Edda Vite Ramos. Continuaremos pendientes para llevarles las incidencias, los pormenores en esta conferencia matutina semanal del gobierno del estado desde la Sala del Pueblo en la sede del Ejecutivo estatal. Continuamos con más en Enlace Hidalgo. En un momento regresamos con más noticias. Enlace Hidalgo, primera emisión. Sintonizas NQ, Radio Sin Límites. Teléfono de cabina 7550640, WhatsApp 7751511090. Síguenos en todas las redes sociales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jywZQSnFxdfFWBvbbiGG9MzR5og0Lm8K/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ricardo Alvizo Contreras</t>
+  </si>
+  <si>
+    <t>Durante su intervención en la conferencia matutina del Gobierno del Estado de Hidalgo, el doctor Carlos Francisco Ávila Zúñiga informó que en el estado de Hidalgo existen 35 personas a la espera de un trasplante de órgano, mientras que más de 300 hidalguenses se encuentran en la lista de espera a nivel nacional, la cual supera las 18,000 personas en todo el país. Ante esta situación, destacó el compromiso de las autoridades de salud estatales por fortalecer la cultura de donación, reconocer a las familias de los donadores y garantizar que los procesos médicos para los trasplantes se realicen de manera segura para salvaguardar la vida de los pacientes.</t>
+  </si>
+  <si>
+    <t>Ceetra</t>
+  </si>
+  <si>
+    <t>Trasplante de órganos</t>
+  </si>
+  <si>
+    <t>El doctor Carlos Francisco Ávila Zúñiga dio a conocer que en el estado de Hidalgo hay 35 personas en espera de un trasplante de un órgano y que más de 300 hidalguenses están en la misma condición en la lista nacional y en total en nuestro país son más de 18,000 personas quienes esperan un órgano. De ahí el compromiso de las autoridades de salud en la entidad de pues seguir fomentando esta cultura de donación y su reconocimiento a las familias de las personas donadoras, a las propias personas donantes y también dijo que es un compromiso el evitar que por procesos se pudieran en un momento dado poner en riesgo un trasplante, un órgano de una persona que ya está pues esperándolo para salvar la vida o mejorar su calidad de vida.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MlBrgBOUqqzbG278jDrmLbeNrVuwv50O/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Carlos Francisco Ávila Zúñiga</t>
+  </si>
+  <si>
+    <t>Durante la conferencia matutina semanal del gobierno del estado, encabezada en la introducción por el titular de comunicación Edmundo Pineda López, se presentaron los avances en materia de salud, protección civil y del sistema DIF Hidalgo. Entre los anuncios principales, se destacó la remodelación del Aeropuerto Nacional Juan Guillermo Villasana en Pachuca, obra que no había recibido mantenimiento en más de 30 años y que ahora fortalecerá la capacidad de respuesta ante emergencias mediante traslados aéreos y de órganos. Asimismo, el doctor Carlos Francisco Ávila Zúñiga intervino para resaltar los logros del estado en materia de donación y trasplante de órganos, posicionando a Hidalgo por encima de la media nacional gracias al altruismo de los donantes y al respaldo de las autoridades de salud.</t>
+  </si>
+  <si>
+    <t>Presentador (Edmundo Pineda): Vamos a iniciar con la transmisión de la conferencia matutina semanal del gobierno del estado, ya está iniciando el titular de comunicación, Edmundo Pineda López, está haciendo la presentación de quienes darán la información esta mañana en temas de salud, protección civil y del sistema DIF Hidalgo. Son los funcionarios que están en este momento pues ya listos para dar la información de esta mañana de lunes 19 de octubre de 2026. Vamos a enlazarnos ya a la conferencia matutina semanal del gobierno del estado. Edmundo Pineda continúa con la presentación de esta conferencia. digitalización. Bueno, además el gobernador del estado estará en la inauguración de la remodelación del Aeropuerto Nacional Juan Guillermo Villasana. Hace más de 30 años que no se hacía alguna actividad de mantenimiento, al menos de mantenimiento en este importante aeropuerto. Y justamente hace un año, comentaba con el titular del sistema DIF, con el subsecretario de Protección Civil y también con el doctor Carlos Francisco Ávila, que estuvimos desde muy temprano, al mediodía, por la tarde, la noche, de madrugada, durante varias semanas en el centro de operaciones del Aeropuerto Juan Guillermo Villasana. Porque justamente hace un año sentíamos los estragos de la vaguada monzónica que afectó diferentes regiones de nuestra entidad y que con el apoyo de la Sedena, de la Marina, de la sociedad civil, las y los hidalguenses pudimos salir adelante. Hace ya, hace un año del duro golpe de la vaguada monzónica. En esta remodelación del Aeropuerto Nacional Juan Guillermo Villasana destaca, entre otras acciones, el valor que implica la ambulancia aérea, el traslado de órganos, que las unidades móviles vayan a regiones y comunidades apartadas para apoyar a la población que así lo requiere cuando la situación es urgente, tiene un valor fundamental y por eso hemos considerado que es momento propicio una vez que se entrega la remodelación del Aeropuerto Nacional establecido en Pachuca que nos acompañe el doctor Carlos Francisco Ávila Zúñiga precisamente para hablar de la importancia del traslado de órganos y la ambulancia aérea en Hidalgo. Y si es tan amable y nos acompaña en este micrófono, por favor, doctor.   Dr. Carlos Francisco Ávila Zúñiga: Muy buenos días a todos, a todas y a todos, a los medios de comunicación que nos acompañan esta mañana. Un saludo muy especial sobre todo a todas las familias hidalguenses que nos siguen a través de la señal de Radio y Televisión de Hidalgo y también por las plataformas digitales y agradezco profundamente la invitación de este espacio de comunicación pública que nos permite visibilizar temas prioritarios e indispensables para el bienestar de nuestra población. Agradezco de manera especial sobre todo a la doctora Vanessa Escalante Arroyo, secretaria de salud de Hidalgo y sobre todo al gobernador al licenciado Julio Menchaca Salazar por el respaldo y el compromiso para el fortalecimiento de la donación y trasplantes de nuestro estado. Y hoy quiero hablarles de algo que va mucho más allá de las cifras, los hospitales y los procedimientos médicos, quiero hablarles de vida, de esperanza y sobre todo de amor que un ser humano puede ofrecer a otro. Imagínense que una madre que está en espera de una llamada, saber si su hijo va a recibir un riñón, a una persona que ha pasado años pegado a una máquina de hemodiálisis o alguien que espera recuperar la vista y poder volver a ver a sus seres queridos. El programa de trasplantes de donación y órganos y tejidos se ha consolidado bajo la firme premisa que en Hidalgo primero el pueblo. Hoy con orgullo podemos decir que Hidalgo se ha posicionado como un referente en donación de órganos y tejidos y detrás de cada trasplante existe una historia que pocas veces conocemos, de una persona que es un donante, una familia que en ocasiones en medio del dolor decide dar una muestra de vida, una una fortaleza encuentra para poder dar esperanza a otras vidas porque donar tejidos ante todos es un acto voluntario y altruista. Hoy podemos decir que en Hidalgo ha logrado avances importantes y se ha posicionado como un referente en materia de donación de órganos. En la primera de diapositiva vemos que tenemos en Hidalgo una tasa de donación de 15.2 donantes por millón de habitantes y esto es tres veces del promedio nacional y eso es algo que podemos sentirnos orgullosos. De ese promedio 175 donaciones se han pedido concretar y se han obtenido 493 órganos, de los cuales estas donaciones 38 han sido multiorgánicas. ¿A qué referimos esto? A decir que son procesos en los cuales se pueden procurar distintos órganos. Es el inicio de la conferencia matutina semanal este lunes 19 de octubre de 2026. Ya se ha dado cuenta acerca de las remodelaciones en el aeropuerto Nacional Juan Guillermo Villasana en la capital del estado y también de la relevancia que esto tiene, sobre todo para el tema de las emergencias, entre otras, es justo lo que se habla ahora del traslado de órganos, la adecuada procuración de órganos para su trasplante. Seguiremos pendientes, vamos a la pausa promocional, continuamos con mucho más en la primera emisión de Enlace Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1avtLP2TO5UdElHebBkx5snFZCOVdgKNR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Sistema DIF Hidalgo, Secretaría de Salud de Hidalgo</t>
+  </si>
+  <si>
+    <t>Carlos Francisco Ávila Zúñiga, Julio Menchaca, Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Durante su colaboración semanal, el maestro José Luis Lima Morales reflexionó acerca de las discusiones recientes en la Cámara de Diputados y los ayuntamientos sobre las reformas constitucionales y la propuesta de otorgar facultades a los presidentes municipales para celebrar contratos sin la intervención de la asamblea municipal. El ponente señaló que, si bien la agilización administrativa puede ser legítima, es fundamental equilibrarla con la transparencia, la rendición de cuentas y la división de poderes. Asimismo, reconoció la postura respetuosa del gobernador estatal hacia el Poder Legislativo e hizo un llamado a las y los regidores municipales para fundamentar con rigor jurídico sus intervenciones y votaciones, priorizando siempre el interés público y el fortalecimiento institucional.</t>
+  </si>
+  <si>
+    <t>José Luis Lima</t>
+  </si>
+  <si>
+    <t>Reforma a contrataciones municipales</t>
+  </si>
+  <si>
+    <t>Continuamos desde Pachuca. Es el momento de compartirle el segmento de opinión. Saludamos al maestro José Luis Lima Morales.
+Mi amigo Juan Carlos, ¿cómo estás? Muy buenos días, como todos los días lunes. Un fuerte abrazo para ti y para todos quienes nos escuchan por esta estación de NQ Radio. Su amigo José Luis Lima les manda un fuerte abrazo. En este día voy a hacer un comentario con respecto a lo que se ha dado últimamente tanto en la Cámara de Diputados como en los municipios, en sus asambleas, en el debate que existe con regidores y los presidentes municipales. Y me refiero a esto porque quiero expresar que toda reforma constitucional representa una oportunidad para revisar nuestras instituciones, mejorar su funcionamiento y encontrar mecanismos que permitan a las autoridades responder con mayor eficacia a las necesidades de la sociedad. En ese contexto, considero importante reflexionar sobre la propuesta de permitir que los presidentes municipales puedan celebrar determinados contratos sin la intervención de la asamblea municipal. La intención de agilizar los procedimientos administrativos puede ser legítima; sin embargo, también es importante valorar cómo podemos conciliar esa agilidad con la participación colegiada, la transparencia y la responsabilidad en el manejo de los recursos públicos. Quiero destacar que el gobernador Julio Menchaca ha sido respetuoso de las decisiones que corresponden al Poder Legislativo, y esa actitud institucional merece ser correspondida con el mismo respeto hacia las atribuciones y deliberaciones de nuestros diputados. En ese sentido, respaldamos el respeto a la división de poderes y reconocemos que es precisamente en el Congreso donde deben analizarse, discutiverse y resolverse este tipo de propuestas. Mi reflexión no pretende cuestionar la reforma, sino invitar a que su análisis permita encontrar el mejor equilibrio entre la eficiencia administrativa y el fortalecimiento de los gobiernos municipales. En ese sentido es que hoy me estoy expresando, porque yo invitaría primero a las y los regidores a quienes se suben a hacer uso del micrófono en sus asambleas y, la verdad, muchos de ellos no tienen ni idea de lo que están votando. Yo sí quiero felicitar a aquellos regidores mujeres y hombres que con sustento jurídico han expresado su votación a favor o en contra; a ellos felicitarlos, porque una cosa es subirse a tomar el micrófono con conocimiento y otra cosa es subirse a hacer ridículo. Estoy convencido de que cuando las instituciones dialogan, escuchan distintas opiniones y toman decisiones con visión de estado que en finalmente se benefician, pues, amigas y amigos, somos nosotros los ciudadanos, porque gobernar no solamente significa tomar decisiones con rapidez, también significa hacerlo con responsabilidad, transparencia y pensando siempre en el interés público. El fortalecimiento de nuestras instituciones es una tarea compartida y el respeto entre los poderes públicos es una condición indispensable para seguir construyendo un Hidalgo con mejores gobiernos y mayores resultados para su gente. Me despido diciéndoles que deseo que tengan una semana de mucho éxito.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Q8Iv98RDHkX9KIUrOjkQ9u2P3YpuMoKK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Durante la emisión de *Las Vocales Radio* como todos los lunes, Andrés Torres y Alberto Gonzpalez analizaron el formato actual de las comparecencias de los secretarios del gabinete estatal ante el Congreso del Estado, señalando que este se encuentra superado y ya no cumple con el propósito de profundizar en los asuntos de interés público. Se discutió el caso específico de la Secretaría de Movilidad y Transporte, cuyo funcionamiento fue duramente cuestionado, comparando su gestión con deficiencias en la rendición de cuentas a los usuarios. Se planteó la necesidad de buscar un esquema mucho más ágil y riguroso para las comparecencias que permita abordar tanto los temas torales del estado como las responsabilidades de los funcionarios en temas lo que hizo Eduardo Iturbe en un inicio de esta administración en Comunicación Social, los múltiples cambios que ha habido, así como las quejas que hay, por ejemplo, con el subejercicio de cinco años seguidos en Radio y Televisión de Hidalgo, Donde este año han estado presupuestadas 14 millones de pesos para dos estaciones, una en AM en Pachuca y otra en FM en Tenango de Doria, Dinero que nadie sabe dónde está y que debe responder a esto Carlos Barra. En este sentido, también señaló que la estación "La Voz de la Sierra Gorda" en Jacala lleva un mes fuera del aire debido a la negligencia de las autoridades de Radio y Televisión de Hidalgo, las cuales supuestamente priorizan la autopromoción sobre la solución técnica y operativa de los medios públicos. Finalmente destaca que en estas comparecencias ahora se esté incluyendo al Oficial Mayor. También se abordó la reforma impulsada por el diputado local Miguel Moreno al artículo 141, fracción XV, de la Constitución del Estado, la cual busca modificar la relación y el nivel de compromiso de los regidores dentro de los cabildos. El propósito principal de la normativa no es quitarles facultades a los regidores, sino obligarlos a involucrarse activamente en temas presupuestales, de planeación y en la aprobación de obras y proyectos dentro de los municipios. Con esta modificación se pretende evitar que los alcaldes tengan un "cheque en blanco" en la asignación de obras o solicitud de créditos, manteniendo candados estrictos donde se requiere la aprobación de las dos terceras partes del cabildo.</t>
+  </si>
+  <si>
+    <t>Andrés Torres Y Alberto Gonzálezz</t>
+  </si>
+  <si>
+    <t>TV local</t>
+  </si>
+  <si>
+    <t>La secretaria de Movilidad y Transporte es una, la verdad, lo siento como un atentado a mi inteligencia como pasajero que me diga que ha logrado cambios y transformaciones. La ruta 47, he exhibido he he tengo documentado, uno que otro pone su tarjetón, copia de su tarjetón en el parabrisas para que yo lo vea en la ventanilla y a un lado la vigencia de su seguro. ¿Y las demás, este, colectivas? Los taxis, desde que ella llegó, quitaron el tarifario, ¿sabe en la ventanilla? Y ahora se está diciendo que va a poner un taxímetro. Y entonces la aplicación en la que se gastó este el gobierno de Omar Fayad, la aplicación del taxi contigo para el chofer y para el usuario, ¿dónde está su inversión?  La Huasteca. O sea, eso es lo que creo que salta de la zona de Tizayuca, que me dice... Hay que saltar de los funcionarios de su burbuja y se vayan a los este Sí, o o o va más allá. Congreso, hagan una comparecencia y, ¿verdad, no? No, no, no, entiendo, entiendo lo que tú estás diciendo y coincido contigo. Yo lo planteaba la semana pasada desde la otra perspectiva, desde el Congreso. Y yo pienso que pues también si el formato pues no exige, ¿no? pues también los secretarios pues no pueden hacer mayor cosa. No los estoy defendiendo, por supuesto que coincido plenamente contigo, pero pues si te dicen "Vamos a hacer dos comparecencias diarias", pues a lo mejor habrá secretarías que puedan, pues no digo que sea un tema más importante que otro, pero por su naturaleza pues tengan tengan menos información, o sea, menos eh pues no sé, interesante para los diputados hacer preguntas, pero hay secretarías, obviamente por su naturaleza, pues hay mucho, todos queremos saber muchas cosas, ¿no?   Aldo Falcón: Así es. Y hay muchos temas interesantes. Entonces a mí se me hace que de entrada te digan "Tienes 2 horas", ¡híjole! Y luego me hace ya de ahí dices "Bueno, en lo que hago mi video, en lo que presenta algunos poco, poco se puede abrevar, poco se puede disecar. Este, todo queda pendiente además, ¿no? Porque si hay alguna situación que el secretario desconozca, no sepa, o haya información que no se pueda decir allí precisamente para no extenderse, pues queda de "Ah, yo se lo mando, ¿no?" "Yo se lo se lo abro con el conocimiento próximamente".  Entonces yo sí creo que el formato está superado. Si el propósito de las comparecencias de los integrantes del gabinete del gobernador ante el Congreso es ir a detalle en los temas de cada una de estas secretarías, pues no está cumpliendo por desde el formato, ¿no? Ahora, de lo que hayan hecho los secretarios o no en una de sus responsabilidades, pues también este habría que hacer un análisis, ¿no? Porque habrá quien diga "Yo no, yo sí cumplí, ¿no?" "Yo no cumplí." Este, a lo mejor desde otra perspectiva, ¿no? Este, de repente cuando empiezan a hablar de cifras y cifras y cifras, pues tú puedes decir lo que quieras, ¿no? O sea, del secretario de trabajo, que nos diga cuántos eh juicios eh laborales tiene a partir de que llegaron los gobiernos a los ayuntamientos emanados de Morena y que despidieron gente. O sea, es válido despedir gente porque quieres integrar a tu equipo, pero hay que despedirlos con la legalidad que corresponde en cuanto al finiquito o en total de la liquidación. Hay que ver cuántos, ¿no? Cuántos están ahí en pantanados de entrada Tizayuca, yo tengo el antecedente y me hablaron hace como dos semanas que son 100 150 los que despidieron argumentando este el gobierno 2024 que este pues eran aviadores, que estaban demás, pues sacó a 150 y volvió a meter a otros 750.  Digo que ya ya han intentado inventar fórmulas, ya han tratado de traer diferentes eh eh situaciones, ¿no? Para para este formato de las comparecencias. Yo no estoy diciendo que desaparezcan, lo que estoy diciendo es que tendríamos que buscar un formato que fuera mucho más ágil, pero que también permitiera pues hablar de los temas personales, de los temas torales, ¿no? de nuestro estado. Este año incorporaron eh los diputados la presencia del Oficial Mayor, una figura que en lo que tradicionalmente no comparece ante el Congreso, ¿no? Si se trata de eso, yo les diría incorporen a la comunicación social, ¿no?   Porque si hay un escándalo en esta administración, eso es lo que hizo Eduardo Iturbe, ¿eh? Un inicio de esta administración con en comunicación social, los múltiples cambios que ha habido, ¿no? Las quejas que hay, por ejemplo, con uso de ejercicio de cinco años seguidos en Radio y Televisión de Hidalgo, ¿no? Donde este año han estado presupuestadas 14 millones de pesos para dos estaciones, una en AM en Pachuca y otra en FM en Tenango de Doria, y ese dinero pues nadie sabe dónde está, porque sí fue presupuestado, porque sí fue aprobado por el Congreso, pero desgraciadamente, señor Carlos Barra, pues se vinieron, nadie sabe dónde está, si fue devuelto, si si es su ejercicio, nadie sabe dónde está. Lo único cierto es que estaban presupuestadas y estaba eh planeado para el 2026 la apertura de dos estaciones más y no se va a hacer. Entonces, tendrían que comparecer los responsables de estos temas, por ejemplo, porque también en los temas de comunicación se gasta muchísimo, muchísimo dinero, ¿no? Y nadie da razón de ello, ¿no?   Y que además se sigue utilizando la fórmula del pasado, ¿no? El olvido. Al olvido. A dejarlo ahí y este, como dices, después le pasas los datos y en ese después, pues ya no, pues sí, ¿no?  O sabes que nada más algunos diputados así se se este se los mandaron, ¿o no? Y que lo hagan público, ¿no? Este y también los diputados que hagan públicos o pues si estamos hablando de comparecencias, también sus informes no quedan más que un empastado, un librito donde vienen las fotos, ¿no? Estuve ahí en la ceremonia, asistí al desfile, este entregué una despensa, apoyé a una persona, sí, pero más allá, ¿no? O sea, con esta polémica de la reforma al este a la al presidente, al presidente municipal, no en este momento no recuerdo el artículo, pero eh de que no pase por el Cabildo. No, sí, por supuesto. Eso es eso es el artículo 141 de la Constitución del Estado, la fracción XV.  Pero este de acuerdo a lo que han explicado, no tiene, no está liberado el alcalde para que no consulte al Cabildo. Tiene que tener dos terceras partes de la aprobación del Cabildo para lo mismo que en el endeudamiento, solicitud de crédito, para créditos, créditos, financiamiento. Y esto pasa también por el Congreso, recuerda. Y en el tema de las licitaciones, es decir, las obras, no las va a asignar directamente el alcalde sin pasar por el Cabildo. Le tendrá que presentar el proyecto de construcción, tendrá que ser citado validado ante las instancias correspondientes, la Secretaría de Infraestructura en caso de obra pública, y dos terceras partes del Cabildo tendrán que aprobarlo.   Yo yo decía a un ejercicio eh parlamentario o el famoso parlamento abierto, ¿no? Hacer una consulta tanto a los colegios como a los mismos regidores, ¿no?, a los mismos cabildos. Esto nutrir, nutrir para que no surgiera ahorita esta polémica en la que cada quien tiene su versión, ¿no? Y ya unieron a varios este regidores de distintos partidos y ya hicieron ahí una agrupación que está haciendo más ruido que la que ya iba a cumplir o cumplió 2 años, que es la Asociación de Alcaldes de Hidalgo. O de ahí se pudo haber analizado esta iniciativa, desmenuzarla para no generar esta controversia donde mientras en Pachuca, que es de Morena, se aprobó el cabildo sí aprobó esta lo que se quiere, la ruta, la ruta porque es la mitad más uno de ayuntamientos, y en el de San Salvador, que es de Morena, ahí la echaron para abajo.   Entonces, creo a eso me refiero, más que a al sentido del al sentido de la este de iniciativa, sino al trabajo que debe de haber, ¿no? El trabajo que eh pues retomo esto que le dijo la diputada local de la Ciudad de México panista a Clara Brugada cuando llegó su informe, pues que ellos no le están aplaudiendo, es un ejercicio de unos y de otros, o sea, el poder legislativo y el poder ejecutivo rendir cuentas, transparencia y dárselo a conocer a la población.   Entonces, creo que es por ahí, ¿no?, el trabajo que se debe de hacer desde lo que estábamos hablando, las comparecencias, que es el poder ejecutivo, quienes escuchan o quienes los llaman en el escenario del Congreso, pues también ahí está el el trabajo, ¿no?   Aldo Falcón: En el legislativo. Así es. Pues bueno, han sido muchos años de comparecencias y no no han dejado el que yo recuerde nunca.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M26NbKWafGdUGDQVr6iOOs_-Nvj94hiV/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Secretaría de Movilidad y Transporte, Congreso, Gobierno, Secretaría de Infraestructura</t>
+  </si>
+  <si>
+    <t>Carlos Barra Moulain</t>
+  </si>
+  <si>
+    <t>Omar Fayad, Citlalli Hernández, Eduardo Iturbe, Clara Brugada.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jZuGe0sqyqlPZcd6h6BFMhTIYPLyKd49/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Secretaría de Movilidad y Transporte, Congreso, Gobierno, Secretaría de Infraestructura, Radio y Televisión de Hidalgo</t>
+  </si>
+  <si>
+    <t>Omar Fayad, Citlalli Hernández, Carlos Barra, Eduardo Iturbe, Clara Brugada.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eXHqE5khvsu9m-72M0sDIOZ4gSK3MhO-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso, Gobierno, Secretaría de Infraestructura, Radio y Televisión de Hidalgo</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>Hoy continúan las comparecencias en el Congreso del Estado en la 66 legislatura. Hoy tenemos la comparecencia del Secretario de Infraestructura y posteriormente la de Medio Ambiente.</t>
+  </si>
+  <si>
+    <t>Semarnath</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_y9mMoOLhbsSufe1n5G39Q9kxtGtzENp/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SIPDUS</t>
+  </si>
+  <si>
+    <t>Andés Torres comenta: lamento muchísimo darles esta noticia, pero ya tenemos un mes fuera del aire allá en 91.1 de frecuencia modulada, "La Voz de la Sierra Gorda" allá en Jacala. Pues este, nosotros ya hicimos las solicitudes correspondientes, ya sabe, ¿no?, la negligencia, el nepotismo, esta eh pues necedad y desconocimiento, ¿no?, de nuestras autoridades de Radio y Televisión de Hidalgo, que pues están más preocupadas en promoverse a sí mismo, en salvar su pellejo, en agarrar el siguiente hueso, que en ponerse a trabajar, en conocer algo, hacer algo, ¿no?, por Radio y Televisión de Hidalgo, pues dicen que no, que no es importante arreglar la estación y que ahí se puede quedar sin señal. Bueno, pues ese es este cada quien su responsabilidad. Hablé con Alejandro Velázquez hace un par de días y hablábamos precisamente de esta situación anómala, de esta eh pues situación que es, pues evidentemente una situación de corrupción, ¿no?, de desconocimiento y, por supuesto, pues es una infamia que alguien esté utilizando recursos públicos para autopromoverse en lugar de trabajar y cumplir con su responsabilidad. Pero bueno, pues ya cada quien, ¿no?</t>
+  </si>
+  <si>
+    <t>Jacala</t>
+  </si>
+  <si>
+    <t>Yo lamento muchísimo darles esta noticia, pero ya tenemos un mes fuera del aire allá en 91.1 de frecuencia modulada, la voz de la Sierra Gorda allá en Jacala pues este, nosotros ya hicimos las solicitudes correspondientes, ya saben la negligencia, el nepotismo, esta necedad y desconocimiento de nuestras autoridades de Radio y Televisión de Hidalgo que pues están más preocupadas en promoverse a sí mismo, en salvar su pellejo en agarrar el siguiente hueso, que en ponerse a trabajar, que en conocer algo, hacer algo, traer televisión y algo, pues dicen que no, que no es importante arreglar la estación y que ahí se puede quedar sin señal. Bueno, pues ese es cada quien su responsabilidad. Hablé con Alejandro Velázquez hace un par de días y hablábamos precisamente de esta situación anómala, de esta situación que es evidentemente una situación de corrupción, de desconocimiento y por supuesto es una infamia que alguien esté utilizando recursos públicos para autopromoverse en lugar de trabajar y cumplir con su responsabilidad. Pero bueno, pues ya cada quien, ¿no?</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xGK7PMENDoUJdXJtpDWsMG7EwCo9XzjZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEGOBH</t>
+  </si>
+  <si>
+    <t>Alejandro Velázquez Mendoza</t>
+  </si>
+  <si>
+    <t>Radioescucha: El ISSSTE de Tulancingo, ¿cómo es posible que no tengan ni una sola cama de hospitalización y tampoco un quirófano, con una población de 250,000 habitantes y que muchos eh maestros también eh vienen de otros municipios y también solo tres consultorios y ninguna especialidad? Es responsabilidad d el gobernador en turno de solicitar el mejoramiento del ISSSTE Tula, Ixmiquilpan tienen todo lo antes mencionado, ¿cómo es posible?</t>
+  </si>
+  <si>
+    <t>Deficiencias hospitalarias</t>
+  </si>
+  <si>
+    <t>El Issste de Tulancingo, ¿cómo es posible que no tengan una sola cama de hospitalización? Y tampoco un quirófano con una población de 250 mil habitantes y que muchos maestros también vienen de otros municipios. Y también solo tres consultorios y ninguna especialidad. Es responsabilidad del gobernador en turno de solicitar el mejoramiento del Issste. Tula e Ixmiquilpan, tienen todo lo antes mencionado. ¿Cómo es posible?</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xr4wVM2K63kn-yen-G_-uUj5q9gUuxQQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Daniel Martínez: están reportando que hace unos momentos ocurrió un ataque armado al interior de las oficinas de Servicios Regionales de Educación en la zona de Media Sierras. De hecho, en este momento me están actualizando información de que hay movimiento policíaco, hay atención médica, aparentemente habrían baleado, habrían atacado con arma de fuego a una persona al interior de las oficinas de servicios regionales de educación y por eso la movilización que se está observando en este momento. Conforme vaya evolucionando la información, en conforme se vaya dando más información al respecto, este pues por acá le irán platicando qué es lo que está ocurriendo, ¿sale? ...pues vamos a ver si hay personas detenidas y sobre todo qué pasó, qué pasó, por qué del ataque.</t>
+  </si>
+  <si>
+    <t>Están reportando que hace unos momentos ocurrió un ataque armado al interior de las oficinas de servicios regionales de educación en la zona de Medias Tierras. De hecho, en este momento me están actualizando información de que hay movimiento policíaco, hay atención médica. Aparentemente habrían baleado, habrían atacado con arma de fuego a una persona al interior de las oficinas de servicios regionales de educación y por eso la movilización que se está observando en este momento. Conforme vaya evolucionando la información, conforme se vaya dando más información al respecto, pues por acá le vamos platicando qué es lo que está ocurriendo. Yo espero que se encuentre bien, de verdad de todo corazón que se encuentre bien la persona atacada y vamos a ver si hay personas detenidas y sobre todo qué pasó, qué pasó el porqué del ataque</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aTKXQymYihyHdDZyKqMAVpfB4No91zvM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>En los cuatro años que lleva la actual administración del Gobierno del Estado de Hidalgo, Junta Local de Conciliación y Arbitraje ha resuelto 2 mil 590 expedientes, que representan el 50 por ciento de avance. Consultar atlas. Lo anterior fue informado por el titular de la Secretaría del Trabajo y Previsión Social del Estado de Hidalgo, Óscar Javier González Hernández, durante su comparecencia ante el Congreso del Estado de Hidalgo, este viernes 16 de octubre. Señaló que en el año más reciente, se resolvieron 466 expedientes en beneficio de 138 trabajadores que esperaban la conclusión de sus demandas laborales. Mientras que el Tribunal de Conciliación y Arbitraje ha celebrado, en cuatro años, 6 mil 886 convenios en beneficio de 6 mil 889 trabajadores del sector público, lo que representa un monto total de 191 millones 58 mil 875 pesos mediante el diálogo. El funcionario destacó que en dicho tribunal se concluyeron mil expedientes laborales en beneficio de 934 trabajadores, los cuales se encontraban pendientes de resolver. Puntualizó que en cuatro años, se han dictado 705 laudos en beneficio de 992 personas que han concluido sus asuntos laborales. Destacó que, en el último año, se dictaron 327 laudos a favor de 501 trabajadores. Además, en cuatro años se han solicitado 23 mil 180 audiencias de conciliación, de las cuales 16 mil 535 controversias se resolvieron de forma satisfactoria y se emitieron 6 mil 645 constancias de no conciliación. Con ello, y gracias al trabajo del personal de la dependencia, Hidalgo se coloca en primer lugar nacional en tiempo de conciliación de los procesos conciliatorios, con un promedio de 21 días, de los 45 que se establecen en la ley. Desde el inicio de la administración, se han realizado cerca de 11 mil asesorías y en el último año, se han brindado 3 mil 121 asesorías a trabajadores y sindicatos ante posibles conflictos entre trabajadores y empleadores. Ello ha significado la celebración de mil 608 convenios por un monto de 49.5 millones de pesos; además, en cuatro años, se ingresaron 2 mil 371 demandas y, en el último año, van 732. Mientras que, en materia de juicios políticos, se han resuelto 2 mil 478 juicios, de los cuales mil 547 resultaron a favor de las y los trabajadores, con un monto equivalente a 59 millones 510 mil 952 pesos.</t>
+  </si>
+  <si>
+    <t>También hubo comparecencia por parte del secretario del Trabajo y Previsión Social de Hidalgo, quien destacó sobre todo los apoyos en materia de justicia laboral.   Izza Hernández: Así es, Daniel. En los 4 años que lleva la actual administración del gobierno del Estado de Hidalgo, la Junta Local de Conciliación y Arbitraje ha resuelto 2,590 expedientes, que representan el 50% de avance. Todo esto fue informado por el titular de la Secretaría del Trabajo y Previsión Social del Estado de Hidalgo, Óscar Javier González Hernández, durante la comparecencia ante el Congreso del Estado de Hidalgo este viernes 16 de octubre. Señaló que el año más reciente se resolvieron 466 expedientes en beneficio de 138 trabajadores que esperaban la conclusión de sus demandas laborales; mientras que el Tribunal de Conciliación y Arbitraje ha celebrado en 4 años 6,886 convenios en beneficio de 6,889 trabajadores del sector público, lo que representa un monto total de 191 millones 58,875 pesos mediante el diálogo. Y pues el funcionario destacó que en dicho tribunal se concluyeron 1,000 expedientes laborales esto en beneficio de 934 trabajadores, los cuales pues se encontraban pendientes de resolver. De hecho puntualizó que en 4 años se han dictado 705 laudos en beneficio de 992 personas pues que han concluido sus asuntos laborales, así lo destacó; y también dijo que pues en el último año se dictaron 327 laudos a favor de 501 trabajadores. Además también en 4 años se han solicitado 23,180 audiencias de conciliación, de las cuales 16,535 controversias se resolvieron de forma satisfactoria y emitieron también 6,645 constancias de no conciliación. Con ello y gracias al trabajo del personal de la dependencia, Hidalgo se coloca en el primer lugar nacional esto en tiempo de conciliación de los procesos conciliatorios, con un promedio de 21 días de los 45 que establecen precisamente por la ley. Desde el inicio de la administración se han realizado cerca de 11,000 asesorías y en el último año se han brindado de hecho 3,121 asesorías a trabajadores y sindicatos ante posibles conflictos entre trabajadores y empleados. Ello significa la celebración de 1,608 convenios, esto por un monto de 49.5 millones de pesos. Además también en 4 años se ingresaron 2,371 demandas y en el último año van 732. Mientras que en materia de juicios políticos se han resuelto 2,478 juicios, de los cuales 1,547 resultaron a favor de las y los trabajadores; eso con un monto equivalente de 59,510,952 pesos. Finalmente y de esta manera, Daniel, es como destaca el secretario estatal el trabajo en labores de conciliación laboral.   Daniel Martínez: Y reiteramos, sobre todo el enfoque fue las atenciones en materia de asesoría jurídica a las y los trabajadores en Hidalgo, Isa.   Izza Hernández: Es correcto, Daniel, así como lo acabas de mencionar y también pues parte de lo que destaca es el lugar que en este momento ocupa el estado de Hidalgo precisamente en este tipo de procedimientos, ¿no? Entonces es uno de los números que más pues...</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IBSS61w5aE7eh3TccKUfQFD6dC_Z1EX2/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Oscar Javier González</t>
+  </si>
+  <si>
+    <t>El Hospital General de Actopan quedará concluido en diciembre de este mismo año, previendo que el de Tlaxcoapan entre en operación antes de finalizar el 2026, declaró la secretaria de Salud de Hidalgo (SSH), Vanessa Escalante Arroyo. Durante su comparecencia ante el Congreso del Estado de Hidalgo, realizada este viernes 16 de octubre, recordó que el primer nosocomio citado será administrado por el sistema IMSS Bienestar, y en el segundo caso, por el IMSS ordinario. En la construcción del Hospital General de Actopan se invierten 503 millones 24 mil 612 pesos, sumado a 355 millones de pesos para su equipamiento. El objetivo es brindar atención médica especializada a 132 mil habitantes de siete municipios del Valle del Mezquital, incrementando la capacidad hospitalaria de 30 a 60 camas, además de contar con cuatro quirófanos. Escalante Arroyo señaló que la plantilla laboral y los recursos necesarios, como medicamentos e insumos para su operación están contemplados por el Gobierno federal, a través del IMSS-Bienestar. En cuanto a los hospitales generales de Pachuca y Tula de Allende, informó que se invirtieron 7.9 millones de pesos en adecuaciones para poner en funcionamiento sus tomógrafos, luego de que ambos nosocomios permanecieran nueve meses y dos años, respectivamente, sin estos equipos. “Esto permitirá agilizar los diagnósticos, reducir la espera y evitar que las y los pacientes paguen estos estudios fuera del hospital”, expresó. Escalante Arroyo informó a su vez que en reunión reciente con la presidenta de México, Claudia Sheinbaum Pardo, con directoras y directores de hospitales transferidos al IMSS-Bienestar, se planteó revisar y resolver el tema de los precarios salarios que recibe el personal médico adscrito al sector oficial. A su vez, se propuso la contratación de más profesionales de la salud, entre ellos especialistas, enfermeras, enfermeros y médicos generales. También se expuso la falta de ambulancias en Hidalgo, las necesidades de insumos de consumo y medicamentos en las unidades médicas; de acuerdo a Escalante Arroyo, la Federación se comprometió a dar seguimiento a estos planteamientos.</t>
+  </si>
+  <si>
+    <t>Jessenia Romero</t>
+  </si>
+  <si>
+    <t>**Transcripción estenográfica:**
+**Daniel Martínez:** Durante la comparecencia que presentó Vanessa Acosta... de titular de la Secretaría de Salud del estado de Hidalgo, obviamente, en el Congreso del Estado el pasado viernes, tocó en qué va el asunto de poner en funcionamiento los hospitales de Actopan y Tlaxcoapan, que estarán a cargo del IMSS y del IMSS-Bienestar precisamente, Jess.
+**Jessenia Romero:** Así es, Daniel. El Hospital General de Actopan de hecho quedará concluido este mismo año, previendo que el de Tlaxcoapan entre pues en operación antes de finalizar el 2026. Esto fue lo que dijo la secretaria de Salud en Hidalgo, Vanessa Escalante Arroyo, durante su comparecencia realizada este viernes. Recordó que el primer nosocomio citado sería administrado por el sistema IMSS-Bienestar y el segundo por el IMSS ordinario. En la construcción del Hospital General de Actopan se invirtieron 503 millones 24 mil 612 pesos, sumado a los 315 millones de pesos para su equipamiento. El objetivo es brindar atención médica especializada a 132 mil habitantes de siete municipios del Valle del Mezquital, incrementando la capacidad hospitalaria de 30 a 60 camas, además de contar con cuatro quirófanos. Escalante Arroyo señaló que la plantilla laboral y los recursos necesarios, como medicamentos e insumos para su operación, están contemplados por el gobierno federal a través del IMSS-Bienestar. En cuanto a los hospitales generales de Pachuca y Tula de Allende, informó que se invirtieron 7.9 millones de pesos en adecuaciones para poner eh poner en funcionamiento sus tomógrafos, luego de que ambos nosocomios permanecieran nueve meses y dos años respectivamente sin estos equipos. Esto va a permitir agilizar los diagnósticos, reducir la espera, evitar que las y los pacientes paguen estos estudios fuera del hospital, fue lo que expresó. Escalante Arroyo informó a su vez que en reunión reciente con la presidenta de México, Claudia Sheinbaum, con directoras y directores de hospitales transferidos al IMSS-Bienestar, se planteó revisar y resolver el tema de los precarios salarios que recibe el personal médico adscrito al sector oficial. A su vez se propuso incluso la contratación de más profesionales de la salud, entre ellos especialistas, enfermeras, enfermeros, médicos generales, en fin. Se expuso también la falta de ambulancias en el estado de Hidalgo, la necesidad de insumos, de consumo, de eh y medicamentos en las unidades médicas. De acuerdo a Escalante Arroyo, la Federación se comprometió a dar seguimiento a estos planteamientos. Por su parte, la diputada Claudia Lilia Luna consideró que el convenio con el IMSS-Bienestar deberá cancelarse. Dijo: "Yo sigo cuestionando por qué no cancelamos el convenio con el IMSS-Bienestar si no ha funcionado. Es complicado, no sé si doble o triple que tenemos una Secretaría de Salud que no pueda hacer nada, en donde cada año te quitan y te ponen atribuciones de acuerdo con eh como se vaya modificando el esquema". Y bueno, pues también fue el posicionamiento de la diputada.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JcoHO7ShuU_EPHX_aMoXGYJsqY7hHn74/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>, Congreso del Estado, IMSS, IMSS-Bienestar,</t>
+  </si>
+  <si>
+    <t>Claudia Lilia Luna, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Por medio de un comunicado oficial, se dio a conocer que el titular de la Secretaría de la Contraloría en el Estado de Hidalgo, Álvaro Bardales Ramírez, respaldó la eliminación de autorizaciones duplicadas para las contrataciones municipales. Lo anterior, luego de que un grupo de asambleístas de varios municipios de la entidad se han manifestado públicamente respecto a la de reforma al artículo 141 de la Constitución Política del Estado de Hidalgo. La reforma establece la autorización para que establezcan acuerdos y contratos sin la obligación de ser autorizados por los integrantes de la Asamblea Municipal respectiva. Los asambleístas que se oponen a la reforma, señalan que con esta se les resta facultades a los integrantes de los cuerpos edilicios. Al respecto, Bardales Ramírez señaló que los recursos públicos no pueden quedar sujetos a disputas políticas, intereses personales o incapacidad para construir acuerdos. Señaló que, cuando el presupuesto ya fue aprobado y se cumplen los requisitos legales para contratar, exigir nuevamente el aval del Cabildo puede detener las mismas obras y acciones que el ayuntamiento autorizó. El funcionario estatal señala que revisar el gasto constituye una obligación, pero utilizar una autorización pendiente para obtener plazas, contratos o beneficios personales representa una conducta que debe investigarse cuando existan elementos. La Contraloría recibe constantemente quejas de presidentes municipales, contralores internos y tesoreros porque las autorizaciones se detienen y el presupuesto no se ejecuta. Se señala que las consecuencias recaen en las comunidades: obras que no comienzan, servicios que se retrasan y necesidades que siguen sin respuesta. Frente al argumento de que la reforma debilita la vigilancia, Bardales sostuvo que la contratación pública tiene obligaciones que deben cumplirse: procedimientos de obra y adquisiciones, suficiencia presupuestaria, integración de expedientes, comprobación de pagos y fiscalización. También intervienen los órganos internos de control y la ciudadanía organizada en comités de Contraloría Social. “La preocupación por preservar los contrapesos es legítima; también lo es exigir que esos controles funcionen y permitan atender a la población. Ninguna facultad pública debe convertirse en un coto de poder ni en una oportunidad para negociar beneficios particulares”, señala el comunicado. “El señalamiento alcanza también a las presidencias municipales: agilizar los procedimientos no justifica contrataciones arbitrarias, proveedores favorecidos ni obras deficientes. Quien ejerce el presupuesto debe acreditar cada decisión y responder por cualquier irregularidad”. A ello se agrega que “existen recursos federales sujetos a plazos cuyo incumplimiento puede generar la obligación de devolverlos. Una confrontación política puede terminar costándole a una comunidad el agua, el drenaje o la calle que esperaba.</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales, en calidad de Contralor del Estado de Hidalgo, también salió, en calidad de defensor en este caso, de las modificaciones de la reforma que se hizo al artículo 114 de la Constitución Política del Estado de Hidalgo, esto para que sean los presidentes, presidentas municipales, quienes decidan directamente los convenios, contratos y demás, sin necesidad de que le hagan aprobación el cabildo o estrellas. Así es, de hecho, por medio de un comunicado oficial se dio a conocer Acerca el titular de la Secretaría de la Contraloría en el Estado de Hidalgo, Álvaro Bardales, respaldó la eliminación de autorizaciones duplicadas para la contratación municipal. Esto luego de que un grupo de asambleístas de varios municipios de la entidad se habían manifestado públicamente respecto a esta reforma al artículo 141 de la Constitución Política del Estado de Hidalgo. La reforma establece la autorización para que se den los acuerdos y contratos sin la obligación de ser autorizados por integrantes de la Asamblea Municipal respectiva. Los asambleístas que se oponen a la reforma señalan que con esta se les resta facultades a los integrantes de los cuerpos edilicios. Al respecto, Bardales señaló que los recursos públicos no pueden quedar sujetos a disputas políticas, intereses personales o incapacidad para construir acuerdos. Señaló que cuando el presupuesto ya fue aprobado y se cumplen los requisitos legales para contratar, Exigir nuevamente el aval del cabildo puede tener las mismas obras y acciones que el ayuntamiento ya habría autorizado El funcionario se que revisar el gasto constituye una obligación pero utilizar una autorización pendiente para obtener plazas contratos o beneficios personales s representa una conducta que debe investigarse cuando existan elementos La Contralor recibe constantemente quejas de presidentes municipales contralores internos y tesoreros porque las autorizaciones se detienen y el presupuesto no se ejecuta Se señala que las consecuencias recaen en las comunidades, obras que no comienzan, servicios que se retrasan y necesidades que siguen sin respuesta. Frente al aumento de que la reforma debilita la vigilancia, Bardales sostuvo que la contratación pública tiene obligaciones que deben cumplirse, procedimientos de obra y adquisiciones, suficiencia presupuestaria, integración de expedientes, comprobación de pagos y fiscalización. También intervienen los órganos internos de control y la ciudadanía organizada en comités de contraloría social. La preocupación por preservar los contrapesos es legítima. También no es exigir que esos controles funcionen y permitan atender a la población. ninguna facultad pública debe convertirse en un coto de poder ni en una oportunidad para negociar beneficios particulares esto es lo que se puede leer en el comunicado el señalamiento también alcanza a las presidencias municipales agilizar los procedimientos, no justifica contrataciones arbitrarias y a ellos agrega que existen recursos federales sujetos a plazos cuyo incumplimiento puede generar la obligación de devolverlos Bueno, que en todo caso nadie está discutiendo acerca de la rendición de cuentas y la revisión de que estén bien hechas las obras. Lo que se está discutiendo es de que revises el contrato, los términos del contrato, el convenio, el acuerdo, lo que vayas a firmar antes de que se firme precisamente para evitar dobles revisiones. Sí, finalmente este tema de transparencia, además de que también ellos dicen, se nos limitan nuestras funciones y pues bueno, ahí están también los posicionamientos y usted también tendrá su mejor opinión al respecto.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Y0QIkFqIgvMbk1QHmhxYXvJUo_kJfD4g/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>OCSAD/Bol.1322-A/2026</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo amplía oportunidades de venta para emprendedores con discapacidad</t>
+  </si>
+  <si>
+    <t>Una de las cuestiones que enfatiza el gobierno del estado de Hidalgo, es el apoyo que se ha brindado al sector, a las personas que tienen algún tipo de discapacidad permanente, para que colocaran algún negocio, algún stand, algún puesto dentro de instalaciones de la feria, obvio que para apoyarse económicamente, Izza. Izza Hernández: Es correcto, con el propósito de fortalecer los emprendimientos y ampliar las oportunidades de desarrollo económico de las personas con discapacidad. El Gobierno de Hidalgo a través de la Secretaría de Bienestar e Inclusión Social, impulsa espacios de comercialización y vinculación también con otras instituciones. Al respecto Alfonso Hayyim Flores Barrera, quien es director general de inclusión para las personas con discapacidad de la Secretaría del Bienestar e Inclusión Social de Hidalgo, explicó que cinco familias emprendedoras eh participaron precisamente en estos pabellones artesanal y comercial también de la Feria de San Francisco Pachuca 2026, donde ofrecen semillas, dulces, pan, eh café, chocolate, mole, tejidos también, jabones. Aseguró también que estas acciones buscaron pues de alguna forma fortalecer la posibilidad de empleo y también desarrollo económico, además de fortalecer la adquisición de habilidades, la con la convivencia y la construcción también de redes de apoyo. Durante este año alrededor de 30 personas emprendedoras con discapacidad han participado en estos espacios, donde también se promueven habilidades para el trabajo, la convivencia y también la creación de redes de apoyo con la participación de sus familias y personas cuidadoras. De hecho, su participación en esta edición deriva también del acompañamiento de bueno, que el organismo ha brindado como tal durante este año a personas con discapacidad en diversas ferias de emprendimiento eh obviamente del estado y pues eh el cual también contempla alianzas en todas las dependencias para ampliar las alternativas de comercialización y de esa manera ofrecer orientación sobre registro de marcas, elaboración de etiquetas y herramientas también pues que contribuyan a mejorar la presentación de los productos. Estamos siempre eh pues con las puertas abiertas para poder apoyar de muchas formas y buscar también que hay un mejor posicionamiento, más vinculación con las instituciones y todas las facilidades para las familias y las personas con discapacidad, así lo afirmó Flores Barrera. No obstante, las personas con discapacidad interesadas en fortalecer pues un negocio o presentar a lo mejor algún proyecto de emprendimiento, pueden acudir a la Dirección General de Inclusión para las personas con discapacidad, que está ubicada en el Centro Administrativo del Bienestar y Desarrollo Rural en la capital hidalguense y bueno, pues el gobierno de Hidalgo eh promueve precisamente esta inclusión que eh se traduce en oportunidades concretas para poder comercializar pues productos, consolidar obviamente también modelos de negocio, ampliar la participación de las personas con discapacidad en la economía.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/185FMh0VuSTn4CFj_4w5X36TmIpZ68iPr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Alfonso Flores Barrera</t>
+  </si>
+  <si>
+    <t>Las lluvias registradas este fin de semana en el Estado de Hidalgo, han generado afectaciones, incluso cierre a la circulación en diversas vialidades. En Tenango de Doria, en la región Otomí-Tepehua, fue cerrada la vialidad a la altura de la localidad de Cerro Chiquito, en dirección a San José del Valle. Ello debido al incremento en los niveles de aguas en el río ubicado en la zona, además que se reportaron derrumbes que bloquearon carreteras. Debido a estas condiciones, no hay paso por esta vía, por lo que poblados ubicados en esta parte del municipio permanecen momentáneamente incomunicados. Además, se reportaron derrumbes que bloquearon carreteras. La posibilidad de habilitar el paso de manera restringida permanece en evaluación, en espera de que descienda el nivel del río y las condiciones permitan transitar de forma segura. Una de las afectaciones más importantes se reportó en la carretera San Mateo–San Bartolo Tutotepec, que permanece completamente cerrada debido a un derrumbe que cubrió la vía. La ruta alterna tampoco puede utilizarse, ya que está obstruida por material de construcción. Además, que un árbol cayó sobre la vía Metepec–Tenango de Doria. Protección Civil pidió no intentar cruzar por estos puntos, ante la posibilidad de nuevos deslaves y desprendimientos ocasionados por la humedad del terreno. En la carretera Pachuca–Tampico, personal y maquinaria de la Secretaría de Infraestructura Comunicaciones y Transportes (SICT) Hidalgo realizaron labores para retirar rocas y durante los trabajos, la circulación permaneció habilitada por solo un carril. En Xochiatipan el aumento del nivel del río Garcés obligó a interrumpir el tránsito vehicular hacia el municipio de Xochiatipan, luego de que el agua rebasara el vado provisional. Mientras que en el tramo carretero Nicolás Flores–Cardonal se reporta la caída de piedras, lo que se ha limitado la circulación en dicha vialidad, para evitar el registro de alguna emergencia. La Subsecretaría de Protección Civil y Gestión de Riesgos del Gobierno de Hidalgo exhortó a la población a mantener y reforzar las medidas preventivas, señalando que está activo el semáforo amarillo, que establece medidas de vigilancia y prevención. Se advirtió que la disminución o suspensión temporal de las lluvias no significa que el peligro haya desaparecido, ya que la saturación del terreno puede ocasionar movimientos de tierra incluso cuando no se registran precipitaciones. Como parte de las medidas preventivas, la dependencia exhortó a la población a evitar cruzar ríos, arroyos, vados y caminos inundados, tanto a pie como en vehículo, así como mantenerse alejada de cauces, barrancas y laderas inestables. También pidió extremar precauciones al transitar por carreteras y caminos rurales, respetar los cierres y señalamientos viales.</t>
+  </si>
+  <si>
+    <t>Le comentaba hace un momento que por obvia razón está siendo muy complicado circular por la Sierra Otomí-Tepeha, así como por la parte norte del estado, a partir de las lluvias que se han presentado en días, en semanas anteriores, y reiteramos lo dicho por los cuerpos de protección civil, ha dejado de llover, pero por una parte va a seguir lloviendo y por otra parte, en la temporada de secas, se va asentando, reasentando la tierra, y por lo tanto la humedad que se queda atrapada pues va tratándose allí por los deslaves. Lo que está reportando en este momento la Secretaría de Protección Civil del Estado de Hidalgo junto con la Secretaría de Infraestructura, Comunicaciones y Transportes y la Secretaría de Infraestructura del Estado de Hidalgo son afectaciones que se están presentando. Por ejemplo, Tenango de Doria fue cerrada a la vialidad a la altura de la localidad de Cerro Chiquito en dirección a San José del Valle. Esto debido al incremento en los niveles de agua ubicados en la zona además de que se reportaron derrumbes que bloquearon carreteras debido a estas condiciones no hay paso por esta vía por lo que poblados ubicados en esa parte del municipio permanecen incomunicados en la actualización correspondiente veo que a las 6.55 de la mañana del día de hoy continúan todavía con paso controlado lo que comentaba Isa hace un ratito una de las afectaciones más importantes también se reportó en la carretera San Mateo Bartolom que permanece completamente cerrada debido a un derrumbe que cubrió la vía en el cual se está trabajando con maquinaria para retirar el material petreo la tierra y la piedra La ruta alterna tampoco puede utilizarse ya que está obstruida por material de construcción, además de que un árbol cayó sobre la vía Metepec-Tenango de Adoria, el cual se retiró. Protección Civil pidió no intentar cruzar eso sí por estos puntos ante la posibilidad de nuevos deslaves y desprendimientos ocasionados por la humedad del terreno. En la carretera Pachuca-Tampico, el personal y maquinaria de la SICT Hidalgo realizaron labores para retirar rocas y durante los trabajos la circulación permaneció habilitada por un solo carril. En Xochitlán, el aumento en los niveles del río Garcés obligó a interrumpir el tránsito vehicular hacia municipios de Xochitlán precisamente luego de que el agua rebasara el vado provisional. Mientras que en el tramo carretero Nicolás Flores Cardonal, en el Valle del Mezquital, se reporta la caída de piedras, lo que ha limitado las circulaciones hacia esa vialidad para evitar el registro de alguna emergencia. le reitero que la subterránea de protección civil y gestión de riesgos del gobierno de Hidalgo exhorta a la población a que por favor no insistan si le están diciendo que el paso está cerrado o controlado o que tienen que esperar este tantito, haga caso no rebase, y bueno, si lo logra porque hay vías como le comentaba hace rato la Pahuatlán San Mateo donde es imposible que circule un solo auto por lo estrecho de la vialidad sumado al tema de de lodo, que ha caído en esas zonas en días y en horas recientes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UC0LgHX-z6-hT78JeKJVKkYnHiZwlR0P/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SIPDUS, SICT</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hFSLuVjXg6rNtQzT836JpgUfK02vN-Sc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Subsecretaría de Protección Civil del Estado de Hidalgo,  SICT</t>
+  </si>
+  <si>
+    <t>SSH/Bol.179/2026</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud del Estado de Hidalgo informó que, en el marco del Día Mundial de la Lucha contra el Cáncer de Mama, en Hidalgo se detectaron 186 casos en lo que va de 2026, al corte del 3 de octubre, con una tasa de 13.5 por cada 100 mil mujeres del mismo grupo de edad. La dependencia detalló que se realizaron 8 mil 718 exploraciones clínicas de mama y 5 mil 30 mastografías de tamizaje mediante una unidad móvil. Mientras que, en 2025, se registraron 355 casos de cáncer de mama en Hidalgo, con una tasa de 33.7 por cada 100 mil mujeres de 25 años y más. Eduardo Padilla González, encargado de la Subdirección de Atención en las Etapas de la Vida, de la Subsecretaría de Salud Pública, asumió que identificar la enfermedad en etapas tempranas es fundamental para mejorar el pronóstico y las posibilidades de tratamiento. De acuerdo con el funcionario, la estrategia incluyó la detección, valoración y confirmación diagnóstica. No obstante, se instó a las mujeres a conocer el aspecto y la consistencia habituales de sus mamas para reconocer posibles alteraciones, como bolitas, cambios en la piel, modificaciones en el pezón o secreciones inusuales. La SSH recomendó solicitar orientación del personal sanitario sobre los estudios de detección adecuados, de acuerdo con la edad y los antecedentes personales, así como consultar los resultados y realizar las pruebas complementarias cuando estén indicadas.</t>
+  </si>
+  <si>
+    <t>Cáncer De Mama</t>
+  </si>
+  <si>
+    <t>¿Qué reporta la Secretaría de Salud del Estado de Hidalgo, Izza, en el comunicado respecto a este tema, después de conocerse acerca de este Día Mundial de la Lucha contra el Cáncer de Mama? Pues bien, les platicamos que la Secretaría de Salud del Estado de Hidalgo informó que en el marco del Día de la Lucha contra el Cáncer de Mama, Aquí en el estado de Hidalgo se detectaron 186 casos en lo que va de estos 2026 al corte del 3 de octubre con una tasa de 13.5 por cada 100.000 mujeres del mismo grupo de edad. De hecho la dependencia detalló que se realizaron 8.718 exploraciones clínicas de mama y 5.030 mastografías de tamizaje, esto mediante una unidad móvil. De hecho, mientras que en 2025 se registraron 355 casos de cáncer de mama en Hidalgo, con una tasa de 33.7 por cada 100.000 mujeres de 25 años y más, de hecho Eduardo Padilla González, encargado de la Subdirección de Atención en las Etapas de la Vida, la Subsecretaría también de Salud Pública, asumió que identificar la enfermedad en etapas tempranas es fundamental para poder mejorar el pronóstico y las posibilidades de tratamiento. De hecho y de acuerdo con el funcionario la estrategia incluye la detección valoración y confirmación diagnóstico también No obstante se insta también a las mujeres a conocer el aspecto y la consistencia de manera habitual de sus mamas para reconocer posibles alteraciones como bolitas, cambios en la piel, modificaciones en el pezón o secreciones inusuales. Entonces la Secretaría de Salud de Hidalgo ha recomendado solicitar orientación del personal sanitario Sobre los estudios de detección adecuados y de acuerdo con la edad y también los antecedentes personales Así como consultar los resultados y realizar también las pruebas complementarias cuando estén indicadas Entonces pues si son 186 casos de cáncer de mama en lo que va a este 2026 Y pues este día mundial de lucha contra el cáncer de mama Daniel Como siempre lo decimos, es para recordar que siempre hay momento para hacer la detección temprana y siempre, siempre es oportuno hacer la exploración adecuada. Y obviamente hay cierta edad en la cual es más recomendable, pero a cualquier edad es de verdad muy importante que se realice la exploración correspondiente. Y pues ante cualquier sospecha, alguna situación vaya que de repente pensemos que no es habitual, que no es normal, pues acudir directamente con el especialista.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TZFL-UCc6LFHsTp3-BA1A_tbZJEPao5b/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Eduardo Padilla González</t>
+  </si>
+  <si>
+    <t>Daniel Martínez: ...justamente en ese mismo mes de junio, cuando estuvo de visita de trabajo en la región Tulancingo, Napoleón González Pérez, a pregunta expresa de compañeras, compañeros de medios de comunicación de la región, le preguntaron que qué iban a hacer, ¿no?, con estas denuncias a lo que dijo: "Voy a pedir de inmediato, voy a pedir de inmediato una revisión. Apenas eh la semana pasada, a mediados de la semana pasada, González Pérez dijo que apenas iba a pedir la revisión y Vanessa Escalante en el en el TCC de Rauche le dice: 'Pues en otro ya empezamos a revisar, nada más que les vamos a dar a conocer los resultados en cuanto terminemos la revisión de las muestras que hemos tomado, ¿eh? Izza Hernández: Sí, incluso mencionan, no necesitan pedirnos, ya nosotros estamos tomando cartas en el asunto, estamos pues revisando el tema.</t>
+  </si>
+  <si>
+    <t>Huachileche</t>
+  </si>
+  <si>
+    <t>Valle de Tulancingo</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud en Hidalgo (SSH) ya realiza desde hace meses revisión de muestreos de la leche que se ofrece en Tulancingo a cuatro pesos por litro. Lo anterior fue informado por la titular de la dependencia estatal, Vanessa Escalante Arroyo, durante su comparecencia realizada este viernes 16 de octubre ante integrantes del Congreso del Estado de Hidalgo. Previamente, el titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh), Napoleón González Pérez, durante su respectiva comparecencia, anunció ante los legisladores locales que solicitaría ante la SSH que se realizaran inspecciones a la leche que se ofrece en el Valle de Tulancingo. En junio de este mismo año, en visita de trabajo al Valle de Tulancingo, había asegurado que tuvo conversación con la SSH para que por medio de la Comisión estatal para la Prevención de Riegos Sanitarios (Copriseh) se revisara la calidad y sanidad de la leche que llega sobre todo del Bajío mexicano. “No es necesario que nuestro compañero secretario nos lo solicite; nosotros ya iniciamos desde hace tiempo”, declaró Escalante Arroyo durante la comparecencia a su cargo. Justamente durante el mes de junio de este año, productores lecheros del Valle de Tulancingo denunciaron que a la región estaban ingresando unidades con lácteo supuestamente proveniente de la región Bajío, ofreciendo el litro a cuatro pesos. Además de representar competencia desleal, los productores locales señalaron que dicho precio causa sospecha respecto a la calidad, y por tanto, si es adecuado para consumo humano. La titular de la SSH señaló que a través de la Copriseh, ya se tienen programados nuevos muestreos para los próximos meses. “Esto no deberíamos decirlo porque ponemos en alerta a la comunidad, pero vamos a estar nosotros supervisando este tipo de circunstancias, porque entendemos también la competencia desleal que se está dando a los productores en el estado de Hidalgo”, enfatizó ante los legisladores del Congreso del Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural de Hidalgo</t>
+  </si>
+  <si>
+    <t>En unos instantes agenda igual en unos minutos más el gobernador Julio Menchaca Salazar encabezará la inauguración de las áreas administrativas de Innovación Gubernamental, Centro de datos e inteligencia artificial del Estado de Hidalgo, se realizará a las 11:00 en el estacionamiento del aeropuerto Juan Guillermo Villasana.</t>
+  </si>
+  <si>
+    <t>Aldo Falcón: En unos instantes agenda igual en unos minutos más el gobernador Julio Menchaca Salazar encabezará la inauguración de las áreas administrativas de innovación gubernamental, centro de datos e inteligencia artificial del Estado de Hidalgo, se realizará a las 10:45 en el estacionamiento del aeropuerto Juan Guillermo Villasana. Andrés Torres: Acá en el sur de la capital hidalguense a las 11 de la mañana. Aldo Falcón: A las 11 de la mañana. Andrés Torres: Va a ser el evento que encabezará el gobernador esta inauguración.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RQUFZoTxZ3sgNnMQWmCXrOGeN9Eu2Nct/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Samperio Ortiz, muy buenos días, Andrés y Aldo, después de un tiempo de no estar en contacto con ustedes, hoy los saludo. Hay una fuga de agua aquí en San Antonio el Desmonte, en la calle de Capricornio, ya tienen mucho tiempo y las autoridades no hacen caso.</t>
+  </si>
+  <si>
+    <t>Fuga De Agua</t>
+  </si>
+  <si>
+    <t>Samperio Ortiz, muy buenos días, Andrés y Aldo, después de un tiempo de no estar en contacto con ustedes, hoy los saludo. Hay una fuga de agua aquí en San Antonio el Desmonte, en la calle de Capricornio, si ya tienen mucho tiempo y las autoridades no hacen caso, excelente inicio de semana. Muchas gracias, muy amables, muy buenos días, bueno, pues para las autoridades nos ayuden, aquí en la calle de Capricornio, en la colonia San Antonio del Desmonte.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11ivBvTyl4AJ0D_t4-revgH00tqJrDmVH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bZ_RADxw2MILs--8-RYSqSVeqsweNtWQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEMARNATH</t>
+  </si>
+  <si>
+    <t>UPLAPH/Bol.159-A/2026</t>
+  </si>
+  <si>
+    <t>Hidalgo fortalece la participación ciudadana en la Consulta Pública del POZMVM</t>
+  </si>
+  <si>
+    <t>ZMVM</t>
+  </si>
+  <si>
+    <t>Durante la décimo cuarta sesión ordinaria de 2026 del Secretario Técnico Conjunto del Consejo de Desarrollo Metropolitano del Valle de México, autoridades federales representantes de la Ciudad de México y del Estado de Hidalgo, Morelos, se dieron seguimiento a los avances de la consulta pública de la consulta indígena del programa de orientación de la zona metropolitana del Valle de México. En representación de Hidalgo, el Coordinador General de Planeación y Proyectos encargados del despacho de la Unidad de Planeación Prospectiva, respectiva, Onésimo Rodrigo Serrano Rivera destacó que los avances de la consulta pública de la entidad, así como la importancia de incorporar propuestas ciudadanas en la construcción de una visión metropolitana compartida. Respecto a la consulta indígena, se informó que Hidalgo se ha desarrollado protocolos de consulta en los municipios de Tula de Allende con el propósito de promover la participación, el diálogo en ambos pueblos de las comunidades indígenas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tR_qJX8FhzDPeacwUpeE184xbF8t9uAc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Segobh/TI.05/2026</t>
+  </si>
+  <si>
+    <t>Hidalgo mantiene política de cero tolerancia a la corrupción y garantiza el respeto a los derechos humanos</t>
+  </si>
+  <si>
+    <t>Persecución política</t>
+  </si>
+  <si>
+    <t>En el secretario de gobierno Guillermo Oliver Reina rechazó que exista persecución política contra los integrantes del Partido del Trabajo y afirmó que el respeto a los derechos humanos es un principio fundamental en la actuación del gobierno de Hidalgo. Ante los señalamientos de representantes de ese partido sobre presuntas motivaciones políticas en los procedimientos judiciales que enfrentan algunos de sus integrantes, el funcionario sostuvo que la actuación gubernamental se rige por el respeto a los derechos humanos y la legalidad. En Hidalgo no existe un régimen de persecución política. Sin embargo, sí hay una política de cero tolerancia a la corrupción y a la impunidad. Por ello, las investigaciones correspondientes deben seguir su curso, sin importar la afiliación partidista de las personas involucradas. Si algo respeta el gobierno del Estado de Hidalgo, son los derechos humanos, se empatizó Guillermo Olivares Reina al reiterar que el compromiso institucional es actuar con apego a la ley, sin distinciones partidistas y con pleno respeto a las garantías individuales. Bueno, pues vaya que ha generado cierto movimiento en las redes sociales, yo le diría que expectativa en las redes sociales porque a este asunto de la supuesta persecución hacia algunas personalidades del Partido del Trabajo pues le vino muy bien lo hicieron muy lo sintonizaron muy bien y lo cuadraron muy bien con el tema de la reciente aprobación de una ley en el Congreso del Estado de Hidalgo para reducir el n de regidores en los cabildos El asunto es que la dirigencia del Partido del Trabajo no está de acuerdo con que los diputados del Partido del Trabajo en el Congreso Estatal votaran a favor esta ley. Entonces, bueno, pues es un tema que yo entiendo que es un tema interno. Sin embargo, en esta situación, las autoridades del Partido del Trabajo en Hidalgo aprovecharon para decir, y también los representantes federales del Partido del Trabajo, acusaron persecución política. que vamos a ver qué se resuelve todo esto, entiendo que, y así lo anunciaron los representantes del Partido del Trabajo en Hidalgo, y acudirán a las instancias internas de ese organismo político, a sus órganos jurisdiccionales, para conocer, para saber, para promover en todo caso algún tipo de penalización en contra de sus diputados, que entiendo votaron en contra del espíritu del partido, al menos de lo que están en este momento manifestando, respecto a esta ley de reducción de regidores y respecto a las persecuciones que acusan, bueno, pues todo eso ya está en manos de los tribunales, así que serán las autoridades correspondientes quienes determinen si o no responsabilidad de estas personas señaladas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1869QVduSFKROcbZNCyY2HS28JwkUQ8SL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos del Gobierno del Estado de Hidalgo emitió una alerta con días de anticipación y envió personal a monitorear el clima en diferentes zonas afectadas. En Xochiatipan, un vado se derrumbó, dejando incomunicadas 35 comunidades sin electricidad y telefonía. En Tenango de Doria, el río creció y se tomó la precaución de resguardar el área para evitar el paso peatonal. Desde el viernes, se reportaron intensas lluvias en San Bartolo Tutotepec y Tenango de Doria, ocasionando la caída de árboles y materiales en la carretera. A pesar de que hubo cierre de la vía, las brigadas locales lograron retirar los obstáculos, y ahora la carretera está transitable. Sin embargo, las lluvias pueden seguir causando problemas, y se advierte sobre el riesgo del crecimiento del vado mencionado. Se compartieron videos en redes sociales de inundaciones en Soteapan, donde se reportó que una persona pudo ser arrastrada por la corriente y se encuentra desaparecida. También hubo fuertes lluvias en Huejutla, causando inundaciones en varias colonias, pero hasta ahora no se han reportado incidentes graves en las carreteras, aunque sí la caída de algunos árboles. La alerta se mantiene activa y la Subsecretaría de Protección Civil y la Secretaría de Gobierno continúan supervisando las áreas afectadas. Se recomienda que la población esté atenta a la señal de Radio y Televisión de Hidalgo para recibir actualizaciones sobre el clima y acciones a seguir en caso de una contingencia.</t>
+  </si>
+  <si>
+    <t>Andrés Torres: La Subsecretaría de Protección Civil y Gestión de Riesgos del Gobierno del Estado de Hidalgo nos dio esta alerta con varios días de anticipación. Personal de la subsecretaría se trasladó a estas zonas para estar muy atentos monitorizando el comportamiento pues del fenómeno climático. Cuéntanos. Aldo Falcón: Así es Andrés, algunas de las afectaciones que se presentaron en diferentes municipios, principalmente en Soteapan, donde el vado lamentablemente se ha derrumbado. Un vado es una zona baja, se inundó, dejando incomunicadas a 35 comunidades y también sin energía eléctrica ni tampoco con telefonía. El Ayuntamiento de Tenango de Doria dio a conocer que el río ubicado en el cerro Chiquito con dirección a San José del Valle también presenta incremento en su cauce, por tal motivo fue resguardado para evitar el paso peatonal. Andrés Torres: Desde el viernes nos reportaban nuestros amigos allá en San Bartolo Tutotepec y en Tenango de Doria que las intensas lluvias habían generado la caída de árboles, algunos materiales, sobre todo en la carretera que une San Bartolo Tutotepec con Tenango de Doria, hubo necesidad de retiro de materiales. Por momentos la carretera estuvo cerrada, pero gracias al trabajo de las brigadas de las presidencias municipales, de la Secretaría de Infraestructura y por supuesto personal de Protección Civil, no fue necesario, bueno, pues mayor a la situación y se retiró este material. La carretera está libre, se puede transitar. Sin embargo, sin embargo, advierten las lluvias constantes, los escurrimientos pueden generar todavía el crecimiento de este puente vado al que hablaba Aldo, esto en Soteapan, que es en la Huasteca, y bueno, esto genera y puede representar un riesgo para la población. Videos que circularon en las redes sociales, sobre todo en la Huasteca el fin de semana, muestran como la corriente allá en Soteapan, precisamente en esta zona del vado, se arrastró a una persona. No tenemos confirmado todavía este si esta persona desafortunadamente murió, pero todo el reporte extraoficial es que hay una persona desaparecida. Muchísima lluvia allá en Huejutla el viernes, el sábado, mucha lluvia en muchas zonas inundadas, incluso en la misma cabecera municipal, bueno, pues varias colonias tuvieron problemas con la crecida del agua. Afortunadamente, afortunadamente no se reportan incidentes mayores, caída de material sobre la carretera Pachuca-Huejutla o México-Tampico Vía Corta y también se reportaron algunos árboles que cayeron y crecías en los ríos, pero afortunadamente nada más. La alerta se mantiene hasta que bueno, pues tengamos los saldos ya totalmente confirmados. La Subsecretaría de Protección Civil, la Secretaría de Gobierno mantienen la supervisión en estas regiones de nuestro estado y por supuesto, yo le insisto, por favor, muy atentos a la señal de Radio y Televisión de Hidalgo, como toda la semana pasada, esta semana continuaremos dándoles el reporte sobre el pronóstico del clima y, en caso de una contingencia, por supuesto estaremos dando aviso para que la gente sepa qué hacer, a dónde dirigirse y por supuesto este en todo momento contribuir para que la gente esté segura.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dDiV-bBl-vkn82qa7w0q6gKnXFDXg9tD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SIPDUS, Radio y Televisión de Hidalgo</t>
   </si>
 </sst>
 </file>
@@ -1085,8 +1874,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X28" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X28" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X66" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X66" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1482,12 +2271,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="81.140625" bestFit="1" customWidth="1"/>
@@ -1556,39 +2345,39 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6">
         <v>46311</v>
@@ -1597,54 +2386,68 @@
         <v>58</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
+      <c r="P2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" s="5">
+        <v>68</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
+      <c r="W2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6">
         <v>46311</v>
@@ -1653,54 +2456,66 @@
         <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+      <c r="Q3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S3" s="3">
+        <v>47</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
+      <c r="W3" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6">
         <v>46311</v>
@@ -1709,54 +2524,68 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
+      <c r="P4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" s="3">
+        <v>52</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="V4" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>46311</v>
@@ -1765,54 +2594,66 @@
         <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+      <c r="P5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S5" s="3">
+        <v>7</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="W5" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6">
         <v>46311</v>
@@ -1821,54 +2662,66 @@
         <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
+      <c r="P6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S6" s="3">
+        <v>159</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="W6" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6">
         <v>46311</v>
@@ -1877,211 +2730,265 @@
         <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S7" s="3">
+        <v>64</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6">
         <v>46311</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S8" s="3">
+        <v>70</v>
+      </c>
+      <c r="T8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
+      <c r="U8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C9" s="6">
         <v>46311</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
+      <c r="P9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S9" s="3">
+        <v>98</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C10" s="6">
         <v>46311</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S10" s="3">
+        <v>39</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -2089,447 +2996,555 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C11" s="6">
         <v>46311</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="L11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="N11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
+      <c r="P11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" s="3">
+        <v>99</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C12" s="6">
         <v>46311</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="N12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
+      <c r="P12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S12" s="3">
+        <v>154</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6">
         <v>46311</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="L13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="N13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+      <c r="P13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S13" s="3">
+        <v>166</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
+      <c r="V13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="X13" s="3"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="C14" s="6">
         <v>46311</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
+      <c r="P14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S14" s="3">
+        <v>37</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
+      <c r="W14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C15" s="6">
         <v>46311</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="P15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S15" s="3">
+        <v>59</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
+      <c r="W15" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="X15" s="3"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C16" s="6">
         <v>46311</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
+      <c r="P16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S16" s="3">
+        <v>189</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="W16" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="X16" s="3"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="C17" s="6">
         <v>46311</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O17" s="3" t="s">
+      <c r="S17" s="3">
+        <v>157</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
       <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="W17" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="C18" s="6">
         <v>46311</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M18" s="3" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S18" s="3">
+        <v>29</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2537,55 +3552,65 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="6">
         <v>46311</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+        <v>159</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S19" s="3">
+        <v>75</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2593,391 +3618,483 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="6">
         <v>46311</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I20" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
+      <c r="R20" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
+      <c r="W20" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" s="6">
         <v>46311</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I21" s="3" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="P21" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S21" s="3">
+        <v>11</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
+      <c r="V21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="6">
         <v>46311</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
+      <c r="P22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S22" s="3">
+        <v>11</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
+      <c r="V22" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C23" s="6">
         <v>46311</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
+      <c r="P23" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S23" s="3">
+        <v>82</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
+      <c r="W23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6">
         <v>46311</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
+      <c r="P24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S24" s="3">
+        <v>11</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="W24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C25" s="6">
         <v>46311</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="P25" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S25" s="3">
+        <v>516</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="6">
         <v>46311</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
+      <c r="P26" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S26" s="3">
+        <v>135</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2985,55 +4102,65 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="6">
         <v>46311</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
+        <v>192</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S27" s="3">
+        <v>62</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3041,59 +4168,2697 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="6">
         <v>46311</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
+      <c r="P28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S28" s="3">
+        <v>58</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6">
+        <v>46311</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S29" s="3">
+        <v>204</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>1</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="6">
+        <v>46311</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S30" s="3">
+        <v>26</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>21</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S31" s="3">
+        <v>105</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="X31" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>20</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S32" s="3">
+        <v>112</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>19</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S33" s="3">
+        <v>101</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>16</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S34" s="3">
+        <v>279</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>15</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S35" s="3">
+        <v>148</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>14</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S36" s="3">
+        <v>32</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>12</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S37" s="3">
+        <v>14</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X37" s="3"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S38" s="3">
+        <v>113</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>10</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S39" s="3">
+        <v>357</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>9</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S40" s="3">
+        <v>49</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="X40" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>7</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S41" s="3">
+        <v>355</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S42" s="3">
+        <v>57</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="X42" s="3"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>3</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S43" s="3">
+        <v>385</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>1</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S44" s="3">
+        <v>275</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X44" s="3"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>37</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S45" s="3">
+        <v>543</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>36</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S46" s="3">
+        <v>543</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>35</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S47" s="3">
+        <v>543</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>34</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S48" s="3">
+        <v>13</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>33</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S49" s="3">
+        <v>72</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>28</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S50" s="3">
+        <v>22</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X50" s="3"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>26</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S51" s="3">
+        <v>59</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>25</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C52" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S52" s="3">
+        <v>201</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="X52" s="3"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>24</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S53" s="3">
+        <v>166</v>
+      </c>
+      <c r="T53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U53" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V53" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="W53" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X53" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>21</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S54" s="3">
+        <v>207</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="X54" s="3"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>19</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C55" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S55" s="3">
+        <v>181</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U55" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>15</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S56" s="3">
+        <v>170</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U56" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V56" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>14</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S57" s="3">
+        <v>170</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>13</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3">
+        <v>162</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="X58" s="3"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>12</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>11</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>10</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S61" s="3">
+        <v>23</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X61" s="3"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>8</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S62" s="3">
+        <v>21</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>6</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S63" s="3">
+        <v>13</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>5</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S64" s="3">
+        <v>47</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U64" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="X64" s="3"/>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>4</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C65" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q65" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S65" s="3">
+        <v>184</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U65" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="X65" s="3"/>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>1</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S66" s="3">
+        <v>217</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F4AC71-1668-4B8A-87B9-CBD066D5B99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09ECEF80-D5F3-4D32-BE12-8E24D4083AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="277">
   <si>
     <t>#</t>
   </si>
@@ -110,9 +110,6 @@
     <t>Segobh</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
     <t>Opinión</t>
   </si>
   <si>
@@ -170,15 +167,6 @@
     <t>Contenido</t>
   </si>
   <si>
-    <t>Saderh</t>
-  </si>
-  <si>
-    <t>OCSAD</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
     <t>Canal del Pueblo</t>
   </si>
   <si>
@@ -215,9 +203,6 @@
     <t>Aldo Falcón</t>
   </si>
   <si>
-    <t>STPSH</t>
-  </si>
-  <si>
     <t>SSH</t>
   </si>
   <si>
@@ -242,12 +227,6 @@
     <t>Enlace Hidalgo2</t>
   </si>
   <si>
-    <t>Conferencia magistral</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
     <t>Tulancingo</t>
   </si>
   <si>
@@ -257,304 +236,662 @@
     <t>Semarnath</t>
   </si>
   <si>
-    <t>Cáncer De Mama</t>
-  </si>
-  <si>
-    <t>Un hombre fue localizado sin vida en la comunidad de El Chamizal, perteneciente al municipio de Tezontepec de Aldama, Hidalgo, presentando múltiples heridas por impactos de arma de fuego tras el reporte de detonaciones el martes 20 de octubre. Elementos policíacos y cuerpos de emergencia acudieron al lugar, confirmando el fallecimiento de la víctima y procediendo al acordonamiento de la zona. Posteriormente, se solicitó la intervención de la Procuraduría General de Justicia del Estado de Hidalgo para realizar las diligencias ministeriales e iniciar con la investigación, encontrándose el cuerpo en calidad de desconocido hasta el momento.</t>
-  </si>
-  <si>
     <t>Localización de cuerpo</t>
   </si>
   <si>
-    <t>Informativa</t>
-  </si>
-  <si>
     <t>Tezontepec de Aldama</t>
   </si>
   <si>
-    <t>Padres de familia de la Escuela Primaria Benito Juárez bloquearon vialidades principales en la zona centro de Huejutla para exigir el cierre del turno vespertino (correspondiente a la primaria Ildefonso Velázquez Ibarra), el cual comparte las mismas instalaciones. La movilización se originó por desacuerdos en el pago de cuotas escolares y la supuesta falta de aportaciones equitativas por parte del turno vespertino, postura que fue rechazada por los tutores de dicho turno, quienes afirman haber cumplido con los pagos establecidos. Los manifestantes exigen a las autoridades educativas la reubicación de la primaria Ildefonso Velázquez Ibarra para resolver estas diferencias.</t>
-  </si>
-  <si>
     <t>Básica</t>
   </si>
   <si>
     <t>Queja padres de familia</t>
   </si>
   <si>
-    <t>Negativa</t>
-  </si>
-  <si>
-    <t>Huejutla</t>
-  </si>
-  <si>
-    <t>Locutor Irving Sánchez da lectura a comentario de radioescucha que , reporta irregularidades en el servicio de transporte público (colectivas de la ruta Rojo Gómez), específicamente por no respetar los semáforos y provocar situaciones de riesgo. Ante esto, Locutor Jesús Riveros recordó a la ciudadanía la importancia de formalizar sus quejas ante la Secretaría de Movilidad y Transporte del Estado de Hidalgo mediante el número telefónico 800 503 2002 o 771 526 1284, el correo electrónico quejatransporte@hidalgo.gob.mx, o directamente en las oficinas correspondientes conforme al artículo 286 de la Ley de Movilidad y Transporte, destacando que es indispensable contar con el número de la unidad para dar un seguimiento oficial.</t>
-  </si>
-  <si>
     <t>STCH</t>
   </si>
   <si>
     <t>Queja transporte público</t>
   </si>
   <si>
-    <t>Canal 12 Huejutla</t>
-  </si>
-  <si>
-    <t>En entrevista para el espacio de contacto informativo, la coordinadora estatal del INEGI en Hidalgo, Laura Silvia González Quintos, presentó los resultados de la Encuesta Intercensal 2025, destacando que el estado cuenta actualmente con 3,245,595 habitantes, lo que refleja un crecimiento continuo pero a un ritmo menor (tasa promedio anual de 0.9%) en comparación con el censo de 2020, posicionando a la entidad en el lugar 16 a nivel nacional. Asimismo, la funcionaria detalló una disminución en la tasa global de fecundidad (pasando de 1.8 a 1.1 hijos por mujer), cambios en la estructura poblacional con mayor presencia de adultos mayores, y modificaciones en el acceso a tecnologías e internet, el cual subió del 39.3% al 70.5% en cinco años. Finalmente, en cuanto a población hablante de lengua indígena se registraron 352,062 personas (11.2%), y se informó sobre la reorganización en las categorías de afiliación a los servicios de salud y el parque habitacional, que aumentó a más de un millón de viviendas.</t>
-  </si>
-  <si>
-    <t>Taide Salazar</t>
-  </si>
-  <si>
-    <t>Contacto Informativo M</t>
-  </si>
-  <si>
-    <t>Entrevista pautada</t>
-  </si>
-  <si>
-    <t>Censo Inegi</t>
-  </si>
-  <si>
-    <t>Positiva</t>
-  </si>
-  <si>
-    <t>Segobh/Coespo/Bol.41/2026</t>
-  </si>
-  <si>
     <t>Radio Lobo 96.7 FM</t>
   </si>
   <si>
-    <t>Día Mundial contra el Cáncer de Mama: la detección oportuna puede salvar vidas</t>
-  </si>
-  <si>
     <t>Gina Lorenzo</t>
   </si>
   <si>
     <t>Enlace Noticias</t>
   </si>
   <si>
-    <t>Coespo</t>
-  </si>
-  <si>
-    <t>Saderh/Bol.85/2026</t>
-  </si>
-  <si>
-    <t>Entrega Saderh apoyos productivos a 476 agro productores</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>Zapotlán</t>
-  </si>
-  <si>
     <t>SDPEE-OCSAD/FN.37/2026</t>
   </si>
   <si>
     <t>Julio Menchaca recorre subestación Hidalgo de CFE</t>
   </si>
   <si>
-    <t>Recorrido por instalaciones</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1328/2026</t>
-  </si>
-  <si>
-    <t>Menchaca Salazar entrega nuevo Centro de Datos y remodelación del aeropuerto de Pachuca.</t>
-  </si>
-  <si>
-    <t>Centro de datos</t>
-  </si>
-  <si>
     <t>SSH/Bol.181/2026</t>
   </si>
   <si>
-    <t>SSH hace un llamado a reforzar medidas de prevención ante el incremento de enfermedades respiratorias.</t>
-  </si>
-  <si>
-    <t>Prevención de enfermedades</t>
-  </si>
-  <si>
     <t>Semarnath/Bol.SN-L/2026</t>
   </si>
   <si>
-    <t>Semarnath Hidalgo fortalece la restauración forestal y la protección ambiental con inversión, ciencia y trabajo en territorio</t>
-  </si>
-  <si>
-    <t>Sipdus/Bol.61/2026</t>
-  </si>
-  <si>
-    <t>Julio Menchaca invierte más de 25 mil mdp en infraestructura pública: Alejandro Sánchez</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1938/2026</t>
-  </si>
-  <si>
-    <t>SEPH realiza el concurso de oratoria “Mi palabra es hoy mi voz y mi fortaleza 2026”</t>
-  </si>
-  <si>
-    <t>Concurso de oratoria</t>
-  </si>
-  <si>
-    <t>Se dio a conocer que el secretario de Educación Pública, Natividad Castrejón Valdez, tiene programada su comparecencia ante el Congreso del Estado para el día de hoy.</t>
-  </si>
-  <si>
-    <t>Menchaca Salazar entrega nuevo Centro de Datos y remodelación del aeropuerto de Pachuca</t>
-  </si>
-  <si>
-    <t>Sobre la llegada y operación de plataformas de transporte como Uber, el gobernador del estado señaló que el servicio no está prohibido en esencia, pero debe operar bajo los cauces legales y contar con la concesión formal de transporte individual. El mandatario indicó que ofrecer el servicio al margen de la ley implica asumir responsabilidades legales ante el Ministerio Público, y puntualizó que, aunque es necesario buscar opciones y alternativas para los usuarios, los operadores y concesionarios tradicionales también deben cumplir con su compromiso de atención al público de manera responsable.</t>
-  </si>
-  <si>
     <t>Apps de transporte</t>
   </si>
   <si>
-    <t>Semot/Bol.4/2026</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte (SEMOT) de Hidalgo advirtió que aplicará procedimientos administrativos y sanciones a quienes presten el servicio de transporte a través de la aplicación Uber en Pachuca. Aunque la plataforma comenzó a operar recientemente permitiendo solicitar viajes, la dependencia señaló que este esquema no está contemplado en la Ley de Movilidad y Transporte del estado, por lo que resulta ilegal al no contar con una concesión formal. Asimismo, la SEMOT indicó que se procederá con denuncias penales y multas a los operadores detectados, mientras que el gobernador señaló que cualquier cambio en la materia debe realizarse primero por la vía legislativa, con información de LSRH.</t>
-  </si>
-  <si>
-    <t>Entrevista en cabina a las doctoras Miriam Olvera Cuéllar y Alma Delia Vite Rojo, profesoras investigadoras de la Universidad Politécnica de Tulancingo, quienes presentaron los resultados de una investigación publicada recientemente en un capítulo de libro enfocado en la inteligencia artificial. El estudio, realizado en febrero y marzo de 2026 junto con la Red de Estudios Latinoamericanos de Internet mediante 548 encuestas válidas, analizó la percepción de distintos grupos etarios. Los hallazgos revelaron que los jóvenes de 18 a 26 años son quienes muestran mayor preocupación —especialmente en torno al reemplazo laboral y el uso cotidiano de la tecnología—, mientras que los adultos mayores presentan menor inquietud, pero requieren mayor capacitación digital. Asimismo, las investigadoras destacaron el respaldo institucional de la universidad y adelantaron que ya trabajan en nuevas líneas sobre el uso de la inteligencia artificial en la educación preescolar y media superior.</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Entrevista</t>
-  </si>
-  <si>
-    <t>Investigación académica</t>
-  </si>
-  <si>
-    <t>Durante su colaboración matutina, David Cárdenas informó sobre la comparecencia de Mónica Mixtega respecto a los trabajos de limpieza y trituración de lirio acuático para prevenir su proliferación, un tema prioritario para el estado de Hidalgo. Se destacó que, mediante el plan maestro de la Conagua implementado por el gobierno de la presidenta Claudia Sheinbaum, la superficie afectada por el lirio disminuyó de 900 a 443 hectáreas, respaldado por una inversión superior a los 33 millones de pesos para la adquisición de cuatro nuevas trituradoras. Asimismo, se mencionó la combinación de estrategias de control biológico y químico, cuidando el impacto en el agua para riego, y el fortalecimiento del equipo operativo en beneficio de la ciudadanía.</t>
-  </si>
-  <si>
-    <t>Ayer ocurrió un trágico accidente en la mina de San Juan Pachuca, donde murieron dos trabajadores por la caída de material. Según la Secretaría de Seguridad Pública, se recibió una llamada de emergencia informando que dos personas estaban atrapadas en la mina. Al llegar los equipos de rescate, encontraron los cuerpos de ambos trabajadores, uno de 25 años y el otro de 45 años. Ante esta situación, la Procuraduría General de Justicia ha comenzado una investigación del evento. Este accidente resalta la peligrosidad de trabajar en minas, como la histórica mina de San Juan Pachuca.</t>
-  </si>
-  <si>
-    <t>Accidente en mina</t>
-  </si>
-  <si>
-    <t>En la Feria San Francisco Pachuca 2026, dos funcionarios de la Secretaría de Educación Pública se pelearon al cierre del evento. La riña ocurrió el domingo por la noche en un bar, donde al parecer habían estado consumiendo alcohol. Aunque se desconoce quién inició la pelea, ambos decidieron resolver sus diferencias a golpes. Los videos del incidente y la prominencia de estos funcionarios, uno de los cuales es hermano del Subsecretario de Educación, han generado un gran revuelo en las redes sociales y los medios de comunicación. Sin embargo, hasta ahora no se ha informado si fueron detenidos o si enfrentarán alguna acción administrativa por su</t>
-  </si>
-  <si>
-    <t>Funcionario ebrio</t>
-  </si>
-  <si>
-    <t>SSPH/Bol.987/2026</t>
-  </si>
-  <si>
-    <t>Policía Estatal recupera tractocamión robado y detiene a un asaltante tras persecución en Emiliano Zapata</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>Emiliano Zapata</t>
-  </si>
-  <si>
-    <t>STPSH/TI.05/2026</t>
-  </si>
-  <si>
-    <t>Dos trabajadores de la mina de Loreto fallecieron luego de que una estructura y material cayeran sobre ellos y los aplastara, confirmaron autoridades del municipio de Pachuca. Autoridades confirmaron que en el accidente ocurrido durante la tarde del lunes 19 de octubre, los trabajadores quedaron atrapados bajo los escombros. Al sitio acudió personal de atención a emergencias para iniciar las labores de rescate de las personas; tras recuperar los cuerpos se realizó valoración de su estado físico, confirmando que ya no contaban con signos vitales. La Procuraduría General de Justicia del Estado de Hidalgo inició las investigaciones respectivas al caso, para conocer las circunstancias en las que se registró el accidente, así como las causas. Con ello se deslindarán las responsabilidades legales respectivas al caso. A su vez, la Secretaría del Trabajo y Previsión Social de Hidalgo dio a conocer que puso a su disposición, de manera gratuita, los servicios de asesoría y orientación de la Procuraduría Estatal de la Defensa del Trabajo, en caso de que requieran acompañamiento en materia laboral. La dependencia señala a través de un comunicado oficial que estableció comunicación con la representación en la entidad de la Secretaría del Trabajo y Previsión Social del Gobierno de México para atender el caso. La dependencia estatal señaló que, debido a las características del centro laboral y a las circunstancias del accidente, la atención del caso corresponde a las autoridades federales, conforme a las normativas legales vigentes. Se precisó que este apoyo busca brindar orientación a los familiares sobre los asuntos laborales que pudieran derivarse del accidente. Al tiempo, la dependencia estatal expresó su solidaridad con las familias de los trabajadores fallecidos ante el caso ocurrido en el inicio de esta semana.</t>
-  </si>
-  <si>
-    <t>El cuerpo de una persona fue localizado la tarde del domingo 18 de octubre en las inmediaciones de las minas del Cerro del Judío, en los límites de Pachuca y San Agustín Tlaxiaca. Vecinos de la zona reportaron a instituciones de seguridad pública respecto al hallazgo del cuerpo de una persona flotando en una zona con agua acumulada por las recientes lluvias, en las faldas del cerro. Al sitio acudieron elementos de Protección Civil de ambos municipios, Policía Estatal, Bomberos de Hidalgo y personal de la Comisión de Búsqueda de Personas del Estado de Hidalgo, realizando labores para el rescate del cuerpo. De manera preliminar, se señaló que el cuerpo podría corresponder a J.C.G.C., un joven de 27 años con domicilio en Santiago Tlapacoya y quien contaba con una ficha de búsqueda. Sin embargo, hasta el momento, las autoridades no han confirmado oficialmente su identidad, así como la causa del fallecimiento. Autoridades ministeriales han iniciado investigación respecto al caso, para establecer lo ocurrido, así como las responsabilidades legales respectivas.</t>
-  </si>
-  <si>
-    <t>CBPEH</t>
-  </si>
-  <si>
     <t>San Agustín Tlaxiaca</t>
   </si>
   <si>
-    <t>La plataforma Uber todavía no cuenta con autorización para prestar servicios de transporte en Pachuca, afirmó el gobernador de Hidalgo, Julio Menchaca Salazar. Advirtió que, si comienza a operar sin los permisos correspondientes, podría haber sanciones para quienes participen en la prestación de los viajes. En entrevista, el titular del Poder Ejecutivo del Estado de Hidalgo sostuvo que la legislación vigente aún no permite la operación de esta modalidad de transporte y señaló que, hasta el momento, la empresa no se ha acercado al gobierno estatal para dialogar sobre su posible incorporación. Menchaca Salazar indicó que las personas que decidan ofrecer viajes mediante la aplicación podrían enfrentar sanciones conforme a la ley. También mencionó posibles consecuencias legales por fraude, aunque precisó que corresponderá al Ministerio Público determinar si existe alguna conducta que deba investigarse. El gobernador reconoció que no descarta la posibilidad de ampliar las alternativas de movilidad para la población; sin embargo, reiteró que cualquier servicio deberá ajustarse a las disposiciones legales vigentes. Asimismo, hizo un llamado a quienes buscan obtener ingresos como conductores de la plataforma para que consideren las implicaciones de trabajar sin autorización. Añadió que el Gabinete de Seguridad definirá las acciones de supervisión para detectar la posible prestación de servicios mediante aplicaciones que no cuenten con los permisos correspondientes. Finalmente, Menchaca Salazar pidió evitar generalizaciones contra quienes trabajan en el transporte público y reconoció que existen operadores que cumplen con sus responsabilidades.</t>
-  </si>
-  <si>
-    <t>Hasta el momento, se ha finalizado 45 de las 213 obras de reconstrucción de infraestructura dañada por la vaguada monzónica registrada en octubre del año pasado en varios municipios del Estado de Hidalgo. El dato fue ofrecido por Alejandro Sánchez García, titular de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible en el Estado de Hidalgo (Sipdus), en el marco de su comparecencia ante legisladores del Congreso estatal, realizada este lunes 19 de octubre. La cifra de obras concretadas representa el 21 por ciento del total de las establecidas; el funcionario señaló que el avance total de dichas obras para resarcir los daños, alcanza el 58 por ciento. Las 45 obras concluidas contaron con una inversión global por 491 millones de pesos, mientras que otras 82 se encuentran en ejecución, con un monto asignado por 868 millones. Además, otras 55 obras están en proceso de contratación, por 454 millones; y 31 en validación, con inversión por 348 millones. En total, se contempla una inversión de 2 mil 164 millones de pesos para 213 obras a desarrollarse en los municipios con mayores afectaciones, producto de las torrenciales lluvias registradas en el mes de octubre del año pasado. En el caso del Estado de Hidalgo, la vaguada monzónica provocó 675 derrumbes y 158 deslaves en 28 de los 84 municipios de Hidalgo. Además, dejó incomunicadas 236 comunidades, dañó 50 puentes, inutilizó 190 sistemas de agua y drenaje y ocasionó el bloqueo de 359 caminos. Veracruz, San Luis Potosí y Querétaro, son otras entidades del país afectadas por las torrenciales lluvias registradas en octubre del año pasado. Cabe señalar que previamente la titular de la Secretaría de Hacienda en Hidalgo, Esther Ramírez Vargas, informó en su respectiva comparecencia que se tienen considerados dos mil 400 millones de pesos para atender la rehabilitación de infraestructura dañada por la vaguada del 2025.Consultar atlas Sobre la diferencia de 236 millones de pesos, el titular de la Sipdus, señaló que corresponde a obras a cargo del Instituto de Infraestructura Física Educativa y a infraestructura de agua potable reportada por los municipios. Por otra parte, el funcionario calificó como histórica la inversión de 25 mil millones de pesos destinada a infraestructura pública durante la administración. Entre los resultados, destacó el mejoramiento de 847 kilómetros de caminos rurales en 33 municipios y 118 localidades. Asimismo, indicó que, con una inversión superior a los 3 mil 46 millones de pesos, se atendieron vialidades urbanas en 71 municipios, con la construcción, ampliación y mejoramiento de más de 269 kilómetros de calles, avenidas, bulevares, guarniciones y banquetas. En materia de agua potable, informó una inversión de más de 5 mil 239 millones de pesos para construir y mejorar pozos, líneas de conducción y redes de distribución en 68 municipios, además, destacó 6 mil 616 millones de pesos para rescatar y modernizar 329 espacios públicos. Respecto al saneamiento, el secretario reportó la construcción de 37 plantas de tratamiento de aguas residuales en 20 municipios, lo que permitió alcanzar una cobertura estatal del 32 por ciento.</t>
-  </si>
-  <si>
-    <t>Abrimos con dos temas de seguridad pública esta mañana: eh el asunto ocurrido el día de ayer en Media Sierras y la cuestión la advertencia que hace la diputada Yarabi González en el caso de la Sierra Otomí-Tepehua y concretamente de Acaxochitlán. Y me parece muy pertinente compartir esta reflexión completísima, muy concreta respecto a los temas de seguridad. Señalan que en materia de seguridad la preocupación que hoy compartimos no es exclusiva de nuestro municipio, es una realidad que se vive a nivel estatal y nacional. Cuando la mayoría de los ciudadanos coincidimos en que la estrategia de seguridad no está funcionando, difícilmente podemos estar equivocados. Hace algunos meses el señor gobernador afirmó que Hidalgo era tan seguro que hasta los delincuentes venían a vivir aquí. -Que hacían operaciones, ¿eh? Recuerdo más o menos las declaraciones del gobernador que se parecían delicadas-. Con todo respeto, la realidad que vivimos día a día demuestra lo contrario. Lo que hemos visto en el crecimiento y el arraigo de la delincuencia en nuestro estado. Un problema que no solo obedece a una estrategia de seguridad insuficiente, sino también a la falta de empleo, de oportunidades y de un diagnóstico honesto de la realidad. Ante esto, es momento que como ciudadanos asumamos una postura activa, reflexiva y responsable. Hablamos de niños desaparecidos, de jóvenes y de trabajadores que no regresan a casa, de personas que pierden la vida en su propio centro de trabajo. Es evidente que la situación ha rebasado a las autoridades. Por ello es indispensable que actuemos como sociedad con unidad y exigencia, pero también con propuesta. Gracias, me parece importante y pertinente ante la realidad que estamos viviendo.</t>
-  </si>
-  <si>
-    <t>Estrategia de seguridad</t>
-  </si>
-  <si>
-    <t>Con la asistencia de aproximadamente mil supervisores, docentes, madres, padres de familia y personas tutoras de escuelas de educación básica de las 12 regiones de la entidad, el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, impartió la conferencia magistral "El papel de las madres, padres, personas y tutoras también con formación de las infancias". Durante este mensaje, el titular de la SEP Hidalgo destacó que desde el inicio de la administración del gobernador Julio Menchaca Salazar, la atención integral a la comunidad escolar ha sido una prioridad, esto como parte de estos esfuerzos y de hecho sí señaló también la creación de la Dirección General de Acompañamiento Socioemocional y Educativo, instancia pues concebida para brindar herramientas y estrategia también pues a las familias y también a las instituciones educativas que contribuyan al desarrollo integral de las y los estudiantes. Y pues en la conferencia en Actividad Castrejón abordó la importancia pues de atender las necesidades fundamentales de las niñas y los niños, entre ellas pues el afecto, el tiempo también de calidad, el acceso a información adecuada y también las condiciones materiales indispensables para el crecimiento digno. De hecho y así mismo hizo un llamado también a madres y a padres de familia para poder mantener una escuela activa con sus hijas, con sus hijos, acompañar, acompañarlos de manera cercana a las distintas etapas de su vida y permanecer también atentos pues a sus emociones y cambios de conducta. De hecho, subrayó que el entorno familiar constituye también la primera red de apoyo y aprendizaje para las niñas. Y pues en el encuentro estuvieron presentes el titular de la oficina de enlace educativo del Gobierno de México en Hidalgo, José Nereo Olguín Moreno, el subsecretario de educación media superior y superior Daniel Fragoso Torres, entre otros funcionarios también. Pero bien, de esa manera es como Natividad Castrejón destaca el papel de las familias en la formación de niñas y niños.</t>
-  </si>
-  <si>
-    <t>Daniel Martínez: Bueno, pues yo creo que tiene que ser una revisada de las estrategias en materia de prevención, sobre todo de prevención del delito y cuando sea necesario de atención. ¿Botón de muestra? ¿Qué tanto han funcionado los patrullajes, no? Con ese incremento de más del doble del registro de robo de vehículos automotores en Acaxochitlán, 130.3% de aumento entre el 2025 al comparativo de lo que va del presente 2026, 130%. Y la ubicación que señala con preocupación la diputada Yarabi González, la ubicación geográfica de Acaxochitlán que permite el paso de personas que están dedicadas a hechos delictivos, sobre todo provenientes de Cuautepec o hacia Cuautepec y provenientes del estado de Puebla o hacia el estado de Puebla. Bueno, estamos haciendo patrullajes. Bueno, creo que hay que revisar la estrategia de vigilancia y prevención del delito.</t>
-  </si>
-  <si>
-    <t>Acaxochitlán</t>
-  </si>
-  <si>
-    <t>Debido a su colindancia con el municipio de Cuautepec, así como con municipios del Estado de Puebla, Acaxochitlán enfrenta inseguridad, debido a que su ubicación geográfica es estratégica para grupos delincuenciales. Lo anterior fue planteado por Yarabi González Martínez, diputada por el distrito IX local, con cabecera en Metepec, durante la comparecencia, la semana pasada, de Salvador Cruz Neri, titular de la Secretaría de Seguridad Pública de Hidalgo (SSH). Señaló que de acuerdo con el Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP), este año Acaxochitlán registró 76 carpetas de investigación por robo de vehículo. La cantidad significa un aumento del 130.3 por ciento en este tipo de delito, en el comparativo con el año anterior. A ello se agregan 76 76 denuncias ante el Ministerio Público por violencia familiar y nueve más por narcomenudeo. Uno de los asuntos más graves que se registraron en la demarcación, ocurrió el pasado 20 de febrero de este año, cuando fueron localizados dos cuerpos sin vida en un camino que comunica con el Estado de Puebla. De acuerdo a reportes de la misma SSPH, las víctimas habrían fallecido fuera de Hidalgo y sus cadáveres fueron abandonados en ese sitio, recordó González Martínez. “También se detectaron 439 tomas de hidrocarburo en el municipio Cuautepec de Hinojosa y ha habido algunos enfrentamientos en comunidades de Acaxochitlán, como Santiago Tepepa”, refirió la legisladora del Congreso del Estado de Hidalgo. Dijo entender las dificultades que enfrentan las autoridades de los tres niveles de gobierno por ser una zona que registra marcada incidencia de delitos de alto impacto. Por lo que durante la comparecencia de Cruz Neri, le solicitó que citara las acciones específicas están implementado para reforzar su vigilancia, así como un análisis de las zonas dentro de Acaxochitlán con mayor incidencia delictiva. Al respecto, el mando policiaco estatal dijo que existe patrullaje constante dentro del municipio por parte de elementos de la SSPH, lo que se refleja en el aseguramiento de vehículos automotores, así como de madera sustraída por tala clandestina. “Los patrullajes que tenemos en los límites con esta entidad (Puebla) han funcionado, pero estamos pendientes para atender cualquier situación”, enfatizó Cruz Neri.</t>
-  </si>
-  <si>
-    <t>Daniel Martínez: comentan que qué onda este con gobierno del estado de Hidalgo, ¿qué es lo que está haciendo falta para que se permita la entrada de servicio de plataformas de transporte de pasajeros, sobre todo lo que se refiere a la modalidad taxis? Cito textual, "El lema del gobierno del estado es primero el pueblo, pero no permite que dicho pueblo elija en qué transportarse. Deben hacer una consulta para que los pobladores de Pachuca decidan si quieren o no los servicios de taxis de aplicación".</t>
-  </si>
-  <si>
-    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) expresó sus condolencias por el homicidio de un trabajador adscrito a la Subsecretaría de Servicios Regionales de Educación en Tulancingo, quien perdió la vida tras un ataque con arma de fuego registrado la mañana de este lunes, en el exterior de las oficinas de la dependencia. A través de un comunicado, la SEPH informó que brinda acompañamiento institucional a los familiares, amistades y compañeros de trabajo de la víctima, además de señalar que colabora con las autoridades competentes en las investigaciones correspondientes. De acuerdo con los reportes preliminares, el trabajador fue agredido a balazos en las inmediaciones del inmueble, ubicado en la colonia La Herradura. Tras el reporte de la agresión, elementos de seguridad y cuerpos de emergencia acudieron al lugar; sin embargo, la persona ya no contaba con signos vitales. Las autoridades ministeriales realizan las diligencias correspondientes para esclarecer los hechos e identificar a los responsables. Hasta el momento, no se han dado a conocer mayores detalles sobre el móvil del ataque.</t>
-  </si>
-  <si>
-    <t>Condolencias</t>
-  </si>
-  <si>
-    <t>El gobernador tiene un evento en Pachuca a la 1 de la tarde junto con Pemex hará entrega de equipamiento para fortalecer la infraestructura pública, esto se realizará en las instalaciones de la Comisión de Agua, Alcantarillado y Sistemas Intermunicipales (Caasim).</t>
-  </si>
-  <si>
-    <t>Infraestructura Hidráulica</t>
-  </si>
-  <si>
-    <t>En unos momentos más se llevarán a cabo las diferentes comparecencias por parte del secretario de Educación Pública, Natividad Castrejón. Esto será a las 10 de la mañana y horas más tarde el maestro Onésimo Serrano Rivera de la Secretaría de Planeación a las 4 de la tarde.</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1329/2026</t>
-  </si>
-  <si>
-    <t>Concluye sin incidentes Feria de San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>Reunión Gabinete De Seguridad</t>
-  </si>
-  <si>
-    <t>Radioescucha: "Aquí en Huejutla circulan varias unidades de taxis piratas autorizadas por el mismo coordinador del transporte, Omar. Se observan que usan las mismas placas en diferentes carros, lo que hacen poner es solamente una placa en cada carro". Andrés Torres comenta que lamentablemente es muy común que haya transporte público "pirata".</t>
-  </si>
-  <si>
-    <t>Transporte pirata</t>
-  </si>
-  <si>
-    <t>Andrés Torres en respuesta al radioescucha Lorenzo Cruz, quien señala que Uber ha llegado a Pachuca, pero sostiene que esto no es legal en el estado de Hidalgo y que como concesionarios de taxi ellos pagan impuestos. Andrés Torres responde que tiene razón, señalando que Uber no ha entrado a Pachuca, sino que han identificado algunos vehículos de Uber que estaban circulando. El gobernador Julio Menchaca declaró que no hay permisos o concesiones para Uber en el estado, y que los vehículos de esta plataforma serán sancionados. Según el gobernador y la Secretaría del Transporte, cualquier vehículo que preste servicio de Uber en Hidalgo será detenido y multado. Aunque algunos vehículos están circulando sin permiso, al ser ubicados, pueden enfrentar el decomiso del auto y multas. La declaración del gobernador es clara: Uber no está autorizado para operar en territorio hidalguense. Esto ha sido motivado por la aparición de vehículos de Uber en la zona, lo que llevó a la necesidad de una respuesta contundente del gobierno estatal. En resumen, Uber no tiene autorización para funcionar en Hidalgo y cualquier infracción será sancionada.</t>
-  </si>
-  <si>
-    <t>Fuera del aire de la Emisión de Vocales Radio, Andrés Torres emitió el siguiente comentario: El otro día vino aquí, dice que a grabar y no tiene ni idea ni dónde se prenden las cosas. Había que grabar un texto. No lo leo, yo lo leo. Somos locutores, no lectores. ¿No? Este, piensa que cualquiera puede pasar, ¿no? Este, no sabe impostar la voz, ¿no? No sabe hacer pausas, ¿no? ¿Aquí cuántas veces yo hago pausa y Aldo me se adelanta? Yo así estamos haciendo la pausa. No, pues no. No, no tiene ni idea, no, no tiene ni idea. No, no, ahorita yo Ese día mejor lo despaché, "Ay, mira, vete a chayotear para allá con la secretaria", "Mire, déjeme trabajar", ¿no? Pues es lo que hace, ¿no? Chayotear a todos los secretarios, despide a todos. E inmediatamente Napoleón me dijo, "Ya está" ¿No? Todos, a todos despide. ¿No? Se estaban quejando también los de Coespo, ¿no? Que no les este que no les quisieran hacer su programa de televisión, ¿no? ¿Qué les pidieron? Sí, imagínate. Es un tema bien interesante, chayotear dentro del gobierno, o sea, ¿eres parte del gobierno y chayotear dentro del gobierno? Así le hacía también Alan, Alan también les pedía. Una vez Natividad Castrejón nos dijo que le pidió 2,000 pesos, ¿ah? Aquí en entrevista, aquí en entrevista nos dijo, "Alan me pidió 2,000 pesos." Está grabado, güey, viendo el programa. Este señor le pidió que dos plazas, ¿no? A dos plazas a la Secretaría de Turismo, ¿no? Barrera le pidió dos plazas para sus hijos de para los hijos de sus directores. Napo también En la junta con el gobernador, lo único que pidió fue que su carro tuviera llanta de refacción porque su carro no tenía llanta de refacción. ¿Qué necesitas? Y ahí sí, no se fue, no se fue de gobierno ese día hasta que le dieron un vehículo. No fuera para trabajar, porque entonces ni se presenta, ¿no? No me voy hasta que me den mi vehículo con mi llanta de refacción. Qué lado, ¿no? Pero bueno, es lo que de verdad es lo que también uno dice, "Ahí está." Cuando dicen, "No puedes exigir." Pues, ¿qué puedes esperar? ¿Qué puedes esperar de alguien que siempre se ha dedicado a engañar? ¿No? El tipo no sabe nada de medios de comunicación, es evidente, ¿no? Como ya no puede ir al área académica, porque está vetado en todas las escuelas por acosador sexual. Fue expulsado de las áreas por acosador sexual, todos los maestros te lo dicen. En la universidad también salió por acoso sexual. En todas las escuelas ha tenido problemas, en todas las escuelas donde va a pedir pidió trabajo en el Tec de Monterrey también ya me lo confirmaron. Ni siquiera lo recibieron. ¿No? Entonces, al verse vetado de la del mundo académico, pues se tuvo que meter a hacer TikToks, ¿no? Y luego ya se dijo periodista.</t>
-  </si>
-  <si>
-    <t>La Voz de la Sierra Gorda en Jacala de Ledezma sigue fuera del aire en la frecuencia 91.1, y no hay soluciones a la vista. La administración enfrenta problemas financieros, no pueden manejar 10 millones de pesos y les han devuelto documentación para justificar gastos. No les cuadran las cuentas a pesar de que falsifican facturas, documentos y firmas. De hecho, se perdieron más de 14 millones de pesos, que fueron autorizados por el Congreso en 2026 para instalar dos nuevas estaciones de radio, una en Pachuca y otra en Tenango de Doria. Este dinero está en el aire y se desconoce su paradero. Aunque estaba presupuestado y aprobado, nadie sabe si se devolvió o se ejerció. Esto impide la apertura de las estaciones programadas para 2026. Andrés Torres asevera que tendrían que comparecer los responsables de estos temas, por ejemplo, porque también en los temas de comunicación se gasta muchísimo, muchísimo dinero y nadie da razón de ello. "En lugar de pedir vales de gasolina, lugares de estacionamiento, hagan fiestas para festejarse entre ellos y festinarse sus burradas, mejor se pongan a trabajar, ¿no? Mejor aprendan cuáles son los lineamientos eh oficiales del gobierno del estado de los diferentes programas que maneja la Secretaría de Hacienda, la Unidad de Planeación y Prospectiva, la propia Secretaría de Gobierno, ni qué decir de por ejemplo otras áreas como la Oficialía Mayor porque todas en todas están reprobados. Y bueno pues mejor en lugar de estarle haciendo al canelas, ¿no?, en lugar de torcer la boca y estar enojados y levantar actas de abandono de empleo y abrir y levantar este todos los días falsos en contra de los trabajadores, ¿no? Porque ya no pueden de demandas, eso sí, ¿eh? Ya tienen muchas demandas ante la Procuraduría General de Justicia del Estado de Hidalgo, ¿no? Ya no es ya no es nada más demandas laborales, ya son demandas que van a otro tipo de nivel. Pero ellos siguen diciendo que los de radio somos los malos."</t>
-  </si>
-  <si>
-    <t>Subejercicio</t>
-  </si>
-  <si>
-    <t>Nos preguntaron sobre la estación de radio en Tula. En noviembre de 2022, cerraron 11 estaciones del Sistema Estatal de Radio, incluida la de Tula. No hay planes ni intención de recuperar las transmisiones o contratar una licencia para esa región. Es una pena, pero este problema es resultado de las decisiones de administraciones pasadas que ignoraron las necesidades de las estaciones de radio, lo que llevó a perder las concesiones.</t>
-  </si>
-  <si>
-    <t>SEMOTH procederá conforme a derecho ante la operación de transporte sin autorización en Hidalgo</t>
-  </si>
-  <si>
-    <t>El gobernador fue cuestionado por la prensa sobre los autos de alquiler, conocidos como Uber. Mencionó que hay una invasión de vehículos de esta plataforma en el estado. El gobernador afirmó que estos vehículos no cuentan con permisos y están operando fuera de la ley. También indicó que, por esta razón, podrían ser sancionados. La Secretaría de Transporte emitió un boletín sobre este tema.</t>
-  </si>
-  <si>
-    <t>Ayer, temprano en la mañana, un funcionario de la Secretaría de Educación Pública en Tulancingo fue asesinado a tiros por una persona que se acercó mientras viajaba en bicicleta. El incidente ocurrió en las instalaciones de la SEPH, donde el agresor disparó al menos dos veces, causando la muerte del funcionario. La Secretaría emitió un comunicado confirmando lo sucedido y aclarando que las autoridades de la Procuraduría General de Justicia y de Seguridad Pública son responsables de investigar el caso. El funcionario tenía 67 años. Después del ataque, el presunto homicida huyó en bicicleta, lo que llevó a las autoridades a implementar un operativo de búsqueda, pero hasta el momento no han logrado localizarlo. Se informó que el agresor se dirigió hacia una comunidad cercana, Medias Tierras, en Cuautepec. Pese a los esfuerzos de los efectivos de seguridad, no se ha encontrado al sospechoso. Este trágico hecho fue notificado poco después de que terminara el programa Las Vocales Radio. La comunidad se encuentra conmocionada por el asesinato del funcionario en un espacio tan público y se espera que las investigaciones avancen para dar con el responsable.</t>
-  </si>
-  <si>
-    <t>Hay una campaña de vacunación invernal que comenzó el pasado lunes, patrocinada por la Secretaría de Salud del estado. Se dispone de más de 1,500,000 dosis gratuitas. Los grupos prioritarios son niños menores de 5 años, adultos mayores y personas con enfermedades crónico-degenerativas. Sin embargo, se recomienda que todas las personas se vacunen, ya sea contra el COVID o contra la influenza estacional.</t>
-  </si>
-  <si>
     <t>Vacunación</t>
   </si>
   <si>
-    <t>La Subsecretaría de Protección Civil del Gobierno del Estado de Hidalgo ha confirmado que las lluvias continuarán en el este del estado, especialmente en la región Otomí-Tepehua y en la Sierra, incluyendo San Bartolo Tutotepec y Tenango de Doria. También se espera un descenso importante de temperaturas en la mayoría del estado, con registros de hasta 4 grados en algunas áreas, y entre 6 y 8 grados en Pachuca esta mañana. Se recomienda a la población abrigarse bien y prepararse, ya que este descenso de temperaturas continuara hasta febrero. Actualmente, se están sintiendo los efectos del segundo frente frío que afecta al país, lo que ha llevado a una marcada disminución de la temperatura. La Subsecretaría de Protección Civil, informa sobre el pronóstico para el 20 de octubre de 2026. Se esperan chubascos de 5 a 25 mm, sobre todo en el este de Hidalgo, con temperaturas entre 0 y 5 grados. También se pronostican vientos de 10 a 20 km por hora, con rachas de 30 a 50 km por hora.</t>
+    <t>Andrés Tores respecto a la marcha de la UAEH, comentó: Si viene en transporte público también planteé que pudiera haber cortes en el Tuzobús, en las corridas del Tuzobús. Hasta el momento la Secretaría del Transporte no nos ha confirmado que vaya a haber algún cambio en las corridas del Tuzobús. Seguramente al momento que avance la marcha, seguramente sí habrá suspensión en las corridas del Tuzobús.</t>
+  </si>
+  <si>
+    <t>Sitmah</t>
+  </si>
+  <si>
+    <t>Recorte Operativo</t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>Si viene en transporte público también planteé que pudiera haber cortes en el Tuzobús, en las corridas del Tuzobús. Hasta el momento la Secretaría del Transporte no nos ha confirmado que vaya a haber algún cambio en las corridas del Tuzobús. Seguramente al momento que avance la marcha, seguramente sí habrá suspensión en las corridas del Tuzobús.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yDN7uNOPGwz59xLlvMfuLHZ0CBCJRPKv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Segundos</t>
+  </si>
+  <si>
+    <t>Andrés Torres en respuesta a un radioescucha que comenta: "Ojalá arreglen la estación de radio, hace mucha falta". Andrés Torres responde que el director de Radio y Televisión "no conoce la sierra, pregúntale para dónde es la sierra. Pero si no conoce la tiene, no conoce el estado, obviamente, no quiere conocer el estado, ¿no? Ni las instalaciones de Radio y Televisión de Hidalgo, ¿no? Ya tiene qué ¿cuántos meses? Bueno, por favor, es un asunto ya que se desborda por todos lados, sí."</t>
+  </si>
+  <si>
+    <t>Negativo</t>
+  </si>
+  <si>
+    <t>Otro ejemplo rápidamente, Luis Manuel nos escribe, dice, buen día, saludos del corazón de la Sierra, amanecemos con lluvia, otro problema con la lluvia, ojalá... -No conoce la sierra, pregúntale para dónde es la Sierra-. Y dice, ojalá arregle la estación de radio, hace mucha falta. -Pero si no conoce la sierra, no conoce el Estado, obviamente no quiere conocer el Estado, ¿no? Ni siquiera las instalaciones de radio venido, ¿no? Ya tiene que... ¿Cuántos meses? ¿No? Por favor, es un asunto ya que se desborda por todos lados-.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14w1EerUFxyHxnm6oqec89CCWL_r8ECwt/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Andrés Torres menciona que están recibiendo y compartiendo fotos en redes sociales sobre la marcha de la UAEH, y, "aunque se enoje el tiranito [risas], ¿no?, el tiranito local, este porque es información que nos ayuda a todos". Asimismo, señala: "es que la verdad te puede, a mí me dan ganas de llorar que tenemos una persona ignorante, prepotente, por supuesto, un acosador [risas], ¿no?, confirmado, certificado, que, pues no encuentra la manera de obstaculizar, de por supuesto, atacar y siempre, siempre, siempre estar este acosando a los trabajadores de Radio y Televisión de Hidalgo, porque lo que le queda es trabajar [risas], ¿no? Siempre, siempre este difamando, siempre mintiendo [risas], ¿no? Nosotros no nos manejamos de esa manera [risas], ¿no? Ayer yo platicaba sobre sus antecedentes penales [risas], ¿no?, que por cierto tiene varios y que pues resulta que pues nunca los puso en su currículum, ¿no? No los no los reportaba, así que, bueno, pues cada quien cada quien sabrá. Aldo Falcón por su parte destaca el impacto positivo que las personas en distintos municipios, como desde la Huasteca hasta la capital de Hidalgo, agradecen por ayudar a resolver problemas como una fuga de agua. También destacan que algunos no tienen acceso a la estación de radio. Se preguntan cómo se puede llegar a toda la gente, ya que no todo se puede hacer a través de la radio, especialmente con el avance de la tecnología. Andrés responde que: "Aquí el problema es, si no dotas, si tú, por ejemplo, dices, "No quiero que tengan redes sociales", como nos dijeron ayer nuestra dirección general. Entonces, dátanos, dótanos de redes sociales, saben que no tenemos intranet, aben que el decreto para entregar a Radio y Televisión de Hidalgo cinco concesiones de radio en Tlanchinol, Huejutla, Atlapexco, Huichapan y Jacala, obliga a Radio y Televisión de Hidalgo a transmitir en internet. Si no cumplimos con ese precepto, es posible que se nos retiren nuevamente las concesiones. Pero eso no se trabaja, eso no es importante. Lo importante es por qué Las Vocales Radio y Andrés Torres están trabajando [risas], ¿no? ¿Por qué lo ven a él? ¿Por qué le escriben a él? ¿Por qué la por qué no me escriben a mí? ¿Por qué no? Pues no te hablan y no te escriben a ti porque no eres nadie [risas], así de simple, porque en temas informativos no eres nadie, ¿no? Y entonces, pues por eso, simple y llanamente, pues quieres [risas], ¿no?, pero perjudicar, acosar, difamar, hostigar todo el tiempo. Me llama también muchísimo la atención que nadie hace nada. Que nadie hace nada, no, yo sí, yo sí levanto la voz, yo sí me digo, yo sí este denuncio, porque pues yo no voy a permitir que una persona que además es un neófito, es un total y pleno ignorante en temas de comunicación, en temas informativos, en temas, por supuesto, periodísticos, pues quiera este incidir en algo que además ni es su dinero, ay, porque dice que es dinero público. Mentira, estamos utilizando nuestro propio dinero, estamos metiendo dinero de nuestra bolsa para poder cumplir con este precepto de informar que estamos obligados a hacerlo, ¿no?". Aldo está de acuerdo con lo que Andrés dice. Andrés concluye que es necesario seguir trabajando, a pesar de las dificultades y las críticas que enfrentan.</t>
+  </si>
+  <si>
+    <t>Hostigamiento Laboral</t>
+  </si>
+  <si>
+    <t>Andrés Torres: Nos están mandando fotos, ahorita las vamos a compartir en nuestras redes sociales, aunque se enoje el tiranito [risas], ¿no?, el tiranito local, este porque es información que nos ayuda a todos. No te debe dar risa, no, no, es que la verdad te puede, a mí me dan ganas de llorar que tenemos una persona ignorante, prepotente, por supuesto, un acosador [risas], ¿no?, confirmado, certificado, que pues no encuentra la manera de obstaculizar, de por supuesto, atacar y siempre, siempre, siempre estar este acosando a los trabajadores de Radio y Televisión de Hidalgo, porque lo que le queda es trabajar [risas], ¿no? Siempre, siempre este difamando, siempre mintiendo [risas], ¿no? Nosotros no nos manejamos de esa manera [risas], ¿no? Ayer yo platicaba sobre sus antecedentes penales [risas], ¿no?, que por cierto tiene varios y que pues resulta que pues nunca los puso en su currículum, ¿no? No los no los reportaba, así que, bueno, pues cada quien cada quien sabrá. Acuérdate, Aldo. **Aldo Falcón:** Disculpa, Andrés, que te interrumpa, pero a ver, este, se hace, no sé, ya ni con el término, pero por ejemplo, muchas personas si se ven a través de nuestros comentarios, ninguno son inventados, todos los mensajes los estamos leyendo, mucha gente que nos comenta desde la Huasteca, la capital hidalguense, Mineral de la Reforma, todas las áreas, donde nos preguntan problemas que tienen. Ayer una persona nos agradecía por un problema que tuvo una fuga de agua, el cual dijo: "Muchas gracias, gracias, ustedes pudieron resolver este problema". Algunas personas, "No tengo radio, ¿cómo comunicarme con ustedes? No, no llega la estación hasta acá". En Pachuca, ahorita, por ejemplo, estamos este bloqueo, el cual dicen, "Pues es que cómo yo no sabía de este bloqueo, gracias a ustedes estoy informado". Pero por medio de redes sociales, ahora que también nos dicen, "No, tampoco pueden hacerlo", entonces, ¿cómo llegas a toda esta gente? No todo no todo relativamente se puede hacer de a través por radio, lamentablemente ya muchas veces te alcanza la tecnología. **Andrés Torres:** Aquí el problema es, si no dotas, si tú, por ejemplo, dices, "No quiero que tengan redes sociales", como nos dijeron ayer nuestra dirección general. Entonces, dátanos, dótanos de redes sociales, saben que no tenemos intranet, saben que el decreto para entregar a Radio y Televisión de Hidalgo cinco concesiones de radio en Tlanchinol, Huejutla, Atlapexco, Huichapan y Jacala, obliga a Radio y Televisión de Hidalgo a transmitir en internet. Si no cumplimos con ese precepto, es posible que se nos retiren nuevamente las concesiones. Pero eso no se trabaja, eso no es importante. Lo importante es por qué Las Vocales Radio y Andrés Torres están trabajando [risas], ¿no? ¿Por qué lo ven a él? ¿Por qué le escriben a él? ¿Por qué la por qué no me escriben a mí? ¿Por qué no? Pues no te hablan y no te escriben a ti porque no eres nadie [risas], así de simple, porque en temas informativos no eres nadie, ¿no? Y entonces, pues por eso, simple y llanamente, pues quieres [risas], ¿no?, pero perjudicar, acosar, difamar, hostigar todo el tiempo. Me llama también muchísimo la atención que nadie hace nada. Que nadie hace nada, no, yo sí, yo sí levanto la voz, yo sí me digo, yo sí este denuncio, porque pues yo no voy a permitir que una persona que además es un neófito, es un total y pleno ignorante en temas de comunicación, en temas informativos, en temas, por supuesto, periodísticos, pues quiera este incidir en algo que además ni es su dinero, ay, porque dice que es dinero público. Mentira, estamos utilizando nuestro propio dinero, estamos metiendo dinero de nuestra bolsa para poder cumplir con este precepto de informar que estamos obligados a hacerlo, ¿no? **Andrés Torres:** Pero bueno, pues mira, yo te repito, también hay que dedicarle mucho tiempo [risas], ¿no? Porque así chiquito, como es chiquito, como debe estar todo negro.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1N6AgN7ZoJ24oc4z1eJIi0epoE-aMfj0L/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El cuerpo sin vida de una persona en avanzado estado de descomposición fue localizado esta tarde por vecinos de la comunidad de Palmillas, en el municipio de Mixquiahuala. El hallazgo movilizó a elementos de la Policía Municipal y de Protección Civil, quienes acudieron al lugar y confirmaron la presencia del cadáver en las aguas del canal. Los hechos fueron notificados al Ministerio Público, que ordenó el rescate de los restos humanos y las diligencias correspondientes para su levantamiento y traslado al Servicio Médico Forense, donde se realizarán los estudios necesarios para determinar el género y la identidad de la persona. Hasta el momento no se tienen mayores datos para determinar precisamente la identidad de la persona localizada sin vida.</t>
+  </si>
+  <si>
+    <t>Localización De Restos</t>
+  </si>
+  <si>
+    <t>Mixquiahuala</t>
+  </si>
+  <si>
+    <t>Por otra parte, en Mixquiahuala se localizó también un cuerpo sin vida, en este caso un avanzado estado de descomposición. Esto sucedió en la comunidad de Palmillas. El hallazgo movilizó a elementos de la Policía Municipal y de Protección Civil, quienes acudieron al lugar y confirmaron la presencia del cuerpo sin vida en las aguas del canal. Los hechos fueron notificados al Ministerio Público, que ordenó el rescate de los restos humanos y las diligencias correspondientes para su levantamiento y traslado al Servicio Médico Forense, donde se realizarán los estudios necesarios para determinar el género y la identidad de la persona. Hasta el momento no se tienen mayores datos para determinar precisamente la identidad de la persona localizada sin vida.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YMVgauZHpVh9tBoa9wF-oc9F5aWKbtSv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Ultra Noticias</t>
+  </si>
+  <si>
+    <t>El cuerpo sin vida de un hombre, con varios impactos de arma de fuego, fue localizado en un canal de agua para riego ubicado en el municipio de Tezontepec de Aldama. De acuerdo con los primeros reportes, la víctima, que permanece en calidad de desconocida, presentaba heridas en las extremidades inferiores y en el abdomen, presuntamente ocasionadas por proyectiles de arma de fuego. El hallazgo se registró en un paraje ubicado en los límites de las comunidades de Huitel y Achichilco, donde elementos de las policías municipal y estatal acudieron tras recibir el reporte. Personal de la Procuraduría General de Justicia del Estado de Hidalgo inició las investigaciones respectivas al caso para determinar las responsabilidades legales correspondientes.</t>
+  </si>
+  <si>
+    <t>El cuerpo sin vida de un hombre con varios impactos de arma de fuego fue localizado en el canal de agua de riego, ubicado en el municipio de Tezontepec de Aldama. De acuerdo con los primeros reportes, la víctima, que permanece en calidad de desconocida, presentaba heridas en extremidades inferiores y en el abdomen, presuntamente ocasionados por proyectiles de arma de fuego. Y bien, el hallazgo se registró en un paraje ubicado en los límites de las comunidades de Huitel y Achichilco, donde elementos de la policía municipal y estatal acudieron tras recibir el reporte. El personal de la Procuraduría General de Justicia del Estado de Hidalgo inició las investigaciones respectivas al caso para poder determinar las responsabilidades legales correspondientes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RSNmGtB2q5ZQt0l_AUI7gTYvhw4W1MCg/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El hallazgo de un hombre sin vida movilizó este martes a corporaciones de seguridad y personal ministerial en la comunidad de Santa Catarina, en el municipio de San Agustín Tlaxiaca. El cuerpo fue localizado en un camino de terracería y, de acuerdo con los primeros reportes, presentaba aparentes signos de violencia. La identidad de la víctima no había sido establecida hasta el momento de los primeros informes. Tras el hallazgo, elementos de seguridad acordonaron el área para facilitar las diligencias periciales. Personal de la Procuraduría General de Justicia del Estado de Hidalgo realizó las actuaciones correspondientes y el traslado del cuerpo al Servicio Médico Forense. Las autoridades iniciaron las investigaciones para determinar las circunstancias de la muerte y esclarecer los hechos.</t>
+  </si>
+  <si>
+    <t>El hallazgo de un hombre sin vida movilizó este martes a corporaciones de seguridad y personal ministerial en la comunidad de Santa Catarina, en el municipio de San Agustín Tlaxiaca. De hecho, el cuerpo fue localizado en un camino de terracería y, de acuerdo con los primeros reportes, presentaba aparentes signos de violencia. La identidad de la víctima no había sido establecida hasta el momento en los primeros informes y, tras este hallazgo, elementos de seguridad acordonaron el área para poder facilitar las diligencias periciales. personal de la Procuraduría General de Justicia del Estado de Hidalgo, realizó las actuaciones también correspondientes y el traslado del cuerpo al Servicio Médico Forense. Las autoridades iniciaron las investigaciones para poder determinar las circunstancias de la muerte y esclarecer los hechos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1P5txQRw7rxbXTMf98w_k5HJwexq25SLj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha: Las plataformas digitales de transporte son necesarias en Hidalgo, ya que funcionan en la Ciudad de México, Estado de México, Guadalajara y Monterrey, permitiendo que el usuario pague y merezca un mejor servicio, precio justo, seguridad, atención y unidades dignas. La competencia no obligará a tener un mejor transporte público, y existe un amparo que permite a Uber operar, siendo un servicio solicitado por más del 80% de los hidalguenses. Bajo la premisa de que "el pueblo es primero", es momento de escuchar a la ciudadanía, ya que las plataformas no solo representan un mejor servicio, sino también empleo e ingresos para los hidalguenses.</t>
+  </si>
+  <si>
+    <t>Las plataformas digitales de transporte son necesarias en Hidalgo. No es casualidad que funcionen en la Ciudad de México, en el Estado de México, Guadalajara y Monterrey. El usuario paga y merece un mejor servicio, precio justo, seguridad, atención y unidades dignas. La competencia nos obligará a tener un mejor transporte público. Existe un amparo que permite a Uber operar y más del 80% de los hidalguenses piden este servicio. Yo no sé. Si nos dice dónde está la encuesta o la estadística, porfa. Insisto, no defiendo a nadie. Si el lema es primero el pueblo, es momento de escuchar al pueblo. Las plataformas no solo son mejor servicio, son empleo e ingresos para los hidalguenses.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZzRDMC2CXuhqbtDfgWeuIf3DxMZxww0t/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Anda buscando el Gobierno del Estado de Hidalgo un terreno donde se pueda hacer construcción de vivienda del bienestar, uno de los programas estrella del gobierno federal, porque resulta que el que tenía considerado en Ixmiquilpan pues tiene pues problemas ahí de tenencia, esto para la construcción de 750 viviendas y esto lo declaró el secretario de Gobierno del Estado de Hidalgo, Guillermo Olivares Reyna, recordando que se había previsto inicialmente hacer la construcción en la comunidad del Valante en Ixmiquilpan, pero ahí tiene, le insisto, este problemas agrarios. En este sentido, como parte de la glosa del cuarto informe de gobierno del mandatario Julio Menchaca Salazar, tras el cuestionamiento de la diputada Cynthia Citlali Delgado Mendoza sobre este tema, Olivares Reyna explicó que el conflicto ha dificultado el avance del proyecto y añadiendo que incluso se ofreció asesoría jurídica para regularizar el predio original, pero al considerar que el proceso podría prolongarse, decidieron buscar un nuevo predio. Las Casas del Bienestar, dijo, reclaman celeridad, que se arranca en cuanto antes y es por eso que se decidió buscar un nuevo predio. Como alternativa indicó que se ofreció un terreno en donación donde podrían construirse las viviendas, siempre y cuando cumplan con los requisitos legales y técnicos. Mencionó que se trabajan los aspectos relacionados con un pozo de agua y una planta de tratamiento para hacer viable este proyecto. De acuerdo con los antecedentes del conflicto, la disputa por la tenencia de la tierra se prolonga desde hace 80 años, entonces pues que es muy complicado de que puedan utilizar el espacio que se tenía considerado originalmente en el Valante en Ixmiquilpan, pues porque no pueden usarlo porque hay un problema de tenencia legal en ese en ese espacio. Bueno, este de hecho hay versiones periodísticas que afirman que cuando el personal relacionado con el proyecto intentó descargar material para construir los cimientos de las viviendas, habitantes de la zona pues de plano se los se los impidieron y les dijeron "no, aquí no pueden descargar.</t>
+  </si>
+  <si>
+    <t>Plan Nacional De Vivienda</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TRv0I3miksBufVCVUuB3qJMlsuZCHLNA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Cynthia Citlali Delgado Mendoza</t>
+  </si>
+  <si>
+    <t>Radioescucha: Una colectiva de la Ruta Indeco Aldama pasó 10.38 de la mañana ayer, ocurrió un acto de discriminación hacia un adolescente con discapacidad, iban a subirla y se arrancó.</t>
+  </si>
+  <si>
+    <t>Una colectiva de la Ruta Indeco Aldama pasó 10.38 de la mañana ayer, ocurrió un acto de discriminación hacia un adolescente con discapacidad, iban a subirla y se arrancó.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1g8kBmIL_zu7X6gmD9Exo9hJWgUo3YYWV/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Daniel Mertínez: Insisto, Hidalgo, ella es de los pocos estados del país que no cuentan con estos servicios. Sean buenos o sean malos, pues ahora sí que la experiencia de cada quien, pero es increíble que no formemos parte de ese concierto tecnológico actual ya. Y es gusto en saludarte y bueno, le decía a Isa fuera del aire hace ratito, pónganse de acuerdo, por una parte el gobernador dice que estamos preparando denuncias, por otra parte el presidente de la Juanta de Gobierno dice, bueno, vamos a revisar el tema y a lo mejor lo legislamos.</t>
+  </si>
+  <si>
+    <t>Insisto, Hidalgo, ella es de los pocos estados del país que no cuentan con estos servicios. Sean buenos o sean malos, pues ahora sí que la experiencia de cada quien, pero es increíble que no formemos parte de ese concierto tecnológico actual ya. Y es gusto en saludarte y bueno, le decía a Isa fuera del aire hace ratito, pónganse de acuerdo, por una parte el gobernador dice que estamos preparando denuncias, por otra parte el presidente de la Juanta de Gobierno dice, bueno, vamos a revisar el tema y a lo mejor lo legislamos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1juFbHR6zbh9bbXSQlrbzOD0C9Xc9bCh_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso</t>
+  </si>
+  <si>
+    <t>Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Andrés Velázquez Vázquez</t>
+  </si>
+  <si>
+    <t>Radioescucha: se dice primero el pueblo, pues el pueblo no viaja en helicóptero o vehículo particular, nuestros políticos no usan taxi, o sea, no sufren servicio de transporte público. ¿Por qué no hacen sus clásicas encuestas al pueblo sobre lo que les conviene para ellos?</t>
+  </si>
+  <si>
+    <t>Por acá nos están compartiendo un punto de vista. Hablando de servicios de plataforma, se dice primero el pueblo, pues el pueblo no viaja en helicóptero o vehículo particular, nuestros políticos no usan taxi, o sea, no sufren servicio de transporte público. ¿Por qué no hacen sus clásicas encuestas al pueblo? Solo lo que les conviene para ellos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NOWim0QYeESCn6KaIsRprndlURNSt4Y1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Semot/TI.79/2026</t>
+  </si>
+  <si>
+    <t>Daniel Martínez: Y veo en la tarjeta informativa que envía Movilidad y transporte del Estado de Hidalgo, digo, no le toca esa chamba, pero sí informar qué es lo que pasó, que no hay ninguna información acerca de si hay alguna persona detenida como presunto responsable del intento de robo que denunció el taxista. El taxista registrado adecuadamente, el taxista tiene su licencia y está registrado adecuadamente, pero ni una palabra, si detuvieron a la persona que presuntamente intentó el asalto. ni una palabra en la tarjeta informativa bueno, 9.53 más temas de seguridad pública</t>
+  </si>
+  <si>
+    <t>Accidente transporte público</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yhqLwrQjB6XzaqWOzG1qpSRRa8_TnzmG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El operador de un taxi terminó impactándose contra un poste, presuntamente al resistirse a un asalto por parte de un pasajero que viajaba en dicha unidad de transporte individual. La situación se registró en la carretera Pachuca-Actopan, a la altura del puente del Barrio del Judío, resultando dos personas lesionadas durante la situación. Se conoció que uno de los pasajeros del taxi habría intentado asaltar al conductor y, durante el forcejeo, lo lesionó en una mano y en el rostro. Ante esta situación, el operador de la unidad perdió el control del vehículo y se impactó contra un poste, el cual cayó y provocó que un motociclista derrapara. Elementos de Seguridad Pública, Tránsito y Protección Civil de San Agustín Tlaxiaca acudieron al lugar para atender la emergencia y brindar atención a los involucrados. El saldo fue de dos personas lesionadas: el conductor del taxi y el motociclista, quienes fueron valorados por paramédicos y presentaron policontusiones, sin lesiones de gravedad. La Secretaría de Movilidad y Transporte en Hidalgo (Semoth), dio a conocer a través del Sistema de Transporte Convencional de Hidalgo (STCH), informó que dio seguimiento al caso y confirmó que el operador contaba con licencia vigente y que la unidad tenía su documentación en regla.</t>
+  </si>
+  <si>
+    <t>Asalto a transporte público</t>
+  </si>
+  <si>
+    <t>Ayer se reportó eh un accidente ocurrido en eh sobre la carretera Pachuca-Actopan a la altura del puente del barrio El Judío, ya dentro de San Agustín Tlaxiaca. Eh una un taxi se fue contra un poste y derivado del poste, pues se había pasado un motociclista que derrapó y que quedó lesionado igual que que el taxista. Dirías que es un accidente más, un desafortunado eh este accidente más. Pero resulta que al platicar con el taxista, este les comenta a los oficiales de seguridad pública que le intentaron asaltar, que subió un pasajero, que lo lo amagó este y comenzaron a forcejear, obviamente para tratar de evitar el asalto y en el forcejeo perdió el control del vehículo, se terminó estampando contra el poste. Eh afortunadamente el asunto quedó en en policonsusiones, tanto para el motociclista como para el taxista.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1s5sXifN-B9-y569ok0o3pjbM0JhzJKmE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1934/2026</t>
+  </si>
+  <si>
+    <t>Capacita SEPH a supervisores escolares en acompañamiento pedagógico</t>
+  </si>
+  <si>
+    <t>MEJORA EDUCATIVA</t>
+  </si>
+  <si>
+    <t>Izza Hernández: La Secretaría de Educación Pública del Estado de Hidalgo realizó el curso en la función supervisora para la transformación y la mejora continua. De hecho, todo esto enfocado a fortalecer el acompañamiento pedagógico y las prácticas también de supervisión en las escuelas de la entidad. En representación del secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, la subsecretaria de Educación Básica, Nancy Adriana León Vite, participó en el inicio del curso, donde pues destacó que la supervisión escolar es fundamental para poder orientar el trabajo de las comunidades educativas desde una perspectiva de liderazgo pedagógico y también en concordancia con los principios de la Nueva Escuela Mexicana. Y pues el curso aborda temas relacionados con las bases normativas de la función supervisora, el diagnóstico socioeducativo también, la mejora continua y también el acompañamiento pedagógico con el objetivo de fortalecer el trabajo colaborativo pues entre supervisores, directivos y docentes. La capacitación está buscando fortalecer las competencias de las figuras supervisoras para poder atender las necesidades educativas, brindar acompañamiento técnico pedagógico y también administrativo e inmediata de alguna forma también en conflictos y contribuir a la gestión escolar. Asimismo, reconoció el trabajo de la directora general de Desarrollo Curricular, hablamos de María del Rosario Ramírez Hernández, por la organización de este encuentro en conjunto con los centros de maestros, así como también la labor de la directora de Formación Continua, María de Lourdes Reyes Pérez, y también el director de Investigación Educativa, Óscar Monter Fuentes, en el desarrollo de acciones formativas dirigidas a las figuras educativas. Y pues en esta reunión de hecho participó también la directora general técnica de la SEPH, Leiza Aida Fernández Vega, también la titular de la unidad de gestión técnica, estamos hablando de Claudia Huerta Ruiz, y el director de evaluación e información educativa, Mario Covarrubias López. De esta manera es como se su sede esta capacitación por parte de la SEPH y bueno, directamente a los supervisores escolares en acompañamiento pedagógico.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pM1xobEFg8u_IalqI89AvDhjEHpyluAk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Comunicado gubernamental</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón, María del Rosario Ramírez Hernández, Leyza Aída Fernández Vega, Claudia Huerta Ruíz, Mario Covarrubias López, María de Lourdes Reyes Pérez, Oscar Monter Fuentes</t>
+  </si>
+  <si>
+    <t>El relleno sanitario del Huixmi, que está ubicado en Pachuca, y es que contaría con una vida útil estimada de alrededor de 2 años, uno por cada celda de disposición de residuos. Esto lo informó Mónica Patricia Mixtega Trejo, la titular de la Secretaría de Medio Ambiente y Recursos Naturales del Estado de Hidalgo, durante su comparecencia ante el Congreso local el día 19 de octubre. La funcionaria explicó que en este espacio operan dos empresas particulares: Consultas Nacionales de Información y Asesorías S.A. de C.V., y Marsacot, las cuales cuentan con celdas diferentes para recibir los residuos sólidos urbanos de al menos 14 municipios hidalguenses, principalmente de la zona metropolitana de Pachuca. Ante esta situación, indicó que el gobierno municipal de Pachuca trabajaría en la actualización del programa de ordenamiento ecológico local con la finalidad de abrir más celdas para la disposición de residuos. Otro de los temas que fue abordado durante la comparecencia fue la situación de la presa Requena, donde actualmente se estima la presencia de más de 159,000 toneladas de lirio acuático. Mixtega Trejo informó sobre el proyecto para adquirir cuatro nuevas máquinas trituradoras destinadas a reducir la presencia de esta planta en el embalse y sus alrededores; sin embargo, reconoció que los equipos todavía no han sido comprados y que no habría tampoco fecha para poder adquirirlos. Explico que el procedimiento depende de los procesos de licitación, los cuales podrían tardar alrededor de tres meses, y para esta compra se contempla una inversión aproximada de 33 millones de pesos. En otros temas, la funcionaria señaló que existen 84 unidades económicas generadoras de residuos de manejo especial, un sector que requiere acciones de regulación y seguimiento para procurar una disposición adecuada de los desechos. También informó sobre la dispersión de 19 millones de esferas de semillas en una superficie de 11 hectáreas, aunque será necesario precisar el alcance y los resultados de esta intervención para conocer también su impacto ambiental.</t>
+  </si>
+  <si>
+    <t>Izza Hernández: Y vamos a continuar con el tema del relleno sanitario del Huixmi, que está ubicado en Pachuca, y es que contaría con una vida útil estimada de alrededor de 2 años, uno por cada celda de disposición de residuos. Esto lo informó Mónica Patricia Mixtega Trejo, la titular de la Secretaría de Medio Ambiente y Recursos Naturales del Estado de Hidalgo, durante su comparecencia ante el Congreso local el día 19 de octubre. La funcionaria explicó que en este espacio operan dos empresas particulares: Consultas Nacionales de Información y Asesorías S.A. de C.V., y Marsacot, las cuales cuentan con celdas diferentes para recibir los residuos sólidos urbanos de al menos 14 municipios hidalguenses, principalmente de la zona metropolitana de Pachuca. Ante esta situación, indicó que el gobierno municipal de Pachuca trabajaría en la actualización del programa de ordenamiento ecológico local con la finalidad de abrir más celdas para la disposición de residuos. Otro de los temas que fue abordado durante la comparecencia fue la situación de la presa Requena, donde actualmente se estima la presencia de más de 159,000 toneladas de lirio acuático. Mixtega Trejo informó sobre el proyecto para adquirir cuatro nuevas máquinas trituradoras destinadas a reducir la presencia de esta planta en el embalse y sus alrededores; sin embargo, reconoció que los equipos todavía no han sido comprados y que no habría tampoco fecha para poder adquirirlos. Explico que el procedimiento depende de los procesos de licitación, los cuales podrían tardar alrededor de tres meses, y para esta compra se contempla una inversión aproximada de 33 millones de pesos. En otros temas, la funcionaria señaló que existen 84 unidades económicas generadoras de residuos de manejo especial, un sector que requiere acciones de regulación y seguimiento para procurar una disposición adecuada de los desechos. También informó sobre la dispersión de 19 millones de esferas de semillas en una superficie de 11 hectáreas, aunque será necesario precisar el alcance y los resultados de esta intervención para conocer también su impacto ambiental. Daniel Martínez: Esto en el marco de la propia comparecencia de la titular de la SEMARNAT Hidalgo, que ¡vaya que sí tiene este chambita! Yo creo que uno de los temas fundamentales también es lo de la recuperación del entorno ecológico en el Valle de en el Valle de Tula-Tepeji, que ¡vaya que también ha habido discusión acerca del relleno sanitario que se encuentra en esa zona, Yes! Jessenia Romero: Sí, finalmente ha sido todo un tema esta situación, así que bueno, pues esto es parte de lo que se está realizando y esto es parte también de las acciones que dio a conocer en su comparecencia.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YglAd69g-ZXnJnqxaLEJi2OcypRPdY2N/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Mónica Mixtega</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1940/2026</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) ha destinado 148 millones 782 mil pesos para atender escuelas afectadas en su infraestructura por la vaguada monzónica del año pasado. Lo anterior fue informado por el titular de la dependencia estatal, Natividad Castrejón Valdez, durante su comparecencia ante el Congreso del Estado de Hidalgo, este martes 20 de octubre. Una de las atenciones que destacó el funcionario estatal, fue sobre la Escuela Secundaria General “Caudillo del Sur”, donde se invierten 16 millones 800 mil pesos y los trabajos registran un avance del 60 por ciento. Mientras que en un plantel de educación preescolar dentro del mismo municipio, existe avance en su rehabilitación del 45 por ciento y una escuela primaria, del 55 por ciento. “Eso llevó casi seis meses después de la vaguada, hasta que Conagua tomó la decisión de construir un enorme muro que impida otra vez el desborde del río. Entonces se decidió que sí se repararan las escuelas que estaban ahí”, señaló. Castrejón Valdez explicó que la intervención se retrasó debido a que se analizaba la posibilidad de reconstruir las escuelas en otros lugares, ante el riesgo que representaba su ubicación. Además, actualmente se ejecutan once obras de rehabilitación a planteles educativos en los municipios de Huehuetla, Tlahuiltepa, Tianguistengo y Tepehuacán. El funcionario estatal señaló que 56 millones de pesos destinados a la atención de las escuelas afectadas corresponden al seguro institucional, mientras que el resto de los recursos proviene del gobierno estatal. Como parte de las gestiones realizadas ante el gobierno federal, se entregaron 10 mil bienes y equipos para reponer parte de lo perdido y contribuir a la recuperación de los planteles. Además, se distribuyeron 525 computadoras portátiles entre el personal docente y administrativo. Castrejón Valdez recordó que, al inicio de la emergencia, se recibieron más de 250 reportes de escuelas afectadas; sin embargo, durante el proceso de revisión y limpieza se determinó que muchas de ellas únicamente presentaban acumulación de lodo y residuos ocasionados por las lluvias. Después de un análisis se contabilizaron 99 planteles con afectaciones 19 con daños graves, 36 con daños moderados y 44 con daños leves.</t>
+  </si>
+  <si>
+    <t>Uno de los grandes temas, y creo que es la tercera o cuarta dependencia estatal que toca el tema de las atenciones que se han brindado durante, o sí, después de la vaguada monzónica para rehabilitar infraestructura social, en este caso educativa, donde hubo información por parte del propio Catejón Valdés en su comparecencia oficial de ayer en el Congreso del Estado. Así es, Daniel. Le compartimos que la Secretaría de Educación Pública de Hidalgo ha destinado 148 millones 782 mil pesos en atender escuelas afectadas en su infraestructura por la vaguada monzónica del año pasado. Esto fue informado por Natividad Castrejón durante su comparecencia ante el Congreso el día de ayer martes 20 de octubre. Una de las atenciones que destacó el funcionario fue sobre la Escuela Secundaria General Caudillo del Sur, donde se invirtieron 16 millones 800 mil pesos y los trabajos registran un avance de 60%, mientras que en un plantel de educación preescolar dentro del mismo municipio existe avance en su rehabilitación del 45%, en una escuela primaria también el 55%. Eso llevó casi seis meses después de la vaguada monzónica hasta que Conagua tomó la decisión de construir un enorme muro que impida otra vez el desborde del río. Entonces ya se decidió que sí se repararan las escuelas que estaban ahí ubicadas. Castrejón Valdés explicó que la intervención se retrasó debido a que se analizaba la posibilidad de reconstruir las escuelas en otros lugares ante el riesgo que representaba también la ubicación. Obviamente se tenían que hacer estudios técnicos primero para determinar si se reconstruían nuevamente o finalmente se volvían a construir en algún otro lugar. Además, actualmente se ejecutan 11 obras de rehabilitación a planteles educativos en los municipios de Huehuetla, Tlahuiltepa, Tianguistengo y Tepehuacán. El funcionario estatal se que 56 millones de pesos destinados a la atención de las escuelas afectadas corresponden al seguro institucional mientras que el resto de los recursos proviene de gobierno estatal Como parte de las gestiones realizadas ante el gobierno federal se entregaron 10 mil bienes y equipos para reponer parte de lo perdido y contribuir a la recuperación de los planteles. Además, se distribuyen 525 computadoras portátiles entre personal docente y administrativo. Castrejón Valdés recordó que al inicio de la emergencia se recibieron más de 250 reportes de escuelas afectadas Sin embargo, durante el proceso de revisión y limpieza se determinó que muchas de ellas únicamente presentaban acumulación de lodo o residuos que habían sido ocasionados por la lluvia Después de un análisis se contabilizaron 99 planteles con afectaciones, 19 con daños graves, 36 con daños moderados y 44 con daños leves Natividad Castrejón informó que durante la administración se han destinado 2.700 millones de pesos a infraestructura educativa De los cuales 780 millones corresponden al periodo reportado en 1.500 planteles A esta inversión se suman más de 4.400 millones de pesos destinados en cuatro años a la entrega de útiles, uniforme, calzado y libros Para alrededor de 570 mil estudiantes por ciclo escolar Bueno, insisto, por obvias razones ha sido un gran tema acerca de la rehabilitación de los espacios dañados por la abogada monzónica para obras públicas, para educación. Entiendo que el día de hoy Bienestar también va a estar ya en tu comparecencia y no dudo que vayan a tocar el tema también de la abogada monzónica por obvias razones. Sí, claro, y pues estamos hablando de que todavía se sigue trabajando, al menos según lo que reportó el día de ayer Castrejón Valdés, es que al menos llevan, por ejemplo, algunas obras con 45% de avance, 55%, entonces todavía se sigue trabajando al respecto y hasta el momento se han destinado 148.782.000 pesos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hwkL1MgfNnqERs0P3nJNzuN3LL5fw6Z8/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>La devolución de las 80 hectáreas que solicitan estudiantes de la Escuela Normal Rural Luis Villarreal, conocida como El Mexe, no está contemplada por el momento, afirmó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón Valdez, durante su comparecencia ante el Congreso estatal. Mientras el funcionario presentaba información ante los legisladores, un grupo de normalistas se concentró en el exterior del recinto y bloqueó los accesos, lo que dificultó el tránsito de ciudadanos, trabajadores legislativos, periodistas y funcionarios que se encontraban en el lugar. Los manifestantes expresaron sus demandas mediante consignas y mantas. La movilización también generó cuestionamientos entre los diputados. Marco Antonio Mendoza Bustamante pidió que algún representante de la Secretaría de Educación saliera a escuchar a los estudiantes, al considerar necesario atender sus planteamientos relacionados con el marco curricular común, la formación docente y diversos asuntos administrativos. En respuesta, Castrejón Valdez aseguró que las autoridades mantienen abiertas las mesas de negociación con los normalistas. Detalló que durante la semana anterior se realizaron dos encuentros en la Ciudad de México, uno estatal y otro nacional, con la participación de la Secretaría de Gobernación. Asimismo, indicó que la siguiente reunión está prevista para el 3 de noviembre y que se han llevado a cabo más de 50 encuentros de trabajo. No obstante, el titular de la SEPH cuestionó la intervención de Roberto Azpeitia en el conflicto y lo acusó de utilizar las demandas de la comunidad normalista con fines políticos personales. Según el secretario, Azpeitia no forma parte de la planta académica de El Mexe ni cuenta con una representación formal de la institución. Castrejón también lo vinculó con la toma de las instalaciones de la dependencia ocurrida en febrero de 2026, durante la cual, aseguró, se registraron daños en puertas y cristales. Añadió que existe una carpeta de investigación relacionada con esos hechos. El funcionario sostuvo que, debido a esa situación, no considera viable establecer una interlocución con Azpeitia, aunque afirmó que las negociaciones con los estudiantes continúan. La postura de la dependencia mantiene sin respuesta favorable la exigencia de recuperar las 80 hectáreas reclamadas por los normalistas.</t>
+  </si>
+  <si>
+    <t>Francisco I. Madero</t>
+  </si>
+  <si>
+    <t>En cuestiones legislativas, el día de ayer, hubo, siguen las comparecencias en el Congreso del Estado de Hidalgo, tocó al titular de la Secretaría de Educación Pública Estatal, Natividad Castrejón, en donde habló en principio del tema del Meche, Isa, en tanto había protestas del Meche afuera del Congreso del Estado de Hidalgo. Es correcto, Daniel, así como lo estás adelantando, y es que la devolución de las 80 hectáreas que solicitan estudiantes de la Escuela Normal Rural Luis Villarreal, conocida como el Meche, no está contemplada por el momento, así lo afirmó el titular de la Secretaría de Educación Pública de Hidalgo, Natividad Castro Convaldez, todo esto durante la comparecencia ante el Congreso Estatal. Mientras el funcionario presentaba la información ante los legisladores, un grupo de normalistas se concentró en el exterior del recinto y bloqueó los accesos, lo que dificultó, de hecho, el tránsito de ciudadanos, también de trabajadores legislativos, periodistas y funcionarios que se encontraban en ese lugar. Los manifestantes expresaron sus demandas mediante consignas y también mantas. La movilización también generó bastantes cuestionamientos entre los diputados. Marco Antonio Mendoza Bustamante, de hecho, pidió que algún representante de la Secretaría de Educación saliera a escuchar a los estudiantes al considerar necesario entender estos planteamientos relacionados con el marco curricular común, la formación docente y también diversos asuntos administrativos. Y pues en respuesta Castrejón Valdés aseguró que las autoridades mantienen abiertas las mesas de negociación, eso con los normalistas, y detalló también que durante la semana anterior se realizaron dos encuentros, uno en la Ciudad de M uno estatal y otro nacional pues con la participación de la Secretar de Gobernación asimismo también indicó que la siguiente reunión está prevista para el 13 de noviembre y que se han llevado a cabo m de 50 encuentros de trabajo No obstante, el titular de la CEPIDALGO cuestionó la intervención de Roberto Aspeitia, de hecho también en el conflicto, y lo acusó directamente de utilizar las demandas de la comunidad normalista con fines políticos personales. Según el secretario, Aspeitia de hecho no forma parte de la planta académica del Meche ni cuenta con una representación formal de la institución. Y bien Castrejón también lo vinculó con la toma de las instalaciones de la dependencia ocurrida en febrero del 2026, durante la cual aseguró se registraron daños en puentes y cristales. De hecho añadió que existe una carpeta de investigación relacionada con estos hechos. Pero sí el funcionario sostuvo que debido a esta situación no considera viable establecer como tal y de alguna forma también pues negociaciones con los estudiantes y obviamente también esto es continua la postura de la dependencia mantiene sin respuesta favorable la exigencia de recuperar estas 80 hectáreas reclamadas por los normalistas. Y pues prácticamente esto fue todo lo que sucedió, Daniel. Y pues sí, mientras tanto está a un lado el hecho de devolver las 80 hectáreas reclamadas por estudiantes del MESH. De hecho, le puso nombre y apellido por lo que comentabas en su momento, Isa, a quien podría ser el responsable, a quien podría estar detrás de las protestas y manifestaciones que ya tienen años, por cierto, ¿ven? Es correcto, Daniel, así como lo acabas de mencionar, sí ya tienen muchísimo tiempo y sabemos perfectamente que no es nada, pero nada, nada nuevo que se manifiesten de esta manera y que hagan este tipo de peticiones. Vamos a ver qué pasa más adelante porque ya llevan ratito precisamente con este tipo de peticiones.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ueeSWAppHqm8mWnO3lJcoNEco_UgQYBH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Roberto Azpeitia</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/Bol.1330/2026</t>
+  </si>
+  <si>
+    <t>Menchaca Salazar logra gestión histórica ante Pemex por más de 654 millones de pesos</t>
+  </si>
+  <si>
+    <t>Jessenia Romero</t>
+  </si>
+  <si>
+    <t>Donación Pemex</t>
+  </si>
+  <si>
+    <t>Daniel Martínez: El gobernador Julio Menchaca Salazar estuvo presente con funcionarios de Petróleos Mexicanos para recibir eh inversión eh este atención a gestiones que se habían realizado con la paraestatal, Izza. Izza Hernández: Es correcto, Daniel, de hecho les contamos y precisamente que desde las instalaciones de la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, el gobernador Julio Menchaca Salazar encabezó la entrega de equipamiento por 78,614,370 pesos, este resultado de las gestiones realizadas por o ante Petróleos Mexicanos, que desde 2022 pues han permitido a Hidalgo recibir donaciones por más de 654 millones de pesos, para poder fortalecer los servicios públicos, la infraestructura carretera, la salud y también la educación. El abandono durante mucho tiempo ha sido atacado, ha sido trabajado también por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, atendiendo el compromiso que tenemos con nuestra patria chica y también ahí encontramos de manera solidaria a Pemex, así lo aseveró el mandatario estatal, esto al manifestar el agradecimiento del pueblo hidalguense, todo esto por el apoyo solidario que se brindó pues en las comunidades afectadas, eso por la vaguada monzónica, a través de la donación de combustible, unidades médicas también y maquinaria. Y pues en este sentido, Menchaca Salazar dio a conocer que pues para esta entrega de alguna forma Pemex sí proporcionó 5,000 toneladas de toneladas de asfalto, 500 luminarias, dos camiones tanque, también un camión desazolve, ahora sí que también dos retroexcavadoras y dos ambulancias y equipamiento pues que estaría contribuyendo a fortalecer la capacidad operativa de los servicios públicos y la atención a la población. Y en su momento, el director de Responsabilidad Social de Pemex, Raúl Ojeda Sukieta, refirió que las donaciones realizadas por la empresa mexicana pues son muestra del esfuerzo que mujeres y hombres llevan a cabo en la refinería de Tula, esto en la planta coquizadora, así como también en cada uno de los espacios pues que se han le son conferidos y pues Alejandro Vázquez Mendoza, quien es secretario del Despacho del Poder Ejecutivo del Estado de Hidalgo, pues externó el conocimiento y el reconocimiento a la presidenta Claudia Sheinbaum y también al personal de Pemex por el respaldo de manera permanente al desarrollo de la entidad. Este encuentro va mucho más allá de la recepción administrativa de estas unidades y de la maquinaria también que hoy tenemos aquí, nos recuerda que la riqueza del país sobra pues sentido, cobra sentido, también pleno únicamente pues cuando regresa al pueblo, parte de lo que dio a conocer y entre los resultados Vázquez Mendoza destacó la donación de 23,200 toneladas de asfalto, estas destinadas a la rehabilitación de 42 vialidades en nueve municipios con una superficie de 560,000 metros cuadrados, asimismo también pues informó que se estarían realizando trabajos en el bulevar Refinería-Tula, mientras que se contemplan pues nuevas intervenciones en Pachuca, en Huejutla entre otras demarcaciones y pues en materia de salud esta colaboración ha permitido brindar 178,910 servicios eh pues mediante unidades médicas móviles en 59 municipios, además también de la realización de 10,000 mastografías en 23 municipios, ampliando de esta manera el acceso a la atención y detección también oportuna. Finalmente, el respaldo de Pemex y también pues estaría reflejando la donación importante de 53 unidades vehiculares, 500 tinacos y equipamiento de 200 aulas de 89 escuelas distribuidas en 18 municipios. Parte de lo que se da a conocer con esta información Menchaca Salazar que logra esta gestión histórica ante Pemex por más de 654 millones de pesos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QgI9uim6BczVD33I1IVimM-Sfgw1mYi3/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SIPDUS, Procuraduría General de Justicia del Estado de Hidalgo, Secretaría del Trabajo y Previsión Social de Hidalgo</t>
+  </si>
+  <si>
+    <t>Raúl Ojeda Zubieta, Alejandro Velázquez Mendoza, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>El Gobierno de Hidalgo alista una denuncia contra Uber por su presunta prestación de servicios de transporte en Pachuca sin contar con la autorización correspondiente, informó el gobernador Julio Menchaca Salazar, quien prevé que el recurso sea presentado ante la Procuraduría General de Justicia del Estado en los próximos días. El mandatario explicó que la Coordinación General Jurídica trabaja en la integración del documento para que el Ministerio Público determine si existen elementos para investigar posibles infracciones y establecer responsabilidades. Tras un evento de entrega de donaciones de Petróleos Mexicanos (Pemex), Menchaca señaló que la legislación contempla sanciones relacionadas con el uso irregular de servicios públicos. Añadió que el análisis podría incluir tanto a quienes impulsan la operación de la plataforma como a las personas que ofrezcan viajes mediante ella. Respecto a la posibilidad de que Uber obtenga los permisos necesarios, el gobernador indicó que la empresa puede participar en los procedimientos establecidos; sin embargo, afirmó que actualmente no se han autorizado nuevas concesiones para rutas u otras modalidades de transporte público, debido a la saturación que, según dijo, enfrenta el sector en Hidalgo. Menchaca Salazar reconoció que mejorar la movilidad será uno de los asuntos pendientes durante la parte final de su administración, ante las necesidades de traslado de la población. En otro tema, llamó a los usuarios del transporte público a presentar denuncias formales cuando enfrenten malos tratos o agresiones por parte de operadores. Señaló que estos procedimientos permiten a las autoridades investigar los casos y, si corresponde, aplicar sanciones a conductores o concesionarios.</t>
+  </si>
+  <si>
+    <t>Vamos viendo cómo evoluciona este tema, hablando de transporte, Isa. Pues ahora sí que Toma y Daca, en el asunto de los servicios de plataforma, que si entran, que si no entran, que si es legal, que si no es, que es ilegal. Ya había planteado el fin de semana el gobernador Julio Menchaca Salazar, a principios de la semana más bien, el tema de que si estaban circulando estas aplicaciones, estos autos por aplicación, pues estaban en una cuestión ilegal. E incluso ayer hizo un anuncio que se me hace curioso lo que declaró casi al mismo tiempo el presidente de la Junta de Gobierno del Congreso del Estado de Hidalgo sobre el tema. Empezamos contigo, si nos permites. Es correcto, Daniel. El gobierno del Estado de Hidalgo estaría listando una denuncia en contra de Uber por la presunta prestación de servicios de transporte en Pachuca sin contar con la autorización correspondiente. Así lo informó el gobernador Julio Menchaca Salazar, quien prevé que el recurso sea prestado ante la Procuraduría General de Justicia del Estado de Hidalgo. Esto en los próximos días. Y pues el mandatario explicó que la Coordinación General Jurídica trabaja en integración del documento para el Ministerio Público para que él determine directamente si existen elementos para poder investigar posibles infracciones y establecer también responsabilidades. Y pues tras un evento de entrega de donaciones de petróleos mexicanos de Pemex, Menchaca señaló que la legislación contempla sanciones relacionadas con el uso irregular de servicios públicos. De hecho, añadió que el análisis podría incluir tanto a quienes impulsan la operación de plataforma como también a las personas que ofrezcan viajes mediante ella. Y respecto a la posibilidad de que Uber obtenga los permisos necesarios, el gobernador sí indicó que la empresa puede participar en los procedimientos establecidos. Sin embargo, afirmó que actualmente no se han autorizado nuevas concesiones para rutas u otras modalidades también de transporte p Todo esto debido a la saturación que de acuerdo con lo que dijo estar enfrentando el sector en Hidalgo Y pues Menchaca Salazar reconoció que mejorar la movilidad ser uno de los asuntos pendientes durante la parte final de su administración ante las necesidades de traslado de la población. Y pues en otro tema, también llamó a los usuarios de transporte público a presentar denuncias formales cuando enfrenten malos tratos o agresiones por parte de operadores. De hecho, señaló que estos procedimientos permiten a las autoridades pues investigar los casos y corresponde también aplicar sanciones a conductores o concesionarios. Entonces, pues de esta manera es como el gobierno de Hidalgo pues estaría preparando una denuncia contra Uber por posible operación irregular. Sí, viendo por acá, Isa, lo que comentabas también hace un momentito de que el propio gobernador Menchaca Salazar pues está invitando también a quienes son usuarios del Servicio de Transporte público de pasajeros, sea colectivo, sea taxi, de que en caso de agresiones también denuncien. Insisto, así como se señala, es que qué mal conductor, es que qué mal operador me tocó, también está la parte de los que son excelentes operadores y que son la mayoría, y también habemos buenos, malos, pésimos y lo que sigue pasajeros, Isa. Es correcto, pues finalmente hay de todo, Daniel, digo, como siempre lo hemos dicho, y lamentablemente por algunos pagan todo así hablando o de manera general. O sea, si hablamos en este caso, por ejemplo, de los prestadores de servicio e incluso hasta de los mismos pasajeros, pero bien, pues sí, en efecto, lo que hizo el gobernador es un llamado a los usuarios de transporte público para presentar las denuncias formales cuando en alguna ocasión enfrenten algún tipo de maltrato. De hecho, recordemos que algunas de las personas que más sufren de maltrato, por ejemplo, son las personas adultas mayores. Ahora sí que nos han llegado los reportes directamente aquí a cabina. Entonces, pues bien, ese tipo de anuncios, hacerlas formales, como lo dijo el gobernador.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yY_pcbAaRrCROlv1leoXK7qFxFzIDNwR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>En cuestión de agenda, se espera que en unos minutos más el gobernador Julio Menchaca Salazar encabece el Congreso Nacional de Moda y Vestido 2026. Esto se realizará en el Auditorio Gota de Plata a las 19 horas.</t>
+  </si>
+  <si>
+    <t>Agenda gobernador</t>
+  </si>
+  <si>
+    <t>En cuestión de agenda, se espera que en unos minutos más el gobernador Julio Menchaca Salazar encabece el Congreso Nacional de Moda y Vestido 2026. Esto se realizará en el Hotel de Gota de Plata a las 19 horas. Muy bien, va a estar este evento aquí en el Centro Cultural Hidalguense, ¿no? Dentro del Centro Cultural Hidalguense el gobernador encabezará esta inauguración.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iqeIYYe56IanWP96lTECcrzp8fKGbmHR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>UPLAPH/Citnova/Bol.13/2026</t>
+  </si>
+  <si>
+    <t>Protege Hidalgo el conocimiento para impulsar la innovación</t>
+  </si>
+  <si>
+    <t>Citnova</t>
+  </si>
+  <si>
+    <t>Propiedad intelectual</t>
+  </si>
+  <si>
+    <t>Andrés Torres:El gobierno de nuestro estado encabezado por Julio Menchaca fortalece las capacidades de la comunidad científica, tecnológica y emprendedora para que sus ideas e investigaciones se conviertan en oportunidades de desarrollo a través del Consejo de Ciencia, Tecnología e Innovación de Hidalgo, el Citnova, que acaba de poner en marcha el en segundo curso introductorio a la propiedad intelectual. Esta interactiva iniciativa busca acercar herramientas para identificar, proteger y gestionar los resultados de las investigaciones, invenciones y proyectos creativos mediante figuras como las patentes, los modelos de utilidad, derechos de autor y registro de marcas, fundamentales para aprovechar el valor del conocimiento. Durante la inauguración virtual de esta eh evento, el director general del Citnova, Francisco Patiño Cardona, destacó la importancia de fortalecer las capacidades de las y los hidalguenses para proteger sus creaciones y generar nuevas oportunidades de innovación y desarrollo. La capacitación coordinada por la Subdirección Adjunta de Gestión y Propiedad Intelectual está dirigida a estudiantes, investigadores, científicos, tecnólogos, personas emprendedoras, profesionales, creativos y público en general. Con ellos se promueve una cultura de protección del conocimiento y la vinculación entre instituciones académicas, centros de investigación y empresas de así como emprendedores. El curso es gratuito, se imparte en una modalidad virtual y contempla 10 horas distribuidas en cinco sesiones, eh todo programada para los días 20, 21, 22, 27 y 28 de octubre del presente año. Al finalizar, las personas participantes podrán identificar alternativas de protección para sus proyectos y conocer las rutas generales para gestionar sus gestiones e invenciones ante las autoridades competentes. Bueno, pues es muy importante proteger la propiedad intelectual y déjenme decirle que aunque pudiera ser un asunto que a usted le pareciera lejano, hay muchos muchos investigadores, hay muchos inventores, es el término popular, en nuestro estado, que todos los días están trabajando, que todos los días están produciendo este en diferentes áreas y pues qué mejor que tengan información para proteger sus</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aqhxW4sr29r81LCrtpoi0-nv9ZyE7kgK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Francisco Patiño Cardona</t>
+  </si>
+  <si>
+    <t>El día de ayer se llevó a cabo la comparecencia del secretario de educación pública, Natividad Castrejón. La comparecencia fue larga e interesante, abordando temas como la eficiencia terminal en educación, la infraestructura educativa, la dinámica social y las nuevas condiciones de seguridad en las escuelas, así como los planes y programas de estudio. Durante esta comparecencia, alumnos de la Normal Rural Luis Villarreal de El Mexe protestaron por mejores instalaciones y exigieron la devolución de las antiguas instalaciones en Tepatepec, Francisco I. Madero. Bloquearon los accesos al Congreso del Estado, cerrando la calle que lleva al Congreso, así como a las instalaciones del Poder Judicial y de Radio y Televisión de Hidalgo. La manifestación fue pacífica, pero causó complicaciones en el tránsito. Los estudiantes exigían la asistencia del secretario a sus asambleas para abordar su pliego petitorio. La situación se prolongó durante varias horas, dificultando la entrada y salida del Congreso. La comparecencia de Onésimo Serrano, encargado de la Unidad de Planeación y Prospectiva del Gobierno del Estado de Hidalgo, sufrió un retraso. Al final, el secretario se retiró por una salida alterna, y los estudiantes se fueron sin incidentes, dejando solo un bloqueo temporal. La agenda legislativa avanzó y Onésimo Serrano pudo realizar su comparecencia.</t>
+  </si>
+  <si>
+    <t>El día de ayer se llevó a efecto la comparecencia del secretario de educación pública de nuestro estado, Natividad Castrejón. Fue una comparecencia muy larga, una comparecencia muy interesante, se hablaron de temas que son de interés general como la eficiencia terminal en los niveles de educación de nuestro estado, infraestructura en temas educativos, nuevas condiciones de la sociedad, la dinámica social y las nuevas condiciones de seguridad en las escuelas, los planes y programas de estudio. Ayer durante el desarrollo de esta comparecencia del secretario de educación ante la LXVI Legislatura, hubo una protesta por parte de alumnos de la Normal Rural Luis Villarreal de El Mexe, quienes continúan con sus manifestaciones y exigencias para que se amplíen las instalaciones y se les devuelvan las instalaciones de la antigua normal rural allá en la región de Tepatepec en el municipio de Francisco I. Madero. Bloquearon los accesos al Congreso del Estado, cerrando la calle que da acceso al Congreso, a las instalaciones del Poder Judicial y de Radio y Televisión de Hidalgo. La manifestación fue pacífica, pero impidieron la circulación en la zona y complicaron el tránsito. Exigían que el secretario asistiera a sus asambleas y convocatorias para resolverles su pliego petitorio. El asunto se complicó durante varias horas sin dejar salir ni entrar a nadie al Congreso. La otra comparecencia pactada y agendada para el día de ayer en la LXVI Legislatura, la del encargado de la Unidad de Planeación y Prospectiva del Gobierno del Estado de Hidalgo, Onésimo Serrano, tuvo un considerable retraso. Al final el secretario se retiró por una salida alterna habilitada para abandonar el recinto, y los estudiantes de la Normal Rural Luis Villarreal del Mexe se retiraron sin incidentes, quedando solo el bloqueo temporal de unas horas en las instalaciones del Congreso. Avanzó la agenda legislativa y Onésimo Serrano pudo dar su comparecencia correspondiente a la Unidad de Planeación y Prospectiva.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10eOyIkYWcIui2KWvfOli6bmQWczRpL8I/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso del Estado, Poder Judicial, Radio y Televisión de Hidalgo, Unidad de Planeación y Prospectiva.</t>
+  </si>
+  <si>
+    <t>Onésimo Serrano Rivera</t>
+  </si>
+  <si>
+    <t>Recorrido Por Instalaciones</t>
+  </si>
+  <si>
+    <t>Positivo</t>
+  </si>
+  <si>
+    <t>El gobernador de nuestro estado, Aldo Falcón, ayer recorrió la subestación de la Comisión Federal de Electricidad para hacer una supervisión de las adecuaciones, de las rehabilitaciones y sobre todo para ver cómo se ha fortalecido esta paraestatal para lo que corresponde al suministro de energía eléctrica en las diferentes regiones de nuestro estado. Así se acompaña del personal de la Comisión Federal de Electricidad, el gobernador Julio Menchaca, Salazar recorrió las instalaciones de la sub estación de CFE, un espacio Comisión Federal de Electricidad un espacio que forma parte del programa de desarrollo del Sistema Eléctrico Nacional 2021-2035 y el suministro de la zona metropolitana de Pachuca Muy bien, esta supervisión, les repito es parte de los trabajos de coordinación porque uno de los principales problemas que tenemos en diferentes regiones de nuestro estado, por ejemplo la Huasteca, es que el tendido eléctrico la instalación, los temas que tienen que ver con la distribución de la electricidad en nuestro estado, bueno, pues hay una sobrecarga y una sobresaturación, eso no es un problema del estado de Hidalgo, es un problema en muchas entidades, no es propio del estado de Hidalgo, en muchas entidades, y bueno, la paraestatal Función Federal de Electricidad anunció ya desde hace varios meses que ampliará su infraestructura para que cada vez sea mejor la distribución y por supuesto la dotación de energía en regiones como la Huasteca y la Sierra en nuestro estado. Por eso el tema de esta coordinación y esta supervisión es parte de estos trabajos que se anunciaron hace varios meses para fortalecer la infraestructura de la Comisión Federal de Electricidad en todo el Estado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CMuS5d1UBwMP8yAruW_azCosSHvndjDA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El gobernador de nuestro estado, Julio Menchaca Salazar, ayer tuvo actividad y se reunió con autoridades de la paraestatal Pemex, desde las instalaciones de la CAASIM, de la Comisión Nacional de Agua y Alcantarillado y Sistemas Intermunicipales, el gobernador Julio Menchaca encabezó la entrega de equipamiento por un total de 78,614,370 pesos, esto gracias a las gestiones que se realizaron ante Petróleos Mexicanos, este que desde el 2022 pues le permitieron a nuestro estado recibir donaciones que superan los 654 millones de pesos, todo esto para fortalecer los servicios públicos de infraestructura carretera, la salud y, por supuesto, la educación. El abandono que durante mucho tiempo ha sido atacado, dice así, el abandono que durante mucho tiempo ha sido atacado, ha sido trabajado por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, atendiendo el compromiso que tenemos con nuestra patria chica, y ahí encontramos solidariamente a Pemex, aseveró el mandatario estatal al manifestar el agradecimiento del pueblo hidalguense para el apoyo solidario que brindó en las comunidades afectadas por la vaguada monzónica a través de donaciones de combustible, unidades médicas y maquinaria. En esta participación, el gobernador Julio Menchaca dijo que para esta entrega Pemex proporcionó 5,000 toneladas de asfalto, de asfalto, 5,000 luminarias, dos camiones tanque, un camión de desazolve, dos retroexcavadoras y dos ambulancias, equipamiento que contribuirá a fortalecer la capacidad operativa de los servicios públicos y la atención a la población. En su momento, el director de Responsabilidad Social de Pemex, Raúl Ojeda Zubieta, refirió que las donaciones realizadas por la empresa mexicana son muestra del esfuerzo que mujeres y hombres llevan a efecto en la refinería de Tula, en la planta coquizadora, así como en cada uno de los espacios que les son conferidos. Alejandro Velázquez Mendoza, secretario de Despacho del Poder Ejecutivo del Estado de Hidalgo, externó reconocimiento, el reconocimiento a la presidenta Claudia Sheinbaum y al personal, por supuesto, de la paraestatal Pemex por el respaldo permanente al desarrollo de la entidad. En este encuentro va mucho más allá de la representación o de la recepción administrativa de estas unidades y de las maquinarias que hoy ya tenemos aquí, nos recuerda que la riqueza del país cobra sentido pleno únicamente cuando regresa al pueblo convertida en obras, en infraestructura, en justicia social, puntualizó el funcionario y recordó que la coordinación con Pemex, instruida por el gobernador Julio Menchaca, permitió que del 2022 a la fecha se gestionaran cursos por más de 654 millones de pesos. En estos entre estos principales resultados el el secretario del despacho dijo que hay una donación de 23,200 toneladas de asfalto, estas fueron destinadas a la rehabilitación de 42 vialidades en nueve municipios con una superficie de 5,600 m2. De la misma forma, dijo que se realizan trabajos en el bulevar de la Refinería Tula, mientras que también se contemplan nuevas inversiones para Pachuca y Huejutla, intervenciones en Pachuca y Huejutla entre otras demarcaciones. Aldo Falcón: En materia de salud, en esta colaboración ha permitido brindar 178,910 servicios mediante unidades médicas móviles en 59 municipios, además se realizaron 10,000 mastografías en 23 municipios aplicando el acceso atención de la perdón de la detección oportuna. Finalmente, el respaldo de Pemex también se refleja en la donación de 53 unidades vehiculares, 500 tinacos de equipamiento para 200 aulas de 89 de 89 escuelas distribuidas en 18 municipios que se suman a la rehabilitación y reforestación de 3.9 km de la ciclovía andador peatonal del Río de las Avenidas en Pachuca en beneficio de 304 314,000 habitantes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kVU4i2g6p2tszznjAeGtwbTEuZEwnqzE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SIPDUS (CAASIM)</t>
+  </si>
+  <si>
+    <t>Vecinos de San Agustín Tlaxiaca reportaron objetos sospechosos, bolsas de plástico, en un área desierta cerca de Santa Catarina. Al llegar, la policía encontró dos cuerpos sin vida. Uno de ellos estaba dentro de una bolsa en la carretera Pachuca-Actopan. Además, en el mismo municipio, se halló a una persona degollada en un hotel, dentro de una habitación. Esta persona aparentemente entró con otra que logró escapar sin ser vista por la seguridad del lugar.</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>Tuvimos ayer un incidente, pues un desafortunado incidente, hubo un reporte por parte de vecinos de la zona de San Agustín Tlaxiaca respecto a unos objetos, unas bolsas de plástico que fueron localizadas en un paraje ahí abandonado, un paraje desértico cerca de la zona de Santa Catarina. Al acudir la policía localizó varios, dos cuerpos sin vida. Aldo Capón. Así es Andrés, lamentablemente este hallazgo que se reportó la mañana del día de ayer en la carretera Pachuca-Actopan, en su tramo correspondiente a San Agustín de la Ciudad, que es la comunidad de Santa Catarina, donde fue localizado el cuerpo de una persona dentro de una bolsa. Igualmente en este mismo municipio se fue localizado en el interior de un hotel una persona degollada dentro de una habitación, aparentemente ingresó con otra persona, la cual logró salir sin ser detectada por la seguridad del mismo establecimiento.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zIQpVIiBGgjpqxa5kCaflFhOgZPV9nvu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Está la campaña estatal de vacunación, vacunación invernal, que la Secretaría de Salud puso en operación hace unos días. Hay más de un millón quinientas mil dosis de vacunas contra el COVID, contra la influencia estacional. Por favor, acuda a su clínica, a su centro de salud más cercano. Hay que estar bien inmunizados, hay que estar preparados para esta temporada invernal, principalmente niños menores de cinco años, adultos mayores. Es muy importante que reciban sus vacunas. Todo es gratuito. Esto todo es, por supuesto, gratuito en el tema de la salud acá en el estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15Io4lEaXYBpFWT2j7n0ztGP5QCD-YjTV/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Andrés Torres: Gracias a toda la gente que nos sigue a través de las redes sociales, que nos escribe diariamente, que está muy pendiente de las vocales, les repito, más de 12 años de transmisiones interrumpidas, a punto de cumplir 13 años, y sobre todo le agradezco muchísimo a la gente que todos los días, todos los días sin excepción, nos saluda, gracias, creo que prácticamente es el único programa de radio y televisión de algo que tiene interacción con el auditorio, ¿no? Somos el único, bueno y tenemos interacción Porque como están cortados los teléfonos Por falta de pago, pues nosotros Tenemos que poner un teléfono Tenemos que poner un canal de WAF Todo eso A cuenta de La propia producción Y pues mire Con la agradable noticia de que Muchísima, muchísima gente Nos escucha todos los días</t>
+  </si>
+  <si>
+    <t>Precariedad laboral</t>
+  </si>
+  <si>
+    <t>Gracias a toda la gente que nos sigue a través de las redes sociales, que nos escribe diariamente, que está muy pendiente de las vocales, les repito, más de 12 años de transmisiones interrumpidas, a punto de cumplir 13 años, y sobre todo le agradezco muchísimo a la gente que todos los días, todos los días sin excepción, nos saluda, gracias, creo que prácticamente es el único programa de radio y televisión de algo que tiene interacción con el auditorio, ¿no? Somos el único, bueno y tenemos interacción Porque como están cortados los teléfonos Por falta de pago, pues nosotros Tenemos que poner un teléfono Tenemos que poner un canal de WAF Todo eso A cuenta de La propia producción Y pues mire Con la agradable noticia de que Muchísima, muchísima gente Nos escucha todos los días</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1efLLBmzgDLMaHEXFBx79VCioh7vPS-aB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Andrés Torres: cumplimos un mes fuera del aire en nuestra estación 91.1 de frecuencia modulada allá en Jacala de Ledezma. Bueno, pues yo apelo a las autoridades que nos ayuden para que podamos resolver este asunto. Evidentemente el área administrativa y el área de ingeniería no lo pueden resolver. Ahí ellos tendrán que dar cuentas Por qué este asunto no avanza Lo que nos corresponde a nosotros es estar pendientes Tener nuestras programaciones a punto Y el personal ahí pendiente para que estemos En el momento de que se restablezca la señal Trabajar como nos corresponde</t>
+  </si>
+  <si>
+    <t>Vamos a iniciar rápidamente con nuestro recorrido, no sin antes recordarles cumplimos un mes fuera del aire en nuestra estación 91.1 de frecuencia modulada allá en Jacala de Ledesma. Bueno, pues yo apelo a las autoridades que nos ayuden para que podamos resolver este asunto. Evidentemente el área administrativa y el área de ingeniería no lo pueden resolver. Ahí ellos tendrán que dar cuentas Por qué este asunto no avanza Lo que nos corresponde a nosotros es estar pendientes Tener nuestras programaciones a punto Y el personal ahí pendiente para que estemos En el momento de que se restablezca la señal Trabajar como nos corresponde</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HU_7S4nKVp_AIQPjL5BnjnyCIf1HfdVz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Hay una onda fría y un frente frío en todo el territorio nacional, especialmente en el estado de Hidalgo. La Subsecretaría de Protección Civil del Estado pide a la población estar atentos a la bajada de temperaturas, sobre todo en áreas altas, donde se esperan heladas y temperaturas de hasta 0 grados. Para el 21 de octubre de 2026, se informa que habrá chubascos de 5 a 25 milímetros y temperaturas de 0 a 5 grados. También se pronostican vientos de 20 a 30 kilómetros por hora, con rachas de 40 a 60 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>Recordándole que hay una onda fría, tenemos frente frío acá en la territorio, pues prácticamente en todo el territorio nacional, pero en el estado de Hidalgo hay un llamado que nos hace la subsecretaría de protección civil del gobierno del estado a través de la secretaría de gobierno para estar muy atentos ante estos descensos de temperaturas, sobre todo en zonas altas de nuestro estado, Se esperan heladas, temperaturas hasta de 0 grados Vamos por favor Aldo Falcón ¿Qué nos dice la Subsecretaría de Protección Civil? Así es Andrés, la Subsecretaría de Protección Civil Y Gestión de Riesgos Informa a la población que para este 21 de octubre de 2026 De acuerdo con el aviso número 585 Del pronóstico meteorológico general Del Servicio Meteorológico Nacional Se prevén intervalos de chubascos de 5 a 25 milímetros Asimismo se pronostican temperaturas de 0 a 5 grados Con vientos de 20 a 30 kilómetros por hora con rachas de 40 a 60 km por hora.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/103LSbwMf-t8eOEh0Oe_nbr3b6MJKfimt/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SSH hace un llamado a reforzar medidas de prevención ante el incremento de enfermedades respiratorias</t>
+  </si>
+  <si>
+    <t>Prevención De Enfermedades</t>
+  </si>
+  <si>
+    <t>Nos vamos hasta el estado de Hidalgo. La Secretaría de Salud de Hidalgo hace un llamado a reforzar medidas de prevención ante el incremento de enfermedades respiratorias. Tras el descenso de temperatura se suman más de 380,000 casos de estos padecimientos en la entidad. Como parte de las acciones preventivas y de promoción de la salud impulsadas por el gobierno de Julio Menchaca Salazar, la Secretaría de Salud de Hidalgo, encabezada por Vanessa Escalante Arroyo, mantiene el llamado a la población para fortalecer las medidas de autocuidado durante la actual temporada de frío y con especial atención a los grupos más vulnerables. De acuerdo con las cifras epidemiológicas, actualmente la entidad registra 380,323 casos de infecciones respiratorias agudas, lo que representa un decremento de 8.2% respecto al mismo periodo del 2025, cuando se contabilizaron 414,106 casos. Los municipios con mayor número de casos son Pachuca, Tulancingo, Tula, Ixmiquilpan y Actopan. Por lo anterior y con el curso de con el curso del actual frente frío número dos, la Secretaría de Salud de Hidalgo recomienda abrigarse adecuadamente, evitar cambios bruscos de temperatura, mantener una alimentación equilibrada, lavarse las manos frecuentemente y practicar el estornudo de etiqueta. También se invita a revisar y complementar el esquema de vacunación contra la influenza, COVID-19 y neumococo, conforme a las indicaciones correspondientes, de acuerdo con Rubí Vargas Vargas, coordinadora de comunidades y municipios de la Subsecretaría de Salud Pública, es necesario que antes de ante las bajas que ante las bajas temperaturas se extremen precauciones en el hogar, evitar intoxicaciones por monóxido de carbono y quemaduras, particularmente al utilizar equipos de calefacción. Agregó que se recomienda no encender anafres o braseros en espacios cerrados. Vamos a escuchar parte de lo que destaca la coordinadora de comunidades y municipios de la Subsecretaría de Salud Pública, Rubí Vargas Vargas.
+“La temporada de frío o temporada invernal, se incrementan de manera importante las enfermedades respiratorias. Por esta razón, la Secretaría de Salud fortalece las acciones de promoción y difusión sobre recomendaciones para enfrentar efectos negativos a la salud de forma prioritaria en grupos vulnerables como menores de 5 años, adultos mayores, personas en situación de calle o pobreza extrema. Entre las medidas preventivas que podemos compartir con la población en general son pues lavarse las manos de forma frecuente antes de consumir o preparar alimentos, después de utilizar el baño y en especial después de tener contacto con personas enfermas, cubrir nariz y boca al toser o estornudar con el ángulo del codo, lo que llamamos estornudo de etiqueta, o bien hacerlo con un pañuelo. Esto disminuirá el riesgo de contagio de las personas a nuestro alrededor. Abrigarse con ropa adecuada como gorro, guantes, bufanda, evitar en lo posible los cambios bruscos de temperatura y corrientes de aire frío, consumir suficientes líquidos, consumir frutas y verduras ricas en vitaminas A, C y D. Importante vacunarse contra influenza y COVID, además de neumococo de acuerdo a la edad correspondiente”.
+Señaló que ante síntomas como fiebre, tos, escurrimiento nasal o cansancio, es importante evitar la automedicación y acudir a valoración médica. Si se presenta dificultad para respirar o dolor torácico, se debe buscar atención médica urgente. Es lo que se destaca desde la Secretaría de Salud del Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19ovqUJXYnhhpCr8EIktWgsi1-4O6gjF7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Rubí Vargas Vargas</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Locutor Jesús Riveros da lectura a comentario de radioescucha que reporta retrasos y deficiencias en una obra de infraestructura cercana al plantel Cecyte en Tulancingo, señalando que los trabajos han permanecido pausados por casi un año. La inconformidad destaca la falta de banquetas para los estudiantes, lo cual genera condiciones de riesgo en la época de lluvias debido a la acumulación de lodo y resbalones de los alumnos, sin que haya una fecha definida para la pavimentación de la zona.</t>
+  </si>
+  <si>
+    <t>Media superior</t>
+  </si>
+  <si>
+    <t>Continuamos con más información. También por acá nos están enviando este reporte que ya ha sido canalizado a las autoridades sobre... bueno, nos dicen: "Buenas tardes, llevamos ya casi un año en el Cecyte de Tulancingo y esta obra va en pausas. Eh, pues nos dice que que ve que la están haciendo mal. Los alumnos no tienen banqueta para caminar y está muy peligroso por el lodo en esta época de lluvias. Los chicos incluso se han resbalado". Y nos comparte la imagen de una parte donde dice: "Aquí ni siquiera hay para cuándo les pavimenten a los a los alumnos". Esto para los alumnos que van al Cecyte y con gusto lo lo compartimos en instantes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nw6B9Mn6YEdPKd98f68_ihsiaMEcVcZi/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Locutor Jesús Riveros da lectura a comentario de radioescucha que reporta su inconformidad ante la venta de credenciales escolares en la Escuela Secundaria Técnica 48 Japón, ubicada en la colonia La Cañada. La denunciante señaló que la credencial tiene un costo de $60 pesos y que las autoridades del plantel informaron que por el momento no será utilizada hasta nuevo aviso, expresando que esta medida le parece un negocio irregular.</t>
+  </si>
+  <si>
+    <t>Bueno, y hablando de educación precisamente nos están por acá reportando, reportando que nos dicen: "Buenas tardes, sí yo le comento soy una madre de familia que estoy inconforme por una por una eh este credencial dice, sí por una credencial que están vendiendo en la Técnica 48 Japón ubicada en la colonia La Cañada. Su costo es de $60 pesos y dicen que por el momento no se ocupará hasta que les avisen. La verdad que opino todo es negocio".</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OyMm4diHKQJLQvaelnEZ6CnL8Ihmkc3A/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Hidalgo consolida liderazgo en indicadores educativos a nivel nacional</t>
+  </si>
+  <si>
+    <t>Déjeme compartirle la información que emite la Secretaría de Educación Pública y es que ayer, precisamente, el secretario Natividad Castrejón compareció ante el Congreso del Estado, donde informó que Hidalgo avanza en el fortalecimiento de su sistema educativo y escala una posición, una mejor posición para colocarse como el octavo estado del país con mejor desempeño en eficiencia terminal. A este logro se suma el progreso obtenido en el diagnóstico de los ejercicios integradores de aprendizaje y la inversión sostenida en infraestructura educativa, ciencia y tecnología, así como del deporte, que amplía las oportunidades de desarrollo para las y los estudiantes. Durante estos cuatro años, el proyecto educativo de la actual administración ha impulsado la formación de estudiantes capaces de transformar sus comunidades, fortalecer su identidad y contribuir a una sociedad más justa y humana. Cada trayectoria escolar suma al bienestar colectivo y nos acerca a un propósito común: sabernos un solo Hidalgo. Así lo expuso el secretario de Educación Pública, como le digo, durante su comparecencia ante las y los integrantes del Congreso del Estado, como parte de la glosa del cuarto informe del gobernador Julio Menchaca Salazar. En cuanto a indicadores, Hidalgo ha tenido significativas mejoras en todos los niveles para que las y los estudiantes permanezcan y concluyan sus estudios satisfactoriamente. En este contexto, Natividad Castrejón informó que la entidad mantuvo el 39% de la proporción de estudiantes que concluyen la educación superior por cada 100 que ingresan a primero de primaria. Este indicador sitúa a Hidalgo en el octavo lugar nacional, lo que representa un avance de una posición respecto al año anterior. Uno de los avances más sobresalientes se registró en educación media superior, donde la eficiencia terminal pasó del 63.2% en el ciclo escolar 2021-2022 a 75.6% en el 2024-2025, lo que significó un incremento de 12.4 porcentuales —puntos porcentuales—. En educación superior también se logró un importante incremento en eficiencia terminal, la cual avanzó de 69.6 a 84.5%, es decir, una mejora de 19. —perdón, de 14.9 puntos porcentuales—. En cuanto al bachillerato, con el propósito de ampliar las oportunidades educativas, el secretario destacó la incorporación de seis servicios de educación media superior que permitieron garantizar la presencia de al menos un plantel público de este nivel de bachillerato en cada uno de los 84 municipios de Hidalgo. A estas acciones se suman la creación de 12 nuevos servicios de educación media superior; dos son bachilleratos generales, dos telebachilleratos comunitarios y ocho operarán bajo el modelo de bachillerato nacional Margarita Maza para atender a jóvenes de 6 municipios y ofrecer alternativas flexibles que faciliten la continuidad de sus estudios. Asimismo, se iniciaron las gestiones para construir 10 planteles de telebachillerato comunitario con instalaciones propias en zonas rurales, todo eso mediante una inversión de 290 millones de pesos. Y una de las cosas que también destacó el secretario es la red de laboratorios STEM; subrayó que la entidad continúa fortaleciendo la formación científica y tecnológica de sus estudiantes en educación media superior y superior con esta red de laboratorios STEM, es una red, dijo, la más grande del país y son espacios que impulsan el aprendizaje práctico y se acercan a las y los jóvenes a disciplinas estratégicas como robótica, inteligencia artificial, automatización y drones, y actualmente 47 planteles cuentan cuentan con laboratorios STEM en beneficio de alrededor de 60,000 estudiantes. Y durante esta administración se han destinado 120 millones de pesos a estos espacios, de los cuales 30 millones corresponden al periodo reportado utilizado para equipar 11 nuevos laboratorios, estos espacios que han contribuido a impulsar el talento estudiantil; ejemplo de ello es la participación de 54 estudiantes de ocho instituciones de educación media superior y superior quienes asistieron al campamento mundial VEX Robotics 2026, celebrado en San Luis, Missouri, como parte de la delegación nacional, demostrando el potencial de las y los jóvenes hidalguenses en ciencia, tecnología e innovación. En este ámbito la entidad también destacó por ser sede de la primera competencia Girl Powered México 2025-2026, que reunió a 115 equipos de niñas y mujeres de 12 estados de la república y más de 3000 asistentes. Estaremos tocando otros tópicos, pero después de hacer una pausa, una pausa, por supuesto, y regresamos con más aquí en Enlace Hidalgo. Cerramos el tema de la Secretaría de Educación Pública y continuamos. Perfectos, bueno pues Natividad Castrejón informó que durante la administración se han destinado 2,700 millones de pesos a infraestructura educativa, de los cuales 780 millones corresponden al periodo reportado con acciones en alrededor de 1,500 planteles en beneficio de 160,000 estudiantes. Las obras incluyen la construcción y rehabilitación de aulas sanitarios, bardas perimetrales, canchas, techumbres e instalaciones eléctricas. A esta inversión se suman más de 4,400 millones de pesos destinados en 4 años a la entrega de útiles, uniformes, calzado y libros para alrededor de 570,000 estudiantes por ciclo escolar, apoyos que representan un alivio para la economía de miles de familias hidalguenses al reducir los gastos escolares y permitir que más recursos se destinen a otras necesidades del hogar, además de ampliar las oportunidades para que niñas, niños y jóvenes continúen sus estudios. Y en otros temas, también para fortalecer los aprendizajes mediante el acompañamiento docente para valorar los avances y las áreas de oportunidad, Castrejón explicó que durante el ciclo escolar 2025-2026 se aplicaron los ejercicios integradores del aprendizaje a 371,556 estudiantes de 3,237 escuelas con el objetivo de identificar las fortalezas en los cuatro campos formativos del plan de estudios. A partir de esta información señaló en se orientaron y decisiones también pedagógicas y acciones de acompañamiento. Para atender estas áreas, mediante el sistema de alerta temprana se focalizaron 722 escuelas prioritarias de preescolar, primaria y secundaria de donde alrededor de 4,000 docentes participaron en acciones de diagnóstico, acompañamiento, tutoría y seguimiento individualizado con énfasis en lectura, escritura y también en matemáticas. La infraestructura también deportiva de Hidalgo creció con la construcción de la ciudad deportiva de alto rendimiento, proyecto en el que se invirtieron 529 millones de pesos y que cuenta con instalaciones para la práctica de 35 disciplinas, además de espacios para albergar competencias nacionales. Este complejo impulsa la preparación de deportistas de alto rendimiento y amplía las oportunidades para las prácticas de deporte social en beneficio de más de 300,000 hidalguenses. Resalta, además, que durante estos cuatro años las y los deportistas hidalguenses de alto rendimiento obtuvieron 536 medallas en la Olimpiada Nacional y Paralimpiada, 161 de oro, 165 medallas de plata y 210 de bronce. En el periodo que se informa se obtuvieron 63 medallas y también ejercimos 16.7 millones de pesos para otorgar apoyos a 1,350 deportistas y también entrenadores. Natividad Castrejón subrayó que la formación integral también requiere atender el bienestar emocional y garantizar entornos seguros donde niñas, niños y adolescentes y jóvenes puedan desarrollarse en condiciones de respeto y convivencia pacífica. Mediante el programa de acompañamiento socioemocional, la SEP ha atendido a 820,000 integrantes de la comunidad escolar durante 4 años. Las acciones implementadas en 4,500 planteles de educación básica, media superior y superior promueven la empatía, la gestión y regulación emocional, así como la resolución pacífica de conflictos. En materia de prevención y atención de la violencia, se actualizaron y pusieron en marcha protocolos para prevenir, detectar y atender el acoso y el maltrato escolar en todas las escuelas de educación básica. Asimismo, Hidalgo cuenta con un marco local de convivencia escolar actualizado que protege los derechos de niñas, niños y adolescentes. Natividad Castrejón reiteró que el compromiso de la política educativa es generar que todas y todos los estudiantes aprendan y permanezcan también en las aulas y también también también que concluyan sus estudios con las herramientas necesarias para construir su proyecto de vida, sin importar su lugar de origen y las condiciones económicas de su familia. Reconoció, además, que aún existen retos para fortalecer los aprendizajes, garantizar entornos escolares seguros e impulsar el desarrollo integral y el deporte, por lo que es indispensable trabajar cada día, sumar esfuerzos y reconocer el compromiso de quienes hacen posible la educación en el Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Bl-Ta1xxrMLot2udu1rropO1nb3_euHs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Durante su comparecencia ante el Congreso de Hidalgo, la secretaria de movilidad y transporte, Lyzbeth Robles Gutiérrez, informó sobre las acciones de su dependencia en el marco de la glosa del cuarto informe del gobernador Julio Menchaca Salazar. Ante cuestionamientos de la diputada Claudia Lira Luna sobre la problemática del tráfico en las horas pico al sur y centro de Pachuca, la secretaria indicó que se realizarán análisis técnicos mediante cámaras con inteligencia artificial instaladas en puentes del bulevar Felipe Ángeles. Asimismo, reiteró que la legislación vigente protege y establece la exclusividad del carril confinado para el transporte masivo (BRT) con el fin de garantizar una movilidad segura y eficiente.</t>
+  </si>
+  <si>
+    <t>Y esta mañana compareció en el Congreso de Hidalgo la maestra Lyzbeth Robles Gutiérrez, secretaria de movilidad y transporte. El presidente del Congreso, Andrés Velázquez, dio la bienvenida a la maestra Lyzbeth  Robles Gutiérrez.
+...la escuela, las autoridades, ir al trabajo o recibir atención médica comienza para muchas personas con la posibilidad de trasladarse. La movilidad forma parte de las oportunidades que una comunidad puede aprovechar cada día. Hoy recibimos a la maestra Lyzbeth Robles Gutiérrez, secretaria de movilidad y transporte, en el marco de la glosa del cuarto informe del gobernador, el licenciado Julio Menchaca Salazar. Secretaria, sea usted bienvenida a esta soberanía. En esta ruta informativa en este congreso de Hidalgo la maestra Lyzbeth  Robles Gutiérrez emitió mensaje, da a conocer el informe y también respondió algunas cuestiones. La diputada Claudia Lira Luna preguntó acerca de un exhorto que realizó a esa Secretaría de Movilidad y Transporte para llevar a cabo mesas de análisis o estudio para dar salida y que ya no existiera el problema de tráfico en las horas pico en el sur de Pachuca. Escuchemos a la legisladora Claudia Lira Islas.
+...un análisis o un estudio para dar viabilidad y que no exista ese problema de tráfico precisamente en las horas pico en los tramos de la de la del sur de Pachuca y en algunos tramos del centro de Pachuca.
+Señor secretario, por favor. Es cuánto. En esta respuesta que se dio durante ese marco, también Lyzbeth  Robles señaló, este exhorto en su momento no había llegado precisamente a su oficina, por lo tanto, informó que se están llevando a cabo, desde luego también, ya a sacar vehículos y habrá mesas. En este instante se mencionó, se va a llevar a cabo el análisis clínico con cámaras para medir el número de unidades que circulan y entonces estar en posibilidades de realizar acciones. También subrayó que existe una ley en materia de transporte vigente en torno a carril exclusivo y que contempla la utilización de un carril único para el transporte público. Esa ley tiene más de 10 años. La respuesta, Lyzbeth  Robles Gutiérrez, señaló una explicación clara.
+Que hizo el anuncio de que estaríamos realizando un análisis por medio de unas cámaras que se van a situar en tres puentes sobre el bulevar Felipe Ángeles, en donde tenemos también puentes a cargo del Sistema Integrado de Transporte Masivo, y que en esas cámaras que tienen utilización de inteligencia artificial nos va a permitir también medir el número de unidades conjuntamente con la información que pueda ser proporcionada por seguridad pública y por seguridad pública y tránsito municipal de Pachuca. Que una vez que tengamos eso y que a la vez se haga la reunión correspondiente o las acciones inherentes a través de la coordinación que en su momento se origine por la Secretaría de Gobierno, estaremos en posibilidad de pronunciarnos de fondo. En ese momento yo mencioné lo que legalmente le correspondía a la Secretaría y al organismo mencionado en torno al carril exclusivo. El carril exclusivo la ley establece que se debe de privilegiar obviamente para la operación y eficacia adecuada del transporte masivo, insisto que fue originado hace más de 10 años con una infraestructura en la cual cuenta con además de puentes y estaciones con el carril adecuado y exclusivo para que pueda brindar un servicio eficaz con las frecuencias de pasos correspondientes. Y además es un tema de seguridad vial. Cuando las unidades de vehículos particulares transitan sobre un carril exclusivo, el congestionamiento se extiende no solamente a los carriles en donde de manera ordinaria transitan los vehículos particulares, sino que se extiende también ese congestionamiento vial hacia el carril exclusivo, lo cual incrementa el congestionamiento a lo ancho de toda la vialidad. Las vialidades son de todas y de todos y también debemos aprender a compartir las y está apegado a la ley, a las políticas internacionales, nacionales y estatales, el hecho de que exista carril confinado para que las unidades de transporte masivo, que son generalmente en este caso a través de unidades BRT, se pueda llevar a cabo de manera óptima.
+Bueno, en esta materia la respuesta entregada esta mañana, el día de mañana tendremos más la continuidad, es un adelanto de lo que se menciona, pero bueno, es un asunto de ley. Cuando se llevó a cabo la construcción de este instrumento de movilidad, pues la ley señala es un carril exclusivo, es un carril único para el transporte público. Y efectivamente, si se abre entonces, pues ya no solamente va a haber dos carriles saturados, sino van a ser tres. Aquí el tema está también en la educación vial que tenemos cada uno de las y los ciudadanos. El día de ayer por la tarde, vemos que esto es muy común. Hay un el carril derecho, perdón, para habilitarse y salir hacia en Pachuca hacia la parte sur, pues está muy comprometido. Eh asomar la vuelta y procurar meterse y entonces esto genera que los demás vehículos también pues vayan atorándose, enfrentándose y haciéndose nudos. También depende mucho, desde luego, no es ánimo de justificar a nadie, pero lo hemos comentado. En cuanto al hecho de las motocicletas, el día de ayer también manejando, vemos un joven haciendo malabares, subiéndose a su motocicleta, casi parado en los asientos, metiéndose entre un vehículo y otro, pues todos esos son son riesgos y desde luego también con la lluvia, con todo esto, si se habilitan los vehículos al carril de transporte público, pues obviamente va a generar más conflicto, pero es un tema, como se subrayó esta mañana, es un tema de ley. Es la ley la que determinó así que se hiciera este carril único, pero esa ley tiene diez años.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lBQoZXW74i8PDOlrAoo5FkQbpdeHcX9o/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Andrés Velázquez Vázquez, Claudia Lilia Luna</t>
+  </si>
+  <si>
+    <t>UPLAPH/Bol.160/2026</t>
+  </si>
+  <si>
+    <t>Durante su intervención, Onésimo Serrano destacó que a partir de la actualización del Plan Estatal de Desarrollo se ha brindado acompañamiento a las dependencias y organismos del gobierno de Hidalgo para alinear sus programas sectoriales, institucionales y especiales, actualizando cerca de 84 instrumentos de planeación y capacitando a los 84 municipios con una metodología homologada para los periodos 2024-2027. Asimismo, señaló la importancia de la coordinación interinstitucional y la participación ciudadana mediante el COPLADEIH y los COPLADEM, habiendo participado en más de 300 sesiones para definir obras y acciones prioritarias con las comunidades.</t>
+  </si>
+  <si>
+    <t>Precisamente vamos a escuchar el audio de Onésimo, Onésimo Serrano.
+“A partir de la actualización del Plan Estatal de Desarrollo, acompañamos a las dependencias y organismos del gobierno de Hidalgo en la alineación de sus programas sectoriales, institucionales y especiales. Cerca de 84 instrumentos de planeación se están actualizando. Asimismo, capacitamos a 84 instancias de planeación municipal de Hidalgo con una metodología homologada, para contar con una visión articulada en la entidad. Con ello se actualizan los planes municipales de desarrollo 2024-2027. En ambos casos, elaboramos guías metodológicas y brindamos capacitación y acompañamiento técnico. Pero la planeación no se limita a establecer objetivos y programas, requiere de coordinación entre las instituciones, los municipios y la participación ciudadana. Para ello, a través de las sesiones del Comité de Planeación para el Desarrollo del Estado, el COPLADEIH, integrado por representantes de este honorable Congreso, del Senado, de la Cámara de Diputados, de las delegaciones federales, de los municipios, de las y los titulares de las dependencias del Poder Ejecutivo estatal, así como de representantes de diversos sectores de la sociedad, evaluamos los procesos de planeación institucional, articulamos esfuerzos interinstitucionales e incorporamos las aportaciones de sus integrantes en la formulación, ejecución, evaluación y actualización de los instrumentos de planeación. Esta estrategia para el desarrollo también busca fortalecer los sistemas municipales de planeación democrática. Durante el periodo que se informa, hemos participado en más de 300 sesiones de los COPLADEM, espacios donde cada municipio, en ejercicio de su autonomía, identifica junto con su comunidad las obras y acciones prioritarias. Como escuchamos, Onésimo Serrano destacó que la planeación se ha consolidado como una herramienta para articular la participación ciudadana, la información territorial, el conocimiento científico y la coordinación institucional con el propósito de orientar las decisiones públicas hacia las necesidades de las y los hidalguenses”.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JXEiey-1qoIi5Myc4TcvEGH7EFAM9m6Y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Uno de los ejes emblemáticos de la administración encabezada por el gobernador Julio Menchaca Salazar ha sido la educación, logrando posicionar a Hidalgo en el octavo lugar nacional en eficiencia terminal. Se destaca que el 39% de los alumnos que ingresan a primaria logran concluir la educación superior, incrementando la eficiencia terminal en 12.4 puntos porcentuales. Asimismo, la entidad cuenta con la red de laboratorios de ciencia y tecnología más grande del país, abarcando 47 planteles que benefician a cerca de 60,000 estudiantes, además de haberse destinado más de 4,400 millones de pesos en apoyos a la economía en este sector.</t>
+  </si>
+  <si>
+    <t>Uno de los temas emblemáticos del gobierno encabezado por Julio Menchaca Salazar es la educación. Hidalgo, señalaba yo, ha sido uno de los estados, las entidades que una mayor y mejor inversión se han colocado en la educación. Octavo lugar nacional en eficiencia terminal. Hidalgo avanzó una posición, alcanzó un 39% de estudiantes que sí concluyen la educación superior por cada 100 que ingresan a primaria. Hay una mayor conclusión de estudios, la eficiencia terminal aumentó en 12.4 puntos porcentuales. Hay una mayor cobertura educativa, liderazgo en ciencia y tecnología, Hidalgo cuenta con la red de laboratorios más grande del país con 47 planteles que benefician cerca de 60,000 estudiantes. Apoyos a la economía, como ya escuchábamos, más de 4,400 millones de pesos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YcgpEF5MTlYyMluzp0Gxi8tkI9wxZk1y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Durante su comparecencia ante el Congreso del Estado como parte de la glosa del informe de gobierno de Julio Menchaca Salazar, el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdés, informó que la entidad escaló al octavo lugar nacional en eficiencia educativa. El funcionario destacó el incremento en la conclusión de estudios de nivel medio superior y superior, así como una inversión acumulada de 2,700 millones de pesos en infraestructura, de los cuales 780 millones se destinaron recientemente a 1,500 planteles. Asimismo, resaltó una inversión de más de 4,400 millones de pesos en la entrega de útiles y uniformes escolares para aproximadamente 570,000 alumnos por ciclo escolar.</t>
+  </si>
+  <si>
+    <t>Continuamos esta tarde en la información de las comparecencias en el Congreso del Estado de Hidalgo el día de ayer, primera hora estuvo el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdés. Tienes la información.
+Hidalgo avanzó al octavo lugar nacional en eficiencia educativa, así lo informó el secretario de Educación Pública Estatal, Natividad Castrejón Valdés, durante su comparecencia ante el Congreso del Estado como parte de la glosa del informe de gobierno de Julio Menchaca Salazar. 
+Tenemos una convicción firme: educar es ampliar las posibilidades de transformar el presente y el futuro de Hidalgo. 
+Ante las y los legisladores, el funcionario presentó los principales indicadores y acciones desarrollados en el sector educativo, entre los que destacó el incremento en la conclusión de estudios de nivel medio superior y superior, así como las inversiones destinadas a infraestructura, apoyos escolares y bienestar de la comunidad educativa. En cuanto a materia de infraestructura, el titular de la SEPH reportó una inversión acumulada de 2,700 millones de pesos durante la actual administración; de ese monto, 780 millones de pesos se destinaron recientemente a trabajos en 1,500 planteles educativos. Entre otros temas y respecto a los apoyos para estudiantes, el secretario informó que se han invertido más de 4,400 millones de pesos en la entrega de útiles y uniformes escolares, con una cobertura aproximada de 570,000 alumnos por ciclo escolar.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eVmC89aMtg5nhNWYD-7uctVrA4ecpOzM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, anunció que el coordinador jurídico del estado, Raúl Serret Lara, prepara una denuncia penal contra la plataforma Uber por operar en Pachuca de manera ilegal y sin los permisos correspondientes. El mandatario estatal señaló que la ley contempla sanciones tanto para quienes promueven el servicio irregular como para aquellos que lo utilizan con fines de lucro sin estar debidamente registrados. Asimismo, aclaró que aunque la legislación permite concursar por una concesión estatal, prestar el servicio operando de forma arbitraria constituye una ilegalidad.</t>
+  </si>
+  <si>
+    <t>De una vez le informo, de una vez vámonos tendidos. En este hilo informativo, el gobernador de Hidalgo, Julio Menchaca Salazar, dio a conocer que el coordinador jurídico del gobierno del Estado, Raúl Serret Lara, integra ya una carpeta formal para iniciar una denuncia penal contra Uber, luego de que la empresa habilitara en su plataforma la opción de operar en Pachuca de manera ilegal. Asimismo, se ha señalado que la legislación penal contempla disposiciones para sancionar el uso indebido de un servicio público, en este caso, el mandatario explicó, podrían incurrir en una falta tanto quienes promueven la plataforma como quienes de manera no consciente y con la intención de generar un ingreso son engañados. Mire usted, eh utilizar una plataforma, que se comentaba el día de ayer, bueno, pues, Dios no lo quiera, algo sucede, ¿no? ¿Y quién responda? No va a haber quien responda. Ni por usted, ni por lo que suceda. ¿Por qué razón? Porque no están registrados. O sea, es ilegal. El titular del Ejecutivo estatal reconoció que la legislación vigente permite sí que las empresas que brindan servicio de transporte por aplicaciones puedan concursar por una concesión en el estado, sin embargo, una cosa es concursar y que se apruebe, y otra cosa, decir, ya estoy trabajando, eso es ilegal. Una pausa, regreso.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-mdOTt5QJ9KjW0_NNca5gpHumv4dv_eW/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Raúl Serret Lara</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hoFcwsY6qo0Gd4usbJ97dHcCFwDpeBz5/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Pemex</t>
+  </si>
+  <si>
+    <t>Raúl Ojeda Zubietta, Alejandro Velázquez Mendoza</t>
+  </si>
+  <si>
+    <t>Cultura/Bol.713/2026</t>
+  </si>
+  <si>
+    <t>Caravana Cultural llenará de arte Xochicoatlán</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Caravanas Culturales</t>
+  </si>
+  <si>
+    <t>Xochicoatlán</t>
+  </si>
+  <si>
+    <t>Y por otra parte, le comento que la Secretaría de Cultura estatal anunció una serie de actividades artísticas para las familias de Singuilucan. El programa se realizará hoy, 21 de octubre, en la Plaza Bicentenario; reunirá a cinco agrupaciones con intérpretes locales y de otras regiones. El evento forma parte de la caravana cultural cuyo objetivo es acercar espectáculos escénicos y musicales a las regiones del estado, así como fomentar el arte y las tradiciones. Cabe señalar que este día pues esta caravana tendrá una duración de más de 3 horas y va a comenzar con el grupo de danza Nexti, integrado por estudiantes del CBTA número 6, esto a las 3:30 de la tarde. 15 horas con 35 minutos es la hora exacta que da a conocer para el inicio de estas actividades. A las 4 de la tarde con 10 minutos tiene se tiene programada la presencia de Los Bohemios de Hidalgo y a las 5 de la tarde subirá al escenario el grupo de danza Santa María Magdalena, dedicado a preservar los bailes tradicionales de su comunidad. Las últimas dos actuaciones estarán vinculadas con la música popular. A las 5:30 de la tarde tocará la Banda de Viento Tradicional Tres Estrellas de Oro, mientras que el Trío Encanto Juvenil cerrará la jornada a partir de las 6 de la tarde. Es lo que se tiene programado para este día en el municipio de Singuilucan, la Plaza Bicentenario de este municipio serrano de Singuilucan con la llegada de las caravanas culturales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_x5j3W7UGU1NpJvDCPIagH1ngfsuUMP5/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El Gobierno de Julio Menchaca Salazar fortalece la planeación estatal con participación, evaluación e innovación.</t>
+  </si>
+  <si>
+    <t>En el calendario de comparecencias también ya tocó el turno a nombre de la Unidad de Planeación y Prospectiva, pues brindar la información a los integrantes de la Sexagésima Sexta Legislatura local en la glosa del cuarto informe de gobierno, al encargado del despacho de esta unidad, Onésimo Serrano Rivera, quien destacó que el trabajo de esta institución se organiza en cuatro ejes que forman parte de un mismo ciclo: planear permite, dijo, definir el rumbo; implementar, lleva las prioridades al territorio; evaluar ayuda a conocer los avances y corregir lo que haga falta; e innovar facilita la relación de las personas con las instituciones. Como parte de la actualización del Plan Estatal de Desarrollo, dijo, se incorporaron 26,367 propuestas ciudadanas en los nuevos nueve ejes generales y tres ejes transversales que integran este plan, con un horizonte hacia 2040. A partir de este instrumento, la unidad acompañó la elaboración de 84 instrumentos y la actualización de los planes municipales de desarrollo 2024-2027. Las 84 instancias municipales de planeación recibieron capacitación con una metodología homologada. La coordinación con los municipios también se refleja en la participación de la unidad en más de 300 sesiones de los comités de planeación para el desarrollo municipal. En materia metropolitana, Hidalgo pasó de un municipio reconocido a ocho dentro de la zona metropolitana del Valle de México. La actualización del programa de ordenación de esta zona ha incluido sesiones técnicas, reuniones de trabajo, talleres participativos, consultas ciudadanas y consultas a pueblos y comunidades indígenas. Entre los proyectos de planeación territorial se encuentran tres programas parciales de desarrollo urbano vinculados con las nuevas rutas ferroviarias, un plan de movilidad urbana sustentable para siete municipios de la zona metropolitana de Pachuca y la estrategia de parcelas demostrativas en el marco del Programa Nacional de Tecnificación. En estas últimas se han observado ahorros de agua de hasta 80% mediante riego por goteo. A través de la Comisión Estatal para el Desarrollo de los Pueblos Indígenas, los programas de atención llegaron a 45 municipios con presencia indígena. Más de 21,000 personas fueron beneficiadas con las macrojornadas "Haber, Haber". La política en ciencia, tecnología e innovación combina formación, financiamiento y reconocimiento. Este año se sumaron 115 personas becadas y se contemplan 105 iniciativas científicas de innovación. También se impulsa proyectos aplicados como el laboratorio de nuevos alimentos, este también la participación fundamental se destacó en esta comparecencia de las mujeres en el desarrollo científico. La evaluación permite revisar si las políticas públicas están produciendo los resultados esperados. El Laboratorio de Políticas Públicas suma casi 100 productos de información y 35 instrumentos técnicos, entre plataformas, tableros y mapas web, trabajo que fue reconocido por el Sistema Nacional de Información Estadística y Geográfica del INEGI. En materia de digitalización y simplificación administrativa, se eliminaron 296 requisitos en 118 trámites cotidianos en coordinación con seis municipios; de estos, 83 ya cuentan con plazos de resolución más cortos. A nivel estatal, se se modelaron más de 300 trámites, se simplificaron 202 trámites y servicios y se activaron siete trámites en línea del Registro Civil. Durante su intervención, Onésimo Serrano Rivera subrayó que la planeación debe mantenerse vinculada con el territorio, reconocer las brechas que todavía existen y utilizar información para fortalecer las decisiones públicas. Así la comparecencia del encargado del despacho de la Unidad de Planeación y Prospectiva del Gobierno del Estado.</t>
+  </si>
+  <si>
+    <t>Congreso del Estado Hidalgo</t>
+  </si>
+  <si>
+    <t>A raíz de los conflictos regulatorios con el servicio de Uber en el estado de Hidalgo, donde el gobierno estatal anunció denuncias por operar sin permisos, comenzó a promocionarse en Pachuca y Tulancingo una nueva plataforma mexicana llamada "Pronto". Esta aplicación ofrece servicios de transporte de pasajeros y paquetería bajo un modelo de suscripción fija para los conductores y sin comisión por trayecto, operando de manera digital. Sin embargo, la entrada de estas plataformas en la entidad continúa generando cuestionamientos por parte de las autoridades y el gremio transportista debido a la falta de concesiones formales bajo la legislación vigente en el estado.</t>
+  </si>
+  <si>
+    <t>Y, pues bueno, a raíz de este, eh pues de este conflicto entre entre Uber y el gobierno del Estado de Hidalgo, que por cierto el gobernador informó, informó que la coordinación general jurídica de su gobierno, pues prepara una denuncia contra Uber por su presunta operación sin los permisos correspondientes y, pues además, pidió a los usuarios del transporte público denunciar formalmente cualquier maltrato o agresión de los conductores. Eh, pues bueno, eh dijo que esta denuncia podrá presentarse en esta misma semana, pero ayer comenzó a circular en redes sociales otra aplicación, otra plataforma que está ofreciendo también el servicio de transporte. Esta plataforma, que se llama Pronto y que es de origen mexicano, comenzó ya a promoverse también en la capital hidalguense, pero también aquí en Tulancingo y usted recordará que hace unos meses intentó también publicitarse, ofrecer el servicio, pero, pero pues no se lo permitieron tanto el gremio de de transportistas como, pues obviamente el gobierno del Estado, por eh pues por no contar con la concesión correspondiente. Le comparto con información de la silla rota que además de Uber, esta aplicación comienza a promoverse en distintas ciudades del Estado de Hidalgo, entre ellas Pachuca y Tulancingo, conocida como Pronto, una plataforma mexicana cuya publicidad ya anuncia su entrada también a Pachuca y que conecta personas que necesitan un traslado con conductores registrados en su sistema. La difusión de estos anuncios, pues, obviamente dio de qué hablar después de que eh pues usuarios de Uber ya hayan reportado que pueden cotizar y solicitar viajes en Pachuca y, en el caso de Pronto, la publicidad anticipa su llegada, aunque la información disponible no precisa una fecha de inicio, las zonas que atenderá o el número de unidades que tendrá en la ciudad. La plataforma permite ingresar un destino, consultar el precio estimado antes de confirmar el servicio y entre sus modalidades aparecen Clásico, para transporte de pasajeros y Pick-Up, destinado al traslado de paquetes y otros artículos, y los pagos pueden realizarse en efectivo o mediante un monedero electrónico de acuerdo con la descripción de la empresa. También ha informado que tienen un botón SOS con el cual dan seguimiento al recorrido en tiempo real y la posibilidad de compartir el viaje, que el usuario puede consultar información del conductor y del vehículo, además de comunicarse mediante un chat interno sin proporcionar su número telefónico. Otras funciones es el programa llamado Socio Pronto, con categorías Plata, Oro, Platino y Diamante, y según la compañía estos niveles ofrecen beneficios como prioridad de asignación en horas de mayor demanda, atención preferente y opciones para viajar nuevamente con conductores favoritos. Estas características generales anunciadas por la plataforma, todavía falta conocer cuáles estarán disponibles desde su entrada aquí en el estado de Hidalgo. Para quienes conducen, Pronto promueve un modelo sin comisión por trayecto y la empresa afirma que los operadores conservan el 100% de lo cobrado por sus viajes bajo un esquema de suscripción fija y pueden elegir sus horarios de conexión. Esta aplicación que eh pues aseguran ya ya tiene presencia aquí en Hidalgo, por lo menos tiene un antecedente, ya que comenzó a anunciarse desde 2025 mediante espectaculares y publicaciones digitales, pero bueno, su su operación aquí en Tulancingo ha generado diversos cuestionamientos sobre las autorizaciones necesarias para prestar el servicio. Y, pues bueno, eh la promoción de estas plataformas ocurre mientras el gobierno mantiene su advertencia sobre los servicios de transporte que funcionen sin autorización, y al referirse a Uber sostuvo que la legislación vigente no contempla su operación en las condiciones propuestas, es decir, hay que modificar la ley aquí en el Estado para permitir la operación de este tipo de plataformas digitales que ofrecen el servicio de el conocido ahora como transporte individual. Son 10 de la mañana con 20 minutos, vamos a hacer una pausa nuevamente y regresamos desde la capital hidalguense con más aquí en Enlace Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1X8MJc-AkLJW5nUhJu1f1lBvyEoznKloY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Silla Rota Hidalgo</t>
+  </si>
+  <si>
+    <t>Continuamos en Pachuca, en esta primera emisión de Enlace Hidalgo, y le voy a compartir información de la comparecencia del secretario de Educación Pública en la entidad, Natividad Castrejón Valdez, ante la Sexagésima Sexta Legislatura Local. En este ejercicio de rendición de cuentas, pues consideró el como uno de los principales logros el fortalecimiento en el sistema educativo y escalar una posición para colocarse como el octavo estado del país con mejor desempeño en eficiencia terminal. A este logro se suma el progreso obtenido del diagnóstico de los ejercicios integradores del aprendizaje y la inversión sostenida en infraestructura educativa, ciencia, tecnología y deporte, que amplía las oportunidades de desarrollo para las y los estudiantes. Durante estos cuatro años, el proyecto educativo de la actual administración ha impulsado la formación de estudiantes capaces de transformar sus comunidades, fortalecer su identidad y contribuir a una sociedad más justa y humana. Cada trayectoria escolar suma al bienestar colectivo y nos acerca a un propósito común, sabernos un solo Hidalgo. Así lo expuso el secretario de Educación Pública en la entidad, Natividad Castrejón Valdez, durante esta comparecencia ante los integrantes, las y los integrantes de la Sexagésima Sexta Legislatura Local. La educación en Hidalgo, dijo, ha tenido significativas mejoras en todos los niveles para que las y los estudiantes permanezcan y concluyan sus estudios satisfactoriamente. En este contexto, destacó que la entidad se mantuvo, mantuvo el 39% de la proporción de estudiantes que concluyen la educación superior por cada 100 que ingresan a primero de primaria. Este indicador sitúa a Hidalgo en el octavo lugar nacional, lo que representa un avance de una posición respecto al año anterior. Uno de los avances más sobresalientes se registró en la educación media superior, donde la eficiencia terminal pasó del 63.2% en el ciclo escolar 2021-2022 al 75.6% en el ciclo 2024-2025. La educación superior también se logró un importante incremento en eficiencia terminal, avanzó del 69.6 al 84.5%. Con el propósito de ampliar las oportunidades educativas, el secretario destacó la incorporación de seis servicios de educación media superior que permitieron garantizar la presencia de al menos un plantel público de este nivel en cada uno de los 84 municipios. También subrayó que la entidad continúa el fortalecimiento de la formación científica y tecnológica de sus estudiantes en educación media superior y superior, superior con la red de laboratorios STEM más grande del país. Actualmente, 47 planteles cuentan con laboratorios STEM en beneficio de alrededor de 60,000 estudiantes. También, Natividad Castrejón informó que durante la administración estatal se han destinado 2,700 millones de pesos a infraestructura educativa, de los cuales 780 millones corresponden al periodo reportado con acciones en alrededor de 1,500 planteles y beneficio para 160,000 estudiantes. Eh, comentó que para valorar los avances y las áreas de oportunidad, durante el ciclo escolar 2025-2026 se aplicaron los ejercicios integradores del aprendizaje a 371,456 estudiantes de 3,237 escuelas con el objetivo de identificar las fortalezas en los cuatro campos formativos del plan de estudio. De en otro tema, también eh dijo que se apuesta en Hidalgo por el talento deportivo, con la inversión en alto rendimiento, la infraestructura deportiva de Hidalgo creció con la construcción de la Ciudad Deportiva de Alto Rendimiento, se invirtieron 529 millones de pesos y cuenta con instalaciones para la práctica de 35 disciplinas deportivas. Y en otros temas luego ya a pregunta de medios de comunicación, el secretario de Educación Natividad Castrejón también se refirió a la seguridad en los planteles educativos. Este es parte de lo que dijo el titular de los servicios educativos en la entidad.
+Al contrario, el los daños ocasionados por las lluvias en las semanas eh o de lo que va de del ciclo escolar, eh se tiene que ver en otro programa diferente al tema de anegada. Ya tanto planeación como como la Dirección General del INIFEX están haciendo la revisión de los daños eh ocasionados para poder hacer ya un programa. Eh primero, si se requiere el apoyo de intervención del seguro institucional y si no eh de la Secretaría. Pero eh tenemos la obligación y la instrucción del gobernador de dar respuestas eh prontas a las comunidades educativas que sean afectadas. Eh de los reportes en lo que va del año, llevamos 228 reportes en este ciclo escolar, y del tema de la introducción de armas, conozco eh solo dos, conozco el de Huasca, que fue el más sonado eh mediáticamente, eh fue en la escuela Secundaria General 3 de Gobierno Manzano, eh donde un alumno aportaba un arma eh calibre 22 con algunos cartuchos útiles. Eh, tuvimos otro reporte 
+Bien, esto es parte también de la el intercambio de información con medios de de comunicación por parte del secretario de Educación Pública en la entidad, Natividad Castrejón. Vámonos a la pausa, regresamos con mucho más en Enlace Hidalgo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NDxnI2doaqJ1DVdVPTYD0BK2B7_8MVjj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Bien, y por otra parte ya David Cárdenas nos ha compartido información acerca de estas aportaciones que realiza Petróleos Mexicanos al gobierno del Estado. Le complemento esta información comentándole que fue en las instalaciones de la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, donde el gobernador Julio Menchaca encabezó la entrega de equipamiento por 78 millones 614,370 pesos, resultado de las gestiones realizadas ante Petróleos Mexicanos, que desde 2022 han permitido a Hidalgo recibir donaciones por más de 654 millones de pesos para fortalecer los servicios públicos, la infraestructura carretera, salud y educación. En este contexto, el titular de la oficina del despacho del Poder Ejecutivo, Alejandro Velázquez Mendoza, externó el reconocimiento a la presidenta Claudia Sheinbaum y al personal de Pemex por el respaldo permanente al desarrollo de la entidad. Esto es parte de lo que mencionó Alejandro Velázquez Mendoza.
+Este encuentro va mucho más allá de la recepción administrativa de estas unidades y de la maquinaria que hoy tenemos aquí. Nos recuerda que la riqueza del país cobra sentido pleno únicamente cuando regresa al pueblo, convertida en obras, en infraestructura, en justicia social. Esta sinergia institucional ha permitido que de 2022 a la fecha hayamos gestionado más de 654 millones de pesos en donaciones acumuladas para fortalecer la infraestructura local.
+Y por su parte, el gobernador Julio Menchaca, como ya nos ha comentado David Cárdenas, se refirió al compromiso, a la solidaridad de Petróleos Mexicanos con el pueblo hidalguense. Así lo comentó el mandatario estatal.
+El abandono durante mucho tiempo ha sido atacado, ha sido trabajado por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, atendiendo el compromiso que tenemos con nuestra patria chica y ahí encontramos solidariamente a Pemex.
+Bien, esto es parte de lo que sucedió en esta entrega, esta nueva entrega de equipamiento por parte de Petróleos Mexicanos, con lo cual se suman ya 654 millones de pesos otorgados por la empresa nacional al estado de Hidalgo en diferentes formas para apoyar el desarrollo de la entidad.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FY-oAnuB-v6Ex7fkKXgLrXMmVYQ0M-8X/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>PEMEX</t>
+  </si>
+  <si>
+    <t>Alejandro Velázquez Mendoza, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Y le comparto este dato que le había comentado al inicio de este espacio informativo. Como parte de las acciones de prevención y promoción de la salud, la Secretaría de Salud mantiene el llamado a la población para fortalecer las medidas de autocuidado durante la actual temporada de frío y con especial atención a los grupos más vulnerables. De acuerdo con las cifras epidemiológicas actuales, la entidad registra 380,323 casos de infecciones respiratorias agudas, lo que representa un decremento de 8.2% respecto al mismo periodo de 2025, cuando se contabilizaron 414,106 casos. Los municipios con mayor número de casos son Pachuca, Tulancingo, Tula, Ixmiquilpan y Actopan. Por lo anterior y con el curso del actual frente frío, la Secretaría de Salud recomienda abrigarse adecuadamente, evitar cambios bruscos de temperatura, mantener una alimentación equilibrada, lavarse las manos frecuentemente y practicar el estornudo de etiqueta. También invita a revisar y complementar esquemas de vacunación contra influenza, COVID-19 y neumococo, conforme a las indicaciones correspondientes. Por supuesto, el hecho de que disminuyan las cifras respecto al año pasado de infecciones respiratorias agudas no implica bajar la guardia, por el contrario, implica que algunas cosas pues están realizándose de manera adecuada, que estamos contribuyendo de manera adecuada para que esto suceda de esta manera y pues hay que seguir en ese camino, en ese tenor. Le comparto lo que dice al respecto Rubí Vargas Vargas, ella es la coordinadora de comunidades y municipios de la Subsecretaría de Salud en la entidad.
+...temporada de frío o temporada invernal se incrementan de manera importante las enfermedades respiratorias. Por esta razón, la Secretaría de Salud fortalece las acciones de promoción y difusión sobre recomendaciones para enfrentar efectos negativos a la salud de forma prioritaria en grupos vulnerables como menores de 5 años, adultos mayores, personas en situación de calle o pobreza extrema. Entre las medidas preventivas que podemos compartir con la población en general son pues lavarse las manos de forma frecuente antes de consumir o preparar alimentos, después de utilizar el baño y en especial después de tener contacto con personas enfermas. Cubrir nariz y boca al toser o estornudar con el ángulo del codo, lo que llamamos estornudo de etiqueta o bien hacerlo con un pañuelo. Esto disminuirá el riesgo de contagio de las personas a nuestro alrededor. Abrigarse con ropa adecuada como gorro, guantes, bufanda, evitar en lo posible los cambios bruscos de temperatura y corrientes de aire frío, consumir suficientes líquidos, consumir frutas y verduras ricas en vitaminas A, C y D, importante vacunarse contra influenza y COVID, además de neumococo de acuerdo a la edad correspondiente.
+Bien, es lo que dice la responsable de la coordinadora de comunidades y municipios de la Subsecretaría de Salud, Rubí Vargas, y bueno, hacer énfasis en esto de que ante síntomas como fiebre, tos, escurrimiento nasal o cansancio es importante evitar la automedicación y acudir a la valoración médica, sobre todo si se presenta dificultad para respirar o dolor torácico, bueno, estos ya son síntomas más delicados y evidentemente es muy importante acudir de inmediato ante el especialista en salud.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16VXHs2GgPi4tRBpFohdec1YJhdeLMYgE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Vanesa Escalante</t>
+  </si>
+  <si>
+    <t>En la conferencia matutina del gabinete de energía, se destacó el papel estratégico de Petróleos Mexicanos (Pemex) en la economía nacional y su impacto en el estado de Hidalgo. El gobernador Julio Menchaca Salazar informó sobre una gestión histórica con Pemex superior a los 654 millones de pesos, la cual incluye un reciente paquete de apoyo con 5,000 toneladas de asfalto, equipo de salud y maquinaria. Por su parte, el director de Pemex, Juan Carlos Carpio, señaló que la producción de barriles diarios se mantiene estable y la refinación ha incrementado al 81% en comparación con 2018, impulsada por la operación constante de las refinerías, la refinería Olmeca y la modernización de la planta ubicada en Tula. Asimismo, se resaltó una inversión cercana a los 6,600 millones de pesos destinada a proyectos comunitarios y caminos en la región entre 2025 y 2026, informó David Cárdenas durante su colaboración matutina.</t>
+  </si>
+  <si>
+    <t>..Y déjame saludar ya, con mucho gusto ya lo tengo en la línea telefónica a nuestro colaborador y amigo David Cárdenas. David, muy buenos días, ¿cómo estás?
+Buenos días, Jesús. Buen día, este gran auditorio. Dando seguimiento a la conferencia de la prensa, de la Presidenta de México, en donde pues se han dado cita el día de hoy el gabinete de energía. Y bueno, los medios de comunicación dando seguimiento también, Jesús, a todo lo que tiene que ver... En ocasiones se ve distante lo que está aconteciendo en Pemex, hasta que nos brindan también la información y desde luego la vamos pulsando y vamos, este, conociendo la importancia de esta empresa, que es una empresa rectora a nivel nacional y que es una empresa que más recursos genera y desde luego también al junto con las remesas que llegan de trabajadoras, trabajadores de México, nuestro país pues mantiene una solidez, una economía pues que permite también no solamente en la competencia al interior mantener los niveles de nuestra moneda. El día de ayer el Gobierno del Estado, como ya conocemos, informó a través del gobernador Julio Menchaca Salazar que Petróleos Mexicanos proporcionó 5,000 toneladas de asfalto, 500 luminarias, dos camiones tanque, un camión de desazolve, dos retroexcavadoras y dos ambulancias. Esto tiene un valor, este, evidentemente económico elevado, un valor superior a los 78 millones de pesos, en donde el gobernador Julio Menchaca logró la gestión histórica ante Petróleos Mexicanos por más de 654 millones de pesos. En esto ha tenido que ver también Alejandro Velázquez Mendoza, titular del despacho del gobierno del Estado de Hidalgo. Con la pregunta también, obviamente, ¿de dónde sale este recurso? ¿Por qué Pemex apoya? ¿Cuál es el papel que está desarrollando en la economía y que es muy importante? Esta mañana, el director de Petróleos Mexicanos, Juan Carlos Carpio, informó... Pemex ha elevado su refinación al 81% y consolida la producción petrolera. Tiene una producción elevada que no se había tenido. Uno de los logros centrales es el incremento en la refinación, evidentemente esto permite entonces tener también mayor producción de barriles diarios y, por lo tanto, una operación que permite que el costo, el precio de los combustibles no se eleven. La integración de la refinería Olmeca ha beneficiado y también las mejoras en las instalaciones estratégicas como la refinería de Tula. Vamos a escuchar, Jesús, lo que dijo Juan Carlos Carpio hace unos minutos en esta conferencia matutina en donde la Secretaría de Energía está presente, así como el director general de Petróleos Mexicanos.
+...pues las cifras concretas son las siguientes: hoy mantenemos una producción estable cercana a la meta de 1.8 millones de barriles diarios, alcanzando 1.76 millones de barriles por día. La producción de gas natural aumentó 7.5% respecto a 2024 y supera los 4,900... El segundo resultado es que estamos refinando más petróleo en México. Actualmente refinamos 81% más petróleo que en 2018, al pasar de alrededor de 612,000 barriles por día a más de 1,100,000 barriles diarios. Esto ha sido posible gracias a la operación constante de las refinerías, la incorporación de la refinería Olmeca y las mejoras operativas en instalaciones estratégicas de la refinería ubicada en Tula. Estamos aprovechando mejor nuestros recursos para generar más combustibles de alto valor que utilizan diariamente millones de mexicanos.
+El gobernador Julio Menchaca Salazar el día de ayer señalaba el abandono, durante mucho tiempo ha sido atacado, ha sido trabajado por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, teniendo el compromiso con nuestra patria chica, y ahí encontramos, señor gobernador, solidariamente a Petróleos Mexicanos. Esta alianza, desde luego, permite no solamente que la refinería se encuentre en el estado de Hidalgo, sino que genera también beneficios. Parte de lo que se ha destacado esta mañana, Pemex también amplió la relación cercana con las comunidades donde opera. Entre 2025 y septiembre de 2026 se destinaron casi 6,600 millones... de apoyos a comunidades y regiones estratégicas. Sus recursos se traducen en caminos, proyectos productivos... Hola, hola, David. ¿David, nos escuchas? Por ahí estamos teniendo... El gobierno federal, el gobierno... que el gobierno federal, el gobierno del estado lleva a cabo esa alianza también en favor de la economía de la propia entidad. Es el reporte...</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zHmbl2aTUV1NCkzOaAN6se2G_dynw7I0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Pemex, Gobierno federal</t>
+  </si>
+  <si>
+    <t>Alejandro Velázquez Mendoza, Juan Carlos Carpio</t>
   </si>
 </sst>
 </file>
@@ -1259,8 +1596,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X52" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X52" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X47" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X47" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1656,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -1730,82 +2067,92 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" s="5">
+        <v>26</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -1813,53 +2160,63 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S3" s="3">
+        <v>29</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1867,53 +2224,63 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S4" s="3">
+        <v>238</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1921,215 +2288,261 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S5" s="3">
+        <v>34</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" s="3">
+        <v>42</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="C7" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S7" s="3">
+        <v>46</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S8" s="3">
+        <v>38</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -2137,107 +2550,131 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
+      <c r="P9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="3">
+        <v>114</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="W9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S10" s="3">
+        <v>10</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -2245,107 +2682,133 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
+      <c r="P11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S11" s="3">
+        <v>28</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="V11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="3">
         <v>17</v>
       </c>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="T12" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -2353,53 +2816,63 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C13" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S13" s="3">
+        <v>37</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -2407,32 +2880,32 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="C14" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>15</v>
@@ -2441,160 +2914,202 @@
         <v>16</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S14" s="3">
+        <v>64</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="C15" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
+      <c r="P15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S15" s="3">
+        <v>137</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="W15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C16" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
+      <c r="P16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S16" s="3">
+        <v>155</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="V16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="X16" s="3"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C17" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>15</v>
@@ -2603,52 +3118,68 @@
         <v>16</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S17" s="3">
+        <v>230</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="C18" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>15</v>
@@ -2657,106 +3188,140 @@
         <v>16</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S18" s="3">
+        <v>233</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="W18" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C19" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S19" s="3">
+        <v>237</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>15</v>
@@ -2765,343 +3330,445 @@
         <v>16</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
+      <c r="P20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S20" s="3">
+        <v>236</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="P21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S21" s="3">
+        <v>22</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
+      <c r="W21" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="X21" s="3"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="C22" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S22" s="3">
+        <v>137</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
+      <c r="W22" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="C23" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
+      <c r="P23" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S23" s="3">
+        <v>243</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
+      <c r="V23" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="C24" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S24" s="3">
+        <v>116</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
+      <c r="W24" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="X24" s="3"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C25" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="P25" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S25" s="3">
+        <v>253</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="C26" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S26" s="3">
+        <v>55</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3109,53 +3776,63 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S27" s="3">
+        <v>40</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3163,53 +3840,63 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
+      <c r="P28" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S28" s="3">
+        <v>53</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -3217,53 +3904,63 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="C29" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="L29" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S29" s="3">
+        <v>48</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3271,53 +3968,63 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
+      <c r="P30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S30" s="3">
+        <v>57</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3325,107 +4032,133 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="C31" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>146</v>
+        <v>210</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S31" s="3">
+        <v>226</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
+      <c r="W31" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="X31" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S32" s="3">
+        <v>44</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3433,53 +4166,63 @@
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S33" s="3">
+        <v>32</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3487,32 +4230,32 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C34" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>24</v>
@@ -3521,52 +4264,70 @@
         <v>16</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
+      <c r="P34" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S34" s="3">
+        <v>599</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>151</v>
+        <v>227</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>15</v>
@@ -3575,154 +4336,198 @@
         <v>16</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S35" s="3">
+        <v>413</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
+      <c r="V35" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="C36" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
+      <c r="P36" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S36" s="3">
+        <v>131</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
+      <c r="V36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="X36" s="3"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C37" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
+      <c r="P37" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S37" s="3">
+        <v>50</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
+      <c r="W37" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C38" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>155</v>
+        <v>239</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>20</v>
@@ -3734,782 +4539,662 @@
         <v>15</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O38" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
+      <c r="P38" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S38" s="3">
+        <v>115</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
+      <c r="W38" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
+        <v>12</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="C39" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>157</v>
+        <v>242</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
+      <c r="P39" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S39" s="3">
+        <v>82</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
+      <c r="W39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X39" s="3" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C40" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
+      <c r="Q40" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S40" s="3">
+        <v>142</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U40" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X40" s="3" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>18</v>
+        <v>249</v>
       </c>
       <c r="C41" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>121</v>
+        <v>252</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
+        <v>253</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S41" s="3">
+        <v>102</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="C42" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P42" s="3"/>
+      <c r="P42" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
+      <c r="R42" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S42" s="3">
+        <v>258</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="X42" s="3"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S43" s="3">
+        <v>274</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
+      <c r="W43" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="X43" s="3"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C44" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S44" s="3">
+        <v>391</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
+      <c r="W44" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C45" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S45" s="3">
+        <v>175</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="C46" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
+      <c r="P46" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S46" s="3">
+        <v>219</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
+      <c r="W46" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C47" s="6">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S47" s="3">
+        <v>311</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>6</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="6">
-        <v>46315</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>4</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="6">
-        <v>46315</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>3</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="6">
-        <v>46315</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>2</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="6">
-        <v>46315</v>
-      </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>1</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" s="6">
-        <v>46315</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
+      <c r="V47" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>276</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09ECEF80-D5F3-4D32-BE12-8E24D4083AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD60BAE9-5BB7-41F8-9CA0-CDF0939A26BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="214">
   <si>
     <t>#</t>
   </si>
@@ -98,9 +98,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>SSPH</t>
-  </si>
-  <si>
     <t>SEPH</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>NQ 90.1 FM</t>
   </si>
   <si>
-    <t>PGJEH</t>
-  </si>
-  <si>
     <t>Ke Buena 106.7 FM</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t>PC</t>
   </si>
   <si>
-    <t>Aldo Falcón</t>
-  </si>
-  <si>
     <t>SSH</t>
   </si>
   <si>
@@ -212,9 +203,6 @@
     <t>RTVH</t>
   </si>
   <si>
-    <t>Mal Desempeño</t>
-  </si>
-  <si>
     <t>Alerta Meteorológica</t>
   </si>
   <si>
@@ -233,27 +221,6 @@
     <t>TV local</t>
   </si>
   <si>
-    <t>Semarnath</t>
-  </si>
-  <si>
-    <t>Localización de cuerpo</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Básica</t>
-  </si>
-  <si>
-    <t>Queja padres de familia</t>
-  </si>
-  <si>
-    <t>STCH</t>
-  </si>
-  <si>
-    <t>Queja transporte público</t>
-  </si>
-  <si>
     <t>Radio Lobo 96.7 FM</t>
   </si>
   <si>
@@ -266,632 +233,478 @@
     <t>SDPEE-OCSAD/FN.37/2026</t>
   </si>
   <si>
-    <t>Julio Menchaca recorre subestación Hidalgo de CFE</t>
-  </si>
-  <si>
-    <t>SSH/Bol.181/2026</t>
-  </si>
-  <si>
-    <t>Semarnath/Bol.SN-L/2026</t>
-  </si>
-  <si>
     <t>Apps de transporte</t>
   </si>
   <si>
-    <t>San Agustín Tlaxiaca</t>
-  </si>
-  <si>
     <t>Vacunación</t>
   </si>
   <si>
-    <t>Andrés Tores respecto a la marcha de la UAEH, comentó: Si viene en transporte público también planteé que pudiera haber cortes en el Tuzobús, en las corridas del Tuzobús. Hasta el momento la Secretaría del Transporte no nos ha confirmado que vaya a haber algún cambio en las corridas del Tuzobús. Seguramente al momento que avance la marcha, seguramente sí habrá suspensión en las corridas del Tuzobús.</t>
-  </si>
-  <si>
-    <t>Sitmah</t>
-  </si>
-  <si>
-    <t>Recorte Operativo</t>
-  </si>
-  <si>
     <t>Neutro</t>
   </si>
   <si>
-    <t>Si viene en transporte público también planteé que pudiera haber cortes en el Tuzobús, en las corridas del Tuzobús. Hasta el momento la Secretaría del Transporte no nos ha confirmado que vaya a haber algún cambio en las corridas del Tuzobús. Seguramente al momento que avance la marcha, seguramente sí habrá suspensión en las corridas del Tuzobús.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1yDN7uNOPGwz59xLlvMfuLHZ0CBCJRPKv/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
     <t>Segundos</t>
   </si>
   <si>
-    <t>Andrés Torres en respuesta a un radioescucha que comenta: "Ojalá arreglen la estación de radio, hace mucha falta". Andrés Torres responde que el director de Radio y Televisión "no conoce la sierra, pregúntale para dónde es la sierra. Pero si no conoce la tiene, no conoce el estado, obviamente, no quiere conocer el estado, ¿no? Ni las instalaciones de Radio y Televisión de Hidalgo, ¿no? Ya tiene qué ¿cuántos meses? Bueno, por favor, es un asunto ya que se desborda por todos lados, sí."</t>
-  </si>
-  <si>
     <t>Negativo</t>
   </si>
   <si>
-    <t>Otro ejemplo rápidamente, Luis Manuel nos escribe, dice, buen día, saludos del corazón de la Sierra, amanecemos con lluvia, otro problema con la lluvia, ojalá... -No conoce la sierra, pregúntale para dónde es la Sierra-. Y dice, ojalá arregle la estación de radio, hace mucha falta. -Pero si no conoce la sierra, no conoce el Estado, obviamente no quiere conocer el Estado, ¿no? Ni siquiera las instalaciones de radio venido, ¿no? Ya tiene que... ¿Cuántos meses? ¿No? Por favor, es un asunto ya que se desborda por todos lados-.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14w1EerUFxyHxnm6oqec89CCWL_r8ECwt/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Andrés Torres menciona que están recibiendo y compartiendo fotos en redes sociales sobre la marcha de la UAEH, y, "aunque se enoje el tiranito [risas], ¿no?, el tiranito local, este porque es información que nos ayuda a todos". Asimismo, señala: "es que la verdad te puede, a mí me dan ganas de llorar que tenemos una persona ignorante, prepotente, por supuesto, un acosador [risas], ¿no?, confirmado, certificado, que, pues no encuentra la manera de obstaculizar, de por supuesto, atacar y siempre, siempre, siempre estar este acosando a los trabajadores de Radio y Televisión de Hidalgo, porque lo que le queda es trabajar [risas], ¿no? Siempre, siempre este difamando, siempre mintiendo [risas], ¿no? Nosotros no nos manejamos de esa manera [risas], ¿no? Ayer yo platicaba sobre sus antecedentes penales [risas], ¿no?, que por cierto tiene varios y que pues resulta que pues nunca los puso en su currículum, ¿no? No los no los reportaba, así que, bueno, pues cada quien cada quien sabrá. Aldo Falcón por su parte destaca el impacto positivo que las personas en distintos municipios, como desde la Huasteca hasta la capital de Hidalgo, agradecen por ayudar a resolver problemas como una fuga de agua. También destacan que algunos no tienen acceso a la estación de radio. Se preguntan cómo se puede llegar a toda la gente, ya que no todo se puede hacer a través de la radio, especialmente con el avance de la tecnología. Andrés responde que: "Aquí el problema es, si no dotas, si tú, por ejemplo, dices, "No quiero que tengan redes sociales", como nos dijeron ayer nuestra dirección general. Entonces, dátanos, dótanos de redes sociales, saben que no tenemos intranet, aben que el decreto para entregar a Radio y Televisión de Hidalgo cinco concesiones de radio en Tlanchinol, Huejutla, Atlapexco, Huichapan y Jacala, obliga a Radio y Televisión de Hidalgo a transmitir en internet. Si no cumplimos con ese precepto, es posible que se nos retiren nuevamente las concesiones. Pero eso no se trabaja, eso no es importante. Lo importante es por qué Las Vocales Radio y Andrés Torres están trabajando [risas], ¿no? ¿Por qué lo ven a él? ¿Por qué le escriben a él? ¿Por qué la por qué no me escriben a mí? ¿Por qué no? Pues no te hablan y no te escriben a ti porque no eres nadie [risas], así de simple, porque en temas informativos no eres nadie, ¿no? Y entonces, pues por eso, simple y llanamente, pues quieres [risas], ¿no?, pero perjudicar, acosar, difamar, hostigar todo el tiempo. Me llama también muchísimo la atención que nadie hace nada. Que nadie hace nada, no, yo sí, yo sí levanto la voz, yo sí me digo, yo sí este denuncio, porque pues yo no voy a permitir que una persona que además es un neófito, es un total y pleno ignorante en temas de comunicación, en temas informativos, en temas, por supuesto, periodísticos, pues quiera este incidir en algo que además ni es su dinero, ay, porque dice que es dinero público. Mentira, estamos utilizando nuestro propio dinero, estamos metiendo dinero de nuestra bolsa para poder cumplir con este precepto de informar que estamos obligados a hacerlo, ¿no?". Aldo está de acuerdo con lo que Andrés dice. Andrés concluye que es necesario seguir trabajando, a pesar de las dificultades y las críticas que enfrentan.</t>
-  </si>
-  <si>
-    <t>Hostigamiento Laboral</t>
-  </si>
-  <si>
-    <t>Andrés Torres: Nos están mandando fotos, ahorita las vamos a compartir en nuestras redes sociales, aunque se enoje el tiranito [risas], ¿no?, el tiranito local, este porque es información que nos ayuda a todos. No te debe dar risa, no, no, es que la verdad te puede, a mí me dan ganas de llorar que tenemos una persona ignorante, prepotente, por supuesto, un acosador [risas], ¿no?, confirmado, certificado, que pues no encuentra la manera de obstaculizar, de por supuesto, atacar y siempre, siempre, siempre estar este acosando a los trabajadores de Radio y Televisión de Hidalgo, porque lo que le queda es trabajar [risas], ¿no? Siempre, siempre este difamando, siempre mintiendo [risas], ¿no? Nosotros no nos manejamos de esa manera [risas], ¿no? Ayer yo platicaba sobre sus antecedentes penales [risas], ¿no?, que por cierto tiene varios y que pues resulta que pues nunca los puso en su currículum, ¿no? No los no los reportaba, así que, bueno, pues cada quien cada quien sabrá. Acuérdate, Aldo. **Aldo Falcón:** Disculpa, Andrés, que te interrumpa, pero a ver, este, se hace, no sé, ya ni con el término, pero por ejemplo, muchas personas si se ven a través de nuestros comentarios, ninguno son inventados, todos los mensajes los estamos leyendo, mucha gente que nos comenta desde la Huasteca, la capital hidalguense, Mineral de la Reforma, todas las áreas, donde nos preguntan problemas que tienen. Ayer una persona nos agradecía por un problema que tuvo una fuga de agua, el cual dijo: "Muchas gracias, gracias, ustedes pudieron resolver este problema". Algunas personas, "No tengo radio, ¿cómo comunicarme con ustedes? No, no llega la estación hasta acá". En Pachuca, ahorita, por ejemplo, estamos este bloqueo, el cual dicen, "Pues es que cómo yo no sabía de este bloqueo, gracias a ustedes estoy informado". Pero por medio de redes sociales, ahora que también nos dicen, "No, tampoco pueden hacerlo", entonces, ¿cómo llegas a toda esta gente? No todo no todo relativamente se puede hacer de a través por radio, lamentablemente ya muchas veces te alcanza la tecnología. **Andrés Torres:** Aquí el problema es, si no dotas, si tú, por ejemplo, dices, "No quiero que tengan redes sociales", como nos dijeron ayer nuestra dirección general. Entonces, dátanos, dótanos de redes sociales, saben que no tenemos intranet, saben que el decreto para entregar a Radio y Televisión de Hidalgo cinco concesiones de radio en Tlanchinol, Huejutla, Atlapexco, Huichapan y Jacala, obliga a Radio y Televisión de Hidalgo a transmitir en internet. Si no cumplimos con ese precepto, es posible que se nos retiren nuevamente las concesiones. Pero eso no se trabaja, eso no es importante. Lo importante es por qué Las Vocales Radio y Andrés Torres están trabajando [risas], ¿no? ¿Por qué lo ven a él? ¿Por qué le escriben a él? ¿Por qué la por qué no me escriben a mí? ¿Por qué no? Pues no te hablan y no te escriben a ti porque no eres nadie [risas], así de simple, porque en temas informativos no eres nadie, ¿no? Y entonces, pues por eso, simple y llanamente, pues quieres [risas], ¿no?, pero perjudicar, acosar, difamar, hostigar todo el tiempo. Me llama también muchísimo la atención que nadie hace nada. Que nadie hace nada, no, yo sí, yo sí levanto la voz, yo sí me digo, yo sí este denuncio, porque pues yo no voy a permitir que una persona que además es un neófito, es un total y pleno ignorante en temas de comunicación, en temas informativos, en temas, por supuesto, periodísticos, pues quiera este incidir en algo que además ni es su dinero, ay, porque dice que es dinero público. Mentira, estamos utilizando nuestro propio dinero, estamos metiendo dinero de nuestra bolsa para poder cumplir con este precepto de informar que estamos obligados a hacerlo, ¿no? **Andrés Torres:** Pero bueno, pues mira, yo te repito, también hay que dedicarle mucho tiempo [risas], ¿no? Porque así chiquito, como es chiquito, como debe estar todo negro.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1N6AgN7ZoJ24oc4z1eJIi0epoE-aMfj0L/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El cuerpo sin vida de una persona en avanzado estado de descomposición fue localizado esta tarde por vecinos de la comunidad de Palmillas, en el municipio de Mixquiahuala. El hallazgo movilizó a elementos de la Policía Municipal y de Protección Civil, quienes acudieron al lugar y confirmaron la presencia del cadáver en las aguas del canal. Los hechos fueron notificados al Ministerio Público, que ordenó el rescate de los restos humanos y las diligencias correspondientes para su levantamiento y traslado al Servicio Médico Forense, donde se realizarán los estudios necesarios para determinar el género y la identidad de la persona. Hasta el momento no se tienen mayores datos para determinar precisamente la identidad de la persona localizada sin vida.</t>
-  </si>
-  <si>
-    <t>Localización De Restos</t>
-  </si>
-  <si>
-    <t>Mixquiahuala</t>
-  </si>
-  <si>
-    <t>Por otra parte, en Mixquiahuala se localizó también un cuerpo sin vida, en este caso un avanzado estado de descomposición. Esto sucedió en la comunidad de Palmillas. El hallazgo movilizó a elementos de la Policía Municipal y de Protección Civil, quienes acudieron al lugar y confirmaron la presencia del cuerpo sin vida en las aguas del canal. Los hechos fueron notificados al Ministerio Público, que ordenó el rescate de los restos humanos y las diligencias correspondientes para su levantamiento y traslado al Servicio Médico Forense, donde se realizarán los estudios necesarios para determinar el género y la identidad de la persona. Hasta el momento no se tienen mayores datos para determinar precisamente la identidad de la persona localizada sin vida.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YMVgauZHpVh9tBoa9wF-oc9F5aWKbtSv/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
     <t>Ultra Noticias</t>
   </si>
   <si>
-    <t>El cuerpo sin vida de un hombre, con varios impactos de arma de fuego, fue localizado en un canal de agua para riego ubicado en el municipio de Tezontepec de Aldama. De acuerdo con los primeros reportes, la víctima, que permanece en calidad de desconocida, presentaba heridas en las extremidades inferiores y en el abdomen, presuntamente ocasionadas por proyectiles de arma de fuego. El hallazgo se registró en un paraje ubicado en los límites de las comunidades de Huitel y Achichilco, donde elementos de las policías municipal y estatal acudieron tras recibir el reporte. Personal de la Procuraduría General de Justicia del Estado de Hidalgo inició las investigaciones respectivas al caso para determinar las responsabilidades legales correspondientes.</t>
-  </si>
-  <si>
-    <t>El cuerpo sin vida de un hombre con varios impactos de arma de fuego fue localizado en el canal de agua de riego, ubicado en el municipio de Tezontepec de Aldama. De acuerdo con los primeros reportes, la víctima, que permanece en calidad de desconocida, presentaba heridas en extremidades inferiores y en el abdomen, presuntamente ocasionados por proyectiles de arma de fuego. Y bien, el hallazgo se registró en un paraje ubicado en los límites de las comunidades de Huitel y Achichilco, donde elementos de la policía municipal y estatal acudieron tras recibir el reporte. El personal de la Procuraduría General de Justicia del Estado de Hidalgo inició las investigaciones respectivas al caso para poder determinar las responsabilidades legales correspondientes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1RSNmGtB2q5ZQt0l_AUI7gTYvhw4W1MCg/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El hallazgo de un hombre sin vida movilizó este martes a corporaciones de seguridad y personal ministerial en la comunidad de Santa Catarina, en el municipio de San Agustín Tlaxiaca. El cuerpo fue localizado en un camino de terracería y, de acuerdo con los primeros reportes, presentaba aparentes signos de violencia. La identidad de la víctima no había sido establecida hasta el momento de los primeros informes. Tras el hallazgo, elementos de seguridad acordonaron el área para facilitar las diligencias periciales. Personal de la Procuraduría General de Justicia del Estado de Hidalgo realizó las actuaciones correspondientes y el traslado del cuerpo al Servicio Médico Forense. Las autoridades iniciaron las investigaciones para determinar las circunstancias de la muerte y esclarecer los hechos.</t>
-  </si>
-  <si>
-    <t>El hallazgo de un hombre sin vida movilizó este martes a corporaciones de seguridad y personal ministerial en la comunidad de Santa Catarina, en el municipio de San Agustín Tlaxiaca. De hecho, el cuerpo fue localizado en un camino de terracería y, de acuerdo con los primeros reportes, presentaba aparentes signos de violencia. La identidad de la víctima no había sido establecida hasta el momento en los primeros informes y, tras este hallazgo, elementos de seguridad acordonaron el área para poder facilitar las diligencias periciales. personal de la Procuraduría General de Justicia del Estado de Hidalgo, realizó las actuaciones también correspondientes y el traslado del cuerpo al Servicio Médico Forense. Las autoridades iniciaron las investigaciones para poder determinar las circunstancias de la muerte y esclarecer los hechos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1P5txQRw7rxbXTMf98w_k5HJwexq25SLj/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Radioescucha: Las plataformas digitales de transporte son necesarias en Hidalgo, ya que funcionan en la Ciudad de México, Estado de México, Guadalajara y Monterrey, permitiendo que el usuario pague y merezca un mejor servicio, precio justo, seguridad, atención y unidades dignas. La competencia no obligará a tener un mejor transporte público, y existe un amparo que permite a Uber operar, siendo un servicio solicitado por más del 80% de los hidalguenses. Bajo la premisa de que "el pueblo es primero", es momento de escuchar a la ciudadanía, ya que las plataformas no solo representan un mejor servicio, sino también empleo e ingresos para los hidalguenses.</t>
-  </si>
-  <si>
-    <t>Las plataformas digitales de transporte son necesarias en Hidalgo. No es casualidad que funcionen en la Ciudad de México, en el Estado de México, Guadalajara y Monterrey. El usuario paga y merece un mejor servicio, precio justo, seguridad, atención y unidades dignas. La competencia nos obligará a tener un mejor transporte público. Existe un amparo que permite a Uber operar y más del 80% de los hidalguenses piden este servicio. Yo no sé. Si nos dice dónde está la encuesta o la estadística, porfa. Insisto, no defiendo a nadie. Si el lema es primero el pueblo, es momento de escuchar al pueblo. Las plataformas no solo son mejor servicio, son empleo e ingresos para los hidalguenses.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ZzRDMC2CXuhqbtDfgWeuIf3DxMZxww0t/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Anda buscando el Gobierno del Estado de Hidalgo un terreno donde se pueda hacer construcción de vivienda del bienestar, uno de los programas estrella del gobierno federal, porque resulta que el que tenía considerado en Ixmiquilpan pues tiene pues problemas ahí de tenencia, esto para la construcción de 750 viviendas y esto lo declaró el secretario de Gobierno del Estado de Hidalgo, Guillermo Olivares Reyna, recordando que se había previsto inicialmente hacer la construcción en la comunidad del Valante en Ixmiquilpan, pero ahí tiene, le insisto, este problemas agrarios. En este sentido, como parte de la glosa del cuarto informe de gobierno del mandatario Julio Menchaca Salazar, tras el cuestionamiento de la diputada Cynthia Citlali Delgado Mendoza sobre este tema, Olivares Reyna explicó que el conflicto ha dificultado el avance del proyecto y añadiendo que incluso se ofreció asesoría jurídica para regularizar el predio original, pero al considerar que el proceso podría prolongarse, decidieron buscar un nuevo predio. Las Casas del Bienestar, dijo, reclaman celeridad, que se arranca en cuanto antes y es por eso que se decidió buscar un nuevo predio. Como alternativa indicó que se ofreció un terreno en donación donde podrían construirse las viviendas, siempre y cuando cumplan con los requisitos legales y técnicos. Mencionó que se trabajan los aspectos relacionados con un pozo de agua y una planta de tratamiento para hacer viable este proyecto. De acuerdo con los antecedentes del conflicto, la disputa por la tenencia de la tierra se prolonga desde hace 80 años, entonces pues que es muy complicado de que puedan utilizar el espacio que se tenía considerado originalmente en el Valante en Ixmiquilpan, pues porque no pueden usarlo porque hay un problema de tenencia legal en ese en ese espacio. Bueno, este de hecho hay versiones periodísticas que afirman que cuando el personal relacionado con el proyecto intentó descargar material para construir los cimientos de las viviendas, habitantes de la zona pues de plano se los se los impidieron y les dijeron "no, aquí no pueden descargar.</t>
-  </si>
-  <si>
     <t>Plan Nacional De Vivienda</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1TRv0I3miksBufVCVUuB3qJMlsuZCHLNA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Guillermo Olivares Reyna</t>
-  </si>
-  <si>
-    <t>Cynthia Citlali Delgado Mendoza</t>
-  </si>
-  <si>
-    <t>Radioescucha: Una colectiva de la Ruta Indeco Aldama pasó 10.38 de la mañana ayer, ocurrió un acto de discriminación hacia un adolescente con discapacidad, iban a subirla y se arrancó.</t>
-  </si>
-  <si>
-    <t>Una colectiva de la Ruta Indeco Aldama pasó 10.38 de la mañana ayer, ocurrió un acto de discriminación hacia un adolescente con discapacidad, iban a subirla y se arrancó.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1g8kBmIL_zu7X6gmD9Exo9hJWgUo3YYWV/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Daniel Mertínez: Insisto, Hidalgo, ella es de los pocos estados del país que no cuentan con estos servicios. Sean buenos o sean malos, pues ahora sí que la experiencia de cada quien, pero es increíble que no formemos parte de ese concierto tecnológico actual ya. Y es gusto en saludarte y bueno, le decía a Isa fuera del aire hace ratito, pónganse de acuerdo, por una parte el gobernador dice que estamos preparando denuncias, por otra parte el presidente de la Juanta de Gobierno dice, bueno, vamos a revisar el tema y a lo mejor lo legislamos.</t>
-  </si>
-  <si>
-    <t>Insisto, Hidalgo, ella es de los pocos estados del país que no cuentan con estos servicios. Sean buenos o sean malos, pues ahora sí que la experiencia de cada quien, pero es increíble que no formemos parte de ese concierto tecnológico actual ya. Y es gusto en saludarte y bueno, le decía a Isa fuera del aire hace ratito, pónganse de acuerdo, por una parte el gobernador dice que estamos preparando denuncias, por otra parte el presidente de la Juanta de Gobierno dice, bueno, vamos a revisar el tema y a lo mejor lo legislamos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1juFbHR6zbh9bbXSQlrbzOD0C9Xc9bCh_/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Congreso</t>
   </si>
   <si>
     <t>Julio Menchaca</t>
   </si>
   <si>
-    <t>Andrés Velázquez Vázquez</t>
-  </si>
-  <si>
-    <t>Radioescucha: se dice primero el pueblo, pues el pueblo no viaja en helicóptero o vehículo particular, nuestros políticos no usan taxi, o sea, no sufren servicio de transporte público. ¿Por qué no hacen sus clásicas encuestas al pueblo sobre lo que les conviene para ellos?</t>
-  </si>
-  <si>
-    <t>Por acá nos están compartiendo un punto de vista. Hablando de servicios de plataforma, se dice primero el pueblo, pues el pueblo no viaja en helicóptero o vehículo particular, nuestros políticos no usan taxi, o sea, no sufren servicio de transporte público. ¿Por qué no hacen sus clásicas encuestas al pueblo? Solo lo que les conviene para ellos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1NOWim0QYeESCn6KaIsRprndlURNSt4Y1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Semot/TI.79/2026</t>
-  </si>
-  <si>
-    <t>Daniel Martínez: Y veo en la tarjeta informativa que envía Movilidad y transporte del Estado de Hidalgo, digo, no le toca esa chamba, pero sí informar qué es lo que pasó, que no hay ninguna información acerca de si hay alguna persona detenida como presunto responsable del intento de robo que denunció el taxista. El taxista registrado adecuadamente, el taxista tiene su licencia y está registrado adecuadamente, pero ni una palabra, si detuvieron a la persona que presuntamente intentó el asalto. ni una palabra en la tarjeta informativa bueno, 9.53 más temas de seguridad pública</t>
-  </si>
-  <si>
-    <t>Accidente transporte público</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1yhqLwrQjB6XzaqWOzG1qpSRRa8_TnzmG/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El operador de un taxi terminó impactándose contra un poste, presuntamente al resistirse a un asalto por parte de un pasajero que viajaba en dicha unidad de transporte individual. La situación se registró en la carretera Pachuca-Actopan, a la altura del puente del Barrio del Judío, resultando dos personas lesionadas durante la situación. Se conoció que uno de los pasajeros del taxi habría intentado asaltar al conductor y, durante el forcejeo, lo lesionó en una mano y en el rostro. Ante esta situación, el operador de la unidad perdió el control del vehículo y se impactó contra un poste, el cual cayó y provocó que un motociclista derrapara. Elementos de Seguridad Pública, Tránsito y Protección Civil de San Agustín Tlaxiaca acudieron al lugar para atender la emergencia y brindar atención a los involucrados. El saldo fue de dos personas lesionadas: el conductor del taxi y el motociclista, quienes fueron valorados por paramédicos y presentaron policontusiones, sin lesiones de gravedad. La Secretaría de Movilidad y Transporte en Hidalgo (Semoth), dio a conocer a través del Sistema de Transporte Convencional de Hidalgo (STCH), informó que dio seguimiento al caso y confirmó que el operador contaba con licencia vigente y que la unidad tenía su documentación en regla.</t>
-  </si>
-  <si>
-    <t>Asalto a transporte público</t>
-  </si>
-  <si>
-    <t>Ayer se reportó eh un accidente ocurrido en eh sobre la carretera Pachuca-Actopan a la altura del puente del barrio El Judío, ya dentro de San Agustín Tlaxiaca. Eh una un taxi se fue contra un poste y derivado del poste, pues se había pasado un motociclista que derrapó y que quedó lesionado igual que que el taxista. Dirías que es un accidente más, un desafortunado eh este accidente más. Pero resulta que al platicar con el taxista, este les comenta a los oficiales de seguridad pública que le intentaron asaltar, que subió un pasajero, que lo lo amagó este y comenzaron a forcejear, obviamente para tratar de evitar el asalto y en el forcejeo perdió el control del vehículo, se terminó estampando contra el poste. Eh afortunadamente el asunto quedó en en policonsusiones, tanto para el motociclista como para el taxista.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1s5sXifN-B9-y569ok0o3pjbM0JhzJKmE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1934/2026</t>
-  </si>
-  <si>
-    <t>Capacita SEPH a supervisores escolares en acompañamiento pedagógico</t>
-  </si>
-  <si>
-    <t>MEJORA EDUCATIVA</t>
-  </si>
-  <si>
-    <t>Izza Hernández: La Secretaría de Educación Pública del Estado de Hidalgo realizó el curso en la función supervisora para la transformación y la mejora continua. De hecho, todo esto enfocado a fortalecer el acompañamiento pedagógico y las prácticas también de supervisión en las escuelas de la entidad. En representación del secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, la subsecretaria de Educación Básica, Nancy Adriana León Vite, participó en el inicio del curso, donde pues destacó que la supervisión escolar es fundamental para poder orientar el trabajo de las comunidades educativas desde una perspectiva de liderazgo pedagógico y también en concordancia con los principios de la Nueva Escuela Mexicana. Y pues el curso aborda temas relacionados con las bases normativas de la función supervisora, el diagnóstico socioeducativo también, la mejora continua y también el acompañamiento pedagógico con el objetivo de fortalecer el trabajo colaborativo pues entre supervisores, directivos y docentes. La capacitación está buscando fortalecer las competencias de las figuras supervisoras para poder atender las necesidades educativas, brindar acompañamiento técnico pedagógico y también administrativo e inmediata de alguna forma también en conflictos y contribuir a la gestión escolar. Asimismo, reconoció el trabajo de la directora general de Desarrollo Curricular, hablamos de María del Rosario Ramírez Hernández, por la organización de este encuentro en conjunto con los centros de maestros, así como también la labor de la directora de Formación Continua, María de Lourdes Reyes Pérez, y también el director de Investigación Educativa, Óscar Monter Fuentes, en el desarrollo de acciones formativas dirigidas a las figuras educativas. Y pues en esta reunión de hecho participó también la directora general técnica de la SEPH, Leiza Aida Fernández Vega, también la titular de la unidad de gestión técnica, estamos hablando de Claudia Huerta Ruiz, y el director de evaluación e información educativa, Mario Covarrubias López. De esta manera es como se su sede esta capacitación por parte de la SEPH y bueno, directamente a los supervisores escolares en acompañamiento pedagógico.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1pM1xobEFg8u_IalqI89AvDhjEHpyluAk/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Nancy Adriana León Vite</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón, María del Rosario Ramírez Hernández, Leyza Aída Fernández Vega, Claudia Huerta Ruíz, Mario Covarrubias López, María de Lourdes Reyes Pérez, Oscar Monter Fuentes</t>
-  </si>
-  <si>
-    <t>El relleno sanitario del Huixmi, que está ubicado en Pachuca, y es que contaría con una vida útil estimada de alrededor de 2 años, uno por cada celda de disposición de residuos. Esto lo informó Mónica Patricia Mixtega Trejo, la titular de la Secretaría de Medio Ambiente y Recursos Naturales del Estado de Hidalgo, durante su comparecencia ante el Congreso local el día 19 de octubre. La funcionaria explicó que en este espacio operan dos empresas particulares: Consultas Nacionales de Información y Asesorías S.A. de C.V., y Marsacot, las cuales cuentan con celdas diferentes para recibir los residuos sólidos urbanos de al menos 14 municipios hidalguenses, principalmente de la zona metropolitana de Pachuca. Ante esta situación, indicó que el gobierno municipal de Pachuca trabajaría en la actualización del programa de ordenamiento ecológico local con la finalidad de abrir más celdas para la disposición de residuos. Otro de los temas que fue abordado durante la comparecencia fue la situación de la presa Requena, donde actualmente se estima la presencia de más de 159,000 toneladas de lirio acuático. Mixtega Trejo informó sobre el proyecto para adquirir cuatro nuevas máquinas trituradoras destinadas a reducir la presencia de esta planta en el embalse y sus alrededores; sin embargo, reconoció que los equipos todavía no han sido comprados y que no habría tampoco fecha para poder adquirirlos. Explico que el procedimiento depende de los procesos de licitación, los cuales podrían tardar alrededor de tres meses, y para esta compra se contempla una inversión aproximada de 33 millones de pesos. En otros temas, la funcionaria señaló que existen 84 unidades económicas generadoras de residuos de manejo especial, un sector que requiere acciones de regulación y seguimiento para procurar una disposición adecuada de los desechos. También informó sobre la dispersión de 19 millones de esferas de semillas en una superficie de 11 hectáreas, aunque será necesario precisar el alcance y los resultados de esta intervención para conocer también su impacto ambiental.</t>
-  </si>
-  <si>
-    <t>Izza Hernández: Y vamos a continuar con el tema del relleno sanitario del Huixmi, que está ubicado en Pachuca, y es que contaría con una vida útil estimada de alrededor de 2 años, uno por cada celda de disposición de residuos. Esto lo informó Mónica Patricia Mixtega Trejo, la titular de la Secretaría de Medio Ambiente y Recursos Naturales del Estado de Hidalgo, durante su comparecencia ante el Congreso local el día 19 de octubre. La funcionaria explicó que en este espacio operan dos empresas particulares: Consultas Nacionales de Información y Asesorías S.A. de C.V., y Marsacot, las cuales cuentan con celdas diferentes para recibir los residuos sólidos urbanos de al menos 14 municipios hidalguenses, principalmente de la zona metropolitana de Pachuca. Ante esta situación, indicó que el gobierno municipal de Pachuca trabajaría en la actualización del programa de ordenamiento ecológico local con la finalidad de abrir más celdas para la disposición de residuos. Otro de los temas que fue abordado durante la comparecencia fue la situación de la presa Requena, donde actualmente se estima la presencia de más de 159,000 toneladas de lirio acuático. Mixtega Trejo informó sobre el proyecto para adquirir cuatro nuevas máquinas trituradoras destinadas a reducir la presencia de esta planta en el embalse y sus alrededores; sin embargo, reconoció que los equipos todavía no han sido comprados y que no habría tampoco fecha para poder adquirirlos. Explico que el procedimiento depende de los procesos de licitación, los cuales podrían tardar alrededor de tres meses, y para esta compra se contempla una inversión aproximada de 33 millones de pesos. En otros temas, la funcionaria señaló que existen 84 unidades económicas generadoras de residuos de manejo especial, un sector que requiere acciones de regulación y seguimiento para procurar una disposición adecuada de los desechos. También informó sobre la dispersión de 19 millones de esferas de semillas en una superficie de 11 hectáreas, aunque será necesario precisar el alcance y los resultados de esta intervención para conocer también su impacto ambiental. Daniel Martínez: Esto en el marco de la propia comparecencia de la titular de la SEMARNAT Hidalgo, que ¡vaya que sí tiene este chambita! Yo creo que uno de los temas fundamentales también es lo de la recuperación del entorno ecológico en el Valle de en el Valle de Tula-Tepeji, que ¡vaya que también ha habido discusión acerca del relleno sanitario que se encuentra en esa zona, Yes! Jessenia Romero: Sí, finalmente ha sido todo un tema esta situación, así que bueno, pues esto es parte de lo que se está realizando y esto es parte también de las acciones que dio a conocer en su comparecencia.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YglAd69g-ZXnJnqxaLEJi2OcypRPdY2N/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Mónica Mixtega</t>
-  </si>
-  <si>
     <t>SEPH/Bol.1940/2026</t>
   </si>
   <si>
-    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) ha destinado 148 millones 782 mil pesos para atender escuelas afectadas en su infraestructura por la vaguada monzónica del año pasado. Lo anterior fue informado por el titular de la dependencia estatal, Natividad Castrejón Valdez, durante su comparecencia ante el Congreso del Estado de Hidalgo, este martes 20 de octubre. Una de las atenciones que destacó el funcionario estatal, fue sobre la Escuela Secundaria General “Caudillo del Sur”, donde se invierten 16 millones 800 mil pesos y los trabajos registran un avance del 60 por ciento. Mientras que en un plantel de educación preescolar dentro del mismo municipio, existe avance en su rehabilitación del 45 por ciento y una escuela primaria, del 55 por ciento. “Eso llevó casi seis meses después de la vaguada, hasta que Conagua tomó la decisión de construir un enorme muro que impida otra vez el desborde del río. Entonces se decidió que sí se repararan las escuelas que estaban ahí”, señaló. Castrejón Valdez explicó que la intervención se retrasó debido a que se analizaba la posibilidad de reconstruir las escuelas en otros lugares, ante el riesgo que representaba su ubicación. Además, actualmente se ejecutan once obras de rehabilitación a planteles educativos en los municipios de Huehuetla, Tlahuiltepa, Tianguistengo y Tepehuacán. El funcionario estatal señaló que 56 millones de pesos destinados a la atención de las escuelas afectadas corresponden al seguro institucional, mientras que el resto de los recursos proviene del gobierno estatal. Como parte de las gestiones realizadas ante el gobierno federal, se entregaron 10 mil bienes y equipos para reponer parte de lo perdido y contribuir a la recuperación de los planteles. Además, se distribuyeron 525 computadoras portátiles entre el personal docente y administrativo. Castrejón Valdez recordó que, al inicio de la emergencia, se recibieron más de 250 reportes de escuelas afectadas; sin embargo, durante el proceso de revisión y limpieza se determinó que muchas de ellas únicamente presentaban acumulación de lodo y residuos ocasionados por las lluvias. Después de un análisis se contabilizaron 99 planteles con afectaciones 19 con daños graves, 36 con daños moderados y 44 con daños leves.</t>
-  </si>
-  <si>
-    <t>Uno de los grandes temas, y creo que es la tercera o cuarta dependencia estatal que toca el tema de las atenciones que se han brindado durante, o sí, después de la vaguada monzónica para rehabilitar infraestructura social, en este caso educativa, donde hubo información por parte del propio Catejón Valdés en su comparecencia oficial de ayer en el Congreso del Estado. Así es, Daniel. Le compartimos que la Secretaría de Educación Pública de Hidalgo ha destinado 148 millones 782 mil pesos en atender escuelas afectadas en su infraestructura por la vaguada monzónica del año pasado. Esto fue informado por Natividad Castrejón durante su comparecencia ante el Congreso el día de ayer martes 20 de octubre. Una de las atenciones que destacó el funcionario fue sobre la Escuela Secundaria General Caudillo del Sur, donde se invirtieron 16 millones 800 mil pesos y los trabajos registran un avance de 60%, mientras que en un plantel de educación preescolar dentro del mismo municipio existe avance en su rehabilitación del 45%, en una escuela primaria también el 55%. Eso llevó casi seis meses después de la vaguada monzónica hasta que Conagua tomó la decisión de construir un enorme muro que impida otra vez el desborde del río. Entonces ya se decidió que sí se repararan las escuelas que estaban ahí ubicadas. Castrejón Valdés explicó que la intervención se retrasó debido a que se analizaba la posibilidad de reconstruir las escuelas en otros lugares ante el riesgo que representaba también la ubicación. Obviamente se tenían que hacer estudios técnicos primero para determinar si se reconstruían nuevamente o finalmente se volvían a construir en algún otro lugar. Además, actualmente se ejecutan 11 obras de rehabilitación a planteles educativos en los municipios de Huehuetla, Tlahuiltepa, Tianguistengo y Tepehuacán. El funcionario estatal se que 56 millones de pesos destinados a la atención de las escuelas afectadas corresponden al seguro institucional mientras que el resto de los recursos proviene de gobierno estatal Como parte de las gestiones realizadas ante el gobierno federal se entregaron 10 mil bienes y equipos para reponer parte de lo perdido y contribuir a la recuperación de los planteles. Además, se distribuyen 525 computadoras portátiles entre personal docente y administrativo. Castrejón Valdés recordó que al inicio de la emergencia se recibieron más de 250 reportes de escuelas afectadas Sin embargo, durante el proceso de revisión y limpieza se determinó que muchas de ellas únicamente presentaban acumulación de lodo o residuos que habían sido ocasionados por la lluvia Después de un análisis se contabilizaron 99 planteles con afectaciones, 19 con daños graves, 36 con daños moderados y 44 con daños leves Natividad Castrejón informó que durante la administración se han destinado 2.700 millones de pesos a infraestructura educativa De los cuales 780 millones corresponden al periodo reportado en 1.500 planteles A esta inversión se suman más de 4.400 millones de pesos destinados en cuatro años a la entrega de útiles, uniforme, calzado y libros Para alrededor de 570 mil estudiantes por ciclo escolar Bueno, insisto, por obvias razones ha sido un gran tema acerca de la rehabilitación de los espacios dañados por la abogada monzónica para obras públicas, para educación. Entiendo que el día de hoy Bienestar también va a estar ya en tu comparecencia y no dudo que vayan a tocar el tema también de la abogada monzónica por obvias razones. Sí, claro, y pues estamos hablando de que todavía se sigue trabajando, al menos según lo que reportó el día de ayer Castrejón Valdés, es que al menos llevan, por ejemplo, algunas obras con 45% de avance, 55%, entonces todavía se sigue trabajando al respecto y hasta el momento se han destinado 148.782.000 pesos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hwkL1MgfNnqERs0P3nJNzuN3LL5fw6Z8/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Natividad Castrejón</t>
   </si>
   <si>
-    <t>La devolución de las 80 hectáreas que solicitan estudiantes de la Escuela Normal Rural Luis Villarreal, conocida como El Mexe, no está contemplada por el momento, afirmó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón Valdez, durante su comparecencia ante el Congreso estatal. Mientras el funcionario presentaba información ante los legisladores, un grupo de normalistas se concentró en el exterior del recinto y bloqueó los accesos, lo que dificultó el tránsito de ciudadanos, trabajadores legislativos, periodistas y funcionarios que se encontraban en el lugar. Los manifestantes expresaron sus demandas mediante consignas y mantas. La movilización también generó cuestionamientos entre los diputados. Marco Antonio Mendoza Bustamante pidió que algún representante de la Secretaría de Educación saliera a escuchar a los estudiantes, al considerar necesario atender sus planteamientos relacionados con el marco curricular común, la formación docente y diversos asuntos administrativos. En respuesta, Castrejón Valdez aseguró que las autoridades mantienen abiertas las mesas de negociación con los normalistas. Detalló que durante la semana anterior se realizaron dos encuentros en la Ciudad de México, uno estatal y otro nacional, con la participación de la Secretaría de Gobernación. Asimismo, indicó que la siguiente reunión está prevista para el 3 de noviembre y que se han llevado a cabo más de 50 encuentros de trabajo. No obstante, el titular de la SEPH cuestionó la intervención de Roberto Azpeitia en el conflicto y lo acusó de utilizar las demandas de la comunidad normalista con fines políticos personales. Según el secretario, Azpeitia no forma parte de la planta académica de El Mexe ni cuenta con una representación formal de la institución. Castrejón también lo vinculó con la toma de las instalaciones de la dependencia ocurrida en febrero de 2026, durante la cual, aseguró, se registraron daños en puertas y cristales. Añadió que existe una carpeta de investigación relacionada con esos hechos. El funcionario sostuvo que, debido a esa situación, no considera viable establecer una interlocución con Azpeitia, aunque afirmó que las negociaciones con los estudiantes continúan. La postura de la dependencia mantiene sin respuesta favorable la exigencia de recuperar las 80 hectáreas reclamadas por los normalistas.</t>
-  </si>
-  <si>
-    <t>Francisco I. Madero</t>
-  </si>
-  <si>
-    <t>En cuestiones legislativas, el día de ayer, hubo, siguen las comparecencias en el Congreso del Estado de Hidalgo, tocó al titular de la Secretaría de Educación Pública Estatal, Natividad Castrejón, en donde habló en principio del tema del Meche, Isa, en tanto había protestas del Meche afuera del Congreso del Estado de Hidalgo. Es correcto, Daniel, así como lo estás adelantando, y es que la devolución de las 80 hectáreas que solicitan estudiantes de la Escuela Normal Rural Luis Villarreal, conocida como el Meche, no está contemplada por el momento, así lo afirmó el titular de la Secretaría de Educación Pública de Hidalgo, Natividad Castro Convaldez, todo esto durante la comparecencia ante el Congreso Estatal. Mientras el funcionario presentaba la información ante los legisladores, un grupo de normalistas se concentró en el exterior del recinto y bloqueó los accesos, lo que dificultó, de hecho, el tránsito de ciudadanos, también de trabajadores legislativos, periodistas y funcionarios que se encontraban en ese lugar. Los manifestantes expresaron sus demandas mediante consignas y también mantas. La movilización también generó bastantes cuestionamientos entre los diputados. Marco Antonio Mendoza Bustamante, de hecho, pidió que algún representante de la Secretaría de Educación saliera a escuchar a los estudiantes al considerar necesario entender estos planteamientos relacionados con el marco curricular común, la formación docente y también diversos asuntos administrativos. Y pues en respuesta Castrejón Valdés aseguró que las autoridades mantienen abiertas las mesas de negociación, eso con los normalistas, y detalló también que durante la semana anterior se realizaron dos encuentros, uno en la Ciudad de M uno estatal y otro nacional pues con la participación de la Secretar de Gobernación asimismo también indicó que la siguiente reunión está prevista para el 13 de noviembre y que se han llevado a cabo m de 50 encuentros de trabajo No obstante, el titular de la CEPIDALGO cuestionó la intervención de Roberto Aspeitia, de hecho también en el conflicto, y lo acusó directamente de utilizar las demandas de la comunidad normalista con fines políticos personales. Según el secretario, Aspeitia de hecho no forma parte de la planta académica del Meche ni cuenta con una representación formal de la institución. Y bien Castrejón también lo vinculó con la toma de las instalaciones de la dependencia ocurrida en febrero del 2026, durante la cual aseguró se registraron daños en puentes y cristales. De hecho añadió que existe una carpeta de investigación relacionada con estos hechos. Pero sí el funcionario sostuvo que debido a esta situación no considera viable establecer como tal y de alguna forma también pues negociaciones con los estudiantes y obviamente también esto es continua la postura de la dependencia mantiene sin respuesta favorable la exigencia de recuperar estas 80 hectáreas reclamadas por los normalistas. Y pues prácticamente esto fue todo lo que sucedió, Daniel. Y pues sí, mientras tanto está a un lado el hecho de devolver las 80 hectáreas reclamadas por estudiantes del MESH. De hecho, le puso nombre y apellido por lo que comentabas en su momento, Isa, a quien podría ser el responsable, a quien podría estar detrás de las protestas y manifestaciones que ya tienen años, por cierto, ¿ven? Es correcto, Daniel, así como lo acabas de mencionar, sí ya tienen muchísimo tiempo y sabemos perfectamente que no es nada, pero nada, nada nuevo que se manifiesten de esta manera y que hagan este tipo de peticiones. Vamos a ver qué pasa más adelante porque ya llevan ratito precisamente con este tipo de peticiones.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ueeSWAppHqm8mWnO3lJcoNEco_UgQYBH/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Roberto Azpeitia</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1330/2026</t>
-  </si>
-  <si>
-    <t>Menchaca Salazar logra gestión histórica ante Pemex por más de 654 millones de pesos</t>
-  </si>
-  <si>
     <t>Jessenia Romero</t>
   </si>
   <si>
-    <t>Donación Pemex</t>
-  </si>
-  <si>
-    <t>Daniel Martínez: El gobernador Julio Menchaca Salazar estuvo presente con funcionarios de Petróleos Mexicanos para recibir eh inversión eh este atención a gestiones que se habían realizado con la paraestatal, Izza. Izza Hernández: Es correcto, Daniel, de hecho les contamos y precisamente que desde las instalaciones de la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, el gobernador Julio Menchaca Salazar encabezó la entrega de equipamiento por 78,614,370 pesos, este resultado de las gestiones realizadas por o ante Petróleos Mexicanos, que desde 2022 pues han permitido a Hidalgo recibir donaciones por más de 654 millones de pesos, para poder fortalecer los servicios públicos, la infraestructura carretera, la salud y también la educación. El abandono durante mucho tiempo ha sido atacado, ha sido trabajado también por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, atendiendo el compromiso que tenemos con nuestra patria chica y también ahí encontramos de manera solidaria a Pemex, así lo aseveró el mandatario estatal, esto al manifestar el agradecimiento del pueblo hidalguense, todo esto por el apoyo solidario que se brindó pues en las comunidades afectadas, eso por la vaguada monzónica, a través de la donación de combustible, unidades médicas también y maquinaria. Y pues en este sentido, Menchaca Salazar dio a conocer que pues para esta entrega de alguna forma Pemex sí proporcionó 5,000 toneladas de toneladas de asfalto, 500 luminarias, dos camiones tanque, también un camión desazolve, ahora sí que también dos retroexcavadoras y dos ambulancias y equipamiento pues que estaría contribuyendo a fortalecer la capacidad operativa de los servicios públicos y la atención a la población. Y en su momento, el director de Responsabilidad Social de Pemex, Raúl Ojeda Sukieta, refirió que las donaciones realizadas por la empresa mexicana pues son muestra del esfuerzo que mujeres y hombres llevan a cabo en la refinería de Tula, esto en la planta coquizadora, así como también en cada uno de los espacios pues que se han le son conferidos y pues Alejandro Vázquez Mendoza, quien es secretario del Despacho del Poder Ejecutivo del Estado de Hidalgo, pues externó el conocimiento y el reconocimiento a la presidenta Claudia Sheinbaum y también al personal de Pemex por el respaldo de manera permanente al desarrollo de la entidad. Este encuentro va mucho más allá de la recepción administrativa de estas unidades y de la maquinaria también que hoy tenemos aquí, nos recuerda que la riqueza del país sobra pues sentido, cobra sentido, también pleno únicamente pues cuando regresa al pueblo, parte de lo que dio a conocer y entre los resultados Vázquez Mendoza destacó la donación de 23,200 toneladas de asfalto, estas destinadas a la rehabilitación de 42 vialidades en nueve municipios con una superficie de 560,000 metros cuadrados, asimismo también pues informó que se estarían realizando trabajos en el bulevar Refinería-Tula, mientras que se contemplan pues nuevas intervenciones en Pachuca, en Huejutla entre otras demarcaciones y pues en materia de salud esta colaboración ha permitido brindar 178,910 servicios eh pues mediante unidades médicas móviles en 59 municipios, además también de la realización de 10,000 mastografías en 23 municipios, ampliando de esta manera el acceso a la atención y detección también oportuna. Finalmente, el respaldo de Pemex y también pues estaría reflejando la donación importante de 53 unidades vehiculares, 500 tinacos y equipamiento de 200 aulas de 89 escuelas distribuidas en 18 municipios. Parte de lo que se da a conocer con esta información Menchaca Salazar que logra esta gestión histórica ante Pemex por más de 654 millones de pesos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1QgI9uim6BczVD33I1IVimM-Sfgw1mYi3/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SIPDUS, Procuraduría General de Justicia del Estado de Hidalgo, Secretaría del Trabajo y Previsión Social de Hidalgo</t>
-  </si>
-  <si>
-    <t>Raúl Ojeda Zubieta, Alejandro Velázquez Mendoza, Claudia Sheinbaum</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo alista una denuncia contra Uber por su presunta prestación de servicios de transporte en Pachuca sin contar con la autorización correspondiente, informó el gobernador Julio Menchaca Salazar, quien prevé que el recurso sea presentado ante la Procuraduría General de Justicia del Estado en los próximos días. El mandatario explicó que la Coordinación General Jurídica trabaja en la integración del documento para que el Ministerio Público determine si existen elementos para investigar posibles infracciones y establecer responsabilidades. Tras un evento de entrega de donaciones de Petróleos Mexicanos (Pemex), Menchaca señaló que la legislación contempla sanciones relacionadas con el uso irregular de servicios públicos. Añadió que el análisis podría incluir tanto a quienes impulsan la operación de la plataforma como a las personas que ofrezcan viajes mediante ella. Respecto a la posibilidad de que Uber obtenga los permisos necesarios, el gobernador indicó que la empresa puede participar en los procedimientos establecidos; sin embargo, afirmó que actualmente no se han autorizado nuevas concesiones para rutas u otras modalidades de transporte público, debido a la saturación que, según dijo, enfrenta el sector en Hidalgo. Menchaca Salazar reconoció que mejorar la movilidad será uno de los asuntos pendientes durante la parte final de su administración, ante las necesidades de traslado de la población. En otro tema, llamó a los usuarios del transporte público a presentar denuncias formales cuando enfrenten malos tratos o agresiones por parte de operadores. Señaló que estos procedimientos permiten a las autoridades investigar los casos y, si corresponde, aplicar sanciones a conductores o concesionarios.</t>
-  </si>
-  <si>
-    <t>Vamos viendo cómo evoluciona este tema, hablando de transporte, Isa. Pues ahora sí que Toma y Daca, en el asunto de los servicios de plataforma, que si entran, que si no entran, que si es legal, que si no es, que es ilegal. Ya había planteado el fin de semana el gobernador Julio Menchaca Salazar, a principios de la semana más bien, el tema de que si estaban circulando estas aplicaciones, estos autos por aplicación, pues estaban en una cuestión ilegal. E incluso ayer hizo un anuncio que se me hace curioso lo que declaró casi al mismo tiempo el presidente de la Junta de Gobierno del Congreso del Estado de Hidalgo sobre el tema. Empezamos contigo, si nos permites. Es correcto, Daniel. El gobierno del Estado de Hidalgo estaría listando una denuncia en contra de Uber por la presunta prestación de servicios de transporte en Pachuca sin contar con la autorización correspondiente. Así lo informó el gobernador Julio Menchaca Salazar, quien prevé que el recurso sea prestado ante la Procuraduría General de Justicia del Estado de Hidalgo. Esto en los próximos días. Y pues el mandatario explicó que la Coordinación General Jurídica trabaja en integración del documento para el Ministerio Público para que él determine directamente si existen elementos para poder investigar posibles infracciones y establecer también responsabilidades. Y pues tras un evento de entrega de donaciones de petróleos mexicanos de Pemex, Menchaca señaló que la legislación contempla sanciones relacionadas con el uso irregular de servicios públicos. De hecho, añadió que el análisis podría incluir tanto a quienes impulsan la operación de plataforma como también a las personas que ofrezcan viajes mediante ella. Y respecto a la posibilidad de que Uber obtenga los permisos necesarios, el gobernador sí indicó que la empresa puede participar en los procedimientos establecidos. Sin embargo, afirmó que actualmente no se han autorizado nuevas concesiones para rutas u otras modalidades también de transporte p Todo esto debido a la saturación que de acuerdo con lo que dijo estar enfrentando el sector en Hidalgo Y pues Menchaca Salazar reconoció que mejorar la movilidad ser uno de los asuntos pendientes durante la parte final de su administración ante las necesidades de traslado de la población. Y pues en otro tema, también llamó a los usuarios de transporte público a presentar denuncias formales cuando enfrenten malos tratos o agresiones por parte de operadores. De hecho, señaló que estos procedimientos permiten a las autoridades pues investigar los casos y corresponde también aplicar sanciones a conductores o concesionarios. Entonces, pues de esta manera es como el gobierno de Hidalgo pues estaría preparando una denuncia contra Uber por posible operación irregular. Sí, viendo por acá, Isa, lo que comentabas también hace un momentito de que el propio gobernador Menchaca Salazar pues está invitando también a quienes son usuarios del Servicio de Transporte público de pasajeros, sea colectivo, sea taxi, de que en caso de agresiones también denuncien. Insisto, así como se señala, es que qué mal conductor, es que qué mal operador me tocó, también está la parte de los que son excelentes operadores y que son la mayoría, y también habemos buenos, malos, pésimos y lo que sigue pasajeros, Isa. Es correcto, pues finalmente hay de todo, Daniel, digo, como siempre lo hemos dicho, y lamentablemente por algunos pagan todo así hablando o de manera general. O sea, si hablamos en este caso, por ejemplo, de los prestadores de servicio e incluso hasta de los mismos pasajeros, pero bien, pues sí, en efecto, lo que hizo el gobernador es un llamado a los usuarios de transporte público para presentar las denuncias formales cuando en alguna ocasión enfrenten algún tipo de maltrato. De hecho, recordemos que algunas de las personas que más sufren de maltrato, por ejemplo, son las personas adultas mayores. Ahora sí que nos han llegado los reportes directamente aquí a cabina. Entonces, pues bien, ese tipo de anuncios, hacerlas formales, como lo dijo el gobernador.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1yY_pcbAaRrCROlv1leoXK7qFxFzIDNwR/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>En cuestión de agenda, se espera que en unos minutos más el gobernador Julio Menchaca Salazar encabece el Congreso Nacional de Moda y Vestido 2026. Esto se realizará en el Auditorio Gota de Plata a las 19 horas.</t>
-  </si>
-  <si>
-    <t>Agenda gobernador</t>
-  </si>
-  <si>
-    <t>En cuestión de agenda, se espera que en unos minutos más el gobernador Julio Menchaca Salazar encabece el Congreso Nacional de Moda y Vestido 2026. Esto se realizará en el Hotel de Gota de Plata a las 19 horas. Muy bien, va a estar este evento aquí en el Centro Cultural Hidalguense, ¿no? Dentro del Centro Cultural Hidalguense el gobernador encabezará esta inauguración.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1iqeIYYe56IanWP96lTECcrzp8fKGbmHR/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>UPLAPH/Citnova/Bol.13/2026</t>
-  </si>
-  <si>
-    <t>Protege Hidalgo el conocimiento para impulsar la innovación</t>
-  </si>
-  <si>
-    <t>Citnova</t>
-  </si>
-  <si>
-    <t>Propiedad intelectual</t>
-  </si>
-  <si>
-    <t>Andrés Torres:El gobierno de nuestro estado encabezado por Julio Menchaca fortalece las capacidades de la comunidad científica, tecnológica y emprendedora para que sus ideas e investigaciones se conviertan en oportunidades de desarrollo a través del Consejo de Ciencia, Tecnología e Innovación de Hidalgo, el Citnova, que acaba de poner en marcha el en segundo curso introductorio a la propiedad intelectual. Esta interactiva iniciativa busca acercar herramientas para identificar, proteger y gestionar los resultados de las investigaciones, invenciones y proyectos creativos mediante figuras como las patentes, los modelos de utilidad, derechos de autor y registro de marcas, fundamentales para aprovechar el valor del conocimiento. Durante la inauguración virtual de esta eh evento, el director general del Citnova, Francisco Patiño Cardona, destacó la importancia de fortalecer las capacidades de las y los hidalguenses para proteger sus creaciones y generar nuevas oportunidades de innovación y desarrollo. La capacitación coordinada por la Subdirección Adjunta de Gestión y Propiedad Intelectual está dirigida a estudiantes, investigadores, científicos, tecnólogos, personas emprendedoras, profesionales, creativos y público en general. Con ellos se promueve una cultura de protección del conocimiento y la vinculación entre instituciones académicas, centros de investigación y empresas de así como emprendedores. El curso es gratuito, se imparte en una modalidad virtual y contempla 10 horas distribuidas en cinco sesiones, eh todo programada para los días 20, 21, 22, 27 y 28 de octubre del presente año. Al finalizar, las personas participantes podrán identificar alternativas de protección para sus proyectos y conocer las rutas generales para gestionar sus gestiones e invenciones ante las autoridades competentes. Bueno, pues es muy importante proteger la propiedad intelectual y déjenme decirle que aunque pudiera ser un asunto que a usted le pareciera lejano, hay muchos muchos investigadores, hay muchos inventores, es el término popular, en nuestro estado, que todos los días están trabajando, que todos los días están produciendo este en diferentes áreas y pues qué mejor que tengan información para proteger sus</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1aqhxW4sr29r81LCrtpoi0-nv9ZyE7kgK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Francisco Patiño Cardona</t>
-  </si>
-  <si>
-    <t>El día de ayer se llevó a cabo la comparecencia del secretario de educación pública, Natividad Castrejón. La comparecencia fue larga e interesante, abordando temas como la eficiencia terminal en educación, la infraestructura educativa, la dinámica social y las nuevas condiciones de seguridad en las escuelas, así como los planes y programas de estudio. Durante esta comparecencia, alumnos de la Normal Rural Luis Villarreal de El Mexe protestaron por mejores instalaciones y exigieron la devolución de las antiguas instalaciones en Tepatepec, Francisco I. Madero. Bloquearon los accesos al Congreso del Estado, cerrando la calle que lleva al Congreso, así como a las instalaciones del Poder Judicial y de Radio y Televisión de Hidalgo. La manifestación fue pacífica, pero causó complicaciones en el tránsito. Los estudiantes exigían la asistencia del secretario a sus asambleas para abordar su pliego petitorio. La situación se prolongó durante varias horas, dificultando la entrada y salida del Congreso. La comparecencia de Onésimo Serrano, encargado de la Unidad de Planeación y Prospectiva del Gobierno del Estado de Hidalgo, sufrió un retraso. Al final, el secretario se retiró por una salida alterna, y los estudiantes se fueron sin incidentes, dejando solo un bloqueo temporal. La agenda legislativa avanzó y Onésimo Serrano pudo realizar su comparecencia.</t>
-  </si>
-  <si>
-    <t>El día de ayer se llevó a efecto la comparecencia del secretario de educación pública de nuestro estado, Natividad Castrejón. Fue una comparecencia muy larga, una comparecencia muy interesante, se hablaron de temas que son de interés general como la eficiencia terminal en los niveles de educación de nuestro estado, infraestructura en temas educativos, nuevas condiciones de la sociedad, la dinámica social y las nuevas condiciones de seguridad en las escuelas, los planes y programas de estudio. Ayer durante el desarrollo de esta comparecencia del secretario de educación ante la LXVI Legislatura, hubo una protesta por parte de alumnos de la Normal Rural Luis Villarreal de El Mexe, quienes continúan con sus manifestaciones y exigencias para que se amplíen las instalaciones y se les devuelvan las instalaciones de la antigua normal rural allá en la región de Tepatepec en el municipio de Francisco I. Madero. Bloquearon los accesos al Congreso del Estado, cerrando la calle que da acceso al Congreso, a las instalaciones del Poder Judicial y de Radio y Televisión de Hidalgo. La manifestación fue pacífica, pero impidieron la circulación en la zona y complicaron el tránsito. Exigían que el secretario asistiera a sus asambleas y convocatorias para resolverles su pliego petitorio. El asunto se complicó durante varias horas sin dejar salir ni entrar a nadie al Congreso. La otra comparecencia pactada y agendada para el día de ayer en la LXVI Legislatura, la del encargado de la Unidad de Planeación y Prospectiva del Gobierno del Estado de Hidalgo, Onésimo Serrano, tuvo un considerable retraso. Al final el secretario se retiró por una salida alterna habilitada para abandonar el recinto, y los estudiantes de la Normal Rural Luis Villarreal del Mexe se retiraron sin incidentes, quedando solo el bloqueo temporal de unas horas en las instalaciones del Congreso. Avanzó la agenda legislativa y Onésimo Serrano pudo dar su comparecencia correspondiente a la Unidad de Planeación y Prospectiva.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10eOyIkYWcIui2KWvfOli6bmQWczRpL8I/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Congreso del Estado, Poder Judicial, Radio y Televisión de Hidalgo, Unidad de Planeación y Prospectiva.</t>
-  </si>
-  <si>
-    <t>Onésimo Serrano Rivera</t>
-  </si>
-  <si>
-    <t>Recorrido Por Instalaciones</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
-    <t>El gobernador de nuestro estado, Aldo Falcón, ayer recorrió la subestación de la Comisión Federal de Electricidad para hacer una supervisión de las adecuaciones, de las rehabilitaciones y sobre todo para ver cómo se ha fortalecido esta paraestatal para lo que corresponde al suministro de energía eléctrica en las diferentes regiones de nuestro estado. Así se acompaña del personal de la Comisión Federal de Electricidad, el gobernador Julio Menchaca, Salazar recorrió las instalaciones de la sub estación de CFE, un espacio Comisión Federal de Electricidad un espacio que forma parte del programa de desarrollo del Sistema Eléctrico Nacional 2021-2035 y el suministro de la zona metropolitana de Pachuca Muy bien, esta supervisión, les repito es parte de los trabajos de coordinación porque uno de los principales problemas que tenemos en diferentes regiones de nuestro estado, por ejemplo la Huasteca, es que el tendido eléctrico la instalación, los temas que tienen que ver con la distribución de la electricidad en nuestro estado, bueno, pues hay una sobrecarga y una sobresaturación, eso no es un problema del estado de Hidalgo, es un problema en muchas entidades, no es propio del estado de Hidalgo, en muchas entidades, y bueno, la paraestatal Función Federal de Electricidad anunció ya desde hace varios meses que ampliará su infraestructura para que cada vez sea mejor la distribución y por supuesto la dotación de energía en regiones como la Huasteca y la Sierra en nuestro estado. Por eso el tema de esta coordinación y esta supervisión es parte de estos trabajos que se anunciaron hace varios meses para fortalecer la infraestructura de la Comisión Federal de Electricidad en todo el Estado.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CMuS5d1UBwMP8yAruW_azCosSHvndjDA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El gobernador de nuestro estado, Julio Menchaca Salazar, ayer tuvo actividad y se reunió con autoridades de la paraestatal Pemex, desde las instalaciones de la CAASIM, de la Comisión Nacional de Agua y Alcantarillado y Sistemas Intermunicipales, el gobernador Julio Menchaca encabezó la entrega de equipamiento por un total de 78,614,370 pesos, esto gracias a las gestiones que se realizaron ante Petróleos Mexicanos, este que desde el 2022 pues le permitieron a nuestro estado recibir donaciones que superan los 654 millones de pesos, todo esto para fortalecer los servicios públicos de infraestructura carretera, la salud y, por supuesto, la educación. El abandono que durante mucho tiempo ha sido atacado, dice así, el abandono que durante mucho tiempo ha sido atacado, ha sido trabajado por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, atendiendo el compromiso que tenemos con nuestra patria chica, y ahí encontramos solidariamente a Pemex, aseveró el mandatario estatal al manifestar el agradecimiento del pueblo hidalguense para el apoyo solidario que brindó en las comunidades afectadas por la vaguada monzónica a través de donaciones de combustible, unidades médicas y maquinaria. En esta participación, el gobernador Julio Menchaca dijo que para esta entrega Pemex proporcionó 5,000 toneladas de asfalto, de asfalto, 5,000 luminarias, dos camiones tanque, un camión de desazolve, dos retroexcavadoras y dos ambulancias, equipamiento que contribuirá a fortalecer la capacidad operativa de los servicios públicos y la atención a la población. En su momento, el director de Responsabilidad Social de Pemex, Raúl Ojeda Zubieta, refirió que las donaciones realizadas por la empresa mexicana son muestra del esfuerzo que mujeres y hombres llevan a efecto en la refinería de Tula, en la planta coquizadora, así como en cada uno de los espacios que les son conferidos. Alejandro Velázquez Mendoza, secretario de Despacho del Poder Ejecutivo del Estado de Hidalgo, externó reconocimiento, el reconocimiento a la presidenta Claudia Sheinbaum y al personal, por supuesto, de la paraestatal Pemex por el respaldo permanente al desarrollo de la entidad. En este encuentro va mucho más allá de la representación o de la recepción administrativa de estas unidades y de las maquinarias que hoy ya tenemos aquí, nos recuerda que la riqueza del país cobra sentido pleno únicamente cuando regresa al pueblo convertida en obras, en infraestructura, en justicia social, puntualizó el funcionario y recordó que la coordinación con Pemex, instruida por el gobernador Julio Menchaca, permitió que del 2022 a la fecha se gestionaran cursos por más de 654 millones de pesos. En estos entre estos principales resultados el el secretario del despacho dijo que hay una donación de 23,200 toneladas de asfalto, estas fueron destinadas a la rehabilitación de 42 vialidades en nueve municipios con una superficie de 5,600 m2. De la misma forma, dijo que se realizan trabajos en el bulevar de la Refinería Tula, mientras que también se contemplan nuevas inversiones para Pachuca y Huejutla, intervenciones en Pachuca y Huejutla entre otras demarcaciones. Aldo Falcón: En materia de salud, en esta colaboración ha permitido brindar 178,910 servicios mediante unidades médicas móviles en 59 municipios, además se realizaron 10,000 mastografías en 23 municipios aplicando el acceso atención de la perdón de la detección oportuna. Finalmente, el respaldo de Pemex también se refleja en la donación de 53 unidades vehiculares, 500 tinacos de equipamiento para 200 aulas de 89 de 89 escuelas distribuidas en 18 municipios que se suman a la rehabilitación y reforestación de 3.9 km de la ciclovía andador peatonal del Río de las Avenidas en Pachuca en beneficio de 304 314,000 habitantes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1kVU4i2g6p2tszznjAeGtwbTEuZEwnqzE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SIPDUS (CAASIM)</t>
-  </si>
-  <si>
-    <t>Vecinos de San Agustín Tlaxiaca reportaron objetos sospechosos, bolsas de plástico, en un área desierta cerca de Santa Catarina. Al llegar, la policía encontró dos cuerpos sin vida. Uno de ellos estaba dentro de una bolsa en la carretera Pachuca-Actopan. Además, en el mismo municipio, se halló a una persona degollada en un hotel, dentro de una habitación. Esta persona aparentemente entró con otra que logró escapar sin ser vista por la seguridad del lugar.</t>
-  </si>
-  <si>
-    <t>Tlaxcala</t>
-  </si>
-  <si>
-    <t>Tuvimos ayer un incidente, pues un desafortunado incidente, hubo un reporte por parte de vecinos de la zona de San Agustín Tlaxiaca respecto a unos objetos, unas bolsas de plástico que fueron localizadas en un paraje ahí abandonado, un paraje desértico cerca de la zona de Santa Catarina. Al acudir la policía localizó varios, dos cuerpos sin vida. Aldo Capón. Así es Andrés, lamentablemente este hallazgo que se reportó la mañana del día de ayer en la carretera Pachuca-Actopan, en su tramo correspondiente a San Agustín de la Ciudad, que es la comunidad de Santa Catarina, donde fue localizado el cuerpo de una persona dentro de una bolsa. Igualmente en este mismo municipio se fue localizado en el interior de un hotel una persona degollada dentro de una habitación, aparentemente ingresó con otra persona, la cual logró salir sin ser detectada por la seguridad del mismo establecimiento.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zIQpVIiBGgjpqxa5kCaflFhOgZPV9nvu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Está la campaña estatal de vacunación, vacunación invernal, que la Secretaría de Salud puso en operación hace unos días. Hay más de un millón quinientas mil dosis de vacunas contra el COVID, contra la influencia estacional. Por favor, acuda a su clínica, a su centro de salud más cercano. Hay que estar bien inmunizados, hay que estar preparados para esta temporada invernal, principalmente niños menores de cinco años, adultos mayores. Es muy importante que reciban sus vacunas. Todo es gratuito. Esto todo es, por supuesto, gratuito en el tema de la salud acá en el estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/15Io4lEaXYBpFWT2j7n0ztGP5QCD-YjTV/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Andrés Torres: Gracias a toda la gente que nos sigue a través de las redes sociales, que nos escribe diariamente, que está muy pendiente de las vocales, les repito, más de 12 años de transmisiones interrumpidas, a punto de cumplir 13 años, y sobre todo le agradezco muchísimo a la gente que todos los días, todos los días sin excepción, nos saluda, gracias, creo que prácticamente es el único programa de radio y televisión de algo que tiene interacción con el auditorio, ¿no? Somos el único, bueno y tenemos interacción Porque como están cortados los teléfonos Por falta de pago, pues nosotros Tenemos que poner un teléfono Tenemos que poner un canal de WAF Todo eso A cuenta de La propia producción Y pues mire Con la agradable noticia de que Muchísima, muchísima gente Nos escucha todos los días</t>
-  </si>
-  <si>
     <t>Precariedad laboral</t>
   </si>
   <si>
-    <t>Gracias a toda la gente que nos sigue a través de las redes sociales, que nos escribe diariamente, que está muy pendiente de las vocales, les repito, más de 12 años de transmisiones interrumpidas, a punto de cumplir 13 años, y sobre todo le agradezco muchísimo a la gente que todos los días, todos los días sin excepción, nos saluda, gracias, creo que prácticamente es el único programa de radio y televisión de algo que tiene interacción con el auditorio, ¿no? Somos el único, bueno y tenemos interacción Porque como están cortados los teléfonos Por falta de pago, pues nosotros Tenemos que poner un teléfono Tenemos que poner un canal de WAF Todo eso A cuenta de La propia producción Y pues mire Con la agradable noticia de que Muchísima, muchísima gente Nos escucha todos los días</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1efLLBmzgDLMaHEXFBx79VCioh7vPS-aB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Andrés Torres: cumplimos un mes fuera del aire en nuestra estación 91.1 de frecuencia modulada allá en Jacala de Ledezma. Bueno, pues yo apelo a las autoridades que nos ayuden para que podamos resolver este asunto. Evidentemente el área administrativa y el área de ingeniería no lo pueden resolver. Ahí ellos tendrán que dar cuentas Por qué este asunto no avanza Lo que nos corresponde a nosotros es estar pendientes Tener nuestras programaciones a punto Y el personal ahí pendiente para que estemos En el momento de que se restablezca la señal Trabajar como nos corresponde</t>
-  </si>
-  <si>
-    <t>Vamos a iniciar rápidamente con nuestro recorrido, no sin antes recordarles cumplimos un mes fuera del aire en nuestra estación 91.1 de frecuencia modulada allá en Jacala de Ledesma. Bueno, pues yo apelo a las autoridades que nos ayuden para que podamos resolver este asunto. Evidentemente el área administrativa y el área de ingeniería no lo pueden resolver. Ahí ellos tendrán que dar cuentas Por qué este asunto no avanza Lo que nos corresponde a nosotros es estar pendientes Tener nuestras programaciones a punto Y el personal ahí pendiente para que estemos En el momento de que se restablezca la señal Trabajar como nos corresponde</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HU_7S4nKVp_AIQPjL5BnjnyCIf1HfdVz/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Hay una onda fría y un frente frío en todo el territorio nacional, especialmente en el estado de Hidalgo. La Subsecretaría de Protección Civil del Estado pide a la población estar atentos a la bajada de temperaturas, sobre todo en áreas altas, donde se esperan heladas y temperaturas de hasta 0 grados. Para el 21 de octubre de 2026, se informa que habrá chubascos de 5 a 25 milímetros y temperaturas de 0 a 5 grados. También se pronostican vientos de 20 a 30 kilómetros por hora, con rachas de 40 a 60 kilómetros por hora.</t>
-  </si>
-  <si>
-    <t>Recordándole que hay una onda fría, tenemos frente frío acá en la territorio, pues prácticamente en todo el territorio nacional, pero en el estado de Hidalgo hay un llamado que nos hace la subsecretaría de protección civil del gobierno del estado a través de la secretaría de gobierno para estar muy atentos ante estos descensos de temperaturas, sobre todo en zonas altas de nuestro estado, Se esperan heladas, temperaturas hasta de 0 grados Vamos por favor Aldo Falcón ¿Qué nos dice la Subsecretaría de Protección Civil? Así es Andrés, la Subsecretaría de Protección Civil Y Gestión de Riesgos Informa a la población que para este 21 de octubre de 2026 De acuerdo con el aviso número 585 Del pronóstico meteorológico general Del Servicio Meteorológico Nacional Se prevén intervalos de chubascos de 5 a 25 milímetros Asimismo se pronostican temperaturas de 0 a 5 grados Con vientos de 20 a 30 kilómetros por hora con rachas de 40 a 60 km por hora.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/103LSbwMf-t8eOEh0Oe_nbr3b6MJKfimt/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SSH hace un llamado a reforzar medidas de prevención ante el incremento de enfermedades respiratorias</t>
-  </si>
-  <si>
     <t>Prevención De Enfermedades</t>
   </si>
   <si>
-    <t>Nos vamos hasta el estado de Hidalgo. La Secretaría de Salud de Hidalgo hace un llamado a reforzar medidas de prevención ante el incremento de enfermedades respiratorias. Tras el descenso de temperatura se suman más de 380,000 casos de estos padecimientos en la entidad. Como parte de las acciones preventivas y de promoción de la salud impulsadas por el gobierno de Julio Menchaca Salazar, la Secretaría de Salud de Hidalgo, encabezada por Vanessa Escalante Arroyo, mantiene el llamado a la población para fortalecer las medidas de autocuidado durante la actual temporada de frío y con especial atención a los grupos más vulnerables. De acuerdo con las cifras epidemiológicas, actualmente la entidad registra 380,323 casos de infecciones respiratorias agudas, lo que representa un decremento de 8.2% respecto al mismo periodo del 2025, cuando se contabilizaron 414,106 casos. Los municipios con mayor número de casos son Pachuca, Tulancingo, Tula, Ixmiquilpan y Actopan. Por lo anterior y con el curso de con el curso del actual frente frío número dos, la Secretaría de Salud de Hidalgo recomienda abrigarse adecuadamente, evitar cambios bruscos de temperatura, mantener una alimentación equilibrada, lavarse las manos frecuentemente y practicar el estornudo de etiqueta. También se invita a revisar y complementar el esquema de vacunación contra la influenza, COVID-19 y neumococo, conforme a las indicaciones correspondientes, de acuerdo con Rubí Vargas Vargas, coordinadora de comunidades y municipios de la Subsecretaría de Salud Pública, es necesario que antes de ante las bajas que ante las bajas temperaturas se extremen precauciones en el hogar, evitar intoxicaciones por monóxido de carbono y quemaduras, particularmente al utilizar equipos de calefacción. Agregó que se recomienda no encender anafres o braseros en espacios cerrados. Vamos a escuchar parte de lo que destaca la coordinadora de comunidades y municipios de la Subsecretaría de Salud Pública, Rubí Vargas Vargas.
-“La temporada de frío o temporada invernal, se incrementan de manera importante las enfermedades respiratorias. Por esta razón, la Secretaría de Salud fortalece las acciones de promoción y difusión sobre recomendaciones para enfrentar efectos negativos a la salud de forma prioritaria en grupos vulnerables como menores de 5 años, adultos mayores, personas en situación de calle o pobreza extrema. Entre las medidas preventivas que podemos compartir con la población en general son pues lavarse las manos de forma frecuente antes de consumir o preparar alimentos, después de utilizar el baño y en especial después de tener contacto con personas enfermas, cubrir nariz y boca al toser o estornudar con el ángulo del codo, lo que llamamos estornudo de etiqueta, o bien hacerlo con un pañuelo. Esto disminuirá el riesgo de contagio de las personas a nuestro alrededor. Abrigarse con ropa adecuada como gorro, guantes, bufanda, evitar en lo posible los cambios bruscos de temperatura y corrientes de aire frío, consumir suficientes líquidos, consumir frutas y verduras ricas en vitaminas A, C y D. Importante vacunarse contra influenza y COVID, además de neumococo de acuerdo a la edad correspondiente”.
-Señaló que ante síntomas como fiebre, tos, escurrimiento nasal o cansancio, es importante evitar la automedicación y acudir a valoración médica. Si se presenta dificultad para respirar o dolor torácico, se debe buscar atención médica urgente. Es lo que se destaca desde la Secretaría de Salud del Estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/19ovqUJXYnhhpCr8EIktWgsi1-4O6gjF7/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Rubí Vargas Vargas</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
-    <t>Locutor Jesús Riveros da lectura a comentario de radioescucha que reporta retrasos y deficiencias en una obra de infraestructura cercana al plantel Cecyte en Tulancingo, señalando que los trabajos han permanecido pausados por casi un año. La inconformidad destaca la falta de banquetas para los estudiantes, lo cual genera condiciones de riesgo en la época de lluvias debido a la acumulación de lodo y resbalones de los alumnos, sin que haya una fecha definida para la pavimentación de la zona.</t>
-  </si>
-  <si>
-    <t>Media superior</t>
-  </si>
-  <si>
-    <t>Continuamos con más información. También por acá nos están enviando este reporte que ya ha sido canalizado a las autoridades sobre... bueno, nos dicen: "Buenas tardes, llevamos ya casi un año en el Cecyte de Tulancingo y esta obra va en pausas. Eh, pues nos dice que que ve que la están haciendo mal. Los alumnos no tienen banqueta para caminar y está muy peligroso por el lodo en esta época de lluvias. Los chicos incluso se han resbalado". Y nos comparte la imagen de una parte donde dice: "Aquí ni siquiera hay para cuándo les pavimenten a los a los alumnos". Esto para los alumnos que van al Cecyte y con gusto lo lo compartimos en instantes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nw6B9Mn6YEdPKd98f68_ihsiaMEcVcZi/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Locutor Jesús Riveros da lectura a comentario de radioescucha que reporta su inconformidad ante la venta de credenciales escolares en la Escuela Secundaria Técnica 48 Japón, ubicada en la colonia La Cañada. La denunciante señaló que la credencial tiene un costo de $60 pesos y que las autoridades del plantel informaron que por el momento no será utilizada hasta nuevo aviso, expresando que esta medida le parece un negocio irregular.</t>
-  </si>
-  <si>
-    <t>Bueno, y hablando de educación precisamente nos están por acá reportando, reportando que nos dicen: "Buenas tardes, sí yo le comento soy una madre de familia que estoy inconforme por una por una eh este credencial dice, sí por una credencial que están vendiendo en la Técnica 48 Japón ubicada en la colonia La Cañada. Su costo es de $60 pesos y dicen que por el momento no se ocupará hasta que les avisen. La verdad que opino todo es negocio".</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1OyMm4diHKQJLQvaelnEZ6CnL8Ihmkc3A/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Hidalgo consolida liderazgo en indicadores educativos a nivel nacional</t>
   </si>
   <si>
-    <t>Déjeme compartirle la información que emite la Secretaría de Educación Pública y es que ayer, precisamente, el secretario Natividad Castrejón compareció ante el Congreso del Estado, donde informó que Hidalgo avanza en el fortalecimiento de su sistema educativo y escala una posición, una mejor posición para colocarse como el octavo estado del país con mejor desempeño en eficiencia terminal. A este logro se suma el progreso obtenido en el diagnóstico de los ejercicios integradores de aprendizaje y la inversión sostenida en infraestructura educativa, ciencia y tecnología, así como del deporte, que amplía las oportunidades de desarrollo para las y los estudiantes. Durante estos cuatro años, el proyecto educativo de la actual administración ha impulsado la formación de estudiantes capaces de transformar sus comunidades, fortalecer su identidad y contribuir a una sociedad más justa y humana. Cada trayectoria escolar suma al bienestar colectivo y nos acerca a un propósito común: sabernos un solo Hidalgo. Así lo expuso el secretario de Educación Pública, como le digo, durante su comparecencia ante las y los integrantes del Congreso del Estado, como parte de la glosa del cuarto informe del gobernador Julio Menchaca Salazar. En cuanto a indicadores, Hidalgo ha tenido significativas mejoras en todos los niveles para que las y los estudiantes permanezcan y concluyan sus estudios satisfactoriamente. En este contexto, Natividad Castrejón informó que la entidad mantuvo el 39% de la proporción de estudiantes que concluyen la educación superior por cada 100 que ingresan a primero de primaria. Este indicador sitúa a Hidalgo en el octavo lugar nacional, lo que representa un avance de una posición respecto al año anterior. Uno de los avances más sobresalientes se registró en educación media superior, donde la eficiencia terminal pasó del 63.2% en el ciclo escolar 2021-2022 a 75.6% en el 2024-2025, lo que significó un incremento de 12.4 porcentuales —puntos porcentuales—. En educación superior también se logró un importante incremento en eficiencia terminal, la cual avanzó de 69.6 a 84.5%, es decir, una mejora de 19. —perdón, de 14.9 puntos porcentuales—. En cuanto al bachillerato, con el propósito de ampliar las oportunidades educativas, el secretario destacó la incorporación de seis servicios de educación media superior que permitieron garantizar la presencia de al menos un plantel público de este nivel de bachillerato en cada uno de los 84 municipios de Hidalgo. A estas acciones se suman la creación de 12 nuevos servicios de educación media superior; dos son bachilleratos generales, dos telebachilleratos comunitarios y ocho operarán bajo el modelo de bachillerato nacional Margarita Maza para atender a jóvenes de 6 municipios y ofrecer alternativas flexibles que faciliten la continuidad de sus estudios. Asimismo, se iniciaron las gestiones para construir 10 planteles de telebachillerato comunitario con instalaciones propias en zonas rurales, todo eso mediante una inversión de 290 millones de pesos. Y una de las cosas que también destacó el secretario es la red de laboratorios STEM; subrayó que la entidad continúa fortaleciendo la formación científica y tecnológica de sus estudiantes en educación media superior y superior con esta red de laboratorios STEM, es una red, dijo, la más grande del país y son espacios que impulsan el aprendizaje práctico y se acercan a las y los jóvenes a disciplinas estratégicas como robótica, inteligencia artificial, automatización y drones, y actualmente 47 planteles cuentan cuentan con laboratorios STEM en beneficio de alrededor de 60,000 estudiantes. Y durante esta administración se han destinado 120 millones de pesos a estos espacios, de los cuales 30 millones corresponden al periodo reportado utilizado para equipar 11 nuevos laboratorios, estos espacios que han contribuido a impulsar el talento estudiantil; ejemplo de ello es la participación de 54 estudiantes de ocho instituciones de educación media superior y superior quienes asistieron al campamento mundial VEX Robotics 2026, celebrado en San Luis, Missouri, como parte de la delegación nacional, demostrando el potencial de las y los jóvenes hidalguenses en ciencia, tecnología e innovación. En este ámbito la entidad también destacó por ser sede de la primera competencia Girl Powered México 2025-2026, que reunió a 115 equipos de niñas y mujeres de 12 estados de la república y más de 3000 asistentes. Estaremos tocando otros tópicos, pero después de hacer una pausa, una pausa, por supuesto, y regresamos con más aquí en Enlace Hidalgo. Cerramos el tema de la Secretaría de Educación Pública y continuamos. Perfectos, bueno pues Natividad Castrejón informó que durante la administración se han destinado 2,700 millones de pesos a infraestructura educativa, de los cuales 780 millones corresponden al periodo reportado con acciones en alrededor de 1,500 planteles en beneficio de 160,000 estudiantes. Las obras incluyen la construcción y rehabilitación de aulas sanitarios, bardas perimetrales, canchas, techumbres e instalaciones eléctricas. A esta inversión se suman más de 4,400 millones de pesos destinados en 4 años a la entrega de útiles, uniformes, calzado y libros para alrededor de 570,000 estudiantes por ciclo escolar, apoyos que representan un alivio para la economía de miles de familias hidalguenses al reducir los gastos escolares y permitir que más recursos se destinen a otras necesidades del hogar, además de ampliar las oportunidades para que niñas, niños y jóvenes continúen sus estudios. Y en otros temas, también para fortalecer los aprendizajes mediante el acompañamiento docente para valorar los avances y las áreas de oportunidad, Castrejón explicó que durante el ciclo escolar 2025-2026 se aplicaron los ejercicios integradores del aprendizaje a 371,556 estudiantes de 3,237 escuelas con el objetivo de identificar las fortalezas en los cuatro campos formativos del plan de estudios. A partir de esta información señaló en se orientaron y decisiones también pedagógicas y acciones de acompañamiento. Para atender estas áreas, mediante el sistema de alerta temprana se focalizaron 722 escuelas prioritarias de preescolar, primaria y secundaria de donde alrededor de 4,000 docentes participaron en acciones de diagnóstico, acompañamiento, tutoría y seguimiento individualizado con énfasis en lectura, escritura y también en matemáticas. La infraestructura también deportiva de Hidalgo creció con la construcción de la ciudad deportiva de alto rendimiento, proyecto en el que se invirtieron 529 millones de pesos y que cuenta con instalaciones para la práctica de 35 disciplinas, además de espacios para albergar competencias nacionales. Este complejo impulsa la preparación de deportistas de alto rendimiento y amplía las oportunidades para las prácticas de deporte social en beneficio de más de 300,000 hidalguenses. Resalta, además, que durante estos cuatro años las y los deportistas hidalguenses de alto rendimiento obtuvieron 536 medallas en la Olimpiada Nacional y Paralimpiada, 161 de oro, 165 medallas de plata y 210 de bronce. En el periodo que se informa se obtuvieron 63 medallas y también ejercimos 16.7 millones de pesos para otorgar apoyos a 1,350 deportistas y también entrenadores. Natividad Castrejón subrayó que la formación integral también requiere atender el bienestar emocional y garantizar entornos seguros donde niñas, niños y adolescentes y jóvenes puedan desarrollarse en condiciones de respeto y convivencia pacífica. Mediante el programa de acompañamiento socioemocional, la SEP ha atendido a 820,000 integrantes de la comunidad escolar durante 4 años. Las acciones implementadas en 4,500 planteles de educación básica, media superior y superior promueven la empatía, la gestión y regulación emocional, así como la resolución pacífica de conflictos. En materia de prevención y atención de la violencia, se actualizaron y pusieron en marcha protocolos para prevenir, detectar y atender el acoso y el maltrato escolar en todas las escuelas de educación básica. Asimismo, Hidalgo cuenta con un marco local de convivencia escolar actualizado que protege los derechos de niñas, niños y adolescentes. Natividad Castrejón reiteró que el compromiso de la política educativa es generar que todas y todos los estudiantes aprendan y permanezcan también en las aulas y también también también que concluyan sus estudios con las herramientas necesarias para construir su proyecto de vida, sin importar su lugar de origen y las condiciones económicas de su familia. Reconoció, además, que aún existen retos para fortalecer los aprendizajes, garantizar entornos escolares seguros e impulsar el desarrollo integral y el deporte, por lo que es indispensable trabajar cada día, sumar esfuerzos y reconocer el compromiso de quienes hacen posible la educación en el Estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Bl-Ta1xxrMLot2udu1rropO1nb3_euHs/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Congreso del Estado de Hidalgo</t>
   </si>
   <si>
-    <t>Durante su comparecencia ante el Congreso de Hidalgo, la secretaria de movilidad y transporte, Lyzbeth Robles Gutiérrez, informó sobre las acciones de su dependencia en el marco de la glosa del cuarto informe del gobernador Julio Menchaca Salazar. Ante cuestionamientos de la diputada Claudia Lira Luna sobre la problemática del tráfico en las horas pico al sur y centro de Pachuca, la secretaria indicó que se realizarán análisis técnicos mediante cámaras con inteligencia artificial instaladas en puentes del bulevar Felipe Ángeles. Asimismo, reiteró que la legislación vigente protege y establece la exclusividad del carril confinado para el transporte masivo (BRT) con el fin de garantizar una movilidad segura y eficiente.</t>
-  </si>
-  <si>
-    <t>Y esta mañana compareció en el Congreso de Hidalgo la maestra Lyzbeth Robles Gutiérrez, secretaria de movilidad y transporte. El presidente del Congreso, Andrés Velázquez, dio la bienvenida a la maestra Lyzbeth  Robles Gutiérrez.
-...la escuela, las autoridades, ir al trabajo o recibir atención médica comienza para muchas personas con la posibilidad de trasladarse. La movilidad forma parte de las oportunidades que una comunidad puede aprovechar cada día. Hoy recibimos a la maestra Lyzbeth Robles Gutiérrez, secretaria de movilidad y transporte, en el marco de la glosa del cuarto informe del gobernador, el licenciado Julio Menchaca Salazar. Secretaria, sea usted bienvenida a esta soberanía. En esta ruta informativa en este congreso de Hidalgo la maestra Lyzbeth  Robles Gutiérrez emitió mensaje, da a conocer el informe y también respondió algunas cuestiones. La diputada Claudia Lira Luna preguntó acerca de un exhorto que realizó a esa Secretaría de Movilidad y Transporte para llevar a cabo mesas de análisis o estudio para dar salida y que ya no existiera el problema de tráfico en las horas pico en el sur de Pachuca. Escuchemos a la legisladora Claudia Lira Islas.
-...un análisis o un estudio para dar viabilidad y que no exista ese problema de tráfico precisamente en las horas pico en los tramos de la de la del sur de Pachuca y en algunos tramos del centro de Pachuca.
-Señor secretario, por favor. Es cuánto. En esta respuesta que se dio durante ese marco, también Lyzbeth  Robles señaló, este exhorto en su momento no había llegado precisamente a su oficina, por lo tanto, informó que se están llevando a cabo, desde luego también, ya a sacar vehículos y habrá mesas. En este instante se mencionó, se va a llevar a cabo el análisis clínico con cámaras para medir el número de unidades que circulan y entonces estar en posibilidades de realizar acciones. También subrayó que existe una ley en materia de transporte vigente en torno a carril exclusivo y que contempla la utilización de un carril único para el transporte público. Esa ley tiene más de 10 años. La respuesta, Lyzbeth  Robles Gutiérrez, señaló una explicación clara.
-Que hizo el anuncio de que estaríamos realizando un análisis por medio de unas cámaras que se van a situar en tres puentes sobre el bulevar Felipe Ángeles, en donde tenemos también puentes a cargo del Sistema Integrado de Transporte Masivo, y que en esas cámaras que tienen utilización de inteligencia artificial nos va a permitir también medir el número de unidades conjuntamente con la información que pueda ser proporcionada por seguridad pública y por seguridad pública y tránsito municipal de Pachuca. Que una vez que tengamos eso y que a la vez se haga la reunión correspondiente o las acciones inherentes a través de la coordinación que en su momento se origine por la Secretaría de Gobierno, estaremos en posibilidad de pronunciarnos de fondo. En ese momento yo mencioné lo que legalmente le correspondía a la Secretaría y al organismo mencionado en torno al carril exclusivo. El carril exclusivo la ley establece que se debe de privilegiar obviamente para la operación y eficacia adecuada del transporte masivo, insisto que fue originado hace más de 10 años con una infraestructura en la cual cuenta con además de puentes y estaciones con el carril adecuado y exclusivo para que pueda brindar un servicio eficaz con las frecuencias de pasos correspondientes. Y además es un tema de seguridad vial. Cuando las unidades de vehículos particulares transitan sobre un carril exclusivo, el congestionamiento se extiende no solamente a los carriles en donde de manera ordinaria transitan los vehículos particulares, sino que se extiende también ese congestionamiento vial hacia el carril exclusivo, lo cual incrementa el congestionamiento a lo ancho de toda la vialidad. Las vialidades son de todas y de todos y también debemos aprender a compartir las y está apegado a la ley, a las políticas internacionales, nacionales y estatales, el hecho de que exista carril confinado para que las unidades de transporte masivo, que son generalmente en este caso a través de unidades BRT, se pueda llevar a cabo de manera óptima.
-Bueno, en esta materia la respuesta entregada esta mañana, el día de mañana tendremos más la continuidad, es un adelanto de lo que se menciona, pero bueno, es un asunto de ley. Cuando se llevó a cabo la construcción de este instrumento de movilidad, pues la ley señala es un carril exclusivo, es un carril único para el transporte público. Y efectivamente, si se abre entonces, pues ya no solamente va a haber dos carriles saturados, sino van a ser tres. Aquí el tema está también en la educación vial que tenemos cada uno de las y los ciudadanos. El día de ayer por la tarde, vemos que esto es muy común. Hay un el carril derecho, perdón, para habilitarse y salir hacia en Pachuca hacia la parte sur, pues está muy comprometido. Eh asomar la vuelta y procurar meterse y entonces esto genera que los demás vehículos también pues vayan atorándose, enfrentándose y haciéndose nudos. También depende mucho, desde luego, no es ánimo de justificar a nadie, pero lo hemos comentado. En cuanto al hecho de las motocicletas, el día de ayer también manejando, vemos un joven haciendo malabares, subiéndose a su motocicleta, casi parado en los asientos, metiéndose entre un vehículo y otro, pues todos esos son son riesgos y desde luego también con la lluvia, con todo esto, si se habilitan los vehículos al carril de transporte público, pues obviamente va a generar más conflicto, pero es un tema, como se subrayó esta mañana, es un tema de ley. Es la ley la que determinó así que se hiciera este carril único, pero esa ley tiene diez años.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1lBQoZXW74i8PDOlrAoo5FkQbpdeHcX9o/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Lyzbeth Robles</t>
   </si>
   <si>
-    <t>Julio Menchaca, Andrés Velázquez Vázquez, Claudia Lilia Luna</t>
-  </si>
-  <si>
-    <t>UPLAPH/Bol.160/2026</t>
-  </si>
-  <si>
-    <t>Durante su intervención, Onésimo Serrano destacó que a partir de la actualización del Plan Estatal de Desarrollo se ha brindado acompañamiento a las dependencias y organismos del gobierno de Hidalgo para alinear sus programas sectoriales, institucionales y especiales, actualizando cerca de 84 instrumentos de planeación y capacitando a los 84 municipios con una metodología homologada para los periodos 2024-2027. Asimismo, señaló la importancia de la coordinación interinstitucional y la participación ciudadana mediante el COPLADEIH y los COPLADEM, habiendo participado en más de 300 sesiones para definir obras y acciones prioritarias con las comunidades.</t>
-  </si>
-  <si>
-    <t>Precisamente vamos a escuchar el audio de Onésimo, Onésimo Serrano.
-“A partir de la actualización del Plan Estatal de Desarrollo, acompañamos a las dependencias y organismos del gobierno de Hidalgo en la alineación de sus programas sectoriales, institucionales y especiales. Cerca de 84 instrumentos de planeación se están actualizando. Asimismo, capacitamos a 84 instancias de planeación municipal de Hidalgo con una metodología homologada, para contar con una visión articulada en la entidad. Con ello se actualizan los planes municipales de desarrollo 2024-2027. En ambos casos, elaboramos guías metodológicas y brindamos capacitación y acompañamiento técnico. Pero la planeación no se limita a establecer objetivos y programas, requiere de coordinación entre las instituciones, los municipios y la participación ciudadana. Para ello, a través de las sesiones del Comité de Planeación para el Desarrollo del Estado, el COPLADEIH, integrado por representantes de este honorable Congreso, del Senado, de la Cámara de Diputados, de las delegaciones federales, de los municipios, de las y los titulares de las dependencias del Poder Ejecutivo estatal, así como de representantes de diversos sectores de la sociedad, evaluamos los procesos de planeación institucional, articulamos esfuerzos interinstitucionales e incorporamos las aportaciones de sus integrantes en la formulación, ejecución, evaluación y actualización de los instrumentos de planeación. Esta estrategia para el desarrollo también busca fortalecer los sistemas municipales de planeación democrática. Durante el periodo que se informa, hemos participado en más de 300 sesiones de los COPLADEM, espacios donde cada municipio, en ejercicio de su autonomía, identifica junto con su comunidad las obras y acciones prioritarias. Como escuchamos, Onésimo Serrano destacó que la planeación se ha consolidado como una herramienta para articular la participación ciudadana, la información territorial, el conocimiento científico y la coordinación institucional con el propósito de orientar las decisiones públicas hacia las necesidades de las y los hidalguenses”.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JXEiey-1qoIi5Myc4TcvEGH7EFAM9m6Y/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Uno de los ejes emblemáticos de la administración encabezada por el gobernador Julio Menchaca Salazar ha sido la educación, logrando posicionar a Hidalgo en el octavo lugar nacional en eficiencia terminal. Se destaca que el 39% de los alumnos que ingresan a primaria logran concluir la educación superior, incrementando la eficiencia terminal en 12.4 puntos porcentuales. Asimismo, la entidad cuenta con la red de laboratorios de ciencia y tecnología más grande del país, abarcando 47 planteles que benefician a cerca de 60,000 estudiantes, además de haberse destinado más de 4,400 millones de pesos en apoyos a la economía en este sector.</t>
-  </si>
-  <si>
-    <t>Uno de los temas emblemáticos del gobierno encabezado por Julio Menchaca Salazar es la educación. Hidalgo, señalaba yo, ha sido uno de los estados, las entidades que una mayor y mejor inversión se han colocado en la educación. Octavo lugar nacional en eficiencia terminal. Hidalgo avanzó una posición, alcanzó un 39% de estudiantes que sí concluyen la educación superior por cada 100 que ingresan a primaria. Hay una mayor conclusión de estudios, la eficiencia terminal aumentó en 12.4 puntos porcentuales. Hay una mayor cobertura educativa, liderazgo en ciencia y tecnología, Hidalgo cuenta con la red de laboratorios más grande del país con 47 planteles que benefician cerca de 60,000 estudiantes. Apoyos a la economía, como ya escuchábamos, más de 4,400 millones de pesos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YcgpEF5MTlYyMluzp0Gxi8tkI9wxZk1y/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Durante su comparecencia ante el Congreso del Estado como parte de la glosa del informe de gobierno de Julio Menchaca Salazar, el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdés, informó que la entidad escaló al octavo lugar nacional en eficiencia educativa. El funcionario destacó el incremento en la conclusión de estudios de nivel medio superior y superior, así como una inversión acumulada de 2,700 millones de pesos en infraestructura, de los cuales 780 millones se destinaron recientemente a 1,500 planteles. Asimismo, resaltó una inversión de más de 4,400 millones de pesos en la entrega de útiles y uniformes escolares para aproximadamente 570,000 alumnos por ciclo escolar.</t>
-  </si>
-  <si>
-    <t>Continuamos esta tarde en la información de las comparecencias en el Congreso del Estado de Hidalgo el día de ayer, primera hora estuvo el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdés. Tienes la información.
-Hidalgo avanzó al octavo lugar nacional en eficiencia educativa, así lo informó el secretario de Educación Pública Estatal, Natividad Castrejón Valdés, durante su comparecencia ante el Congreso del Estado como parte de la glosa del informe de gobierno de Julio Menchaca Salazar. 
-Tenemos una convicción firme: educar es ampliar las posibilidades de transformar el presente y el futuro de Hidalgo. 
-Ante las y los legisladores, el funcionario presentó los principales indicadores y acciones desarrollados en el sector educativo, entre los que destacó el incremento en la conclusión de estudios de nivel medio superior y superior, así como las inversiones destinadas a infraestructura, apoyos escolares y bienestar de la comunidad educativa. En cuanto a materia de infraestructura, el titular de la SEPH reportó una inversión acumulada de 2,700 millones de pesos durante la actual administración; de ese monto, 780 millones de pesos se destinaron recientemente a trabajos en 1,500 planteles educativos. Entre otros temas y respecto a los apoyos para estudiantes, el secretario informó que se han invertido más de 4,400 millones de pesos en la entrega de útiles y uniformes escolares, con una cobertura aproximada de 570,000 alumnos por ciclo escolar.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1eVmC89aMtg5nhNWYD-7uctVrA4ecpOzM/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, anunció que el coordinador jurídico del estado, Raúl Serret Lara, prepara una denuncia penal contra la plataforma Uber por operar en Pachuca de manera ilegal y sin los permisos correspondientes. El mandatario estatal señaló que la ley contempla sanciones tanto para quienes promueven el servicio irregular como para aquellos que lo utilizan con fines de lucro sin estar debidamente registrados. Asimismo, aclaró que aunque la legislación permite concursar por una concesión estatal, prestar el servicio operando de forma arbitraria constituye una ilegalidad.</t>
-  </si>
-  <si>
-    <t>De una vez le informo, de una vez vámonos tendidos. En este hilo informativo, el gobernador de Hidalgo, Julio Menchaca Salazar, dio a conocer que el coordinador jurídico del gobierno del Estado, Raúl Serret Lara, integra ya una carpeta formal para iniciar una denuncia penal contra Uber, luego de que la empresa habilitara en su plataforma la opción de operar en Pachuca de manera ilegal. Asimismo, se ha señalado que la legislación penal contempla disposiciones para sancionar el uso indebido de un servicio público, en este caso, el mandatario explicó, podrían incurrir en una falta tanto quienes promueven la plataforma como quienes de manera no consciente y con la intención de generar un ingreso son engañados. Mire usted, eh utilizar una plataforma, que se comentaba el día de ayer, bueno, pues, Dios no lo quiera, algo sucede, ¿no? ¿Y quién responda? No va a haber quien responda. Ni por usted, ni por lo que suceda. ¿Por qué razón? Porque no están registrados. O sea, es ilegal. El titular del Ejecutivo estatal reconoció que la legislación vigente permite sí que las empresas que brindan servicio de transporte por aplicaciones puedan concursar por una concesión en el estado, sin embargo, una cosa es concursar y que se apruebe, y otra cosa, decir, ya estoy trabajando, eso es ilegal. Una pausa, regreso.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1-mdOTt5QJ9KjW0_NNca5gpHumv4dv_eW/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Raúl Serret Lara</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hoFcwsY6qo0Gd4usbJ97dHcCFwDpeBz5/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Pemex</t>
-  </si>
-  <si>
-    <t>Raúl Ojeda Zubietta, Alejandro Velázquez Mendoza</t>
-  </si>
-  <si>
-    <t>Cultura/Bol.713/2026</t>
-  </si>
-  <si>
-    <t>Caravana Cultural llenará de arte Xochicoatlán</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
-    <t>Caravanas Culturales</t>
-  </si>
-  <si>
-    <t>Xochicoatlán</t>
-  </si>
-  <si>
-    <t>Y por otra parte, le comento que la Secretaría de Cultura estatal anunció una serie de actividades artísticas para las familias de Singuilucan. El programa se realizará hoy, 21 de octubre, en la Plaza Bicentenario; reunirá a cinco agrupaciones con intérpretes locales y de otras regiones. El evento forma parte de la caravana cultural cuyo objetivo es acercar espectáculos escénicos y musicales a las regiones del estado, así como fomentar el arte y las tradiciones. Cabe señalar que este día pues esta caravana tendrá una duración de más de 3 horas y va a comenzar con el grupo de danza Nexti, integrado por estudiantes del CBTA número 6, esto a las 3:30 de la tarde. 15 horas con 35 minutos es la hora exacta que da a conocer para el inicio de estas actividades. A las 4 de la tarde con 10 minutos tiene se tiene programada la presencia de Los Bohemios de Hidalgo y a las 5 de la tarde subirá al escenario el grupo de danza Santa María Magdalena, dedicado a preservar los bailes tradicionales de su comunidad. Las últimas dos actuaciones estarán vinculadas con la música popular. A las 5:30 de la tarde tocará la Banda de Viento Tradicional Tres Estrellas de Oro, mientras que el Trío Encanto Juvenil cerrará la jornada a partir de las 6 de la tarde. Es lo que se tiene programado para este día en el municipio de Singuilucan, la Plaza Bicentenario de este municipio serrano de Singuilucan con la llegada de las caravanas culturales.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1_x5j3W7UGU1NpJvDCPIagH1ngfsuUMP5/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El Gobierno de Julio Menchaca Salazar fortalece la planeación estatal con participación, evaluación e innovación.</t>
-  </si>
-  <si>
-    <t>En el calendario de comparecencias también ya tocó el turno a nombre de la Unidad de Planeación y Prospectiva, pues brindar la información a los integrantes de la Sexagésima Sexta Legislatura local en la glosa del cuarto informe de gobierno, al encargado del despacho de esta unidad, Onésimo Serrano Rivera, quien destacó que el trabajo de esta institución se organiza en cuatro ejes que forman parte de un mismo ciclo: planear permite, dijo, definir el rumbo; implementar, lleva las prioridades al territorio; evaluar ayuda a conocer los avances y corregir lo que haga falta; e innovar facilita la relación de las personas con las instituciones. Como parte de la actualización del Plan Estatal de Desarrollo, dijo, se incorporaron 26,367 propuestas ciudadanas en los nuevos nueve ejes generales y tres ejes transversales que integran este plan, con un horizonte hacia 2040. A partir de este instrumento, la unidad acompañó la elaboración de 84 instrumentos y la actualización de los planes municipales de desarrollo 2024-2027. Las 84 instancias municipales de planeación recibieron capacitación con una metodología homologada. La coordinación con los municipios también se refleja en la participación de la unidad en más de 300 sesiones de los comités de planeación para el desarrollo municipal. En materia metropolitana, Hidalgo pasó de un municipio reconocido a ocho dentro de la zona metropolitana del Valle de México. La actualización del programa de ordenación de esta zona ha incluido sesiones técnicas, reuniones de trabajo, talleres participativos, consultas ciudadanas y consultas a pueblos y comunidades indígenas. Entre los proyectos de planeación territorial se encuentran tres programas parciales de desarrollo urbano vinculados con las nuevas rutas ferroviarias, un plan de movilidad urbana sustentable para siete municipios de la zona metropolitana de Pachuca y la estrategia de parcelas demostrativas en el marco del Programa Nacional de Tecnificación. En estas últimas se han observado ahorros de agua de hasta 80% mediante riego por goteo. A través de la Comisión Estatal para el Desarrollo de los Pueblos Indígenas, los programas de atención llegaron a 45 municipios con presencia indígena. Más de 21,000 personas fueron beneficiadas con las macrojornadas "Haber, Haber". La política en ciencia, tecnología e innovación combina formación, financiamiento y reconocimiento. Este año se sumaron 115 personas becadas y se contemplan 105 iniciativas científicas de innovación. También se impulsa proyectos aplicados como el laboratorio de nuevos alimentos, este también la participación fundamental se destacó en esta comparecencia de las mujeres en el desarrollo científico. La evaluación permite revisar si las políticas públicas están produciendo los resultados esperados. El Laboratorio de Políticas Públicas suma casi 100 productos de información y 35 instrumentos técnicos, entre plataformas, tableros y mapas web, trabajo que fue reconocido por el Sistema Nacional de Información Estadística y Geográfica del INEGI. En materia de digitalización y simplificación administrativa, se eliminaron 296 requisitos en 118 trámites cotidianos en coordinación con seis municipios; de estos, 83 ya cuentan con plazos de resolución más cortos. A nivel estatal, se se modelaron más de 300 trámites, se simplificaron 202 trámites y servicios y se activaron siete trámites en línea del Registro Civil. Durante su intervención, Onésimo Serrano Rivera subrayó que la planeación debe mantenerse vinculada con el territorio, reconocer las brechas que todavía existen y utilizar información para fortalecer las decisiones públicas. Así la comparecencia del encargado del despacho de la Unidad de Planeación y Prospectiva del Gobierno del Estado.</t>
-  </si>
-  <si>
-    <t>Congreso del Estado Hidalgo</t>
-  </si>
-  <si>
-    <t>A raíz de los conflictos regulatorios con el servicio de Uber en el estado de Hidalgo, donde el gobierno estatal anunció denuncias por operar sin permisos, comenzó a promocionarse en Pachuca y Tulancingo una nueva plataforma mexicana llamada "Pronto". Esta aplicación ofrece servicios de transporte de pasajeros y paquetería bajo un modelo de suscripción fija para los conductores y sin comisión por trayecto, operando de manera digital. Sin embargo, la entrada de estas plataformas en la entidad continúa generando cuestionamientos por parte de las autoridades y el gremio transportista debido a la falta de concesiones formales bajo la legislación vigente en el estado.</t>
-  </si>
-  <si>
-    <t>Y, pues bueno, a raíz de este, eh pues de este conflicto entre entre Uber y el gobierno del Estado de Hidalgo, que por cierto el gobernador informó, informó que la coordinación general jurídica de su gobierno, pues prepara una denuncia contra Uber por su presunta operación sin los permisos correspondientes y, pues además, pidió a los usuarios del transporte público denunciar formalmente cualquier maltrato o agresión de los conductores. Eh, pues bueno, eh dijo que esta denuncia podrá presentarse en esta misma semana, pero ayer comenzó a circular en redes sociales otra aplicación, otra plataforma que está ofreciendo también el servicio de transporte. Esta plataforma, que se llama Pronto y que es de origen mexicano, comenzó ya a promoverse también en la capital hidalguense, pero también aquí en Tulancingo y usted recordará que hace unos meses intentó también publicitarse, ofrecer el servicio, pero, pero pues no se lo permitieron tanto el gremio de de transportistas como, pues obviamente el gobierno del Estado, por eh pues por no contar con la concesión correspondiente. Le comparto con información de la silla rota que además de Uber, esta aplicación comienza a promoverse en distintas ciudades del Estado de Hidalgo, entre ellas Pachuca y Tulancingo, conocida como Pronto, una plataforma mexicana cuya publicidad ya anuncia su entrada también a Pachuca y que conecta personas que necesitan un traslado con conductores registrados en su sistema. La difusión de estos anuncios, pues, obviamente dio de qué hablar después de que eh pues usuarios de Uber ya hayan reportado que pueden cotizar y solicitar viajes en Pachuca y, en el caso de Pronto, la publicidad anticipa su llegada, aunque la información disponible no precisa una fecha de inicio, las zonas que atenderá o el número de unidades que tendrá en la ciudad. La plataforma permite ingresar un destino, consultar el precio estimado antes de confirmar el servicio y entre sus modalidades aparecen Clásico, para transporte de pasajeros y Pick-Up, destinado al traslado de paquetes y otros artículos, y los pagos pueden realizarse en efectivo o mediante un monedero electrónico de acuerdo con la descripción de la empresa. También ha informado que tienen un botón SOS con el cual dan seguimiento al recorrido en tiempo real y la posibilidad de compartir el viaje, que el usuario puede consultar información del conductor y del vehículo, además de comunicarse mediante un chat interno sin proporcionar su número telefónico. Otras funciones es el programa llamado Socio Pronto, con categorías Plata, Oro, Platino y Diamante, y según la compañía estos niveles ofrecen beneficios como prioridad de asignación en horas de mayor demanda, atención preferente y opciones para viajar nuevamente con conductores favoritos. Estas características generales anunciadas por la plataforma, todavía falta conocer cuáles estarán disponibles desde su entrada aquí en el estado de Hidalgo. Para quienes conducen, Pronto promueve un modelo sin comisión por trayecto y la empresa afirma que los operadores conservan el 100% de lo cobrado por sus viajes bajo un esquema de suscripción fija y pueden elegir sus horarios de conexión. Esta aplicación que eh pues aseguran ya ya tiene presencia aquí en Hidalgo, por lo menos tiene un antecedente, ya que comenzó a anunciarse desde 2025 mediante espectaculares y publicaciones digitales, pero bueno, su su operación aquí en Tulancingo ha generado diversos cuestionamientos sobre las autorizaciones necesarias para prestar el servicio. Y, pues bueno, eh la promoción de estas plataformas ocurre mientras el gobierno mantiene su advertencia sobre los servicios de transporte que funcionen sin autorización, y al referirse a Uber sostuvo que la legislación vigente no contempla su operación en las condiciones propuestas, es decir, hay que modificar la ley aquí en el Estado para permitir la operación de este tipo de plataformas digitales que ofrecen el servicio de el conocido ahora como transporte individual. Son 10 de la mañana con 20 minutos, vamos a hacer una pausa nuevamente y regresamos desde la capital hidalguense con más aquí en Enlace Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1X8MJc-AkLJW5nUhJu1f1lBvyEoznKloY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Silla Rota Hidalgo</t>
-  </si>
-  <si>
-    <t>Continuamos en Pachuca, en esta primera emisión de Enlace Hidalgo, y le voy a compartir información de la comparecencia del secretario de Educación Pública en la entidad, Natividad Castrejón Valdez, ante la Sexagésima Sexta Legislatura Local. En este ejercicio de rendición de cuentas, pues consideró el como uno de los principales logros el fortalecimiento en el sistema educativo y escalar una posición para colocarse como el octavo estado del país con mejor desempeño en eficiencia terminal. A este logro se suma el progreso obtenido del diagnóstico de los ejercicios integradores del aprendizaje y la inversión sostenida en infraestructura educativa, ciencia, tecnología y deporte, que amplía las oportunidades de desarrollo para las y los estudiantes. Durante estos cuatro años, el proyecto educativo de la actual administración ha impulsado la formación de estudiantes capaces de transformar sus comunidades, fortalecer su identidad y contribuir a una sociedad más justa y humana. Cada trayectoria escolar suma al bienestar colectivo y nos acerca a un propósito común, sabernos un solo Hidalgo. Así lo expuso el secretario de Educación Pública en la entidad, Natividad Castrejón Valdez, durante esta comparecencia ante los integrantes, las y los integrantes de la Sexagésima Sexta Legislatura Local. La educación en Hidalgo, dijo, ha tenido significativas mejoras en todos los niveles para que las y los estudiantes permanezcan y concluyan sus estudios satisfactoriamente. En este contexto, destacó que la entidad se mantuvo, mantuvo el 39% de la proporción de estudiantes que concluyen la educación superior por cada 100 que ingresan a primero de primaria. Este indicador sitúa a Hidalgo en el octavo lugar nacional, lo que representa un avance de una posición respecto al año anterior. Uno de los avances más sobresalientes se registró en la educación media superior, donde la eficiencia terminal pasó del 63.2% en el ciclo escolar 2021-2022 al 75.6% en el ciclo 2024-2025. La educación superior también se logró un importante incremento en eficiencia terminal, avanzó del 69.6 al 84.5%. Con el propósito de ampliar las oportunidades educativas, el secretario destacó la incorporación de seis servicios de educación media superior que permitieron garantizar la presencia de al menos un plantel público de este nivel en cada uno de los 84 municipios. También subrayó que la entidad continúa el fortalecimiento de la formación científica y tecnológica de sus estudiantes en educación media superior y superior, superior con la red de laboratorios STEM más grande del país. Actualmente, 47 planteles cuentan con laboratorios STEM en beneficio de alrededor de 60,000 estudiantes. También, Natividad Castrejón informó que durante la administración estatal se han destinado 2,700 millones de pesos a infraestructura educativa, de los cuales 780 millones corresponden al periodo reportado con acciones en alrededor de 1,500 planteles y beneficio para 160,000 estudiantes. Eh, comentó que para valorar los avances y las áreas de oportunidad, durante el ciclo escolar 2025-2026 se aplicaron los ejercicios integradores del aprendizaje a 371,456 estudiantes de 3,237 escuelas con el objetivo de identificar las fortalezas en los cuatro campos formativos del plan de estudio. De en otro tema, también eh dijo que se apuesta en Hidalgo por el talento deportivo, con la inversión en alto rendimiento, la infraestructura deportiva de Hidalgo creció con la construcción de la Ciudad Deportiva de Alto Rendimiento, se invirtieron 529 millones de pesos y cuenta con instalaciones para la práctica de 35 disciplinas deportivas. Y en otros temas luego ya a pregunta de medios de comunicación, el secretario de Educación Natividad Castrejón también se refirió a la seguridad en los planteles educativos. Este es parte de lo que dijo el titular de los servicios educativos en la entidad.
-Al contrario, el los daños ocasionados por las lluvias en las semanas eh o de lo que va de del ciclo escolar, eh se tiene que ver en otro programa diferente al tema de anegada. Ya tanto planeación como como la Dirección General del INIFEX están haciendo la revisión de los daños eh ocasionados para poder hacer ya un programa. Eh primero, si se requiere el apoyo de intervención del seguro institucional y si no eh de la Secretaría. Pero eh tenemos la obligación y la instrucción del gobernador de dar respuestas eh prontas a las comunidades educativas que sean afectadas. Eh de los reportes en lo que va del año, llevamos 228 reportes en este ciclo escolar, y del tema de la introducción de armas, conozco eh solo dos, conozco el de Huasca, que fue el más sonado eh mediáticamente, eh fue en la escuela Secundaria General 3 de Gobierno Manzano, eh donde un alumno aportaba un arma eh calibre 22 con algunos cartuchos útiles. Eh, tuvimos otro reporte 
-Bien, esto es parte también de la el intercambio de información con medios de de comunicación por parte del secretario de Educación Pública en la entidad, Natividad Castrejón. Vámonos a la pausa, regresamos con mucho más en Enlace Hidalgo</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1NDxnI2doaqJ1DVdVPTYD0BK2B7_8MVjj/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Bien, y por otra parte ya David Cárdenas nos ha compartido información acerca de estas aportaciones que realiza Petróleos Mexicanos al gobierno del Estado. Le complemento esta información comentándole que fue en las instalaciones de la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, donde el gobernador Julio Menchaca encabezó la entrega de equipamiento por 78 millones 614,370 pesos, resultado de las gestiones realizadas ante Petróleos Mexicanos, que desde 2022 han permitido a Hidalgo recibir donaciones por más de 654 millones de pesos para fortalecer los servicios públicos, la infraestructura carretera, salud y educación. En este contexto, el titular de la oficina del despacho del Poder Ejecutivo, Alejandro Velázquez Mendoza, externó el reconocimiento a la presidenta Claudia Sheinbaum y al personal de Pemex por el respaldo permanente al desarrollo de la entidad. Esto es parte de lo que mencionó Alejandro Velázquez Mendoza.
-Este encuentro va mucho más allá de la recepción administrativa de estas unidades y de la maquinaria que hoy tenemos aquí. Nos recuerda que la riqueza del país cobra sentido pleno únicamente cuando regresa al pueblo, convertida en obras, en infraestructura, en justicia social. Esta sinergia institucional ha permitido que de 2022 a la fecha hayamos gestionado más de 654 millones de pesos en donaciones acumuladas para fortalecer la infraestructura local.
-Y por su parte, el gobernador Julio Menchaca, como ya nos ha comentado David Cárdenas, se refirió al compromiso, a la solidaridad de Petróleos Mexicanos con el pueblo hidalguense. Así lo comentó el mandatario estatal.
-El abandono durante mucho tiempo ha sido atacado, ha sido trabajado por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, atendiendo el compromiso que tenemos con nuestra patria chica y ahí encontramos solidariamente a Pemex.
-Bien, esto es parte de lo que sucedió en esta entrega, esta nueva entrega de equipamiento por parte de Petróleos Mexicanos, con lo cual se suman ya 654 millones de pesos otorgados por la empresa nacional al estado de Hidalgo en diferentes formas para apoyar el desarrollo de la entidad.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FY-oAnuB-v6Ex7fkKXgLrXMmVYQ0M-8X/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>PEMEX</t>
-  </si>
-  <si>
-    <t>Alejandro Velázquez Mendoza, Claudia Sheinbaum</t>
-  </si>
-  <si>
-    <t>Y le comparto este dato que le había comentado al inicio de este espacio informativo. Como parte de las acciones de prevención y promoción de la salud, la Secretaría de Salud mantiene el llamado a la población para fortalecer las medidas de autocuidado durante la actual temporada de frío y con especial atención a los grupos más vulnerables. De acuerdo con las cifras epidemiológicas actuales, la entidad registra 380,323 casos de infecciones respiratorias agudas, lo que representa un decremento de 8.2% respecto al mismo periodo de 2025, cuando se contabilizaron 414,106 casos. Los municipios con mayor número de casos son Pachuca, Tulancingo, Tula, Ixmiquilpan y Actopan. Por lo anterior y con el curso del actual frente frío, la Secretaría de Salud recomienda abrigarse adecuadamente, evitar cambios bruscos de temperatura, mantener una alimentación equilibrada, lavarse las manos frecuentemente y practicar el estornudo de etiqueta. También invita a revisar y complementar esquemas de vacunación contra influenza, COVID-19 y neumococo, conforme a las indicaciones correspondientes. Por supuesto, el hecho de que disminuyan las cifras respecto al año pasado de infecciones respiratorias agudas no implica bajar la guardia, por el contrario, implica que algunas cosas pues están realizándose de manera adecuada, que estamos contribuyendo de manera adecuada para que esto suceda de esta manera y pues hay que seguir en ese camino, en ese tenor. Le comparto lo que dice al respecto Rubí Vargas Vargas, ella es la coordinadora de comunidades y municipios de la Subsecretaría de Salud en la entidad.
-...temporada de frío o temporada invernal se incrementan de manera importante las enfermedades respiratorias. Por esta razón, la Secretaría de Salud fortalece las acciones de promoción y difusión sobre recomendaciones para enfrentar efectos negativos a la salud de forma prioritaria en grupos vulnerables como menores de 5 años, adultos mayores, personas en situación de calle o pobreza extrema. Entre las medidas preventivas que podemos compartir con la población en general son pues lavarse las manos de forma frecuente antes de consumir o preparar alimentos, después de utilizar el baño y en especial después de tener contacto con personas enfermas. Cubrir nariz y boca al toser o estornudar con el ángulo del codo, lo que llamamos estornudo de etiqueta o bien hacerlo con un pañuelo. Esto disminuirá el riesgo de contagio de las personas a nuestro alrededor. Abrigarse con ropa adecuada como gorro, guantes, bufanda, evitar en lo posible los cambios bruscos de temperatura y corrientes de aire frío, consumir suficientes líquidos, consumir frutas y verduras ricas en vitaminas A, C y D, importante vacunarse contra influenza y COVID, además de neumococo de acuerdo a la edad correspondiente.
-Bien, es lo que dice la responsable de la coordinadora de comunidades y municipios de la Subsecretaría de Salud, Rubí Vargas, y bueno, hacer énfasis en esto de que ante síntomas como fiebre, tos, escurrimiento nasal o cansancio es importante evitar la automedicación y acudir a la valoración médica, sobre todo si se presenta dificultad para respirar o dolor torácico, bueno, estos ya son síntomas más delicados y evidentemente es muy importante acudir de inmediato ante el especialista en salud.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/16VXHs2GgPi4tRBpFohdec1YJhdeLMYgE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Vanesa Escalante</t>
-  </si>
-  <si>
-    <t>En la conferencia matutina del gabinete de energía, se destacó el papel estratégico de Petróleos Mexicanos (Pemex) en la economía nacional y su impacto en el estado de Hidalgo. El gobernador Julio Menchaca Salazar informó sobre una gestión histórica con Pemex superior a los 654 millones de pesos, la cual incluye un reciente paquete de apoyo con 5,000 toneladas de asfalto, equipo de salud y maquinaria. Por su parte, el director de Pemex, Juan Carlos Carpio, señaló que la producción de barriles diarios se mantiene estable y la refinación ha incrementado al 81% en comparación con 2018, impulsada por la operación constante de las refinerías, la refinería Olmeca y la modernización de la planta ubicada en Tula. Asimismo, se resaltó una inversión cercana a los 6,600 millones de pesos destinada a proyectos comunitarios y caminos en la región entre 2025 y 2026, informó David Cárdenas durante su colaboración matutina.</t>
-  </si>
-  <si>
-    <t>..Y déjame saludar ya, con mucho gusto ya lo tengo en la línea telefónica a nuestro colaborador y amigo David Cárdenas. David, muy buenos días, ¿cómo estás?
-Buenos días, Jesús. Buen día, este gran auditorio. Dando seguimiento a la conferencia de la prensa, de la Presidenta de México, en donde pues se han dado cita el día de hoy el gabinete de energía. Y bueno, los medios de comunicación dando seguimiento también, Jesús, a todo lo que tiene que ver... En ocasiones se ve distante lo que está aconteciendo en Pemex, hasta que nos brindan también la información y desde luego la vamos pulsando y vamos, este, conociendo la importancia de esta empresa, que es una empresa rectora a nivel nacional y que es una empresa que más recursos genera y desde luego también al junto con las remesas que llegan de trabajadoras, trabajadores de México, nuestro país pues mantiene una solidez, una economía pues que permite también no solamente en la competencia al interior mantener los niveles de nuestra moneda. El día de ayer el Gobierno del Estado, como ya conocemos, informó a través del gobernador Julio Menchaca Salazar que Petróleos Mexicanos proporcionó 5,000 toneladas de asfalto, 500 luminarias, dos camiones tanque, un camión de desazolve, dos retroexcavadoras y dos ambulancias. Esto tiene un valor, este, evidentemente económico elevado, un valor superior a los 78 millones de pesos, en donde el gobernador Julio Menchaca logró la gestión histórica ante Petróleos Mexicanos por más de 654 millones de pesos. En esto ha tenido que ver también Alejandro Velázquez Mendoza, titular del despacho del gobierno del Estado de Hidalgo. Con la pregunta también, obviamente, ¿de dónde sale este recurso? ¿Por qué Pemex apoya? ¿Cuál es el papel que está desarrollando en la economía y que es muy importante? Esta mañana, el director de Petróleos Mexicanos, Juan Carlos Carpio, informó... Pemex ha elevado su refinación al 81% y consolida la producción petrolera. Tiene una producción elevada que no se había tenido. Uno de los logros centrales es el incremento en la refinación, evidentemente esto permite entonces tener también mayor producción de barriles diarios y, por lo tanto, una operación que permite que el costo, el precio de los combustibles no se eleven. La integración de la refinería Olmeca ha beneficiado y también las mejoras en las instalaciones estratégicas como la refinería de Tula. Vamos a escuchar, Jesús, lo que dijo Juan Carlos Carpio hace unos minutos en esta conferencia matutina en donde la Secretaría de Energía está presente, así como el director general de Petróleos Mexicanos.
-...pues las cifras concretas son las siguientes: hoy mantenemos una producción estable cercana a la meta de 1.8 millones de barriles diarios, alcanzando 1.76 millones de barriles por día. La producción de gas natural aumentó 7.5% respecto a 2024 y supera los 4,900... El segundo resultado es que estamos refinando más petróleo en México. Actualmente refinamos 81% más petróleo que en 2018, al pasar de alrededor de 612,000 barriles por día a más de 1,100,000 barriles diarios. Esto ha sido posible gracias a la operación constante de las refinerías, la incorporación de la refinería Olmeca y las mejoras operativas en instalaciones estratégicas de la refinería ubicada en Tula. Estamos aprovechando mejor nuestros recursos para generar más combustibles de alto valor que utilizan diariamente millones de mexicanos.
-El gobernador Julio Menchaca Salazar el día de ayer señalaba el abandono, durante mucho tiempo ha sido atacado, ha sido trabajado por miles de hidalguenses, mujeres y hombres, desde su responsabilidad, teniendo el compromiso con nuestra patria chica, y ahí encontramos, señor gobernador, solidariamente a Petróleos Mexicanos. Esta alianza, desde luego, permite no solamente que la refinería se encuentre en el estado de Hidalgo, sino que genera también beneficios. Parte de lo que se ha destacado esta mañana, Pemex también amplió la relación cercana con las comunidades donde opera. Entre 2025 y septiembre de 2026 se destinaron casi 6,600 millones... de apoyos a comunidades y regiones estratégicas. Sus recursos se traducen en caminos, proyectos productivos... Hola, hola, David. ¿David, nos escuchas? Por ahí estamos teniendo... El gobierno federal, el gobierno... que el gobierno federal, el gobierno del estado lleva a cabo esa alianza también en favor de la economía de la propia entidad. Es el reporte...</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zHmbl2aTUV1NCkzOaAN6se2G_dynw7I0/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Pemex, Gobierno federal</t>
-  </si>
-  <si>
-    <t>Alejandro Velázquez Mendoza, Juan Carlos Carpio</t>
+    <t>SDPEE-OCSAD/FN.38/2026</t>
+  </si>
+  <si>
+    <t>Para el Estado de Hidalgo se tiene considerada una meta de construcción de 66 mil 500 Viviendas del Bienestar, ubicadas en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo. Lo anterior fue señalado durante la reunión encabezada por la Presidenta de México, Claudia Sheinbaum Pardo, en Palacio Nacional, donde se evaluaron los avances de dicho programa, en donde participó el Gobernador de Hidalgo, Julio Menchaca Salazar, junto con alcaldesas y alcaldes donde actualmente se construyen las viviendas. En la reunión se estableció la posibilidad de incorporar más municipios de Hidalgo al Programa Nacional de Vivienda para el Bienestar, para lo cual se está realizando la evaluación de terrenos, condiciones legales, entre otros temas. De acuerdo al Gobierno Federal, cada vivienda tiene un costo promedio de construcción de 600 mil pesos y están a cargo del Instituto del Fondo Nacional de la Vivienda para los Trabajadores (Infonavit) y la Comisión Nacional de Vivienda (Conavi). Del total de hogares, 11 mil 500 serán edificados por el Infonavit y 20 mil por la Conavi, de acuerdo a lo establecido previamente. Como parte de esta estrategia nacional, que contempla la construcción de 1.8 millones de viviendas, incluyendo al Estado de Hidalgo, con el objetivo de ampliar el acceso de las familias a una vivienda digna. Actualmente están en construcción 5 mil 990 viviendas nuevas en los municipios del Estado de Hidalgo ya señalados. Cabe señalar que los municipios donde se asientan las viviendas deben facilitar el acceso a servicios como agua potable, drenaje y electricidad, además de atender los trámites catastrales, avalúos y escrituración de las casas y departamentos. El Gobernador Menchaca Salazar acompañó a la mandataria nacional en un encuentro para revisar los avances del proceso de modernización del IMSS-Bienestar, junto a 23 gobernadoras y gobernadores que están integrados al sistema de atención a la salud.</t>
+  </si>
+  <si>
+    <t>CDMX</t>
+  </si>
+  <si>
+    <t>Ayer hubo reunión en Palacio Nacional con el gobernador Julio Mechaca Salazar, con alcaldesas y alcaldes de municipios donde están construyendo viviendas del bienestar, Izza. Es correcto, Daniel. Para el Estado de Hidalgo se tiene considerada una meta de construcción de 66.500 viviendas del bienestar. Estas ubicadas en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo. Todo esto fue señalado durante la reunión encabezada por la Presidenta de México, Claudia Sheinbaum Pardo, en Palacio Nacional, donde se evaluaron los avances de dicho programa, en donde participó el gobernador de Hidalgo, Julio Menchaca Salazar, junto con alcaldesas y también alcaldes, donde actualmente se construyen viviendas. Y pues en la reunión se estableció la posibilidad de incorporar más municipios de Hidalgo al Programa Nacional de Vivienda y Bienestar, para lo cual se está realizando la evaluación de terrenos, condiciones legales, entre otros temas. Y de acuerdo con el gobierno federal, cada vivienda tiene un costo promedio de construcción de 600 mil pesos y están a cargo del Instituto del Fondo Nacional de Vivienda para los Trabajadores y también la Comisión Nacional de Vivienda. Pues el total de hogares, 11.500 serían edificados por el Infonavit y 20.000 por la Conavi, de acuerdo con lo establecido previamente. Y como parte de la estrategia nacional que contempla la construcción de 1.8 millones de viviendas, incluyendo al Estado de Hidalgo, con el objetivo de ampliar el acceso a las familias a una vivienda digna. Actualmente están en construcción 5.990 viviendas nuevas en los municipios del estado de Hidalgo Que ya mencionamos y cabe señalar que los municipios donde se asientan las viviendas Deben facilitar el acceso a servicios como agua potable, drenaje, electricidad Además también de atender los trámites catastrales, avalúos y también escrituración de estas casas y departamentos</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vmOTaE-tpY9v_DIvopciX2BUjPhXyjLA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Radioescucha: es increíble que sabiendo el nefasto servicio que tiene el transporte público, con autos ya de 20 años, con vidrios polarizados, sucios y a veces sin cinturón de seguridad, muchos taxistas sin tarjetón o licencia, no permitan la entrada de plataformas.</t>
+  </si>
+  <si>
+    <t>Dicen por acá, es increíble que sabiendo el nefasto servicio que tiene el transporte público, con autos ya de 20 años, con vidrios polarizados, sucios y a veces sin cinturón de seguridad, muchos taxistas sin tarjetón o licencia, no permitan la entrada de plataformas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Z_OMH-4ikeP_uQxCelO5e1O3ptTniLBU/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte en Hidalgo (Semoth) considera la implementación de un sistema integral de trámites y gestión de la información para transporte convencional. Lo anterior fue informado por Lyzbeth Robles Gutiérrez, titular de la dependencia estatal durante su comparecencia ante el Congreso de Hidalgo, realizada el miércoles 21 de octubre. Señaló que también está considerada la modernización tecnológica del servicio y la adquisición de equipo especializado para la inspección vehicular. También se considera un sistema para aplicar pruebas psicométricas a personas conductoras, un estudio de impacto vial en el bulevar Luis Donaldo Colosio, dentro de la Zona Metropolitana de Pachuca, junto con el equipamiento de una unidad móvil para realizar pruebas toxicológicas. La funcionaria señaló que también está considerada la elaboración de los planes de movilidad urbana sustentable de Ixmiquilpan y Huejutla, así como en el Plan Estratégico de Seguridad Vial para el Estado de Hidalgo. Robles Gutiérrez informó que en transporte público convencional, la Semoth desde el año 2022, ha realizado mil 830 operativos de vigilancia y supervisión. Asimismo, explicó que el gobierno estatal destinó 9 millones 500 mil pesos al censo de transporte en Hidalgo. El censo permitió identificar mil 272 rutas de transporte colectivo y 633 sitios de transporte individual. En cuanto al Sistema de Transporte Metropolitano, conocido como Tuzobús, se destacó que se registró un incremento de 24 por ciento de viajes, tras la renovación de unidades. Con la modernización de la flota vehicular, el número de personas usuarias pasó de 75 mil a casi 93 mil, tanto en la ruta troncal como en las alimentadoras. De acuerdo con la funcionaria, el sistema registra una eficiencia operativa de 99 por ciento y una disminución de 56 por ciento en las quejas. La Semoth desarrolla proyectos de renovación de la red semafórica, elaboración de dictámenes estructurales de los puentes a cargo del sistema, mantenimiento y rehabilitación integral de las estaciones del Sistema de Transporte Metropolitano.</t>
+  </si>
+  <si>
+    <t>En otros temas que tocó Lizbeth Robles, la titular de la Secretaría de Movilidad y Transporte del Estado de Hidalgo, en temas generales, señaló que en breve se está considerando la implementación de un sistema integral de trámites y gestión de la información para el transporte convencional. Esto durante la comparecencia que ofreció el día de ayer, señaló que también está considerada la modernización tecnológica del servicio y la adquisición de equipo especializado para inspección vehicular. También se considera un sistema para aplicar pruebas psicométricas a personas conductoras, un estudio de impacto vial en el bulevar Luis Donaldo Colosio, esto último de dentro de la zona metropolitana de Pachuca, junto con el equipamiento de una unidad móvil para realizar pruebas tecnológicas. La funcionaria señaló que también está considerada la elaboración de los de los planes de movilidad urbana sustentable en Ixmiquilpan y Huejutla, así como en el plan estratégico de seguridad vial para el Estado de Hidalgo. Robles Gutiérrez informó que en transporte público convencional, la Secretaría de Movilidad y Transporte de Hidalgo desde el año 2022 ha realizado 1,830 operativos de vigilancia y supervisión, ¿que para qué han servido? Uno se pregunta. También explicó que el Gobierno estatal destinó 9,500,000 pesos al censo de transporte en Hidalgo, el censo permitió identificar 1,272 rutas de transporte colectivo dentro de la entidad y 633 sitios de transporte individual. ¿Y para qué ha servido esa información o para qué va a servir, no? En cuanto al sistema de transporte metropolitano conocido como Tuzobús, se destacó que se registró un incremento del 24% de viajes tras la renovación de las unidades. Con la modernización de la flota vehicular, el número de personas usuarias pasó de 75,000 a casi 93,000, tanto en la ruta troncal como en las alimentadoras, y de acuerdo con la funcionaria, el sistema registra una eficiencia operativa del 99% y una disminución del 56% en las quejas. La Secretaría de Movilidad y Transporte desarrolla proyectos de renovación de la red semafórica ahí en el Tuzobús, elaboración de dictámenes estructurales de los puentes a cargo del sistema, mantenimiento y rehabilitación integral de las estaciones de este sistema de transporte metropolitano.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1c_ygxMXSfOWRz7CJMFBVG4Rvd2swpyok/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha: ojalá que entren las plataformas porque el servicio que se ofrece actualmente en taxis es muy deficiente, hay operadores que son muy despotados.</t>
+  </si>
+  <si>
+    <t>Por acá nos están comentando en este momento, ojalá que entren las plataformas porque el servicio que se ofrece actualmente en taxis es muy deficiente, hay operadores que son muy despotados.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1r21yQrrOgVzDKRK4tu8h0qaJRpS0ezuS/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Daniel Martínez hablando sobre la llega de plataformas de transporte a Hidalgo comenta: me quedo también con las palabras de Andrés Velázquez Vázquez, presidente de la Junta de Gobierno del Congreso del Estado de Hidalgo. Al final de cuentas, la tecnología ya llegó. Más adelante señala que no se debe satanizar un servicio, sino adecuarlo a las necesidades.</t>
+  </si>
+  <si>
+    <t>Ahora, me quedo también con las palabras de Andrés Velázquez Vázquez, presidente de la Junta de Gobierno del Congreso del Estado de Hidalgo. Al final de cuentas, la tecnología ya llegó.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JblBusZuw-4fXLui-Adz5HOFoS5z6Fb7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Nuevamente, por acá nos están mandando mensajes de que consideran que el tema de no permitir las plataformas, además de que no les permite tener otras opciones a quien busca otros servicios que no sean los taxis ordinarios, le está cerrando las puertas a quien quiere llevarse una lanita, un ingreso extra. Ese es el pensamiento o el punto de vista que nos están compartiendo por acá por WhatsApp.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IyvhCjIq94L_r_-Q-lgrzBsh7T4vW5eP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Didi en Tula comenzó a promocionarse mediante una convocatoria dirigida a personas con automóvil propio que estén interesadas en registrarse como socios conductores. La publicidad difundida anuncia la llegada de la plataforma Tula, ahí ofrece como promoción una ganancia garantizada superior superior a 10,000 pesos durante la primera semana de lanzamiento, sujeta a las condiciones establecidas por la empresa. La convocatoria aparece apenas unos días después de que Uber habilitara la posibilidad de solicitar viajes en Pachuca, y esta convocatoria ha sido difundida para Tula de Allende y estaría dirigida a propietarios de vehículos. Entre los principales atractivos promocionales se encuentra la comisión del 9%, horarios flexibles, demanda de viajes y más de 20 funciones de seguridad. La publicidad también ofrece una ganancia garantizada de 10,000 pesos durante la primera semana de lanzamiento y al tratarse de una promoción comercial, el acceso a este beneficio puede estar sujeto a términos y condiciones. Entre los requisitos anunciados para registrarse se encuentran el INE, la licencia de conducir, tarjeta de circulación, una fotografía tomada mediante la aplicación. La empresa también habilitó un número de WhatsApp para poder brindar asesoría a las personas que estén interesadas en registrarse. El día lunes Uber habilitó dentro de su aplicación la posibilidad de consultar y solicitar viajes en Pachuca y como ya lo mencionabas Daniel, el Gobierno del Estado de Hidalgo ha fijado su posicionamiento y ha sostenido que el modelo bajo el cual estas plataformas pretenden prestar el servicio no estaría contemplado actualmente como una modalidad autorizada por la legislación estatal.</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>En Tula, pues resulta que incluso están buscando operadores para otra de estas empresas, es decir, siguen adelante. Sí, de hecho en medio de toda esta controversia que ha habido con la llegada de plataformas digitales de transporte, ahora Didi en Tula comenzó a promocionarse mediante una convocatoria dirigida a personas con automóvil propio que estén interesadas en registrarse como socios conductores. La publicidad difundida anuncia la llegada de la plataforma Tula y ofrece como promoción una ganancia garantizada superior a 10 mil pesos durante la primera semana de lanzamiento, sujeta a las condiciones establecidas por la empresa. La convocatoria aparece apenas unos días después de que Uber habilitará la posibilidad de solicitar viajes en Pachuca Y esta convocatoria ha sido difundida para Tula de Allende y estaría dirigida a propietarios de vehículos Entre los principales atractivos promocionales se encuentra la comisión de 9%, horarios flexibles, demanda de viajes y más de 20 funciones de seguridad La publicidad también ofrece una ganancia garantizada de 10 mil pesos durante la primera semana de lanzamiento y al tratarse de una promoción comercial, el acceso a este beneficio puede estar sujeto a términos y condiciones. Entre los requisitos anunciados para registrarse se encuentran el INE, la licencia de conducir, tarjeta de circulación, una fotografía tomada mediante la aplicación. La empresa también habilitó un número de WhatsApp para poder brindar asesoría a las personas que estén interesadas en registrarse. El día lunes, Uber habilitó dentro de su aplicación la posibilidad de consultar y solicitar viajes en Pachuca y como ya lo mencionaba Daniel, el gobierno del estado de Hidalgo ha fijado su posicionamiento y ha sostenido que el modelo bajo el cual estas plataformas pretenden prestar el servicio no estaría contemplado actualmente como una modalidad autorizada por la legislación estatal.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sVvhxcGaD--jIQj7A2l6toXC-JIuXId1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Entre septiembre del año pasado y el mismo mes de este 2026, la Secretaría de Movilidad y Transporte en Hidalgo (Semoth) ha detectado 129 vehículos que realizaban servicio de transporte para pasajeros por medio de plataformas digitales. El dato fue ofrecido por la titular de la dependencia estatal, Lyzbeth Robles Gutiérrez, durante su comparecencia ante el Congreso de Hidalgo, realizada el miércoles 21 de octubre. La funcionaria agregó que se aplicaron 50 sanciones por prestar el servicio sin contar con la autorización, lo que significó una recaudación por 4 millones 399 mil 125 pesos. En el Estado de Hidalgo se han detectado varias empresas que prestan el servicio, pese a que las actuales normativas en materia de transporte para pasajeros no las tiene contempladas, y por tanto, no están autorizadas para operar. La detección de las 129 unidades particulares que fueron remitidas al corralón, han sido detectadas en varios municipios de la entidad. En cuanto a las sanciones, en Pachuca se han aplicado 26; seguido de Mineral de la Reforma, 11; Tizayuca, 4; Ixmiquilpan, 3; Villa de Tezontepec, 2; así como uno en Tepeapulco, otro en Zempoala y otro en Tolcayuca. No fueron precisados más municipios. La titular de Semoth recordó que con anterioridad Uber promovió diversos juicios de amparo para obtener autorización y así operar en la entidad, pero no consiguió resoluciones favorables; asimismo, aseguró que no hay juicios de garantía vigentes. Respecto al anuncio del gobernador Julio Menchaca Salazar sobre la presentación de denuncias por los viajes que oferta Uber, la secretaria señaló que se trata de una estrategia del Poder Ejecutivo en la que también participa la dependencia a su cargo. Puntualizó que las acciones podrían ocurrir en dos sentidos, tanto en el ámbito administrativo como en la vía penal..</t>
+  </si>
+  <si>
+    <t>El día de ayer fue la comparecencia de Lisbeth Robles al frente de la Secretaría de Movilidad y Transporte del Estado de Hidalgo, donde uno de los temas, y no lo soltamos, Izza, no lo vamos a soltar tampoco, ha sido el asunto de los servicios de transporte por aplicación, en el que se insiste, por lo menos por el momento, a Hidalgo no entran y me sorprendió la cantidad de vehículos que han sido asegurados de septiembre del año pasado a la fecha, porque señalan, no es una ni dos, son varias compañías que están ofreciendo servicio por aplicación en Hidalgo. **Izza Hernández:** Es correcto, entre septiembre del año pasado y el mismo mes de este 2026, resulta que la Secretaría de Movilidad y Transporte de Hidalgo ha detectado 129 vehículos que realizaban servicio de transporte para pasajeros por medio de plataformas digitales. Ese dato fue ofrecido por la titular de la dependencia estatal, Lisbeth Robles Gutiérrez, durante la comparecencia ante el Congreso de Hidalgo, que se realizó este miércoles 21 de octubre. De hecho, la funcionaria agregó que se aplicaron 50 sanciones para poder prestar el servicio sin contar con la autorización, lo que significó, de hecho, una reducción de 4,399,125 pesos. En el estado de Hidalgo se han detectado varias empresas que prestan el servicio, pese a que las actuales normativas en materia de transporte para pasajeros no las tienen contempladas y, por tanto, pues no están autorizadas para operar. Pero sí, la detección de las 129 unidades particulares que fueron remitidas al corralón han sido detectadas en varios municipios de la entidad. De hecho, en cuanto a las sanciones en Pachuca se han aplicado 26, seguido de Mineral de la Reforma con 11, Tizayuca con 4, e Ixmiquilpan con 3, Villa de Tezontepec con 2, así como también uno en Tepeapulco, otro en Zempoala y otro en Tolcayuca. De hecho, no precisaron como tal los municipios, pero la titular de la SEMOT, perdón, recordó que con anterioridad Uber pues promovió diversos juicios de amparo para poder obtener autorización y así operar en la entidad, pero no consiguió resoluciones favorables. Asimismo, aseguró que no hay juicios de garantía vigentes. Pero bien, respecto al anuncio del gobernador Julio Menchaca Salazar sobre la prestación de la presentación de denuncias por los viajes de oferta de Uber, pues la secretaria señaló que se trata de una estrategia del Poder Ejecutivo en la que también participa la dependencia a su cargo, pero sí puntualizó que las acciones podrían pues ocurrir en dos sentidos, tanto en el ámbito administrativo como también en la vía penal. Entonces, pues de esta manera es como pues detectó SEMOT 129 vehículos ofreciendo servicios por plataforma digital de manera</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VYjbeXHDIU-MyEfK9nYolgFPRh8gA0Bw/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Saderh/Bol.87/2026</t>
+  </si>
+  <si>
+    <t>Impulsa Saderh transformación integral de la región Otomí-Tepehua y Valle de Tulancingo</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>Valle de Tulancingo</t>
+  </si>
+  <si>
+    <t>Entregas que se hicieron en la Sierra Otomí- Tepehua para productores agrícolas. Esto por parte, obviamente, de la Secretaría de Desarrollo Agropecuario del Estado de Hidalgo. Es correcto, Daniel. Resulta que en el marco de las estrategias para dinamizar las actividades productivas y consolidar la soberanía alimentaria en la región, el gobierno de Hidalgo encabezado por Julio Menchaca a través de la Secretaría de Agricultura y Desarrollo Rural del Estado de Hidalgo (Saderh) llevó a cabo una entrega de apoyos por un monto total de 7 millones 900 mil 571.71 pesos en beneficio directo de 585 productoras y productores rurales. Agua Blanca de Iturbide, Hidalgo.- El evento, encabezado por el titular de la Saderh, Napoleón González Pérez fue relizado en el municipio de Agua Blanca en donde se extendieron las entregas a los municipios de Santiago Tulantepec, Tulancingo, Acaxochitlán, Metepec, Cuautepec, Acatlán, Singuilucan, Tepeapulco, Apan, Mineral del Chico y Huasca de Ocampo. Durante la jornada se realizó la entrega de semilla de maíz, cebada y jitomate; así como vientres porcinos y ovinos, además de rollos de alambre, molinos picadora, hijuelos de maguey, plantas de manzana gala, limón persa, café Sarchimor, nogal cáscara de papel, equipamiento acuícola, crías de peces (tilapia y carpa) y certificados de sanidad acuícola. Durante el evento el titular de Agricultura en el estado resaltó que cada beneficiario recibirá directamente el programa que solicitó, asegurando que los recursos lleguen sin recortes ni intermediación. El funcionario insistió en que para acceder a estos esquemas no se requiere pertenecer a ninguna agrupación ni contar con la gestión de ningún líder, garantizando con ello un proceso ágil, transparente y accesible donde es fundamental acreditar la condición de trabajador o trabajadora del campo. Con esta medida, el gobierno del estado reafirma su compromiso de dignificar la labor campesina, impulsando a quienes trabajan la tierra día con día y asegurando que cada apoyo se traduzca en bienestar directo y desarrollo productivo para las comunidades hidalguenses. Estas acciones reafirman el compromiso de garantizar que el campo hidalguense cuente con mejores condiciones para producir, crecer y construir un futuro con mayores oportunidades, asegurando que cada apoyo y proyecto se traduzca en bienestar y prosperidad para las familias rurales de la entidad.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DkelJlYSpKieIF32-AkoKKk7L9YnvLS-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>Debido a que desde la temporada de verano de este año se registraron casos de Covid-19 en la región Tulancingo, se espera repunte de casos por influenza estacional durante la temporada invernal. La información fue presentada durante la reunión mensual del Comité Jurisdiccional de Vigilancia Epidemiológica, por lo cual se hizo llamado para aplicarse la vacuna para ambos padecimientos, las cuales ya están disponibles. Durante la sesión de trabajo realizada este miércoles 21 de octubre, se señaló que también se espera durante la temporada invernal, incremento de casos de otras enfermedades broncorespiratorias, como influenza H1N1 y tipo B. Se tiene especial preocupación en la incidencia de virus sincitial respiratorio, una de las principales causas de muerte en niñas y niños de cinco años de edad, por las complicaciones que pueden presentar en su estado de salud. Las autoridades sanitarias han detectado que el grupo entre los 24 a 39 años de edad es donde se presenta el mayor porcentaje de personas que enferman de padecimientos broncorespiratorios. Una de las principales causas de dicha incidencia es debido a que dicho grupo de edad rechaza vacunarse, una de las principales estrategias para evitar este tipo de enfermedades o aminorar sus efectos. En cuanto a fallecimientos por este tipo de padecimientos, en la región correspondiente a la Jurisdicción Sanitaria Regional II, los municipios con mayor registro son Acaxochitlán, Metepec, Santiago Tulantepec, Tulancingo y Tenango de Doria. En el caso de Covid-19, los fallecimientos se han registrado sobre todo en personas con antecedentes de diabetes, hipertensión, obesidad y asma. Mientras que en los fallecimientos por influenza, se registran sobre todo en personas con antecedentes también de diabetes, así como de Enfermedad Pulmonar Obstructiva Crónica y enfermedades renales agudas. Se insistió en reforzar los esquemas de información preventiva a los padecimientos broncorespiratorios, así como la estrategia de vacunación, señalando que existen dosis suficientes para atender a la población. En el caso de la vacunación, adultos mayores, mujeres embarazadas, así como niñas y niños, junto con personas con enfermedades crónico degenerativas, son quienes serán atendidas prioritariamente para ser vacunadas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aw0dGI007LNIdLa4g_G7j3i1wDBVM2wr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Andrés Torres en respuesta a una radioescucha que pregunta por qué no se pasan imágenes en las noticias, argumentando que esto haría el noticiero más completo. Andrés Torres se disculpa y explica que el formato del noticiero ha cambiado a lo largo de los años, ya que llevan 13 años funcionando. Mencionan que hay carencias en Radio y Televisión de Hidalgo que hacen difícil realizar un noticiero de televisión. Actualmente, están haciendo un programa de radio con apoyo visual y desde Pachuca, tienen un equipo muy pequeño, conformado por un camarógrafo, dos conductores y un operador de radio. Explica que la falta de recursos y personal limita sus capacidades. Para crear un noticiero formal, se requiere un equipo grande y completo, algo que ellos no pueden ofrecer debido a su situación. Además, la financiación del proyecto es personal, ya que no reciben apoyo económico para tener imágenes y presentar un formato de noticiero de televisión. El informativo se nutre principalmente de un estilo de radio. También menciona que su programa comenzó con un enfoque de opiniones y no como un noticiero, aunque ahora brinda noticias. Está orgulloso de lo que han logrado con el esfuerzo de sus compañeros y de las personas que apoyan el proyecto. Sin embargo, enfatiza la difícil situación en la que trabajan, con recursos muy limitados. Agradecen a colaboradores que, de forma altruista, contribuyen con información sin recibir pago alguno. Todos los gastos del programa, como transporte y materiales, son cubiertos por ellos mismos. Lamenta los inconvenientes causados por la falta de recursos y reafirma su compromiso de ofrecer la mejor información política y social posible, a pesar de las limitaciones. Se despide disculpándose nuevamente y reafirmando su dedicación al informativo.</t>
+  </si>
+  <si>
+    <t>Nos escribe la terminación 1984, muy buenos días a todos los que participan en Vocales Radio Muchas gracias, buen día Una pregunta, ¿por qué no pasan imágenes de las noticias? Estaría más completo su noticiero, muchas gracias Si, pues es que mira, tenemos un pequeño problema y me disculpo con todo el auditorio El formato de este noticiero se vino modificando a través de muchos, muchos años Prácticamente tenemos ya 13 años con esta informativo, que nació siendo eso, un informativo, un programa de opinión con información debido a las carencias que existen en radio y televisión desde hace décadas pues es prácticamente imposible que podamos hacer un noticiero con los formatos de televisión nosotros estamos haciendo un programa de radio con el apoyo visual, con el apoyo de algunas cámaras y te puedo decir, somos muy poquitos para hacer un programa de televisión como un noticiero formal se necesita un equipo muy grande Un equipo muy importante Nosotros somos apenas 3 personas Un camarógrafo, 2 conductores Y por supuesto nuestro operador de radio Que al mismo tiempo Tiene al aire 3 estaciones Está checando nuestra señal Para Huejutla FM Para Radio Tlanchinol Y estamos apoyando también La señal de Ixmiquilpan Desde aquí, desde Pachuca Entonces estamos de verdad Saturados de trabajo No tenemos ni equipo, capacidad técnica y tampoco capacidad económica Porque además déjame decirte, tendría que ser inversión personal propia Como lo es todo este programa Para tener imágenes y ofrecerle a nuestro auditorio Este formato de noticiero de televisión Somos un noticiero de radio muy muy muy peque Porque bueno pues este formato A mí no me gusta la palabra orgánico pero se ha dado as se ha derivado en un noticiero por cuestiones, pues obviamente del perfil informativo que tengo como profesional, pero el objetivo, si tú revisas, y algún día si gustas te puedo mostrar el proyecto de las vocales radio original, era un programa de opinión, era un programa donde se iban a tratar tres temas desde el punto de vista de la opinión, es un género periodístico y algo noticioso. Hoy estamos haciendo un noticiero, del cual me siento muy orgulloso, sobre todo el trabajo de mis compañeros, del apoyo de mucha gente que se suma a este proyecto, pero es la condición, Estamos trabajando en condiciones De verdad Al límite De los recursos Que tenemos a la mano Todos nuestros colaboradores Alberto González, Milton Cortés Toda la gente que usted Escucha, la que contactamos Por lo regular vía telefónica Son compañeros que de manera altruista Así lo digo, de buena voluntad Como buenos samaritanos Nos apoyan con información no hay ningún pago, no hay ninguna retribución, si nosotros tenemos que trasladarnos a alguna región del estado, si tenemos que hacer alguna cobertura, pues corre por nuestra cuenta todos los gastos, no tenemos grabadoras, no tenemos plumas, no tenemos pilas, no nos dan ningún tipo de apoyo para realizar los trabajos, no es una cámara, un vehículo, gasolina, nada de eso existe aquí, todo lo hacemos a nuestra cuenta, Entonces ofrezco una disculpa porque hacemos lo humanamente posible Por llevarles a usted lo último y lo más importante en la información política</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WYPyqZ1aC4XRTSc10jABQkERXdjsCF9w/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Menchaca y Sheinbaum suman esfuerzos para impulsar el programa Vivienda para el Bienestar en Hidalgo</t>
+  </si>
+  <si>
+    <t>También el gobernador participó en una reunión que fue encabezada por la presidenta Claudia Simo Pardo en el Palacio Nacional. El gobernador se reunió a esta reunión donde se evaluaron los avances del programa de vivienda para el bienestar y se acordó fortalecer la coordinación entre los tres órdenes de gobierno para agilizar su implementación. Como parte de esta estrategia Nacional que contempla la construcción de 1.8 millones de viviendas para el Estado de Hidalgo, se proyectan 66.500 en estos municipios que estarán ubicadas, Aldo, en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo de Bravo, todo esto con el objetivo de ampliar el acceso de las familias hidalguenses a una vivienda digna. Además, el gobernador Julio Menchaca Salazar acompañó a la presidenta de nuestra nación en el encuentro para revisar los avances del proceso de modernización del IS-Bienestar, esto junto a otros 23 gobernadores y gobernadoras de nuestro país. Así que ayer el gobernador también estuvo presente en esta reunión nacional para evaluar estos dos temas fundamentales. El tema de la vivienda del bienestar y el tema del Instituto Mexicano del Seguro Social, hoy IMSS-Bienestar. Y bueno, son dos asuntos que son muy importantes no solo para el Estado de Hidalgo, sino para nuestra nación. Así es, dicho técnicamente el gobernador. Regresamos los avances junto con la presidenta Claudia Ocema de la modernización del IMSS-Bienestar. En Hidalgo trabajamos para que más familias tengan acceso de servicios médicos de calidad.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HGeRJbajAY0gJBbiyww2dQMFadHXEsgs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/Bol.1331/2026</t>
+  </si>
+  <si>
+    <t>El gobernador de nuestro estado, Julio Menchaca Salazar, asistió a este evento denominado Congreso Nacional de la Moda y el Vestido 2026. Con la convicción de respaldar a todos los sectores económicos, el gobernador Julio Menchaca Salazar inauguró el Congreso de Moda y Vestido 2026, que por primera vez se lleva a cabo en nuestro estado y que es un bastión de la industria textil. Hidalgo tiene una historia ligada desde la fabricación de hilo hasta la confección de prendas. Asumo el compromiso de acompañar esta importante actividad que desarrollan y se genere en un bienestar compartido. El mandatario estatal reconoció el trabajo del sector empresarial que en sinergia con la administración estatal elevó los índices del estado en la actividad económica. En este evento también estuvo presente José Pablo Maauad, presidente de la Cámara Nacional de la Industria del Vestido, y otros representantes de la Cámara Nacional de la Industria Textil, como Rafael Torres y también Juan Porras Manrilla, tesorero de la Confederación de Cámaras Industriales de los Estados Unidos Mexicanos y, bueno, pues en el evento se destacó el crecimiento del sector textil en nuestro estado. El gobernador de Hidalgo también, pues destacó, como lo escuchan ustedes, la tradición que tiene desde muchos, muchos, hace muchos años nuestro estado en el tema textil, sobre todo en regiones muy identificadas, como usted lo sabe, la zona de Tulancingo, la zona de Cuautepec, son por antonomasia zonas textileras en nuestro estado. Aldo Falcón: también comenta el gobernador Julio Menchaca, Hidalgo es el quinto productor nacional de prendas de vestir. En el Congreso Nacional de Moda y Vestido reconocemos a quienes hacen posible esta actividad que generan empleos e ingresos para las familias hidalguenses.</t>
+  </si>
+  <si>
+    <t>Reunión con Empresarios</t>
+  </si>
+  <si>
+    <t>El gobernador de nuestro estado, Julio Menchaca Salazar, asistió a este evento denominado Congreso Nacional de la Moda y el Vestido 2026. Con la convicción de respaldar a todos los sectores económicos, el gobernador Julio Menchaca Salazar inauguró el Congreso de Moda y Vestido 2026, Que por primera vez se lleva a cabo en nuestro estado y que es un bastión de la industria textil Hidalgo tiene una historia ligada desde la fabricación de hilo hasta la confección de prendas Asumo el compromiso de acompañar esta importante actividad que desarrollan y se genere en un bienestar compartido El mandatario estatal reconoció el trabajo del sector empresarial que en sinergia con la administración estatal elevó los índices del Estado en la actividad económica. En este evento también estuvo presente José Pablo Maguad, presidente de la Cámara Nacional de Industria del Vestido y otros representantes de la Cámara Nacional de la Industria Textil como Rafael Torres y también Juan Porras Brambila, tesorero de la Confederación de las Cámaras Industriales de los Estados Unidos Mexicanos y bueno pues en el evento se destacó el crecimiento del sector textil en nuestro estado ¿Qué le parece si escuchamos las palabras del gobernador Julio Menchaca en la inauguración de este Congreso Nacional de Moda y Vestido 2026? Aldo, por favor. El gobernador de Hidalgo también destacó, como lo escuchan ustedes, la tradición que tiene. Desde hace muchos años nuestro estado en el tema textil, sobre todo en regiones muy identificadas, como usted lo sabe, la zona de Tulancingo, la zona de Cuautepec, son por autonomía zonas textileras en nuestro estado. Así es dicho también comenta el gobernador Julio Menchaca. Hidalgo es el quinto productor nacional de prendas de vestir. En el Congreso Nacional de Moda y Vestido reconocemos a quienes hacen posible esta actividad que genera empleos e ingresos para las familias hidalguenses. Muy bien, esto como parte de las actividades del gobernador Julio Menchaca ayer en esta capital hidalguense.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bGsTxWGiA-OPZo1vHSQTVL76jnhLxRmu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>José Pablo Maauad Pontón, Juan Porras Brambila, Guillermo Austreberto Vera Rodríguez</t>
+  </si>
+  <si>
+    <t>Hoy es un día muy importante porque por primera vez en la historia, un Oficial Mayor comparecerá ante el Congreso. Esto forma parte de una tradición que inició el ex gobernador Jesús Murillo Canan en los años 90, donde los miembros del gabinete del gobernador presentan sus informes ante los diputados. El gobernador Julio Menchaca Salazar presentó su cuarto informe de actividades en septiembre, el cual incluye los logros y metas de su equipo. Este proceso de comparecencias siempre ha generado diversas opiniones entre los diputados y la población, ya que a algunos les interesa y a otros no. Sin embargo, la comparecencia de hoy se destaca porque busca mejorar la transparencia y la rendición de cuentas. Orlando Ángeles, el Oficial Mayor, comparecerá a las 4 de la tarde, y es una oportunidad para que se expliquen los detalles sobre el gasto y la aplicación de recursos del gobierno. Este evento resalta la intención de las autoridades de resolver dudas y proporcionar claridad sobre el uso del dinero público. Se espera que esto contribuya a un mejor entendimiento de las responsabilidades del gobierno y fomente el diálogo entre autoridades y representantes populares. Mañana se discutirá en este espacio qué resultados dejó la comparecencia de Orlando Ángeles.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor</t>
+  </si>
+  <si>
+    <t>Hoy es un día muy importante, tenemos en esta agenda de las comparecencias de los integrantes del gabinete del gobernador Julio Menchaca Salazar por primera vez en la historia la comparecencia de un oficial mayor. Como yo les he platicado, recordarán ustedes, si no se los cuento, desde allá, desde los lejanos años 90, el ex gobernador Jesús Murillo Canan implementó esta modalidad de comparecencias parte de los secretarios de los integrantes del gabinete en la glosa de los informes de los gobernadores el mandatario estatal Julio Menchaca Salazar presentó en días pasados en septiembre su cuarto informe de actividades las logros, las metas todos los temas que incluyen el trabajo del gobernador y de su equipo están contenidos en ese informe, fueron contenidos en ese informe y como es tradición, las y los diputados, los integrantes de la legislatura local convocan a cada uno de estos secretarios y secretarias para que se presenten ante el pleno del Congreso y hablen a detalle sobre los temas de su responsabilidad sobre los temas que tienen que ver con la secretar que dirigen As se ha hecho durante muchos a y bueno pues el tema de las comparecencias a algunos los deja satisfechos, a otros no, a algunos les interesa, a otros no. Bueno, ha sido un tema del cual se ha opinado muchísimo, pero por primera vez en la historia y con el propósito de abonar, de fortalecer la cultura de la transparencia y de la información y sobre todo de la rendición de cuentas, puntual rendición de cuentas, hoy comparecerá por primera vez en el Congreso del Estado un oficial mayor, en este caso Orlando Ángeles, la comparecencia será a las 4 de la tarde y me parece algo que hay que destacar y algo que hay que reconocer porque esto es la voluntad de las autoridades por resolver dudas, por por supuesto dar a conocer cómo, cuándo, por qué, en qué y cuánto se gastan los dineros, se aplican los recursos y pues por supuesto estar abiertos a los cuestionamientos de los representantes populares, en este caso los diputados locales. Mañana estaremos platicando aquí Qué resulta de esta comparecencia del oficial mayor Orlando Ángeles.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1z1N2XOPuKnedk2Q4w2OtBl9N477Y1kTP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Edgar Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Andrés Torres antes de iniciar la transmisión de "Las Vocales Radio" por televisión comenta lo siguiente: "...digamos que funcionarios ignorantes, ¿no? e hijos de la rechingada. Son unos hijos de chingada. Y cobarde. Le molesta al señor director de Radio y Televisión de Hidalgo que nosotros tengamos redes sociales, ¿por qué? Porque él es un acosador y un delincuente. Nosotros sí somos trabajadores, nosotros sí somos gente de medios de comunicación, de certificados, no somos arribistas, ¿no? Y ojalá y me esté viendo y le pasen la nota al señor director, es un cobarde. Así, un cobarde. Para que quede bien claro, cuando guste, a la hora que quiera, lo podemos este aclarar. Lo podemos aclarar.</t>
+  </si>
+  <si>
+    <t>Peyorativo</t>
+  </si>
+  <si>
+    <t>...digamos que funcionarios ignorantes, ¿no? E hijos de la rechingada. Y cobarde. Le molesta al señor director de Radio Televisión de Algo que nosotros tengamos redes sociales. ¿Por qué? Porque él es un acosador y un delincuente. Nosotros sí somos trabajadores, nosotros sí somos gente de medios de comunicación, de certificados, no somos arrigbistas, ¿no? Y sobre todo, y ojalá y me esté viendo Y le pasen la nota al señor director Es un cobarde Un cobarde Para que quede bien claro Cuando guste, a la hora que quiera Lo podemos aclarar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FgVJcDf21wJHX8Zkgf6WkdzQoGEwmLGK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Seguimos fuera del aire allá en Jacala de Ledezma, ya cumplimos un mes fuera del aire en el 91.1 de frecuencia modulada, les ofrecemos una disculpa. Bueno, pues estamos esperando que las áreas técnicas y administrativas pues resuelvan los problemas allá en la estación.</t>
+  </si>
+  <si>
+    <t>Jacala</t>
+  </si>
+  <si>
+    <t>Seguimos fuera del aire en Jacala de Ledezma, ya cumplimos un mes fuera del aire en 91.1 de frecuencia modulada, les ofrecemos una disculpa. Bueno, pues estamos esperando que las áreas técnicas y administrativas resuelvan los problemas allá en la estación.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EIHpEHdWZ875y0Z5lGMUigfReoeksS50/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud lleva a cabo una campaña de vacunación contra el Covid y antiinfluenza estacional. Se recomienda que la gente se acerque a la clínica, hospital o centro de salud más cercano para recibir su vacuna, que es gratuita. Las prioridades son niños menores de 5 años, adultos mayores y personas con enfermedades crónicas. Hay más de 1,500,000 dosis disponibles en todo el estado para proteger a la población, especialmente en la temporada invernal que se aproxima, para enfrentar el Covid y la influenza.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud continúa con la campaña de vacunación anti-COVID, antiinfluencia estacional. Por favor, acérquese si ese es su voluntad, si ese es su deseo, pero es lo deseable, es lo recomendable. Hay que ir a la clínica de salud más cercana a su domicilio, al hospital, al centro de salud, para que los vacunen, para que solicite usted su vacuna. Es totalmente gratuito, principalmente niños menores de 5 años, adultos mayores y por supuesto personas que tengan enfermedades crónico-degenerativas serán los principales en este momento los principales sectores a atender pero hay vacunas disponibles, hay más de 1.500.000 dosis en todo el estado y son totalmente gratuitas por supuesto para que usted esté bien protegido y en esta temporada invernal que ya se acerca, bueno pues le hagamos frente al COVID y con mucho también cuidado con el tema de la influenza estacional Así es, acude a su centro de salud, como bien mencionas, es completamente gratis la vacuna.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Op9VkCfBeO_0_dkd4eP18B0EcTRUOF_m/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Recordándoles que tenemos una advertencia, tenemos la alerta que nos da la Subsecretaría de Protección Civil y Gestión de Riesgos del Gobierno del Estado de Hidalgo, dependiente de la Secretaría de Gobierno, respecto a los temas del clima. Se esperan descensos de temperatura nuevamente y lluvias, lluvias moderadas en buena parte del estado. Sin embargo, la Subsecretaría de Protección Civil nos dice, "Hay que estar muy atentos, por favor, no hay que bajar la guardia en estos días que, bueno, pues el clima está en esta situación cambiante". La Subsecretaría de Protección Civil y Gestión de Riesgos informa a la población que para este 22 de octubre de 2026, de acuerdo con el aviso número 587 del Pronóstico Meteorológico General del Servicio Meteorológico Nacional, se prevén intervalos de chubascos de 5 a 25 milímetros. Asimismo, se pronostican temperaturas mínimas de 0 a 5 grados, con vientos de 10 a 20 kilómetros por hora y con rachas de 30 a 50 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>Recordándoles que tenemos una advertencia, tenemos la alerta que nos da la Subsecretaría de Protección Civil del Gobierno del Estado de Hidalgo dependiente de la Secretaría de Gobierno respecto a los temas del clima. Se esperan descensos de temperatura nuevamente y lluvias, lluvias moderadas en buena parte del Estado. Sin embargo, la Subsecretaría de Protección Civil nos dice, hay que estar muy atentos, Por favor, no hay que bajar la guardia en estos días que, bueno, pues el clima está en esta situación cambiante. A ver, Aldo Facón, por favor, ayúdanos. Así es, la Subsecretaría de Protección Civil y Gestión de Riesgos informa a la población que para este 22 de octubre de 2026, de acuerdo con el aviso número 587 del pronóstico meteorológico general del Servicio Meteorológico Nacional, se prevén intervalos de chubascos de 5 a 25 milímetros. Asimismo, se pronostican temperaturas mínimas de 0 a 5 grados Con vientos de 10 a 20 kilómetros por hora y con rachas de 30 a 50 kilómetros por hora Descenso importante de temperaturas sobre todo en las zonas altas</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fZReCZRuC21NzECDSOgkeP6lULV7NWW1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1941/2026</t>
+  </si>
+  <si>
+    <t>Con publicación editorial, SEPH impulsa la preservación de la lengua Náhuatl y su legado cultural</t>
+  </si>
+  <si>
+    <t>CELCI</t>
+  </si>
+  <si>
+    <t>Preservación Lenguas Maternas</t>
+  </si>
+  <si>
+    <t>Huejutla</t>
+  </si>
+  <si>
+    <t>Déjeme compartirle rápidamente que como parte de las acciones para preservar y transmitir la riqueza cultural de Hidalgo, la Secretaría de Educación Pública, a través del Centro Estatal de Lenguas y Culturas Indígenas, presentó el libro "Palabras que nos que no se lleva el viento", una publicación que reúne textos en lengua náhuatl y mantiene viva su escritura, la transmisión de conocimientos y el reconocimiento de las lenguas originales originarias, perdón, esto como parte de las acciones impulsadas por el gobierno de Julio Menchaca Salazar para fortalecer la identidad cultural y preservar el patrimonio de los pueblos originarios. La obra integra textos elaborados por maestras y maestros de educación indígena, así como por personal del sector salud que participa como evaluador en los procesos de admisión al servicio docente y cuenta con certificación en lengua náhuatl. Los escritos son resultado del taller de actualización del alfabeto y escritura creativa, un espacio de aprendizaje y creación literaria en el que las y los participantes abordaron temas como el trabajo, la salud, los recuerdos de la niñez, el agua y las experiencias de vida cotidiana mediante diversos géneros y formatos de escritura. Entre los aportes de la publicación destaca la incorporación de las nuevas grafías del alfabeto conforme a la nueva norma de escritura de la lengua náhuatl, lo que contribuye al desarrollo de habilidades escritas y a la consolidación de criterios comunes para su uso y enseñanza. Estas acciones se alinean con la visión educativa del gobernador y del secretario de Educación Pública de promover una educación inclusiva, intercultural y humanista que reconozca la diversidad lingüística como parte fundamental de la identidad y la riqueza cultural de Hidalgo. La presentación se realizó en las instalaciones del Instituto Tecnológico de Huejutla, como parte del Día Internacional de la Medicina Tradicional, una fecha que destaca la importancia de preservar los conocimientos ancestrales de los pueblos originarios a través del Elcelsi, el Centro Estatal de Lenguas y Culturas Indígenas. La SEPH impulsa espacios de creación escrita en lengua materna para contribuir a la difusión de las lenguas indígenas y propiciar que las voces, experiencias y saberes de sus hablantes se transmitan a las nuevas generaciones.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mChRg8BmLKyfxVlSHkYGdsdGkMNlS3QA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Pacula</t>
+  </si>
+  <si>
+    <t>La entidad se posiciona como referente nacional en la permanencia y  egreso de  estudiantes de preparatorias y universidades, apoyos educativos y fortalecimiento de infraestructura   
+Hidalgo avanza en el fortalecimiento de su sistema educativo y escala una posición para colocarse como el octavo estado del país con mejor desempeño en eficiencia terminal; a este logro se suma el progreso obtenido del diagnóstico de los Ejercicios Integradores del Aprendizaje y la inversión sostenida en infraestructura educativa, ciencia, tecnología y deporte, que amplía las oportunidades de desarrollo para las y los estudiantes. 
+Durante estos cuatro años, el proyecto educativo de la actual administración ha impulsado la formación de estudiantes capaces de transformar sus comunidades, fortalecer su identidad y contribuir a una sociedad más justa y humana. Cada trayectoria escolar suma al bienestar colectivo y nos acerca a un propósito común: sabernos un solo Hidalgo.
+Así lo expuso el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, durante su comparecencia ante las y los integrantes del Congreso del Estado, como parte de la Glosa del Cuarto Informe del gobernador Julio Menchaca Salazar.
+Hidalgo mejora los indicadores de trayectoria educativa
+La educación en Hidalgo ha tenido significativas mejoras en todos los niveles para que las y los estudiantes  permanezcan y concluyan sus estudios satisfactoriamente. En este contexto, Natividad Castrejón informó que la entidad mantuvo el 39 por ciento de la proporción de estudiantes que concluyen la educación superior por cada 100 que ingresan a primero de primaria. Este indicador sitúa a Hidalgo en el octavo lugar nacional, lo que representa un avance de una posición respecto al año anterior.
+Uno de los avances más sobresalientes se registró en educación media superior, donde la eficiencia terminal pasó de 63.2 por ciento en el ciclo escolar 2021-2022 a 75.6 por ciento en 2024-2025, lo que significó un incremento de 12.4 puntos porcentuales.
+En educación superior también se logró un importante incremento en eficiencia terminal, la cual avanzó de 69.6 a 84.5 por ciento, es decir una mejora de 14.9 puntos porcentuales. 
+SEPH acerca bachillerato a jóvenes de todo el estado 
+Con el propósito de ampliar las oportunidades educativas, el secretario destacó la incorporación de seis servicios de educación media superior, que permitieron garantizar la presencia de al menos un plantel público de este nivel en cada uno de los 84 municipios de Hidalgo.
+A estas acciones se suma la creación de 12 nuevos servicios de educación media superior; dos son Bachilleratos Generales, dos Telebachilleratos Comunitarios y ocho operarán bajo el modelo de Bachillerato Nacional Margarita Maza, para atender a jóvenes de seis municipios y ofrecer alternativas flexibles que faciliten la continuidad de sus estudios.
+Asimismo, se iniciaron las gestiones para construir 10 planteles de Telebachillerato Comunitario con instalaciones propias en zonas rurales, todo esto mediante una inversión de 290 millones de pesos.
+Hidalgo con la red de laboratorios STEM más grande del país; destaca en competencias internacionales</t>
+  </si>
+  <si>
+    <t>Semot/Bol.05/2026</t>
+  </si>
+  <si>
+    <t>Durante su comparecencia ante la sexagésima sexta Legislatura local, la titular de la Secretaría de Movilidad y Transporte (Semot), Lyzbeth Robles Gutiérrez, destacó la incorporación de tecnología avanzada —como cámaras con inteligencia artificial y sistemas de videovigilancia— en las unidades de transporte masivo. Asimismo, abordó las problemáticas viales de la zona metropolitana, enfatizando la importancia de respetar el carril exclusivo del Tuzobús para garantizar la seguridad vial, optimizar las frecuencias de paso y evitar el congestionamiento generado por la invasión de vehículos particulares.</t>
+  </si>
+  <si>
+    <t>En otra comparecencia y seguía compartiendo con usted, compareció ante la sexagésima sexta Legislatura la titular de la Semot, Lisbeth Robles Gutiérrez. Informó que se han incorporado unidades con inteligencia artificial, videovigilancia y accesibilidad universal. Como parte de la glosa del cuarto informe del gobernador Julio Menchaca, la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez, compareció y ahí él destacaba los trabajos que están haciendo para poder desahogar la salida hacia la ciudad de México, digamos Pachuca, Tizayuca, Estado de México, la Ciudad de México, hay una aglomeración constante y ya hemos comentado tanto por las lluvias, algunas obras y también nuestra participación que en ocasiones es plan de desesperación por ser primeros pues nos lleva a generar también o tener una falta de civilidad en la conducción en el manejo. No son casos generales, son casos particulares, pero nos ha tocado y entonces alguien en la desesperación dice, "Pues yo me voy a la vía en donde pasa la unidad de transporte público." Desde luego, desde luego, sin dejar de lado que en muchas ocasiones se ha mencionado, lleva un paciente, hay una ambulancia, o sea, hay hay hay varios hechos que se concatenan para que se genere esto que conocemos ya entonces como un nudo. Al día de ayer la secretaria de movilidad, Lisbeth Robles Gutiérrez, señaló, es un tema de ley, asisten a ley, claro, habrá mesas de trabajo, se está analizando para que se tome una determinación y nadie resulte afectado. Recordemos lo que dijo Lyzbeth Robles Gutiérrez.
+“Se hizo el anuncio de que estaríamos realizando un análisis por medio de unas cámaras que se van a situar en tres puentes sobre el bulevar Felipe Ángeles, en donde tenemos también puentes a cargo del Sistema Integrado de Transporte Masivo y que en esas cámaras que tienen utilización de inteligencia artificial nos va a permitir también medir el número de unidades conjuntamente con la información que pueda ser proporcionada por Seguridad Pública y por Seguridad Pública y Tránsito Municipal de Pachuca. Eh una vez que tengamos eso y que a la vez se haga la reunión correspondiente o las acciones inherentes a través de la coordinación que en su momento se origine por la Secretaría de Gobierno, estaremos en posibilidad de anunciamos de fondo. En ese momento yo mencioné lo que legalmente correspondía a la Secretaría y al organismo mencionado en torno al carril exclusivo. El carril exclusivo la ley establece que se debe de privilegiar obviamente para la operación eficaz y adecuada del transporte masivo, insisto que fue originado hace más de 10 años con una infraestructura en la cual cuenta un además de puentes y estaciones con el carril adecuado y exclusivo para que pueda brindar un servicio eficaz con las frecuencias de paso correspondientes y además es un tema de seguridad vial. Cuando las unidades de vehículos particulares transitan sobre un carril exclusivo, el congestionamiento se extiende no solamente a los carriles en donde de manera ordinaria transitan los vehículos particulares, sino que se extiende también ese congestionamiento vial hacia el carril exclusivo, lo cual incrementa el congestionamiento a lo ancho de toda la vialidad. Las vialidades son de todas y de todos y también debemos aprender a compartirlas y está apegado a la ley, a las políticas internacionales, nacionales y estatales el hecho de que exista un carril confinado para que las unidades de transporte masivo, que son generalmente en este caso a través de unidades BRT, se pueda llevar a cabo de manera óptima”.
+Parte de lo que se destacó en la comparecencia en el día de ayer.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XvooEDZYdTnWodsPZSfxNmNGdrt3SsLr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Sebiso/Bol.698/2026</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, compareció ante el Congreso del Estado para detallar los avances del cuarto informe de gobierno. Destacó que los programas sociales se triplicaron de 4 a 12 acciones directas, alcanzando un presupuesto de 400 millones de pesos destinados a combatir la pobreza y apoyar a sectores vulnerables, incluidos adultos mayores, personas con discapacidad y cuidadoras. Asimismo, resaltó la cobertura territorial mediante las "Casas del Pueblo" para eliminar intermediarios en la entrega de apoyos. No obstante, señaló los retos en el registro e integración de artesanos en ciertas demarcaciones como la comarca minera y parte del Valle del Mezquital, a pesar de los 15 millones de pesos asignados a este sector.</t>
+  </si>
+  <si>
+    <t>Bienestar</t>
+  </si>
+  <si>
+    <t>El titular de la Sebiso, Ricardo Gómez Moreno, en comparecencia ante el Congreso de Hidalgo, informó que la cobertura de programas pasó de 4 a 12 acciones directas en la gestión del gobernador Julio Menchaca Salazar, un incremento histórico. Y el presupuesto y alcance destacan 400 millones de pesos para combatir la pobreza y la deficiencia de recursos para cuidadores de personas con discapacidad. Durante la glosa del cuarto informe de gobierno, el secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, informó que ante el Congreso del Estado que en 2026 esta dependencia triplicó sus programas sociales, pasando de 4 a 12 acciones directas dirigidas a combatir la pobreza. El funcionario destacó la cobertura territorial alcanzada en comunidades de difícil acceso dentro de los municipios de Metztitlán, Huehuetla y Tlahuiltepa, donde se atendió a población históricamente marginada y, de manera particular, a personas cuidadoras de adultos mayores y también hay apoyo para adultos mayores.
+Nuestro compromiso es generar mejores condiciones de atención a favor de nuestras personas adultas mayores. Vivir en plenitud debe realizarse con compromiso a favor de quienes con sus enseñanzas y dedicación sostienen con orgullo a nuestro estado. Como parte de la estrategia para acercar la política social a través de la Dirección General de las y los Servidores del Pueblo, nos ha permitido fortalecer nuestro trabajo territorial, nuestra cobertura operativa. Se han optimizado los tiempos de entrega, se brinda una atención directa y, lo más importante, sin intermediarios, vigilándose de cerca la entrega final de los apoyos otorgados por la secretaría. De igual manera, se han realizado entrega de tarjetas no solo en las cabeceras municipales, sino también en las comunidades más alejadas. Además, se han llevado a cabo entrevistas de verificación y validación de la información proporcionada por las personas solicitantes”.
+En este mismo tema, también Ricardo Gómez Moreno señaló que se ha brindado apoyo a personas que tienen esta actividad importante en materia de artesanías, pero también destacó algo que no dejó de llamar la atención, hay artesanas y artesanos que se les ha invitado a que se sumen, se registren en las convocatorias, en el padrón de artesanas y artesanos y en algunas partes ha sido muy limitada la respuesta. Ricardo Gómez Moreno señaló:
+“En esta parte, conforme a la intervención y al video, establecimos todas las acciones que hemos venido generando a favor de todas las personas artesanas. En el programa este año contamos con 15 millones de pesos, beneficiamos a 1,425 personas artesanas. Y de manera muy puntual, en la comarca minera, que hemos tenido, que si bien esta es una parte del Valle del Mezquital, pero sí hemos tenido entre Tasquillo e Itzmapan y la los municipios de Actopan, Pizafores, Chafoluacán, la Misión, sí hemos tenido muy pocos registros. Incluso eh hemos habilitado los mismos en la Casa del Pueblo de Itzmapan, buscando que se registren más de esa región, porque prácticamente eh te puedo corroborar que el la gran mayoría se registra de la Huasteca eh por obviedad, porque allá, por supuesto, hay muchísimas personas artesanas. Lo que es este eh el Autonmi Tetegua, principalmente de Tenango, San Bartolo y un poco menos de Huehuetla, eh lo que es el Valle del Mezquital, pero de mayor número lo que es principalmente Alfalhucan e Itzmiquilpan, es donde más se absorbe el registro. Y entonces eh los recursos que hemos dirigido eh prácticamente se han absorbido en estas tres regiones, como como lo hemos comentado. Pero bueno, te pudiera comentar que eh en este contexto, para este año, lo que te decía, en Alfalhucan son 37 las personas beneficiarias, en Hacala solo son cuatro, en Tasquillo solo son tres y no tenemos en Itzmapan, lo que te decía. Entonces, sí hemos trabajado mucho más en esas regiones, pero a pesar de que hemos llevado las inscripciones directamente a eh Itzmapan, no hemos logrado que se inscriban, entonces es un trabajo que tenemos que fortalecer todavía más, pero lo estamos haciendo de una manera muy puntual, porque sí tenemos muy detectado en dónde tenemos un gran número de inscripciones, pero en dónde realmente nos falta que muchas personas artesanas se inscriban a los programas, pero eh también te comento, en la participación de la Feria de San Francisco, logramos traer personas artesanas de esas regiones, pero no hemos logrado que se inscriban durante el tiempo que tenemos aperturada las ventanillas para los mismos”.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FArVGXiAE8JGBD1r9Wb6P2k_7HDwccZu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Julio Menchaca,</t>
+  </si>
+  <si>
+    <t>Durante su visita a la subestación Hidalgo en Pachuca, el gobernador Julio Menchaca Salazar reafirmó la estrecha colaboración y coordinación con la Comisión Federal de Electricidad (CFE), acompañado por funcionarios estatales como el secretario de desarrollo económico, Carlos Henkel Escorza, y la directora de la agencia estatal de energía, Ivonne Margarita Ramírez Núñez. En el encuentro con el encargado de la gerencia de la división Centro Oriente de la CFE, Jesús Alberto Armenta Lara, se destacó la importancia estratégica de la infraestructura eléctrica para garantizar servicios seguros y de calidad que impulsen el desarrollo social y económico del Estado.</t>
+  </si>
+  <si>
+    <t>Recorrido por instalaciones</t>
+  </si>
+  <si>
+    <t>Le había comentado, lo dije al principio, eh la Comisión Federal de Electricidad reafirma su colaboración con el gobierno de Hidalgo, con la visita del mandatario Julio Menchaca Salazar. Durante la visita del mandatario a la subestación Hidalgo en Pachuca, la Comisión Federal de Electricidad ha reafirmado su compromiso de mantener una estrecha colaboración y coordinación con el gobierno estatal, acompañado del secretario de desarrollo económico, ingeniero Carlos Henkel Escorza y la directora de la agencia estatal de energía, arquitecta Ivonne Margarita Ramírez Núñez, el maestro Julio Menchaca fue recibido, el gobernador fue recibido el lunes 19 de octubre por el encargado de la gerencia de la división Centro Oriente de la Comisión Federal de Electricidad, ingeniero Jesús Alberto Armenta Lara. Durante este encuentro se destacó la relevancia estratégica de la infraestructura e instalaciones eléctricas de la comisión, que son fundamentales para garantizar el servicio que sea seguro, confiable y de calidad, contribuyendo pues al desarrollo económico, social y el bienestar de las familias hidalguenses. Esta visita del mandatario refleja la sólida relación de trabajo con la Comisión Federal de Electricidad basada en tres puntos: el diálogo, la cooperación y el objetivo común de atender necesidades de la ciudadanía con eficiencia y visión de futuro. Vamos a hacer una pausa, al retorno tenemos más en la información.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JeOx85Jed3zI51lZNvcwZU1VzqEqqmTk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, inauguró el Congreso de Moda y Vestido 2026, reafirmando el compromiso estatal de consolidar a la entidad como un bastión de la industria textil y de la confección. Respaldado por la Canaive y la Canaintex, el sector busca alinearse con el Plan México para impulsar la competitividad, la atracción de inversiones y el desarrollo económico. Asimismo, ante retos globales como el contrabando y la informalidad, se destacó que la paz laboral y la estabilidad de Hidalgo posicionan al estado como una de las mejores opciones para el crecimiento de nuevos negocios.</t>
+  </si>
+  <si>
+    <t>Reunión Con Empresarios</t>
+  </si>
+  <si>
+    <t>Bueno, le informo a usted, Hidalgo se consolida como bastión industrial de la moda y el textil. Hay un respaldo gubernamental, el gobernador Julio Menchaca inauguró el día de ayer el histórico Congreso de Moda y Vestido 2026 en este estado. La Canaive y la Canaintex impulsan la competitividad y, desde luego, hay una alineación con el plan México. El sector refuerza la agenda del gobierno federal con paso social y atracción de inversiones. Como vemos, cada eslabón va formando una cadena de circunstancias y de modelo, desde luego, que fortalece el desarrollo. En el marco de la inauguración del primer Congreso de Moda y Vestido 2026 en el estado, el gobernador Menchaca Salazar ha reafirmado su compromiso con el sector empresarial para consolidar a Hidalgo como el bastión de la industria textil y de la confección en el país. El gobernador destacó la arraigada tradición de Hidalgo desde la elaboración de hilos hasta la confección de prendas, Julio Menchaca Salazar destacó:
+“Hidalgo tiene una historia, ligada desde la fabricación del hilo hasta la confección de prendas. Asumo, como lo he hecho desde un principio, el compromiso de acompañar esa importante actividad que desarrollan y que se genere un bienestar compartido”. 
+Frente a desafíos globales como la informalidad, el contrabando y el robo al transporte, la Cámara Nacional de la Industria Textil ha señalado que el sector avanza en una estrategia alineada al Plan México del gobierno federal y, desde luego, concluyen que la estabilidad y paz laboral de Hidalgo posicionan a nuestro estado como una de las mejores opciones para el crecimiento de nuevos negocios. Enhorabuena también, todo esto genera desarrollo, genera empleo, genera tranquilidad, paz social y, sobre todo, entra con se corre como corresponde a Hidalgo en la competencia en todos los mercados.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FrO0INuX5Ev0fIh9ksxREOlyP2KHE1J1/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Cultura/Bol.721/2026</t>
+  </si>
+  <si>
+    <t>Hidalgo lleva tradición del Xantolo a Berlín, Alemania</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>Y ya para concluir, desde Pachuca, le comento esto que, por supuesto, nos llena de orgullo: el hecho de que las festividades, las tradiciones hidalguenses, como el Xantolo, pues lleguen a otras latitudes. Será en Berlín, Alemania, donde se establecerá un altar conmemorativo, esto en la Embajada de México allá en en Alemania, para mostrar al público de Berlín específicamente cómo se celebra el Día de Muertos en la Huasteca hidalguense. Y esta en esta celebración, en esta muestra de la tradición mexicana, informó el embajador de México en Alemania, Francisco Quiroga Fernández, también participará Atlisco, Puebla, con sus monumentales catrinas. Así es que el Xantolo de la Huasteca hidalguense y las catrinas monumentales de Atlisco, Puebla, estarán presentes en Berlín, Alemania, donde el público está muy ávido de presenciar, de conocer más de las tradiciones mexicanas, y qué mejor que sea en particular de las tradiciones hidalguenses.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XIzy_WUX5P5dQTq8r8CBl6Q6se_sO3Qq/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Embajada de México en Alemania</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo</t>
+  </si>
+  <si>
+    <t>Francisco Quiroga Fernández, Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Triplicó Sebiso apoyos para sectores vulnerables de Hidalgo: Ricardo Gómez Moreno durante su comparecencia ante representantes del Congreso del Estado.</t>
+  </si>
+  <si>
+    <t>En su comparecencia ante el Congreso del Estado, como parte de la glosa del cuarto informe de gobierno, el titular de la Secretaría de Bienestar e Inclusión Social, Ricardo Gómez Moreno, destacó que la gestión de tres veces más recursos y programas sociales, la atención a zonas de difícil acceso y a sectores históricamente olvidados, forman parte de las acciones que durante 2026 realizó la administración estatal a través de la dependencia que encabeza. En su intervención destacó que esta dependencia se se triplicaron los programas de en comparación con la administración anterior, pasando de 4 a 12 acciones en atención social. Explicó que la estrategia de este año contempló llevar los programas de la Secretaría de Bienestar e Inclusión Social hasta las comunidades más lejanas y con rezago persistente, lugares a los que en algunos casos se llegó a pie por lo intrincado de la geografía estatal. Comunidades como Tlatemaya, Metztitlán, Nexcay, el Catrín, la Piña, la Tortuga y las Juntas, en Huehuetla, Nueva Reynosa y Coyocala, en Tlahuiltepa, por mencionar algunas, donde se escuchó a la población que jamás había sido atendida por un secretario de la entidad. De igual forma, Gómez Moreno habló sobre el programa para quienes asisten de tiempo completo a personas con discapacidad múltiple permanente para que este año se haya duplicado su presupuesto que pasó de 5 a 10 millones de pesos en beneficio de 950 familias. Asimismo, con el programa de desarrollo inclusivo dirigido a la comunidad LGBT+ se impulsó a este sector en temas de salud, derechos humanos y desarrollo económico con un presupuesto de 5 millones de pesos en apoyo de 291 personas. Respecto al programa de bienestar y desarrollo, comentó que en el periodo reportado se benefició a 38,000 personas en situación de pobreza y alta marginación con un presupuesto de 400 millones de pesos. De igual forma, una estrategia de gran impacto es la del programa Madres Trabajadoras que en 2026 otorgó 12,300 apoyos económicos para igual número de mujeres que pues no abandonen sus estudios o trabajos por las labores propias de la maternidad y puedan así buscar un mejor futuro. Un sector donde se emplean muchas mujeres es el artesanal, por ello se destinaron recursos, dijo Ricardo Gómez, por 1,500,000 pesos para el programa Fomento Artesanal, que mediante concursos, reconocimientos y acciones de difusión buscan darle realce a las creaciones de las artesanas y artesanos de la entidad. En el mismo sector, el programa Bienestar para Personas Artesanas se distribuyeron 10,000 pesos para 1,425 creadores. Desglosó que en temas de atención a migrantes se invirtieron 5 millones de pesos que se utilizaron para la apertura de proyectos productivos para la población migrante. De la misma forma, se asesoró a migrantes y sus familias en trámites migratorios. En el rubro de juventudes destacó las capacitaciones, pláticas, reconocimientos, financiamiento a emprendimiento y otros servicios con una inversión de 6 millones 200,000 pesos. Para que las personas adultas mayores vivan una mejor vejez, se invirtió en remodelaciones y equipamiento, así como gasto de operación de centros gerontológicos y casas de día, con recursos por 37.7 millones de pesos, además de la entrega de 3,522 apoyos funcionales. En su mensaje de cierre, Ricardo Gómez Moreno comentó que la instrucción del gobernador Julio Menchaca fue que las acciones y programas que se han acercado al se acerquen a las puertas de quienes más lo necesitan y eso se logró a través de las y los servidores del pueblo que, mediante sus 27 Casas del Pueblo, permiten la entrega de los programas de esta y otras secretarías de la administración estatal, atendiendo directamente a más de 214,000 personas, es lo que informó ante legisladores el secretario de Bienestar.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10WHy3EWy6JaLGtcuEGzTLBOuQ5AUkxUo/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>En el marco del desarrollo de la industria del vestido en el estado, locutor Juan Carlos Santamaría destacó la importante colaboración y vinculación con el sector académico e instituciones de educación superior en la entidad, tales como la Universidad de la Sierra Hidalguense y la Universidad Politécnica de Tulancingo. Estos centros educativos impulsan la investigación y la innovación en el diseño de prendas funcionales que propicien el bienestar integral de las personas. Asimismo, se destacó que la infraestructura de la región, aunada a los trabajos de seguridad y recuperación de transporte de mercancías, consolidan a Hidalgo como un punto clave y atractivo para la inversión en el sector textil y de la moda.</t>
+  </si>
+  <si>
+    <t>Y en este contexto de la industria del vestido, cabe recordar también la suma de la academia. En este espacio informativo hemos tenido la oportunidad de platicar con docentes y con alumnos de la universidad eh de la de la Huasteca, de la Sierra Hidalguense, perdón, donde existe esta carrera. Ahí está justo en el municipio de Sahuatipan, un productor de de mezclilla, de prendas de de mezclilla, entre otras cosas, por supuesto, pero de manera preponderante de de esta eh pues eh popular ropa. Y y bueno, eh en esto que dicen los empresarios, de que no solamente es la la confección de de ropa, sino también buscar la innovación, y en este sentido hemos platicado con docentes e incluso con el propio rector de la Universidad Politécnica de Tulancingo, quienes nos han eh compartido que en esta búsqueda de la innovación buscan que que la ropa no solamente sea cómoda, sea agradable a la vista, sino que eh tenga algunos elementos que permitan un bienestar integral de las personas. Y, bueno, pues eso se está haciendo desde la academia en la entidad. Eh, universidades, instituciones como la Universidad de la Sierra Hidalguense y la Politécnica de Tulancingo, y es parte de lo que conforma un entorno eh pues adecuado para el desarrollo de la industria de la moda y el vestido en la entidad. Esto, aunado también a las eh a los trabajos que se realizan en materia de seguridad y, de hecho, también le hemos podido compartir algunos resultados de la recuperación de eh transporte eh pesado con mercancías, algunas pertenecientes justamente a este sector, al sector eh textil y y bueno, todo todo esto hace de Hidalgo un punto atractivo, no solamente para la realización de este congreso, sino sobre todo para la inversión en el sector textil, en el sector de la moda y el vestido.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1442YUW74WBWjSRPeRWbWUnRLnh8ZQlJT/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Congreso Nacional de Moda y Vestido 2026.</t>
+  </si>
+  <si>
+    <t>Y en y en más información del gobierno del Estado le comento que eh pues eh el gobernador inauguró el Congreso de Moda y Vestido, que por primera vez se lleva a cabo en el estado, que es un bastión de esta industria. En este sentido, esto es parte de lo que destacó el mandatario estatal.
+“Hidalgo tiene una historia, ligada desde la fabricación del hilo hasta la confección de prendas. Asumo, como lo he hecho desde un principio, el compromiso de acompañar esa importante actividad que desarrollan y que se genere un bienestar compartido”. 
+El Ejecutivo estatal reconoció el trabajo del sector empresarial que, en sinergia con las administraciones estatal, ha elevado los índices del estado en actividad económica. Recordemos, por supuesto, que Hidalgo está a la vanguardia en cuanto a actividad industrial. José Pablo Maauad Pontón, en este contexto, él es el presidente de la Cámara Nacional de la Industria del Vestido, detalló que el congreso es un espacio para entender el entorno y vislumbrar el futuro de la industria de la moda y el vestido, destacando el intercambio de ideas, experiencias y buenas prácticas. Además, puso a disposición del gobierno de Hidalgo la experiencia técnica, la vinculación productiva y el acompañamiento para ayudar en los procesos de compra de uniformes. Dijo José Pablo Maauad: Hidalgo es un bastión de nuestro sector, por eso estamos hoy aquí durante su carrera pública ha sido siempre un amigo impulsor de nuestra industria. Aquí presente, desde los polos de confección de Singuilucan, Tulancingo, Cuautepec, Pachuca, Tizayuca y Axacuba, a las fábricas textiles de Tepeji, agradecemos y reconocemos su apoyo, manifestó el dirigente empresarial. Rafael Torres, él es presidente de la Cámara Nacional de la Industria Textil, recordó que este sector enfrenta presiones relacionadas con el contrabando, mayores costos laborales, robo al transporte, prácticas ilegales e informalidad que debilitan la cadena productiva, lo cual se afronta desde este sector con el avance de una agenda de sustitución de importaciones y fortalecimiento de contenido nacional. Durante su mensaje, Juan Porras Brambila, tesorero de la Confederación de Cámaras Industriales de los Estados Unidos Mexicanos, refirió que la industria del vestido es mucho más que moda y confección, resaltando la innovación, el talento y el esfuerzo de miles de mujeres y hombres que son respaldados en su actividad económica mediante el plan México de la presidenta Claudia Sheinbaum. "El bienestar vendrá por el trabajo", afirmó Guillermo Austerberto Vera Rodríguez, presidente de la Cámara Nacional de la Industria del Vestido, Delegación Hidalgo, al destacar que en la entidad existe paz social y laboral, logrando ocupar los primeros lugares de crecimiento y buen clima para hacer negocios.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eqkUg7ShBkFQZoYcW5gps7y5ogRTJ4e0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>José Pablo Maauad Pontón, Rafael Torres, Juan Porras Brambila, Guillermo Austerberto Vera Rodríguez, Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Estamos con información desde Pachuca y le comento que el gobernador Julio Menchaca participó en la reunión encabezada por la presidenta Claudia Sheinbaum Pardo en Palacio Nacional, donde se evaluaron los avances del programa Vivienda para el Bienestar y se acordó fortalecer la coordinación entre los tres órdenes de gobierno para agilizar su implementación. Como parte de esta estrategia nacional, que contempla la construcción de 1.8 millones de viviendas, en el estado de Hidalgo se proyectan 66,500 en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo, con el objetivo de ampliar el acceso de las familias hidalguenses a una vivienda digna. Asimismo, Menchaca Salazar acompañó a la mandataria nacional en un encuentro para revisar los avances del proceso de modernización del IMSS Bienestar junto a 23 gobernadoras y gobernadores —también son 24 las entidades, recordemos— donde se ha implementado el programa, el sistema del IMSS Bienestar.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sGMtR7c4TgF_2QWpJJBXvYMIwRdR2_zr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum,</t>
+  </si>
+  <si>
+    <t>A cuatro años de este gobierno, la SEMOT avanza en la ejecución de acciones necesarias tendientes a planificar la movilidad</t>
+  </si>
+  <si>
+    <t>En otros temas, le comento acerca de la comparecencia de la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez ante la sexagésima sexta Legislatura local, donde detalló, ante ellos detalló los logros alcanzados durante el cuarto año de la administración que encabeza el gobernador Julio Menchaca Salazar. Durante su intervención, la secretaria informó que se actualizaron y complementaron los planes integrales de movilidad urbana sustentable de las zonas metropolitanas de Tula y Tulancingo, además de elaborarse el plan del municipio de Tizayuca. Estos instrumentos de planeación cuentan con una inversión superior a los 25 millones de pesos. En el mismo sentido, la titular de la dependencia informó que se encuentran en proceso de ejecución los planes integrales de movilidad urbana sustentable de Huejutla y de Ixmiquilpan. Por otra parte, la titular de la Semot enfatizó que el sistema integrado de transporte masivo de Hidalgo cuenta con una flota vehicular consistente en 140 unidades nuevas con capacidad de 80, 50 y 15 personas pasajeras, con tecnología de última generación, con cámaras de videovigilancia, inteligencia artificial que permite analizar los hábitos de conducción, asientos preferentes destinados a mujeres, personas con discapacidad y adultos mayores. De la misma manera, la secretaria afirmó que con el propósito de mantener el servicio de movilidad incluyente e integral en el sistema de transporte masivo, a través de ocho unidades equipadas con elevadores para sillas de ruedas, tres corralillos de sujeción, sistema de comunicación visual y auditiva y pantallas con proyecciones en lengua de señas mexicanas, se han atendido a personas con discapacidad, adultos mayores y con movilidad reducida. De igual forma, se llevaron a cabo acciones tendientes a despejar el carril exclusivo, mismas que consistieron en realizar inspecciones para evitar su invasión previa socialización e aplicación de 203 amonestaciones a la población, sin pretender fines recaudatorios, afirmó la secretaria, sino salvaguardar, dijo, la vida y la integridad de las personas usuarias, del personal conductor y de todas aquellas que transitan en su área de influencia. En este sentido, a partir del 16 de agosto de 2026, inició la aplicación de sanciones para quienes invaden el carril exclusivo del sistema, con multas que van de los 20 a los 30 UMAs. Durante el periodo que se informa, se han infraccionado un total de 67 personas con un monto equivalente a 157,208 pesos. Asimismo, la secretaria subrayó que, asumiendo la responsabilidad de la operación directa del sistema de transporte metropolitano, el estado a través del sistema integrado de transporte masivo, fortaleció su infraestructura para enfrentar este desafío, destacando la incorporación de 351 personas conductoras quienes recibieron una amplia capacitación en diversos temas para brindar un servicio a la altura de la exigencia de la población. En lo referente al sistema de transporte convencional, con el propósito de modernizar la gestión documental relacionada con las concesiones de transporte público y garantizar el resguardo adecuado de esta información, se destinó una inversión de 7.7 millones de pesos en la conversión de documentos físicos a formatos digitales y la implementación de una plataforma tecnológica para la consulta y localización electrónica de expedientes relacionados con las concesiones del transporte público convencional. La secretaria añadió que para la mejora del transporte público se realizaron diversas acciones, entre las que destacan 1,830 operativos de vigilancia y supervisión, el operativo Transporte Seguro y la aplicación de pruebas toxicológicas gratuitas. Además, la titular refirió que con una inversión de 9 millones y medio se realizó el censo del transporte del estado con el objetivo de generar información confiable y actualizada sobre las condiciones en que se presta el servicio en las vías públicas de la entidad. Por otra parte, expresó que para el ejercicio presupuestal 2026 se están llevando a cabo proyectos para contribuir a mejorar la seguridad en el sistema de transporte. La titular de la Semot concluyó que no se puede concebir una movilidad sin seguridad vial, razón por la cual es importante precisar que las acciones de los entes que realizan los entes públicos en esta materia serán insuficientes si no se incorpora la sociedad para fomentar una cultura vial. Es parte de la comparecencia de la secretaria Lyzbeth Robles Gutiérrez ante el Congreso del Estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1x5RVMwB0hjEH4GkQ-a5ndnTLOQGeWdCj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos informó que se pronostican lluvias fuertes, chubascos, así como un descenso en las temperaturas y vientos con rachas de hasta 50 km/h, afectando principalmente las regiones norte y este de Hidalgo. Debido a la acumulación previa de humedad en los suelos, las autoridades advirtieron sobre el riesgo latente de deslaves, derrumbes, inundaciones y crecidas de ríos. Ante este panorama, se emitieron diversas recomendaciones a la población, tales como evitar cruzar cuerpos de agua o calles inundadas, respetar los cierres carreteros y mantenerse informados ante cualquier señal de peligro.</t>
+  </si>
+  <si>
+    <t>Continuamos en Pachuca, son las 9:00 de la mañana con 2 minutos y le comento que comparte la Subsecretaría de Protección Civil y Gestión de Riesgos que se prevén lluvias fuertes en el norte y en el este del estado de Hidalgo. Persiste el riesgo de deslaves y derrumbes. Para este 22 de octubre el Servicio Meteorológico Nacional pronostica chubascos con lluvias puntuales fuertes de 25 a 50 mm, principalmente en las regiones norte y este del estado. Además, se prevén temperaturas mínimas de 0 a 5 °C, vientos de 10 a 20 km por hora con rachas de 30 a 50 km por hora. Las lluvias recientes han favorecido la acumulación de humedad en el suelo, por lo que podrían presentarse nuevos deslaves y derrumbes, desprendimientos de material, incluso cuando las precipitaciones disminuyan o cesen. También podrían registrarse escurrimientos, inundaciones e incrementos en los niveles de ríos y arroyos en zonas susceptibles. Y por supuesto, las autoridades recomiendan no cruzar ríos, arroyos, vados ni calles inundadas, ni a pie ni en vehículo; respetar los cierres carreteros, evitar transitar por caminos afectados por derrumbes, lodo o corrientes de agua y utilizar únicamente rutas confirmadas como seguras. Y por supuesto, si habitan en zonas susceptibles a inundaciones o deslizamientos, mantenerse atentos a las señales de peligro y atender las indicaciones de las autoridades, esto es fundamental, por supuesto.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JIza6SaujKIhMikRpYVNymZABP-YwsN-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>UPLAPH/Bol.161/2026</t>
+  </si>
+  <si>
+    <t>En su colaboración semanal, el especialista Gustavo Rosales compartió los pormenores del Epic Travers Hidalgo 2026, una exigente competencia multideportiva programada del 23 al 25 de octubre que contará con la participación de 150 atletas nacionales e internacionales. El recorrido constará de 230 kilómetros distribuidos en 9 municipios del estado (Mineral del Chico, Atotonilco el Grande, Actopan, Santiago de Anaya, Cardonal, Metztitlán, Ixmiquilpan, Tasquillo y Zimapán), e incluirá 30 km de trail, cañón, 35 km de ciclismo de montaña y 20 km de paddle board en aguas abiertas bajo condiciones de clima frío.</t>
+  </si>
+  <si>
+    <t>Justa Deportiva</t>
+  </si>
+  <si>
+    <t>¿Con qué nos seguimos, Gustavo?
+Seguimos con una carrera que a mí en lo particular me emociona bastante. Esto pues desarrollado, yo creo que se preveían otras condiciones climatológicas, sin embargo, parece ser que va a estar en medio de un frío arrollador, si lo podríamos denominar de esta manera, el Epic Travers Hidalgo 2026, en donde tendrá presencia en 9 municipios, 230 km de eh de aventura. La verdad es que sí va a estar supersupercomplicada esta competencia, desarrollarse del 23 al 25 de octubre, 150 atletas nacionales e internacionales, y tendrá presencia en los siguientes municipios: Mineral del Chico, Atotonilco el Grande, Axtopan, Santiago de Anaya, Cardonal, Metztitlán, Xmiquilpan, Tasquillo, perdón, y Zimapán. En donde, a ver, la la competencia se va a desarrollar de la siguiente forma: son 30 km de trail, recorrido en cañón y 35 km de ciclismo de montaña, además de 20 km de paddle board en aguas abiertas, lo cual, de verdad, estará muy muy exigente. Definitivamente, algo que destacar este Epic Travers Hidalgo, definitivamente una una competencia que va a estar muy interesante, sobre todo, como ya lo decía, muchas condiciones climatológicas. Esto me hace recordar, Juan Carlos, hace pues ya hace muchos muchos años cuando alguna empresa de televisión traía a nuestra entidad eh eh o el el Hidalgo Extreme Adventure y le ponían el el sufijo del año en el cual se iba a disputar. La verdad es que trajo en algún momento unos aviones impresionantes a lo que antes era llamado el Parque Venustiano y bueno, pues ahora con esta competencia Epic Travers Hidalgo, bueno, pues estará retomándose algo relativamente similar. Así que bueno, pues el inicio a las 6 de la mañana, a las 6 de la mañana, la verdad es que es muy temprano, así que bueno, pues todos pendientes, todos pendientes de esta competencia.
+Que por todo lo que nos comentas, hace honor a su nombre, será una competencia épica.
+Definitivamente, definitivamente. No sé si todavía haya eh algunos algunos lugares disponibles, pero bueno, va a ser emocionante, eso no hay duda alguna, Juan Carlos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HNafhPsQVnJUWhZnxMuBR2BGdJv50O7L/view?usp=drivesdk</t>
   </si>
 </sst>
 </file>
@@ -1596,8 +1409,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X47" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X47" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X33" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X33" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1993,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -2067,155 +1880,161 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C2" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S2" s="5">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="U2" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
+      <c r="W2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="S3" s="3">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -2224,324 +2043,322 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S4" s="3">
-        <v>238</v>
+        <v>122</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U4" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
+      <c r="W4" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q5" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="R5" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S5" s="3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S6" s="3">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S7" s="3">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="S8" s="3">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -2550,29 +2367,29 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>5</v>
@@ -2584,66 +2401,70 @@
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S9" s="3">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="W9" s="3" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="C10" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>23</v>
@@ -2652,162 +2473,164 @@
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q10" s="3" t="s">
+      <c r="S10" s="3">
+        <v>172</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S10" s="3">
-        <v>10</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="R11" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S11" s="3">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="S12" s="3">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -2816,715 +2639,691 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="C13" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S13" s="3">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U13" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
+      <c r="W13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S14" s="3">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
+      <c r="W14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="N15" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S15" s="3">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C16" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="S16" s="3">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U16" s="3"/>
-      <c r="V16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="W16" s="3" t="s">
-        <v>149</v>
-      </c>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
       <c r="X16" s="3"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="C17" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S17" s="3">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>154</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
       <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S18" s="3">
-        <v>233</v>
+        <v>61</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="C19" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S19" s="3">
-        <v>237</v>
+        <v>65</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="W19" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X19" s="3" t="s">
-        <v>167</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C20" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="S20" s="3">
-        <v>236</v>
+        <v>139</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X20" s="3"/>
+        <v>75</v>
+      </c>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="C21" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>174</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Q21" s="3"/>
       <c r="R21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S21" s="3">
-        <v>22</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U21" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X21" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C22" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S22" s="3">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C23" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>5</v>
@@ -3533,369 +3332,373 @@
         <v>15</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="S23" s="3">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U23" s="3"/>
-      <c r="V23" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C24" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S24" s="3">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="X24" s="3"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="C25" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="S25" s="3">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V25" s="3" t="s">
-        <v>193</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X25" s="3" t="s">
-        <v>167</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="X25" s="3"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="C26" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S26" s="3">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="S27" s="3">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="L28" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>201</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M28" s="3"/>
       <c r="N28" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="S28" s="3">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -3904,29 +3707,29 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>52</v>
@@ -3935,62 +3738,66 @@
         <v>23</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M29" s="3"/>
       <c r="N29" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S29" s="3">
-        <v>48</v>
+        <v>189</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U29" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
+      <c r="W29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>52</v>
@@ -3999,165 +3806,169 @@
         <v>15</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>58</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S30" s="3">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U30" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="U30" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
+      <c r="W30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X30" s="3" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="C31" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="S31" s="3">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="s">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>215</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>217</v>
+        <v>50</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S32" s="3">
+        <v>98</v>
+      </c>
+      <c r="T32" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S32" s="3">
-        <v>44</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -4166,1035 +3977,67 @@
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>18</v>
+        <v>209</v>
       </c>
       <c r="C33" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S33" s="3">
+        <v>134</v>
+      </c>
+      <c r="T33" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S33" s="3">
-        <v>32</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>18</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S34" s="3">
-        <v>599</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>16</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S35" s="3">
-        <v>413</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>15</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C36" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S36" s="3">
-        <v>131</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="W36" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="X36" s="3"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>14</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C37" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S37" s="3">
-        <v>50</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="X37" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>13</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S38" s="3">
-        <v>115</v>
-      </c>
-      <c r="T38" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="X38" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>12</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S39" s="3">
-        <v>82</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X39" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>11</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C40" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S40" s="3">
-        <v>142</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V40" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="W40" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X40" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>8</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C41" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S41" s="3">
-        <v>102</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>7</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C42" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S42" s="3">
-        <v>258</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="X42" s="3"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>6</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S43" s="3">
-        <v>274</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X43" s="3"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>5</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C44" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S44" s="3">
-        <v>391</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>4</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C45" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S45" s="3">
-        <v>175</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>3</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="S46" s="3">
-        <v>219</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>1</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C47" s="6">
-        <v>46316</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S47" s="3">
-        <v>311</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>276</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD60BAE9-5BB7-41F8-9CA0-CDF0939A26BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295D66AC-957B-49DA-BC1F-C320CE447CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="173">
   <si>
     <t>#</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Boletín</t>
   </si>
   <si>
-    <t>Semot</t>
-  </si>
-  <si>
     <t>NQ 90.1 FM</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>Daniel Martínez</t>
   </si>
   <si>
-    <t>Planeación</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
@@ -221,21 +215,6 @@
     <t>TV local</t>
   </si>
   <si>
-    <t>Radio Lobo 96.7 FM</t>
-  </si>
-  <si>
-    <t>Gina Lorenzo</t>
-  </si>
-  <si>
-    <t>Enlace Noticias</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/FN.37/2026</t>
-  </si>
-  <si>
-    <t>Apps de transporte</t>
-  </si>
-  <si>
     <t>Vacunación</t>
   </si>
   <si>
@@ -257,454 +236,380 @@
     <t>Ultra Noticias</t>
   </si>
   <si>
-    <t>Plan Nacional De Vivienda</t>
-  </si>
-  <si>
-    <t>Congreso</t>
-  </si>
-  <si>
     <t>Julio Menchaca</t>
   </si>
   <si>
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>SEPH/Bol.1940/2026</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>Jessenia Romero</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
-    <t>Precariedad laboral</t>
-  </si>
-  <si>
-    <t>Prevención De Enfermedades</t>
-  </si>
-  <si>
-    <t>Hidalgo consolida liderazgo en indicadores educativos a nivel nacional</t>
-  </si>
-  <si>
     <t>Congreso del Estado de Hidalgo</t>
   </si>
   <si>
-    <t>Lyzbeth Robles</t>
-  </si>
-  <si>
-    <t>Cultura</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/FN.38/2026</t>
-  </si>
-  <si>
-    <t>Para el Estado de Hidalgo se tiene considerada una meta de construcción de 66 mil 500 Viviendas del Bienestar, ubicadas en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo. Lo anterior fue señalado durante la reunión encabezada por la Presidenta de México, Claudia Sheinbaum Pardo, en Palacio Nacional, donde se evaluaron los avances de dicho programa, en donde participó el Gobernador de Hidalgo, Julio Menchaca Salazar, junto con alcaldesas y alcaldes donde actualmente se construyen las viviendas. En la reunión se estableció la posibilidad de incorporar más municipios de Hidalgo al Programa Nacional de Vivienda para el Bienestar, para lo cual se está realizando la evaluación de terrenos, condiciones legales, entre otros temas. De acuerdo al Gobierno Federal, cada vivienda tiene un costo promedio de construcción de 600 mil pesos y están a cargo del Instituto del Fondo Nacional de la Vivienda para los Trabajadores (Infonavit) y la Comisión Nacional de Vivienda (Conavi). Del total de hogares, 11 mil 500 serán edificados por el Infonavit y 20 mil por la Conavi, de acuerdo a lo establecido previamente. Como parte de esta estrategia nacional, que contempla la construcción de 1.8 millones de viviendas, incluyendo al Estado de Hidalgo, con el objetivo de ampliar el acceso de las familias a una vivienda digna. Actualmente están en construcción 5 mil 990 viviendas nuevas en los municipios del Estado de Hidalgo ya señalados. Cabe señalar que los municipios donde se asientan las viviendas deben facilitar el acceso a servicios como agua potable, drenaje y electricidad, además de atender los trámites catastrales, avalúos y escrituración de las casas y departamentos. El Gobernador Menchaca Salazar acompañó a la mandataria nacional en un encuentro para revisar los avances del proceso de modernización del IMSS-Bienestar, junto a 23 gobernadoras y gobernadores que están integrados al sistema de atención a la salud.</t>
-  </si>
-  <si>
-    <t>CDMX</t>
-  </si>
-  <si>
-    <t>Ayer hubo reunión en Palacio Nacional con el gobernador Julio Mechaca Salazar, con alcaldesas y alcaldes de municipios donde están construyendo viviendas del bienestar, Izza. Es correcto, Daniel. Para el Estado de Hidalgo se tiene considerada una meta de construcción de 66.500 viviendas del bienestar. Estas ubicadas en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo. Todo esto fue señalado durante la reunión encabezada por la Presidenta de México, Claudia Sheinbaum Pardo, en Palacio Nacional, donde se evaluaron los avances de dicho programa, en donde participó el gobernador de Hidalgo, Julio Menchaca Salazar, junto con alcaldesas y también alcaldes, donde actualmente se construyen viviendas. Y pues en la reunión se estableció la posibilidad de incorporar más municipios de Hidalgo al Programa Nacional de Vivienda y Bienestar, para lo cual se está realizando la evaluación de terrenos, condiciones legales, entre otros temas. Y de acuerdo con el gobierno federal, cada vivienda tiene un costo promedio de construcción de 600 mil pesos y están a cargo del Instituto del Fondo Nacional de Vivienda para los Trabajadores y también la Comisión Nacional de Vivienda. Pues el total de hogares, 11.500 serían edificados por el Infonavit y 20.000 por la Conavi, de acuerdo con lo establecido previamente. Y como parte de la estrategia nacional que contempla la construcción de 1.8 millones de viviendas, incluyendo al Estado de Hidalgo, con el objetivo de ampliar el acceso a las familias a una vivienda digna. Actualmente están en construcción 5.990 viviendas nuevas en los municipios del estado de Hidalgo Que ya mencionamos y cabe señalar que los municipios donde se asientan las viviendas Deben facilitar el acceso a servicios como agua potable, drenaje, electricidad Además también de atender los trámites catastrales, avalúos y también escrituración de estas casas y departamentos</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1vmOTaE-tpY9v_DIvopciX2BUjPhXyjLA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum</t>
-  </si>
-  <si>
-    <t>Radioescucha: es increíble que sabiendo el nefasto servicio que tiene el transporte público, con autos ya de 20 años, con vidrios polarizados, sucios y a veces sin cinturón de seguridad, muchos taxistas sin tarjetón o licencia, no permitan la entrada de plataformas.</t>
-  </si>
-  <si>
-    <t>Dicen por acá, es increíble que sabiendo el nefasto servicio que tiene el transporte público, con autos ya de 20 años, con vidrios polarizados, sucios y a veces sin cinturón de seguridad, muchos taxistas sin tarjetón o licencia, no permitan la entrada de plataformas.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Z_OMH-4ikeP_uQxCelO5e1O3ptTniLBU/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte en Hidalgo (Semoth) considera la implementación de un sistema integral de trámites y gestión de la información para transporte convencional. Lo anterior fue informado por Lyzbeth Robles Gutiérrez, titular de la dependencia estatal durante su comparecencia ante el Congreso de Hidalgo, realizada el miércoles 21 de octubre. Señaló que también está considerada la modernización tecnológica del servicio y la adquisición de equipo especializado para la inspección vehicular. También se considera un sistema para aplicar pruebas psicométricas a personas conductoras, un estudio de impacto vial en el bulevar Luis Donaldo Colosio, dentro de la Zona Metropolitana de Pachuca, junto con el equipamiento de una unidad móvil para realizar pruebas toxicológicas. La funcionaria señaló que también está considerada la elaboración de los planes de movilidad urbana sustentable de Ixmiquilpan y Huejutla, así como en el Plan Estratégico de Seguridad Vial para el Estado de Hidalgo. Robles Gutiérrez informó que en transporte público convencional, la Semoth desde el año 2022, ha realizado mil 830 operativos de vigilancia y supervisión. Asimismo, explicó que el gobierno estatal destinó 9 millones 500 mil pesos al censo de transporte en Hidalgo. El censo permitió identificar mil 272 rutas de transporte colectivo y 633 sitios de transporte individual. En cuanto al Sistema de Transporte Metropolitano, conocido como Tuzobús, se destacó que se registró un incremento de 24 por ciento de viajes, tras la renovación de unidades. Con la modernización de la flota vehicular, el número de personas usuarias pasó de 75 mil a casi 93 mil, tanto en la ruta troncal como en las alimentadoras. De acuerdo con la funcionaria, el sistema registra una eficiencia operativa de 99 por ciento y una disminución de 56 por ciento en las quejas. La Semoth desarrolla proyectos de renovación de la red semafórica, elaboración de dictámenes estructurales de los puentes a cargo del sistema, mantenimiento y rehabilitación integral de las estaciones del Sistema de Transporte Metropolitano.</t>
-  </si>
-  <si>
-    <t>En otros temas que tocó Lizbeth Robles, la titular de la Secretaría de Movilidad y Transporte del Estado de Hidalgo, en temas generales, señaló que en breve se está considerando la implementación de un sistema integral de trámites y gestión de la información para el transporte convencional. Esto durante la comparecencia que ofreció el día de ayer, señaló que también está considerada la modernización tecnológica del servicio y la adquisición de equipo especializado para inspección vehicular. También se considera un sistema para aplicar pruebas psicométricas a personas conductoras, un estudio de impacto vial en el bulevar Luis Donaldo Colosio, esto último de dentro de la zona metropolitana de Pachuca, junto con el equipamiento de una unidad móvil para realizar pruebas tecnológicas. La funcionaria señaló que también está considerada la elaboración de los de los planes de movilidad urbana sustentable en Ixmiquilpan y Huejutla, así como en el plan estratégico de seguridad vial para el Estado de Hidalgo. Robles Gutiérrez informó que en transporte público convencional, la Secretaría de Movilidad y Transporte de Hidalgo desde el año 2022 ha realizado 1,830 operativos de vigilancia y supervisión, ¿que para qué han servido? Uno se pregunta. También explicó que el Gobierno estatal destinó 9,500,000 pesos al censo de transporte en Hidalgo, el censo permitió identificar 1,272 rutas de transporte colectivo dentro de la entidad y 633 sitios de transporte individual. ¿Y para qué ha servido esa información o para qué va a servir, no? En cuanto al sistema de transporte metropolitano conocido como Tuzobús, se destacó que se registró un incremento del 24% de viajes tras la renovación de las unidades. Con la modernización de la flota vehicular, el número de personas usuarias pasó de 75,000 a casi 93,000, tanto en la ruta troncal como en las alimentadoras, y de acuerdo con la funcionaria, el sistema registra una eficiencia operativa del 99% y una disminución del 56% en las quejas. La Secretaría de Movilidad y Transporte desarrolla proyectos de renovación de la red semafórica ahí en el Tuzobús, elaboración de dictámenes estructurales de los puentes a cargo del sistema, mantenimiento y rehabilitación integral de las estaciones de este sistema de transporte metropolitano.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1c_ygxMXSfOWRz7CJMFBVG4Rvd2swpyok/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Radioescucha: ojalá que entren las plataformas porque el servicio que se ofrece actualmente en taxis es muy deficiente, hay operadores que son muy despotados.</t>
-  </si>
-  <si>
-    <t>Por acá nos están comentando en este momento, ojalá que entren las plataformas porque el servicio que se ofrece actualmente en taxis es muy deficiente, hay operadores que son muy despotados.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1r21yQrrOgVzDKRK4tu8h0qaJRpS0ezuS/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Daniel Martínez hablando sobre la llega de plataformas de transporte a Hidalgo comenta: me quedo también con las palabras de Andrés Velázquez Vázquez, presidente de la Junta de Gobierno del Congreso del Estado de Hidalgo. Al final de cuentas, la tecnología ya llegó. Más adelante señala que no se debe satanizar un servicio, sino adecuarlo a las necesidades.</t>
-  </si>
-  <si>
-    <t>Ahora, me quedo también con las palabras de Andrés Velázquez Vázquez, presidente de la Junta de Gobierno del Congreso del Estado de Hidalgo. Al final de cuentas, la tecnología ya llegó.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JblBusZuw-4fXLui-Adz5HOFoS5z6Fb7/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Nuevamente, por acá nos están mandando mensajes de que consideran que el tema de no permitir las plataformas, además de que no les permite tener otras opciones a quien busca otros servicios que no sean los taxis ordinarios, le está cerrando las puertas a quien quiere llevarse una lanita, un ingreso extra. Ese es el pensamiento o el punto de vista que nos están compartiendo por acá por WhatsApp.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1IyvhCjIq94L_r_-Q-lgrzBsh7T4vW5eP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Didi en Tula comenzó a promocionarse mediante una convocatoria dirigida a personas con automóvil propio que estén interesadas en registrarse como socios conductores. La publicidad difundida anuncia la llegada de la plataforma Tula, ahí ofrece como promoción una ganancia garantizada superior superior a 10,000 pesos durante la primera semana de lanzamiento, sujeta a las condiciones establecidas por la empresa. La convocatoria aparece apenas unos días después de que Uber habilitara la posibilidad de solicitar viajes en Pachuca, y esta convocatoria ha sido difundida para Tula de Allende y estaría dirigida a propietarios de vehículos. Entre los principales atractivos promocionales se encuentra la comisión del 9%, horarios flexibles, demanda de viajes y más de 20 funciones de seguridad. La publicidad también ofrece una ganancia garantizada de 10,000 pesos durante la primera semana de lanzamiento y al tratarse de una promoción comercial, el acceso a este beneficio puede estar sujeto a términos y condiciones. Entre los requisitos anunciados para registrarse se encuentran el INE, la licencia de conducir, tarjeta de circulación, una fotografía tomada mediante la aplicación. La empresa también habilitó un número de WhatsApp para poder brindar asesoría a las personas que estén interesadas en registrarse. El día lunes Uber habilitó dentro de su aplicación la posibilidad de consultar y solicitar viajes en Pachuca y como ya lo mencionabas Daniel, el Gobierno del Estado de Hidalgo ha fijado su posicionamiento y ha sostenido que el modelo bajo el cual estas plataformas pretenden prestar el servicio no estaría contemplado actualmente como una modalidad autorizada por la legislación estatal.</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>En Tula, pues resulta que incluso están buscando operadores para otra de estas empresas, es decir, siguen adelante. Sí, de hecho en medio de toda esta controversia que ha habido con la llegada de plataformas digitales de transporte, ahora Didi en Tula comenzó a promocionarse mediante una convocatoria dirigida a personas con automóvil propio que estén interesadas en registrarse como socios conductores. La publicidad difundida anuncia la llegada de la plataforma Tula y ofrece como promoción una ganancia garantizada superior a 10 mil pesos durante la primera semana de lanzamiento, sujeta a las condiciones establecidas por la empresa. La convocatoria aparece apenas unos días después de que Uber habilitará la posibilidad de solicitar viajes en Pachuca Y esta convocatoria ha sido difundida para Tula de Allende y estaría dirigida a propietarios de vehículos Entre los principales atractivos promocionales se encuentra la comisión de 9%, horarios flexibles, demanda de viajes y más de 20 funciones de seguridad La publicidad también ofrece una ganancia garantizada de 10 mil pesos durante la primera semana de lanzamiento y al tratarse de una promoción comercial, el acceso a este beneficio puede estar sujeto a términos y condiciones. Entre los requisitos anunciados para registrarse se encuentran el INE, la licencia de conducir, tarjeta de circulación, una fotografía tomada mediante la aplicación. La empresa también habilitó un número de WhatsApp para poder brindar asesoría a las personas que estén interesadas en registrarse. El día lunes, Uber habilitó dentro de su aplicación la posibilidad de consultar y solicitar viajes en Pachuca y como ya lo mencionaba Daniel, el gobierno del estado de Hidalgo ha fijado su posicionamiento y ha sostenido que el modelo bajo el cual estas plataformas pretenden prestar el servicio no estaría contemplado actualmente como una modalidad autorizada por la legislación estatal.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1sVvhxcGaD--jIQj7A2l6toXC-JIuXId1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Entre septiembre del año pasado y el mismo mes de este 2026, la Secretaría de Movilidad y Transporte en Hidalgo (Semoth) ha detectado 129 vehículos que realizaban servicio de transporte para pasajeros por medio de plataformas digitales. El dato fue ofrecido por la titular de la dependencia estatal, Lyzbeth Robles Gutiérrez, durante su comparecencia ante el Congreso de Hidalgo, realizada el miércoles 21 de octubre. La funcionaria agregó que se aplicaron 50 sanciones por prestar el servicio sin contar con la autorización, lo que significó una recaudación por 4 millones 399 mil 125 pesos. En el Estado de Hidalgo se han detectado varias empresas que prestan el servicio, pese a que las actuales normativas en materia de transporte para pasajeros no las tiene contempladas, y por tanto, no están autorizadas para operar. La detección de las 129 unidades particulares que fueron remitidas al corralón, han sido detectadas en varios municipios de la entidad. En cuanto a las sanciones, en Pachuca se han aplicado 26; seguido de Mineral de la Reforma, 11; Tizayuca, 4; Ixmiquilpan, 3; Villa de Tezontepec, 2; así como uno en Tepeapulco, otro en Zempoala y otro en Tolcayuca. No fueron precisados más municipios. La titular de Semoth recordó que con anterioridad Uber promovió diversos juicios de amparo para obtener autorización y así operar en la entidad, pero no consiguió resoluciones favorables; asimismo, aseguró que no hay juicios de garantía vigentes. Respecto al anuncio del gobernador Julio Menchaca Salazar sobre la presentación de denuncias por los viajes que oferta Uber, la secretaria señaló que se trata de una estrategia del Poder Ejecutivo en la que también participa la dependencia a su cargo. Puntualizó que las acciones podrían ocurrir en dos sentidos, tanto en el ámbito administrativo como en la vía penal..</t>
-  </si>
-  <si>
-    <t>El día de ayer fue la comparecencia de Lisbeth Robles al frente de la Secretaría de Movilidad y Transporte del Estado de Hidalgo, donde uno de los temas, y no lo soltamos, Izza, no lo vamos a soltar tampoco, ha sido el asunto de los servicios de transporte por aplicación, en el que se insiste, por lo menos por el momento, a Hidalgo no entran y me sorprendió la cantidad de vehículos que han sido asegurados de septiembre del año pasado a la fecha, porque señalan, no es una ni dos, son varias compañías que están ofreciendo servicio por aplicación en Hidalgo. **Izza Hernández:** Es correcto, entre septiembre del año pasado y el mismo mes de este 2026, resulta que la Secretaría de Movilidad y Transporte de Hidalgo ha detectado 129 vehículos que realizaban servicio de transporte para pasajeros por medio de plataformas digitales. Ese dato fue ofrecido por la titular de la dependencia estatal, Lisbeth Robles Gutiérrez, durante la comparecencia ante el Congreso de Hidalgo, que se realizó este miércoles 21 de octubre. De hecho, la funcionaria agregó que se aplicaron 50 sanciones para poder prestar el servicio sin contar con la autorización, lo que significó, de hecho, una reducción de 4,399,125 pesos. En el estado de Hidalgo se han detectado varias empresas que prestan el servicio, pese a que las actuales normativas en materia de transporte para pasajeros no las tienen contempladas y, por tanto, pues no están autorizadas para operar. Pero sí, la detección de las 129 unidades particulares que fueron remitidas al corralón han sido detectadas en varios municipios de la entidad. De hecho, en cuanto a las sanciones en Pachuca se han aplicado 26, seguido de Mineral de la Reforma con 11, Tizayuca con 4, e Ixmiquilpan con 3, Villa de Tezontepec con 2, así como también uno en Tepeapulco, otro en Zempoala y otro en Tolcayuca. De hecho, no precisaron como tal los municipios, pero la titular de la SEMOT, perdón, recordó que con anterioridad Uber pues promovió diversos juicios de amparo para poder obtener autorización y así operar en la entidad, pero no consiguió resoluciones favorables. Asimismo, aseguró que no hay juicios de garantía vigentes. Pero bien, respecto al anuncio del gobernador Julio Menchaca Salazar sobre la prestación de la presentación de denuncias por los viajes de oferta de Uber, pues la secretaria señaló que se trata de una estrategia del Poder Ejecutivo en la que también participa la dependencia a su cargo, pero sí puntualizó que las acciones podrían pues ocurrir en dos sentidos, tanto en el ámbito administrativo como también en la vía penal. Entonces, pues de esta manera es como pues detectó SEMOT 129 vehículos ofreciendo servicios por plataforma digital de manera</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VYjbeXHDIU-MyEfK9nYolgFPRh8gA0Bw/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Saderh/Bol.87/2026</t>
-  </si>
-  <si>
-    <t>Impulsa Saderh transformación integral de la región Otomí-Tepehua y Valle de Tulancingo</t>
-  </si>
-  <si>
     <t>Saderh</t>
   </si>
   <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>Valle de Tulancingo</t>
-  </si>
-  <si>
-    <t>Entregas que se hicieron en la Sierra Otomí- Tepehua para productores agrícolas. Esto por parte, obviamente, de la Secretaría de Desarrollo Agropecuario del Estado de Hidalgo. Es correcto, Daniel. Resulta que en el marco de las estrategias para dinamizar las actividades productivas y consolidar la soberanía alimentaria en la región, el gobierno de Hidalgo encabezado por Julio Menchaca a través de la Secretaría de Agricultura y Desarrollo Rural del Estado de Hidalgo (Saderh) llevó a cabo una entrega de apoyos por un monto total de 7 millones 900 mil 571.71 pesos en beneficio directo de 585 productoras y productores rurales. Agua Blanca de Iturbide, Hidalgo.- El evento, encabezado por el titular de la Saderh, Napoleón González Pérez fue relizado en el municipio de Agua Blanca en donde se extendieron las entregas a los municipios de Santiago Tulantepec, Tulancingo, Acaxochitlán, Metepec, Cuautepec, Acatlán, Singuilucan, Tepeapulco, Apan, Mineral del Chico y Huasca de Ocampo. Durante la jornada se realizó la entrega de semilla de maíz, cebada y jitomate; así como vientres porcinos y ovinos, además de rollos de alambre, molinos picadora, hijuelos de maguey, plantas de manzana gala, limón persa, café Sarchimor, nogal cáscara de papel, equipamiento acuícola, crías de peces (tilapia y carpa) y certificados de sanidad acuícola. Durante el evento el titular de Agricultura en el estado resaltó que cada beneficiario recibirá directamente el programa que solicitó, asegurando que los recursos lleguen sin recortes ni intermediación. El funcionario insistió en que para acceder a estos esquemas no se requiere pertenecer a ninguna agrupación ni contar con la gestión de ningún líder, garantizando con ello un proceso ágil, transparente y accesible donde es fundamental acreditar la condición de trabajador o trabajadora del campo. Con esta medida, el gobierno del estado reafirma su compromiso de dignificar la labor campesina, impulsando a quienes trabajan la tierra día con día y asegurando que cada apoyo se traduzca en bienestar directo y desarrollo productivo para las comunidades hidalguenses. Estas acciones reafirman el compromiso de garantizar que el campo hidalguense cuente con mejores condiciones para producir, crecer y construir un futuro con mayores oportunidades, asegurando que cada apoyo y proyecto se traduzca en bienestar y prosperidad para las familias rurales de la entidad.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1DkelJlYSpKieIF32-AkoKKk7L9YnvLS-/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Napoleón González Pérez</t>
   </si>
   <si>
-    <t>Debido a que desde la temporada de verano de este año se registraron casos de Covid-19 en la región Tulancingo, se espera repunte de casos por influenza estacional durante la temporada invernal. La información fue presentada durante la reunión mensual del Comité Jurisdiccional de Vigilancia Epidemiológica, por lo cual se hizo llamado para aplicarse la vacuna para ambos padecimientos, las cuales ya están disponibles. Durante la sesión de trabajo realizada este miércoles 21 de octubre, se señaló que también se espera durante la temporada invernal, incremento de casos de otras enfermedades broncorespiratorias, como influenza H1N1 y tipo B. Se tiene especial preocupación en la incidencia de virus sincitial respiratorio, una de las principales causas de muerte en niñas y niños de cinco años de edad, por las complicaciones que pueden presentar en su estado de salud. Las autoridades sanitarias han detectado que el grupo entre los 24 a 39 años de edad es donde se presenta el mayor porcentaje de personas que enferman de padecimientos broncorespiratorios. Una de las principales causas de dicha incidencia es debido a que dicho grupo de edad rechaza vacunarse, una de las principales estrategias para evitar este tipo de enfermedades o aminorar sus efectos. En cuanto a fallecimientos por este tipo de padecimientos, en la región correspondiente a la Jurisdicción Sanitaria Regional II, los municipios con mayor registro son Acaxochitlán, Metepec, Santiago Tulantepec, Tulancingo y Tenango de Doria. En el caso de Covid-19, los fallecimientos se han registrado sobre todo en personas con antecedentes de diabetes, hipertensión, obesidad y asma. Mientras que en los fallecimientos por influenza, se registran sobre todo en personas con antecedentes también de diabetes, así como de Enfermedad Pulmonar Obstructiva Crónica y enfermedades renales agudas. Se insistió en reforzar los esquemas de información preventiva a los padecimientos broncorespiratorios, así como la estrategia de vacunación, señalando que existen dosis suficientes para atender a la población. En el caso de la vacunación, adultos mayores, mujeres embarazadas, así como niñas y niños, junto con personas con enfermedades crónico degenerativas, son quienes serán atendidas prioritariamente para ser vacunadas.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1aw0dGI007LNIdLa4g_G7j3i1wDBVM2wr/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Andrés Torres en respuesta a una radioescucha que pregunta por qué no se pasan imágenes en las noticias, argumentando que esto haría el noticiero más completo. Andrés Torres se disculpa y explica que el formato del noticiero ha cambiado a lo largo de los años, ya que llevan 13 años funcionando. Mencionan que hay carencias en Radio y Televisión de Hidalgo que hacen difícil realizar un noticiero de televisión. Actualmente, están haciendo un programa de radio con apoyo visual y desde Pachuca, tienen un equipo muy pequeño, conformado por un camarógrafo, dos conductores y un operador de radio. Explica que la falta de recursos y personal limita sus capacidades. Para crear un noticiero formal, se requiere un equipo grande y completo, algo que ellos no pueden ofrecer debido a su situación. Además, la financiación del proyecto es personal, ya que no reciben apoyo económico para tener imágenes y presentar un formato de noticiero de televisión. El informativo se nutre principalmente de un estilo de radio. También menciona que su programa comenzó con un enfoque de opiniones y no como un noticiero, aunque ahora brinda noticias. Está orgulloso de lo que han logrado con el esfuerzo de sus compañeros y de las personas que apoyan el proyecto. Sin embargo, enfatiza la difícil situación en la que trabajan, con recursos muy limitados. Agradecen a colaboradores que, de forma altruista, contribuyen con información sin recibir pago alguno. Todos los gastos del programa, como transporte y materiales, son cubiertos por ellos mismos. Lamenta los inconvenientes causados por la falta de recursos y reafirma su compromiso de ofrecer la mejor información política y social posible, a pesar de las limitaciones. Se despide disculpándose nuevamente y reafirmando su dedicación al informativo.</t>
-  </si>
-  <si>
-    <t>Nos escribe la terminación 1984, muy buenos días a todos los que participan en Vocales Radio Muchas gracias, buen día Una pregunta, ¿por qué no pasan imágenes de las noticias? Estaría más completo su noticiero, muchas gracias Si, pues es que mira, tenemos un pequeño problema y me disculpo con todo el auditorio El formato de este noticiero se vino modificando a través de muchos, muchos años Prácticamente tenemos ya 13 años con esta informativo, que nació siendo eso, un informativo, un programa de opinión con información debido a las carencias que existen en radio y televisión desde hace décadas pues es prácticamente imposible que podamos hacer un noticiero con los formatos de televisión nosotros estamos haciendo un programa de radio con el apoyo visual, con el apoyo de algunas cámaras y te puedo decir, somos muy poquitos para hacer un programa de televisión como un noticiero formal se necesita un equipo muy grande Un equipo muy importante Nosotros somos apenas 3 personas Un camarógrafo, 2 conductores Y por supuesto nuestro operador de radio Que al mismo tiempo Tiene al aire 3 estaciones Está checando nuestra señal Para Huejutla FM Para Radio Tlanchinol Y estamos apoyando también La señal de Ixmiquilpan Desde aquí, desde Pachuca Entonces estamos de verdad Saturados de trabajo No tenemos ni equipo, capacidad técnica y tampoco capacidad económica Porque además déjame decirte, tendría que ser inversión personal propia Como lo es todo este programa Para tener imágenes y ofrecerle a nuestro auditorio Este formato de noticiero de televisión Somos un noticiero de radio muy muy muy peque Porque bueno pues este formato A mí no me gusta la palabra orgánico pero se ha dado as se ha derivado en un noticiero por cuestiones, pues obviamente del perfil informativo que tengo como profesional, pero el objetivo, si tú revisas, y algún día si gustas te puedo mostrar el proyecto de las vocales radio original, era un programa de opinión, era un programa donde se iban a tratar tres temas desde el punto de vista de la opinión, es un género periodístico y algo noticioso. Hoy estamos haciendo un noticiero, del cual me siento muy orgulloso, sobre todo el trabajo de mis compañeros, del apoyo de mucha gente que se suma a este proyecto, pero es la condición, Estamos trabajando en condiciones De verdad Al límite De los recursos Que tenemos a la mano Todos nuestros colaboradores Alberto González, Milton Cortés Toda la gente que usted Escucha, la que contactamos Por lo regular vía telefónica Son compañeros que de manera altruista Así lo digo, de buena voluntad Como buenos samaritanos Nos apoyan con información no hay ningún pago, no hay ninguna retribución, si nosotros tenemos que trasladarnos a alguna región del estado, si tenemos que hacer alguna cobertura, pues corre por nuestra cuenta todos los gastos, no tenemos grabadoras, no tenemos plumas, no tenemos pilas, no nos dan ningún tipo de apoyo para realizar los trabajos, no es una cámara, un vehículo, gasolina, nada de eso existe aquí, todo lo hacemos a nuestra cuenta, Entonces ofrezco una disculpa porque hacemos lo humanamente posible Por llevarles a usted lo último y lo más importante en la información política</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1WYPyqZ1aC4XRTSc10jABQkERXdjsCF9w/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Menchaca y Sheinbaum suman esfuerzos para impulsar el programa Vivienda para el Bienestar en Hidalgo</t>
-  </si>
-  <si>
-    <t>También el gobernador participó en una reunión que fue encabezada por la presidenta Claudia Simo Pardo en el Palacio Nacional. El gobernador se reunió a esta reunión donde se evaluaron los avances del programa de vivienda para el bienestar y se acordó fortalecer la coordinación entre los tres órdenes de gobierno para agilizar su implementación. Como parte de esta estrategia Nacional que contempla la construcción de 1.8 millones de viviendas para el Estado de Hidalgo, se proyectan 66.500 en estos municipios que estarán ubicadas, Aldo, en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo de Bravo, todo esto con el objetivo de ampliar el acceso de las familias hidalguenses a una vivienda digna. Además, el gobernador Julio Menchaca Salazar acompañó a la presidenta de nuestra nación en el encuentro para revisar los avances del proceso de modernización del IS-Bienestar, esto junto a otros 23 gobernadores y gobernadoras de nuestro país. Así que ayer el gobernador también estuvo presente en esta reunión nacional para evaluar estos dos temas fundamentales. El tema de la vivienda del bienestar y el tema del Instituto Mexicano del Seguro Social, hoy IMSS-Bienestar. Y bueno, son dos asuntos que son muy importantes no solo para el Estado de Hidalgo, sino para nuestra nación. Así es, dicho técnicamente el gobernador. Regresamos los avances junto con la presidenta Claudia Ocema de la modernización del IMSS-Bienestar. En Hidalgo trabajamos para que más familias tengan acceso de servicios médicos de calidad.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HGeRJbajAY0gJBbiyww2dQMFadHXEsgs/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1331/2026</t>
-  </si>
-  <si>
-    <t>El gobernador de nuestro estado, Julio Menchaca Salazar, asistió a este evento denominado Congreso Nacional de la Moda y el Vestido 2026. Con la convicción de respaldar a todos los sectores económicos, el gobernador Julio Menchaca Salazar inauguró el Congreso de Moda y Vestido 2026, que por primera vez se lleva a cabo en nuestro estado y que es un bastión de la industria textil. Hidalgo tiene una historia ligada desde la fabricación de hilo hasta la confección de prendas. Asumo el compromiso de acompañar esta importante actividad que desarrollan y se genere en un bienestar compartido. El mandatario estatal reconoció el trabajo del sector empresarial que en sinergia con la administración estatal elevó los índices del estado en la actividad económica. En este evento también estuvo presente José Pablo Maauad, presidente de la Cámara Nacional de la Industria del Vestido, y otros representantes de la Cámara Nacional de la Industria Textil, como Rafael Torres y también Juan Porras Manrilla, tesorero de la Confederación de Cámaras Industriales de los Estados Unidos Mexicanos y, bueno, pues en el evento se destacó el crecimiento del sector textil en nuestro estado. El gobernador de Hidalgo también, pues destacó, como lo escuchan ustedes, la tradición que tiene desde muchos, muchos, hace muchos años nuestro estado en el tema textil, sobre todo en regiones muy identificadas, como usted lo sabe, la zona de Tulancingo, la zona de Cuautepec, son por antonomasia zonas textileras en nuestro estado. Aldo Falcón: también comenta el gobernador Julio Menchaca, Hidalgo es el quinto productor nacional de prendas de vestir. En el Congreso Nacional de Moda y Vestido reconocemos a quienes hacen posible esta actividad que generan empleos e ingresos para las familias hidalguenses.</t>
-  </si>
-  <si>
     <t>Reunión con Empresarios</t>
   </si>
   <si>
-    <t>El gobernador de nuestro estado, Julio Menchaca Salazar, asistió a este evento denominado Congreso Nacional de la Moda y el Vestido 2026. Con la convicción de respaldar a todos los sectores económicos, el gobernador Julio Menchaca Salazar inauguró el Congreso de Moda y Vestido 2026, Que por primera vez se lleva a cabo en nuestro estado y que es un bastión de la industria textil Hidalgo tiene una historia ligada desde la fabricación de hilo hasta la confección de prendas Asumo el compromiso de acompañar esta importante actividad que desarrollan y se genere en un bienestar compartido El mandatario estatal reconoció el trabajo del sector empresarial que en sinergia con la administración estatal elevó los índices del Estado en la actividad económica. En este evento también estuvo presente José Pablo Maguad, presidente de la Cámara Nacional de Industria del Vestido y otros representantes de la Cámara Nacional de la Industria Textil como Rafael Torres y también Juan Porras Brambila, tesorero de la Confederación de las Cámaras Industriales de los Estados Unidos Mexicanos y bueno pues en el evento se destacó el crecimiento del sector textil en nuestro estado ¿Qué le parece si escuchamos las palabras del gobernador Julio Menchaca en la inauguración de este Congreso Nacional de Moda y Vestido 2026? Aldo, por favor. El gobernador de Hidalgo también destacó, como lo escuchan ustedes, la tradición que tiene. Desde hace muchos años nuestro estado en el tema textil, sobre todo en regiones muy identificadas, como usted lo sabe, la zona de Tulancingo, la zona de Cuautepec, son por autonomía zonas textileras en nuestro estado. Así es dicho también comenta el gobernador Julio Menchaca. Hidalgo es el quinto productor nacional de prendas de vestir. En el Congreso Nacional de Moda y Vestido reconocemos a quienes hacen posible esta actividad que genera empleos e ingresos para las familias hidalguenses. Muy bien, esto como parte de las actividades del gobernador Julio Menchaca ayer en esta capital hidalguense.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bGsTxWGiA-OPZo1vHSQTVL76jnhLxRmu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>José Pablo Maauad Pontón, Juan Porras Brambila, Guillermo Austreberto Vera Rodríguez</t>
-  </si>
-  <si>
-    <t>Hoy es un día muy importante porque por primera vez en la historia, un Oficial Mayor comparecerá ante el Congreso. Esto forma parte de una tradición que inició el ex gobernador Jesús Murillo Canan en los años 90, donde los miembros del gabinete del gobernador presentan sus informes ante los diputados. El gobernador Julio Menchaca Salazar presentó su cuarto informe de actividades en septiembre, el cual incluye los logros y metas de su equipo. Este proceso de comparecencias siempre ha generado diversas opiniones entre los diputados y la población, ya que a algunos les interesa y a otros no. Sin embargo, la comparecencia de hoy se destaca porque busca mejorar la transparencia y la rendición de cuentas. Orlando Ángeles, el Oficial Mayor, comparecerá a las 4 de la tarde, y es una oportunidad para que se expliquen los detalles sobre el gasto y la aplicación de recursos del gobierno. Este evento resalta la intención de las autoridades de resolver dudas y proporcionar claridad sobre el uso del dinero público. Se espera que esto contribuya a un mejor entendimiento de las responsabilidades del gobierno y fomente el diálogo entre autoridades y representantes populares. Mañana se discutirá en este espacio qué resultados dejó la comparecencia de Orlando Ángeles.</t>
-  </si>
-  <si>
     <t>Oficialía Mayor</t>
   </si>
   <si>
-    <t>Hoy es un día muy importante, tenemos en esta agenda de las comparecencias de los integrantes del gabinete del gobernador Julio Menchaca Salazar por primera vez en la historia la comparecencia de un oficial mayor. Como yo les he platicado, recordarán ustedes, si no se los cuento, desde allá, desde los lejanos años 90, el ex gobernador Jesús Murillo Canan implementó esta modalidad de comparecencias parte de los secretarios de los integrantes del gabinete en la glosa de los informes de los gobernadores el mandatario estatal Julio Menchaca Salazar presentó en días pasados en septiembre su cuarto informe de actividades las logros, las metas todos los temas que incluyen el trabajo del gobernador y de su equipo están contenidos en ese informe, fueron contenidos en ese informe y como es tradición, las y los diputados, los integrantes de la legislatura local convocan a cada uno de estos secretarios y secretarias para que se presenten ante el pleno del Congreso y hablen a detalle sobre los temas de su responsabilidad sobre los temas que tienen que ver con la secretar que dirigen As se ha hecho durante muchos a y bueno pues el tema de las comparecencias a algunos los deja satisfechos, a otros no, a algunos les interesa, a otros no. Bueno, ha sido un tema del cual se ha opinado muchísimo, pero por primera vez en la historia y con el propósito de abonar, de fortalecer la cultura de la transparencia y de la información y sobre todo de la rendición de cuentas, puntual rendición de cuentas, hoy comparecerá por primera vez en el Congreso del Estado un oficial mayor, en este caso Orlando Ángeles, la comparecencia será a las 4 de la tarde y me parece algo que hay que destacar y algo que hay que reconocer porque esto es la voluntad de las autoridades por resolver dudas, por por supuesto dar a conocer cómo, cuándo, por qué, en qué y cuánto se gastan los dineros, se aplican los recursos y pues por supuesto estar abiertos a los cuestionamientos de los representantes populares, en este caso los diputados locales. Mañana estaremos platicando aquí Qué resulta de esta comparecencia del oficial mayor Orlando Ángeles.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1z1N2XOPuKnedk2Q4w2OtBl9N477Y1kTP/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Edgar Orlando Ángeles Pérez</t>
   </si>
   <si>
-    <t>Andrés Torres antes de iniciar la transmisión de "Las Vocales Radio" por televisión comenta lo siguiente: "...digamos que funcionarios ignorantes, ¿no? e hijos de la rechingada. Son unos hijos de chingada. Y cobarde. Le molesta al señor director de Radio y Televisión de Hidalgo que nosotros tengamos redes sociales, ¿por qué? Porque él es un acosador y un delincuente. Nosotros sí somos trabajadores, nosotros sí somos gente de medios de comunicación, de certificados, no somos arribistas, ¿no? Y ojalá y me esté viendo y le pasen la nota al señor director, es un cobarde. Así, un cobarde. Para que quede bien claro, cuando guste, a la hora que quiera, lo podemos este aclarar. Lo podemos aclarar.</t>
-  </si>
-  <si>
-    <t>Peyorativo</t>
-  </si>
-  <si>
-    <t>...digamos que funcionarios ignorantes, ¿no? E hijos de la rechingada. Y cobarde. Le molesta al señor director de Radio Televisión de Algo que nosotros tengamos redes sociales. ¿Por qué? Porque él es un acosador y un delincuente. Nosotros sí somos trabajadores, nosotros sí somos gente de medios de comunicación, de certificados, no somos arrigbistas, ¿no? Y sobre todo, y ojalá y me esté viendo Y le pasen la nota al señor director Es un cobarde Un cobarde Para que quede bien claro Cuando guste, a la hora que quiera Lo podemos aclarar</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FgVJcDf21wJHX8Zkgf6WkdzQoGEwmLGK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Seguimos fuera del aire allá en Jacala de Ledezma, ya cumplimos un mes fuera del aire en el 91.1 de frecuencia modulada, les ofrecemos una disculpa. Bueno, pues estamos esperando que las áreas técnicas y administrativas pues resuelvan los problemas allá en la estación.</t>
-  </si>
-  <si>
     <t>Jacala</t>
   </si>
   <si>
-    <t>Seguimos fuera del aire en Jacala de Ledezma, ya cumplimos un mes fuera del aire en 91.1 de frecuencia modulada, les ofrecemos una disculpa. Bueno, pues estamos esperando que las áreas técnicas y administrativas resuelvan los problemas allá en la estación.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1EIHpEHdWZ875y0Z5lGMUigfReoeksS50/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud lleva a cabo una campaña de vacunación contra el Covid y antiinfluenza estacional. Se recomienda que la gente se acerque a la clínica, hospital o centro de salud más cercano para recibir su vacuna, que es gratuita. Las prioridades son niños menores de 5 años, adultos mayores y personas con enfermedades crónicas. Hay más de 1,500,000 dosis disponibles en todo el estado para proteger a la población, especialmente en la temporada invernal que se aproxima, para enfrentar el Covid y la influenza.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud continúa con la campaña de vacunación anti-COVID, antiinfluencia estacional. Por favor, acérquese si ese es su voluntad, si ese es su deseo, pero es lo deseable, es lo recomendable. Hay que ir a la clínica de salud más cercana a su domicilio, al hospital, al centro de salud, para que los vacunen, para que solicite usted su vacuna. Es totalmente gratuito, principalmente niños menores de 5 años, adultos mayores y por supuesto personas que tengan enfermedades crónico-degenerativas serán los principales en este momento los principales sectores a atender pero hay vacunas disponibles, hay más de 1.500.000 dosis en todo el estado y son totalmente gratuitas por supuesto para que usted esté bien protegido y en esta temporada invernal que ya se acerca, bueno pues le hagamos frente al COVID y con mucho también cuidado con el tema de la influenza estacional Así es, acude a su centro de salud, como bien mencionas, es completamente gratis la vacuna.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Op9VkCfBeO_0_dkd4eP18B0EcTRUOF_m/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Recordándoles que tenemos una advertencia, tenemos la alerta que nos da la Subsecretaría de Protección Civil y Gestión de Riesgos del Gobierno del Estado de Hidalgo, dependiente de la Secretaría de Gobierno, respecto a los temas del clima. Se esperan descensos de temperatura nuevamente y lluvias, lluvias moderadas en buena parte del estado. Sin embargo, la Subsecretaría de Protección Civil nos dice, "Hay que estar muy atentos, por favor, no hay que bajar la guardia en estos días que, bueno, pues el clima está en esta situación cambiante". La Subsecretaría de Protección Civil y Gestión de Riesgos informa a la población que para este 22 de octubre de 2026, de acuerdo con el aviso número 587 del Pronóstico Meteorológico General del Servicio Meteorológico Nacional, se prevén intervalos de chubascos de 5 a 25 milímetros. Asimismo, se pronostican temperaturas mínimas de 0 a 5 grados, con vientos de 10 a 20 kilómetros por hora y con rachas de 30 a 50 kilómetros por hora.</t>
-  </si>
-  <si>
-    <t>Recordándoles que tenemos una advertencia, tenemos la alerta que nos da la Subsecretaría de Protección Civil del Gobierno del Estado de Hidalgo dependiente de la Secretaría de Gobierno respecto a los temas del clima. Se esperan descensos de temperatura nuevamente y lluvias, lluvias moderadas en buena parte del Estado. Sin embargo, la Subsecretaría de Protección Civil nos dice, hay que estar muy atentos, Por favor, no hay que bajar la guardia en estos días que, bueno, pues el clima está en esta situación cambiante. A ver, Aldo Facón, por favor, ayúdanos. Así es, la Subsecretaría de Protección Civil y Gestión de Riesgos informa a la población que para este 22 de octubre de 2026, de acuerdo con el aviso número 587 del pronóstico meteorológico general del Servicio Meteorológico Nacional, se prevén intervalos de chubascos de 5 a 25 milímetros. Asimismo, se pronostican temperaturas mínimas de 0 a 5 grados Con vientos de 10 a 20 kilómetros por hora y con rachas de 30 a 50 kilómetros por hora Descenso importante de temperaturas sobre todo en las zonas altas</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1fZReCZRuC21NzECDSOgkeP6lULV7NWW1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1941/2026</t>
-  </si>
-  <si>
-    <t>Con publicación editorial, SEPH impulsa la preservación de la lengua Náhuatl y su legado cultural</t>
-  </si>
-  <si>
-    <t>CELCI</t>
-  </si>
-  <si>
-    <t>Preservación Lenguas Maternas</t>
-  </si>
-  <si>
-    <t>Huejutla</t>
-  </si>
-  <si>
-    <t>Déjeme compartirle rápidamente que como parte de las acciones para preservar y transmitir la riqueza cultural de Hidalgo, la Secretaría de Educación Pública, a través del Centro Estatal de Lenguas y Culturas Indígenas, presentó el libro "Palabras que nos que no se lleva el viento", una publicación que reúne textos en lengua náhuatl y mantiene viva su escritura, la transmisión de conocimientos y el reconocimiento de las lenguas originales originarias, perdón, esto como parte de las acciones impulsadas por el gobierno de Julio Menchaca Salazar para fortalecer la identidad cultural y preservar el patrimonio de los pueblos originarios. La obra integra textos elaborados por maestras y maestros de educación indígena, así como por personal del sector salud que participa como evaluador en los procesos de admisión al servicio docente y cuenta con certificación en lengua náhuatl. Los escritos son resultado del taller de actualización del alfabeto y escritura creativa, un espacio de aprendizaje y creación literaria en el que las y los participantes abordaron temas como el trabajo, la salud, los recuerdos de la niñez, el agua y las experiencias de vida cotidiana mediante diversos géneros y formatos de escritura. Entre los aportes de la publicación destaca la incorporación de las nuevas grafías del alfabeto conforme a la nueva norma de escritura de la lengua náhuatl, lo que contribuye al desarrollo de habilidades escritas y a la consolidación de criterios comunes para su uso y enseñanza. Estas acciones se alinean con la visión educativa del gobernador y del secretario de Educación Pública de promover una educación inclusiva, intercultural y humanista que reconozca la diversidad lingüística como parte fundamental de la identidad y la riqueza cultural de Hidalgo. La presentación se realizó en las instalaciones del Instituto Tecnológico de Huejutla, como parte del Día Internacional de la Medicina Tradicional, una fecha que destaca la importancia de preservar los conocimientos ancestrales de los pueblos originarios a través del Elcelsi, el Centro Estatal de Lenguas y Culturas Indígenas. La SEPH impulsa espacios de creación escrita en lengua materna para contribuir a la difusión de las lenguas indígenas y propiciar que las voces, experiencias y saberes de sus hablantes se transmitan a las nuevas generaciones.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1mChRg8BmLKyfxVlSHkYGdsdGkMNlS3QA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Pacula</t>
-  </si>
-  <si>
-    <t>La entidad se posiciona como referente nacional en la permanencia y  egreso de  estudiantes de preparatorias y universidades, apoyos educativos y fortalecimiento de infraestructura   
-Hidalgo avanza en el fortalecimiento de su sistema educativo y escala una posición para colocarse como el octavo estado del país con mejor desempeño en eficiencia terminal; a este logro se suma el progreso obtenido del diagnóstico de los Ejercicios Integradores del Aprendizaje y la inversión sostenida en infraestructura educativa, ciencia, tecnología y deporte, que amplía las oportunidades de desarrollo para las y los estudiantes. 
-Durante estos cuatro años, el proyecto educativo de la actual administración ha impulsado la formación de estudiantes capaces de transformar sus comunidades, fortalecer su identidad y contribuir a una sociedad más justa y humana. Cada trayectoria escolar suma al bienestar colectivo y nos acerca a un propósito común: sabernos un solo Hidalgo.
-Así lo expuso el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, durante su comparecencia ante las y los integrantes del Congreso del Estado, como parte de la Glosa del Cuarto Informe del gobernador Julio Menchaca Salazar.
-Hidalgo mejora los indicadores de trayectoria educativa
-La educación en Hidalgo ha tenido significativas mejoras en todos los niveles para que las y los estudiantes  permanezcan y concluyan sus estudios satisfactoriamente. En este contexto, Natividad Castrejón informó que la entidad mantuvo el 39 por ciento de la proporción de estudiantes que concluyen la educación superior por cada 100 que ingresan a primero de primaria. Este indicador sitúa a Hidalgo en el octavo lugar nacional, lo que representa un avance de una posición respecto al año anterior.
-Uno de los avances más sobresalientes se registró en educación media superior, donde la eficiencia terminal pasó de 63.2 por ciento en el ciclo escolar 2021-2022 a 75.6 por ciento en 2024-2025, lo que significó un incremento de 12.4 puntos porcentuales.
-En educación superior también se logró un importante incremento en eficiencia terminal, la cual avanzó de 69.6 a 84.5 por ciento, es decir una mejora de 14.9 puntos porcentuales. 
-SEPH acerca bachillerato a jóvenes de todo el estado 
-Con el propósito de ampliar las oportunidades educativas, el secretario destacó la incorporación de seis servicios de educación media superior, que permitieron garantizar la presencia de al menos un plantel público de este nivel en cada uno de los 84 municipios de Hidalgo.
-A estas acciones se suma la creación de 12 nuevos servicios de educación media superior; dos son Bachilleratos Generales, dos Telebachilleratos Comunitarios y ocho operarán bajo el modelo de Bachillerato Nacional Margarita Maza, para atender a jóvenes de seis municipios y ofrecer alternativas flexibles que faciliten la continuidad de sus estudios.
-Asimismo, se iniciaron las gestiones para construir 10 planteles de Telebachillerato Comunitario con instalaciones propias en zonas rurales, todo esto mediante una inversión de 290 millones de pesos.
-Hidalgo con la red de laboratorios STEM más grande del país; destaca en competencias internacionales</t>
-  </si>
-  <si>
-    <t>Semot/Bol.05/2026</t>
-  </si>
-  <si>
-    <t>Durante su comparecencia ante la sexagésima sexta Legislatura local, la titular de la Secretaría de Movilidad y Transporte (Semot), Lyzbeth Robles Gutiérrez, destacó la incorporación de tecnología avanzada —como cámaras con inteligencia artificial y sistemas de videovigilancia— en las unidades de transporte masivo. Asimismo, abordó las problemáticas viales de la zona metropolitana, enfatizando la importancia de respetar el carril exclusivo del Tuzobús para garantizar la seguridad vial, optimizar las frecuencias de paso y evitar el congestionamiento generado por la invasión de vehículos particulares.</t>
-  </si>
-  <si>
-    <t>En otra comparecencia y seguía compartiendo con usted, compareció ante la sexagésima sexta Legislatura la titular de la Semot, Lisbeth Robles Gutiérrez. Informó que se han incorporado unidades con inteligencia artificial, videovigilancia y accesibilidad universal. Como parte de la glosa del cuarto informe del gobernador Julio Menchaca, la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez, compareció y ahí él destacaba los trabajos que están haciendo para poder desahogar la salida hacia la ciudad de México, digamos Pachuca, Tizayuca, Estado de México, la Ciudad de México, hay una aglomeración constante y ya hemos comentado tanto por las lluvias, algunas obras y también nuestra participación que en ocasiones es plan de desesperación por ser primeros pues nos lleva a generar también o tener una falta de civilidad en la conducción en el manejo. No son casos generales, son casos particulares, pero nos ha tocado y entonces alguien en la desesperación dice, "Pues yo me voy a la vía en donde pasa la unidad de transporte público." Desde luego, desde luego, sin dejar de lado que en muchas ocasiones se ha mencionado, lleva un paciente, hay una ambulancia, o sea, hay hay hay varios hechos que se concatenan para que se genere esto que conocemos ya entonces como un nudo. Al día de ayer la secretaria de movilidad, Lisbeth Robles Gutiérrez, señaló, es un tema de ley, asisten a ley, claro, habrá mesas de trabajo, se está analizando para que se tome una determinación y nadie resulte afectado. Recordemos lo que dijo Lyzbeth Robles Gutiérrez.
-“Se hizo el anuncio de que estaríamos realizando un análisis por medio de unas cámaras que se van a situar en tres puentes sobre el bulevar Felipe Ángeles, en donde tenemos también puentes a cargo del Sistema Integrado de Transporte Masivo y que en esas cámaras que tienen utilización de inteligencia artificial nos va a permitir también medir el número de unidades conjuntamente con la información que pueda ser proporcionada por Seguridad Pública y por Seguridad Pública y Tránsito Municipal de Pachuca. Eh una vez que tengamos eso y que a la vez se haga la reunión correspondiente o las acciones inherentes a través de la coordinación que en su momento se origine por la Secretaría de Gobierno, estaremos en posibilidad de anunciamos de fondo. En ese momento yo mencioné lo que legalmente correspondía a la Secretaría y al organismo mencionado en torno al carril exclusivo. El carril exclusivo la ley establece que se debe de privilegiar obviamente para la operación eficaz y adecuada del transporte masivo, insisto que fue originado hace más de 10 años con una infraestructura en la cual cuenta un además de puentes y estaciones con el carril adecuado y exclusivo para que pueda brindar un servicio eficaz con las frecuencias de paso correspondientes y además es un tema de seguridad vial. Cuando las unidades de vehículos particulares transitan sobre un carril exclusivo, el congestionamiento se extiende no solamente a los carriles en donde de manera ordinaria transitan los vehículos particulares, sino que se extiende también ese congestionamiento vial hacia el carril exclusivo, lo cual incrementa el congestionamiento a lo ancho de toda la vialidad. Las vialidades son de todas y de todos y también debemos aprender a compartirlas y está apegado a la ley, a las políticas internacionales, nacionales y estatales el hecho de que exista un carril confinado para que las unidades de transporte masivo, que son generalmente en este caso a través de unidades BRT, se pueda llevar a cabo de manera óptima”.
-Parte de lo que se destacó en la comparecencia en el día de ayer.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1XvooEDZYdTnWodsPZSfxNmNGdrt3SsLr/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Sebiso/Bol.698/2026</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, compareció ante el Congreso del Estado para detallar los avances del cuarto informe de gobierno. Destacó que los programas sociales se triplicaron de 4 a 12 acciones directas, alcanzando un presupuesto de 400 millones de pesos destinados a combatir la pobreza y apoyar a sectores vulnerables, incluidos adultos mayores, personas con discapacidad y cuidadoras. Asimismo, resaltó la cobertura territorial mediante las "Casas del Pueblo" para eliminar intermediarios en la entrega de apoyos. No obstante, señaló los retos en el registro e integración de artesanos en ciertas demarcaciones como la comarca minera y parte del Valle del Mezquital, a pesar de los 15 millones de pesos asignados a este sector.</t>
-  </si>
-  <si>
-    <t>Bienestar</t>
-  </si>
-  <si>
-    <t>El titular de la Sebiso, Ricardo Gómez Moreno, en comparecencia ante el Congreso de Hidalgo, informó que la cobertura de programas pasó de 4 a 12 acciones directas en la gestión del gobernador Julio Menchaca Salazar, un incremento histórico. Y el presupuesto y alcance destacan 400 millones de pesos para combatir la pobreza y la deficiencia de recursos para cuidadores de personas con discapacidad. Durante la glosa del cuarto informe de gobierno, el secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, informó que ante el Congreso del Estado que en 2026 esta dependencia triplicó sus programas sociales, pasando de 4 a 12 acciones directas dirigidas a combatir la pobreza. El funcionario destacó la cobertura territorial alcanzada en comunidades de difícil acceso dentro de los municipios de Metztitlán, Huehuetla y Tlahuiltepa, donde se atendió a población históricamente marginada y, de manera particular, a personas cuidadoras de adultos mayores y también hay apoyo para adultos mayores.
-Nuestro compromiso es generar mejores condiciones de atención a favor de nuestras personas adultas mayores. Vivir en plenitud debe realizarse con compromiso a favor de quienes con sus enseñanzas y dedicación sostienen con orgullo a nuestro estado. Como parte de la estrategia para acercar la política social a través de la Dirección General de las y los Servidores del Pueblo, nos ha permitido fortalecer nuestro trabajo territorial, nuestra cobertura operativa. Se han optimizado los tiempos de entrega, se brinda una atención directa y, lo más importante, sin intermediarios, vigilándose de cerca la entrega final de los apoyos otorgados por la secretaría. De igual manera, se han realizado entrega de tarjetas no solo en las cabeceras municipales, sino también en las comunidades más alejadas. Además, se han llevado a cabo entrevistas de verificación y validación de la información proporcionada por las personas solicitantes”.
-En este mismo tema, también Ricardo Gómez Moreno señaló que se ha brindado apoyo a personas que tienen esta actividad importante en materia de artesanías, pero también destacó algo que no dejó de llamar la atención, hay artesanas y artesanos que se les ha invitado a que se sumen, se registren en las convocatorias, en el padrón de artesanas y artesanos y en algunas partes ha sido muy limitada la respuesta. Ricardo Gómez Moreno señaló:
-“En esta parte, conforme a la intervención y al video, establecimos todas las acciones que hemos venido generando a favor de todas las personas artesanas. En el programa este año contamos con 15 millones de pesos, beneficiamos a 1,425 personas artesanas. Y de manera muy puntual, en la comarca minera, que hemos tenido, que si bien esta es una parte del Valle del Mezquital, pero sí hemos tenido entre Tasquillo e Itzmapan y la los municipios de Actopan, Pizafores, Chafoluacán, la Misión, sí hemos tenido muy pocos registros. Incluso eh hemos habilitado los mismos en la Casa del Pueblo de Itzmapan, buscando que se registren más de esa región, porque prácticamente eh te puedo corroborar que el la gran mayoría se registra de la Huasteca eh por obviedad, porque allá, por supuesto, hay muchísimas personas artesanas. Lo que es este eh el Autonmi Tetegua, principalmente de Tenango, San Bartolo y un poco menos de Huehuetla, eh lo que es el Valle del Mezquital, pero de mayor número lo que es principalmente Alfalhucan e Itzmiquilpan, es donde más se absorbe el registro. Y entonces eh los recursos que hemos dirigido eh prácticamente se han absorbido en estas tres regiones, como como lo hemos comentado. Pero bueno, te pudiera comentar que eh en este contexto, para este año, lo que te decía, en Alfalhucan son 37 las personas beneficiarias, en Hacala solo son cuatro, en Tasquillo solo son tres y no tenemos en Itzmapan, lo que te decía. Entonces, sí hemos trabajado mucho más en esas regiones, pero a pesar de que hemos llevado las inscripciones directamente a eh Itzmapan, no hemos logrado que se inscriban, entonces es un trabajo que tenemos que fortalecer todavía más, pero lo estamos haciendo de una manera muy puntual, porque sí tenemos muy detectado en dónde tenemos un gran número de inscripciones, pero en dónde realmente nos falta que muchas personas artesanas se inscriban a los programas, pero eh también te comento, en la participación de la Feria de San Francisco, logramos traer personas artesanas de esas regiones, pero no hemos logrado que se inscriban durante el tiempo que tenemos aperturada las ventanillas para los mismos”.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FArVGXiAE8JGBD1r9Wb6P2k_7HDwccZu/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Julio Menchaca,</t>
-  </si>
-  <si>
-    <t>Durante su visita a la subestación Hidalgo en Pachuca, el gobernador Julio Menchaca Salazar reafirmó la estrecha colaboración y coordinación con la Comisión Federal de Electricidad (CFE), acompañado por funcionarios estatales como el secretario de desarrollo económico, Carlos Henkel Escorza, y la directora de la agencia estatal de energía, Ivonne Margarita Ramírez Núñez. En el encuentro con el encargado de la gerencia de la división Centro Oriente de la CFE, Jesús Alberto Armenta Lara, se destacó la importancia estratégica de la infraestructura eléctrica para garantizar servicios seguros y de calidad que impulsen el desarrollo social y económico del Estado.</t>
-  </si>
-  <si>
-    <t>Recorrido por instalaciones</t>
-  </si>
-  <si>
-    <t>Le había comentado, lo dije al principio, eh la Comisión Federal de Electricidad reafirma su colaboración con el gobierno de Hidalgo, con la visita del mandatario Julio Menchaca Salazar. Durante la visita del mandatario a la subestación Hidalgo en Pachuca, la Comisión Federal de Electricidad ha reafirmado su compromiso de mantener una estrecha colaboración y coordinación con el gobierno estatal, acompañado del secretario de desarrollo económico, ingeniero Carlos Henkel Escorza y la directora de la agencia estatal de energía, arquitecta Ivonne Margarita Ramírez Núñez, el maestro Julio Menchaca fue recibido, el gobernador fue recibido el lunes 19 de octubre por el encargado de la gerencia de la división Centro Oriente de la Comisión Federal de Electricidad, ingeniero Jesús Alberto Armenta Lara. Durante este encuentro se destacó la relevancia estratégica de la infraestructura e instalaciones eléctricas de la comisión, que son fundamentales para garantizar el servicio que sea seguro, confiable y de calidad, contribuyendo pues al desarrollo económico, social y el bienestar de las familias hidalguenses. Esta visita del mandatario refleja la sólida relación de trabajo con la Comisión Federal de Electricidad basada en tres puntos: el diálogo, la cooperación y el objetivo común de atender necesidades de la ciudadanía con eficiencia y visión de futuro. Vamos a hacer una pausa, al retorno tenemos más en la información.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JeOx85Jed3zI51lZNvcwZU1VzqEqqmTk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, inauguró el Congreso de Moda y Vestido 2026, reafirmando el compromiso estatal de consolidar a la entidad como un bastión de la industria textil y de la confección. Respaldado por la Canaive y la Canaintex, el sector busca alinearse con el Plan México para impulsar la competitividad, la atracción de inversiones y el desarrollo económico. Asimismo, ante retos globales como el contrabando y la informalidad, se destacó que la paz laboral y la estabilidad de Hidalgo posicionan al estado como una de las mejores opciones para el crecimiento de nuevos negocios.</t>
-  </si>
-  <si>
     <t>Reunión Con Empresarios</t>
   </si>
   <si>
-    <t>Bueno, le informo a usted, Hidalgo se consolida como bastión industrial de la moda y el textil. Hay un respaldo gubernamental, el gobernador Julio Menchaca inauguró el día de ayer el histórico Congreso de Moda y Vestido 2026 en este estado. La Canaive y la Canaintex impulsan la competitividad y, desde luego, hay una alineación con el plan México. El sector refuerza la agenda del gobierno federal con paso social y atracción de inversiones. Como vemos, cada eslabón va formando una cadena de circunstancias y de modelo, desde luego, que fortalece el desarrollo. En el marco de la inauguración del primer Congreso de Moda y Vestido 2026 en el estado, el gobernador Menchaca Salazar ha reafirmado su compromiso con el sector empresarial para consolidar a Hidalgo como el bastión de la industria textil y de la confección en el país. El gobernador destacó la arraigada tradición de Hidalgo desde la elaboración de hilos hasta la confección de prendas, Julio Menchaca Salazar destacó:
-“Hidalgo tiene una historia, ligada desde la fabricación del hilo hasta la confección de prendas. Asumo, como lo he hecho desde un principio, el compromiso de acompañar esa importante actividad que desarrollan y que se genere un bienestar compartido”. 
-Frente a desafíos globales como la informalidad, el contrabando y el robo al transporte, la Cámara Nacional de la Industria Textil ha señalado que el sector avanza en una estrategia alineada al Plan México del gobierno federal y, desde luego, concluyen que la estabilidad y paz laboral de Hidalgo posicionan a nuestro estado como una de las mejores opciones para el crecimiento de nuevos negocios. Enhorabuena también, todo esto genera desarrollo, genera empleo, genera tranquilidad, paz social y, sobre todo, entra con se corre como corresponde a Hidalgo en la competencia en todos los mercados.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FrO0INuX5Ev0fIh9ksxREOlyP2KHE1J1/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Cultura/Bol.721/2026</t>
-  </si>
-  <si>
-    <t>Hidalgo lleva tradición del Xantolo a Berlín, Alemania</t>
-  </si>
-  <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>Y ya para concluir, desde Pachuca, le comento esto que, por supuesto, nos llena de orgullo: el hecho de que las festividades, las tradiciones hidalguenses, como el Xantolo, pues lleguen a otras latitudes. Será en Berlín, Alemania, donde se establecerá un altar conmemorativo, esto en la Embajada de México allá en en Alemania, para mostrar al público de Berlín específicamente cómo se celebra el Día de Muertos en la Huasteca hidalguense. Y esta en esta celebración, en esta muestra de la tradición mexicana, informó el embajador de México en Alemania, Francisco Quiroga Fernández, también participará Atlisco, Puebla, con sus monumentales catrinas. Así es que el Xantolo de la Huasteca hidalguense y las catrinas monumentales de Atlisco, Puebla, estarán presentes en Berlín, Alemania, donde el público está muy ávido de presenciar, de conocer más de las tradiciones mexicanas, y qué mejor que sea en particular de las tradiciones hidalguenses.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1XIzy_WUX5P5dQTq8r8CBl6Q6se_sO3Qq/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Embajada de México en Alemania</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo</t>
-  </si>
-  <si>
-    <t>Francisco Quiroga Fernández, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Triplicó Sebiso apoyos para sectores vulnerables de Hidalgo: Ricardo Gómez Moreno durante su comparecencia ante representantes del Congreso del Estado.</t>
-  </si>
-  <si>
-    <t>En su comparecencia ante el Congreso del Estado, como parte de la glosa del cuarto informe de gobierno, el titular de la Secretaría de Bienestar e Inclusión Social, Ricardo Gómez Moreno, destacó que la gestión de tres veces más recursos y programas sociales, la atención a zonas de difícil acceso y a sectores históricamente olvidados, forman parte de las acciones que durante 2026 realizó la administración estatal a través de la dependencia que encabeza. En su intervención destacó que esta dependencia se se triplicaron los programas de en comparación con la administración anterior, pasando de 4 a 12 acciones en atención social. Explicó que la estrategia de este año contempló llevar los programas de la Secretaría de Bienestar e Inclusión Social hasta las comunidades más lejanas y con rezago persistente, lugares a los que en algunos casos se llegó a pie por lo intrincado de la geografía estatal. Comunidades como Tlatemaya, Metztitlán, Nexcay, el Catrín, la Piña, la Tortuga y las Juntas, en Huehuetla, Nueva Reynosa y Coyocala, en Tlahuiltepa, por mencionar algunas, donde se escuchó a la población que jamás había sido atendida por un secretario de la entidad. De igual forma, Gómez Moreno habló sobre el programa para quienes asisten de tiempo completo a personas con discapacidad múltiple permanente para que este año se haya duplicado su presupuesto que pasó de 5 a 10 millones de pesos en beneficio de 950 familias. Asimismo, con el programa de desarrollo inclusivo dirigido a la comunidad LGBT+ se impulsó a este sector en temas de salud, derechos humanos y desarrollo económico con un presupuesto de 5 millones de pesos en apoyo de 291 personas. Respecto al programa de bienestar y desarrollo, comentó que en el periodo reportado se benefició a 38,000 personas en situación de pobreza y alta marginación con un presupuesto de 400 millones de pesos. De igual forma, una estrategia de gran impacto es la del programa Madres Trabajadoras que en 2026 otorgó 12,300 apoyos económicos para igual número de mujeres que pues no abandonen sus estudios o trabajos por las labores propias de la maternidad y puedan así buscar un mejor futuro. Un sector donde se emplean muchas mujeres es el artesanal, por ello se destinaron recursos, dijo Ricardo Gómez, por 1,500,000 pesos para el programa Fomento Artesanal, que mediante concursos, reconocimientos y acciones de difusión buscan darle realce a las creaciones de las artesanas y artesanos de la entidad. En el mismo sector, el programa Bienestar para Personas Artesanas se distribuyeron 10,000 pesos para 1,425 creadores. Desglosó que en temas de atención a migrantes se invirtieron 5 millones de pesos que se utilizaron para la apertura de proyectos productivos para la población migrante. De la misma forma, se asesoró a migrantes y sus familias en trámites migratorios. En el rubro de juventudes destacó las capacitaciones, pláticas, reconocimientos, financiamiento a emprendimiento y otros servicios con una inversión de 6 millones 200,000 pesos. Para que las personas adultas mayores vivan una mejor vejez, se invirtió en remodelaciones y equipamiento, así como gasto de operación de centros gerontológicos y casas de día, con recursos por 37.7 millones de pesos, además de la entrega de 3,522 apoyos funcionales. En su mensaje de cierre, Ricardo Gómez Moreno comentó que la instrucción del gobernador Julio Menchaca fue que las acciones y programas que se han acercado al se acerquen a las puertas de quienes más lo necesitan y eso se logró a través de las y los servidores del pueblo que, mediante sus 27 Casas del Pueblo, permiten la entrega de los programas de esta y otras secretarías de la administración estatal, atendiendo directamente a más de 214,000 personas, es lo que informó ante legisladores el secretario de Bienestar.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10WHy3EWy6JaLGtcuEGzTLBOuQ5AUkxUo/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>En el marco del desarrollo de la industria del vestido en el estado, locutor Juan Carlos Santamaría destacó la importante colaboración y vinculación con el sector académico e instituciones de educación superior en la entidad, tales como la Universidad de la Sierra Hidalguense y la Universidad Politécnica de Tulancingo. Estos centros educativos impulsan la investigación y la innovación en el diseño de prendas funcionales que propicien el bienestar integral de las personas. Asimismo, se destacó que la infraestructura de la región, aunada a los trabajos de seguridad y recuperación de transporte de mercancías, consolidan a Hidalgo como un punto clave y atractivo para la inversión en el sector textil y de la moda.</t>
-  </si>
-  <si>
-    <t>Y en este contexto de la industria del vestido, cabe recordar también la suma de la academia. En este espacio informativo hemos tenido la oportunidad de platicar con docentes y con alumnos de la universidad eh de la de la Huasteca, de la Sierra Hidalguense, perdón, donde existe esta carrera. Ahí está justo en el municipio de Sahuatipan, un productor de de mezclilla, de prendas de de mezclilla, entre otras cosas, por supuesto, pero de manera preponderante de de esta eh pues eh popular ropa. Y y bueno, eh en esto que dicen los empresarios, de que no solamente es la la confección de de ropa, sino también buscar la innovación, y en este sentido hemos platicado con docentes e incluso con el propio rector de la Universidad Politécnica de Tulancingo, quienes nos han eh compartido que en esta búsqueda de la innovación buscan que que la ropa no solamente sea cómoda, sea agradable a la vista, sino que eh tenga algunos elementos que permitan un bienestar integral de las personas. Y, bueno, pues eso se está haciendo desde la academia en la entidad. Eh, universidades, instituciones como la Universidad de la Sierra Hidalguense y la Politécnica de Tulancingo, y es parte de lo que conforma un entorno eh pues adecuado para el desarrollo de la industria de la moda y el vestido en la entidad. Esto, aunado también a las eh a los trabajos que se realizan en materia de seguridad y, de hecho, también le hemos podido compartir algunos resultados de la recuperación de eh transporte eh pesado con mercancías, algunas pertenecientes justamente a este sector, al sector eh textil y y bueno, todo todo esto hace de Hidalgo un punto atractivo, no solamente para la realización de este congreso, sino sobre todo para la inversión en el sector textil, en el sector de la moda y el vestido.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1442YUW74WBWjSRPeRWbWUnRLnh8ZQlJT/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Congreso Nacional de Moda y Vestido 2026.</t>
-  </si>
-  <si>
-    <t>Y en y en más información del gobierno del Estado le comento que eh pues eh el gobernador inauguró el Congreso de Moda y Vestido, que por primera vez se lleva a cabo en el estado, que es un bastión de esta industria. En este sentido, esto es parte de lo que destacó el mandatario estatal.
-“Hidalgo tiene una historia, ligada desde la fabricación del hilo hasta la confección de prendas. Asumo, como lo he hecho desde un principio, el compromiso de acompañar esa importante actividad que desarrollan y que se genere un bienestar compartido”. 
-El Ejecutivo estatal reconoció el trabajo del sector empresarial que, en sinergia con las administraciones estatal, ha elevado los índices del estado en actividad económica. Recordemos, por supuesto, que Hidalgo está a la vanguardia en cuanto a actividad industrial. José Pablo Maauad Pontón, en este contexto, él es el presidente de la Cámara Nacional de la Industria del Vestido, detalló que el congreso es un espacio para entender el entorno y vislumbrar el futuro de la industria de la moda y el vestido, destacando el intercambio de ideas, experiencias y buenas prácticas. Además, puso a disposición del gobierno de Hidalgo la experiencia técnica, la vinculación productiva y el acompañamiento para ayudar en los procesos de compra de uniformes. Dijo José Pablo Maauad: Hidalgo es un bastión de nuestro sector, por eso estamos hoy aquí durante su carrera pública ha sido siempre un amigo impulsor de nuestra industria. Aquí presente, desde los polos de confección de Singuilucan, Tulancingo, Cuautepec, Pachuca, Tizayuca y Axacuba, a las fábricas textiles de Tepeji, agradecemos y reconocemos su apoyo, manifestó el dirigente empresarial. Rafael Torres, él es presidente de la Cámara Nacional de la Industria Textil, recordó que este sector enfrenta presiones relacionadas con el contrabando, mayores costos laborales, robo al transporte, prácticas ilegales e informalidad que debilitan la cadena productiva, lo cual se afronta desde este sector con el avance de una agenda de sustitución de importaciones y fortalecimiento de contenido nacional. Durante su mensaje, Juan Porras Brambila, tesorero de la Confederación de Cámaras Industriales de los Estados Unidos Mexicanos, refirió que la industria del vestido es mucho más que moda y confección, resaltando la innovación, el talento y el esfuerzo de miles de mujeres y hombres que son respaldados en su actividad económica mediante el plan México de la presidenta Claudia Sheinbaum. "El bienestar vendrá por el trabajo", afirmó Guillermo Austerberto Vera Rodríguez, presidente de la Cámara Nacional de la Industria del Vestido, Delegación Hidalgo, al destacar que en la entidad existe paz social y laboral, logrando ocupar los primeros lugares de crecimiento y buen clima para hacer negocios.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1eqkUg7ShBkFQZoYcW5gps7y5ogRTJ4e0/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>José Pablo Maauad Pontón, Rafael Torres, Juan Porras Brambila, Guillermo Austerberto Vera Rodríguez, Claudia Sheinbaum</t>
-  </si>
-  <si>
-    <t>Estamos con información desde Pachuca y le comento que el gobernador Julio Menchaca participó en la reunión encabezada por la presidenta Claudia Sheinbaum Pardo en Palacio Nacional, donde se evaluaron los avances del programa Vivienda para el Bienestar y se acordó fortalecer la coordinación entre los tres órdenes de gobierno para agilizar su implementación. Como parte de esta estrategia nacional, que contempla la construcción de 1.8 millones de viviendas, en el estado de Hidalgo se proyectan 66,500 en los municipios de San Agustín Tlaxiaca, Mineral de la Reforma, Tepeapulco, Tepeji del Río, Zempoala, Actopan y Tulancingo, con el objetivo de ampliar el acceso de las familias hidalguenses a una vivienda digna. Asimismo, Menchaca Salazar acompañó a la mandataria nacional en un encuentro para revisar los avances del proceso de modernización del IMSS Bienestar junto a 23 gobernadoras y gobernadores —también son 24 las entidades, recordemos— donde se ha implementado el programa, el sistema del IMSS Bienestar.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1sGMtR7c4TgF_2QWpJJBXvYMIwRdR2_zr/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum,</t>
-  </si>
-  <si>
-    <t>A cuatro años de este gobierno, la SEMOT avanza en la ejecución de acciones necesarias tendientes a planificar la movilidad</t>
-  </si>
-  <si>
-    <t>En otros temas, le comento acerca de la comparecencia de la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez ante la sexagésima sexta Legislatura local, donde detalló, ante ellos detalló los logros alcanzados durante el cuarto año de la administración que encabeza el gobernador Julio Menchaca Salazar. Durante su intervención, la secretaria informó que se actualizaron y complementaron los planes integrales de movilidad urbana sustentable de las zonas metropolitanas de Tula y Tulancingo, además de elaborarse el plan del municipio de Tizayuca. Estos instrumentos de planeación cuentan con una inversión superior a los 25 millones de pesos. En el mismo sentido, la titular de la dependencia informó que se encuentran en proceso de ejecución los planes integrales de movilidad urbana sustentable de Huejutla y de Ixmiquilpan. Por otra parte, la titular de la Semot enfatizó que el sistema integrado de transporte masivo de Hidalgo cuenta con una flota vehicular consistente en 140 unidades nuevas con capacidad de 80, 50 y 15 personas pasajeras, con tecnología de última generación, con cámaras de videovigilancia, inteligencia artificial que permite analizar los hábitos de conducción, asientos preferentes destinados a mujeres, personas con discapacidad y adultos mayores. De la misma manera, la secretaria afirmó que con el propósito de mantener el servicio de movilidad incluyente e integral en el sistema de transporte masivo, a través de ocho unidades equipadas con elevadores para sillas de ruedas, tres corralillos de sujeción, sistema de comunicación visual y auditiva y pantallas con proyecciones en lengua de señas mexicanas, se han atendido a personas con discapacidad, adultos mayores y con movilidad reducida. De igual forma, se llevaron a cabo acciones tendientes a despejar el carril exclusivo, mismas que consistieron en realizar inspecciones para evitar su invasión previa socialización e aplicación de 203 amonestaciones a la población, sin pretender fines recaudatorios, afirmó la secretaria, sino salvaguardar, dijo, la vida y la integridad de las personas usuarias, del personal conductor y de todas aquellas que transitan en su área de influencia. En este sentido, a partir del 16 de agosto de 2026, inició la aplicación de sanciones para quienes invaden el carril exclusivo del sistema, con multas que van de los 20 a los 30 UMAs. Durante el periodo que se informa, se han infraccionado un total de 67 personas con un monto equivalente a 157,208 pesos. Asimismo, la secretaria subrayó que, asumiendo la responsabilidad de la operación directa del sistema de transporte metropolitano, el estado a través del sistema integrado de transporte masivo, fortaleció su infraestructura para enfrentar este desafío, destacando la incorporación de 351 personas conductoras quienes recibieron una amplia capacitación en diversos temas para brindar un servicio a la altura de la exigencia de la población. En lo referente al sistema de transporte convencional, con el propósito de modernizar la gestión documental relacionada con las concesiones de transporte público y garantizar el resguardo adecuado de esta información, se destinó una inversión de 7.7 millones de pesos en la conversión de documentos físicos a formatos digitales y la implementación de una plataforma tecnológica para la consulta y localización electrónica de expedientes relacionados con las concesiones del transporte público convencional. La secretaria añadió que para la mejora del transporte público se realizaron diversas acciones, entre las que destacan 1,830 operativos de vigilancia y supervisión, el operativo Transporte Seguro y la aplicación de pruebas toxicológicas gratuitas. Además, la titular refirió que con una inversión de 9 millones y medio se realizó el censo del transporte del estado con el objetivo de generar información confiable y actualizada sobre las condiciones en que se presta el servicio en las vías públicas de la entidad. Por otra parte, expresó que para el ejercicio presupuestal 2026 se están llevando a cabo proyectos para contribuir a mejorar la seguridad en el sistema de transporte. La titular de la Semot concluyó que no se puede concebir una movilidad sin seguridad vial, razón por la cual es importante precisar que las acciones de los entes que realizan los entes públicos en esta materia serán insuficientes si no se incorpora la sociedad para fomentar una cultura vial. Es parte de la comparecencia de la secretaria Lyzbeth Robles Gutiérrez ante el Congreso del Estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1x5RVMwB0hjEH4GkQ-a5ndnTLOQGeWdCj/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos informó que se pronostican lluvias fuertes, chubascos, así como un descenso en las temperaturas y vientos con rachas de hasta 50 km/h, afectando principalmente las regiones norte y este de Hidalgo. Debido a la acumulación previa de humedad en los suelos, las autoridades advirtieron sobre el riesgo latente de deslaves, derrumbes, inundaciones y crecidas de ríos. Ante este panorama, se emitieron diversas recomendaciones a la población, tales como evitar cruzar cuerpos de agua o calles inundadas, respetar los cierres carreteros y mantenerse informados ante cualquier señal de peligro.</t>
-  </si>
-  <si>
-    <t>Continuamos en Pachuca, son las 9:00 de la mañana con 2 minutos y le comento que comparte la Subsecretaría de Protección Civil y Gestión de Riesgos que se prevén lluvias fuertes en el norte y en el este del estado de Hidalgo. Persiste el riesgo de deslaves y derrumbes. Para este 22 de octubre el Servicio Meteorológico Nacional pronostica chubascos con lluvias puntuales fuertes de 25 a 50 mm, principalmente en las regiones norte y este del estado. Además, se prevén temperaturas mínimas de 0 a 5 °C, vientos de 10 a 20 km por hora con rachas de 30 a 50 km por hora. Las lluvias recientes han favorecido la acumulación de humedad en el suelo, por lo que podrían presentarse nuevos deslaves y derrumbes, desprendimientos de material, incluso cuando las precipitaciones disminuyan o cesen. También podrían registrarse escurrimientos, inundaciones e incrementos en los niveles de ríos y arroyos en zonas susceptibles. Y por supuesto, las autoridades recomiendan no cruzar ríos, arroyos, vados ni calles inundadas, ni a pie ni en vehículo; respetar los cierres carreteros, evitar transitar por caminos afectados por derrumbes, lodo o corrientes de agua y utilizar únicamente rutas confirmadas como seguras. Y por supuesto, si habitan en zonas susceptibles a inundaciones o deslizamientos, mantenerse atentos a las señales de peligro y atender las indicaciones de las autoridades, esto es fundamental, por supuesto.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JIza6SaujKIhMikRpYVNymZABP-YwsN-/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>UPLAPH/Bol.161/2026</t>
-  </si>
-  <si>
-    <t>En su colaboración semanal, el especialista Gustavo Rosales compartió los pormenores del Epic Travers Hidalgo 2026, una exigente competencia multideportiva programada del 23 al 25 de octubre que contará con la participación de 150 atletas nacionales e internacionales. El recorrido constará de 230 kilómetros distribuidos en 9 municipios del estado (Mineral del Chico, Atotonilco el Grande, Actopan, Santiago de Anaya, Cardonal, Metztitlán, Ixmiquilpan, Tasquillo y Zimapán), e incluirá 30 km de trail, cañón, 35 km de ciclismo de montaña y 20 km de paddle board en aguas abiertas bajo condiciones de clima frío.</t>
-  </si>
-  <si>
-    <t>Justa Deportiva</t>
-  </si>
-  <si>
-    <t>¿Con qué nos seguimos, Gustavo?
-Seguimos con una carrera que a mí en lo particular me emociona bastante. Esto pues desarrollado, yo creo que se preveían otras condiciones climatológicas, sin embargo, parece ser que va a estar en medio de un frío arrollador, si lo podríamos denominar de esta manera, el Epic Travers Hidalgo 2026, en donde tendrá presencia en 9 municipios, 230 km de eh de aventura. La verdad es que sí va a estar supersupercomplicada esta competencia, desarrollarse del 23 al 25 de octubre, 150 atletas nacionales e internacionales, y tendrá presencia en los siguientes municipios: Mineral del Chico, Atotonilco el Grande, Axtopan, Santiago de Anaya, Cardonal, Metztitlán, Xmiquilpan, Tasquillo, perdón, y Zimapán. En donde, a ver, la la competencia se va a desarrollar de la siguiente forma: son 30 km de trail, recorrido en cañón y 35 km de ciclismo de montaña, además de 20 km de paddle board en aguas abiertas, lo cual, de verdad, estará muy muy exigente. Definitivamente, algo que destacar este Epic Travers Hidalgo, definitivamente una una competencia que va a estar muy interesante, sobre todo, como ya lo decía, muchas condiciones climatológicas. Esto me hace recordar, Juan Carlos, hace pues ya hace muchos muchos años cuando alguna empresa de televisión traía a nuestra entidad eh eh o el el Hidalgo Extreme Adventure y le ponían el el sufijo del año en el cual se iba a disputar. La verdad es que trajo en algún momento unos aviones impresionantes a lo que antes era llamado el Parque Venustiano y bueno, pues ahora con esta competencia Epic Travers Hidalgo, bueno, pues estará retomándose algo relativamente similar. Así que bueno, pues el inicio a las 6 de la mañana, a las 6 de la mañana, la verdad es que es muy temprano, así que bueno, pues todos pendientes, todos pendientes de esta competencia.
-Que por todo lo que nos comentas, hace honor a su nombre, será una competencia épica.
-Definitivamente, definitivamente. No sé si todavía haya eh algunos algunos lugares disponibles, pero bueno, va a ser emocionante, eso no hay duda alguna, Juan Carlos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HNafhPsQVnJUWhZnxMuBR2BGdJv50O7L/view?usp=drivesdk</t>
+    <t>SEPH/Bol.1944/2026</t>
+  </si>
+  <si>
+    <t>Yazmin Leonardo</t>
+  </si>
+  <si>
+    <t>UTEC e ICATHI fortalecen la vinculación para la capacitación laboral y desarrollo profesional</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Firma De Convenio</t>
+  </si>
+  <si>
+    <t>Continuamos con más información. Le comparto que la Universidad Tecnológica de Tulancingo y el Instituto de Capacitación para el Trabajo del Estado de Hidalgo formalizaron un convenio de colaboración para sumar capacidades en materia de formación y capacitación, esto con el propósito de responder pues a las necesidades del sector productivo y ampliar las oportunidades de desarrollo profesional para estudiantes, egresados y población en general.
+El acuerdo fue suscrito por el rector de la UTEC, Tito Dorantes Castillo, y el director general del ICATHI, Jorge Israel Acosta Benítez, quienes encabezaron esta alianza entre ambas instituciones públicas.
+Uno de los principales alcances de este acuerdo es la posibilidad de desarrollar acciones conjuntas de evaluación y certificación de competencias laborales, a fin de reconocer los conocimientos, habilidades, destrezas y experiencias de las personas y fortalecer sus perfiles profesionales.
+El rector de la UTEC destacó que este convenio complementa eh pues el modelo educativo de la universidad, que se sustenta en la formación práctica, la innovación, el desarrollo tecnológico y la vinculación con los sectores productivo, público y social.
+Por su parte, el ICATHI ofrece alternativas de capacitación para que la población adquiera y fortalezca habilidades que faciliten su incorporación al mercado laboral.
+Durante Castillo señaló que esta alianza busca acercar la formación académica y la capacitación a las necesidades pues de empresas y organizaciones en un entorno laboral que demanda perfiles especializados y competencias demostrables.
+Este tipo de alianzas forman parte de la visión educativa del gobernador Julio Menchaca Salazar y del secretario de educación pública de Hidalgo, Natividad Castrejón Valdez, orientada a fortalecer la educación superior y su vinculación con las necesidades del Estado.
+Así la información, información de educación que con gusto les comparto</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EHmDgLAwHaXZM_iLrvMqrdtqZzr9b3XZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Tito Dorantes Castillo</t>
+  </si>
+  <si>
+    <t>Jorge Israel Acosta Benítez, Julio Menchaca, Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Locutor Irving Sánchez da lectura a comentario de radioescucha que reporta el estado crítico de la entre Santiago Tulantepec y Tulancingo, abarcando desde el crucero de Genisa hasta después de Medias Tierras. Los reportes señalan que la ruta se encuentra en peores condiciones que un camino rural, con numerosos baches y hoyos incrementados por las recientes lluvias. A pesar de las afectaciones diarias para quienes transitan por la zona, los inconformes denuncian que las autoridades no han hecho nada para solucionar este problema que lleva años deteriorándose.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Carretera En Mal Estado</t>
+  </si>
+  <si>
+    <t>"Reportan que en la carretera es cierto, o sea, la carretera Santiago-Tulancingo, Tulancingo-Santiago ya es imposible pasar desde el crucero de Geniza hasta después de Medias Tierras."   "A pesar de los reportes las autoridades no hacen nada y hay quienes todos los días deben circular por ahí hacia Santiago, hacia Tulancingo, viceversa."   "Sí, efectivamente, bueno, pues ya no es ni carretera, ya parece está peor que un camino rural."   "Está en muy malas condiciones y vaya que con la lluvia también se ha generado mucho más eh baches, hoyos ya..."   "y esto cabe aclarar que no es de este de estos eh últimos años, eso tiene mucho tiempo que se viene deteriorando este tramo de la carpeta asfáltica de la carretera, o bueno, de esa vía de comunicación hacia Santiago, Tulantepec y Tulancingo."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JSY9VWy046Iayrj3r-wg-InNk362CFUW/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>OM/Bol.SN-A/2026</t>
+  </si>
+  <si>
+    <t>En un hecho histórico para el Poder Legislativo de Hidalgo, el oficial mayor Edgar Orlando Ángeles Pérez compareció por primera vez ante las y los diputados de la Sexagésima Sexta Legislatura, como parte de la glosa del informe del gobernador Julio Menchaca Salazar. Durante su comparecencia, el funcionario expuso los avances en materia de transparencia y modernización, señalando las condiciones críticas en las que recibieron la administración —con documentación inconsistente, infraestructura obsoleta y bienes sin control—. Informó que de enero a septiembre de este año se han adjudicado 313 contratos por más de 2,558 millones de pesos (el 97% mediante licitación pública nacional), y destacó la aplicación de penalizaciones y rescisiones que evitaron un daño a las finanzas públicas superior a los 74 millones de pesos. Finalmente, resaltó las acciones de diagnóstico y regularización del patrimonio inmobiliario del estado para garantizar el uso responsable de los recursos públicos.</t>
+  </si>
+  <si>
+    <t>Y dando seguimiento a las comparecencias en el Congreso del Estado de Hidalgo, el Congreso Libre y Soberano del Estado de Hidalgo. Es histórico, por vez primera compareció un oficial mayor, y estoy refiriéndome a Edgar Orlando Ángeles Pérez, oficial mayor que reportó avances en transparencia y modernización, pero también destacó cómo recibió, cómo recibió esta administración los insumos, los artículos, la herramienta, el mobiliario para poder trabajar.
+En sesión ordinaria, el presidente de la Junta de Gobierno, diputado Andrés Velázquez Vázquez, dio la bienvenida al titular de la Oficialía Mayor, Edgar Orlando Ángeles Pérez, quien compareció en el Congreso del Estado Libre y Soberano de Hidalgo como parte del procedimiento relativo al cuarto informe del estado que guardan los diversos ramos de la administración pública encabezada por Julio Menchaca Salazar.
+Esta comparecencia representa un hecho histórico para el poder legislativo estatal al ser, reitero, la primera ocasión en que el titular de la Oficialía Mayor comparece ante las y los diputados de la Sexagésima Sexta Legislatura. Asimismo se precisó que cualquier funcionario de primer nivel de la administración pública estatal puede ser llamado a comparecer con el propósito de fortalecer la transparencia, la rendición de cuentas y el ejercicio de la vigilancia legislativa. No solamente los secretarios, algún titular puede ser llamado también en una comparecencia a que dé a conocer el estado que guarda la administración en su ramo.
+En su mensaje, el legislador destacó también la importancia de una administración pública ordenada, eficiente y transparente, basada en el uso responsable de los recursos, el cuidado del patrimonio público y la mejora de los procesos institucionales.
+Orlando Ángeles señaló cuál fue la mística, la meta al inicio de esta administración.
+'Al inicio de esta administración recibimos una instrucción clara: fortalecer el orden administrativo, mejorar el aprovechamiento de los recursos, modernizar los procedimientos y transparentar la gestión gubernamental'.
+'Encontramos deficientes documentación inconsistente, infraestructura tecnológica obsoleta y bienes muebles e inmuebles sin control ni aprovechamiento'.
+'Ante este escenario, realizamos la revisión de procesos, expedientes, infraestructura y bienes del estado. Emprendimos acciones de regularización, actualización y control'.
+'Restablecimos procedimientos claros y fortalecimos la coordinación institucional para generar resultados verificables'.
+'Nuestra labor se orientó a mejorar las condiciones en las que se opera las que operan las dependencias, optimizar los recursos, cuidar los bienes y dar certeza a los procedimientos administrativos'.
+'Primero, adquisiciones: uno de los asuntos que merece mayor claridad es el de las adquisiciones y contrataciones. Fortalecimos los procedimientos, la contratación, la coordinación entre las instancias participantes y los mecanismos para asegurar el cumplimiento de los contratos'.
+'El Comité de Adquisiciones, Arrendamientos y Servicios del Gobierno fue instalado desde el primer día, desde el primer día de esta gestión, el 5 de septiembre de 2022'.
+'Las secretarías de Hacienda, la Secretaría de Gobierno, la Secretaría de la Contraloría, la Unidad de Planeación y Prospectiva, la Oficialía Mayor y las áreas requeridas'.
+Bueno pues el oficial mayor comunicó avances ya en transparencia, pero además de que documentos, contratos tenían muchos faltantes, Orlando Ángeles señaló también todo lo que se ha tenido que hacer para ordenar y poder iniciar... el trabajo, no, no basta llevar a cabo la entrega-recepción, es desde luego también darle seguimiento a cada uno de los temas. Había un desorden, Orlando Ángeles señaló.
+'De enero a septiembre de este año se han adjudicado 313 contratos por más de 2,558 millones de pesos'.
+'De este monto, 310 contratos equivalen al 97% fueron licitación pública nacional'.
+'También fortalecimos los instrumentos contractuales y los mecanismos de cumplimiento'.
+'En diciembre del 2025 este congreso en materia de adquisiciones, incorporando entre otras leyes que permiten reforzar las garantías de cumplimiento de los contratos, porque contratar no es suficiente, también hay que exigir que todo se cumpla'.
+'Durante esta administración se aplicaron penalizaciones a 35 contratos por un monto total de 5,819,000 pesos'.
+'Asimismo, se rescindieron 6 contratos cuyo valor ascendía a 68 millones de pesos'.
+'En conjunto a las penalizaciones y las recisiones contribuyeron a evitar un posible daño a las finanzas del estado por más de 74 millones de pesos'.
+'Nuestra responsabilidad es actuar conforme a derecho y cumplir la ley'.
+'Estos datos no son solamente cifras administrativas, representan obligaciones exigidas, mecanismos de control y recursos cuya protección debe acreditarse documentalmente'.
+'El patrimonio inmobiliario pertenece a las y los hidalguenses'.
+'Su administración exige conocer qué bienes tenemos, cuál es su situación jurídica y cómo puede cumplir una función para la gente'.
+'Al inicio de esta administración, mediante un proceso de diagnóstico, se identificaron múltiples irregularidades y abusos, como la falta de un inventario consolidado, confiable, inmuebles estatales al margen de la cuenta pública, propiedades pagadas y sin escriturar, intercambio de bienes en condiciones desproporcionadas'.
+'Un inventario inmediato de cómo se recibió y lo que se está haciendo en favor de...'".</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1knLyKSFkdyqatVz6_U9Ng_2IewLsCyY9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Andrés Velázquez Vázquez, Julio Menchaca</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/Bol.1332/2026</t>
+  </si>
+  <si>
+    <t>Convoca Julio Menchaca a sector empresarial a generar prosperidad compartida en todo el país.</t>
+  </si>
+  <si>
+    <t>En respaldo a la Confederación de Cámaras Nacionales de Comercio, Servicios y Turismo, la Concanaco Servytur, el gobernador de Hidalgo, Julio Menchaca Salazar, participó en su Asamblea Nacional, espacio en el que hizo un llamado a este sector para continuar trabajando en sinergia y generar bienestar en beneficio de las familias mexicanas.
+En Hidalgo, señoras y señores, estamos haciendo nuestra parte, se están generando una enorme cantidad de empleos', escuchemos al gobernador del estado de Hidalgo: 
+'En Hidalgo estamos haciendo nuestra parte, se están generando una enorme cantidad de empleos y hacemos una invitación para que haya actividad económica, haya prosperidad, haya bienestar compartido y que esa sinergia del gobierno federal, con nuestra presidenta, con los gobiernos estatales, con los gobiernos municipales sea un ejercicio permanente para la construcción del México que queremos, del México que merecemos'.
+En este sentido, titular del gobierno de Hidalgo reconoció a quienes integran la confederación, pues su esfuerzo, labor y liderazgo, dijo, impacta y se traduce en beneficios para sus comunidades, municipios y estados, encabezados por Octavio de la Torre de Stéffano, presidente nacional de la Concanaco Servytur.
+Hay un programa de la Concanaco Servytur que hemos observado en distintas entidades, el 'Viernes Mexicano', y desde luego lo atractivo para el turismo y atractivo para quienes viven en estos municipios, porque además se consume lo local; consumir local permite que haya un activo circulante dentro de las regiones, las comunidades, los municipios y se va fortaleciendo la economía.
+Por su parte, Gerardo Fernández Noroña, presidente de la Mesa Directiva del Senado de la República, reconoció a las y los empresarios por ser generadores de empleo en sus respectivos entornos, por lo que señaló la importancia de brindar facilidades para el correcto desarrollo de sus actividades.
+Al respecto, Iván de Jesús Ramírez, presidente municipal de Ezequiel Montes, coincidió en que las administraciones estatales y municipales pueden apoyar a las micro y pequeñas empresas en su regularización mediante la simplificación de trámites burocráticos.
+De esta forma, la presencia del gobernador de Hidalgo en la Asamblea Nacional de la Concanaco Servytur fortaleció el diálogo con uno de los sectores clave para la economía nacional, donde además se reiteró la importancia de sumar capacidades entre los gobiernos y la iniciativa privada para impulsar el empleo, favorecer la actividad comercial y las condiciones de desarrollo que beneficien tanto a las empresas como a las familia</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iX7c5XW4ubl0hKmKRXGf00u_WG_PwLIW/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Octavio de la Torre de Stéffano, Higinio Martínez Miranda, Iván Reséndiz Ramírez</t>
+  </si>
+  <si>
+    <t>Segobh/IHM/Bol.45/2026</t>
+  </si>
+  <si>
+    <t>Centro LIBRE contribuye a la preservación de la lengua Hñähñü</t>
+  </si>
+  <si>
+    <t>IHM</t>
+  </si>
+  <si>
+    <t>Centros LIBRE</t>
+  </si>
+  <si>
+    <t>Tecozautla</t>
+  </si>
+  <si>
+    <t>Continuamos, vamos contigo, Ros María, tienes información de los centros libre...
+Desde el mes de julio, cada fin de semana un grupo de mujeres originarias de Tecozautla se reúnen en el centro libre del municipio para aprender, reaprender y revalorizar su lengua materna con la guía de la abogada Elda Mabel Penca Doñú, quien además de su labor como asesora jurídica, imparte el curso 'Introducción básica al ñañú'.
+Originaria de Cardonal, la profesionista del Instituto Hidalguense de las Mujeres asumió el compromiso de aportar sus conocimientos para reforzar la preservación, aprendizaje y uso de las lenguas indígenas más importantes del país, como una herramienta de identidad cultural.
+La finalidad, explica, es contribuir al empoderamiento de las mujeres a través del rescate y reconocimiento del patrimonio lingüístico y cultural de la región otomí, así como brindarles herramientas que favorezcan una participación más activa e incluyente en la sociedad.
+El curso... y concluirá el próximo mes de diciembre, está dirigido a mujeres a partir de los 15 años y consta de seis módulos donde se revisan desde temas básicos hasta expresiones comunes, saludos y conversaciones básicas, por lo que las personas interesadas pueden acudir al centro libre de Tecozautla.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1czKYFfC1XGXDt-jvWCerOXxN8c1YnOGa/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor rinde cuentas sobre el correcto cumplimiento del gasto público</t>
+  </si>
+  <si>
+    <t>Continuamos con información desde Pachuca y bien, pues ya eh han concluido las comparecencias ante el Congreso del Estado la glosa del cuarto informe del gobernador Julio Menchaca Salazar y cabe recordar, ya le decía hace unos momentos, que el calendario original, el calendario inicial contemplaba hasta ayer a las 10 de la mañana la la última comparecencia y sería la de el encargado del despacho de la Procuraduría General de Justicia del Estado, de la cual ya le he dado detalle. Sin embargo, después se sumó la de la Oficialía Mayor del Gobierno del Estado, así es que por primera vez un titular de la Oficialía Mayor del Gobierno del Estado compareció ante el Congreso de la entidad. Orlando Ángeles Pérez, quien rindió cuentas sobre los avances que garantizan el correcto destino de los recursos públicos, mejorar los procesos administrativos y también mejorar las condiciones de quienes trabajan al servicio de las y los hidalguenses.
+Sobre las contrataciones de obra, productos y servicios, destacó que de enero a septiembre se dictaminaron 313 contratos, de los cuales el 99% fueron mediante licitación pública. Asimismo, durante la administración se aplicaron penalizaciones a 35 contratos y se rescindieron 6 contratos por incumplimiento, cuyo valor ascendía a 68 millones de pesos.
+Orlando Ángeles destacó avances en la modernización del gobierno con la digitalización de 28,000 expedientes laborales y el centro de datos, con una inversión de 505 millones de pesos que triplicó la capacidad de almacenamiento de información. También señaló que sobre más de 3,000 puntos de conexión a internet en dependencias y espacios públicos.
+En materia laboral reportó incrementos salariales de entre 5 y 30% durante la administración en beneficio de 13,117 trabajadores. Dijo se mejoraron los ingresos de 1,012 personas jubiladas que percibían menos de un salario mínimo y se modificó el régimen salarial de 431 personas que realizaban labores de riesgo.
+En infraestructura informó que se recuperaron e incorporaron 436 inmuebles al patrimonio estatal, asimismo se dio mantenimiento a 95% de los inmuebles gubernamentales, además de conservar espacios de convivencia como el Parque Cultural Hidalguense, que desde su apertura ha recibido aproximadamente 1 millón de visitantes. Y sin duda que el Parque Cultural Hidalguense ha sido un espacio muy importante en la capital del Estado para la recreación, sí, para el arte, para la cultura, pero también para diversas actividades sociales y de beneficencia. En fin, ha sido un espacio muy relevante este del Parque Cultural Hidalguense, a cargo de la Oficialía Mayor, cuyo titular, Orlando Ángeles, por primera ocasión, o se convirtió en el primer titular de la Oficialía Mayor en ser parte de esta glosa del informe, en ser parte de las comparecencias ante el Congreso.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zyS6YT_lM4UwTg0HZZ8KrmJ0xMilK-lV/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Por otra parte, en respaldo a la Confederación de Cámaras Nacionales de Comercio, Servicios y Turismo, la Concanaco Servytur, el gobernador Julio Menchaca participó en su Asamblea Nacional, espacio en el que hizo un llamado a este sector, al empresarial, para continuar trabajando en sinergia para generar bienestar en beneficio de las familias mexicanas. En este contexto, esto es parte de lo que dijo el mandatario estatal.
+“En Hidalgo estamos haciendo nuestra parte, se están generando una enorme cantidad de empleo y hacemos una invitación para que haya actividad económica, haya prosperidad, haya bienestar compartido y que esa sinergia del gobierno federal, con nuestra presidenta, con los gobiernos estatales, con los gobiernos municipales, sea un ejercicio permanente para la construcción del México que queremos, del México que merecemos”.
+El titular del Ejecutivo estatal reconoció a quienes integran la Confederación, pues su esfuerzo, dijo, labor y liderazgo impacta y se traduce en beneficios para sus comunidades, municipios y estados, encabezados esta confederación por Octavio de la Torre de Stéffano, presidente nacional de la Concanaco Servytur. Por su parte, Higinio Martínez Miranda, presidente de la Mesa Directiva del Senado, reconoció a las y los empresarios por ser generadores de empleo en sus respectivos entornos, por lo que señaló la importancia de brindar facilidades para el correcto desarrollo de sus actividades. Al respecto, Ivar Resendis Ramírez, presidente municipal de Ezequiel Montes, coincidió en que las administraciones estatales y municipales pueden apoyar a las micro y pequeñas empresas en su regularización mediante la simplificación de trámites burocráticos. De esa forma, la presencia del gobernador hidalguense en la Asamblea Nacional de la Concanaco Servytur fortaleció el diálogo con uno de los sectores clave para la economía nacional.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18R_Nkv4hA33FWiLwohrtvGkDYfP7HLrr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/FN.39/2026</t>
+  </si>
+  <si>
+    <t>Menchaca fortalece cooperación hacendaria con la Unión Europea.</t>
+  </si>
+  <si>
+    <t>Cooperación internacional</t>
+  </si>
+  <si>
+    <t>Permítame compartirle información acerca de este estrechar relaciones con la Unión Europea y en temas en temas muy puntuales. Como parte de las acciones para fortalecer las capacidades institucionales de Hidalgo, el gobernador Julio Menchaca Salazar recibió a Stefan Agne, en ministro, consejero y jefe de cooperación de la Delegación de la Unión Europea en México, y a Raúl Carrillo Ruiz, coordinador del proyecto EU4, con quienes dialogó sobre nuevas oportunidades de colaboración en beneficio de la entidad.
+Durante el encuentro, en el que también participó la Secretaría de... la Secretaria de Hacienda, María Esther Ramírez Vargas, se analizaron mecanismos de trabajo conjunto e intercambio de experiencias en el marco del modelo hacendario estatal para la cohesión social, orientado a vincular la modernización de las finanzas públicas con las prioridades de desarrollo de la entidad.
+En esta reunión, forma parte, esta reunión forma parte de los esfuerzos de la actual administración para establecer vínculos estratégicos con organismos internacionales, aprovechar buenas prácticas y avanzar hacia una gestión más eficiente capaz de traducir el uso responsable de los recursos públicos en resultados positivos para la población. Lo que se informa sobre este tema, esta reunión con representantes de la Unión Europea.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nAFragHv-dR6DGV3BZlr1niiUAAIyDR9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Stefan Agne, Raúl Carrillo Ruiz, María Esther Ramírez Vargas</t>
+  </si>
+  <si>
+    <t>Nidia Torres</t>
+  </si>
+  <si>
+    <t>Una persona falleció en la Autopista Arco Norte, luego de que una pipa volcara y provocara afectaciones al tránsito en dirección a Querétaro, a la altura del municipio de Atitalaquia. De acuerdo con información de Protección Civil y Bomberos, el primer incidente ocurrió en el kilómetro 94+400, en el tramo de bajada de Apaxco hacia el municipio mencionado. En ese sitio, una pipa volcó y presentó fisuras en varios puntos de su estructura, tras impactarse lateralmente del lado izquierdo, lo que ocasionó el derrame del diésel que transportaba sobre la zanja central de la autopista. Debido al congestionamiento vehicular generado por este percance, un camión tipo Torton y una camioneta Nissan que se encontraban detenidos por el tráfico fueron impactados por un tráiler. En este accidente en particular, el copiloto de la camioneta perdió la vida al quedar prensado al interior de la unidad. Personal de Bomberos y Protección Civil acudió al lugar para realizar labores de atención a la emergencia, control y prevención de riesgos, en coordinación con las autoridades correspondientes. Cabe destacar que la zona fue acordonada por elementos de Guardia Nacional, División Carreteras, en tanto se notificó lo sucedido a personal de la Procuraduría General de Justicia del Estado de Hidalgo para las investigaciones correspondientes y el posterior retiro del cuerpo por parte del Servicio Médico Forense.</t>
+  </si>
+  <si>
+    <t>PGJEH</t>
+  </si>
+  <si>
+    <t>Levantamiento de cuerpo</t>
+  </si>
+  <si>
+    <t>Atitalaquia</t>
+  </si>
+  <si>
+    <t>Una persona falleció en la autopista Arco Norte luego de que una pipa volcara y provocara afectaciones al tránsito en dirección a Querétaro, la altura del municipio de Atitalaquia, que de acuerdo con información de Protección Civil y Bomberos, el primer incidente ocurrió en el kilómetro 94 más 400 en el tramo de bajada de Apaxco hacia el municipio mencionado. En ese sitio, una pipa volcó y presentó fisuras en varios puntos de su estructura tras impactarse lateralmente del lado izquierdo, lo que ocasionó el derrame del diésel que transportaba sobre la zanja central de la autopista. Debido al congestionamiento vehicular generado por este percance, un camión tipo Thornton y una camioneta Nissan, que se encontraban detenidos por el tráfico, fueron impactados por un tráiler. En ese accidente en particular el copiloto de la camioneta perdió la vida al quedar prensado al interior de la unidad. Personal de bomberos y protección civil acudió al lugar para realizar labores de atención a la emergencia, control y prevención de riesgos en coordinación con las autoridades correspondientes. Cabe destacar que la zona fue acordonada por elementos de Guardia Nacional, División Carreteras, en tanto se notificó lo sucedido a personal de la Procuraduría General de Justicia del Estado de Hidalgo para las investigaciones correspondientes y el posterior retiro del cuerpo por parte del Servicio Médico Forense.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hpFHq57dP-rKj-1h6Z0Ir9PT3VZfEXsV/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SSPH/Bol.988/2026</t>
+  </si>
+  <si>
+    <t>SSPH desarticula punto de narcomenudeo en Tolcayuca y asegura a una mujer reincidente</t>
+  </si>
+  <si>
+    <t>SSPH</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>Tolcayuca</t>
+  </si>
+  <si>
+    <t>Como resultado de labores de inteligencia operativa y acciones permanentes contra el narcomenudeo, la Secretaría de Seguridad Pública de Hidalgo desarticuló un presunto punto de venta y distribución de drogas en Tolcayuca, donde fueron aseguradas 380 dosis de presuntos narcóticos y también una mujer con antecedentes de detención por este mismo delito. La intervención se realizó mediante una orden de cateo en un inmueble ubicado en la colonia El Tildio. De hecho, en el operativo participaron elementos de la Secretaría de Seguridad Pública de Hidalgo, en coordinación también con la Procuraduría General de Justicia del Estado de Hidalgo, la Secretaría de la Defensa Nacional y también la Guardia Nacional. Durante la diligencia fue detenida una mujer identificada con las iniciales JTZ, originaria de la Ciudad de México, quien de acuerdo con información policial había sido arrestada años atrás por su probable participación en actividades relacionadas con narcomenudeo. En el lugar también se incautaron 260 dosis de hierba seca con características similares a la marihuana y 120 de una sustancia granulada con características propias del cristal. Además, también se localizaron la báscula de precisión, bolsas de plástico presuntamente utilizadas para dosificar drogas, una libreta con anotaciones, un teléfono celular y 3.166 pesos en efectivo. Cabe precisar que la detenida es madre de Nigel Iván Lozano Tinoco, alias El Pestañas, quien permanece recluida en el Centro de Reinserción Social en Pachuca desde el paso 3 de febrero del 2025 por un proceso relacionado con el delito de homicidio calificado. La mujer y los indicios también quedaron a disposición de la autoridad competente para poder dar continuidad a las investigaciones correspondientes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YP1RmieAgTANWQJzYQWoB8nuF0cUnrcs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Daniel Martínez sobre el retraso en la construcción del Centro de Acopio Lechero de Tulancingo comentó: Ahora sí que ahí a la espera, esperemos que la gestión de los recursos no termine siendo como... Le voy a pedir a la Secretaría de Salud que revise el asunto de la calidad de la leche en la región y bolas, don Cuco. Que la Secretaría de Salud le responde. Ya la estamos revisando. ¿Cuál petición? A ver si hay gestión al respecto. ¿O qué se hace con el terreno? ¿O si existe la certeza legal del terreno?</t>
+  </si>
+  <si>
+    <t>Centro de Acopio Lechero</t>
+  </si>
+  <si>
+    <t>Ahora sí que ahí a la espera, esperemos que la gestión de los recursos no termine siendo como... Le voy a pedir a la Secretaría de Salud que revise el asunto de la calidad de la leche en la región y bolas, don Cuco. Que la Secretaría de Salud le responde. Ya la estamos revisando. ¿Cuál petición? A ver si hay gestión al respecto. ¿O qué se hace con el terreno? ¿O si existe la certeza legal del terreno?</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A8vGGXYYeHY2EX1HE3Xrp55vaVEkkjow/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEPH realiza el concurso de oratoria “Mi palabra es hoy mi voz y mi fortaleza 2026”</t>
+  </si>
+  <si>
+    <t>Básica</t>
+  </si>
+  <si>
+    <t>Concurso De Oratoria</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública del Estado de Hidalgo señala acerca del concurso, el cuarto concurso de oratoria "Mi palabra es hoy mi voz y mi fortaleza 2026", realizado con el objetivo de fortalecer las habilidades lingüísticas de las y los estudiantes y promover la pluralidad de voces, el reconocimiento de las lenguas originarias, la lectura crítica, la escritura reflexiva y la expresión corporal. Como parte del impulso a la educación que promueven el gobierno de Julio Menchaca Salazar y el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, la SEPH genera espacios para que niñas, niños y adolescentes fortalezcan su expresión oral, desarrollen el pensamiento crítico y ganen confianza para expresar sus ideas ante el público. El concurso reunió a estudiantes de educación básica, quienes demostraron sus habilidades de expresión, argumentación y dominio de la palabra en las tres categorías participantes. En la categoría A, correspondiente a nivel preescolar, ¡mire qué padre desde los chavitititos!, el primer lugar fue para Ivana Guadalupe Paulina Barró, del preescolar general "Club de Leones", el segundo lugar lo obtuvo Valentina Quiterio Quiterio, del preescolar general "Diego Alarcón de Ocaña", y el tercer lugar correspondió a Elías Dionicio Hernández, del preescolar general "El Principio del Saber", los tres planteles pertenecientes al municipio de Ixmiquilpan. En el caso del nivel primaria, la categoría B, el primer lugar fue para Antonio de Jesús Lara Durango, de la primaria general "Lauro Aguirre" de Huejutla, el segundo lugar lo obtuvo Elías Caín Martínez Cruz, de la primaria general "Alfonso Cravioto" de Zimapán, y el tercer lugar fue para Frida Chantal Isidro Hernández, de la primaria indígena "Progreso", esto en Cardonal. En tanto que en secundaria categoría C, el primer lugar fue para Dylan Isaí Lira Aguirre, de la telesecundaria 332 de Cuautepec, ¡abrazote hasta Cuautepec!, el segundo lugar lo obtuvo Yoselin Montes Galloso, de la telesecundaria 508 de San Bartolo Tutotepec, también para él un gran abrazo, y también para María José Pérez Sandoval, de la escuela secundaria "Jesús Romero Flores" ubicada en Apan. A través de estas actividades, las y los estudiantes tuvieron la oportunidad de compartir sus ideas, demostrar su talento y reconocer la diversidad cultural y lingüística de Hidalgo a través de la palabra como medio de expresión y aprendizaje, que es precisamente la intención de este tipo de certámenes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nN2weqIy0AQEcL4l1xbeeRD1akaJO_So/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>PGJEH/Bol.074/2026</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia del Estado de Hidalgo contempla fortalecer su estructura para poder atender de manera específica los casos de extorsión mediante la creación de la fiscalía especializada, que podría comenzar sus funciones en el 2027. Por su parte, Francisco Ángel Fernández Hasbun, quien es encargado del despacho de la Procuraduría, explicó que actualmente este tipo de investigaciones son canalizadas a la Unidad de Atención al Secuestro. Sin embargo, se busca conformar un grupo especializado que pueda permitir ampliar las capacidades de investigación y atención de estos delitos. La nueva área estaría integrada por aproximadamente 50 personas, esto como parte de un proceso. La Procuraduría estará realizando una revisión de los recursos humanos, materiales y operativos también con los que cuenta, además de preparar al personal ministerial que estaría participando en esta fiscalía. El anuncio se realizó durante la comparecencia de Fernández Hasbun ante el Congreso de Hidalgo, esto como parte de la revisión del cuarto informe de gobierno estatal. Durante el encuentro con legisladores, también se dio a conocer un avance en la investigación por el homicidio del estudiante del Mexe y de acuerdo con el encargado de la Procuraduría, las autoridades judiciales concedieron tres órdenes de aprehensión relacionadas con este homicidio calificado de José Antonio Salgado Aparicio, alumno de la Escuela Normal Rural Luis Villarreal. El estudiante fue encontrado, recordemos, sin vida el pasado 7 de septiembre de 2026. La Procuraduría confirmó la obtención de las tres órdenes; aunque no se informó como tal si hasta el momento habían sido ejecutadas ni si se dieron a conocer tampoco algunos detalles sobre las personas señaladas dentro de esta investigación.</t>
+  </si>
+  <si>
+    <t>Con el Procurador de Justicia del Estado Hidalgo se cierran las comparecencias y hace anuncio acerca de una nueva Fiscalía. Es correcto, Daniel. Pues bien, resulta que la Procuraduría General de Justicia del Estado Hidalgo contempla fortalecer su estructura para poder atender, pues de manera específica, los casos de extorsión mediante creación de la Fiscalía Especializada que podría comenzar sus funciones en el 2027. Pero bien, por su parte, Francisco Ángel Fernández Hasmón, quien es encargado del despacho de la Procuraduría, explicó que actualmente este tipo de investigaciones son canalizadas a la unidad de atención al secuestro. Sin embargo, se busca conformar un grupo especializado que pueda permitir ampliar las capacidades de investigación y atención de estos delitos. La nueva área estaría integrada por aproximadamente 50 personas, esto como parte de un proceso, Y bien la Procuraduría estar realizando una revisión de los recursos humanos materiales y operativos también con los que cuenta además de preparar al personal ministerial que estar participando en esta fiscal El anuncio se realizó durante la comparecencia de Fernández Hasbun ante el Congreso de Hidalgo, esto como parte de la revisión del cuarto informe de gobierno estatal, y durante el encuentro con legisladores también se dio a conocer un avance en la investigación para el homicidio del estudiante del Meche, y de acuerdo con el encargado de la Procuraduría, las autoridades judiciales concedieron tres órdenes de aprehensión relacionadas con este homicidio calificado, José Antonio Salgado Aparicio, alumno de la Escuela Normal Luis Villarreal, y pues el estudiante fue encontrado, recordemos, sin vida el pasado 7 de septiembre del 2026. Y resulta que la Procuraduría confirmó la obtención de los tres órdenes, aunque no, no se informó como tal si hasta el momento pues habían sido ejecutadas ni si se dieron a conocer tampoco pues algunos detalles sobre las personas señaladas dentro de esta investigación.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yGhbq9NLK64JDPUg22AKmeNCtHT2Ks7Z/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun</t>
+  </si>
+  <si>
+    <t>Más de seis años han pasado desde el inicio de la construcción del Centro de Acopio Lechero del Valle de Tulancingo, y no existe por lo menos en este momento, indicio alguno de retomar y finalizar su construcción y equipamiento. Durante la comparecencia de Napoleón González Pérez, titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh) ante el Congreso del Estado de Hidalgo, fue cuestionado sobre el tema por el diputado local por Tulancingo, Arturo Gómez Canales. El funcionario respondió ante los legisladores locales que el proyecto corresponde al Gobierno Federal, asegurando que está considerado retomar la obra, junto con el Centro de Acopio Lechero de Tizayuca, el cual también están detenidos los trabajos de construcción y equipamiento. Señaló que para seguir adelante con ambos proyectos, se requiere de presupuesto por aproximadamente 80 millones de pesos. A finales de julio de 2020 fue iniciada la obra en un predio de mil 676.64 metros cuadrados, ubicado en la localidad de San Nicolás el Chico, en Tulancingo. El proyecto está a cargo del gobierno federal a través de Seguridad Alimentaria Mexicana (Segalmex), por medio de su filial Liconsa. Durante la ceremonia de colocación de la primera piedra, se aseguró que la inversión total sería de aproximadamente 12 millones de pesos. De dicha inversión, seis millones serían para la construcción de las instalaciones y los seis millones restantes, en equipamiento. Durante la ceremonia de inicio de construcción, se informó que el espacio tendría capacidad para recibir hasta 30 mil litros de leche diariamente, garantizando a más de 450 productores en la región recibir un precio de garantía adecuado por el alimento. Para el proyecto, el Municipio de Tulancingo aportó el terreno, el gobierno de Hidalgo se encargó de la construcción del inmueble, y el equipamiento especializado correspondía al entonces organismo federal Segalmex. Pero las instalaciones están abandonadas desde hace por lo menos 4 años, incluso siendo ya saqueadas y vandalizadas; testimonios de vecinos en la zona señalan que incluso personas se quedan a pernoctar en el interior. En visita de trabajo realizada en el Valle de Tulancingo a finales del mes de julio de este año, González Pérez recordó que en la inversión considerada para concretar ambos centros de acopio lechero, se deben considerar varios puntos. “No es nada más tener la instalación, es el laboratorio, los tanques, todo el equipamiento, además de los accesos”. En una visita posterior a la misma región realizada el pasado mes de septiembre, el funcionario estatal insistió que siguen las gestiones para contar con recursos que permitan finalizar la construcción y equipamiento de ambos espacios, en Tizayuca y Tulancingo. Enfatizó que junto con dichas gestiones, se revisan detalles legales; en el caso de Tulancingo, por ejemplo, la propiedad del terreno, para tener la certeza de aplicar los eventuales recursos públicos en forma adecuada.</t>
+  </si>
+  <si>
+    <t>Arturo Gómez Canales</t>
+  </si>
+  <si>
+    <t>Las rondas de comparecencias sobre el cuarto informe del gobernador Julio Menchaca Salazar ya concluyeron en la 66 Legislatura del Congreso del Estado. Orlando Ángeles, el oficial mayor del gobierno estatal, fue el último en presentarse ante los diputados locales. Esta es la primera vez en la historia que un oficial mayor comparece en este contexto. Durante su intervención, habló sobre el uso de los recursos públicos y confirmó que el 99% de los contratos en la administración de Menchaca se otorgaron mediante licitaciones públicas. Se discutieron 313 contratos entre enero y septiembre, y el oficial mencionó que se impusieron penalizaciones a 35 contratos y se rescindieron seis por incumplimiento, con un valor total de 68 millones de pesos. Se destaca que esta comparecencia fue una de las más informativas de toda la serie, lo que permitió a los diputados conocer más sobre el desempeño de la oficialía en la administración de Julio Menchaca. También se resaltó que se han recuperado aproximadamente 500 inmuebles que estaban abandonados, lo que ha reducido costos para el gobierno del estado. Además, se mencionó que el porcentaje de licitaciones públicas ha aumentado del 66% al 99%, lo que significa que ya no se realizan a puerta cerrada, como ocurría antes. El oficial mayor explicó que existen diferentes mecanismos para asignar obras, como licitaciones públicas y directas, y que la mayoría de las asignaciones actuales se realizan a través de convocatorias y concursos abiertos.</t>
+  </si>
+  <si>
+    <t>Concluyeron ya las rondas, las agendas de comparecencias en la glosa del cuarto informe del gobernador Julio Menchaca Salazar allá en la 66 legislatura, en la sede del Congreso del Poder Legislativo de nuestro Estado el oficial mayor del gobierno del Estado, Orlando Ángeles, fue el último en comparecer ante las y los diputados locales en la primera vez en un hecho histórico, es la primera vez que un oficial mayor comparece en la glosa del informe ante los diputados locales, habló por supuesto del uso de los recursos públicos y entre las noticias que surgen de esta comparecencia, el oficial mayor Orlando Ángeles confirmó el 99% de las contrataciones, es decir, de los contratos que el gobierno del estado establece al menos en lo que se refiere a la administración del gobernador Tulio Menchaca fueron otorgados a través de licitaciones públicas. El 99% dice parte de esta comparecencia, de enero a septiembre se dictaminaron 313 contratos de los cuales 99% fueron mediante licitación pública. El oficial mayor dijo que durante la administración se aplicaron penalizaciones a 35 contratos y se rescindieron 6 por incumplimiento, cuyo valor ascendía a 68 millones de pesos. Mucha informaci dicen hoy los principales titulares de los medios de comunicaci en Hidalgo que fue una de las comparecencias m nutridas de esta bater de esta agenda que significa la glosa del cuarto informe de gobierno y bueno, qué bien que las y los diputados decidieron ampliar el espectro de, no solamente al gabinete del gobernador Julio Manchaca, sino también a la Oficialía Mayor para hablar sobre las tareas que se han llevado a efecto, las metas que han logrado en la administración de Julio Manchaca. Aldo Falcón. Andrés, también durante esta comparecencia me llamó mucho la atención la recuperación de al menos, bueno, más o menos 500 inmuebles, inmuebles, los cuales estaban abandonados o también se encontraban en algunas afectaciones, reduciendo un costo para el gobierno del Estado. Igual sobre lo que dabas a conocer sobre esto de las licitaciones que avanzaron del 66% al 99%, ya no son a puerta cerrada. Bueno, pues si son licitaciones públicas, pues no pueden ser a puerta cerrada. Anteriormente se realizaban así, y lo que he dado a conocer... La ley contempla la asignación directa para el tema de otorgar obra por parte del gobierno a particulares, hay varios mecanismos, uno de ellos son las licitaciones públicas, otro de ellos es las licitaciones directas. El oficial mayor ayer se refirió específicamente a este asunto, el 99% de las asignaciones que se han hecho han sido asignaciones abiertas, públicas, asignaciones que se hacen a través de una convocatoria y por supuesto se concursa para obtenerla</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pESs3LocZxtVpZyLqog3CfQxp5Jax_lG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar comenta: participé en la Asamblea Nacional de Concanaco Servytur, donde tuve la oportunidad de conversar con el sector empresarial sobre Hidalgo, es una potencia en marcha y su ubicación estratégica, su crecimiento industrial, disposición de colaboración, atraer nuevas inversiones y oportunidades para la familia. La oportunidad de conversar. Ayer el gobernador estuvo en este evento de la Cámara de Canaco Servytur, la Cámara Nacional de Comercio, Servicios, y bueno, los temas empresariales son fundamentales.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar comenta Participé en la Asamblea Nacional de Concanaco Servytur Donde tuve la oportunidad de conservar con el sector empresarial Sobre Hidalgo es una potencia en marcha Y su ubicación estratégica Su crecimiento industrial, disposición de colaboración Atraer nuevas inversiones y oportunidades para la familia La oportunidad de conversar No de conservar, conversar Ayer el gobernador estuvo en este evento de la Cámara de La Canaco Servytur Ayer el gobernador estuvo en este evento de la Cámara de Canaco Servytur, la Cámara Nacional de Comercio, Servicios, y bueno, los temas empresariales son fundamentales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gtjanN4c-TqOmT4fVIJdOGe6abyHKDTP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar sostuvo una reunión con Stefan Agne, ministro consejero y jefe de cooperación de la Delegación de la Unión Europea en México, y con Raúl Carrillo Ruiz, coordinador de proyectos de la Unión Europea ( EU4Equity), con quienes dialogó sobre nuevas oportunidades de colaboración en beneficio del estado. En el encuentro también participó la secretaria de Hacienda, María Esther Ramírez Vargas, donde analizaron mecanismos de trabajo conjunto e intercambio de experiencias en el mercado del modelo hacendario estatal para la cohesión social, orientado a vincular la modernización de las finanzas públicas con las prioridades para el desarrollo en Hidalgo. Esta reunión forma parte de los esfuerzos que la actual administración de Hidalgo realiza para establecer vínculos estratégicos con organismos internacionales, aprovechar las buenas prácticas y avanzar hacia una gestión más eficiente capaz de traducir el uso responsable de los recursos públicos en resultados positivos para la población. Ayer, el gobernador de nuestro estado recibió ahí en sus oficinas a representantes de la Unión Europea, a este señor que se llama Stefan Agne y a Raúl Carrillo Ruiz, ellos representantes de la Unión Europea. El tema: los dineros, los negocios.</t>
+  </si>
+  <si>
+    <t>Ayer el gobernador del estado de Hidalgo, el licenciado Julio Menchaca Salazar, se reunió, recibió aquí en sus oficinas de Palacio de Gobierno aquí en Pachuca, a Estefan Agne, que es ministro, consejero y jefe de cooperación de la Delegación Europea en México, y a Raúl Carrillo Ruiz, coordinador de proyectos de la Unión Europea, las siglas son EU4Equity, con quienes dialogó sobre nuevas oportunidades de colaboración en beneficio de nuestro Estado. En el encuentro también participó la Secretaria de Hacienda, María Esther Ramírez Vargas, y todos analizaron algunos mecanismos de trabajo conjunto e intercambio de experiencias en el mercado del modelo hacendario estatal para la cohesión social orientado a vincular la modernización de las finanzas públicas con las prioridades para desarrollo en Hidalgo. En esta reunión forma parte de los esfuerzos que la actual administración de Hidalgo realiza para establecer vínculos estratégicos con organismos internacionales, aprovechar las buenas prácticas y avanzar hacia una gestión más eficiente Capaz de traducir el uso responsable de los recursos públicos en resultados positivos para la población Ayer el gobernador de nuestro estado recibió en sus oficinas a representantes de la Unión Europea A este señor que se llama Stefan Agne y a Raúl Carrillo Ruiz, ellos representantes de la Unión Europea El tema, los dineros, los negocios</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14_MqqYnb9GWOfkhqJVxNM2UmsY91sYks/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Stefan Agne, María Esther Ramírez Vargas, Raúl Carrillo Ruiz</t>
+  </si>
+  <si>
+    <t>Seguimos fuera del aire allá en el 91.1 de frecuencia modulada La Voz de la Sierra Gorda, la mala noticia es que no solamente seguimos fuera del aire, sino que ni el área administrativa ni el área de ingeniería Radio y Televisión de Hidalgo mueve un dedo para tratar de solucionar este tema. Desafortunadamente la Dirección de Radio no cuenta con recursos técnicos ni mucho menos con recursos administrativos y económicos para solucionar el tema de la transmisión. Nosotros ya hicimos lo que nos correspondía, hicimos el llamado a las autoridades correspondientes para que nos ayuden a solucionar este problema. Mientras tanto, bueno, pues yo les pido que sigamos en redes sociales, estas que tanto nos quieren quitar para que podamos estar en comunicación allá en Zimapán, en Jacala, en por supuesto Pisaflores, Chapulhuacán, en la Misión, Pacula.</t>
+  </si>
+  <si>
+    <t>Seguimos fuera del aire allá en el 91.1 de frecuencia modulada, la voz de la sierra gorda, la mala noticia es que no solamente seguimos fuera del aire, sino que ni el área administrativa, ni el área de ingeniería radio y televisión de algo mueve un dedo para tratar de solucionar este tema. Desafortunadamente la dirección de radio no cuenta con recursos técnicos, Ni mucho menos con recursos administrativos y económicos Para Pues Solucionar el tema de la transmisión Nosotros ya hicimos lo que nos correspondía Hicimos el llamado A las autoridades correspondientes Para que nos ayuden a solucionar este problema Mientras tanto, bueno pues Yo les pido que sigamos en redes sociales Estas que tanto nos quieren quitar Para que podamos estar en comunicación Allí en Zimapán, en Jacala En por supuesto Pisaflores Chapulhuacán en la misión Pacula</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D5BfUnsbkxt-oM8sKpPhsUf67bsm-KmI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud inició ya la campaña de vacunación invernal en todas las clínicas, hospitales, centros de salud de nuestro estado, en las clínicas, hospitales, centros de salud públicos. Hay vacunas para la influenza estacional y también para el COVID. Acuda junto con su familia, acuda, por favor, a estos centros para que sean vacunados, principalmente los niños menores de 5 años, también los adultos mayores, las personas que tengan enfermedades crónico-degenerativas. Es muy importante que estén bien inmunizados en esta temporada invernal que ya se acerca y que se adelanta, como todos los años.</t>
+  </si>
+  <si>
+    <t>Recuerde que la Secretaría de Salud inició ya la campaña de vacunación invernal en todas las clínicas, hospitales, centros de salud de nuestro estado, en las clínicas, hospitales y centros de salud públicos. Hay vacunas para la influenza estacional y también para el COVID. Acuda junto con su familia, acuda por favor a estos centros para que sean vacunados principalmente los niños menores de 5 años, También los adultos mayores Las personas que tengan enfermedades crónico-degenerativas Es muy importante que estén bien inmunizados En esta temporada invernal Que ya se acerque, que se adelanta Como todos los años, se adelanta El invierno empezará por ahí así Del 20 de diciembre Por ahí así del 20 de diciembre Y hasta marzo del año próximo Será la temporada invernal La época invierno Pero bueno, pues los frentes fríos ya Afectan buena parte del país por supuesto incluyendo Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1e5x9bhZLm9F3m7cxalKYjp0mp6o2CqIv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos informa a la población que, para este 23 de octubre de 2026, de acuerdo con el aviso meteorológico del 589 del pronóstico meteorológico general del Servicio Meteorológico Nacional, se pronostican chubascos de lluvia puntuales a fuertes de 25 a 50 mm, principalmente en las regiones norte y este del estado de Hidalgo. Asimismo, se pronostican temperaturas de 0 a 5 °C con vientos de 10 a 20 km/h con rachas de 30 a 50 km/h.</t>
+  </si>
+  <si>
+    <t>Aldo Falcón</t>
+  </si>
+  <si>
+    <t>Es muy importante, les repito, que estemos atentos a las emisiones de Radio Televisión Hidalgo porque hay un llamado de la Subsecretaría de Protección Civil. Aldo Farcón. Así es, la Subsecretaría de Protección Civil y Gestión de Riesgo informa a la población que para este 23 de octubre de 2026, de acuerdo con el aviso meteorológico de 589 del Pronóstico Meteorológico General del Servicio Meteorológico Nacional, se pronostican chubascos de lluvia puntales a fuertes de 25 a 50 milímetros, Principalmente en las regiones norte y este del estado ideal Asimismo se pronostican temperaturas de 0 a 5 grados centígrados Con vientos de 10 a 20 kilómetros por hora Con rachas de 30 a 50 kilómetros por hora Muy bien, bueno, pues ahí está la advertencia que nos hace El llamado que nos hace la solicitud de la subsecretaría de protección civil Les repito, dependiente de la Secretaría de Gobierno del estado Para estar muy atentos, sobre todo en las zonas altas de nuestro estado Se esperan temperaturas de hasta 0 grados es decir, se esperan heladas ya en algunas partes de nuestro estado hay que estar muy atentos hay que por supuesto salir si usted va a salir a su trabajo a la escuela si va a realizar sus actividades No olvide ponerse bien su su Porque vamos a tener Mucho frío estos por lo menos estos Dos días, ¿no? El fin de semana ¿No, Falcón? Así es, Andrés, hay que bajar Como bien me dijiste, hay que salir bien abrigados Porque se esperan bajas temperaturas .</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jrAfQ146okEHiDot-793ovwqKlUDqLZo/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Andrés Torres: Oye, ¿qué tal este la dirección general de radio y televisión de algo que insiste en quitarnos el programa, en quitarnos nuestras redes sociales, en quitarnos de la programación? Si supiera que el gobernador del estado Hidalgo es suscriptor de Las Voces Radio y todas las mañanas por ahí así de las 5 de la mañana estamos ya en contacto enviándole información, intercambiando pues por supuesto conceptos y claro que junto con otros muchos cientos de seguidores de Las Voces todas las mañanas nos informan, nos dan a conocer cuál es el estado del clima, cuál es el estado de tránsito.</t>
+  </si>
+  <si>
+    <t>Acoso laboral</t>
+  </si>
+  <si>
+    <t>Oye, ¿qué tal la Dirección General de Radio y Televisión de Algo que insiste en quitarnos el programa, en quitarnos nuestras redes sociales, en quitarnos de la programación? Si supiera que el gobernador del estado de Hidalgo es suscriptor de las vocales radio, y todas las mañanas, por ahí así a 5 de la mañana, estamos ya en contacto enviándole información, intercambiando, pues por supuesto, conceptos, Y claro que junto con otros muchos cientos de seguidores de las vocales Todas las mañanas nos informan, nos dan a conocer cuál es el estado del clima Cuál es el estado del tránsito Les agradecemos de verdad muchísimo a todas y a todas las personas Que diariamente se ponen en contacto a través de las redes sociales Aquí no tenemos teléfono, aquí está cortado el teléfono Y se ponen en contacto con las vocales radio Les agradecemos de verdad muchísimo Y bueno, pues es la historia de las vocales Ese es el verdadero periodismo No la propaganda No la autoproclamación Y sobre todo la autocomiseración No, aquí sí trabajamos Y afortunadamente tenemos el apoyo de nuestro auditorio Cosa que les agradecemos infinitamente</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FJ_9DaaXqII7DjCZdcTaoUxwNeoPHbaA/view?usp=drivesdk</t>
   </si>
 </sst>
 </file>
@@ -1409,8 +1314,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X33" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X33" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X22" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X22" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1806,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -1880,131 +1785,135 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C2" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D2" s="5"/>
+        <v>46318</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="E2" s="5" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="5">
+        <v>112</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="S2" s="5">
-        <v>110</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="V2" s="5"/>
       <c r="W2" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E3" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>22</v>
@@ -2013,28 +1922,28 @@
         <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S3" s="3">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -2043,29 +1952,31 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="C4" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>5</v>
@@ -2080,494 +1991,522 @@
         <v>20</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S4" s="3">
-        <v>122</v>
+        <v>358</v>
       </c>
       <c r="T4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="X4" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="C5" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E5" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S5" s="3">
+        <v>156</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="3" t="s">
+      <c r="V5" s="3"/>
+      <c r="W5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Q5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S5" s="3">
-        <v>10</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="C6" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D6" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E6" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="S6" s="3">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U6" s="3"/>
+        <v>61</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="C7" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E7" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="S7" s="3">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="T7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
+      <c r="W7" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="C8" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D8" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" s="3">
+        <v>119</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S8" s="3">
-        <v>114</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="W8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="C9" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D9" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E9" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S9" s="3">
+        <v>94</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S9" s="3">
-        <v>164</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S10" s="3">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>75</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="C11" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D11" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S11" s="3">
+        <v>108</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S11" s="3">
-        <v>141</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -2575,231 +2514,239 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E12" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S12" s="3">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
+      <c r="V12" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E13" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" s="3" t="s">
+      <c r="O13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S13" s="3">
+        <v>130</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S13" s="3">
-        <v>104</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="V13" s="3"/>
-      <c r="W13" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="W13" s="3"/>
       <c r="X13" s="3" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C14" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E14" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S14" s="3">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E15" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>5</v>
@@ -2808,291 +2755,307 @@
         <v>15</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
       <c r="R15" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="S15" s="3">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U15" s="3"/>
+        <v>61</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D16" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S16" s="3">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="W16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="C17" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D17" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="O17" s="3" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S17" s="3">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="W17" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="C18" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D18" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="O18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S18" s="3">
+        <v>98</v>
+      </c>
+      <c r="T18" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="W18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D19" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S19" s="3">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
@@ -3101,943 +3064,201 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="C20" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S20" s="3">
         <v>56</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S20" s="3">
-        <v>139</v>
-      </c>
       <c r="T20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>75</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="C21" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D21" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="S21" s="3">
+        <v>138</v>
+      </c>
+      <c r="T21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="W21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="C22" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D22" s="3"/>
+        <v>46318</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S22" s="3">
-        <v>251</v>
+        <v>69</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>14</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S23" s="3">
-        <v>306</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>13</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S24" s="3">
-        <v>82</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X24" s="3"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>12</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S25" s="3">
-        <v>114</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X25" s="3"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>10</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S26" s="3">
-        <v>71</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>9</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S27" s="3">
-        <v>268</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>8</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S28" s="3">
-        <v>133</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S29" s="3">
-        <v>189</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>6</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S30" s="3">
-        <v>69</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X30" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>4</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="S31" s="3">
-        <v>290</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="X31" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>3</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S32" s="3">
-        <v>98</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>2</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="6">
-        <v>46317</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="S33" s="3">
-        <v>134</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295D66AC-957B-49DA-BC1F-C320CE447CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBB646B-3E55-4CA5-AB4E-2E30873401D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -101,9 +101,6 @@
     <t>SEPH</t>
   </si>
   <si>
-    <t>Comparecencias</t>
-  </si>
-  <si>
     <t>Segobh</t>
   </si>
   <si>
@@ -158,51 +155,12 @@
     <t>Contenido</t>
   </si>
   <si>
-    <t>Canal del Pueblo</t>
-  </si>
-  <si>
-    <t>Andrés Torres</t>
-  </si>
-  <si>
-    <t>Vocales Radio</t>
-  </si>
-  <si>
-    <t>Muy negativo</t>
-  </si>
-  <si>
     <t>Radioescucha</t>
   </si>
   <si>
-    <t>Ultra 102.9 FM</t>
-  </si>
-  <si>
-    <t>Izza Hernández</t>
-  </si>
-  <si>
-    <t>Ultra Noticias1</t>
-  </si>
-  <si>
-    <t>Daniel Martínez</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>SSH</t>
-  </si>
-  <si>
     <t>Gobernador</t>
   </si>
   <si>
-    <t>RTVH</t>
-  </si>
-  <si>
-    <t>Alerta Meteorológica</t>
-  </si>
-  <si>
-    <t>Radiodifusoras</t>
-  </si>
-  <si>
     <t>Jesús Riveros</t>
   </si>
   <si>
@@ -212,12 +170,6 @@
     <t>Tulancingo</t>
   </si>
   <si>
-    <t>TV local</t>
-  </si>
-  <si>
-    <t>Vacunación</t>
-  </si>
-  <si>
     <t>Neutro</t>
   </si>
   <si>
@@ -233,383 +185,220 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Ultra Noticias</t>
-  </si>
-  <si>
     <t>Julio Menchaca</t>
   </si>
   <si>
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Positivo</t>
-  </si>
-  <si>
-    <t>Congreso del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Saderh</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez</t>
-  </si>
-  <si>
-    <t>Reunión con Empresarios</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor</t>
-  </si>
-  <si>
-    <t>Edgar Orlando Ángeles Pérez</t>
-  </si>
-  <si>
-    <t>Jacala</t>
-  </si>
-  <si>
-    <t>Reunión Con Empresarios</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1944/2026</t>
-  </si>
-  <si>
-    <t>Yazmin Leonardo</t>
-  </si>
-  <si>
-    <t>UTEC e ICATHI fortalecen la vinculación para la capacitación laboral y desarrollo profesional</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Firma De Convenio</t>
-  </si>
-  <si>
-    <t>Continuamos con más información. Le comparto que la Universidad Tecnológica de Tulancingo y el Instituto de Capacitación para el Trabajo del Estado de Hidalgo formalizaron un convenio de colaboración para sumar capacidades en materia de formación y capacitación, esto con el propósito de responder pues a las necesidades del sector productivo y ampliar las oportunidades de desarrollo profesional para estudiantes, egresados y población en general.
-El acuerdo fue suscrito por el rector de la UTEC, Tito Dorantes Castillo, y el director general del ICATHI, Jorge Israel Acosta Benítez, quienes encabezaron esta alianza entre ambas instituciones públicas.
-Uno de los principales alcances de este acuerdo es la posibilidad de desarrollar acciones conjuntas de evaluación y certificación de competencias laborales, a fin de reconocer los conocimientos, habilidades, destrezas y experiencias de las personas y fortalecer sus perfiles profesionales.
-El rector de la UTEC destacó que este convenio complementa eh pues el modelo educativo de la universidad, que se sustenta en la formación práctica, la innovación, el desarrollo tecnológico y la vinculación con los sectores productivo, público y social.
-Por su parte, el ICATHI ofrece alternativas de capacitación para que la población adquiera y fortalezca habilidades que faciliten su incorporación al mercado laboral.
-Durante Castillo señaló que esta alianza busca acercar la formación académica y la capacitación a las necesidades pues de empresas y organizaciones en un entorno laboral que demanda perfiles especializados y competencias demostrables.
-Este tipo de alianzas forman parte de la visión educativa del gobernador Julio Menchaca Salazar y del secretario de educación pública de Hidalgo, Natividad Castrejón Valdez, orientada a fortalecer la educación superior y su vinculación con las necesidades del Estado.
-Así la información, información de educación que con gusto les comparto</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1EHmDgLAwHaXZM_iLrvMqrdtqZzr9b3XZ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Tito Dorantes Castillo</t>
-  </si>
-  <si>
-    <t>Jorge Israel Acosta Benítez, Julio Menchaca, Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>Locutor Irving Sánchez da lectura a comentario de radioescucha que reporta el estado crítico de la entre Santiago Tulantepec y Tulancingo, abarcando desde el crucero de Genisa hasta después de Medias Tierras. Los reportes señalan que la ruta se encuentra en peores condiciones que un camino rural, con numerosos baches y hoyos incrementados por las recientes lluvias. A pesar de las afectaciones diarias para quienes transitan por la zona, los inconformes denuncian que las autoridades no han hecho nada para solucionar este problema que lleva años deteriorándose.</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Carretera En Mal Estado</t>
-  </si>
-  <si>
-    <t>"Reportan que en la carretera es cierto, o sea, la carretera Santiago-Tulancingo, Tulancingo-Santiago ya es imposible pasar desde el crucero de Geniza hasta después de Medias Tierras."   "A pesar de los reportes las autoridades no hacen nada y hay quienes todos los días deben circular por ahí hacia Santiago, hacia Tulancingo, viceversa."   "Sí, efectivamente, bueno, pues ya no es ni carretera, ya parece está peor que un camino rural."   "Está en muy malas condiciones y vaya que con la lluvia también se ha generado mucho más eh baches, hoyos ya..."   "y esto cabe aclarar que no es de este de estos eh últimos años, eso tiene mucho tiempo que se viene deteriorando este tramo de la carpeta asfáltica de la carretera, o bueno, de esa vía de comunicación hacia Santiago, Tulantepec y Tulancingo."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JSY9VWy046Iayrj3r-wg-InNk362CFUW/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>OM/Bol.SN-A/2026</t>
-  </si>
-  <si>
-    <t>En un hecho histórico para el Poder Legislativo de Hidalgo, el oficial mayor Edgar Orlando Ángeles Pérez compareció por primera vez ante las y los diputados de la Sexagésima Sexta Legislatura, como parte de la glosa del informe del gobernador Julio Menchaca Salazar. Durante su comparecencia, el funcionario expuso los avances en materia de transparencia y modernización, señalando las condiciones críticas en las que recibieron la administración —con documentación inconsistente, infraestructura obsoleta y bienes sin control—. Informó que de enero a septiembre de este año se han adjudicado 313 contratos por más de 2,558 millones de pesos (el 97% mediante licitación pública nacional), y destacó la aplicación de penalizaciones y rescisiones que evitaron un daño a las finanzas públicas superior a los 74 millones de pesos. Finalmente, resaltó las acciones de diagnóstico y regularización del patrimonio inmobiliario del estado para garantizar el uso responsable de los recursos públicos.</t>
-  </si>
-  <si>
-    <t>Y dando seguimiento a las comparecencias en el Congreso del Estado de Hidalgo, el Congreso Libre y Soberano del Estado de Hidalgo. Es histórico, por vez primera compareció un oficial mayor, y estoy refiriéndome a Edgar Orlando Ángeles Pérez, oficial mayor que reportó avances en transparencia y modernización, pero también destacó cómo recibió, cómo recibió esta administración los insumos, los artículos, la herramienta, el mobiliario para poder trabajar.
-En sesión ordinaria, el presidente de la Junta de Gobierno, diputado Andrés Velázquez Vázquez, dio la bienvenida al titular de la Oficialía Mayor, Edgar Orlando Ángeles Pérez, quien compareció en el Congreso del Estado Libre y Soberano de Hidalgo como parte del procedimiento relativo al cuarto informe del estado que guardan los diversos ramos de la administración pública encabezada por Julio Menchaca Salazar.
-Esta comparecencia representa un hecho histórico para el poder legislativo estatal al ser, reitero, la primera ocasión en que el titular de la Oficialía Mayor comparece ante las y los diputados de la Sexagésima Sexta Legislatura. Asimismo se precisó que cualquier funcionario de primer nivel de la administración pública estatal puede ser llamado a comparecer con el propósito de fortalecer la transparencia, la rendición de cuentas y el ejercicio de la vigilancia legislativa. No solamente los secretarios, algún titular puede ser llamado también en una comparecencia a que dé a conocer el estado que guarda la administración en su ramo.
-En su mensaje, el legislador destacó también la importancia de una administración pública ordenada, eficiente y transparente, basada en el uso responsable de los recursos, el cuidado del patrimonio público y la mejora de los procesos institucionales.
-Orlando Ángeles señaló cuál fue la mística, la meta al inicio de esta administración.
-'Al inicio de esta administración recibimos una instrucción clara: fortalecer el orden administrativo, mejorar el aprovechamiento de los recursos, modernizar los procedimientos y transparentar la gestión gubernamental'.
-'Encontramos deficientes documentación inconsistente, infraestructura tecnológica obsoleta y bienes muebles e inmuebles sin control ni aprovechamiento'.
-'Ante este escenario, realizamos la revisión de procesos, expedientes, infraestructura y bienes del estado. Emprendimos acciones de regularización, actualización y control'.
-'Restablecimos procedimientos claros y fortalecimos la coordinación institucional para generar resultados verificables'.
-'Nuestra labor se orientó a mejorar las condiciones en las que se opera las que operan las dependencias, optimizar los recursos, cuidar los bienes y dar certeza a los procedimientos administrativos'.
-'Primero, adquisiciones: uno de los asuntos que merece mayor claridad es el de las adquisiciones y contrataciones. Fortalecimos los procedimientos, la contratación, la coordinación entre las instancias participantes y los mecanismos para asegurar el cumplimiento de los contratos'.
-'El Comité de Adquisiciones, Arrendamientos y Servicios del Gobierno fue instalado desde el primer día, desde el primer día de esta gestión, el 5 de septiembre de 2022'.
-'Las secretarías de Hacienda, la Secretaría de Gobierno, la Secretaría de la Contraloría, la Unidad de Planeación y Prospectiva, la Oficialía Mayor y las áreas requeridas'.
-Bueno pues el oficial mayor comunicó avances ya en transparencia, pero además de que documentos, contratos tenían muchos faltantes, Orlando Ángeles señaló también todo lo que se ha tenido que hacer para ordenar y poder iniciar... el trabajo, no, no basta llevar a cabo la entrega-recepción, es desde luego también darle seguimiento a cada uno de los temas. Había un desorden, Orlando Ángeles señaló.
-'De enero a septiembre de este año se han adjudicado 313 contratos por más de 2,558 millones de pesos'.
-'De este monto, 310 contratos equivalen al 97% fueron licitación pública nacional'.
-'También fortalecimos los instrumentos contractuales y los mecanismos de cumplimiento'.
-'En diciembre del 2025 este congreso en materia de adquisiciones, incorporando entre otras leyes que permiten reforzar las garantías de cumplimiento de los contratos, porque contratar no es suficiente, también hay que exigir que todo se cumpla'.
-'Durante esta administración se aplicaron penalizaciones a 35 contratos por un monto total de 5,819,000 pesos'.
-'Asimismo, se rescindieron 6 contratos cuyo valor ascendía a 68 millones de pesos'.
-'En conjunto a las penalizaciones y las recisiones contribuyeron a evitar un posible daño a las finanzas del estado por más de 74 millones de pesos'.
-'Nuestra responsabilidad es actuar conforme a derecho y cumplir la ley'.
-'Estos datos no son solamente cifras administrativas, representan obligaciones exigidas, mecanismos de control y recursos cuya protección debe acreditarse documentalmente'.
-'El patrimonio inmobiliario pertenece a las y los hidalguenses'.
-'Su administración exige conocer qué bienes tenemos, cuál es su situación jurídica y cómo puede cumplir una función para la gente'.
-'Al inicio de esta administración, mediante un proceso de diagnóstico, se identificaron múltiples irregularidades y abusos, como la falta de un inventario consolidado, confiable, inmuebles estatales al margen de la cuenta pública, propiedades pagadas y sin escriturar, intercambio de bienes en condiciones desproporcionadas'.
-'Un inventario inmediato de cómo se recibió y lo que se está haciendo en favor de...'".</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1knLyKSFkdyqatVz6_U9Ng_2IewLsCyY9/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Andrés Velázquez Vázquez, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1332/2026</t>
-  </si>
-  <si>
-    <t>Convoca Julio Menchaca a sector empresarial a generar prosperidad compartida en todo el país.</t>
-  </si>
-  <si>
-    <t>En respaldo a la Confederación de Cámaras Nacionales de Comercio, Servicios y Turismo, la Concanaco Servytur, el gobernador de Hidalgo, Julio Menchaca Salazar, participó en su Asamblea Nacional, espacio en el que hizo un llamado a este sector para continuar trabajando en sinergia y generar bienestar en beneficio de las familias mexicanas.
-En Hidalgo, señoras y señores, estamos haciendo nuestra parte, se están generando una enorme cantidad de empleos', escuchemos al gobernador del estado de Hidalgo: 
-'En Hidalgo estamos haciendo nuestra parte, se están generando una enorme cantidad de empleos y hacemos una invitación para que haya actividad económica, haya prosperidad, haya bienestar compartido y que esa sinergia del gobierno federal, con nuestra presidenta, con los gobiernos estatales, con los gobiernos municipales sea un ejercicio permanente para la construcción del México que queremos, del México que merecemos'.
-En este sentido, titular del gobierno de Hidalgo reconoció a quienes integran la confederación, pues su esfuerzo, labor y liderazgo, dijo, impacta y se traduce en beneficios para sus comunidades, municipios y estados, encabezados por Octavio de la Torre de Stéffano, presidente nacional de la Concanaco Servytur.
-Hay un programa de la Concanaco Servytur que hemos observado en distintas entidades, el 'Viernes Mexicano', y desde luego lo atractivo para el turismo y atractivo para quienes viven en estos municipios, porque además se consume lo local; consumir local permite que haya un activo circulante dentro de las regiones, las comunidades, los municipios y se va fortaleciendo la economía.
-Por su parte, Gerardo Fernández Noroña, presidente de la Mesa Directiva del Senado de la República, reconoció a las y los empresarios por ser generadores de empleo en sus respectivos entornos, por lo que señaló la importancia de brindar facilidades para el correcto desarrollo de sus actividades.
-Al respecto, Iván de Jesús Ramírez, presidente municipal de Ezequiel Montes, coincidió en que las administraciones estatales y municipales pueden apoyar a las micro y pequeñas empresas en su regularización mediante la simplificación de trámites burocráticos.
-De esta forma, la presencia del gobernador de Hidalgo en la Asamblea Nacional de la Concanaco Servytur fortaleció el diálogo con uno de los sectores clave para la economía nacional, donde además se reiteró la importancia de sumar capacidades entre los gobiernos y la iniciativa privada para impulsar el empleo, favorecer la actividad comercial y las condiciones de desarrollo que beneficien tanto a las empresas como a las familia</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1iX7c5XW4ubl0hKmKRXGf00u_WG_PwLIW/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Octavio de la Torre de Stéffano, Higinio Martínez Miranda, Iván Reséndiz Ramírez</t>
-  </si>
-  <si>
-    <t>Segobh/IHM/Bol.45/2026</t>
-  </si>
-  <si>
-    <t>Centro LIBRE contribuye a la preservación de la lengua Hñähñü</t>
-  </si>
-  <si>
-    <t>IHM</t>
-  </si>
-  <si>
-    <t>Centros LIBRE</t>
-  </si>
-  <si>
-    <t>Tecozautla</t>
-  </si>
-  <si>
-    <t>Continuamos, vamos contigo, Ros María, tienes información de los centros libre...
-Desde el mes de julio, cada fin de semana un grupo de mujeres originarias de Tecozautla se reúnen en el centro libre del municipio para aprender, reaprender y revalorizar su lengua materna con la guía de la abogada Elda Mabel Penca Doñú, quien además de su labor como asesora jurídica, imparte el curso 'Introducción básica al ñañú'.
-Originaria de Cardonal, la profesionista del Instituto Hidalguense de las Mujeres asumió el compromiso de aportar sus conocimientos para reforzar la preservación, aprendizaje y uso de las lenguas indígenas más importantes del país, como una herramienta de identidad cultural.
-La finalidad, explica, es contribuir al empoderamiento de las mujeres a través del rescate y reconocimiento del patrimonio lingüístico y cultural de la región otomí, así como brindarles herramientas que favorezcan una participación más activa e incluyente en la sociedad.
-El curso... y concluirá el próximo mes de diciembre, está dirigido a mujeres a partir de los 15 años y consta de seis módulos donde se revisan desde temas básicos hasta expresiones comunes, saludos y conversaciones básicas, por lo que las personas interesadas pueden acudir al centro libre de Tecozautla.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1czKYFfC1XGXDt-jvWCerOXxN8c1YnOGa/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor rinde cuentas sobre el correcto cumplimiento del gasto público</t>
-  </si>
-  <si>
-    <t>Continuamos con información desde Pachuca y bien, pues ya eh han concluido las comparecencias ante el Congreso del Estado la glosa del cuarto informe del gobernador Julio Menchaca Salazar y cabe recordar, ya le decía hace unos momentos, que el calendario original, el calendario inicial contemplaba hasta ayer a las 10 de la mañana la la última comparecencia y sería la de el encargado del despacho de la Procuraduría General de Justicia del Estado, de la cual ya le he dado detalle. Sin embargo, después se sumó la de la Oficialía Mayor del Gobierno del Estado, así es que por primera vez un titular de la Oficialía Mayor del Gobierno del Estado compareció ante el Congreso de la entidad. Orlando Ángeles Pérez, quien rindió cuentas sobre los avances que garantizan el correcto destino de los recursos públicos, mejorar los procesos administrativos y también mejorar las condiciones de quienes trabajan al servicio de las y los hidalguenses.
-Sobre las contrataciones de obra, productos y servicios, destacó que de enero a septiembre se dictaminaron 313 contratos, de los cuales el 99% fueron mediante licitación pública. Asimismo, durante la administración se aplicaron penalizaciones a 35 contratos y se rescindieron 6 contratos por incumplimiento, cuyo valor ascendía a 68 millones de pesos.
-Orlando Ángeles destacó avances en la modernización del gobierno con la digitalización de 28,000 expedientes laborales y el centro de datos, con una inversión de 505 millones de pesos que triplicó la capacidad de almacenamiento de información. También señaló que sobre más de 3,000 puntos de conexión a internet en dependencias y espacios públicos.
-En materia laboral reportó incrementos salariales de entre 5 y 30% durante la administración en beneficio de 13,117 trabajadores. Dijo se mejoraron los ingresos de 1,012 personas jubiladas que percibían menos de un salario mínimo y se modificó el régimen salarial de 431 personas que realizaban labores de riesgo.
-En infraestructura informó que se recuperaron e incorporaron 436 inmuebles al patrimonio estatal, asimismo se dio mantenimiento a 95% de los inmuebles gubernamentales, además de conservar espacios de convivencia como el Parque Cultural Hidalguense, que desde su apertura ha recibido aproximadamente 1 millón de visitantes. Y sin duda que el Parque Cultural Hidalguense ha sido un espacio muy importante en la capital del Estado para la recreación, sí, para el arte, para la cultura, pero también para diversas actividades sociales y de beneficencia. En fin, ha sido un espacio muy relevante este del Parque Cultural Hidalguense, a cargo de la Oficialía Mayor, cuyo titular, Orlando Ángeles, por primera ocasión, o se convirtió en el primer titular de la Oficialía Mayor en ser parte de esta glosa del informe, en ser parte de las comparecencias ante el Congreso.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zyS6YT_lM4UwTg0HZZ8KrmJ0xMilK-lV/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Por otra parte, en respaldo a la Confederación de Cámaras Nacionales de Comercio, Servicios y Turismo, la Concanaco Servytur, el gobernador Julio Menchaca participó en su Asamblea Nacional, espacio en el que hizo un llamado a este sector, al empresarial, para continuar trabajando en sinergia para generar bienestar en beneficio de las familias mexicanas. En este contexto, esto es parte de lo que dijo el mandatario estatal.
-“En Hidalgo estamos haciendo nuestra parte, se están generando una enorme cantidad de empleo y hacemos una invitación para que haya actividad económica, haya prosperidad, haya bienestar compartido y que esa sinergia del gobierno federal, con nuestra presidenta, con los gobiernos estatales, con los gobiernos municipales, sea un ejercicio permanente para la construcción del México que queremos, del México que merecemos”.
-El titular del Ejecutivo estatal reconoció a quienes integran la Confederación, pues su esfuerzo, dijo, labor y liderazgo impacta y se traduce en beneficios para sus comunidades, municipios y estados, encabezados esta confederación por Octavio de la Torre de Stéffano, presidente nacional de la Concanaco Servytur. Por su parte, Higinio Martínez Miranda, presidente de la Mesa Directiva del Senado, reconoció a las y los empresarios por ser generadores de empleo en sus respectivos entornos, por lo que señaló la importancia de brindar facilidades para el correcto desarrollo de sus actividades. Al respecto, Ivar Resendis Ramírez, presidente municipal de Ezequiel Montes, coincidió en que las administraciones estatales y municipales pueden apoyar a las micro y pequeñas empresas en su regularización mediante la simplificación de trámites burocráticos. De esa forma, la presencia del gobernador hidalguense en la Asamblea Nacional de la Concanaco Servytur fortaleció el diálogo con uno de los sectores clave para la economía nacional.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/18R_Nkv4hA33FWiLwohrtvGkDYfP7HLrr/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/FN.39/2026</t>
-  </si>
-  <si>
-    <t>Menchaca fortalece cooperación hacendaria con la Unión Europea.</t>
-  </si>
-  <si>
-    <t>Cooperación internacional</t>
-  </si>
-  <si>
-    <t>Permítame compartirle información acerca de este estrechar relaciones con la Unión Europea y en temas en temas muy puntuales. Como parte de las acciones para fortalecer las capacidades institucionales de Hidalgo, el gobernador Julio Menchaca Salazar recibió a Stefan Agne, en ministro, consejero y jefe de cooperación de la Delegación de la Unión Europea en México, y a Raúl Carrillo Ruiz, coordinador del proyecto EU4, con quienes dialogó sobre nuevas oportunidades de colaboración en beneficio de la entidad.
-Durante el encuentro, en el que también participó la Secretaría de... la Secretaria de Hacienda, María Esther Ramírez Vargas, se analizaron mecanismos de trabajo conjunto e intercambio de experiencias en el marco del modelo hacendario estatal para la cohesión social, orientado a vincular la modernización de las finanzas públicas con las prioridades de desarrollo de la entidad.
-En esta reunión, forma parte, esta reunión forma parte de los esfuerzos de la actual administración para establecer vínculos estratégicos con organismos internacionales, aprovechar buenas prácticas y avanzar hacia una gestión más eficiente capaz de traducir el uso responsable de los recursos públicos en resultados positivos para la población. Lo que se informa sobre este tema, esta reunión con representantes de la Unión Europea.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nAFragHv-dR6DGV3BZlr1niiUAAIyDR9/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Stefan Agne, Raúl Carrillo Ruiz, María Esther Ramírez Vargas</t>
-  </si>
-  <si>
-    <t>Nidia Torres</t>
-  </si>
-  <si>
-    <t>Una persona falleció en la Autopista Arco Norte, luego de que una pipa volcara y provocara afectaciones al tránsito en dirección a Querétaro, a la altura del municipio de Atitalaquia. De acuerdo con información de Protección Civil y Bomberos, el primer incidente ocurrió en el kilómetro 94+400, en el tramo de bajada de Apaxco hacia el municipio mencionado. En ese sitio, una pipa volcó y presentó fisuras en varios puntos de su estructura, tras impactarse lateralmente del lado izquierdo, lo que ocasionó el derrame del diésel que transportaba sobre la zanja central de la autopista. Debido al congestionamiento vehicular generado por este percance, un camión tipo Torton y una camioneta Nissan que se encontraban detenidos por el tráfico fueron impactados por un tráiler. En este accidente en particular, el copiloto de la camioneta perdió la vida al quedar prensado al interior de la unidad. Personal de Bomberos y Protección Civil acudió al lugar para realizar labores de atención a la emergencia, control y prevención de riesgos, en coordinación con las autoridades correspondientes. Cabe destacar que la zona fue acordonada por elementos de Guardia Nacional, División Carreteras, en tanto se notificó lo sucedido a personal de la Procuraduría General de Justicia del Estado de Hidalgo para las investigaciones correspondientes y el posterior retiro del cuerpo por parte del Servicio Médico Forense.</t>
-  </si>
-  <si>
-    <t>PGJEH</t>
-  </si>
-  <si>
-    <t>Levantamiento de cuerpo</t>
-  </si>
-  <si>
-    <t>Atitalaquia</t>
-  </si>
-  <si>
-    <t>Una persona falleció en la autopista Arco Norte luego de que una pipa volcara y provocara afectaciones al tránsito en dirección a Querétaro, la altura del municipio de Atitalaquia, que de acuerdo con información de Protección Civil y Bomberos, el primer incidente ocurrió en el kilómetro 94 más 400 en el tramo de bajada de Apaxco hacia el municipio mencionado. En ese sitio, una pipa volcó y presentó fisuras en varios puntos de su estructura tras impactarse lateralmente del lado izquierdo, lo que ocasionó el derrame del diésel que transportaba sobre la zanja central de la autopista. Debido al congestionamiento vehicular generado por este percance, un camión tipo Thornton y una camioneta Nissan, que se encontraban detenidos por el tráfico, fueron impactados por un tráiler. En ese accidente en particular el copiloto de la camioneta perdió la vida al quedar prensado al interior de la unidad. Personal de bomberos y protección civil acudió al lugar para realizar labores de atención a la emergencia, control y prevención de riesgos en coordinación con las autoridades correspondientes. Cabe destacar que la zona fue acordonada por elementos de Guardia Nacional, División Carreteras, en tanto se notificó lo sucedido a personal de la Procuraduría General de Justicia del Estado de Hidalgo para las investigaciones correspondientes y el posterior retiro del cuerpo por parte del Servicio Médico Forense.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hpFHq57dP-rKj-1h6Z0Ir9PT3VZfEXsV/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SSPH/Bol.988/2026</t>
-  </si>
-  <si>
-    <t>SSPH desarticula punto de narcomenudeo en Tolcayuca y asegura a una mujer reincidente</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
     <t>Combate Al Narcomenudeo</t>
   </si>
   <si>
-    <t>Tolcayuca</t>
-  </si>
-  <si>
-    <t>Como resultado de labores de inteligencia operativa y acciones permanentes contra el narcomenudeo, la Secretaría de Seguridad Pública de Hidalgo desarticuló un presunto punto de venta y distribución de drogas en Tolcayuca, donde fueron aseguradas 380 dosis de presuntos narcóticos y también una mujer con antecedentes de detención por este mismo delito. La intervención se realizó mediante una orden de cateo en un inmueble ubicado en la colonia El Tildio. De hecho, en el operativo participaron elementos de la Secretaría de Seguridad Pública de Hidalgo, en coordinación también con la Procuraduría General de Justicia del Estado de Hidalgo, la Secretaría de la Defensa Nacional y también la Guardia Nacional. Durante la diligencia fue detenida una mujer identificada con las iniciales JTZ, originaria de la Ciudad de México, quien de acuerdo con información policial había sido arrestada años atrás por su probable participación en actividades relacionadas con narcomenudeo. En el lugar también se incautaron 260 dosis de hierba seca con características similares a la marihuana y 120 de una sustancia granulada con características propias del cristal. Además, también se localizaron la báscula de precisión, bolsas de plástico presuntamente utilizadas para dosificar drogas, una libreta con anotaciones, un teléfono celular y 3.166 pesos en efectivo. Cabe precisar que la detenida es madre de Nigel Iván Lozano Tinoco, alias El Pestañas, quien permanece recluida en el Centro de Reinserción Social en Pachuca desde el paso 3 de febrero del 2025 por un proceso relacionado con el delito de homicidio calificado. La mujer y los indicios también quedaron a disposición de la autoridad competente para poder dar continuidad a las investigaciones correspondientes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YP1RmieAgTANWQJzYQWoB8nuF0cUnrcs/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Daniel Martínez sobre el retraso en la construcción del Centro de Acopio Lechero de Tulancingo comentó: Ahora sí que ahí a la espera, esperemos que la gestión de los recursos no termine siendo como... Le voy a pedir a la Secretaría de Salud que revise el asunto de la calidad de la leche en la región y bolas, don Cuco. Que la Secretaría de Salud le responde. Ya la estamos revisando. ¿Cuál petición? A ver si hay gestión al respecto. ¿O qué se hace con el terreno? ¿O si existe la certeza legal del terreno?</t>
-  </si>
-  <si>
-    <t>Centro de Acopio Lechero</t>
-  </si>
-  <si>
-    <t>Ahora sí que ahí a la espera, esperemos que la gestión de los recursos no termine siendo como... Le voy a pedir a la Secretaría de Salud que revise el asunto de la calidad de la leche en la región y bolas, don Cuco. Que la Secretaría de Salud le responde. Ya la estamos revisando. ¿Cuál petición? A ver si hay gestión al respecto. ¿O qué se hace con el terreno? ¿O si existe la certeza legal del terreno?</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1A8vGGXYYeHY2EX1HE3Xrp55vaVEkkjow/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SEPH realiza el concurso de oratoria “Mi palabra es hoy mi voz y mi fortaleza 2026”</t>
-  </si>
-  <si>
-    <t>Básica</t>
-  </si>
-  <si>
-    <t>Concurso De Oratoria</t>
-  </si>
-  <si>
-    <t>La Secretaría de Educación Pública del Estado de Hidalgo señala acerca del concurso, el cuarto concurso de oratoria "Mi palabra es hoy mi voz y mi fortaleza 2026", realizado con el objetivo de fortalecer las habilidades lingüísticas de las y los estudiantes y promover la pluralidad de voces, el reconocimiento de las lenguas originarias, la lectura crítica, la escritura reflexiva y la expresión corporal. Como parte del impulso a la educación que promueven el gobierno de Julio Menchaca Salazar y el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, la SEPH genera espacios para que niñas, niños y adolescentes fortalezcan su expresión oral, desarrollen el pensamiento crítico y ganen confianza para expresar sus ideas ante el público. El concurso reunió a estudiantes de educación básica, quienes demostraron sus habilidades de expresión, argumentación y dominio de la palabra en las tres categorías participantes. En la categoría A, correspondiente a nivel preescolar, ¡mire qué padre desde los chavitititos!, el primer lugar fue para Ivana Guadalupe Paulina Barró, del preescolar general "Club de Leones", el segundo lugar lo obtuvo Valentina Quiterio Quiterio, del preescolar general "Diego Alarcón de Ocaña", y el tercer lugar correspondió a Elías Dionicio Hernández, del preescolar general "El Principio del Saber", los tres planteles pertenecientes al municipio de Ixmiquilpan. En el caso del nivel primaria, la categoría B, el primer lugar fue para Antonio de Jesús Lara Durango, de la primaria general "Lauro Aguirre" de Huejutla, el segundo lugar lo obtuvo Elías Caín Martínez Cruz, de la primaria general "Alfonso Cravioto" de Zimapán, y el tercer lugar fue para Frida Chantal Isidro Hernández, de la primaria indígena "Progreso", esto en Cardonal. En tanto que en secundaria categoría C, el primer lugar fue para Dylan Isaí Lira Aguirre, de la telesecundaria 332 de Cuautepec, ¡abrazote hasta Cuautepec!, el segundo lugar lo obtuvo Yoselin Montes Galloso, de la telesecundaria 508 de San Bartolo Tutotepec, también para él un gran abrazo, y también para María José Pérez Sandoval, de la escuela secundaria "Jesús Romero Flores" ubicada en Apan. A través de estas actividades, las y los estudiantes tuvieron la oportunidad de compartir sus ideas, demostrar su talento y reconocer la diversidad cultural y lingüística de Hidalgo a través de la palabra como medio de expresión y aprendizaje, que es precisamente la intención de este tipo de certámenes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nN2weqIy0AQEcL4l1xbeeRD1akaJO_So/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>PGJEH/Bol.074/2026</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia del Estado de Hidalgo contempla fortalecer su estructura para poder atender de manera específica los casos de extorsión mediante la creación de la fiscalía especializada, que podría comenzar sus funciones en el 2027. Por su parte, Francisco Ángel Fernández Hasbun, quien es encargado del despacho de la Procuraduría, explicó que actualmente este tipo de investigaciones son canalizadas a la Unidad de Atención al Secuestro. Sin embargo, se busca conformar un grupo especializado que pueda permitir ampliar las capacidades de investigación y atención de estos delitos. La nueva área estaría integrada por aproximadamente 50 personas, esto como parte de un proceso. La Procuraduría estará realizando una revisión de los recursos humanos, materiales y operativos también con los que cuenta, además de preparar al personal ministerial que estaría participando en esta fiscalía. El anuncio se realizó durante la comparecencia de Fernández Hasbun ante el Congreso de Hidalgo, esto como parte de la revisión del cuarto informe de gobierno estatal. Durante el encuentro con legisladores, también se dio a conocer un avance en la investigación por el homicidio del estudiante del Mexe y de acuerdo con el encargado de la Procuraduría, las autoridades judiciales concedieron tres órdenes de aprehensión relacionadas con este homicidio calificado de José Antonio Salgado Aparicio, alumno de la Escuela Normal Rural Luis Villarreal. El estudiante fue encontrado, recordemos, sin vida el pasado 7 de septiembre de 2026. La Procuraduría confirmó la obtención de las tres órdenes; aunque no se informó como tal si hasta el momento habían sido ejecutadas ni si se dieron a conocer tampoco algunos detalles sobre las personas señaladas dentro de esta investigación.</t>
-  </si>
-  <si>
-    <t>Con el Procurador de Justicia del Estado Hidalgo se cierran las comparecencias y hace anuncio acerca de una nueva Fiscalía. Es correcto, Daniel. Pues bien, resulta que la Procuraduría General de Justicia del Estado Hidalgo contempla fortalecer su estructura para poder atender, pues de manera específica, los casos de extorsión mediante creación de la Fiscalía Especializada que podría comenzar sus funciones en el 2027. Pero bien, por su parte, Francisco Ángel Fernández Hasmón, quien es encargado del despacho de la Procuraduría, explicó que actualmente este tipo de investigaciones son canalizadas a la unidad de atención al secuestro. Sin embargo, se busca conformar un grupo especializado que pueda permitir ampliar las capacidades de investigación y atención de estos delitos. La nueva área estaría integrada por aproximadamente 50 personas, esto como parte de un proceso, Y bien la Procuraduría estar realizando una revisión de los recursos humanos materiales y operativos también con los que cuenta además de preparar al personal ministerial que estar participando en esta fiscal El anuncio se realizó durante la comparecencia de Fernández Hasbun ante el Congreso de Hidalgo, esto como parte de la revisión del cuarto informe de gobierno estatal, y durante el encuentro con legisladores también se dio a conocer un avance en la investigación para el homicidio del estudiante del Meche, y de acuerdo con el encargado de la Procuraduría, las autoridades judiciales concedieron tres órdenes de aprehensión relacionadas con este homicidio calificado, José Antonio Salgado Aparicio, alumno de la Escuela Normal Luis Villarreal, y pues el estudiante fue encontrado, recordemos, sin vida el pasado 7 de septiembre del 2026. Y resulta que la Procuraduría confirmó la obtención de los tres órdenes, aunque no, no se informó como tal si hasta el momento pues habían sido ejecutadas ni si se dieron a conocer tampoco pues algunos detalles sobre las personas señaladas dentro de esta investigación.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1yGhbq9NLK64JDPUg22AKmeNCtHT2Ks7Z/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Francisco Fernández Hasbun</t>
-  </si>
-  <si>
-    <t>Más de seis años han pasado desde el inicio de la construcción del Centro de Acopio Lechero del Valle de Tulancingo, y no existe por lo menos en este momento, indicio alguno de retomar y finalizar su construcción y equipamiento. Durante la comparecencia de Napoleón González Pérez, titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh) ante el Congreso del Estado de Hidalgo, fue cuestionado sobre el tema por el diputado local por Tulancingo, Arturo Gómez Canales. El funcionario respondió ante los legisladores locales que el proyecto corresponde al Gobierno Federal, asegurando que está considerado retomar la obra, junto con el Centro de Acopio Lechero de Tizayuca, el cual también están detenidos los trabajos de construcción y equipamiento. Señaló que para seguir adelante con ambos proyectos, se requiere de presupuesto por aproximadamente 80 millones de pesos. A finales de julio de 2020 fue iniciada la obra en un predio de mil 676.64 metros cuadrados, ubicado en la localidad de San Nicolás el Chico, en Tulancingo. El proyecto está a cargo del gobierno federal a través de Seguridad Alimentaria Mexicana (Segalmex), por medio de su filial Liconsa. Durante la ceremonia de colocación de la primera piedra, se aseguró que la inversión total sería de aproximadamente 12 millones de pesos. De dicha inversión, seis millones serían para la construcción de las instalaciones y los seis millones restantes, en equipamiento. Durante la ceremonia de inicio de construcción, se informó que el espacio tendría capacidad para recibir hasta 30 mil litros de leche diariamente, garantizando a más de 450 productores en la región recibir un precio de garantía adecuado por el alimento. Para el proyecto, el Municipio de Tulancingo aportó el terreno, el gobierno de Hidalgo se encargó de la construcción del inmueble, y el equipamiento especializado correspondía al entonces organismo federal Segalmex. Pero las instalaciones están abandonadas desde hace por lo menos 4 años, incluso siendo ya saqueadas y vandalizadas; testimonios de vecinos en la zona señalan que incluso personas se quedan a pernoctar en el interior. En visita de trabajo realizada en el Valle de Tulancingo a finales del mes de julio de este año, González Pérez recordó que en la inversión considerada para concretar ambos centros de acopio lechero, se deben considerar varios puntos. “No es nada más tener la instalación, es el laboratorio, los tanques, todo el equipamiento, además de los accesos”. En una visita posterior a la misma región realizada el pasado mes de septiembre, el funcionario estatal insistió que siguen las gestiones para contar con recursos que permitan finalizar la construcción y equipamiento de ambos espacios, en Tizayuca y Tulancingo. Enfatizó que junto con dichas gestiones, se revisan detalles legales; en el caso de Tulancingo, por ejemplo, la propiedad del terreno, para tener la certeza de aplicar los eventuales recursos públicos en forma adecuada.</t>
-  </si>
-  <si>
-    <t>Arturo Gómez Canales</t>
-  </si>
-  <si>
-    <t>Las rondas de comparecencias sobre el cuarto informe del gobernador Julio Menchaca Salazar ya concluyeron en la 66 Legislatura del Congreso del Estado. Orlando Ángeles, el oficial mayor del gobierno estatal, fue el último en presentarse ante los diputados locales. Esta es la primera vez en la historia que un oficial mayor comparece en este contexto. Durante su intervención, habló sobre el uso de los recursos públicos y confirmó que el 99% de los contratos en la administración de Menchaca se otorgaron mediante licitaciones públicas. Se discutieron 313 contratos entre enero y septiembre, y el oficial mencionó que se impusieron penalizaciones a 35 contratos y se rescindieron seis por incumplimiento, con un valor total de 68 millones de pesos. Se destaca que esta comparecencia fue una de las más informativas de toda la serie, lo que permitió a los diputados conocer más sobre el desempeño de la oficialía en la administración de Julio Menchaca. También se resaltó que se han recuperado aproximadamente 500 inmuebles que estaban abandonados, lo que ha reducido costos para el gobierno del estado. Además, se mencionó que el porcentaje de licitaciones públicas ha aumentado del 66% al 99%, lo que significa que ya no se realizan a puerta cerrada, como ocurría antes. El oficial mayor explicó que existen diferentes mecanismos para asignar obras, como licitaciones públicas y directas, y que la mayoría de las asignaciones actuales se realizan a través de convocatorias y concursos abiertos.</t>
-  </si>
-  <si>
-    <t>Concluyeron ya las rondas, las agendas de comparecencias en la glosa del cuarto informe del gobernador Julio Menchaca Salazar allá en la 66 legislatura, en la sede del Congreso del Poder Legislativo de nuestro Estado el oficial mayor del gobierno del Estado, Orlando Ángeles, fue el último en comparecer ante las y los diputados locales en la primera vez en un hecho histórico, es la primera vez que un oficial mayor comparece en la glosa del informe ante los diputados locales, habló por supuesto del uso de los recursos públicos y entre las noticias que surgen de esta comparecencia, el oficial mayor Orlando Ángeles confirmó el 99% de las contrataciones, es decir, de los contratos que el gobierno del estado establece al menos en lo que se refiere a la administración del gobernador Tulio Menchaca fueron otorgados a través de licitaciones públicas. El 99% dice parte de esta comparecencia, de enero a septiembre se dictaminaron 313 contratos de los cuales 99% fueron mediante licitación pública. El oficial mayor dijo que durante la administración se aplicaron penalizaciones a 35 contratos y se rescindieron 6 por incumplimiento, cuyo valor ascendía a 68 millones de pesos. Mucha informaci dicen hoy los principales titulares de los medios de comunicaci en Hidalgo que fue una de las comparecencias m nutridas de esta bater de esta agenda que significa la glosa del cuarto informe de gobierno y bueno, qué bien que las y los diputados decidieron ampliar el espectro de, no solamente al gabinete del gobernador Julio Manchaca, sino también a la Oficialía Mayor para hablar sobre las tareas que se han llevado a efecto, las metas que han logrado en la administración de Julio Manchaca. Aldo Falcón. Andrés, también durante esta comparecencia me llamó mucho la atención la recuperación de al menos, bueno, más o menos 500 inmuebles, inmuebles, los cuales estaban abandonados o también se encontraban en algunas afectaciones, reduciendo un costo para el gobierno del Estado. Igual sobre lo que dabas a conocer sobre esto de las licitaciones que avanzaron del 66% al 99%, ya no son a puerta cerrada. Bueno, pues si son licitaciones públicas, pues no pueden ser a puerta cerrada. Anteriormente se realizaban así, y lo que he dado a conocer... La ley contempla la asignación directa para el tema de otorgar obra por parte del gobierno a particulares, hay varios mecanismos, uno de ellos son las licitaciones públicas, otro de ellos es las licitaciones directas. El oficial mayor ayer se refirió específicamente a este asunto, el 99% de las asignaciones que se han hecho han sido asignaciones abiertas, públicas, asignaciones que se hacen a través de una convocatoria y por supuesto se concursa para obtenerla</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1pESs3LocZxtVpZyLqog3CfQxp5Jax_lG/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar comenta: participé en la Asamblea Nacional de Concanaco Servytur, donde tuve la oportunidad de conversar con el sector empresarial sobre Hidalgo, es una potencia en marcha y su ubicación estratégica, su crecimiento industrial, disposición de colaboración, atraer nuevas inversiones y oportunidades para la familia. La oportunidad de conversar. Ayer el gobernador estuvo en este evento de la Cámara de Canaco Servytur, la Cámara Nacional de Comercio, Servicios, y bueno, los temas empresariales son fundamentales.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar comenta Participé en la Asamblea Nacional de Concanaco Servytur Donde tuve la oportunidad de conservar con el sector empresarial Sobre Hidalgo es una potencia en marcha Y su ubicación estratégica Su crecimiento industrial, disposición de colaboración Atraer nuevas inversiones y oportunidades para la familia La oportunidad de conversar No de conservar, conversar Ayer el gobernador estuvo en este evento de la Cámara de La Canaco Servytur Ayer el gobernador estuvo en este evento de la Cámara de Canaco Servytur, la Cámara Nacional de Comercio, Servicios, y bueno, los temas empresariales son fundamentales.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gtjanN4c-TqOmT4fVIJdOGe6abyHKDTP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar sostuvo una reunión con Stefan Agne, ministro consejero y jefe de cooperación de la Delegación de la Unión Europea en México, y con Raúl Carrillo Ruiz, coordinador de proyectos de la Unión Europea ( EU4Equity), con quienes dialogó sobre nuevas oportunidades de colaboración en beneficio del estado. En el encuentro también participó la secretaria de Hacienda, María Esther Ramírez Vargas, donde analizaron mecanismos de trabajo conjunto e intercambio de experiencias en el mercado del modelo hacendario estatal para la cohesión social, orientado a vincular la modernización de las finanzas públicas con las prioridades para el desarrollo en Hidalgo. Esta reunión forma parte de los esfuerzos que la actual administración de Hidalgo realiza para establecer vínculos estratégicos con organismos internacionales, aprovechar las buenas prácticas y avanzar hacia una gestión más eficiente capaz de traducir el uso responsable de los recursos públicos en resultados positivos para la población. Ayer, el gobernador de nuestro estado recibió ahí en sus oficinas a representantes de la Unión Europea, a este señor que se llama Stefan Agne y a Raúl Carrillo Ruiz, ellos representantes de la Unión Europea. El tema: los dineros, los negocios.</t>
-  </si>
-  <si>
-    <t>Ayer el gobernador del estado de Hidalgo, el licenciado Julio Menchaca Salazar, se reunió, recibió aquí en sus oficinas de Palacio de Gobierno aquí en Pachuca, a Estefan Agne, que es ministro, consejero y jefe de cooperación de la Delegación Europea en México, y a Raúl Carrillo Ruiz, coordinador de proyectos de la Unión Europea, las siglas son EU4Equity, con quienes dialogó sobre nuevas oportunidades de colaboración en beneficio de nuestro Estado. En el encuentro también participó la Secretaria de Hacienda, María Esther Ramírez Vargas, y todos analizaron algunos mecanismos de trabajo conjunto e intercambio de experiencias en el mercado del modelo hacendario estatal para la cohesión social orientado a vincular la modernización de las finanzas públicas con las prioridades para desarrollo en Hidalgo. En esta reunión forma parte de los esfuerzos que la actual administración de Hidalgo realiza para establecer vínculos estratégicos con organismos internacionales, aprovechar las buenas prácticas y avanzar hacia una gestión más eficiente Capaz de traducir el uso responsable de los recursos públicos en resultados positivos para la población Ayer el gobernador de nuestro estado recibió en sus oficinas a representantes de la Unión Europea A este señor que se llama Stefan Agne y a Raúl Carrillo Ruiz, ellos representantes de la Unión Europea El tema, los dineros, los negocios</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14_MqqYnb9GWOfkhqJVxNM2UmsY91sYks/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Stefan Agne, María Esther Ramírez Vargas, Raúl Carrillo Ruiz</t>
-  </si>
-  <si>
-    <t>Seguimos fuera del aire allá en el 91.1 de frecuencia modulada La Voz de la Sierra Gorda, la mala noticia es que no solamente seguimos fuera del aire, sino que ni el área administrativa ni el área de ingeniería Radio y Televisión de Hidalgo mueve un dedo para tratar de solucionar este tema. Desafortunadamente la Dirección de Radio no cuenta con recursos técnicos ni mucho menos con recursos administrativos y económicos para solucionar el tema de la transmisión. Nosotros ya hicimos lo que nos correspondía, hicimos el llamado a las autoridades correspondientes para que nos ayuden a solucionar este problema. Mientras tanto, bueno, pues yo les pido que sigamos en redes sociales, estas que tanto nos quieren quitar para que podamos estar en comunicación allá en Zimapán, en Jacala, en por supuesto Pisaflores, Chapulhuacán, en la Misión, Pacula.</t>
-  </si>
-  <si>
-    <t>Seguimos fuera del aire allá en el 91.1 de frecuencia modulada, la voz de la sierra gorda, la mala noticia es que no solamente seguimos fuera del aire, sino que ni el área administrativa, ni el área de ingeniería radio y televisión de algo mueve un dedo para tratar de solucionar este tema. Desafortunadamente la dirección de radio no cuenta con recursos técnicos, Ni mucho menos con recursos administrativos y económicos Para Pues Solucionar el tema de la transmisión Nosotros ya hicimos lo que nos correspondía Hicimos el llamado A las autoridades correspondientes Para que nos ayuden a solucionar este problema Mientras tanto, bueno pues Yo les pido que sigamos en redes sociales Estas que tanto nos quieren quitar Para que podamos estar en comunicación Allí en Zimapán, en Jacala En por supuesto Pisaflores Chapulhuacán en la misión Pacula</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1D5BfUnsbkxt-oM8sKpPhsUf67bsm-KmI/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud inició ya la campaña de vacunación invernal en todas las clínicas, hospitales, centros de salud de nuestro estado, en las clínicas, hospitales, centros de salud públicos. Hay vacunas para la influenza estacional y también para el COVID. Acuda junto con su familia, acuda, por favor, a estos centros para que sean vacunados, principalmente los niños menores de 5 años, también los adultos mayores, las personas que tengan enfermedades crónico-degenerativas. Es muy importante que estén bien inmunizados en esta temporada invernal que ya se acerca y que se adelanta, como todos los años.</t>
-  </si>
-  <si>
-    <t>Recuerde que la Secretaría de Salud inició ya la campaña de vacunación invernal en todas las clínicas, hospitales, centros de salud de nuestro estado, en las clínicas, hospitales y centros de salud públicos. Hay vacunas para la influenza estacional y también para el COVID. Acuda junto con su familia, acuda por favor a estos centros para que sean vacunados principalmente los niños menores de 5 años, También los adultos mayores Las personas que tengan enfermedades crónico-degenerativas Es muy importante que estén bien inmunizados En esta temporada invernal Que ya se acerque, que se adelanta Como todos los años, se adelanta El invierno empezará por ahí así Del 20 de diciembre Por ahí así del 20 de diciembre Y hasta marzo del año próximo Será la temporada invernal La época invierno Pero bueno, pues los frentes fríos ya Afectan buena parte del país por supuesto incluyendo Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1e5x9bhZLm9F3m7cxalKYjp0mp6o2CqIv/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Subsecretaría de Protección Civil y Gestión de Riesgos informa a la población que, para este 23 de octubre de 2026, de acuerdo con el aviso meteorológico del 589 del pronóstico meteorológico general del Servicio Meteorológico Nacional, se pronostican chubascos de lluvia puntuales a fuertes de 25 a 50 mm, principalmente en las regiones norte y este del estado de Hidalgo. Asimismo, se pronostican temperaturas de 0 a 5 °C con vientos de 10 a 20 km/h con rachas de 30 a 50 km/h.</t>
-  </si>
-  <si>
-    <t>Aldo Falcón</t>
-  </si>
-  <si>
-    <t>Es muy importante, les repito, que estemos atentos a las emisiones de Radio Televisión Hidalgo porque hay un llamado de la Subsecretaría de Protección Civil. Aldo Farcón. Así es, la Subsecretaría de Protección Civil y Gestión de Riesgo informa a la población que para este 23 de octubre de 2026, de acuerdo con el aviso meteorológico de 589 del Pronóstico Meteorológico General del Servicio Meteorológico Nacional, se pronostican chubascos de lluvia puntales a fuertes de 25 a 50 milímetros, Principalmente en las regiones norte y este del estado ideal Asimismo se pronostican temperaturas de 0 a 5 grados centígrados Con vientos de 10 a 20 kilómetros por hora Con rachas de 30 a 50 kilómetros por hora Muy bien, bueno, pues ahí está la advertencia que nos hace El llamado que nos hace la solicitud de la subsecretaría de protección civil Les repito, dependiente de la Secretaría de Gobierno del estado Para estar muy atentos, sobre todo en las zonas altas de nuestro estado Se esperan temperaturas de hasta 0 grados es decir, se esperan heladas ya en algunas partes de nuestro estado hay que estar muy atentos hay que por supuesto salir si usted va a salir a su trabajo a la escuela si va a realizar sus actividades No olvide ponerse bien su su Porque vamos a tener Mucho frío estos por lo menos estos Dos días, ¿no? El fin de semana ¿No, Falcón? Así es, Andrés, hay que bajar Como bien me dijiste, hay que salir bien abrigados Porque se esperan bajas temperaturas .</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1jrAfQ146okEHiDot-793ovwqKlUDqLZo/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Andrés Torres: Oye, ¿qué tal este la dirección general de radio y televisión de algo que insiste en quitarnos el programa, en quitarnos nuestras redes sociales, en quitarnos de la programación? Si supiera que el gobernador del estado Hidalgo es suscriptor de Las Voces Radio y todas las mañanas por ahí así de las 5 de la mañana estamos ya en contacto enviándole información, intercambiando pues por supuesto conceptos y claro que junto con otros muchos cientos de seguidores de Las Voces todas las mañanas nos informan, nos dan a conocer cuál es el estado del clima, cuál es el estado de tránsito.</t>
-  </si>
-  <si>
-    <t>Acoso laboral</t>
-  </si>
-  <si>
-    <t>Oye, ¿qué tal la Dirección General de Radio y Televisión de Algo que insiste en quitarnos el programa, en quitarnos nuestras redes sociales, en quitarnos de la programación? Si supiera que el gobernador del estado de Hidalgo es suscriptor de las vocales radio, y todas las mañanas, por ahí así a 5 de la mañana, estamos ya en contacto enviándole información, intercambiando, pues por supuesto, conceptos, Y claro que junto con otros muchos cientos de seguidores de las vocales Todas las mañanas nos informan, nos dan a conocer cuál es el estado del clima Cuál es el estado del tránsito Les agradecemos de verdad muchísimo a todas y a todas las personas Que diariamente se ponen en contacto a través de las redes sociales Aquí no tenemos teléfono, aquí está cortado el teléfono Y se ponen en contacto con las vocales radio Les agradecemos de verdad muchísimo Y bueno, pues es la historia de las vocales Ese es el verdadero periodismo No la propaganda No la autoproclamación Y sobre todo la autocomiseración No, aquí sí trabajamos Y afortunadamente tenemos el apoyo de nuestro auditorio Cosa que les agradecemos infinitamente</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FJ_9DaaXqII7DjCZdcTaoUxwNeoPHbaA/view?usp=drivesdk</t>
+    <t>Mañanera</t>
+  </si>
+  <si>
+    <t>Yazmín Leonardo</t>
+  </si>
+  <si>
+    <t>Durante la conferencia matutina del Gobierno del Estado de Hidalgo, la secretaria de Hacienda, Esther Ramírez Vargas, presentó los detalles sobre la visión del presupuesto 2027 para la entidad. Destacó que se mantendrá una recaudación eficiente para financiar más obras y mejores servicios públicos, y mencionó los trabajos recientes de modernización catastral en colaboración con los municipios. Asimismo, informó sobre su encuentro con representantes de la Unión Europea.</t>
+  </si>
+  <si>
+    <t>Hacienda</t>
+  </si>
+  <si>
+    <t>Aclaración en Mañanera</t>
+  </si>
+  <si>
+    <t>Durante la conferencia matutina, la secretaria de Movilidad y Transporte en el estado de Hidalgo, Lizbeth Robles Gutiérrez, informó que se ha formalizado una denuncia ante la Procuraduría General de Justicia del Estado de Hidalgo en contra de la empresa Uber, debido a que la legislación local no permite la operación de plataformas digitales para el traslado de personas. La funcionaria detalló que el Poder Ejecutivo presentó la querella a través de la Coordinación General Jurídica. Asimismo, aclaró que no existe una comunicación formal con dicha compañía y señaló que, aunque otras plataformas han buscado acercarse a la Secretaría (SEMOT), estas no han acreditado su personalidad jurídica o solicitan información a distancia sin certeza sobre la identidad de sus representantes.</t>
+  </si>
+  <si>
+    <t>Semot</t>
+  </si>
+  <si>
+    <t>Apps de transporte</t>
+  </si>
+  <si>
+    <t>SSPH/Bol.989/2026</t>
+  </si>
+  <si>
+    <t>SSPH desmantela dos puntos de narcomenudeo y detiene a ocho personas en Hidalgo</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/Bol.1333/2026</t>
+  </si>
+  <si>
+    <t>Radio Lobo 96.7 FM</t>
+  </si>
+  <si>
+    <t>Ernestina Godoy y Julio Menchaca inauguran los Módulos de Atención Social ¡Sí Confío! de la FGR</t>
+  </si>
+  <si>
+    <t>Gina Lorenzo</t>
+  </si>
+  <si>
+    <t>Enlace Noticias</t>
+  </si>
+  <si>
+    <t>Entrega de instalaciones</t>
+  </si>
+  <si>
+    <t>Segobh/SECESP/Bol.Bol.04/2026</t>
+  </si>
+  <si>
+    <t>Estratégica coordinación con la Federación fortalecerá la seguridad pública en Hidalgo</t>
+  </si>
+  <si>
+    <t>FASP</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1944-A/2026</t>
+  </si>
+  <si>
+    <t>Premia SEPH el talento estudiantil en el 4.º Concurso de Canto “De mi Voz al Canto”</t>
+  </si>
+  <si>
+    <t>Justa Académica</t>
+  </si>
+  <si>
+    <t>Durante la conferencia matutina semanal, la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez, anunció el lanzamiento de un operativo de inspección vehicular extraordinaria enfocado exclusivamente en la verificación de pólizas de seguro de las unidades de transporte público convencional. La funcionaria destacó que esta revisión es de carácter obligatorio y opera de forma paralela a las inspecciones anuales ordinarias. Asimismo, advirtió de manera enérgica a los concesionarios y conductores sobre la trascendencia de contar con un seguro amplio que cumpla con los requisitos estipulados en los artículos 107 y 108 de la ley local (incluyendo coberturas de responsabilidad civil y gastos médicos). Robles Gutiérrez subrayó que la falta de una póliza vigente no solo amerita sanciones económicas o administrativas, sino que puede derivar directamente en la revocación de la concesión. Las revisiones se llevarán a cabo en las instalaciones del Sistema de Transporte Convencional de Hidalgo, oficinas itinerantes, unidades móviles y a través de operativos en campo implementados por la Dirección de Vigilancia y Supervisión. Por último, se abordó brevemente el marco legal que regula la transportación de personas mediante aplicaciones móviles en el estado.</t>
+  </si>
+  <si>
+    <t>Mañanera de Hidalgo</t>
+  </si>
+  <si>
+    <t>Locutor Irving Sánchez da lectura a comentario de radioescucha que reporta irregularidades y deficiencias en el servicio de transporte colectivo de la ruta que va de Tulancingo hacia Acatlán y Almoloya, cuya base se encuentra en Morelos. De acuerdo con el reporte, las unidades no brindan un servicio de calidad, ya que dejan pasajeros varados con frecuencia y señaló que el pasado viernes, a partir de las 4:00 horas, se quedaron sin servicio. Ante esta situación, solicitó que se envíe el reporte a las autoridades o áreas correspondientes para su atención.</t>
+  </si>
+  <si>
+    <t>STCH</t>
+  </si>
+  <si>
+    <t>Queja transporte público</t>
+  </si>
+  <si>
+    <t>Durante la conferencia de prensa matutina del Gobierno del Estado de Hidalgo, se presentaron actividades culturales relacionadas con las festividades tradicionales del Xantolo, destacando la participación de agrupaciones musicales y representantes de municipios como Atlapexco, Huejutla, San Felipe Orizatlán, Calnali y Tlahuelilpan, con el fin de enaltecer las tradiciones de la Huasteca Hidalguense.</t>
+  </si>
+  <si>
+    <t>OCSAD</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>Y regresando a temas estatales, comentarle que hoy por la mañana eh pues se informó que está formalizada, ¿eh?, una denuncia contra Uber ante la Procuraduría General de Justicia del Estado de Hidalgo, debido a que la legislación vigente pues no permite la operación de plataformas digitales para el servicio de traslado de personas. Así lo informó Lizbeth Robles Gutiérrez, secretaria de Movilidad y Transporte a en el estado de Hidalgo, perdón. Y durante esta conferencia matutina detalló que el Poder Ejecutivo presentó ya la querella a través de la Coordinación General Jurídica. Respecto a un posible acercamiento entre la administración estatal y Uber, pues aclaró que no existe una comunicación formal con esta empresa y explicó que tanto esta compañía como otras plataformas buscan a la SEMOT pero sin acreditar su personalidad jurídica, o piden información a distancia por lo que no se tiene certeza de quiénes son estos contactos, vale, los representantes de este estas plataformas, estas aplicaciones y pues bueno, estaremos al pendiente de ello, hay una una denuncia y por supuesto habrá habrá por ahí también un posicionamiento por parte de esta de esta empresa que ofrece el servicio de transporte.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CCAUGcK1nfEj_brc8UKscUG-x3FhyXru/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>En información de la de educación, la Secretaría de Educación Pública aquí en Hidalgo, a través de la Dirección General de Fortalecimiento Educativo, realizó la cuarta edición del concurso de canto infantil y juvenil "De mi voz al canto", con la participación de estudiantes de preescolar, primaria y secundaria. Esto con el propósito de acercar a las y los alumnos desde temprana edad a la música mediante la producción, expresión y composición musical.   Durante el evento, la subsecretaria de Educación Básica, Nancy Adriana León Vite, acompañada del titular de la Unidad de Promoción Voluntaria de la SEPH, Virginia Hurtado Salinas, felicitó a las y los participantes y reconoció el esfuerzo y la preparación detrás de cada presentación. "Cuando llega un niño a un concurso es porque ya recibió toda la preparación que le dieron sus maestros y el valioso apoyo de sus padres", eso es lo que señalaron, y destacó la importancia de abrir espacios para que niñas, niños y adolescentes expresen su talento y desarrollen sus habilidades como parte de la visión educativa del gobernador del estado y del Secretario de Educación Pública.   Por su parte, el Director General de Fortalecimiento Educativo, Martín Pérez Sierra, expresó su reconocimiento y agradecimiento a las familias y al personal docente por acompañar e impulsar de manera constante la formación de los estudiantes.   En la Categoría A, correspondiente a preescolar, el primer lugar fue para Allison Taili Lara Ávila de la escuela Coconetzin de Pachuca; el segundo lugar lo obtuvo Evan Santino Vite Morales del plantel Justo Sierra de Xochicoatlán; y el tercero, Leonardo Israel Cisneros Montalvo de la escuela Octavio Paz de Mineral de la Reforma.   En la Categoría B, de primaria, José de Jesús Vite Castro de la primaria general Benito Juárez de Huejutla obtuvo el primer lugar; Renata Badillo Arteaga de la primaria Francisco I. Madero de Metztitlán quedó en segundo sitio; y Odalis Yenis Monroy Ávila de la primaria indígena Vicente Guerrero de San Bartolo Tutotepec ocupó el tercer lugar.   En la Categoría C, finalmente, de secundaria, el primer lugar correspondió a Diego Said Ponce Vázquez de la Secundaria Técnica número 71 de Mineral de la Reforma; el segundo a Dafne Araceli Castañeda Reyes de la Secundaria General Johannes Kepler de Tizayuca; y el tercero a Omner Zuriel Salazar Sánchez de la Secundaria General Ricardo Garibay de Pachuca.   Con estas acciones, la SEPH reafirma su compromiso con impulsar el arte y la expresión musical en las aulas como parte de la formación integral de las y los alumnos hidalguenses. Así la información, información de la SEPH que compartimos con todos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jZKId7zPhihA__pb8Rm1XICDtAGcp6i6/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite</t>
+  </si>
+  <si>
+    <t>Buenas tardes, quisiera reportar a las micros que van de Tulancingo a Acatlán, Almoloya. No prestan un buen servicio, dejan el pasaje tirado cada rato, el viernes desde las 4 no hubo servicio, su base está en Morelos. Eh sin dice, si no por medio de ustedes me hacen el favor de mandar el reporte a quien corresponda, de antemano gracias. El servicio que no están dando completo, no están dando un buen servicio de Tulancingo a Acatlán, Almoloya, puntos intermedios. Esta es la base que está en Morelos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IQkTk7yde1aMQGxkRGGxohXmSg7hNZOn/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ahora sí entramos de lleno a la información de Hidalgo. Ernestina Godoy y Julio Menchaca inauguraron los módulos de atención social "Sí Confío" de la Fiscalía General de la República. En Hidalgo hay coordinación para atender las demandas de justicia y seguridad de la población, en lo que afirmó Julio Menchaca Salazar. De manera simultánea, las 32 delegaciones de la fiscalía pusieron en marcha los módulos de atención social. Desde Hidalgo, la titular de la Fiscalía General de la República, Ernestina Godoy, y el gobernador Julio Menchaca pusieron en marcha los módulos de atención social "Sí Confío" en las 32 entidades del país. Esa estrategia busca fomentar la confianza ciudadana en la procuración de justicia mediante una atención eficiente y orientación oportuna que promueva la cultura de la denuncia. En Hidalgo tenemos un sentido de pertenencia institucional, hay un trabajo muy coordinado para atender ese reclamo que tienen las y los mexicanos: justicia y seguridad, y eso se ha traducido en la generación de empleos y actividad económica. Vamos a escuchar parte de lo que destaca el mandatario estatal de Hidalgo.
+“En Hidalgo tenemos un sentido de pertenencia institucional, que hay un trabajo muy coordinado para estar ateniendo ese reclamo que tienen las y los mexicanos de justicia y de seguridad, y eso se ha significado en generación de empleos, de actividad económica y de todo lo que puede aspirar a las y los mexicanos el tener un mejor presente y un mejor futuro”.
+Bien, es parte de lo que destaca Julio Menchaca Salazar, pues en torno a estas actividades que se hallan en el estado. Asimismo, tras señalar que la trayectoria de Godoy Ramos brinda certeza sobre la impartición de justicia a nivel nacional, el gobernador reconoció el esfuerzo de la Fiscalía General de la República por impulsar un proyecto humano y sensible que comenzó a operar este día en las 32 delegaciones de la institución. Vamos a escuchar parte de lo que dijo la mandataria estatal, bueno, la Fiscal General de la República, Ernestina Godoy Ramos. Vamos a escuchar lo que ella destaca.
+“Lejos quedaron los tiempos en donde la arrogancia, la indiferencia y el desprecio eran la cara más frecuente de la procuración de justicia a nivel federal. Tenemos una legítima aspiración por erradicar el abuso del poder, el poder de la ventanilla y convertirlo en la puerta de acceso hacia una nueva institución. Nuestro objetivo es que quienes acudan a esta fiscalía encuentren una mano franca, cercana y eficiente, que les devuelva la certeza de que la justicia es posible cuando existe voluntad apasionada por servir y por resolver”.
+Bien, lo que dijo la Fiscal de la República, Ernestina Godoy, en el arranque de estos módulos aquí en el estado de Hidalgo. En ese sentido, Laura Ajarín Pérez Alfonso, coordinadora de los módulos "Sí Confío", señaló que cada persona que acude a la fiscalía tiene una historia distinta, preocupaciones que merecen ser escuchadas y preguntas importantes. Por ello, explicó que la labor del personal comienza por reconocer esa realidad, brindar atención responsable y orientar a las personas sobre los pasos que deben seguir en cada caso. Es lo que se destaca desde el estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HLGlHTznMEuJ7IkcDShBG8zA0FLPufDQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Fiscalía General de la República, Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Ernestina Godoy Ramos</t>
+  </si>
+  <si>
+    <t>Y en más de esta misma ruta, mediante labores de inteligencia operativa y coordinación interinstitucional, la Secretaría de Seguridad Pública de Hidalgo desmanteló dos espacios de venta y distribución de drogas, uno en Pachuca y otro en El Cardonal, donde fueron detenidas ocho personas y aseguradas cientos de dosis de probables drogas. La primera intervención se realizó en la colonia Arboledas, en El Cardonal, donde fue detenido un masculino; en el inmueble se localizaron dosis de hierba seca y también, también sustancias granuladas. El segundo operativo se llevó a cabo en la colonia Felipe Ángeles de la capital de Hidalgo, en donde personal de la Secretaría de Seguridad Pública detuvo a cinco masculinos y dos mujeres; en el predio se encontraron también cientos de dosis de probables estupefacientes.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FPB7rKWeLctDeCur1x0BycY00ShTF9m3/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>En más de la información, el gobierno de Hidalgo y la Secretaría Ejecutiva del Sistema Nacional de Seguridad Pública revisaron los avances de 29 proyectos de inversión correspondientes al ejercicio fiscal 2026, orientados al fortalecimiento de las instituciones de seguridad pública, procuración de justicia y del sistema penitenciario en Hidalgo. Como parte de esta coordinación, la Secretaria Ejecutiva del Consejo Estatal de Seguridad Pública, Diana Belén Elizalde Franco, se reunió con la titular Marcela Figueroa Franco para dar seguimiento a la aplicación de recursos federales, identificar áreas prioritarias de atención y revisar el desarrollo de los proyectos programados para el estado de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T-EPAHtdSLFmrovJulv-LjRfPfmi6GaM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría Ejecutiva del Sistema Nacional de Seguridad Pública, Consejo Estatal de Seguridad Pública</t>
+  </si>
+  <si>
+    <t>Diana Belén Elizalde Franco</t>
+  </si>
+  <si>
+    <t>Marcela Figueroa Franco</t>
+  </si>
+  <si>
+    <t>Ernestina Godoy, Fiscal General de la República, estuvo en Hidalgo con el gobernador Julio Menchaca Salazar e inauguraron los módulos de atención social "Sí Confío" de la Fiscalía General de la República. Desde Hidalgo, la titular de la Fiscalía General de la República, Ernestina Godoy, y el gobernador Julio Menchaca pusieron en marcha estos módulos en las 32 entidades del país. Esa estrategia busca fomentar la confianza ciudadana en la procuración de justicia mediante una atención eficiente y orientación oportuna que promuevan la cultura de la denuncia. El gobernador destacó:
+“En Hidalgo tenemos un sentido de pertenencia institucional, que hay un trabajo muy coordinado para estar ateniendo ese reclamo que tienen las y los mexicanos de justicia y de seguridad, y eso se ha significado en generación de empleos, de actividad económica y de todo lo que puede aspirar a las y los mexicanos el tener un mejor presente y un mejor futuro”. 
+Asimismo, tras señalar que la trayectoria de Ernestina Godoy Ramos brinda certeza sobre la impartición de justicia a nivel nacional, el gobernador reconoció el esfuerzo de la Fiscalía General de la República por impulsar un proyecto humano y sensible que comenzó a operar este día en las 32 delegaciones de la institución. Los módulos de atención social, explicó la Fiscal General de la República, tienen como objetivo facilitar el acercamiento de la ciudadanía a la fiscalía mediante acciones de escucha activa, trato digno, orientación e información útil, así como el registro, la canalización y el seguimiento administrativo de los asuntos presentados por las personas usuarias. Ernestina Godoy señaló:
+“Lejos quedaron los tiempos en donde la arrogancia, la indiferencia y el desprecio eran la cara más frecuente de la procuración de justicia a nivel federal. Tenemos una legítima aspiración por erradicar el abuso del poder, el poder de la ventanilla, y convertirlo en la puerta de acceso hacia una nueva institución. Nuestro objetivo es que quienes acudan a esta fiscalía encuentren una mano franca, cercana y eficiente que les devuelva la certeza de que la justicia es posible cuando existe voluntad apasionada por servir y por resolver”.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G_DyYwkuHWJlakOf4nzocODUCfYshx22/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Fiscalía General de la República</t>
+  </si>
+  <si>
+    <t>Ernestina Godoy</t>
+  </si>
+  <si>
+    <t>stá en estos momentos comenzando la intervención, la participación de la Secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez. Nos dejamos con esta conferencia matutina semanal.   Secretaria Lyzbeth Robles Gutiérrez:
+[...] con los requisitos y coberturas que están establecidos en nuestra ley en el artículo 107 y 108.
+Las coberturas de la póliza de seguro es importante que las tomen en cuenta, porque implica una responsabilidad civil frente a terceros por 10,000 UMAS; gastos médicos por lesiones a cada persona pasajera o persona usuaria, de 3,160 UMAS; la responsabilidad civil por cada pasajero o usuario por el mismo monto; gastos médicos por lesiones a la persona conductora; responsabilidad civil por el conductor y en su caso, responsabilidad por pérdida o daño de equipaje.   Esa es la cobertura que deben de tener los seguros, así lo establece la ley. No es cualquier seguro, sino un seguro amplio que cumpla con estas condiciones. Esta de inspección vehicular extraordinaria que estaremos realizando es paralela o de manera distinta a la revisión ordinaria que se lleva a cabo de manera anual.   ¿Dónde se realizará? Se efectuará en las instalaciones del Sistema de Transporte Convencional de Hidalgo, en todas las oficinas itinerantes que se implementen para tal efecto, en las coordinaciones regionales que se distribuyen en el estado de Hidalgo, en las unidades móviles y en territorio, que es algo que estamos innovando que podrá llevarse a cabo de manera específica por la Dirección de Vigilancia y Supervisión del Sistema de Transporte Convencional de Hidalgo.   Y obviamente esta área tiene a su cargo la supervisión del transporte público, quien además podrá seguir realizando su actividad de manera cotidiana con la revisión de toda la documentación correspondiente y las condiciones de la unidad. Siguiente, por favor.   ¿Cómo se diseñó este mecanismo de inspección? La persona concesionaria o la persona conductora debe presentar la información requerida y el personal autorizado para ello verificará la vigencia y los requisitos de la póliza. Si se acredita el cumplimiento, se colocará un distintivo, será un sticker en donde se anotará el número de la póliza y la vigencia, que permite identificar el seguro vigente. Se integrará un registro digital de las unidades inspeccionadas y los resultados de la misma.   Es importante volver a insistir en este tema por lo siguiente: es un exhorto a las personas transportistas de nuestro sector en el ámbito de transporte convencional, porque esta inspección que únicamente la vamos a enfocar en seguro por temas de seguridad, no sustituye la inspección anual que cotidianamente ellos deben de realizar con la periodicidad anunciada. Se realiza de manera paralela a las acciones permanentes de vigilancia y supervisión que tenemos a través del área respectiva del organismo.   Y este es un punto muy muy importante, por eso nuevamente acudimos a esta conferencia de prensa para insistir sobre la trascendencia del punto. La falta de póliza vigente puede dar a la aplicación, obviamente, de las sanciones previstas en la norma y de tajo la revocación de la concesión.   Entonces es nuevamente subrayar y hacer el exhorto a las personas concesionarias y en su caso también a las personas conductoras del transporte público convencional, deben de portar la póliza con la cobertura amplia y vigente en los términos ya mencionados, porque de manera contraria se abrirán procedimientos administrativos que pueden llegar a la revocación de la concesión. Así que es importante que cumplan.   Si por ahí alguno de nuestros compañeros o compañeras transportistas advierte que ya va a vencer su póliza, por favor, es importante que se adelanten y que cumplan con este requisito, de lo contrario podrá abrirse el procedimiento y se podrá revocar la concesión. Siguiente, por favor.   Con este tema muy muy breve, cerramos este punto. Insisto, las consecuencias por no portar el seguro vigente, además de ser un tema obviamente de seguridad para las y los usuarios que obviamente es el tema más trascendente para el servicio, pues la consecuencia es delicada. Así que sí es un exhorto enérgico para el sector del transporte para que cumplan con este requisito.   Y solamente vamos a vertir algunos comentarios inherentes sobre la transportación de personas a través del uso de aplicaciones móviles que, como bien lo comentó el licenciado Edmundo Pineda, fue uno de los temas de la agenda en la semana anterior.   Quiero comentarles que el actuar del estado, el actuar de la Secretaría de Movilidad y Transporte siempre va a estar apegado a la legislación, a la normatividad. Y nuestra ley vigente establece que la transportación de personas está permitida mediante una autorización del Estado.   (Fragmento final de cierre de transmisión/locución reiterando la intervención de la Secretaria y la revisión especial de seguros).</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10u1egYkY0vePjNP2wNxABI5STJecRYZ_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>..la cobertura de Enlace Hidalgo en esta conferencia matutina semanal del Gobierno del Estado, la secretaria de Hacienda, Esther Ramírez Vargas, acaba de participar informando acerca de cuál es la visión del presupuesto 2027...(tos)
+...perdón, perdón usted... para el estado de Hidalgo. Y algo que ha destacado es que se va a continuar con una recaudación eficiente, dijo que se ha demostrado que esto funciona y redunda en más obras y en mejores servicios para la población. También habló de su encuentro reciente del cual en su momento ya le informamos, encuentro reciente con representantes de la Unión Europea y también acerca de los trabajos en modernización catastral y en este sentido el acompañamiento que llevan a cabo desde el Estado con los municipios para que también puedan modernizar su catastro local y con ello también obtener una mejor recaudación.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CDEm4GmLFLctqWePkM2Btj3sx4aDLABP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>María Esther Ramírez Vargas</t>
+  </si>
+  <si>
+    <t>En estos momentos está iniciando ya la conferencia de todas las semanas allá del Gobierno del Estado de Hidalgo, así que eh pues en instantes estaremos haciendo también el enlace con nuestro compañero Juan Carlos Santa María. En tanto, pues vámonos directamente a la a la conferencia, lo que se está presentando ya precisamente en estos momentos el titular de Comunicación Social del Gobierno del Estado de Hidalgo, quien estará presentando quiénes estarán a cargo en este lunes de la conferencia de prensa, que secretarios y, por supuesto, también cuáles serán los temas a tratar. Así que vamos para allá.
+...de gestión y vinculación de proyectos especiales de la Secretaría del Despacho, Fernando Olvera Juárez, y de Juan de Dios Nochebuena, presidente municipal de Atlapexco. Muy buenos días y muchas gracias por acudir a esta a esta conferencia de prensa. En la cosmovisión de nuestros pueblos, al finalizar octubre y los primeros días de noviembre, hay la posibilidad de un reencuentro, de una cita con las personas que no se nos adelantaron en el camino y que de una manera muy especial en regiones como la Huasteca Hidalguense les damos la bienvenida.
+Se trata de días muy especiales en la sierra, en la Huasteca, en diferentes rincones de nuestro país y casi casi dos días o más de pinceladas que como retrataría nuestro gran Gabriel García Márquez, nuestro Gabo, es una especie de realismo mágico porque dicen que eh a veces los sueños se confunden con la vida porque nunca sabemos cuándo termina una y dónde comienzan los otros.
+Y yo le manifiesto esto porque tenemos aquí una manifestación de vida para recibir a nuestros muertos. Eh son compañeras y compañeros, hermanos de la Huasteca Hidalguense con la representación del Xantolo. Ellos vienen del municipio de Atlapexco. Muy buenos días y gracias por estar aquí. Bienvenidas y bienvenidos.
+Adelante, por favor, producción.
+(Se escucha música tradicional de la Huasteca)
+Esto es parte de la fiesta y del color de la Huasteca Hidalguense, Huejutla, Atlapexco, San Felipe Orizatlán, Calnali, Tlahuelilpan, en fin, es una fiesta de color al que estamos convocados en los días por venir.
+Le quiero presentar un video precisamente de esta celebración, de cómo es en Atlapexco. Si está lista producción, vamos adelante.
+Hemos eh escuchado cómo ha sido un inicio diferente de esta conferencia matutina semanal con la presencia de de de músicos y eh también de de un grupo representativo de la Huasteca Hidalguense dando cuenta de lo que en En Berlín dar una muestra para la celebración del Xantolo en aquella región de la entidad, pero también el día de muertos cada región con su propio sabor y características, pero son días importantes en la tradición mexicana y es así como ha iniciado esta conferencia matutina semanal en la que también habrá información en otros rubros de la Secretaría de Hacienda y de la Secretaría de Movilidad y Transporte. En el cual presente en la conferencia matutina semanal y le seguiremos llevando las eh los detalles, las incidencias de esta conferencia. Continuamos con más en Enlace Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10nOi4fPArJCLzRzLxHi4Tsv0HEdN3Rsp/view?usp=drivesdk</t>
   </si>
 </sst>
 </file>
@@ -1314,8 +1103,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X22" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X22" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X11" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X11" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1711,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -1785,135 +1574,133 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="S2" s="5">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="V2" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="W2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="X2" s="5"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="C3" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>22</v>
@@ -1922,241 +1709,241 @@
         <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P3" s="3" t="s">
+      <c r="R3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="3">
+        <v>165</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S3" s="3">
-        <v>52</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K4" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="S4" s="3">
-        <v>358</v>
+        <v>34</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U4" s="3"/>
-      <c r="V4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C5" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="S5" s="3">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="W5" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C6" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="S6" s="3">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -2164,250 +1951,250 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C7" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="S7" s="3">
-        <v>213</v>
+        <v>42</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X7" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C8" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="S8" s="3">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="V8" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="W8" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="C9" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="S9" s="3">
-        <v>94</v>
+        <v>397</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="6">
+        <v>46321</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>15</v>
@@ -2416,849 +2203,103 @@
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="S10" s="3">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
+      <c r="V10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="C11" s="6">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="S11" s="3">
-        <v>108</v>
+        <v>396</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S12" s="3">
-        <v>29</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>20</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="3">
-        <v>130</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>19</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S14" s="3">
-        <v>120</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="S15" s="3">
-        <v>244</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>10</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S16" s="3">
-        <v>201</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>9</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S17" s="3">
-        <v>37</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="X17" s="3"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>8</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S18" s="3">
-        <v>98</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>5</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S19" s="3">
-        <v>53</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>3</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S20" s="3">
-        <v>56</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>2</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S21" s="3">
-        <v>138</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>1</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S22" s="3">
-        <v>69</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBB646B-3E55-4CA5-AB4E-2E30873401D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6146D694-8520-47B5-A96A-FB30B5E9B91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="224">
   <si>
     <t>#</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Segundos</t>
   </si>
   <si>
-    <t>Negativo</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -191,214 +188,567 @@
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>SSPH</t>
-  </si>
-  <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
     <t>Mañanera</t>
   </si>
   <si>
-    <t>Yazmín Leonardo</t>
-  </si>
-  <si>
-    <t>Durante la conferencia matutina del Gobierno del Estado de Hidalgo, la secretaria de Hacienda, Esther Ramírez Vargas, presentó los detalles sobre la visión del presupuesto 2027 para la entidad. Destacó que se mantendrá una recaudación eficiente para financiar más obras y mejores servicios públicos, y mencionó los trabajos recientes de modernización catastral en colaboración con los municipios. Asimismo, informó sobre su encuentro con representantes de la Unión Europea.</t>
-  </si>
-  <si>
     <t>Hacienda</t>
   </si>
   <si>
-    <t>Aclaración en Mañanera</t>
-  </si>
-  <si>
-    <t>Durante la conferencia matutina, la secretaria de Movilidad y Transporte en el estado de Hidalgo, Lizbeth Robles Gutiérrez, informó que se ha formalizado una denuncia ante la Procuraduría General de Justicia del Estado de Hidalgo en contra de la empresa Uber, debido a que la legislación local no permite la operación de plataformas digitales para el traslado de personas. La funcionaria detalló que el Poder Ejecutivo presentó la querella a través de la Coordinación General Jurídica. Asimismo, aclaró que no existe una comunicación formal con dicha compañía y señaló que, aunque otras plataformas han buscado acercarse a la Secretaría (SEMOT), estas no han acreditado su personalidad jurídica o solicitan información a distancia sin certeza sobre la identidad de sus representantes.</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
     <t>Apps de transporte</t>
   </si>
   <si>
-    <t>SSPH/Bol.989/2026</t>
-  </si>
-  <si>
-    <t>SSPH desmantela dos puntos de narcomenudeo y detiene a ocho personas en Hidalgo</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1333/2026</t>
-  </si>
-  <si>
     <t>Radio Lobo 96.7 FM</t>
   </si>
   <si>
-    <t>Ernestina Godoy y Julio Menchaca inauguran los Módulos de Atención Social ¡Sí Confío! de la FGR</t>
-  </si>
-  <si>
     <t>Gina Lorenzo</t>
   </si>
   <si>
     <t>Enlace Noticias</t>
   </si>
   <si>
-    <t>Entrega de instalaciones</t>
-  </si>
-  <si>
-    <t>Segobh/SECESP/Bol.Bol.04/2026</t>
-  </si>
-  <si>
-    <t>Estratégica coordinación con la Federación fortalecerá la seguridad pública en Hidalgo</t>
-  </si>
-  <si>
-    <t>FASP</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1944-A/2026</t>
-  </si>
-  <si>
-    <t>Premia SEPH el talento estudiantil en el 4.º Concurso de Canto “De mi Voz al Canto”</t>
-  </si>
-  <si>
     <t>Justa Académica</t>
   </si>
   <si>
-    <t>Durante la conferencia matutina semanal, la secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez, anunció el lanzamiento de un operativo de inspección vehicular extraordinaria enfocado exclusivamente en la verificación de pólizas de seguro de las unidades de transporte público convencional. La funcionaria destacó que esta revisión es de carácter obligatorio y opera de forma paralela a las inspecciones anuales ordinarias. Asimismo, advirtió de manera enérgica a los concesionarios y conductores sobre la trascendencia de contar con un seguro amplio que cumpla con los requisitos estipulados en los artículos 107 y 108 de la ley local (incluyendo coberturas de responsabilidad civil y gastos médicos). Robles Gutiérrez subrayó que la falta de una póliza vigente no solo amerita sanciones económicas o administrativas, sino que puede derivar directamente en la revocación de la concesión. Las revisiones se llevarán a cabo en las instalaciones del Sistema de Transporte Convencional de Hidalgo, oficinas itinerantes, unidades móviles y a través de operativos en campo implementados por la Dirección de Vigilancia y Supervisión. Por último, se abordó brevemente el marco legal que regula la transportación de personas mediante aplicaciones móviles en el estado.</t>
-  </si>
-  <si>
-    <t>Mañanera de Hidalgo</t>
-  </si>
-  <si>
-    <t>Locutor Irving Sánchez da lectura a comentario de radioescucha que reporta irregularidades y deficiencias en el servicio de transporte colectivo de la ruta que va de Tulancingo hacia Acatlán y Almoloya, cuya base se encuentra en Morelos. De acuerdo con el reporte, las unidades no brindan un servicio de calidad, ya que dejan pasajeros varados con frecuencia y señaló que el pasado viernes, a partir de las 4:00 horas, se quedaron sin servicio. Ante esta situación, solicitó que se envíe el reporte a las autoridades o áreas correspondientes para su atención.</t>
-  </si>
-  <si>
-    <t>STCH</t>
-  </si>
-  <si>
-    <t>Queja transporte público</t>
-  </si>
-  <si>
-    <t>Durante la conferencia de prensa matutina del Gobierno del Estado de Hidalgo, se presentaron actividades culturales relacionadas con las festividades tradicionales del Xantolo, destacando la participación de agrupaciones musicales y representantes de municipios como Atlapexco, Huejutla, San Felipe Orizatlán, Calnali y Tlahuelilpan, con el fin de enaltecer las tradiciones de la Huasteca Hidalguense.</t>
-  </si>
-  <si>
-    <t>OCSAD</t>
-  </si>
-  <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>Y regresando a temas estatales, comentarle que hoy por la mañana eh pues se informó que está formalizada, ¿eh?, una denuncia contra Uber ante la Procuraduría General de Justicia del Estado de Hidalgo, debido a que la legislación vigente pues no permite la operación de plataformas digitales para el servicio de traslado de personas. Así lo informó Lizbeth Robles Gutiérrez, secretaria de Movilidad y Transporte a en el estado de Hidalgo, perdón. Y durante esta conferencia matutina detalló que el Poder Ejecutivo presentó ya la querella a través de la Coordinación General Jurídica. Respecto a un posible acercamiento entre la administración estatal y Uber, pues aclaró que no existe una comunicación formal con esta empresa y explicó que tanto esta compañía como otras plataformas buscan a la SEMOT pero sin acreditar su personalidad jurídica, o piden información a distancia por lo que no se tiene certeza de quiénes son estos contactos, vale, los representantes de este estas plataformas, estas aplicaciones y pues bueno, estaremos al pendiente de ello, hay una una denuncia y por supuesto habrá habrá por ahí también un posicionamiento por parte de esta de esta empresa que ofrece el servicio de transporte.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CCAUGcK1nfEj_brc8UKscUG-x3FhyXru/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado de Hidalgo</t>
-  </si>
-  <si>
     <t>Lyzbeth Robles</t>
   </si>
   <si>
-    <t>En información de la de educación, la Secretaría de Educación Pública aquí en Hidalgo, a través de la Dirección General de Fortalecimiento Educativo, realizó la cuarta edición del concurso de canto infantil y juvenil "De mi voz al canto", con la participación de estudiantes de preescolar, primaria y secundaria. Esto con el propósito de acercar a las y los alumnos desde temprana edad a la música mediante la producción, expresión y composición musical.   Durante el evento, la subsecretaria de Educación Básica, Nancy Adriana León Vite, acompañada del titular de la Unidad de Promoción Voluntaria de la SEPH, Virginia Hurtado Salinas, felicitó a las y los participantes y reconoció el esfuerzo y la preparación detrás de cada presentación. "Cuando llega un niño a un concurso es porque ya recibió toda la preparación que le dieron sus maestros y el valioso apoyo de sus padres", eso es lo que señalaron, y destacó la importancia de abrir espacios para que niñas, niños y adolescentes expresen su talento y desarrollen sus habilidades como parte de la visión educativa del gobernador del estado y del Secretario de Educación Pública.   Por su parte, el Director General de Fortalecimiento Educativo, Martín Pérez Sierra, expresó su reconocimiento y agradecimiento a las familias y al personal docente por acompañar e impulsar de manera constante la formación de los estudiantes.   En la Categoría A, correspondiente a preescolar, el primer lugar fue para Allison Taili Lara Ávila de la escuela Coconetzin de Pachuca; el segundo lugar lo obtuvo Evan Santino Vite Morales del plantel Justo Sierra de Xochicoatlán; y el tercero, Leonardo Israel Cisneros Montalvo de la escuela Octavio Paz de Mineral de la Reforma.   En la Categoría B, de primaria, José de Jesús Vite Castro de la primaria general Benito Juárez de Huejutla obtuvo el primer lugar; Renata Badillo Arteaga de la primaria Francisco I. Madero de Metztitlán quedó en segundo sitio; y Odalis Yenis Monroy Ávila de la primaria indígena Vicente Guerrero de San Bartolo Tutotepec ocupó el tercer lugar.   En la Categoría C, finalmente, de secundaria, el primer lugar correspondió a Diego Said Ponce Vázquez de la Secundaria Técnica número 71 de Mineral de la Reforma; el segundo a Dafne Araceli Castañeda Reyes de la Secundaria General Johannes Kepler de Tizayuca; y el tercero a Omner Zuriel Salazar Sánchez de la Secundaria General Ricardo Garibay de Pachuca.   Con estas acciones, la SEPH reafirma su compromiso con impulsar el arte y la expresión musical en las aulas como parte de la formación integral de las y los alumnos hidalguenses. Así la información, información de la SEPH que compartimos con todos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1jZKId7zPhihA__pb8Rm1XICDtAGcp6i6/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Nancy Adriana León Vite</t>
-  </si>
-  <si>
-    <t>Buenas tardes, quisiera reportar a las micros que van de Tulancingo a Acatlán, Almoloya. No prestan un buen servicio, dejan el pasaje tirado cada rato, el viernes desde las 4 no hubo servicio, su base está en Morelos. Eh sin dice, si no por medio de ustedes me hacen el favor de mandar el reporte a quien corresponda, de antemano gracias. El servicio que no están dando completo, no están dando un buen servicio de Tulancingo a Acatlán, Almoloya, puntos intermedios. Esta es la base que está en Morelos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1IQkTk7yde1aMQGxkRGGxohXmSg7hNZOn/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Ahora sí entramos de lleno a la información de Hidalgo. Ernestina Godoy y Julio Menchaca inauguraron los módulos de atención social "Sí Confío" de la Fiscalía General de la República. En Hidalgo hay coordinación para atender las demandas de justicia y seguridad de la población, en lo que afirmó Julio Menchaca Salazar. De manera simultánea, las 32 delegaciones de la fiscalía pusieron en marcha los módulos de atención social. Desde Hidalgo, la titular de la Fiscalía General de la República, Ernestina Godoy, y el gobernador Julio Menchaca pusieron en marcha los módulos de atención social "Sí Confío" en las 32 entidades del país. Esa estrategia busca fomentar la confianza ciudadana en la procuración de justicia mediante una atención eficiente y orientación oportuna que promueva la cultura de la denuncia. En Hidalgo tenemos un sentido de pertenencia institucional, hay un trabajo muy coordinado para atender ese reclamo que tienen las y los mexicanos: justicia y seguridad, y eso se ha traducido en la generación de empleos y actividad económica. Vamos a escuchar parte de lo que destaca el mandatario estatal de Hidalgo.
-“En Hidalgo tenemos un sentido de pertenencia institucional, que hay un trabajo muy coordinado para estar ateniendo ese reclamo que tienen las y los mexicanos de justicia y de seguridad, y eso se ha significado en generación de empleos, de actividad económica y de todo lo que puede aspirar a las y los mexicanos el tener un mejor presente y un mejor futuro”.
-Bien, es parte de lo que destaca Julio Menchaca Salazar, pues en torno a estas actividades que se hallan en el estado. Asimismo, tras señalar que la trayectoria de Godoy Ramos brinda certeza sobre la impartición de justicia a nivel nacional, el gobernador reconoció el esfuerzo de la Fiscalía General de la República por impulsar un proyecto humano y sensible que comenzó a operar este día en las 32 delegaciones de la institución. Vamos a escuchar parte de lo que dijo la mandataria estatal, bueno, la Fiscal General de la República, Ernestina Godoy Ramos. Vamos a escuchar lo que ella destaca.
-“Lejos quedaron los tiempos en donde la arrogancia, la indiferencia y el desprecio eran la cara más frecuente de la procuración de justicia a nivel federal. Tenemos una legítima aspiración por erradicar el abuso del poder, el poder de la ventanilla y convertirlo en la puerta de acceso hacia una nueva institución. Nuestro objetivo es que quienes acudan a esta fiscalía encuentren una mano franca, cercana y eficiente, que les devuelva la certeza de que la justicia es posible cuando existe voluntad apasionada por servir y por resolver”.
-Bien, lo que dijo la Fiscal de la República, Ernestina Godoy, en el arranque de estos módulos aquí en el estado de Hidalgo. En ese sentido, Laura Ajarín Pérez Alfonso, coordinadora de los módulos "Sí Confío", señaló que cada persona que acude a la fiscalía tiene una historia distinta, preocupaciones que merecen ser escuchadas y preguntas importantes. Por ello, explicó que la labor del personal comienza por reconocer esa realidad, brindar atención responsable y orientar a las personas sobre los pasos que deben seguir en cada caso. Es lo que se destaca desde el estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HLGlHTznMEuJ7IkcDShBG8zA0FLPufDQ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Fiscalía General de la República, Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Ernestina Godoy Ramos</t>
-  </si>
-  <si>
-    <t>Y en más de esta misma ruta, mediante labores de inteligencia operativa y coordinación interinstitucional, la Secretaría de Seguridad Pública de Hidalgo desmanteló dos espacios de venta y distribución de drogas, uno en Pachuca y otro en El Cardonal, donde fueron detenidas ocho personas y aseguradas cientos de dosis de probables drogas. La primera intervención se realizó en la colonia Arboledas, en El Cardonal, donde fue detenido un masculino; en el inmueble se localizaron dosis de hierba seca y también, también sustancias granuladas. El segundo operativo se llevó a cabo en la colonia Felipe Ángeles de la capital de Hidalgo, en donde personal de la Secretaría de Seguridad Pública detuvo a cinco masculinos y dos mujeres; en el predio se encontraron también cientos de dosis de probables estupefacientes.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1FPB7rKWeLctDeCur1x0BycY00ShTF9m3/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>En más de la información, el gobierno de Hidalgo y la Secretaría Ejecutiva del Sistema Nacional de Seguridad Pública revisaron los avances de 29 proyectos de inversión correspondientes al ejercicio fiscal 2026, orientados al fortalecimiento de las instituciones de seguridad pública, procuración de justicia y del sistema penitenciario en Hidalgo. Como parte de esta coordinación, la Secretaria Ejecutiva del Consejo Estatal de Seguridad Pública, Diana Belén Elizalde Franco, se reunió con la titular Marcela Figueroa Franco para dar seguimiento a la aplicación de recursos federales, identificar áreas prioritarias de atención y revisar el desarrollo de los proyectos programados para el estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1T-EPAHtdSLFmrovJulv-LjRfPfmi6GaM/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría Ejecutiva del Sistema Nacional de Seguridad Pública, Consejo Estatal de Seguridad Pública</t>
-  </si>
-  <si>
-    <t>Diana Belén Elizalde Franco</t>
-  </si>
-  <si>
-    <t>Marcela Figueroa Franco</t>
-  </si>
-  <si>
-    <t>Ernestina Godoy, Fiscal General de la República, estuvo en Hidalgo con el gobernador Julio Menchaca Salazar e inauguraron los módulos de atención social "Sí Confío" de la Fiscalía General de la República. Desde Hidalgo, la titular de la Fiscalía General de la República, Ernestina Godoy, y el gobernador Julio Menchaca pusieron en marcha estos módulos en las 32 entidades del país. Esa estrategia busca fomentar la confianza ciudadana en la procuración de justicia mediante una atención eficiente y orientación oportuna que promuevan la cultura de la denuncia. El gobernador destacó:
-“En Hidalgo tenemos un sentido de pertenencia institucional, que hay un trabajo muy coordinado para estar ateniendo ese reclamo que tienen las y los mexicanos de justicia y de seguridad, y eso se ha significado en generación de empleos, de actividad económica y de todo lo que puede aspirar a las y los mexicanos el tener un mejor presente y un mejor futuro”. 
-Asimismo, tras señalar que la trayectoria de Ernestina Godoy Ramos brinda certeza sobre la impartición de justicia a nivel nacional, el gobernador reconoció el esfuerzo de la Fiscalía General de la República por impulsar un proyecto humano y sensible que comenzó a operar este día en las 32 delegaciones de la institución. Los módulos de atención social, explicó la Fiscal General de la República, tienen como objetivo facilitar el acercamiento de la ciudadanía a la fiscalía mediante acciones de escucha activa, trato digno, orientación e información útil, así como el registro, la canalización y el seguimiento administrativo de los asuntos presentados por las personas usuarias. Ernestina Godoy señaló:
-“Lejos quedaron los tiempos en donde la arrogancia, la indiferencia y el desprecio eran la cara más frecuente de la procuración de justicia a nivel federal. Tenemos una legítima aspiración por erradicar el abuso del poder, el poder de la ventanilla, y convertirlo en la puerta de acceso hacia una nueva institución. Nuestro objetivo es que quienes acudan a esta fiscalía encuentren una mano franca, cercana y eficiente que les devuelva la certeza de que la justicia es posible cuando existe voluntad apasionada por servir y por resolver”.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1G_DyYwkuHWJlakOf4nzocODUCfYshx22/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Fiscalía General de la República</t>
-  </si>
-  <si>
-    <t>Ernestina Godoy</t>
-  </si>
-  <si>
-    <t>stá en estos momentos comenzando la intervención, la participación de la Secretaria de Movilidad y Transporte, Lyzbeth Robles Gutiérrez. Nos dejamos con esta conferencia matutina semanal.   Secretaria Lyzbeth Robles Gutiérrez:
-[...] con los requisitos y coberturas que están establecidos en nuestra ley en el artículo 107 y 108.
-Las coberturas de la póliza de seguro es importante que las tomen en cuenta, porque implica una responsabilidad civil frente a terceros por 10,000 UMAS; gastos médicos por lesiones a cada persona pasajera o persona usuaria, de 3,160 UMAS; la responsabilidad civil por cada pasajero o usuario por el mismo monto; gastos médicos por lesiones a la persona conductora; responsabilidad civil por el conductor y en su caso, responsabilidad por pérdida o daño de equipaje.   Esa es la cobertura que deben de tener los seguros, así lo establece la ley. No es cualquier seguro, sino un seguro amplio que cumpla con estas condiciones. Esta de inspección vehicular extraordinaria que estaremos realizando es paralela o de manera distinta a la revisión ordinaria que se lleva a cabo de manera anual.   ¿Dónde se realizará? Se efectuará en las instalaciones del Sistema de Transporte Convencional de Hidalgo, en todas las oficinas itinerantes que se implementen para tal efecto, en las coordinaciones regionales que se distribuyen en el estado de Hidalgo, en las unidades móviles y en territorio, que es algo que estamos innovando que podrá llevarse a cabo de manera específica por la Dirección de Vigilancia y Supervisión del Sistema de Transporte Convencional de Hidalgo.   Y obviamente esta área tiene a su cargo la supervisión del transporte público, quien además podrá seguir realizando su actividad de manera cotidiana con la revisión de toda la documentación correspondiente y las condiciones de la unidad. Siguiente, por favor.   ¿Cómo se diseñó este mecanismo de inspección? La persona concesionaria o la persona conductora debe presentar la información requerida y el personal autorizado para ello verificará la vigencia y los requisitos de la póliza. Si se acredita el cumplimiento, se colocará un distintivo, será un sticker en donde se anotará el número de la póliza y la vigencia, que permite identificar el seguro vigente. Se integrará un registro digital de las unidades inspeccionadas y los resultados de la misma.   Es importante volver a insistir en este tema por lo siguiente: es un exhorto a las personas transportistas de nuestro sector en el ámbito de transporte convencional, porque esta inspección que únicamente la vamos a enfocar en seguro por temas de seguridad, no sustituye la inspección anual que cotidianamente ellos deben de realizar con la periodicidad anunciada. Se realiza de manera paralela a las acciones permanentes de vigilancia y supervisión que tenemos a través del área respectiva del organismo.   Y este es un punto muy muy importante, por eso nuevamente acudimos a esta conferencia de prensa para insistir sobre la trascendencia del punto. La falta de póliza vigente puede dar a la aplicación, obviamente, de las sanciones previstas en la norma y de tajo la revocación de la concesión.   Entonces es nuevamente subrayar y hacer el exhorto a las personas concesionarias y en su caso también a las personas conductoras del transporte público convencional, deben de portar la póliza con la cobertura amplia y vigente en los términos ya mencionados, porque de manera contraria se abrirán procedimientos administrativos que pueden llegar a la revocación de la concesión. Así que es importante que cumplan.   Si por ahí alguno de nuestros compañeros o compañeras transportistas advierte que ya va a vencer su póliza, por favor, es importante que se adelanten y que cumplan con este requisito, de lo contrario podrá abrirse el procedimiento y se podrá revocar la concesión. Siguiente, por favor.   Con este tema muy muy breve, cerramos este punto. Insisto, las consecuencias por no portar el seguro vigente, además de ser un tema obviamente de seguridad para las y los usuarios que obviamente es el tema más trascendente para el servicio, pues la consecuencia es delicada. Así que sí es un exhorto enérgico para el sector del transporte para que cumplan con este requisito.   Y solamente vamos a vertir algunos comentarios inherentes sobre la transportación de personas a través del uso de aplicaciones móviles que, como bien lo comentó el licenciado Edmundo Pineda, fue uno de los temas de la agenda en la semana anterior.   Quiero comentarles que el actuar del estado, el actuar de la Secretaría de Movilidad y Transporte siempre va a estar apegado a la legislación, a la normatividad. Y nuestra ley vigente establece que la transportación de personas está permitida mediante una autorización del Estado.   (Fragmento final de cierre de transmisión/locución reiterando la intervención de la Secretaria y la revisión especial de seguros).</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10u1egYkY0vePjNP2wNxABI5STJecRYZ_/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>..la cobertura de Enlace Hidalgo en esta conferencia matutina semanal del Gobierno del Estado, la secretaria de Hacienda, Esther Ramírez Vargas, acaba de participar informando acerca de cuál es la visión del presupuesto 2027...(tos)
-...perdón, perdón usted... para el estado de Hidalgo. Y algo que ha destacado es que se va a continuar con una recaudación eficiente, dijo que se ha demostrado que esto funciona y redunda en más obras y en mejores servicios para la población. También habló de su encuentro reciente del cual en su momento ya le informamos, encuentro reciente con representantes de la Unión Europea y también acerca de los trabajos en modernización catastral y en este sentido el acompañamiento que llevan a cabo desde el Estado con los municipios para que también puedan modernizar su catastro local y con ello también obtener una mejor recaudación.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CDEm4GmLFLctqWePkM2Btj3sx4aDLABP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
     <t>María Esther Ramírez Vargas</t>
   </si>
   <si>
-    <t>En estos momentos está iniciando ya la conferencia de todas las semanas allá del Gobierno del Estado de Hidalgo, así que eh pues en instantes estaremos haciendo también el enlace con nuestro compañero Juan Carlos Santa María. En tanto, pues vámonos directamente a la a la conferencia, lo que se está presentando ya precisamente en estos momentos el titular de Comunicación Social del Gobierno del Estado de Hidalgo, quien estará presentando quiénes estarán a cargo en este lunes de la conferencia de prensa, que secretarios y, por supuesto, también cuáles serán los temas a tratar. Así que vamos para allá.
-...de gestión y vinculación de proyectos especiales de la Secretaría del Despacho, Fernando Olvera Juárez, y de Juan de Dios Nochebuena, presidente municipal de Atlapexco. Muy buenos días y muchas gracias por acudir a esta a esta conferencia de prensa. En la cosmovisión de nuestros pueblos, al finalizar octubre y los primeros días de noviembre, hay la posibilidad de un reencuentro, de una cita con las personas que no se nos adelantaron en el camino y que de una manera muy especial en regiones como la Huasteca Hidalguense les damos la bienvenida.
-Se trata de días muy especiales en la sierra, en la Huasteca, en diferentes rincones de nuestro país y casi casi dos días o más de pinceladas que como retrataría nuestro gran Gabriel García Márquez, nuestro Gabo, es una especie de realismo mágico porque dicen que eh a veces los sueños se confunden con la vida porque nunca sabemos cuándo termina una y dónde comienzan los otros.
-Y yo le manifiesto esto porque tenemos aquí una manifestación de vida para recibir a nuestros muertos. Eh son compañeras y compañeros, hermanos de la Huasteca Hidalguense con la representación del Xantolo. Ellos vienen del municipio de Atlapexco. Muy buenos días y gracias por estar aquí. Bienvenidas y bienvenidos.
-Adelante, por favor, producción.
-(Se escucha música tradicional de la Huasteca)
-Esto es parte de la fiesta y del color de la Huasteca Hidalguense, Huejutla, Atlapexco, San Felipe Orizatlán, Calnali, Tlahuelilpan, en fin, es una fiesta de color al que estamos convocados en los días por venir.
-Le quiero presentar un video precisamente de esta celebración, de cómo es en Atlapexco. Si está lista producción, vamos adelante.
-Hemos eh escuchado cómo ha sido un inicio diferente de esta conferencia matutina semanal con la presencia de de de músicos y eh también de de un grupo representativo de la Huasteca Hidalguense dando cuenta de lo que en En Berlín dar una muestra para la celebración del Xantolo en aquella región de la entidad, pero también el día de muertos cada región con su propio sabor y características, pero son días importantes en la tradición mexicana y es así como ha iniciado esta conferencia matutina semanal en la que también habrá información en otros rubros de la Secretaría de Hacienda y de la Secretaría de Movilidad y Transporte. En el cual presente en la conferencia matutina semanal y le seguiremos llevando las eh los detalles, las incidencias de esta conferencia. Continuamos con más en Enlace Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10nOi4fPArJCLzRzLxHi4Tsv0HEdN3Rsp/view?usp=drivesdk</t>
+    <t>Radioescucha reportó el envío de fotografías que confirman casos del virus de Coxsackie en un menor de edad, el cual presenta síntomas característicos en manos, boca y pies. Tras ser llevado al centro de salud, el diagnóstico fue confirmado, por lo que se emitieron agradecimientos por el aviso preventivo para alertar a las autoridades educativas y mantenerlas al pendiente de la situación.</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <t>Brote epidémico</t>
+  </si>
+  <si>
+    <t>Santiago Tulantepec</t>
+  </si>
+  <si>
+    <t>Fíjate que te están enviando, te están enviando en estos momentos las fotos, en efecto sí, de del pequeñito, del pequeñito que sí tiene el virus del Coxsackie.
+ Ajá.
+Y y gracias, gracias por las imágenes y, efectivamente, aparecen en manos, boca y pies, ya nos dicen por acá que lo llevaron al centro de salud y eso le detectaron y pues gracias por el aviso, gracias por el aviso importante perfecto, perfecto.
+Jesús: Para que las autoridades educativas también estén al pendiente.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1645R1UapeM7lSqtSIRVsrQ-jUGWPlQsF/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (CAASIM) informó sobre una suspensión temporal en el suministro de agua potable que afecta a 26 colonias y zonas de Pachuca debido a los trabajos en una línea de conducción vinculados con la ampliación del bulevar Felipe Ángeles. Las labores iniciaron este martes 27 de octubre a las 6:00 horas con una duración estimada de 24 horas. No obstante, la dependencia advirtió que la recuperación del servicio será gradual y podría tomar otras 24 horas adicionales una vez concluidos los trabajos. Entre las zonas afectadas se encuentran colonias como San Antonio, Vistas de Pachuca, Real de San Francisco, Venta Prieta, Puerta de Hierro, entre otras.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Caasim</t>
+  </si>
+  <si>
+    <t>Abasto De Agua</t>
+  </si>
+  <si>
+    <t>Y de Brasil, de Brasil nos regresamos acá a Pachuca, porque como seguramente ya se habrá dado cuenta, habitantes de 26 colonias y zonas de Pachuca pues tienen afectaciones en el suministro de agua potable debido a trabajos en una línea de conducción vinculados con la ampliación del bulevar Felipe Ángeles. Las maniobras comenzaron a las 6:00, 6:00 de la mañana de hoy martes 27 de octubre y tendrán una duración estimada de 24 horas. La Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, la CAASIM, informó que una vez terminada la intervención, la recuperación del servicio será gradual y podría requerir hasta otras 24 horas. Esto significa que el término de los trabajos no implicará el regreso inmediato del agua a todas las zonas involucradas. Si las labores concluyen dentro del plazo previsto, finalizarían alrededor de las 6:00, 6 horas del próximo miércoles, o sea mañana 28 de octubre. Después comenzaría la recuperación que podría extenderse hasta la madrugada del jueves, jueves 29. ¿Qué colonias tienen las afectaciones en el suministro? El aviso de CAASIM contempla afectaciones en Sector Primario, San Antonio, Ampliación San Antonio, Vistas de Pachuca, Rancho la Colonia, Prismas, Carlos Rovirosa, Privada las Torre, las Torres, perdón, Privada de León, Geovillas, Tulipanes, Quinta Bonita y Magisterio. También se incluyen Real de San Francisco, el Paraíso, los Pinos, Bosques del Mineral, Real de la Plata, Real de Pachuca, Isté, Ollamel, Club de Golf, Venta Prieta, Centro Minero, Puerta de Hierro y Plaza del Valle. El comunicado anticipa afectaciones en el abastecimiento, pero no especifica si todas estas zonas tendrán una interrupción total o si algunas registrarán una disminución en el suministro. Tampoco establece horarios diferenciados para cada una. Por ello, quienes viven, quienes viven o tienen negocios en los puntos incluidos, deberán considerar tanto el periodo de intervención como el periodo posterior que necesitará el sistema para recuperar el servicio.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ABqFnUc0FEJN8_q-SVRVR_Ryv_e1uLYg/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Entrevista</t>
+  </si>
+  <si>
+    <t>En el marco de la conmemoración del Día del Médico y la Médica, el gobernador del estado, Julio Menchaca Salazar, encabezó un homenaje para reconocer la trayectoria, vocación y el compromiso social de las y los profesionales de la salud en Hidalgo. Durante su mensaje, en el que compartió una reflexión personal sobre el esfuerzo que implica esta profesión, destacó que la labor médica va más allá de la técnica, implicando sensibilidad ante el dolor humano y un contacto diario y cercano con la población. Asimismo, resaltó la importancia de la preparación constante ante los retos sanitarios y ambientales actuales, reconociendo tanto a quienes laboran en zonas urbanas como a los que desempeñan su labor en las regiones más alejadas del estado.</t>
+  </si>
+  <si>
+    <t>Día del médico</t>
+  </si>
+  <si>
+    <t>Y esta mañana el gobernador Julio Menchaca Salazar encabezó la felicitación y reconocimiento de cada una de las médicas y los médicos y todos los involucrados en la salud del pueblo de Hidalgo. Este en su día, Día de la Médica y el Médico, el gobernador también recordó alguna historia de vida de su vida, eh dio a conocer cuando en su familia pues luchó para que fuesen médicos dentro de los hermanos. Escuchemos al gobernador Julio Menchaca Salazar.
+"Fue mi hermano menor, Andrés. Y a través de él como familiar pues conocimos el sacrificio que se realiza en el estudio. La necesidad que tienen las personas de acudir a quien tienen con quien tienen confianza. Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al Estado de Hidalgo y a México proyectándolo con su saber. En todas las carreras debemos estudiar constantemente, pero particularmente en medicina es fundamentalmente necesario estar preparados porque existen muchos temas que si bien ayudan en la tecnología, también han modificado el esquema ambiental y han generado problemas tan serios como la terrible pandemia que tuvimos hace algunos años".
+En esta celebración el gobernador también señaló la vocación de servicio, eh la sensibilidad en la atención y también desde luego cuando se alcanza, se logra devolver la salud a alguien y verlos caminar, ver a adultos mayores que regresan a casa. El gobernador señaló, médicas y médicos tienen ese contacto diario sensible con la población.
+"Tiene ese contacto diario con el dolor, también con la presión en cada una y en cada uno de ustedes. Así como la satisfacción de ver una persona aliviada, de ver un bebé, un niño que crece, un adulto que se recupera, una persona que se integra a su familia gracias a su esfuerzo, a su conocimiento, a su sabiduría. Por ello me siento, de verdad, emocionado de reconocer la trayectoria, el esfuerzo, el trabajo, la vida de cada una y de cada uno de ustedes, y también de los que no están aquí, que desde su trinchera, allá, en el consultorio, en la clínica, en las zonas más alejadas del Estado, desempeñen con un gran sentido humano, pero sobre todo, con un gran compromiso social. Esta un bello profesión de ser médica y de ser médico. Muchas felicidades".
+El adelanto de lo que ha sido la agenda gubernamental...</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CftEM2WuxxJTmenwdsLsHsOqA9IEA4im/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SDPEE/Bol.260/2026</t>
+  </si>
+  <si>
+    <t>Hidalgo suma más de 654 mdp en apoyos de Pemex para salud, educación e infraestructura</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Donación Pemex</t>
+  </si>
+  <si>
+    <t>Positivo</t>
+  </si>
+  <si>
+    <t>Y en el marco de esta misma conferencia, el día de ayer, Fernando Olvera Juárez, coordinador de gestión y vinculación de proyectos especiales de la Secretaría del Despacho del Gobernador, presentó los resultados de las gestiones realizadas ante Petróleos Mexicanos, que desde 2022 han permitido concretar donaciones en especie por más de 654 millones de pesos para fortalecer los servicios públicos. 
+Fíjese que en el quehacer periodístico eh revisábamos y bueno, no ha habido anteriormente eh que esas participaciones se dieran a conocer, se llevaron seguimiento. Hidalgo suma más de 654 millones de pesos en apoyos de Petróleos Mexicanos para salud, educación e infraestructura en el estado, Fernando Olvera.
+"Bajo el liderazgo del gobernador, el licenciado Julio Menchaca Salazar, la instrucción ha sido clara y contundente: no quedarnos sentados en el escritorio, sino salir a tocar todas las puertas posibles en el ámbito federal y en el sector productivo para traer beneficios directos a la entidad".
+Durante su participación, el funcionario destacó que de 2022 a la fecha, esta colaboración ha permitido incorporar 53 unidades operativas, brindar más de 179,000 servicios médicos en 59 municipios, se han realizado 10,000 mastografías gratuitas y se han entregado más de 9,000 piezas de mobiliario escolar, además de gestionar 23,200 toneladas de asfalto para mejorar 42 vialidades en diferentes puntos de la entidad. 
+Asimismo, informó sobre la reciente entrega de equipamiento por más de 78 millones de pesos, que incluye maquinaria especializada, 2 ambulancias, 500 luminarias y 5,000 toneladas de asfalto. Además, reiteró el compromiso de la Secretaría del Despacho, encabezada por Alejandro Velázquez Mendoza, para continuar fortaleciendo la vinculación con instituciones federales para impulsar acciones que beneficien directamente a las familias hidalguenses.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11kr5SLHpfdxfLI7nddMSbpu0Q-8GhNn6/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Fernando Olvera Juárez</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Alejandro Velázquez Mendoza</t>
+  </si>
+  <si>
+    <t>Hacienda/Bol.17/2026</t>
+  </si>
+  <si>
+    <t>Durante la conferencia de prensa en el Edificio del Gobierno del Estado, la secretaria de Hacienda, María Esther Ramírez Vargas, informó que las estimaciones apuntan a que el presupuesto de Hidalgo para 2027 podría superar los 79,000 millones de pesos, impulsando la inversión en infraestructura, obra pública y programas sociales. La funcionaria subrayó que una recaudación eficiente permite ofrecer mejores servicios y oportunidades, para lo cual es necesario fortalecer la cultura contributiva y apoyar a los municipios. Asimismo, destacó que el estado se consolidó como sede de la Cuarta Sesión Ordinaria de AMEXHUASCA y que, gracias a diversas alianzas académicas e institucionales, Hidalgo se posiciona en el segundo lugar nacional en modernización catastral según la Sedatu.</t>
+  </si>
+  <si>
+    <t>Presupuesto De Egresos</t>
+  </si>
+  <si>
+    <t>En más de la información, durante la conferencia de prensa del día de ayer en el Edificio del Gobierno del Estado, la secretaria de Hacienda, María Esther Ramírez Vargas, dio a conocer que las estimaciones de la Secretaría de Hacienda y Crédito Público apuntan a que Hidalgo podría rebasar los 79,000 millones de pesos de presupuesto para 2027, lo que impulsará la inversión en infraestructura, obra pública y programas sociales. Hidalgo proyecta superar los 79,000 millones de pesos en el presupuesto para el 2027. Escuchemos a la secretaria de Hacienda, María Esther Ramírez.
+"Una recaudación eficiente se traduce en más obras, mejores servicios públicos y mayores oportunidades de desarrollo para quienes más lo necesitan. Sin embargo, esos resultados no se sostienen únicamente con fiscalización, también requiere fortalecer la cultura contributiva y dotar a los municipios de información confiable que les permita administrar sus ingresos con mayor eficiencia y equidad".
+Asimismo, la funcionaria resaltó que Hidalgo se consolidó como sede de la Cuarta Sesión Ordinaria de AMEXHUASCA, yo le dábamos a conocer esta información. Este logro, junto con la Alianza con la Unión Europea y la Universidad Politécnica de Pachuca para impartir el primer diplomado en obligaciones fiscales a nivel nacional, posiciona a Hidalgo en el segundo lugar nacional del Índice de Modernización Catastral de la Sedatu, destacando en transparencia y fortalecimiento de finanzas públicas.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aRE-bXFK_wyVhMLYxP24HwrIbcf1B5bz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/Bol.1336/2026</t>
+  </si>
+  <si>
+    <t>Mediante políticas educativas, Menchaca prioriza recursos para el sector</t>
+  </si>
+  <si>
+    <t>Entrega de reconocimientos</t>
+  </si>
+  <si>
+    <t>Continuamos esta tarde la información, esfuerzo, vocación, años de servicio, presencia, convocatoria, más de 2000 trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el compromiso con el fortalecimiento del sector educativo a través de las políticas educativas. El gobernador del estado prioriza recursos para el sector educativo, esto fue lo que destacó el gobernador Julio Menchaca Salazar.
+"El trabajo que realizan ustedes es sumamente importante, porque genera las condiciones al personal académico de aprendizaje, de trasladar el conocimiento a las nuevas generaciones y de tener ese sentido de pertenencia. El gobierno del estado reitera su compromiso de seguir dirigiendo las políticas públicas y los recursos para fortalecer la educación, porque sin educación no hay transformación".
+En este sentido el gobernador del estado aseguró que en Hidalgo existe una suma de esfuerzos entre la sociedad, las familias, el sector educativo y los gobiernos estatal y federal. Este último encabezado por la presidenta Claudia Sheinbaum, que próximamente va a entregar apoyos económicos a 2,185 familias que perdieron sus viviendas a causa de las lluvias del año pasado. 
+Mari Carmen Mandujano Cerrilla, subsecretaria de Administración y Finanzas, señaló que la labor del personal de apoyo y asistencia a la educación deja huella en la vida de las personas, pues sus integrantes suelen ser el primer apoyo que las y los estudiantes encuentran al llegar al plantel educativo, además su presencia en las escuelas constituye un vínculo entre padres y padres de familia y directivos para contribuir al desarrollo de las actividades educativas, de ahí la importancia de reconocer a quienes acumulan entre 10 y 50 años de trayectoria. 
+Said Vargas Sáenz, secretario general de la Sección 15 del SNTE, coincidió en que las y los trabajadores reconocidos han dedicado su vida y talento al servicio de la educación pública.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uHYWQ8eFuTC1V8Jv5FXp0JqkEL0hOILz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum, Maricarmen Mandujano Cerrilla, Said Vargas Sáenz</t>
+  </si>
+  <si>
+    <t>SEPH/FN.SN-H/2026</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón asiste al lanzamiento del Primer Concurso Nacional de Coros Escolares</t>
+  </si>
+  <si>
+    <t>CDMX</t>
+  </si>
+  <si>
+    <t>Por otra parte, también el titular de los Servicios Educativos en la entidad asistió al lanzamiento del Primer Concurso Nacional de Coros Escolares realizado en Palacio Nacional junto a la presidenta Claudia Sheinbaum Pardo y el titular de la SEP, Mario Delgado. En el evento participó, por parte de Hidalgo, el el coro de la Escuela Primaria Pedro María Anaya de Mixquiahuala. Representó al estado en este encuentro nacional, el cual promueve el talento y la formación artística de niñas y niños. Y por supuesto, este coro de esta escuela Pedro María Anaya de de Mixquiahuala pues tuvo que pasar por un trayecto para lograr esta representación de de Hidalgo en el lanzamiento del Concurso Nacional de de Coros Escolares. Le comparto un unos instantes de lo que fue esta presentación de de coros ahí en Palacio Nacional por el contexto, por el motivo por el que se presentaron de y las canciones que interpretaron, de verdad estremecedores. Este este hecho, este este acto en el que participan todos estos niños con la ilusión de mostrar su talento y que lo hacen además de forma colectiva, colaborando, sabiendo que la voz de todos y cada uno es importante, pero lo son más aún sumados. Le comparto esta parte de esta interpretación.
+(Interpretación musical en coro del tema "Cielito Lindo")
+Locutor: Bien, una pieza clásica de del gusto popular, Cielito Lindo, que además recordemos también pues se llega a interpretar precisamente en triunfos deportivos de de México. Así es que es un una canción emblemática y e interpretada por cientos de voces infantiles. De verdad que ese el momento fue pues bastante emotivo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Dx9eiCigMyDUfVoiWScpOjfgK23aoI-q/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum, Mario Delgado Carrillo</t>
+  </si>
+  <si>
+    <t>SEPH/FN.SN-G/2026</t>
+  </si>
+  <si>
+    <t>Titular de la dependencia participa en plenaria extraordinaria del Conaedu 2026 y asiste al lanzamiento del Primer Concurso Nacional de Coros Escolares</t>
+  </si>
+  <si>
+    <t>CONAEDU</t>
+  </si>
+  <si>
+    <t>Continuamos con con información del ámbito educativo, le comento que el secretario de Educación Pública, Natividad Castrejón, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria del Consejo Nacional de Autoridades Educativas, que encabezó el secretario de Educación Pública del país, Mario Delgado Carrillo. Durante el encuentro se analizaron temas como la Consulta Nacional para la Construcción del Nuevo Sistema de las Maestras y los Maestros, la USICAMM o lo que hasta ahora es la la USICAMM, los avances en la consolidación del Bachillerato Nacional “Margarita Maza” y las acciones para impulsar la Estrategia Nacional “Vive Saludable, Vive Feliz”.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QXziSU4fOWNj9HaD9G0IN9mp6n9JgkiD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Mario Delgado,</t>
+  </si>
+  <si>
+    <t>Entrevista en cabina con la recién egresada de la carrera de Ingeniería en Logística del Instituto Tecnológico Superior del Oriente del Estado de Hidalgo (ITESA), Mexli Ninel Hernández Franco, obtuvo el segundo lugar en el Premio de Excelencia Dual gracias a un proyecto de optimización y digitalización de procesos logísticos implementado en el centro de distribución (Cedis) de la empresa Caxaplax. Durante su entrevista en cabina, la joven destacó cómo su formación práctica y teórica a través del modelo dual en el ITESA le permitió integrarse con éxito al sector laboral e impulsar herramientas tecnológicas para la mejora de flujos de información empresarial.</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Educación dual</t>
+  </si>
+  <si>
+    <t>Apan</t>
+  </si>
+  <si>
+    <t>Y de verdad que es un orgullo recibir en la cabina de NQ en Pachuca a personas distinguidas, a personas exitosas, como Mexli Ninel Hernández Franco, egresada de la Ingeniería en Logística por el Instituto Tecnológico Superior del Oriente del Estado de Hidalgo, el ITESA. ¡Bienvenida! Apenas en diciembre pasado egresaste y ya presentaste un proyecto para una empresa, ya tienes trabajo y ya obtuviste un premio, el segundo lugar en el Premio de Excelencia Dual, pues muchas felicidades por esta trayectoria y ello supone que tu paso por por el ITESA ha sido importante. Muy buen día.
+Buenos días, muchas gracias por la invitación. Y sí, he tenido la oportunidad de participar en estos eventos. Creo que ITESA es es una de las universidades que te brinda estas oportunidades justamente pues para poder desarrollar lo que aprendes dentro de lo que es la carrera. Eh dentro de ITESA pues durante los semestres trabajamos diferentes eh pues cuestiones como la planeación, los almacenes, que te ayudan al final de cuentas al llegar a una a una empresa a poder aplicarlo realmente y creo que también eh te ayuda a crecer pues tus habilidades personales, llegas con con más interés de poder liderar un proyecto, de poder crear diferentes soluciones para lo que son las las empresas y en este caso pues justamente ITESA pues ayuda a combinar la parte teórica con la parte práctica mediante lo que es modelo dual.
+Muy bien, y para ti representó además tener una institución cercana, eres originaria del estado de Hidalgo, de la zona del Altiplano.
+Sí, sí, la verdad es que al estar en Tepeapulco, que es de donde yo provengo, creo que que pues el el pertenecer a esta zona que también aparte es como una zona industrial, pues creo que también te abre el camino a poder conocer no solamente la industria de lo que es la zona, sino también pues a poder crecer a a zonas cercanas o incluso más, como en el caso del premio. Tuve la oportunidad de de poder eh pues conocer diferentes proyectos de diferentes estados y creo que es lo que hace la diferencia que ITESA te da esas herramientas que te permiten pues justamente competir con otros estados o incluso eh pues a nivel nacional, en este caso o o global, se puede decir, porque también puedes pues ir creciendo este este tipo de proyectos.
+¿En qué consiste este este proyecto con el que destacas en este premio de Excelencia Dual?
+El proyecto está basado en el Cedis de Caxaplax. En este caso ellos trabajan productos plásticos y de resina. Eh se se realizó un análisis primero de lo que son las actividades logísticas que se llevan a cabo dentro del centro de distribución y con ello pues se se buscó optimizar justamente esta parte de de la información que se tiene. A veces es muy complicado en los Cedis poder trabajar tanta información diaria, entonces justamente esta herramienta tecnológica se trabajó mediante Excel, mediante macros, tratando de de hacer que toda la información funcionara conjuntamente y que mediante tablas, gráficos, formularios, botones, justamente se se tuviera una una visualización en un dashboard más completa, pero eh en el momento que estás trabajando pues surgen nuevas nuevas cuestiones que la empresa empieza a buscar en ti, que dice, "Okay, está bien tu proyecto, pero necesitas eh que la información esté en tiempo real." Entonces, justamente se avanzó a poder crear otro otra herramienta que en este caso fue mediante una hoja de cálculo con eh pues celdas formuladas que permitieran que la información no estuviera duplicada, que los registros que antes se hacían manuales se hicieran digitales, que se hicieran de forma más rápida y sobre todo que que al pasar esta hoja de cálculo a lo que fue el Uker Estudio nos diera un un dashboard más completo, o sea, nos diera esta parte de los gráficos en tiempo real, que se pudiera utilizar en todo momento, porque al final de cuentas es lo que busca un Cedis, optimizar esta información.
+Muy bien, mencionas que la empresa valoró en primera instancia el proyecto, pero que con base en su labor cotidiana, pues pedía otros elementos. Eso es muy importante, el contacto con con la realidad como estudiantes tú. Tú dentro del ITESA tuviste esta posibilidad de este contacto con con el sector empresarial, con con la realidad laboral.
+Sí, creo que ITESA permite estos contactos porque justamente eh trabaja a la par los conocimientos teóricos, pero también los prácticos. En este caso modelo dual a veces es como tu primera oportunidad de de pasar a lo que es el entorno real. Entonces el pasar a este a este tipo de proyectos yo creo que significa pues algo muy importante porque pasas de lo que ya sabes a hacerlo real, entonces la empresa busca justamente eh líderes, busca personas que que realmente te den soluciones prácticas y que realmente fue lo fue lo que pasó. El proyecto ya se implementó, el proyecto ya está en marcha, entonces eh se hizo una capacitación, se entregaron manuales y demás herramientas que que al final de cuentas a la empresa pues le sirven justamente para seguir trabajando día a día.
+Muy bien, ya con un premio con esta preparación, con este proyecto ya ya en marcha y con con trabajo y muy joven además, por supuesto, ¿hacia dónde apuntas? ¿Qué es lo que visualizas para ti como egresada del ITESA?
+Pues sí, claro, siempre este crecer en el ámbito profesional como ingeniera en logística. La verdad es que ITESA te brinda las herramientas tanto profesionales como personales y en este caso el el poder realizar este tipo de proyectos pues me abrió las puertas incluso a mi primer trabajo. Eh al realizar este tipo de de dashboard, de proyectos que impulsan a crecer a una empresa, digitalizarse en este mundo que a lo mejor lo ven lejano, pero pues al final de cuentas no se necesita tanto en cuanto a mi a mi primer trabajo pues tuve la oportunidad de incluso de de poder decir que que tenía ese proyecto atrás. Incluso me abrió esa puerta de decir, "Okay, ven y trabaja exactamente lo mismo, necesito una herramienta parecida, necesito que que me busques optimizar lo que ya optimizaste en otro lugar."
+Conductor: Muy bien, pues muchas felicidades, de verdad sin duda que seguiremos escuchando hablar de ti seguramente por por todo el camino que te estás abriendo a menos de un año de haber egresado de la carrera de la ingeniería en logística. ¿Algo que desees agregar?
+Pues nada, la verdad es que yo muy agradecida con con la invitación y sobre todo también con con ITESA que que siempre te brinda estas oportunidades y pues más que nada hacer una invitación justamente a los estudiantes a creer en ellos, a impulsar este justamente este tipo de proyectos que no solamente te dejan algo profesional, sino también algo personal, siempre es importante crecer las habilidades de liderazgo para poder entrar a una industria donde pues generalmente es donde vas a crecer profesionalmente, entonces es muy importante para mí pues hacer esa invitación.
+uy bien, pues muchas felicidades nuevamente, que te siga yendo muy bien. Mexli Ninel Hernández Franco, egresada de Ingeniería en Logística del Instituto Tecnológico Superior del Oriente del Estado de Hidalgo, el ITESA. ¡Felicidades!
+Muchas gracias.
+Hasta pronto.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1BuS5LjojNKIS8vPZm_1RsMOqU36JUW7d/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Autoridades llevan a cabo un ejercicio de cateos e investigación en diversos puntos de la ciudad de Tulancingo. Uno de los operativos se registra en las inmediaciones de la Escuela Secundaria Número 2, ubicada en la avenida del Trabajo de la colonia Vicente Guerrero. Estas diligencias derivan de carpetas de investigación en curso, por lo que se exhorta a la ciudadanía a manejar con precaución y evitar obstaculizar la labor de los cuerpos de seguridad.</t>
+  </si>
+  <si>
+    <t>PGJEH</t>
+  </si>
+  <si>
+    <t>Cateo</t>
+  </si>
+  <si>
+    <t>Y pues está confirmado, ya nos tendrán más detalles al respecto desde el Notimóvil. Un ejercicio de de cateo que se está realizando precisamente en distintos puntos aquí de la ciudad de Tulancingo. Son técnicas de investigación consistentes en cateos derivados de investigaciones originadas originadas, perdón, a partir de carpetas de investigación. Uno de estos cateos ahí en las inmediaciones de la Secundaria Número 2, avenida del Trabajo, en la colonia Vicente Guerrero. Así que maneje con mucha precaución y, por supuesto, pues no hay que no hay que de alguna forma obstruir la labor que están haciendo las autoridades en estos en estos momentos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17dxGcdm9F8GEROzCL_fa_GDeYnH0JEnv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Le comento que por su esfuerzo, vocación y años de servicio, más de 2,000 trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el gobernador Julio Menchaca Salazar, quien refrendó su compromiso con el fortalecimiento del sector educativo para transformar la entidad. Así, el mandatario estatal reconoció el trabajo del personal de apoyo y asistencia a la educación.
+"El trabajo que realizan ustedes es sumamente importante, porque genera las condiciones al personal académico de aprendizaje, de trasladar el conocimiento a las nuevas generaciones y de tener ese sentido de pertenencia. El gobierno del estado reitera su compromiso de seguir dirigiendo las políticas públicas y los recursos para fortalecer la educación, porque sin educación no hay transformación".
+"Y bueno, personalmente también he corroborado esta importancia del trabajo que desarrolla el personal de apoyo y asistencia a la educación. Efectivamente, brindan en el día a día herramientas para la continuidad, para el desarrollo del trabajo docente y se hace pues este equipo orientado a fortalecer la educación en su conjunto. Es muy importante esta labor que desarrollan. Muchas felicidades. Estas más de 2,000 personas, servidoras públicas, que han recibido este reconocimiento por su trayectoria como personal de apoyo y asistencia a la educación".
+Menchaca Salazar en este contexto aseguró que en Hidalgo existe una suma de esfuerzos entre la sociedad, las familias, el sector educativo y los gobiernos estatal y federal, este último encabezado por la presidenta Claudia Sheinbaum Pardo, que próximamente entregará apoyos económicos a 2,185 familias que perdieron sus viviendas a causa de las lluvias del año pasado, esto que ya se ha anunciado esta próxima visita de la mandataria nacional. En este marco de la entrega de los estímulos al personal de apoyo y asistencia a la educación, Mari Carmen Mandujano Cerrilla, la subsecretaria de Administración y Finanzas, señaló que la labor de este personal de apoyo deja huella en la vida de las personas, pues sus integrantes suelen ser el primer apoyo que las y los estudiantes encuentran al llegar a la escuela, los estudiantes y las familias.
+Es en muchas ocasiones el primer contacto que tienen en los centros educativos. Además, su presencia en los planteles constituye un vínculo entre madres y padres de familia y directivos para contribuir al desarrollo de las actividades educativas. De ahí la importancia de reconocer a quienes acumulan entre 10 y 50 años de trayectoria de trabajo en este sector. Said Vargas Sáenz, el secretario general de la Sección 15 del Sindicato Nacional de Trabajadores de la Educación (SNTE), coincidió en que las y los trabajadores reconocidos han dedicado su vida y talento al servicio de la educación pública de Hidalgo. Por ello aseguró que el sindicato continuará defendiendo la trayectoria y los derechos de todo el personal del sector. Asimismo, agradeció al gobernador Julio Menchaca, dijo, por ser un aliado permanente de las causas y conquistas sindicales. Destacó que a 4 años del inicio de su gestión se ha mantenido intacto el mapa prestacional del personal educativo y se impulsa una relación de respeto y de trabajo conjunto. Así lo subrayó el dirigente sindical Said Vargas en el marco de esta entrega de reconocimientos por trayectoria a personal de apoyo y asistencia...</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xjVZSSzG2Xr0QFvf5hzLtcuFpElHpEH-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, confirmó que la presidenta de la república, Claudia Sheinbaum, realizará una gira de dos días en la entidad durante el próximo jueves y viernes. El objetivo de la visita es entregar apoyos y tarjetas a las familias afectadas por las lluvias y precipitaciones que ocasionaron daños en diversas regiones y miles de hectáreas siniestradas. La agenda presidencial contemplará actividades y recorridos en municipios como Zacualtipán de Ángeles y Villa de Tezontepec para atender a las poblaciones damnificadas por fenómenos meteorológicos previos.</t>
+  </si>
+  <si>
+    <t>Visita Sheinbaum</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>También se anunció ayer, el gobernador confirmó que nuevamente regresará la presidenta al estado de Hidalgo. Sí, así es, está considerado también en la agenda. En cuanto den la información oficial, les estaremos compartiendo, Jesús. Muchas, muchas gracias, David, estamos en contacto. Muy buen día. Muy, muy buenos días, gracias. Y pues, así la información desde la Ciudad de México. y como le platico en efecto, pues el gobernador Julio Menchaca Salazar confirmó que la mandataria, la presidenta Claudia Sheinbaum, va a regresar al estado de Hidalgo esta semana para una gira de dos días, en la cual pues va a entregar apoyos a familias afectadas por las lluvias y hará recorridos por distintos puntos del estado, así lo declaró ayer el gobernador, señaló que la presidenta va a permanecer en territorio hidalguense durante el próximo jueves y viernes, con una agenda que contempla actividades relacionadas con la atención a las personas damnificadas por la llamada vaguada monzónica de hace un a Uno de los puntos centrales de la visita ser la entrega de tarjetas a familias afectadas por las lluvias luego de las precipitaciones que provocaron da en diferentes regiones de aquí de Hidalgo La emergencia dejó, entre otras afectaciones, miles de hectáreas dañadas, por lo que las autoridades han desplegado distintas acciones para atender a las familias que sufrieron estas pérdidas. De acuerdo con lo adelantado por el gobernador ayer, durante su estancia en Hidalgo, la presidenta también tiene contempladas actividades en los municipios de Zapotlán de Juárez y Villa de Tezontepec. Así, la presidenta tendrá una nueva jornada de actividades en territorio hidalguense, con una agenda que combinará la atención a las zonas afectadas por las lluvias con recorridos por municipios del estado. Así que, como dice David Cárdenas, en cuanto compartan la agenda, la agenda ya oficial de la presidenta, pues estaremos, por supuesto, con la facilidad de compartirles el detalle de su visita.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ia4i40z-YXgF4MtnGwSa7oHvcTnri2rB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Súper Stéreo 100.5 FM</t>
+  </si>
+  <si>
+    <t>Jesús González</t>
+  </si>
+  <si>
+    <t>Enfoque Regional Meridiano</t>
+  </si>
+  <si>
+    <t>Alrededor de 60 personas bloquearon la mañana de hoy martes ambos sentidos de la carretera federal México-Laredo, a la altura de la comunidad de Julián Villagrán, en Ixmiquilpan, para exigir la liberación de dos personas. Al respecto, la titular de Asuntos Agrarios de la Secretaría de Gobierno de Hidalgo, Reyna Serrano, explicó que la movilización tiene su origen en una controversia agraria relacionada con la posesión de terrenos cuya pertenencia reclama la comunidad de Pueblo Nuevo."Derivado de un conflicto agrario.</t>
+  </si>
+  <si>
+    <t>Conflicto agrario</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Alrededor de 60 personas bloquearon la mañana de hoy martes ambos sentidos de la carretera federal México-Laredo, a la altura de la comunidad de Julián Villagrán, en Ixmiquilpan, para exigir la liberación de dos personas. Al respecto, la titular de Asuntos Agrarios de la Secretaría de Gobierno de Hidalgo, Reyna Serrano, explicó que la movilización tiene su origen en una controversia agraria relacionada con la posesión de terrenos cuya pertenencia reclama la comunidad de Pueblo Nuevo."Derivado de un conflicto agrario. Este conflicto agrario data desde el año 2010, en donde pobladores de Julián Villagrán, e incluidas estas personas que actualmente se encuentran recluidas, entraron a tomar posesión de parcelas que pertenecen al núcleo agrario de Pueblo Nuevo. Ambos, Pueblo Nuevo y Julián Villagrán, son dos núcleos agrarios que pertenecen al municipio de Ixmiquilpan. Derivado de que Julián Villagrán toma posesión de varias parcelas y una fracción de uso común del poblado de Pueblo Nuevo, el comisariado ejidal y los ejidatarios afectados inician juicios agrarios ante el Tribunal Agrario. En el 2019, la autoridad agraria resuelve mediante sentencia a favor de Pueblo Nuevo, en donde se les reconoce el mejor derecho a poseer y la titularidad de estas parcelas. Son 15 parcelas y una fracción de uso común, una parcela con destino específico denominada parcela escolar, y en la sentencia se ordena que los pobladores de Julián Villagrán que tienen la posesión hagan la entrega con todos sus frutos y accesiones que contenga la misma. Se han realizado 11 intentos de ejecución en estos juicios agrarios. Derivado de estos intentos de ejecución, se hizo la entrega de cinco parcelas. Estas cinco parcelas fueron delimitadas y tomaron posesión los pobladores de Pueblo Nuevo; sin embargo, los vecinos de Julián Villagrán, de nueva cuenta, entran a tomar posesión aun y cuando ya existen las sentencias dictadas por el Tribunal Agrario."La funcionaria dio a conocer que habitantes de Pueblo Nuevo promovieron denuncias que derivaron en la apertura de carpetas de investigación por el delito de despojo agravado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qvyvDNRf2Aqg-RlIvW5JW_n0dv67JRn9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Reyna Serrano</t>
+  </si>
+  <si>
+    <t>Comenta conductor Jesús Gonzalez : Le pregunto a usted qué piensa del Hoy No Circula. Hace mucho tiempo, no es la primera vez que se hace esta propuesta, hace ya algunos años se decía que también querían echar a andar el Hoy No Circula en esta región de Tula: Tula, Tepeji, algunas zonas cercanas, Tulancingo y en Pachuca. Le comento esto porque ante las condiciones de tránsito que registra la zona metropolitana de Pachuca, el Gobierno de Hidalgo contempla evaluar la viabilidad del programa Hoy No Circula como parte de una estrategia más amplia para atender los problemas de movilidad. La secretaria de Movilidad y Transporte, Lyzbeth Robles, dio a conocer que sostuvo un primer acercamiento con su homóloga de Medio Ambiente y Recursos Naturales, Mónica Mixtega, con quien acordó establecer una mesa de trabajo para examinar los alcances de esta posibilidad</t>
+  </si>
+  <si>
+    <t>Hoy no circula</t>
+  </si>
+  <si>
+    <t>Comenta conductor Jesús Gonzalez : Le pregunto a usted qué piensa del Hoy No Circula. Hace mucho tiempo, no es la primera vez que se hace esta propuesta, hace ya algunos años se decía que también querían echar a andar el Hoy No Circula en esta región de Tula: Tula, Tepeji, algunas zonas cercanas, Tulancingo y en Pachuca. Le comento esto porque ante las condiciones de tránsito que registra la zona metropolitana de Pachuca, el Gobierno de Hidalgo contempla evaluar la viabilidad del programa Hoy No Circula como parte de una estrategia más amplia para atender los problemas de movilidad. La secretaria de Movilidad y Transporte, Lyzbeth Robles, dio a conocer que sostuvo un primer acercamiento con su homóloga de Medio Ambiente y Recursos Naturales, Mónica Mixtega, con quien acordó establecer una mesa de trabajo para examinar los alcances de esta posibilidad. La propuesta surge en un contexto en el que Pachuca figura entre las ciudades con mayores tiempos de congestión vehicular, según el estudio... el estudio denominado «Costo del tráfico 2026», elaborado por el Instituto Mexicano para la Competitividad, el IMCO.  “ Ya tuvimos una llamada, solo llamada telefónica a la secretaria Mixtega y su servidora de SEMARNATH. Acordamos tener una reunión ella y su servidora para platicar sobre los pormenores de esta propuesta del Hoy No Circula, no solamente con base al resultado del IMCO, sino tenemos ya un PIMUS de Pachuca, tenemos censo ya de transporte público realizado a cargo de la Secretaría de Movilidad y Transporte y del Sistema de Transporte Convencional de Hidalgo, tenemos también otros datos que pueden configurar una gran herramienta”</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hALPhVsUIWloRoYx-lzWrVueobyyi29x/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SEMARNATH</t>
+  </si>
+  <si>
+    <t>Mónica Mixtega</t>
+  </si>
+  <si>
+    <t>SDPEE-OCSAD/Bol.1337/2026</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, quien encabezó esta mañana la ceremonia conmemorativa del Día del Médico y la Médica, en cuyo marco se llevó a cabo la entrega de medallas y reconocimientos a profesionales de la salud distinguidos por su trayectoria y desempeño en la entidad."Siempre he pensado que la carrera más difícil profesional es ser médico o médica, porque implica un contacto muy directo con las personas.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, quien encabezó esta mañana la ceremonia conmemorativa del Día del Médico y la Médica, en cuyo marco se llevó a cabo la entrega de medallas y reconocimientos a profesionales de la salud distinguidos por su trayectoria y desempeño en la entidad."Siempre he pensado que la carrera más difícil profesional es ser médico o médica, porque implica un contacto muy directo con las personas. Es, sin duda, una enorme expresión de calidad humana el ejercicio profesional de médico. Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al Estado de Hidalgo y a México, proyectándolo con su saber. Creo que se han realizado las acciones institucionales para que puedan ejercer de mejor manera esa muy noble profesión de ser médicas y de ser médicos. Por ello, me siento de verdad emocionado de reconocer la trayectoria, el esfuerzo, el trabajo, la vida de cada una y de cada uno de ustedes, y también de los que no están aquí, que desde su trinchera allá en el consultorio, en la clínica, en las zonas más alejadas del estado desempeñan con un gran sentido humano, pero sobre todo con un gran compromiso social esta muy bella profesión de ser médica y de ser médico.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12GV5v4vduEt-8QNFpWfmiCjZ7YFPZLMB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Tenemos noticias desde el estado de Hidalgo: Natividad Castrejón Valdéz participa en la plenaria extraordinaria del Consejo Nacional de Autoridades Educativas. El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria 2026 del Consejo Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo. D</t>
+  </si>
+  <si>
+    <t>Tenemos noticias desde el estado de Hidalgo: Natividad Castrejón Valdéz participa en la plenaria extraordinaria del Consejo Nacional de Autoridades Educativas.
+El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria 2026 del Consejo Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo. Durante el encuentro se analizaron temas como la consulta nacional para la construcción de nuevos sistemas de maestras y los maestros, los avances en la consolidación del Bachillerato Nacional Margarita Maza y las acciones para impulsar la estrategia nacional "Vive saludable, vive feliz". Es lo que se destaca en torno a esta importante reunión de Consejo Nacional de Autoridades Educativas allá en lo que respecta a la zona de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1__M3nplF_iFg5xnEA8JOeRw7XmOQDcEA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Natividad Castejón</t>
+  </si>
+  <si>
+    <t>Mario Delgado</t>
+  </si>
+  <si>
+    <t>Christian García</t>
+  </si>
+  <si>
+    <t>Enfoque Regional Matutino</t>
+  </si>
+  <si>
+    <t>Oiga, ya ve que le platicábamos al inicio este coro de la Escuela Primaria Pedro María Anaya de Mixquiahuala. Desde el día de ayer que le mandamos también esta felicitación. Bueno, pues ellos representaron a Hidalgo durante el aniversario de los coros escolares 2026. En el encuentro participaron la presidenta Claudia Sheinbaum Pardo, el secretario de Educación y también el titular de la Secretaría de Educación Pública de Hidalgo, Natividad Castrejón Valdéz.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JbJ43pSK-KjWm_DRt6T6VmtR6OETHOQm/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum, Mario Delgado</t>
+  </si>
+  <si>
+    <t>SSH/Bol.183/2026</t>
+  </si>
+  <si>
+    <t>Que en Mixquiahuala, la Secretaría de Salud de Hidalgo entregó apoyos funcionales a personas que requieren ayuda para desplazarse. La titular, Escalante Arroyo, encabezó la entrega de 19 sillas de ruedas, 6 andaderas y 4 bastones, esto para favorecer la movilidad de los beneficiarios.</t>
+  </si>
+  <si>
+    <t>Auxiliares funcionales</t>
+  </si>
+  <si>
+    <t>Mixquiahuala</t>
+  </si>
+  <si>
+    <t>Que en Mixquiahuala, la Secretaría de Salud de Hidalgo entregó apoyos funcionales a personas que requieren ayuda para desplazarse. La titular, Escalante Arroyo, encabezó la entrega de 19 sillas de ruedas, 6 andaderas y 4 bastones, esto para favorecer la movilidad de los beneficiarios. La funcionaria invitó a la población a identificar a quienes necesiten estos dispositivos y canalizar sus jurisdicciones sanitarias. También llamó a las familias y personas cuidadoras a estar pendientes de la salud y bienestar de las personas adultas mayores.La funcionaria estatal destacó durante la entrega:"Hoy, en el gobierno del gobernador Julio Menchaca Salazar, venimos personalmente a entregar los apoyos y a decirles a todas las personas que si hay gente que ustedes conozcan y sepan que lo necesitan, pueden avisarnos. Por si ustedes conocen a alguien que requiera un bastón, una andadera, un aparato auditivo o algún tipo de apoyo de este tipo, el doctor ahorita se va a coordinar con quien a ustedes les diga... Pero lo que queremos es poderles acercar a ustedes los apoyos funcionales que hay dentro de la Secretaría de Salud del gobierno del Estado. Nuestro interés es entregar y causar una movilidad efectiva."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HoskgUw9QTO_bQUIQL4uno2F_SKB6wpz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Ante los señalamientos por presunto nepotismo y la investigación iniciada por la Contraloría, se informó que renunció a su cargo como secretaria particular de la titular de la Secretaría de Cultura de Hidalgo, Neida Naranjo Baltazar.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor</t>
+  </si>
+  <si>
+    <t>Nepotismo</t>
+  </si>
+  <si>
+    <t>Ante los señalamientos por presunto nepotismo y la investigación iniciada por la Contraloría, se informó que renunció a su cargo como secretaria particular de la titular de la Secretaría de Cultura de Hidalgo, Neida Naranjo Baltazar. La Oficialía Mayor fijó postura sobre el caso:"La Oficialía Mayor confió dos a Baltazar en la dependencia, pero aclaró que no revisa directamente los expedientes de cada contratación. Este trámite responde a las áreas de cada Secretaría. La precisión se da luego de que la Secretaría de Cultura señalara a la Oficialía Mayor de revisar los expedientes, y a la Contraloría como instancia encargada de investigar posibles conflictos."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bvyvmmLc7E_KVDrFK2NRpOF7EfKG2OLL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Cultura, Contraloría</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo</t>
+  </si>
+  <si>
+    <t>OCSAD/Bol.1334/2026</t>
+  </si>
+  <si>
+    <t>Transportistas sin seguro vigente en Hidalgo podría costarles mucho más que una multa. También podrían perder su concesión. la convocatoria y la supervisión podría comenzar a partir de noviembre. Esto lo informó la Secretaría de Movilidad y Transporte, Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>Supervisión de transporte</t>
+  </si>
+  <si>
+    <t>Transportistas sin seguro vigente en Hidalgo podría costarles mucho más que una multa. También podrían perder su concesión. la convocatoria y la supervisión podría comenzar a partir de noviembre. Esto lo informó la Secretaría de Movilidad y Transporte, Lyzbeth Robles Para informar al público que esta semana se emite la circular correspondiente a través de la cual el transporte público convencional  tendrá una revisión binaria única y exclusivamente para la revisión de los... Insistimos en esto por la trascendencia que tiene. Las personas eh concesionarias y las personas conductoras del transporte público convencional, pues la póliza de seguro vigente, que están establecidos en nuestra ley, en el artículo 107 y 108. Las coberturas de la póliza de seguro es importante que las tomas. Lyzbeth Robles destacó los lugares para la revisión: se efectuará, se efectuará en las instalaciones del sistema de transporte oficinas itinerantes que se implementen en las coordinaciones regionales que se distribuyen en el estado de Hidalgo, y en territorio, que es algo que estamos innovando, que podrá llevarse a cabo de manera específica por la Dirección de Vigilancia y Supervisión Transporte Convencional de Hidalgo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zGN0OI0-opTlNV6BKDUx_R0a9l09VyM5/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Las gestiones del gobierno de Hidalgo ante Pemex han permitido incorporar cincuenta y tres unidades operativas, ofrecer ciento setenta y nueve mil servicios médicos en cincuenta y nueve municipios y realizar diez mil mastografías gratuitas desde el dos mil veintidós. V</t>
+  </si>
+  <si>
+    <t>Las gestiones del gobierno de Hidalgo ante Pemex han permitido incorporar cincuenta y tres unidades operativas, ofrecer ciento setenta y nueve mil servicios médicos en cincuenta y nueve municipios y realizar diez mil mastografías gratuitas desde el dos mil veintidós. Vera Juárez, coordinador de gestión y vinculación de proyectos especiales, informó que también los servicios de salud se acercaron a la población con la unidad. Vera Juárez destacó la importancia de acercar los servicios médicos a las comunidades más alejadas:"Salud dignos a las comunidades más alejadas ha sido una encomienda para este gobierno. Con esta convicción de que la atención médica debe ser al alcance de... su operación la unidad médica móvil, la cual ha brindado más de ciento setenta y nueve mil servicios en cincuenta y nueve municipios. Estas atenciones con general y odontológica, además de contar con una farmacia de cuadro básico totalmente gratuito."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13dg1zeGF50YIk5b4lWq9qONAKWGIfxbg/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Hidalgo podría superar los 79 mil millones de pesos de presupuesto para el ejercicio 2027. Así lo informó la secretaria de Hacienda estatal, María Esther Ramírez Vargas, con base en las proyecciones de la Secretaría de Hacienda y Crédito Público (SHCP).</t>
+  </si>
+  <si>
+    <t>Hidalgo podría superar los 79 mil millones de pesos de presupuesto para el ejercicio 2027. Así lo informó la secretaria de Hacienda estatal, María Esther Ramírez Vargas, con base en las proyecciones de la Secretaría de Hacienda y Crédito Público (SHCP). De concretarse, dichos recursos permitirían robustecer la inversión en infraestructura, obra pública y programas sociales.La funcionaria estatal detalló los avances en materia recaudatoria y eficiencia presupuestal:"A cuatro años de administración, hemos incrementado en un 96 por ciento la recaudación de ingresos. ¿Y cómo lo hicimos? Modernizamos los procesos tributarios, ampliamos el padrón de contribuyentes y fortalecimos la fiscalización."Asimismo, Ramírez Vargas resaltó que el estado ha escalado posiciones en el tablero global de eficiencia recaudatoria del Servicio de Administración Tributaria (SAT), pasando de posiciones rezagadas en 2022 hasta ubicarse en el primer lugar a nivel nacional para los periodos 2025 y 2026. Respecto al impacto del presupuesto en las dependencias, indicó:"Por lo pronto no se visualiza, porque el efecto que causa el que se esté incrementando el presupuesto para las ejecutoras del gasto, llámese dependencias, organismos, es precisamente porque es importante el recurso a lo que nosotros denominamos gasto de inversión, obras, acciones y proyectos."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19eIfFSojBHAGZYPv1K4bmPH60Gbwbbxp/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria con Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria con Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo.Durante el encuentro se abordaron diversos temas prioritarios:"Mire, en este... también estuvo ahí el secretario de educación pública de Hidalgo, ayer le decíamos de este coro que es de Mixquiahuala y que estuvo para la mañanera. Bueno pues ahí estuvo también precisamente con ellos."Asimismo, se discutieron asuntos como la consulta nacional para la construcción del nuevo sistema de las maestras y los maestros, los avances en la consolidación del bachillerato nacional y las acciones para impulsar la estrategia nacional "Vive saludable, vive feliz".</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uwimD2y5Prh_3LFPalEm_9fAVcoali0v/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Mire, más de dos mil trabajadores de apoyo y asistencia a la educación en Hidalgo recibieron trayectoria de entre diez y cincuenta años de servicio. Durante la entrega, el gobernador Julio Menchaca destacó que su labor contribuye al mantenimiento de los planteles y refrendó el compromiso de fortalecer la educación pública.</t>
+  </si>
+  <si>
+    <t>Mire, más de dos mil trabajadores de apoyo y asistencia a la educación en Hidalgo recibieron trayectoria de entre diez y cincuenta años de servicio. Durante la entrega, el gobernador Julio Menchaca destacó que su labor contribuye al mantenimiento de los planteles y refrendó el compromiso de fortalecer la educación pública. El gobernador Julio Menchaca señaló: "El trabajo que realizan ustedes es sumamente ... las condiciones al personal académico ... de aprendizaje, de trasladar el conocimiento a las nuevas generaciones ... y de pertenencia. El gobierno del Estado ... reitera su compromiso de seguir dirigiendo las políticas públicas y los recursos ... tal y ser la educación, porque sin educación no hay transformación."Además, el secretario general de la Sección 15 del Sindicato Nacional de Trabajadores de la Educación (SNTE), Said Vargas, reconoció la labor del personal y afirmó que el sindicato seguirá defendiendo sus derechos laborales.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dkTrZ-UO-CjMfLWVC1i_vcoX7IhGAytR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SNTE</t>
+  </si>
+  <si>
+    <t>Said Vargas</t>
+  </si>
+  <si>
+    <t>Anuncian visita de la presidenta Claudia Sheinbaum a Hidalgo y entrega de apoyos Le informamos que se informó que se prevé la visita de la presidenta de México, Claudia Sheinbaum, dos días esta semana.</t>
+  </si>
+  <si>
+    <t>Anuncian visita de la presidenta Claudia Sheinbaum a Hidalgo y entrega de apoyos Le informamos que se informó que se prevé la visita de la presidenta de México, Claudia Sheinbaum, dos días esta semana. La mandataria federal encabezará la entrega de apoyos en tarjetas a las más de dos mil familias que perdieron su vivienda por la vaguada monzónica, así como el arranque de los trabajos del polo de desarrollo de Zapotlán y la inauguración de empresas. El gobernador señaló:"Y creo que viene dos días. En esto, la conversación que tuve ayer, era nada más que nada venía el jueves, pero parece que también el viernes. ¿A qué viene? Bueno, a ver, dos cosas muy importantes. Uno, en las tarjetas, digamos, de las dos mil, más de dos mil familias que perdieron su vivienda y les va a dar un apoyo en las tarjetas, digamos."Asimismo, se detalló la inauguración de proyectos industriales en la entidad: "Y otro muy importante también, es la inauguración de dos espacios de mercado libre, de los cinco que van a estar instalados en Zapotlán de Juárez, de laboratorios Carnot, son inversión francesa, y de la puesta en marcha del polo de desarrollo, o sea, de Villa de Tezontepec a Zapotlán... y en el arranque de los trabajos, de lo que es una inversión importantísima."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cB0T2AI2UYXeFZbU8sZCwrVUEzzuml_J/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Acir 92.5 FM</t>
+  </si>
+  <si>
+    <t>Panorama Informativo</t>
+  </si>
+  <si>
+    <t>Eulalio Larrieta</t>
+  </si>
+  <si>
+    <t>En conferencia de prensa la titular de la secretaria de Movilidad y transporte del Estado de Hidalgo, Lyzbteh Robles, informó que fue presentada una denuncia ante la Procuraduría General de Justicia del Estado de Hidalgo contra la plataforma de taxi por aplicación UBER,</t>
+  </si>
+  <si>
+    <t>La Secretaría de Movilidad y Transporte del Estado de Hidalgo presentó una denuncia formal contra la operación irregular de Uber aquí en Pachuca. Vamos a escuchar.En conferencia de prensa la titular de la secretaria de Movilidad y transporte del Estado de Hidalgo, Lyzbteh Robles, informó que fue presentada una denuncia ante la Procuraduría General de Justicia del Estado de Hidalgo contra la plataforma de taxi por aplicación UBER,  por la presunta operación irregular  en Pachuca.Lyzbeth Robles detalló que fue la Coordinación General Jurídica del gobierno del estado quien llevó a cabo el trámite, reiteró que  La Ley de Movilidad y Transporte no contempla la operación de este servicio en el estado, por lo que es competencia del poder legislativo su regulación. AUDIO Lyzbteh Robles</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KL_3d6MWY7caXtUH9_MboNcpwdbipqcx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Por su esfuerzo, vocación y años de servicio, más de dos mil trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el gobernador Julio Menchaca quien refrendó su compromiso con el fortalecimiento del sector educativo para transformar a la entidad</t>
+  </si>
+  <si>
+    <t>Que el gobernador Julio Menchaca entregó reconocimientos a más de 2.000 trabajadores de la educación que tienen ya elaborando entre 10 y 50 años ahí en el magisterio. Vamos a escuchar la información con Jackie Servino. Por su esfuerzo, vocación y años de servicio, más de dos mil trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el gobernador Julio Menchaca quien refrendó su compromiso con el fortalecimiento del sector educativo para transformar a la entidad.Destacó que el trabajo que realizan es sumamente importante porque generan las condiciones para el aprendizaje, la transmisión del conocimiento a las nuevas generaciones y el desarrollo de un sentido de pertenencia, reiteró su compromiso de seguir orientando las políticas públicas y los recursos al fortalecimiento de la educación, porque sin educación no hay transformación”, expresó el titular del Ejecutivo estatal. Por su parte Maricarmen Mandujano Cerrilla, subsecretaria de Administración y Finanzas, señaló que la labor del personal de apoyo y asistencia a la educación deja huella en la vida de las personas, pues sus integrantes suelen ser el primer apoyo que las y los estudiantes encuentran al llegar a la escuela. Además, su presencia en los planteles constituye un vínculo entre madres y padres de familia y directivos para contribuir al desarrollo de las actividades educativas. De ahí la importancia de reconocer a quienes acumulan entre 10 y 50 años de trayectoria. Jacqueline Servín</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pPLF4uznDa9MpoqtgcIqb-hvq7gYR81f/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Finanzas</t>
+  </si>
+  <si>
+    <t>Maricarmen Mandujano Cerrilla</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca confirmó que los próximos días jueves 29 y viernes 30 de octubre, la presidenta Claudia Sheimbaun visitará nuevamente el estado de Hidalgo,</t>
+  </si>
+  <si>
+    <t>Esta semana la presidenta Claudia Sheinbaum visitará Hidalgo para entregar apoyos a las personas afectadas por la vaguada monsónica del año pasado.El gobernador Julio Menchaca confirmó que los próximos días jueves 29 y viernes 30 de octubre, la presidenta Claudia Sheimbaun visitará nuevamente el estado de Hidalgo, para entregar apoyos a las familias afectadas por la vaguada monzónica del 2025.La presidenta entregará tarjetas a las familias que perdieron sus viviendas, principalmente de las zonas de la sierra y la huasteca hidalguense, se prevé que visite los municipios de Zapotlán y Villa de Tezontepec, AUDIO JMS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18P71W5JHUoZq3ZX035vScQ3xz_II8vef/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Atención a la ciudadanía</t>
+  </si>
+  <si>
+    <t>Eulalio Larrieta agradece a Edith Balderas de la Secretaria de Educación Pública.</t>
+  </si>
+  <si>
+    <t>Eulalio Larrieta agradece a Edith Balderas  de la Secretaria de Educación Pública.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15nmf339xkKWwN6d5eEmGspKAgPY8C6E6/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Edith Balderas</t>
+  </si>
+  <si>
+    <t>Eulalio Larrieta agradece a Uriel Ramirez y Jair Martínez de la SEGOBH, porque esta al pendiente de lo que se necesite y los reportes.</t>
+  </si>
+  <si>
+    <t>Uriel Ramirez y Jair Martínez  de la Secretaría de Gobierno.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xmwMnkONKfKUPfOKHpBbJTxBDGJKmqmP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Uriel Ramirez, Jair Martínez</t>
+  </si>
+  <si>
+    <t>Eulalio Larrieta agradece a Cristian Yahir Castañeda supervisor de la región Pachuca quien nos va atender los reportes que correspondan a la SEMOT</t>
+  </si>
+  <si>
+    <t>Gracias de las diferentes dependencias, está con nosotros Cristian Yahir Castañeda de Movida Transporte.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MrVtPKPvvA6aZBzot6N8upa9lC9_ehaK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Cristian Yahir Castañeda</t>
+  </si>
+  <si>
+    <t>Eulalio Larrieta agradece Paola García y Lic. Sarahi Pineda, por estar atentas a los mensajes de la ciudadanía y por atenderlos.</t>
+  </si>
+  <si>
+    <t>También está con nosotros como siempre Paola García y Sarahi Pineda de Caasim Muchas Gracias</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fI3GeCTKKDfCN7OuQ5DFDj28ycGvWfws/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Paola García, Sarahi Pineda</t>
   </si>
 </sst>
 </file>
@@ -1103,8 +1453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X11" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X11" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X33" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X33" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1500,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -1603,34 +1953,32 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>41</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>15</v>
@@ -1639,56 +1987,50 @@
         <v>16</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>43</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>44</v>
       </c>
       <c r="S2" s="5">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>45</v>
       </c>
       <c r="U2" s="5"/>
-      <c r="V2" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
       <c r="X2" s="5"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="C3" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>40</v>
@@ -1697,146 +2039,140 @@
         <v>41</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="S3" s="3">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="U3" s="3"/>
       <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
-        <v>88</v>
-      </c>
+      <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="S4" s="3">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
+      <c r="W4" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C5" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>22</v>
@@ -1845,60 +2181,56 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" s="3">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>45</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>93</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="V5" s="3"/>
       <c r="W5" s="3" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C6" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>25</v>
@@ -1910,63 +2242,61 @@
         <v>50</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="S6" s="3">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U6" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="W6" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C7" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>25</v>
@@ -1975,10 +2305,10 @@
         <v>26</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>22</v>
@@ -1987,7 +2317,7 @@
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>43</v>
@@ -1996,63 +2326,59 @@
         <v>17</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S7" s="3">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C8" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>22</v>
@@ -2061,60 +2387,56 @@
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S8" s="3">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>104</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C9" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>27</v>
@@ -2123,25 +2445,25 @@
         <v>28</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>106</v>
@@ -2150,39 +2472,41 @@
         <v>107</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="S9" s="3">
-        <v>397</v>
+        <v>42</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U9" s="3"/>
+      <c r="U9" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="X9" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>27</v>
@@ -2191,80 +2515,74 @@
         <v>28</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="S10" s="3">
-        <v>64</v>
+        <v>484</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="U10" s="3"/>
-      <c r="V10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6">
-        <v>46321</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>15</v>
@@ -2273,25 +2591,25 @@
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>43</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="S11" s="3">
-        <v>396</v>
+        <v>43</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>45</v>
@@ -2300,6 +2618,1490 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S12" s="3">
+        <v>242</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3">
+        <v>129</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" s="3">
+        <v>182</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="X14" s="3"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S15" s="3">
+        <v>97</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" s="3">
+        <v>113</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>30</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S17" s="3">
+        <v>56</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>27</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" s="3">
+        <v>28</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>26</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S19" s="3">
+        <v>73</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>23</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" s="3">
+        <v>48</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X20" s="3"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="3">
+        <v>135</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X21" s="3"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S22" s="3">
+        <v>56</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="X22" s="3"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S23" s="3">
+        <v>90</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="X23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>19</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S24" s="3">
+        <v>47</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>18</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S25" s="3">
+        <v>54</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>17</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S26" s="3">
+        <v>77</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>10</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" s="3">
+        <v>56</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>9</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S28" s="3">
+        <v>84</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S29" s="3">
+        <v>77</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>4</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S30" s="3">
+        <v>5</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S31" s="3">
+        <v>3</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>2</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S32" s="3">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="X32" s="3"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>1</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="6">
+        <v>46322</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S33" s="3">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="X33" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6146D694-8520-47B5-A96A-FB30B5E9B91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77A8B8A-109C-4B61-A230-CF6E189CEDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="175">
   <si>
     <t>#</t>
   </si>
@@ -161,15 +161,6 @@
     <t>Gobernador</t>
   </si>
   <si>
-    <t>Jesús Riveros</t>
-  </si>
-  <si>
-    <t>Enlace Hidalgo2</t>
-  </si>
-  <si>
-    <t>Tulancingo</t>
-  </si>
-  <si>
     <t>Neutro</t>
   </si>
   <si>
@@ -188,18 +179,9 @@
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Mañanera</t>
-  </si>
-  <si>
-    <t>Hacienda</t>
-  </si>
-  <si>
     <t>Semot</t>
   </si>
   <si>
-    <t>Apps de transporte</t>
-  </si>
-  <si>
     <t>Radio Lobo 96.7 FM</t>
   </si>
   <si>
@@ -209,39 +191,9 @@
     <t>Enlace Noticias</t>
   </si>
   <si>
-    <t>Justa Académica</t>
-  </si>
-  <si>
-    <t>Lyzbeth Robles</t>
-  </si>
-  <si>
-    <t>María Esther Ramírez Vargas</t>
-  </si>
-  <si>
-    <t>Radioescucha reportó el envío de fotografías que confirman casos del virus de Coxsackie en un menor de edad, el cual presenta síntomas característicos en manos, boca y pies. Tras ser llevado al centro de salud, el diagnóstico fue confirmado, por lo que se emitieron agradecimientos por el aviso preventivo para alertar a las autoridades educativas y mantenerlas al pendiente de la situación.</t>
-  </si>
-  <si>
     <t>SSH</t>
   </si>
   <si>
-    <t>Brote epidémico</t>
-  </si>
-  <si>
-    <t>Santiago Tulantepec</t>
-  </si>
-  <si>
-    <t>Fíjate que te están enviando, te están enviando en estos momentos las fotos, en efecto sí, de del pequeñito, del pequeñito que sí tiene el virus del Coxsackie.
- Ajá.
-Y y gracias, gracias por las imágenes y, efectivamente, aparecen en manos, boca y pies, ya nos dicen por acá que lo llevaron al centro de salud y eso le detectaron y pues gracias por el aviso, gracias por el aviso importante perfecto, perfecto.
-Jesús: Para que las autoridades educativas también estén al pendiente.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1645R1UapeM7lSqtSIRVsrQ-jUGWPlQsF/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (CAASIM) informó sobre una suspensión temporal en el suministro de agua potable que afecta a 26 colonias y zonas de Pachuca debido a los trabajos en una línea de conducción vinculados con la ampliación del bulevar Felipe Ángeles. Las labores iniciaron este martes 27 de octubre a las 6:00 horas con una duración estimada de 24 horas. No obstante, la dependencia advirtió que la recuperación del servicio será gradual y podría tomar otras 24 horas adicionales una vez concluidos los trabajos. Entre las zonas afectadas se encuentran colonias como San Antonio, Vistas de Pachuca, Real de San Francisco, Venta Prieta, Puerta de Hierro, entre otras.</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
@@ -251,214 +203,18 @@
     <t>Abasto De Agua</t>
   </si>
   <si>
-    <t>Y de Brasil, de Brasil nos regresamos acá a Pachuca, porque como seguramente ya se habrá dado cuenta, habitantes de 26 colonias y zonas de Pachuca pues tienen afectaciones en el suministro de agua potable debido a trabajos en una línea de conducción vinculados con la ampliación del bulevar Felipe Ángeles. Las maniobras comenzaron a las 6:00, 6:00 de la mañana de hoy martes 27 de octubre y tendrán una duración estimada de 24 horas. La Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, la CAASIM, informó que una vez terminada la intervención, la recuperación del servicio será gradual y podría requerir hasta otras 24 horas. Esto significa que el término de los trabajos no implicará el regreso inmediato del agua a todas las zonas involucradas. Si las labores concluyen dentro del plazo previsto, finalizarían alrededor de las 6:00, 6 horas del próximo miércoles, o sea mañana 28 de octubre. Después comenzaría la recuperación que podría extenderse hasta la madrugada del jueves, jueves 29. ¿Qué colonias tienen las afectaciones en el suministro? El aviso de CAASIM contempla afectaciones en Sector Primario, San Antonio, Ampliación San Antonio, Vistas de Pachuca, Rancho la Colonia, Prismas, Carlos Rovirosa, Privada las Torre, las Torres, perdón, Privada de León, Geovillas, Tulipanes, Quinta Bonita y Magisterio. También se incluyen Real de San Francisco, el Paraíso, los Pinos, Bosques del Mineral, Real de la Plata, Real de Pachuca, Isté, Ollamel, Club de Golf, Venta Prieta, Centro Minero, Puerta de Hierro y Plaza del Valle. El comunicado anticipa afectaciones en el abastecimiento, pero no especifica si todas estas zonas tendrán una interrupción total o si algunas registrarán una disminución en el suministro. Tampoco establece horarios diferenciados para cada una. Por ello, quienes viven, quienes viven o tienen negocios en los puntos incluidos, deberán considerar tanto el periodo de intervención como el periodo posterior que necesitará el sistema para recuperar el servicio.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ABqFnUc0FEJN8_q-SVRVR_Ryv_e1uLYg/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Entrevista</t>
   </si>
   <si>
-    <t>En el marco de la conmemoración del Día del Médico y la Médica, el gobernador del estado, Julio Menchaca Salazar, encabezó un homenaje para reconocer la trayectoria, vocación y el compromiso social de las y los profesionales de la salud en Hidalgo. Durante su mensaje, en el que compartió una reflexión personal sobre el esfuerzo que implica esta profesión, destacó que la labor médica va más allá de la técnica, implicando sensibilidad ante el dolor humano y un contacto diario y cercano con la población. Asimismo, resaltó la importancia de la preparación constante ante los retos sanitarios y ambientales actuales, reconociendo tanto a quienes laboran en zonas urbanas como a los que desempeñan su labor en las regiones más alejadas del estado.</t>
-  </si>
-  <si>
-    <t>Día del médico</t>
-  </si>
-  <si>
-    <t>Y esta mañana el gobernador Julio Menchaca Salazar encabezó la felicitación y reconocimiento de cada una de las médicas y los médicos y todos los involucrados en la salud del pueblo de Hidalgo. Este en su día, Día de la Médica y el Médico, el gobernador también recordó alguna historia de vida de su vida, eh dio a conocer cuando en su familia pues luchó para que fuesen médicos dentro de los hermanos. Escuchemos al gobernador Julio Menchaca Salazar.
-"Fue mi hermano menor, Andrés. Y a través de él como familiar pues conocimos el sacrificio que se realiza en el estudio. La necesidad que tienen las personas de acudir a quien tienen con quien tienen confianza. Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al Estado de Hidalgo y a México proyectándolo con su saber. En todas las carreras debemos estudiar constantemente, pero particularmente en medicina es fundamentalmente necesario estar preparados porque existen muchos temas que si bien ayudan en la tecnología, también han modificado el esquema ambiental y han generado problemas tan serios como la terrible pandemia que tuvimos hace algunos años".
-En esta celebración el gobernador también señaló la vocación de servicio, eh la sensibilidad en la atención y también desde luego cuando se alcanza, se logra devolver la salud a alguien y verlos caminar, ver a adultos mayores que regresan a casa. El gobernador señaló, médicas y médicos tienen ese contacto diario sensible con la población.
-"Tiene ese contacto diario con el dolor, también con la presión en cada una y en cada uno de ustedes. Así como la satisfacción de ver una persona aliviada, de ver un bebé, un niño que crece, un adulto que se recupera, una persona que se integra a su familia gracias a su esfuerzo, a su conocimiento, a su sabiduría. Por ello me siento, de verdad, emocionado de reconocer la trayectoria, el esfuerzo, el trabajo, la vida de cada una y de cada uno de ustedes, y también de los que no están aquí, que desde su trinchera, allá, en el consultorio, en la clínica, en las zonas más alejadas del Estado, desempeñen con un gran sentido humano, pero sobre todo, con un gran compromiso social. Esta un bello profesión de ser médica y de ser médico. Muchas felicidades".
-El adelanto de lo que ha sido la agenda gubernamental...</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CftEM2WuxxJTmenwdsLsHsOqA9IEA4im/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SDPEE/Bol.260/2026</t>
-  </si>
-  <si>
-    <t>Hidalgo suma más de 654 mdp en apoyos de Pemex para salud, educación e infraestructura</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Donación Pemex</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
-    <t>Y en el marco de esta misma conferencia, el día de ayer, Fernando Olvera Juárez, coordinador de gestión y vinculación de proyectos especiales de la Secretaría del Despacho del Gobernador, presentó los resultados de las gestiones realizadas ante Petróleos Mexicanos, que desde 2022 han permitido concretar donaciones en especie por más de 654 millones de pesos para fortalecer los servicios públicos. 
-Fíjese que en el quehacer periodístico eh revisábamos y bueno, no ha habido anteriormente eh que esas participaciones se dieran a conocer, se llevaron seguimiento. Hidalgo suma más de 654 millones de pesos en apoyos de Petróleos Mexicanos para salud, educación e infraestructura en el estado, Fernando Olvera.
-"Bajo el liderazgo del gobernador, el licenciado Julio Menchaca Salazar, la instrucción ha sido clara y contundente: no quedarnos sentados en el escritorio, sino salir a tocar todas las puertas posibles en el ámbito federal y en el sector productivo para traer beneficios directos a la entidad".
-Durante su participación, el funcionario destacó que de 2022 a la fecha, esta colaboración ha permitido incorporar 53 unidades operativas, brindar más de 179,000 servicios médicos en 59 municipios, se han realizado 10,000 mastografías gratuitas y se han entregado más de 9,000 piezas de mobiliario escolar, además de gestionar 23,200 toneladas de asfalto para mejorar 42 vialidades en diferentes puntos de la entidad. 
-Asimismo, informó sobre la reciente entrega de equipamiento por más de 78 millones de pesos, que incluye maquinaria especializada, 2 ambulancias, 500 luminarias y 5,000 toneladas de asfalto. Además, reiteró el compromiso de la Secretaría del Despacho, encabezada por Alejandro Velázquez Mendoza, para continuar fortaleciendo la vinculación con instituciones federales para impulsar acciones que beneficien directamente a las familias hidalguenses.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/11kr5SLHpfdxfLI7nddMSbpu0Q-8GhNn6/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Fernando Olvera Juárez</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Alejandro Velázquez Mendoza</t>
-  </si>
-  <si>
-    <t>Hacienda/Bol.17/2026</t>
-  </si>
-  <si>
-    <t>Durante la conferencia de prensa en el Edificio del Gobierno del Estado, la secretaria de Hacienda, María Esther Ramírez Vargas, informó que las estimaciones apuntan a que el presupuesto de Hidalgo para 2027 podría superar los 79,000 millones de pesos, impulsando la inversión en infraestructura, obra pública y programas sociales. La funcionaria subrayó que una recaudación eficiente permite ofrecer mejores servicios y oportunidades, para lo cual es necesario fortalecer la cultura contributiva y apoyar a los municipios. Asimismo, destacó que el estado se consolidó como sede de la Cuarta Sesión Ordinaria de AMEXHUASCA y que, gracias a diversas alianzas académicas e institucionales, Hidalgo se posiciona en el segundo lugar nacional en modernización catastral según la Sedatu.</t>
-  </si>
-  <si>
-    <t>Presupuesto De Egresos</t>
-  </si>
-  <si>
-    <t>En más de la información, durante la conferencia de prensa del día de ayer en el Edificio del Gobierno del Estado, la secretaria de Hacienda, María Esther Ramírez Vargas, dio a conocer que las estimaciones de la Secretaría de Hacienda y Crédito Público apuntan a que Hidalgo podría rebasar los 79,000 millones de pesos de presupuesto para 2027, lo que impulsará la inversión en infraestructura, obra pública y programas sociales. Hidalgo proyecta superar los 79,000 millones de pesos en el presupuesto para el 2027. Escuchemos a la secretaria de Hacienda, María Esther Ramírez.
-"Una recaudación eficiente se traduce en más obras, mejores servicios públicos y mayores oportunidades de desarrollo para quienes más lo necesitan. Sin embargo, esos resultados no se sostienen únicamente con fiscalización, también requiere fortalecer la cultura contributiva y dotar a los municipios de información confiable que les permita administrar sus ingresos con mayor eficiencia y equidad".
-Asimismo, la funcionaria resaltó que Hidalgo se consolidó como sede de la Cuarta Sesión Ordinaria de AMEXHUASCA, yo le dábamos a conocer esta información. Este logro, junto con la Alianza con la Unión Europea y la Universidad Politécnica de Pachuca para impartir el primer diplomado en obligaciones fiscales a nivel nacional, posiciona a Hidalgo en el segundo lugar nacional del Índice de Modernización Catastral de la Sedatu, destacando en transparencia y fortalecimiento de finanzas públicas.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1aRE-bXFK_wyVhMLYxP24HwrIbcf1B5bz/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1336/2026</t>
-  </si>
-  <si>
-    <t>Mediante políticas educativas, Menchaca prioriza recursos para el sector</t>
-  </si>
-  <si>
     <t>Entrega de reconocimientos</t>
   </si>
   <si>
-    <t>Continuamos esta tarde la información, esfuerzo, vocación, años de servicio, presencia, convocatoria, más de 2000 trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el compromiso con el fortalecimiento del sector educativo a través de las políticas educativas. El gobernador del estado prioriza recursos para el sector educativo, esto fue lo que destacó el gobernador Julio Menchaca Salazar.
-"El trabajo que realizan ustedes es sumamente importante, porque genera las condiciones al personal académico de aprendizaje, de trasladar el conocimiento a las nuevas generaciones y de tener ese sentido de pertenencia. El gobierno del estado reitera su compromiso de seguir dirigiendo las políticas públicas y los recursos para fortalecer la educación, porque sin educación no hay transformación".
-En este sentido el gobernador del estado aseguró que en Hidalgo existe una suma de esfuerzos entre la sociedad, las familias, el sector educativo y los gobiernos estatal y federal. Este último encabezado por la presidenta Claudia Sheinbaum, que próximamente va a entregar apoyos económicos a 2,185 familias que perdieron sus viviendas a causa de las lluvias del año pasado. 
-Mari Carmen Mandujano Cerrilla, subsecretaria de Administración y Finanzas, señaló que la labor del personal de apoyo y asistencia a la educación deja huella en la vida de las personas, pues sus integrantes suelen ser el primer apoyo que las y los estudiantes encuentran al llegar al plantel educativo, además su presencia en las escuelas constituye un vínculo entre padres y padres de familia y directivos para contribuir al desarrollo de las actividades educativas, de ahí la importancia de reconocer a quienes acumulan entre 10 y 50 años de trayectoria. 
-Said Vargas Sáenz, secretario general de la Sección 15 del SNTE, coincidió en que las y los trabajadores reconocidos han dedicado su vida y talento al servicio de la educación pública.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1uHYWQ8eFuTC1V8Jv5FXp0JqkEL0hOILz/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum, Maricarmen Mandujano Cerrilla, Said Vargas Sáenz</t>
-  </si>
-  <si>
-    <t>SEPH/FN.SN-H/2026</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón asiste al lanzamiento del Primer Concurso Nacional de Coros Escolares</t>
-  </si>
-  <si>
-    <t>CDMX</t>
-  </si>
-  <si>
-    <t>Por otra parte, también el titular de los Servicios Educativos en la entidad asistió al lanzamiento del Primer Concurso Nacional de Coros Escolares realizado en Palacio Nacional junto a la presidenta Claudia Sheinbaum Pardo y el titular de la SEP, Mario Delgado. En el evento participó, por parte de Hidalgo, el el coro de la Escuela Primaria Pedro María Anaya de Mixquiahuala. Representó al estado en este encuentro nacional, el cual promueve el talento y la formación artística de niñas y niños. Y por supuesto, este coro de esta escuela Pedro María Anaya de de Mixquiahuala pues tuvo que pasar por un trayecto para lograr esta representación de de Hidalgo en el lanzamiento del Concurso Nacional de de Coros Escolares. Le comparto un unos instantes de lo que fue esta presentación de de coros ahí en Palacio Nacional por el contexto, por el motivo por el que se presentaron de y las canciones que interpretaron, de verdad estremecedores. Este este hecho, este este acto en el que participan todos estos niños con la ilusión de mostrar su talento y que lo hacen además de forma colectiva, colaborando, sabiendo que la voz de todos y cada uno es importante, pero lo son más aún sumados. Le comparto esta parte de esta interpretación.
-(Interpretación musical en coro del tema "Cielito Lindo")
-Locutor: Bien, una pieza clásica de del gusto popular, Cielito Lindo, que además recordemos también pues se llega a interpretar precisamente en triunfos deportivos de de México. Así es que es un una canción emblemática y e interpretada por cientos de voces infantiles. De verdad que ese el momento fue pues bastante emotivo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Dx9eiCigMyDUfVoiWScpOjfgK23aoI-q/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum, Mario Delgado Carrillo</t>
-  </si>
-  <si>
-    <t>SEPH/FN.SN-G/2026</t>
-  </si>
-  <si>
-    <t>Titular de la dependencia participa en plenaria extraordinaria del Conaedu 2026 y asiste al lanzamiento del Primer Concurso Nacional de Coros Escolares</t>
-  </si>
-  <si>
-    <t>CONAEDU</t>
-  </si>
-  <si>
-    <t>Continuamos con con información del ámbito educativo, le comento que el secretario de Educación Pública, Natividad Castrejón, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria del Consejo Nacional de Autoridades Educativas, que encabezó el secretario de Educación Pública del país, Mario Delgado Carrillo. Durante el encuentro se analizaron temas como la Consulta Nacional para la Construcción del Nuevo Sistema de las Maestras y los Maestros, la USICAMM o lo que hasta ahora es la la USICAMM, los avances en la consolidación del Bachillerato Nacional “Margarita Maza” y las acciones para impulsar la Estrategia Nacional “Vive Saludable, Vive Feliz”.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1QXziSU4fOWNj9HaD9G0IN9mp6n9JgkiD/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Mario Delgado,</t>
-  </si>
-  <si>
-    <t>Entrevista en cabina con la recién egresada de la carrera de Ingeniería en Logística del Instituto Tecnológico Superior del Oriente del Estado de Hidalgo (ITESA), Mexli Ninel Hernández Franco, obtuvo el segundo lugar en el Premio de Excelencia Dual gracias a un proyecto de optimización y digitalización de procesos logísticos implementado en el centro de distribución (Cedis) de la empresa Caxaplax. Durante su entrevista en cabina, la joven destacó cómo su formación práctica y teórica a través del modelo dual en el ITESA le permitió integrarse con éxito al sector laboral e impulsar herramientas tecnológicas para la mejora de flujos de información empresarial.</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Educación dual</t>
-  </si>
-  <si>
-    <t>Apan</t>
-  </si>
-  <si>
-    <t>Y de verdad que es un orgullo recibir en la cabina de NQ en Pachuca a personas distinguidas, a personas exitosas, como Mexli Ninel Hernández Franco, egresada de la Ingeniería en Logística por el Instituto Tecnológico Superior del Oriente del Estado de Hidalgo, el ITESA. ¡Bienvenida! Apenas en diciembre pasado egresaste y ya presentaste un proyecto para una empresa, ya tienes trabajo y ya obtuviste un premio, el segundo lugar en el Premio de Excelencia Dual, pues muchas felicidades por esta trayectoria y ello supone que tu paso por por el ITESA ha sido importante. Muy buen día.
-Buenos días, muchas gracias por la invitación. Y sí, he tenido la oportunidad de participar en estos eventos. Creo que ITESA es es una de las universidades que te brinda estas oportunidades justamente pues para poder desarrollar lo que aprendes dentro de lo que es la carrera. Eh dentro de ITESA pues durante los semestres trabajamos diferentes eh pues cuestiones como la planeación, los almacenes, que te ayudan al final de cuentas al llegar a una a una empresa a poder aplicarlo realmente y creo que también eh te ayuda a crecer pues tus habilidades personales, llegas con con más interés de poder liderar un proyecto, de poder crear diferentes soluciones para lo que son las las empresas y en este caso pues justamente ITESA pues ayuda a combinar la parte teórica con la parte práctica mediante lo que es modelo dual.
-Muy bien, y para ti representó además tener una institución cercana, eres originaria del estado de Hidalgo, de la zona del Altiplano.
-Sí, sí, la verdad es que al estar en Tepeapulco, que es de donde yo provengo, creo que que pues el el pertenecer a esta zona que también aparte es como una zona industrial, pues creo que también te abre el camino a poder conocer no solamente la industria de lo que es la zona, sino también pues a poder crecer a a zonas cercanas o incluso más, como en el caso del premio. Tuve la oportunidad de de poder eh pues conocer diferentes proyectos de diferentes estados y creo que es lo que hace la diferencia que ITESA te da esas herramientas que te permiten pues justamente competir con otros estados o incluso eh pues a nivel nacional, en este caso o o global, se puede decir, porque también puedes pues ir creciendo este este tipo de proyectos.
-¿En qué consiste este este proyecto con el que destacas en este premio de Excelencia Dual?
-El proyecto está basado en el Cedis de Caxaplax. En este caso ellos trabajan productos plásticos y de resina. Eh se se realizó un análisis primero de lo que son las actividades logísticas que se llevan a cabo dentro del centro de distribución y con ello pues se se buscó optimizar justamente esta parte de de la información que se tiene. A veces es muy complicado en los Cedis poder trabajar tanta información diaria, entonces justamente esta herramienta tecnológica se trabajó mediante Excel, mediante macros, tratando de de hacer que toda la información funcionara conjuntamente y que mediante tablas, gráficos, formularios, botones, justamente se se tuviera una una visualización en un dashboard más completa, pero eh en el momento que estás trabajando pues surgen nuevas nuevas cuestiones que la empresa empieza a buscar en ti, que dice, "Okay, está bien tu proyecto, pero necesitas eh que la información esté en tiempo real." Entonces, justamente se avanzó a poder crear otro otra herramienta que en este caso fue mediante una hoja de cálculo con eh pues celdas formuladas que permitieran que la información no estuviera duplicada, que los registros que antes se hacían manuales se hicieran digitales, que se hicieran de forma más rápida y sobre todo que que al pasar esta hoja de cálculo a lo que fue el Uker Estudio nos diera un un dashboard más completo, o sea, nos diera esta parte de los gráficos en tiempo real, que se pudiera utilizar en todo momento, porque al final de cuentas es lo que busca un Cedis, optimizar esta información.
-Muy bien, mencionas que la empresa valoró en primera instancia el proyecto, pero que con base en su labor cotidiana, pues pedía otros elementos. Eso es muy importante, el contacto con con la realidad como estudiantes tú. Tú dentro del ITESA tuviste esta posibilidad de este contacto con con el sector empresarial, con con la realidad laboral.
-Sí, creo que ITESA permite estos contactos porque justamente eh trabaja a la par los conocimientos teóricos, pero también los prácticos. En este caso modelo dual a veces es como tu primera oportunidad de de pasar a lo que es el entorno real. Entonces el pasar a este a este tipo de proyectos yo creo que significa pues algo muy importante porque pasas de lo que ya sabes a hacerlo real, entonces la empresa busca justamente eh líderes, busca personas que que realmente te den soluciones prácticas y que realmente fue lo fue lo que pasó. El proyecto ya se implementó, el proyecto ya está en marcha, entonces eh se hizo una capacitación, se entregaron manuales y demás herramientas que que al final de cuentas a la empresa pues le sirven justamente para seguir trabajando día a día.
-Muy bien, ya con un premio con esta preparación, con este proyecto ya ya en marcha y con con trabajo y muy joven además, por supuesto, ¿hacia dónde apuntas? ¿Qué es lo que visualizas para ti como egresada del ITESA?
-Pues sí, claro, siempre este crecer en el ámbito profesional como ingeniera en logística. La verdad es que ITESA te brinda las herramientas tanto profesionales como personales y en este caso el el poder realizar este tipo de proyectos pues me abrió las puertas incluso a mi primer trabajo. Eh al realizar este tipo de de dashboard, de proyectos que impulsan a crecer a una empresa, digitalizarse en este mundo que a lo mejor lo ven lejano, pero pues al final de cuentas no se necesita tanto en cuanto a mi a mi primer trabajo pues tuve la oportunidad de incluso de de poder decir que que tenía ese proyecto atrás. Incluso me abrió esa puerta de decir, "Okay, ven y trabaja exactamente lo mismo, necesito una herramienta parecida, necesito que que me busques optimizar lo que ya optimizaste en otro lugar."
-Conductor: Muy bien, pues muchas felicidades, de verdad sin duda que seguiremos escuchando hablar de ti seguramente por por todo el camino que te estás abriendo a menos de un año de haber egresado de la carrera de la ingeniería en logística. ¿Algo que desees agregar?
-Pues nada, la verdad es que yo muy agradecida con con la invitación y sobre todo también con con ITESA que que siempre te brinda estas oportunidades y pues más que nada hacer una invitación justamente a los estudiantes a creer en ellos, a impulsar este justamente este tipo de proyectos que no solamente te dejan algo profesional, sino también algo personal, siempre es importante crecer las habilidades de liderazgo para poder entrar a una industria donde pues generalmente es donde vas a crecer profesionalmente, entonces es muy importante para mí pues hacer esa invitación.
-uy bien, pues muchas felicidades nuevamente, que te siga yendo muy bien. Mexli Ninel Hernández Franco, egresada de Ingeniería en Logística del Instituto Tecnológico Superior del Oriente del Estado de Hidalgo, el ITESA. ¡Felicidades!
-Muchas gracias.
-Hasta pronto.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1BuS5LjojNKIS8vPZm_1RsMOqU36JUW7d/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Autoridades llevan a cabo un ejercicio de cateos e investigación en diversos puntos de la ciudad de Tulancingo. Uno de los operativos se registra en las inmediaciones de la Escuela Secundaria Número 2, ubicada en la avenida del Trabajo de la colonia Vicente Guerrero. Estas diligencias derivan de carpetas de investigación en curso, por lo que se exhorta a la ciudadanía a manejar con precaución y evitar obstaculizar la labor de los cuerpos de seguridad.</t>
-  </si>
-  <si>
     <t>PGJEH</t>
   </si>
   <si>
-    <t>Cateo</t>
-  </si>
-  <si>
-    <t>Y pues está confirmado, ya nos tendrán más detalles al respecto desde el Notimóvil. Un ejercicio de de cateo que se está realizando precisamente en distintos puntos aquí de la ciudad de Tulancingo. Son técnicas de investigación consistentes en cateos derivados de investigaciones originadas originadas, perdón, a partir de carpetas de investigación. Uno de estos cateos ahí en las inmediaciones de la Secundaria Número 2, avenida del Trabajo, en la colonia Vicente Guerrero. Así que maneje con mucha precaución y, por supuesto, pues no hay que no hay que de alguna forma obstruir la labor que están haciendo las autoridades en estos en estos momentos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/17dxGcdm9F8GEROzCL_fa_GDeYnH0JEnv/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Le comento que por su esfuerzo, vocación y años de servicio, más de 2,000 trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el gobernador Julio Menchaca Salazar, quien refrendó su compromiso con el fortalecimiento del sector educativo para transformar la entidad. Así, el mandatario estatal reconoció el trabajo del personal de apoyo y asistencia a la educación.
-"El trabajo que realizan ustedes es sumamente importante, porque genera las condiciones al personal académico de aprendizaje, de trasladar el conocimiento a las nuevas generaciones y de tener ese sentido de pertenencia. El gobierno del estado reitera su compromiso de seguir dirigiendo las políticas públicas y los recursos para fortalecer la educación, porque sin educación no hay transformación".
-"Y bueno, personalmente también he corroborado esta importancia del trabajo que desarrolla el personal de apoyo y asistencia a la educación. Efectivamente, brindan en el día a día herramientas para la continuidad, para el desarrollo del trabajo docente y se hace pues este equipo orientado a fortalecer la educación en su conjunto. Es muy importante esta labor que desarrollan. Muchas felicidades. Estas más de 2,000 personas, servidoras públicas, que han recibido este reconocimiento por su trayectoria como personal de apoyo y asistencia a la educación".
-Menchaca Salazar en este contexto aseguró que en Hidalgo existe una suma de esfuerzos entre la sociedad, las familias, el sector educativo y los gobiernos estatal y federal, este último encabezado por la presidenta Claudia Sheinbaum Pardo, que próximamente entregará apoyos económicos a 2,185 familias que perdieron sus viviendas a causa de las lluvias del año pasado, esto que ya se ha anunciado esta próxima visita de la mandataria nacional. En este marco de la entrega de los estímulos al personal de apoyo y asistencia a la educación, Mari Carmen Mandujano Cerrilla, la subsecretaria de Administración y Finanzas, señaló que la labor de este personal de apoyo deja huella en la vida de las personas, pues sus integrantes suelen ser el primer apoyo que las y los estudiantes encuentran al llegar a la escuela, los estudiantes y las familias.
-Es en muchas ocasiones el primer contacto que tienen en los centros educativos. Además, su presencia en los planteles constituye un vínculo entre madres y padres de familia y directivos para contribuir al desarrollo de las actividades educativas. De ahí la importancia de reconocer a quienes acumulan entre 10 y 50 años de trayectoria de trabajo en este sector. Said Vargas Sáenz, el secretario general de la Sección 15 del Sindicato Nacional de Trabajadores de la Educación (SNTE), coincidió en que las y los trabajadores reconocidos han dedicado su vida y talento al servicio de la educación pública de Hidalgo. Por ello aseguró que el sindicato continuará defendiendo la trayectoria y los derechos de todo el personal del sector. Asimismo, agradeció al gobernador Julio Menchaca, dijo, por ser un aliado permanente de las causas y conquistas sindicales. Destacó que a 4 años del inicio de su gestión se ha mantenido intacto el mapa prestacional del personal educativo y se impulsa una relación de respeto y de trabajo conjunto. Así lo subrayó el dirigente sindical Said Vargas en el marco de esta entrega de reconocimientos por trayectoria a personal de apoyo y asistencia...</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1xjVZSSzG2Xr0QFvf5hzLtcuFpElHpEH-/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, confirmó que la presidenta de la república, Claudia Sheinbaum, realizará una gira de dos días en la entidad durante el próximo jueves y viernes. El objetivo de la visita es entregar apoyos y tarjetas a las familias afectadas por las lluvias y precipitaciones que ocasionaron daños en diversas regiones y miles de hectáreas siniestradas. La agenda presidencial contemplará actividades y recorridos en municipios como Zacualtipán de Ángeles y Villa de Tezontepec para atender a las poblaciones damnificadas por fenómenos meteorológicos previos.</t>
-  </si>
-  <si>
-    <t>Visita Sheinbaum</t>
-  </si>
-  <si>
-    <t>Hidalgo</t>
-  </si>
-  <si>
-    <t>También se anunció ayer, el gobernador confirmó que nuevamente regresará la presidenta al estado de Hidalgo. Sí, así es, está considerado también en la agenda. En cuanto den la información oficial, les estaremos compartiendo, Jesús. Muchas, muchas gracias, David, estamos en contacto. Muy buen día. Muy, muy buenos días, gracias. Y pues, así la información desde la Ciudad de México. y como le platico en efecto, pues el gobernador Julio Menchaca Salazar confirmó que la mandataria, la presidenta Claudia Sheinbaum, va a regresar al estado de Hidalgo esta semana para una gira de dos días, en la cual pues va a entregar apoyos a familias afectadas por las lluvias y hará recorridos por distintos puntos del estado, así lo declaró ayer el gobernador, señaló que la presidenta va a permanecer en territorio hidalguense durante el próximo jueves y viernes, con una agenda que contempla actividades relacionadas con la atención a las personas damnificadas por la llamada vaguada monzónica de hace un a Uno de los puntos centrales de la visita ser la entrega de tarjetas a familias afectadas por las lluvias luego de las precipitaciones que provocaron da en diferentes regiones de aquí de Hidalgo La emergencia dejó, entre otras afectaciones, miles de hectáreas dañadas, por lo que las autoridades han desplegado distintas acciones para atender a las familias que sufrieron estas pérdidas. De acuerdo con lo adelantado por el gobernador ayer, durante su estancia en Hidalgo, la presidenta también tiene contempladas actividades en los municipios de Zapotlán de Juárez y Villa de Tezontepec. Así, la presidenta tendrá una nueva jornada de actividades en territorio hidalguense, con una agenda que combinará la atención a las zonas afectadas por las lluvias con recorridos por municipios del estado. Así que, como dice David Cárdenas, en cuanto compartan la agenda, la agenda ya oficial de la presidenta, pues estaremos, por supuesto, con la facilidad de compartirles el detalle de su visita.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ia4i40z-YXgF4MtnGwSa7oHvcTnri2rB/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Súper Stéreo 100.5 FM</t>
   </si>
   <si>
@@ -468,196 +224,21 @@
     <t>Enfoque Regional Meridiano</t>
   </si>
   <si>
-    <t>Alrededor de 60 personas bloquearon la mañana de hoy martes ambos sentidos de la carretera federal México-Laredo, a la altura de la comunidad de Julián Villagrán, en Ixmiquilpan, para exigir la liberación de dos personas. Al respecto, la titular de Asuntos Agrarios de la Secretaría de Gobierno de Hidalgo, Reyna Serrano, explicó que la movilización tiene su origen en una controversia agraria relacionada con la posesión de terrenos cuya pertenencia reclama la comunidad de Pueblo Nuevo."Derivado de un conflicto agrario.</t>
-  </si>
-  <si>
-    <t>Conflicto agrario</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Alrededor de 60 personas bloquearon la mañana de hoy martes ambos sentidos de la carretera federal México-Laredo, a la altura de la comunidad de Julián Villagrán, en Ixmiquilpan, para exigir la liberación de dos personas. Al respecto, la titular de Asuntos Agrarios de la Secretaría de Gobierno de Hidalgo, Reyna Serrano, explicó que la movilización tiene su origen en una controversia agraria relacionada con la posesión de terrenos cuya pertenencia reclama la comunidad de Pueblo Nuevo."Derivado de un conflicto agrario. Este conflicto agrario data desde el año 2010, en donde pobladores de Julián Villagrán, e incluidas estas personas que actualmente se encuentran recluidas, entraron a tomar posesión de parcelas que pertenecen al núcleo agrario de Pueblo Nuevo. Ambos, Pueblo Nuevo y Julián Villagrán, son dos núcleos agrarios que pertenecen al municipio de Ixmiquilpan. Derivado de que Julián Villagrán toma posesión de varias parcelas y una fracción de uso común del poblado de Pueblo Nuevo, el comisariado ejidal y los ejidatarios afectados inician juicios agrarios ante el Tribunal Agrario. En el 2019, la autoridad agraria resuelve mediante sentencia a favor de Pueblo Nuevo, en donde se les reconoce el mejor derecho a poseer y la titularidad de estas parcelas. Son 15 parcelas y una fracción de uso común, una parcela con destino específico denominada parcela escolar, y en la sentencia se ordena que los pobladores de Julián Villagrán que tienen la posesión hagan la entrega con todos sus frutos y accesiones que contenga la misma. Se han realizado 11 intentos de ejecución en estos juicios agrarios. Derivado de estos intentos de ejecución, se hizo la entrega de cinco parcelas. Estas cinco parcelas fueron delimitadas y tomaron posesión los pobladores de Pueblo Nuevo; sin embargo, los vecinos de Julián Villagrán, de nueva cuenta, entran a tomar posesión aun y cuando ya existen las sentencias dictadas por el Tribunal Agrario."La funcionaria dio a conocer que habitantes de Pueblo Nuevo promovieron denuncias que derivaron en la apertura de carpetas de investigación por el delito de despojo agravado.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1qvyvDNRf2Aqg-RlIvW5JW_n0dv67JRn9/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Reyna Serrano</t>
-  </si>
-  <si>
-    <t>Comenta conductor Jesús Gonzalez : Le pregunto a usted qué piensa del Hoy No Circula. Hace mucho tiempo, no es la primera vez que se hace esta propuesta, hace ya algunos años se decía que también querían echar a andar el Hoy No Circula en esta región de Tula: Tula, Tepeji, algunas zonas cercanas, Tulancingo y en Pachuca. Le comento esto porque ante las condiciones de tránsito que registra la zona metropolitana de Pachuca, el Gobierno de Hidalgo contempla evaluar la viabilidad del programa Hoy No Circula como parte de una estrategia más amplia para atender los problemas de movilidad. La secretaria de Movilidad y Transporte, Lyzbeth Robles, dio a conocer que sostuvo un primer acercamiento con su homóloga de Medio Ambiente y Recursos Naturales, Mónica Mixtega, con quien acordó establecer una mesa de trabajo para examinar los alcances de esta posibilidad</t>
-  </si>
-  <si>
     <t>Hoy no circula</t>
   </si>
   <si>
-    <t>Comenta conductor Jesús Gonzalez : Le pregunto a usted qué piensa del Hoy No Circula. Hace mucho tiempo, no es la primera vez que se hace esta propuesta, hace ya algunos años se decía que también querían echar a andar el Hoy No Circula en esta región de Tula: Tula, Tepeji, algunas zonas cercanas, Tulancingo y en Pachuca. Le comento esto porque ante las condiciones de tránsito que registra la zona metropolitana de Pachuca, el Gobierno de Hidalgo contempla evaluar la viabilidad del programa Hoy No Circula como parte de una estrategia más amplia para atender los problemas de movilidad. La secretaria de Movilidad y Transporte, Lyzbeth Robles, dio a conocer que sostuvo un primer acercamiento con su homóloga de Medio Ambiente y Recursos Naturales, Mónica Mixtega, con quien acordó establecer una mesa de trabajo para examinar los alcances de esta posibilidad. La propuesta surge en un contexto en el que Pachuca figura entre las ciudades con mayores tiempos de congestión vehicular, según el estudio... el estudio denominado «Costo del tráfico 2026», elaborado por el Instituto Mexicano para la Competitividad, el IMCO.  “ Ya tuvimos una llamada, solo llamada telefónica a la secretaria Mixtega y su servidora de SEMARNATH. Acordamos tener una reunión ella y su servidora para platicar sobre los pormenores de esta propuesta del Hoy No Circula, no solamente con base al resultado del IMCO, sino tenemos ya un PIMUS de Pachuca, tenemos censo ya de transporte público realizado a cargo de la Secretaría de Movilidad y Transporte y del Sistema de Transporte Convencional de Hidalgo, tenemos también otros datos que pueden configurar una gran herramienta”</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hALPhVsUIWloRoYx-lzWrVueobyyi29x/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SEMARNATH</t>
-  </si>
-  <si>
-    <t>Mónica Mixtega</t>
-  </si>
-  <si>
     <t>SDPEE-OCSAD/Bol.1337/2026</t>
   </si>
   <si>
-    <t>Julio Menchaca Salazar, quien encabezó esta mañana la ceremonia conmemorativa del Día del Médico y la Médica, en cuyo marco se llevó a cabo la entrega de medallas y reconocimientos a profesionales de la salud distinguidos por su trayectoria y desempeño en la entidad."Siempre he pensado que la carrera más difícil profesional es ser médico o médica, porque implica un contacto muy directo con las personas.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, quien encabezó esta mañana la ceremonia conmemorativa del Día del Médico y la Médica, en cuyo marco se llevó a cabo la entrega de medallas y reconocimientos a profesionales de la salud distinguidos por su trayectoria y desempeño en la entidad."Siempre he pensado que la carrera más difícil profesional es ser médico o médica, porque implica un contacto muy directo con las personas. Es, sin duda, una enorme expresión de calidad humana el ejercicio profesional de médico. Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al Estado de Hidalgo y a México, proyectándolo con su saber. Creo que se han realizado las acciones institucionales para que puedan ejercer de mejor manera esa muy noble profesión de ser médicas y de ser médicos. Por ello, me siento de verdad emocionado de reconocer la trayectoria, el esfuerzo, el trabajo, la vida de cada una y de cada uno de ustedes, y también de los que no están aquí, que desde su trinchera allá en el consultorio, en la clínica, en las zonas más alejadas del estado desempeñan con un gran sentido humano, pero sobre todo con un gran compromiso social esta muy bella profesión de ser médica y de ser médico.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/12GV5v4vduEt-8QNFpWfmiCjZ7YFPZLMB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Tenemos noticias desde el estado de Hidalgo: Natividad Castrejón Valdéz participa en la plenaria extraordinaria del Consejo Nacional de Autoridades Educativas. El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria 2026 del Consejo Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo. D</t>
-  </si>
-  <si>
-    <t>Tenemos noticias desde el estado de Hidalgo: Natividad Castrejón Valdéz participa en la plenaria extraordinaria del Consejo Nacional de Autoridades Educativas.
-El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria 2026 del Consejo Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo. Durante el encuentro se analizaron temas como la consulta nacional para la construcción de nuevos sistemas de maestras y los maestros, los avances en la consolidación del Bachillerato Nacional Margarita Maza y las acciones para impulsar la estrategia nacional "Vive saludable, vive feliz". Es lo que se destaca en torno a esta importante reunión de Consejo Nacional de Autoridades Educativas allá en lo que respecta a la zona de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1__M3nplF_iFg5xnEA8JOeRw7XmOQDcEA/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Natividad Castejón</t>
-  </si>
-  <si>
-    <t>Mario Delgado</t>
-  </si>
-  <si>
     <t>Christian García</t>
   </si>
   <si>
     <t>Enfoque Regional Matutino</t>
   </si>
   <si>
-    <t>Oiga, ya ve que le platicábamos al inicio este coro de la Escuela Primaria Pedro María Anaya de Mixquiahuala. Desde el día de ayer que le mandamos también esta felicitación. Bueno, pues ellos representaron a Hidalgo durante el aniversario de los coros escolares 2026. En el encuentro participaron la presidenta Claudia Sheinbaum Pardo, el secretario de Educación y también el titular de la Secretaría de Educación Pública de Hidalgo, Natividad Castrejón Valdéz.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JbJ43pSK-KjWm_DRt6T6VmtR6OETHOQm/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum, Mario Delgado</t>
-  </si>
-  <si>
-    <t>SSH/Bol.183/2026</t>
-  </si>
-  <si>
-    <t>Que en Mixquiahuala, la Secretaría de Salud de Hidalgo entregó apoyos funcionales a personas que requieren ayuda para desplazarse. La titular, Escalante Arroyo, encabezó la entrega de 19 sillas de ruedas, 6 andaderas y 4 bastones, esto para favorecer la movilidad de los beneficiarios.</t>
-  </si>
-  <si>
-    <t>Auxiliares funcionales</t>
-  </si>
-  <si>
-    <t>Mixquiahuala</t>
-  </si>
-  <si>
-    <t>Que en Mixquiahuala, la Secretaría de Salud de Hidalgo entregó apoyos funcionales a personas que requieren ayuda para desplazarse. La titular, Escalante Arroyo, encabezó la entrega de 19 sillas de ruedas, 6 andaderas y 4 bastones, esto para favorecer la movilidad de los beneficiarios. La funcionaria invitó a la población a identificar a quienes necesiten estos dispositivos y canalizar sus jurisdicciones sanitarias. También llamó a las familias y personas cuidadoras a estar pendientes de la salud y bienestar de las personas adultas mayores.La funcionaria estatal destacó durante la entrega:"Hoy, en el gobierno del gobernador Julio Menchaca Salazar, venimos personalmente a entregar los apoyos y a decirles a todas las personas que si hay gente que ustedes conozcan y sepan que lo necesitan, pueden avisarnos. Por si ustedes conocen a alguien que requiera un bastón, una andadera, un aparato auditivo o algún tipo de apoyo de este tipo, el doctor ahorita se va a coordinar con quien a ustedes les diga... Pero lo que queremos es poderles acercar a ustedes los apoyos funcionales que hay dentro de la Secretaría de Salud del gobierno del Estado. Nuestro interés es entregar y causar una movilidad efectiva."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HoskgUw9QTO_bQUIQL4uno2F_SKB6wpz/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Vanesa Escalante Arroyo</t>
   </si>
   <si>
-    <t>Ante los señalamientos por presunto nepotismo y la investigación iniciada por la Contraloría, se informó que renunció a su cargo como secretaria particular de la titular de la Secretaría de Cultura de Hidalgo, Neida Naranjo Baltazar.</t>
-  </si>
-  <si>
-    <t>Oficialía Mayor</t>
-  </si>
-  <si>
-    <t>Nepotismo</t>
-  </si>
-  <si>
-    <t>Ante los señalamientos por presunto nepotismo y la investigación iniciada por la Contraloría, se informó que renunció a su cargo como secretaria particular de la titular de la Secretaría de Cultura de Hidalgo, Neida Naranjo Baltazar. La Oficialía Mayor fijó postura sobre el caso:"La Oficialía Mayor confió dos a Baltazar en la dependencia, pero aclaró que no revisa directamente los expedientes de cada contratación. Este trámite responde a las áreas de cada Secretaría. La precisión se da luego de que la Secretaría de Cultura señalara a la Oficialía Mayor de revisar los expedientes, y a la Contraloría como instancia encargada de investigar posibles conflictos."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1bvyvmmLc7E_KVDrFK2NRpOF7EfKG2OLL/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Cultura, Contraloría</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo</t>
-  </si>
-  <si>
-    <t>OCSAD/Bol.1334/2026</t>
-  </si>
-  <si>
-    <t>Transportistas sin seguro vigente en Hidalgo podría costarles mucho más que una multa. También podrían perder su concesión. la convocatoria y la supervisión podría comenzar a partir de noviembre. Esto lo informó la Secretaría de Movilidad y Transporte, Lyzbeth Robles</t>
-  </si>
-  <si>
-    <t>Supervisión de transporte</t>
-  </si>
-  <si>
-    <t>Transportistas sin seguro vigente en Hidalgo podría costarles mucho más que una multa. También podrían perder su concesión. la convocatoria y la supervisión podría comenzar a partir de noviembre. Esto lo informó la Secretaría de Movilidad y Transporte, Lyzbeth Robles Para informar al público que esta semana se emite la circular correspondiente a través de la cual el transporte público convencional  tendrá una revisión binaria única y exclusivamente para la revisión de los... Insistimos en esto por la trascendencia que tiene. Las personas eh concesionarias y las personas conductoras del transporte público convencional, pues la póliza de seguro vigente, que están establecidos en nuestra ley, en el artículo 107 y 108. Las coberturas de la póliza de seguro es importante que las tomas. Lyzbeth Robles destacó los lugares para la revisión: se efectuará, se efectuará en las instalaciones del sistema de transporte oficinas itinerantes que se implementen en las coordinaciones regionales que se distribuyen en el estado de Hidalgo, y en territorio, que es algo que estamos innovando, que podrá llevarse a cabo de manera específica por la Dirección de Vigilancia y Supervisión Transporte Convencional de Hidalgo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zGN0OI0-opTlNV6BKDUx_R0a9l09VyM5/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Las gestiones del gobierno de Hidalgo ante Pemex han permitido incorporar cincuenta y tres unidades operativas, ofrecer ciento setenta y nueve mil servicios médicos en cincuenta y nueve municipios y realizar diez mil mastografías gratuitas desde el dos mil veintidós. V</t>
-  </si>
-  <si>
-    <t>Las gestiones del gobierno de Hidalgo ante Pemex han permitido incorporar cincuenta y tres unidades operativas, ofrecer ciento setenta y nueve mil servicios médicos en cincuenta y nueve municipios y realizar diez mil mastografías gratuitas desde el dos mil veintidós. Vera Juárez, coordinador de gestión y vinculación de proyectos especiales, informó que también los servicios de salud se acercaron a la población con la unidad. Vera Juárez destacó la importancia de acercar los servicios médicos a las comunidades más alejadas:"Salud dignos a las comunidades más alejadas ha sido una encomienda para este gobierno. Con esta convicción de que la atención médica debe ser al alcance de... su operación la unidad médica móvil, la cual ha brindado más de ciento setenta y nueve mil servicios en cincuenta y nueve municipios. Estas atenciones con general y odontológica, además de contar con una farmacia de cuadro básico totalmente gratuito."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/13dg1zeGF50YIk5b4lWq9qONAKWGIfxbg/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Hidalgo podría superar los 79 mil millones de pesos de presupuesto para el ejercicio 2027. Así lo informó la secretaria de Hacienda estatal, María Esther Ramírez Vargas, con base en las proyecciones de la Secretaría de Hacienda y Crédito Público (SHCP).</t>
-  </si>
-  <si>
-    <t>Hidalgo podría superar los 79 mil millones de pesos de presupuesto para el ejercicio 2027. Así lo informó la secretaria de Hacienda estatal, María Esther Ramírez Vargas, con base en las proyecciones de la Secretaría de Hacienda y Crédito Público (SHCP). De concretarse, dichos recursos permitirían robustecer la inversión en infraestructura, obra pública y programas sociales.La funcionaria estatal detalló los avances en materia recaudatoria y eficiencia presupuestal:"A cuatro años de administración, hemos incrementado en un 96 por ciento la recaudación de ingresos. ¿Y cómo lo hicimos? Modernizamos los procesos tributarios, ampliamos el padrón de contribuyentes y fortalecimos la fiscalización."Asimismo, Ramírez Vargas resaltó que el estado ha escalado posiciones en el tablero global de eficiencia recaudatoria del Servicio de Administración Tributaria (SAT), pasando de posiciones rezagadas en 2022 hasta ubicarse en el primer lugar a nivel nacional para los periodos 2025 y 2026. Respecto al impacto del presupuesto en las dependencias, indicó:"Por lo pronto no se visualiza, porque el efecto que causa el que se esté incrementando el presupuesto para las ejecutoras del gasto, llámese dependencias, organismos, es precisamente porque es importante el recurso a lo que nosotros denominamos gasto de inversión, obras, acciones y proyectos."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/19eIfFSojBHAGZYPv1K4bmPH60Gbwbbxp/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria con Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdéz, participó en la Cuarta Reunión Nacional Plenaria Extraordinaria con Nacional de Autoridades Educativas, encabezada por el titular de la Secretaría de Educación Pública, Mario Delgado Carrillo.Durante el encuentro se abordaron diversos temas prioritarios:"Mire, en este... también estuvo ahí el secretario de educación pública de Hidalgo, ayer le decíamos de este coro que es de Mixquiahuala y que estuvo para la mañanera. Bueno pues ahí estuvo también precisamente con ellos."Asimismo, se discutieron asuntos como la consulta nacional para la construcción del nuevo sistema de las maestras y los maestros, los avances en la consolidación del bachillerato nacional y las acciones para impulsar la estrategia nacional "Vive saludable, vive feliz".</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1uwimD2y5Prh_3LFPalEm_9fAVcoali0v/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Mire, más de dos mil trabajadores de apoyo y asistencia a la educación en Hidalgo recibieron trayectoria de entre diez y cincuenta años de servicio. Durante la entrega, el gobernador Julio Menchaca destacó que su labor contribuye al mantenimiento de los planteles y refrendó el compromiso de fortalecer la educación pública.</t>
-  </si>
-  <si>
-    <t>Mire, más de dos mil trabajadores de apoyo y asistencia a la educación en Hidalgo recibieron trayectoria de entre diez y cincuenta años de servicio. Durante la entrega, el gobernador Julio Menchaca destacó que su labor contribuye al mantenimiento de los planteles y refrendó el compromiso de fortalecer la educación pública. El gobernador Julio Menchaca señaló: "El trabajo que realizan ustedes es sumamente ... las condiciones al personal académico ... de aprendizaje, de trasladar el conocimiento a las nuevas generaciones ... y de pertenencia. El gobierno del Estado ... reitera su compromiso de seguir dirigiendo las políticas públicas y los recursos ... tal y ser la educación, porque sin educación no hay transformación."Además, el secretario general de la Sección 15 del Sindicato Nacional de Trabajadores de la Educación (SNTE), Said Vargas, reconoció la labor del personal y afirmó que el sindicato seguirá defendiendo sus derechos laborales.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1dkTrZ-UO-CjMfLWVC1i_vcoX7IhGAytR/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SNTE</t>
-  </si>
-  <si>
-    <t>Said Vargas</t>
-  </si>
-  <si>
-    <t>Anuncian visita de la presidenta Claudia Sheinbaum a Hidalgo y entrega de apoyos Le informamos que se informó que se prevé la visita de la presidenta de México, Claudia Sheinbaum, dos días esta semana.</t>
-  </si>
-  <si>
-    <t>Anuncian visita de la presidenta Claudia Sheinbaum a Hidalgo y entrega de apoyos Le informamos que se informó que se prevé la visita de la presidenta de México, Claudia Sheinbaum, dos días esta semana. La mandataria federal encabezará la entrega de apoyos en tarjetas a las más de dos mil familias que perdieron su vivienda por la vaguada monzónica, así como el arranque de los trabajos del polo de desarrollo de Zapotlán y la inauguración de empresas. El gobernador señaló:"Y creo que viene dos días. En esto, la conversación que tuve ayer, era nada más que nada venía el jueves, pero parece que también el viernes. ¿A qué viene? Bueno, a ver, dos cosas muy importantes. Uno, en las tarjetas, digamos, de las dos mil, más de dos mil familias que perdieron su vivienda y les va a dar un apoyo en las tarjetas, digamos."Asimismo, se detalló la inauguración de proyectos industriales en la entidad: "Y otro muy importante también, es la inauguración de dos espacios de mercado libre, de los cinco que van a estar instalados en Zapotlán de Juárez, de laboratorios Carnot, son inversión francesa, y de la puesta en marcha del polo de desarrollo, o sea, de Villa de Tezontepec a Zapotlán... y en el arranque de los trabajos, de lo que es una inversión importantísima."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1cB0T2AI2UYXeFZbU8sZCwrVUEzzuml_J/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Claudia Sheinbaum</t>
-  </si>
-  <si>
     <t>Acir 92.5 FM</t>
   </si>
   <si>
@@ -667,39 +248,6 @@
     <t>Eulalio Larrieta</t>
   </si>
   <si>
-    <t>En conferencia de prensa la titular de la secretaria de Movilidad y transporte del Estado de Hidalgo, Lyzbteh Robles, informó que fue presentada una denuncia ante la Procuraduría General de Justicia del Estado de Hidalgo contra la plataforma de taxi por aplicación UBER,</t>
-  </si>
-  <si>
-    <t>La Secretaría de Movilidad y Transporte del Estado de Hidalgo presentó una denuncia formal contra la operación irregular de Uber aquí en Pachuca. Vamos a escuchar.En conferencia de prensa la titular de la secretaria de Movilidad y transporte del Estado de Hidalgo, Lyzbteh Robles, informó que fue presentada una denuncia ante la Procuraduría General de Justicia del Estado de Hidalgo contra la plataforma de taxi por aplicación UBER,  por la presunta operación irregular  en Pachuca.Lyzbeth Robles detalló que fue la Coordinación General Jurídica del gobierno del estado quien llevó a cabo el trámite, reiteró que  La Ley de Movilidad y Transporte no contempla la operación de este servicio en el estado, por lo que es competencia del poder legislativo su regulación. AUDIO Lyzbteh Robles</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1KL_3d6MWY7caXtUH9_MboNcpwdbipqcx/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Por su esfuerzo, vocación y años de servicio, más de dos mil trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el gobernador Julio Menchaca quien refrendó su compromiso con el fortalecimiento del sector educativo para transformar a la entidad</t>
-  </si>
-  <si>
-    <t>Que el gobernador Julio Menchaca entregó reconocimientos a más de 2.000 trabajadores de la educación que tienen ya elaborando entre 10 y 50 años ahí en el magisterio. Vamos a escuchar la información con Jackie Servino. Por su esfuerzo, vocación y años de servicio, más de dos mil trabajadoras y trabajadores de apoyo y asistencia a la educación recibieron un estímulo y fueron reconocidos por el gobernador Julio Menchaca quien refrendó su compromiso con el fortalecimiento del sector educativo para transformar a la entidad.Destacó que el trabajo que realizan es sumamente importante porque generan las condiciones para el aprendizaje, la transmisión del conocimiento a las nuevas generaciones y el desarrollo de un sentido de pertenencia, reiteró su compromiso de seguir orientando las políticas públicas y los recursos al fortalecimiento de la educación, porque sin educación no hay transformación”, expresó el titular del Ejecutivo estatal. Por su parte Maricarmen Mandujano Cerrilla, subsecretaria de Administración y Finanzas, señaló que la labor del personal de apoyo y asistencia a la educación deja huella en la vida de las personas, pues sus integrantes suelen ser el primer apoyo que las y los estudiantes encuentran al llegar a la escuela. Además, su presencia en los planteles constituye un vínculo entre madres y padres de familia y directivos para contribuir al desarrollo de las actividades educativas. De ahí la importancia de reconocer a quienes acumulan entre 10 y 50 años de trayectoria. Jacqueline Servín</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1pPLF4uznDa9MpoqtgcIqb-hvq7gYR81f/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Finanzas</t>
-  </si>
-  <si>
-    <t>Maricarmen Mandujano Cerrilla</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca confirmó que los próximos días jueves 29 y viernes 30 de octubre, la presidenta Claudia Sheimbaun visitará nuevamente el estado de Hidalgo,</t>
-  </si>
-  <si>
-    <t>Esta semana la presidenta Claudia Sheinbaum visitará Hidalgo para entregar apoyos a las personas afectadas por la vaguada monsónica del año pasado.El gobernador Julio Menchaca confirmó que los próximos días jueves 29 y viernes 30 de octubre, la presidenta Claudia Sheimbaun visitará nuevamente el estado de Hidalgo, para entregar apoyos a las familias afectadas por la vaguada monzónica del 2025.La presidenta entregará tarjetas a las familias que perdieron sus viviendas, principalmente de las zonas de la sierra y la huasteca hidalguense, se prevé que visite los municipios de Zapotlán y Villa de Tezontepec, AUDIO JMS</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/18P71W5JHUoZq3ZX035vScQ3xz_II8vef/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Atención a la ciudadanía</t>
   </si>
   <si>
@@ -709,46 +257,327 @@
     <t>Eulalio Larrieta agradece a Edith Balderas  de la Secretaria de Educación Pública.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/15nmf339xkKWwN6d5eEmGspKAgPY8C6E6/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Edith Balderas</t>
   </si>
   <si>
     <t>Eulalio Larrieta agradece a Uriel Ramirez y Jair Martínez de la SEGOBH, porque esta al pendiente de lo que se necesite y los reportes.</t>
   </si>
   <si>
-    <t>Uriel Ramirez y Jair Martínez  de la Secretaría de Gobierno.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1xmwMnkONKfKUPfOKHpBbJTxBDGJKmqmP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Uriel Ramirez, Jair Martínez</t>
-  </si>
-  <si>
     <t>Eulalio Larrieta agradece a Cristian Yahir Castañeda supervisor de la región Pachuca quien nos va atender los reportes que correspondan a la SEMOT</t>
   </si>
   <si>
-    <t>Gracias de las diferentes dependencias, está con nosotros Cristian Yahir Castañeda de Movida Transporte.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1MrVtPKPvvA6aZBzot6N8upa9lC9_ehaK/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Cristian Yahir Castañeda</t>
   </si>
   <si>
     <t>Eulalio Larrieta agradece Paola García y Lic. Sarahi Pineda, por estar atentas a los mensajes de la ciudadanía y por atenderlos.</t>
   </si>
   <si>
-    <t>También está con nosotros como siempre Paola García y Sarahi Pineda de Caasim Muchas Gracias</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1fI3GeCTKKDfCN7OuQ5DFDj28ycGvWfws/view?usp=drivesdk</t>
-  </si>
-  <si>
     <t>Paola García, Sarahi Pineda</t>
+  </si>
+  <si>
+    <t>Izamara Quiroz</t>
+  </si>
+  <si>
+    <t>Vía telefónica a la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar con el tema: Día de muertos</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Entrevista pautada</t>
+  </si>
+  <si>
+    <t>Día De Muertos</t>
+  </si>
+  <si>
+    <t>Vía telefónica a la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar. Secretaria, ¿cómo está? Muy buena tarde.¿Qué tal, Jesús? Muy buena tarde. Muy bien, muchas gracias, gracias por este espacio.Secretaria, cada que platicamos con usted nos da mucho gusto hablar de la cultura de Hidalgo, de nuestra región, del trabajo que está haciendo en la Secretaría que usted encabeza, de verdad que es de mucho gusto, de mucha felicidad. Platíquenos lo que se viene del Día de Muertos, secretaria.Claro que sí, con mucho gusto. Fíjate que desde aquí, desde la Secretaría de Cultura, pues estamos muy contentos porque vamos a tener nuevamente el desfile Fiesta de las Almas, un desfile que convoca a más de 1,000 personas, Jesús. Vamos a hacer un recorrido de aproximadamente 90 minutos, más de 3 kilómetros, 3.4 kilómetros, exactamente, y vamos a partir del centro cultural del Ferrocarril para llegar al reloj de Pachuca.¿Cuándo va a ser este evento, secretaria?
+Sí, quisiera decirte que va a ser el día viernes 30 de octubre en punto de las 5:00 de la tarde. A las 5:00 de la tarde vamos a dar el banderazo y pues de ahí caminar juntos hacia el reloj monumental. Es algo que nos emociona mucho desde aquí, desde desde la Secretaría, porque, como tú sabes, es la celebración más grande pues de los mexicanos, de los hidalguenses y y recordar con con este evento, con este desfile, pues a las almas, a nuestras almas, a nuestros familiares que ya se han ido. Es una manera de de honrarlos, una representación eh pues donde estarán presentes varios municipios y pues también muchas instituciones.Una tradición que tenemos en el estado de Hidalgo, muy marcada, muy nuestra, secretaria, y que esto ha permitido que se lleve a otros países del mundo. Estuvo esta presencia de Hidalgo en Berlín. ¿Cómo les fue, secretaria?Así es, pues algo maravilloso, Jesús, porque es la primera vez que pues llevamos una muestra de nuestra identidad hidalguense, montar un un altar monumental allá en la Embajada de México en en Berlín, pues fue algo muy maravilloso eh visibilizar un un poco de nuestra cultura. En ese sentido eh pues nos acompañó maestras y maestros artesanos de de Huejutla para la elaboración, el presidente municipal también, eh hicimos una muestra también de de los Tenangos, una exposición ahí en la embajada, eh también una muestra de máscaras elaboradas por por madera de acá de la Sierra Baja y nos acompañó también la maestra Cindy, una maestra artesana que trabaja con con fibra del Valle del Mezquital. Eh muy significativo para para nosotros como como estado, te lo decía, porque es la primera vez que que mostramos eh esta riqueza cultural que tenemos. Y por otro lado, no solamente visibilizarlo, sino también abrir espacios para nuestros creadores hidalguenses.Qué emoción me imagino que usted, como secretaria de Cultura, estar en otro país y poder presumir toda la cultura que tenemos en nuestro estado de Hidalgo, secretaria.Así es. Eh tú sabes que bajo el liderazgo de nuestro gobernador Julio Menchaca, pues estamos visibilizando sí aquí en nuestro estado, en todas las regiones, también en otros estados, porque hemos sido invitados en otros estados, pero esta representación de de Hidalgo en en Berlín, pues ha sido muy maravillosa y aparte porque es el inicio de de trabajos que estaremos teniendo. Eh tenemos ya la invitación para dos festivales más eh pues en este eh en aquel bello país. De verdad que fue un momento muymuy significativo para nosotros, pero sobre todo el poder mostrar lo que siempre les digo, esto que nos hace ricos, que es nuestra identidad.¿Va a regresar entonces Hidalgo a Alemania? Eh, fíjate que ya ya tenemos eh pues las conversaciones también con Arenés, que fue quien nos vinculó, la red de investigación de las Américas, con su directora ejecutiva Greta de León y eh ya estamos eh también pues con con la agenda para para regresar a a dos festivales más y pues también que que no sea la la única vez que el Xantolo se visibiliza en en otro país. Se ha hablado también ya de poder montarlo el año siguiente en otro espacio, pero también allá en Alemania.Es un trabajo muy interesante el que viene realizando el gobierno de Hidalgo que encabeza el gobernador Julio Menchaca en el tema cultural y prueba de ello fue la entrega de apoyos al fortalecimiento artístico cultural 2026, que justo se acaba de llevar a cabo hace unas horas. Platíquenos un poco de ello para finalizar, secretaria.Con mucho gusto, Jesús. Fíjate que, efectivamente, hicimos entrega de de apoyos eh del programa eh conocido como PECDA y algo que quiero resaltar y siempre lo digo, tenemos hoy un gobernador que eh se preocupa y fortalece y ha puesto al centro de la transformación a la cultura. Eh desde su llegada, este programa ha incrementado en un 117%, que es algo muy significativo y algo que quiero destacar, Jesús, es que por primera vez se apoyan a espacios culturales independientes. Esto es algo muy muy bueno para la comunidad, porque por un lado se apoyan a los artistas de manera individual, a los colectivos, los proyectos, pero hoy también se les da este impulso a a los espacios, a los foros y y se apoyaron a 12 foros en esta emisión, eh un monto eh muy significativo, 130,000 pesos para cada uno de estos espacios. Eh realmente es un una gran fortaleza para la comunidad artística y cultural.Un gran trabajo el que se lleva a cabo en materia cultural en el estado de Hidalgo. Le agradecemos siempre, secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar, esta información que fortalece lo la información en torno a lo que se realiza en el estado de Hidalgo. Muchas gracias, secretaria.Muchas gracias, Jesús, y hacerles la invitación para que nos acompañen a este gran desfile Fiesta de las Almas, 30 de octubre en punto de las 5:00 de la tarde. Eh si no se han registrado, aún pueden acudir, pueden para para eh visibilizar toda todas las participaciones, pero también pueden acudir con su disfraz de Catrín o de Catrina. Nos va a dar mucho gusto recibirlos. Hasta luego.Al contrario, muchas gracias de poder platicar con usted.
+Gracias, Jesús.Ella es la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YcTR4Apkz5nlGO-A9u1-9WQLvy4qf6mO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Nos vamos hasta el estado de Hidalgo, reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo. Distinguió a 18 profesionales por su dedicación al cuidado de la salud, en reconocimiento a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud. El gobernador de Hidalgo, Julio Menchaca Salazar, encabezó la entrega de medallas y reconocimientos a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. Vamos a escuchar parte de lo que destaca el mandatario de allá del estado de Hidalgo, Julio Menchaca Salazar.</t>
+  </si>
+  <si>
+    <t>Nos vamos hasta el estado de Hidalgo, reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo. Distinguió a 18 profesionales por su dedicación al cuidado de la salud, en reconocimiento a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud. el gobernador de Hidalgo, Julio Menchaca Salazar, encabezó la entrega de medallas y reconocimientos a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. Vamos a escuchar parte de lo que destaca el mandatario de allá del estado de Hidalgo, Julio Menchaca Salazar. Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento, por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber. durante la ceremonia fueron galardonadas y galardonados por su trayectoria y contribuciones al ámbito de la salud Antonio Cristiano Ropeza Montemayor, Armando Robles Guzmán, Armando Cinco Ángeles, Elide Citlaly Vera Ñañez, Elizabeth Gutiérrez Baltazar, Esteban Quevedo Morayla, Guadalupe Ibarra Durán, Gustavo Martín del Campo Olivares e Ignacio Trejo Borboña, al igual de manera de igual manera Irving Azahel Rangel Hern Jos Antonio Madrid G Tagle Jos Francisco Paredes Salazar Jos Luis Garc Le Josefina Guti Castro Luciano Ricardo Mendiola Figueroa No P Gonz Olga Jimena Torres Pe y Rafael Monroy Arias A nombre de las y los galardonados, Guadalupe Ibarra Durán agradeció a las instituciones de salud por permitirle servir con vocación y humanidad al pueblo de Hidalgo, al tiempo que reafirmó la importancia de contar con el acompañamiento de sus seres queridos en esta elección de vida. Gracias a nuestras familias que han soportado y experimentado sacrificios en lo que puntualizó, lo primero es no hacer daño, afirmó la secretaria de Salud, Vanessa Escalante Arroyo, al reconocer la entrega y vocación de servicio profesionalismo del personal médico que día a día trabaja por el bienestar de quienes acuden a los servicios de salud en busca de atención y cuidado. Finalmente, el mandatario estatal recordó que durante su etapa como diputado local trabajó de manera conjunta con el Colegio Médico Hidalguense en una iniciativa de reforma a la legislación con el propósito de brindar certeza jurídica al personal médico mediante el reconocimiento de una excluyente de responsabilidad penal en aquellos casos en los que pese a haberse cumplido los protocolos de atención establecidos, se produjera alguna lesión o pérdida de una vida. Es lo que se destaca desde el estado de Hidalgo en torno a los galardonados médicas y médicos de allá de ese estado.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13M8O54uZGskteflcKmq59p_Qf0M4VvEZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>PGJEH/Bol.077/2026</t>
+  </si>
+  <si>
+    <t>La Agencia de Investigación Criminal detuvo a tres personas en la localidad de Xochitlán de las Flores, aquí en Tula de Allende, por su presunta posesión de narcóticos y armas de fuego. Se trata de dos mujeres y un hombre.</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>La Agencia de Investigación Criminal detuvo a tres personas en la localidad de Xochitlán de las Flores, aquí en Tula de Allende, por su presunta posesión de narcóticos y armas de fuego. Se trata de dos mujeres y un hombre. Durante el operativo, les aseguraron un arma de fuego corta y una larga, esta última con características de fusil tipo AK-47, un cargador abastecido con cartuchos útiles y 149 bolsas con hierba verde, cuya característica de marihuana. Las personas detenidas quedaron a disposición del Ministerio Público que determinará su situación jurídica.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18LztBkWvJ8vhN6OGxSHV553zkGyJQtj-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>También el gobernador de Hidalgo, Julio Menchaca Salazar, destacó el fortalecimiento de las finanzas estatales, con un incremento en la recaudación propia y una reducción de cuarenta y dos por ciento en la deuda pública. De acuerdo con cifras estatales, los ingresos propios pasaron de cuatro mil novecientos dieciséis millones de pesos en dos mil veintiuno, a más de nueve mil seiscientos treinta y seis millones en dos mil veinticinco, lo que representa un aumento del noventa y seis por ciento.</t>
+  </si>
+  <si>
+    <t>Disciplina financiera</t>
+  </si>
+  <si>
+    <t>También el gobernador de Hidalgo, Julio Menchaca Salazar, destacó el fortalecimiento de las finanzas estatales, con un incremento en la recaudación propia y una reducción de cuarenta y dos por ciento en la deuda pública. De acuerdo con cifras estatales, los ingresos propios pasaron de cuatro mil novecientos dieciséis millones de pesos en dos mil veintiuno, a más de nueve mil seiscientos treinta y seis millones en dos mil veinticinco, lo que representa un aumento del noventa y seis por ciento. El mandatario señaló que estos resultados permiten ampliar la capacidad financiera del Estado. La reducción de la deuda corresponde al periodo de dos mil veintidós a dos mil veintiséis.El gobernador Julio Menchaca Salazar enfatizó:"Hidalgo se está distinguiendo a nivel nacional por la recaudación. Acuérdense que en cuatro años superamos el noventa y seis por ciento de la recaudación. Eso implica que estamos recaudando más, que estamos invirtiendo más y que debemos menos, porque hemos también disminuido la deuda en un cuarenta y dos por ciento. Entonces, se está haciendo un gran trabajo por parte de la Secretaría de Hacienda Estatal, tiene el reconocimiento de Hacienda Federal y hoy organismos internacionales, como el evento que se dio el pasado fin de semana, están a la disposición de seguir participando con nosotros, incluso con proyectos que implican inversión, que implican recursos internacionales para ir mejorando y transparentando todo lo que significa la recaudación, no solamente la catastral, sino todo lo que implica la guerra."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11zUHnCb-GuILzWa0r2hNlfvoszRMMq7E/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>HACIENDA</t>
+  </si>
+  <si>
+    <t>Son ya las siete de la mañana con once minutos y vamos con la información porque hay muchas cosas que compartirle en este miércoles, en esta mitad de semana. Miren, el gobernador de Hidalgo, Julio Menchaca Salazar, entregó medallas y reconocimientos a diecinueve médicas y médicos por su trayectoria de aportaciones a la salud en la entidad.</t>
+  </si>
+  <si>
+    <t>Son ya las siete de la mañana con once minutos y vamos con la información porque hay muchas cosas que compartirle en este miércoles, en esta mitad de semana. Miren, el gobernador de Hidalgo, Julio Menchaca Salazar, entregó medallas y reconocimientos a diecinueve médicas y médicos por su trayectoria de aportaciones a la salud en la entidad. Durante la ceremonia destacó su compromiso con las comunidades y las familias hidalguenses.El gobernador Julio Menchaca Salazar señaló:"Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento, por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber."A nombre de las y los galardonados, la doctora Guadalupe Ibarra agradeció a las instituciones de salud y a sus familias por acompañarlos en su labor. La secretaria de Salud, Vanessa Escalante Arroyo, reconoció la vocación y profesionalismo del personal médico. En el acto, Menchaca recordó que cuando fue diputado local, impulsó junto con el Colegio Médico Hidalguense una reforma para dar certeza jurídica a quienes cumplen los protocolos de atención.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HJ7A3sefgEEJhvZre1_aB4z7ATBdnNRe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha Lalo, saludos a todos de parte de tu amigo Gerardo Islas y toda la comunidad de Chavarría, La Calera, El Pedregal, comentando que hoy el «Hoy No Circula»... la realidad es que el gobierno y Semoth quier</t>
+  </si>
+  <si>
+    <t>Negativo</t>
+  </si>
+  <si>
+    <t>Radioescucha  Lalo, saludos a todos de parte de tu amigo Gerardo Islas y toda la comunidad de Chavarría, La Calera, El Pedregal, comentando que hoy el «Hoy No Circula»... la realidad es que el gobierno y Semoth quieren engañar a los hidalguenses. Eso sí yo no lo sé. Lo que sí les digo, que eso del «Hoy No Circula», para mí en lo personal... en lo personal, es una opinión personal, que quede bien claro, no funcionaría porque mucha gente, como se los digo, compraría un vehículo más. Entonces pues como que las cosas no serían iguales</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1euKmzVgTc2TVX_udN065xz_lXoUUJHYe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha Karen Zepeda. «Muy buenos días, licenciado Larrieta, para comentarte que en la colonia Juan C. Doria llevamos una semana sin agua...»</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/135gSO0B6TLpSE1vf3wyxLwDLnYYJ8_Qv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Radioescucha dice: “Hola, muy buenos días, Lalo Larrieta. Disculpe la molestia, pero en Rinconadas de San Francisco, Mineral de la Reforma, tenemos tres días sin agua “</t>
+  </si>
+  <si>
+    <t>Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nNJwVboMYO4G6c3l85tG6G2YuZO4E2Im/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Cultura/Bol.724/2026</t>
+  </si>
+  <si>
+    <t>Danza, música y una ofrenda integral es la jornada cultural gratuita en el Centro de las Artes por el Día de Muertos.</t>
+  </si>
+  <si>
+    <t>Danza, música y una ofrenda integral es la jornada cultural gratuita en el Centro de Artes por el Día de Muertos.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CJgNp9fQZ5-eL1xhOtaGzo1cWjhcF4aG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Neyda Naranjo</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia del Estado de Hidalgo, a través de la Agencia de Investigación Criminal (AIC), detuvo a tres personas en posesión de sustancias con características de narcóticos, así como armas de fuego y cartuchos útiles.</t>
+  </si>
+  <si>
+    <t>La Procuraduría General de Justicia del Estado de Hidalgo, a través de la Agencia de Investigación Criminal (AIC), detuvo a tres personas en posesión de sustancias con características de narcóticos, así como armas de fuego y cartuchos útiles.A los detenidos se les encontró en posesión de 60 bolsas de plástico con una sustancia sólida cristalina de color blanco, un arma de fuego corta y una larga, esta última con características de fusil tipo AK-47, un cargador abastecido con cartuchos útiles y 149 bolsas con hierba verde cuya apariencia es la de la mariguana.Las personas detenidas quedaron a disposición del Ministerio Público, autoridad que determinará su situación jurídica.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1z3RZYQnAcgELT0EWmlgUsBiliIcOt6uP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Vía telefónica Jerusalem Kuri del Campo Directora General del Museo Interactivo El Rehilete con el tema: Noches de Terror. Este 29 de octubre tenemos el concurso de altares. En él hicimos la convocatoria en su momento dirigida a alumnos desde primaria, secundaria, media superior y superior. Ellos van a poner su altar en el Museo El Rehilete.</t>
+  </si>
+  <si>
+    <t>Ahora sí, Jerusalén, ¿cómo estás? Muy buenos días. Hola, hola. Bien, Lalo, gracias a Dios. Saludo con mucho cariño a toda la gente que nos hace favor de escuchar el día de hoy, aquí en tu programa. Perfecto. Pero yo, a ver, yo quiero que me presumas. ¿Son noches de terror? Sí, son noches de terror, pero también les queremos platicar que aquí en el Museo del Rehilete, pues como sabemos y estamos convencidos que no es un lugar solo para visitar, sino que es un lugar donde queremos que siempre despierte la curiosidad de chicos, de grandes, y bueno, pues aquí, amigos, les traemos noticias para este fin de semana. Ah, perfecto. A ver, a mí me interesa, yo soy bien chismoso, bien metiche, en verdad. A ver, ¿qué vamos a tener? En el Dinoparque va a estar sensacional, pero vamos a tener altares, Vamos a estar festejando el Xantolo, Día de Muertos, como lo quieran decir, y nada más en un solo lugar. Sí, en un solo lugar. Ya saben que aquí en el Museo del Reguilete nos encanta siempre la fiesta y preparar cosas increíbles para todos ustedes. Y bueno, esta vez tenemos actividades que integran ciencia, tecnología, arte, cultura, innovación, tradiciones y convivencia familiar. Esto es Lalo, todo lo que va a encerrar este fin de semana Que ustedes están pensando, me quiero disfrazar ¿A dónde voy? ¿Con toda mi familia o con mis amigos? Pues al Museo El Rehilete Pero déjenme les platico y vamos en orden Primero Dios, para este 29 de octubre Tenemos el concurso de altares El concurso de altares que vienen, bueno Vuelven nuestros muertos y vuelve la magia En ello hicimos la convocatoria en su tiempo, en su momento, y bueno, esto va dirigido para alumnos desde la primaria, secundaria, superior, media superior, todos ellos. Y ellos aquí van a poner su altar en el Museo del Rehiletey están todas las actividades. Si ustedes van desde hoy, ya prácticamente están puestos todos los altares de los que se inscribieron del interior del estado. Vamos a tener alrededor de 10 municipios participantes. Y bueno, esto está increíble, Lalo, porque aquí lo que hacemos son sus tradiciones, pero además la intención es ir mucho más allá de la decoración, ¿sí? Antes de construir este altar, los estudiantes investigan, se reúnen. Para nosotros esto es increíble porque lo que también tratamos de fomentar es el trabajo en equipo entre ellos, ¿sí? y que no nada más sea un altar por ponerlo, sino que descubran todo lo que hay detrás, todo lo que es la historia, todo lo que es conectar con los ancestros. Y bueno, el ver a los jóvenes ahí participar de esta manera para nosotros es increíble, es un paso gigantesco el que damos en el Museo del Rehiletepara mantener nuestras tradiciones aquí, sobre todo con esto que es Día de Muertos y de los altares. Esto es muy importante, en verdad, porque se han ido perdiendo nuestras tradiciones. Y si nosotros lo vamos inculcando con los jóvenes, con nuestros hijos, esto lo vamos impulsando y lo vamos a dejar ahí que vaya quedando, pues, en todo lo que nosotros sabemos de dónde venimos, quiénes somos, y creo que es muy importante y hacerlo con Museo del Rehilete, pues nos va a llevar a todo esto a tenerlo más grabado en nosotros cuando nuestros pequeños vayan creciendo. Sí, esto es muy importante porque el dejar en ellos que la cultura también se investiga, se comprende y se crea, y esto al compartirlo con todo el público, bueno, pues nos da esa magia increíble que es lo que tiene que hacer siempre el Museo del Rehilete, porque insisto, no es un lugar solo para visitar, sino es para divertirse, para aprender y para llevarse todos los que van ahí algo en el corazón, una experiencia increíble que les dure para siempre como un buen recuerdo. exactamente como un buen recuerdo y como una buena tradición sí porque lo trasladas a casa con la familia con los amigos y creo que las cosas son más positivas como lo hacíamos desde niños bueno yo ya yo yo jugaba con los picapedras yo les digo no es lo que les decía o sea yo no tengo ningún problema o sea yo pon los huesos de los dinosaurios ah en el altar y con las cosas por el estilo no les platicaba la historia que cuando llegaba el diario a casa pues lo aventaban y me descalabraban Entonces pues yo no ten ning problema en ese aspecto Si ustedes vieran a Lalo de verdad le digo que no diga esas cosas porque está tan joven, tan guapo, todo el rollo aquí, y dice eso, ya se van a imaginar a un señor muy, muy grande. Aunque usted no lo crea, señor Enrique. Bueno, Pedro, Juan, o ustedes que estén en los controles, no lo crean. Pero bueno, aquí lo importante es eso, ¿no? Que tengamos esas tradiciones Yo lo veía en casa con mi madre Que ponía su altar y todo ello Entonces te va quedando ese legado Vamos a poner, por ejemplo ayer Que aparentemente En todas estas experiencias Llegaron los animalitos, los perritos, los peludos, los gatitos Llegaron a los altares Entonces todo este proceso Luego los niños Los niños Y luego ya al final de todo esto Ya es cuando dicen las personas que se accidentaron Es todo un ritual Y si nosotros lo tenemos presente Y si el Museo Rehilete nos lo recuerda Con todos estos jóvenes, pues qué más Sí, tenerlo presente Y siempre nuestros corazones a las personas Que se han adelantado Y bueno, vamos a tener el concurso Y este viernes a las 3 de la tarde Va a ser la premiación Pero además lo muy padre de esto Es que se van a quedar todo el fin de semana Ahí en exposición Para que no solo visites el Museo Rehilete Sino también veas todos estos altares, cómo fueron hechos. Sí, siempre también prevalece aquí la ciencia, Lalo, porque esto fue dedicado a algún científico, a alguna personalidad que ya se adelantó y que, bueno, en honor a ellos, se están haciendo cada quien eligió a alguien, ahí lo descubriremos. Pero además hacen sus tapetes padrísimos. O sea, es una experiencia increíble ir, revivir todo esto en estas fechas tan maravillosas. Y yo les invito a todos los que nos están escuchando que no dejen de ir al Museo del Rehilete a ver esta maravilla de altares que hay. Perfecto, vamos a regresar, vamos a seguir con el programa, pero hoy Jerusalém va a estar con nosotros platicándonos más de todo lo que tenemos. Hacemos la pausa y regresamos en esta mañana y recuerda que asistir al Museo del Rehilete en este fin de semana que estará sensacional, ¿de acuerdo? Hay que ir con toda la familia. Seguimos con Jerusalén Kuri del Campo, está con nosotros en esta mañana del Museo del Rehilete y Dinoparque porque tenemos muchas festividades que están en grande y están sensacionales para que usted visite todo este fin de semana y los días subsecuentes también. ¡Cómo no! ¡Ay, gracias, Lalo! Pues aquí seguimos muy entretenidos viendo cómo se trabaja desde aquí adentro en cabina. Y la verdad que es una experiencia súper padre, así como la que queremos que vivan en el Museo del Rehilete Vamos a recapitular, si les parece. Mañana, primero Dios jueves En esto del concurso de los altares A las 3 de la tarde Va a ser la premiación Y van a estar en exposición Todo el fin de semana Para que no se pierdan nuestras tradiciones A ver, ¿por qué me cambiaste todo el juego? A ver, platícame ¿Qué más vas a tener? Sí, es que son muchas cosas Sí, la verdad que aquí no descansamos Para que ustedes puedan estar divertidos Entretenidos Y en familia o en amigos aquí en el Museo del Rehilete. Vamos, esto es mañana. Sí. Y se quedan ahí en exposición. Después, el viernes, tenemos nuestro tradicional viernes de consejo. Acuérdense que cuando los niños no tienen clases, aquí el Museo del Reguilete les abre las puertas para que ahí los papás estén muy tranquilos de que sus hijos están aprendiendo, divirtiéndose, y además súper, súper cuidaditos. El mensaje va bien para los niños. No son los papás, son los papases. Porque así dicen los niños, ¿no? Para que los papás y las mamás, ahí está, perfecto, para que los papás y las mamás se padrien con los niños al Museo del Rehilete. Pero es súper interesante, de verdad, Lalo, lo que aquí se esmeran todos los que trabajamos aquí en el Museo del Rehilete, porque es el tema cada viernes de consejo, acorde a la época que estamos viviendo, ¿no? Ahorita, en época, en momento, en tradiciones, nos corresponde al México antiguo y vivo. La ciencia ilumina la memoria Aqu todos los ni queremos que aprendan y descubran los s y significados de las ofrendas y del chantolo tambi mientras experimentan con fen relacionados con el color la luz los pigmentos las sombras y la electricidad Entonces aquí todo esto es donde queremos que ellos muestren todo lo que pueden aprender a través de la ciencia y que también la ciencia es la que está presente en nuestra historia, nuestros colores, nuestros materiales, nuestras costumbres y hasta en nuestra manera de recordar. Aquí como hace rato te decía que lo de los alzares iba para personas de niños de primaria, secundaria y también de media superior y superior. Esto va de niños los viernes de consejo de 6 a 14 años y se realiza el viernes, este próximo viernes de 9 a 3 horas. Ahí en el Museo del Rehilete van a estar las inscripciones abiertas hasta ese día también Por si quieren llegar y se deciden a la mera hora Pues esta vez va a tener el plus de los altares Y ellos también todo esto que van a aprender lo van a cerrar haciendo su propio altar A ver, Gerro, también, todo esto de las noches de terror y todo ¿El Museo del Rehilete está en todas sus áreas abiertas? ¿O nada más es un sector el que está abierto funcionando para la noche de terror? Ah, no, pero a las noches de terror, ahí venimos, entonces ya pasamos el 29, el 30. Ah, no, no, pero ahora me explica. ¿Está abierto o está abierto a todos o no está abierto? Las noches de terror son exclusivamente en el Dinoparque. Ah, ok, perfecto. ¿Sí? Y esas noches de terror van a ser, este año les tenemos la noticia de que vamos a hacer tres. Iniciamos en esta nueva administración, bueno, ya nueva, ya son cuatro años en esta administración, Con el gobernador Julio Menchaca Es donde implementamos Estas noches de terror ¿Por qué? Porque bueno, se nos hizo padre la idea De abrir el Dinoparque en la noche Y que vayan con su linterna Que vayan todos disfrazados Y la verdad, la primera vez Hubo muy buena reacción de la gente Pero nos quedamos con ganas de más Nos pidieron otra noche Entonces aumentamos Al siguiente año dos noches de terror Y este año les tenemos la gran noticia de que van a ser tres, el 30, 31 de octubre y 1 de noviembre. Aquí te explico. El museo y el parque, el Dinoparque, están abiertos todo el día, solo que se cierra la taquilla a 5 de la tarde normalmente, y el Dinoparque y el museo a las 7. ¿Qué va a pasar? Que esta vez se abre la taquilla, después de que cierre a las 5 normal del día, A las 6 de la tarde se abre Escuchen bien, amigos, amigas 6 de la tarde se abre Para el Dinoparque exclusivamente Para estas noches de terror Y entonces, aquí va a estar Bueno, increíble Porque ya tenemos Dinosaurios mecatrónicos Mucha gente aún no lo sabe Entonces vayan, conózcanlos Y ahorita en la noche nos lucen Muchísimo más Por todo lo que se están esmerando también quiero decirles los guías que trabajan aquí en el Museo del Rehilete ahorita nos platicas todo eso porque vamos a la pausa ya nos alargamos, vamos a una pausa Jero, seguimos platicando más de todo lo que tenemos precisamente para este fin de semana en el Museo del Rehilete y también Dinoparque todos apúntense para la diversión por favor aquí que ahora ya les vamos a hablar de nuestras super noches de terror en el Dinopark en serio si son de terror mucho, si Ah, bueno, pues entonces, vamos. Y además, mira, es que para cerrar estas actividades especiales de esta temporada, el Dinoparque se transformará en un recorrido nocturno con ambientaciones, personajes y muchas sorpresas. Las Noches de Terror, a todos los que nos están escuchando, ojo, se llevarán a cabo este viernes, sábado y domingo, o sea 30 31 y 1 de noviembre de 6 de la tarde a 9 Muchas personas piensan que nos ha pasado y si quiero aclararlo que a las seis si no llego a las seis entonces ya no llegu No no no Est abierto de seis a nueve. O sea, tú puedes llegar a las seis, seis y media, siete, así. En adelante, hasta las nueve de la noche que se cierra. Y bueno, vamos a tener aquí una entrada general que es de cincuenta pesos por persona y los boletos pueden adquirirse en taquilla el día del evento. Tú llegas, te preparas con tu disfraz, con tu linterna, con todos tus amigos, tus amigas, con la familia, y se lanzan al Dinoparque de ahí del Museo del Rehilete para poder pasar una noche espectacular, una experiencia increíble y diferente sobre todo. Esto es importante. Diferente, diferente, porque de momento queremos buscar algo. ¿A dónde? ¿A dónde? Y si es diferente, pues ya lo hicimos. Y si te van a espantar, pues ya le decimos también En este fin de semana Si en este fin de semana nos vamos a espantar Y nos vamos a espantar de lo lindo En el Dinoparque y el Museo del Rehilete Pues ahí estamos, ¿a poco no? Sí, sí, sí, y a todos los que ya vayan a llegar Medio tarde, bueno, lo más tarde Así para que adquieran sus boletos Es a las ocho, para que tengan todavía Ese recorrido, porque se cierra a las nueve Y todavía puedan una hora Disfrutar de ello Y fíjate que quiero platicarles cómo va a estar esta experiencia, porque contará con cuatro pasajes temáticos diferentes, como el circo del terror, que ya fue todo un éxito en años pasados, y nos lo volvieron a pedir, que esto es con una atmósfera de circo y payasos. ¡Anden! El laboratorio zombie, que recaerá en un espacio invadido por zombies, y también el mundo de Coco, que está inspirado en el color y las tradiciones del Día de Muertos. También vamos a tener otro, que es el Bosque de las Brujas, lleno de misterio y hechicería. ¿Cómo ves, Lalo? Ay, no, hombre, no, está bien. Va a haber diferentes espacios también, amigos, para que puedan sacarse fotografías, ambientaciones especiales a lo largo de este recorrido. Y al último lo que hacemos es rompes Ahí en lo que es el paseo arqueológico Ahí rompemos con una gran verbena Estamos ahí con un DJ, hay baile, hay antojitos Ahí se pueden quedar a ver unas proyecciones Y hacer este momento mágico Para que puedan vivirlo con nosotros en el Museo del Reguilete en el Dinoparque Dije, las brujas, dije, no, si a mis hermanas las tengo encerradas ¡Qué pacho! ¡Qué pacho! Hermanas, ya se van a escapar. Porque no están aquí para pegarle las hermanas, pero sí. Se me van a escapar mis hermanas y se van a ir al Dinopark. Noche de brujas, dicen, pues, ¿cómo? Está bien. Que se disfrace toda la familia. No, ya no es así nada. Prepárense con sus amigos. Saludos de hermanas. Vayan, diviértanse, no olviden su linterna. Lalo, te queremos, por favor, tener ahí presente para que vivas esta experiencia. De todo este gran esfuerzo que hacemos todos los que trabajamos en el Museo del Rehilete, porque ahí van los guías, ¿Sí? Que ellos están preparando también todo esto con nosotros, somos un gran equipo, una gran familia, que que estamos con todo cariño, cada día preparando cosas muy hermosas para ustedes, también modernizando el Museo del Rehilete, tiene ya a partir de esta administración, estos dinosaurios mecatrónicos que han causado sensación, y que no en todos lados están, la verdad que es un privilegio, Muchas cosas que se han venido renovando Y por más que vamos Unos proyectos muy ambiciosos Con todo el apoyo que hemos tenido Del gobernador Julio Menchaca Salazar Así es que vamos adelante con ello No dejen de divertirse Está padrísimo Vengan y encuéntrense con estas noches de terror Gracias Ya aquí apartó su lugar mi hermana Ya me mandó un mensaje Dice ¿Qué pasa? No, está bien, no me paso La verdad que pasó hermana Nada más emocionate Ahí está. Nada más queríamos ver si los estados te escuchan. Ah, no, sí. Perfecto. Vámonos. Son las nueve de la mañana con treinta y un minutos. Vamos a resumen rápidamente en Panorama.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sc3UwJd4sg6ntyF0Iq464eOI5rGkSX0t/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1p9GedDLvB1XhWYbRLhyz65ikgAUqQqu3/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Uriel Ramirez,  Jair Martínez</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14nPg7LVKbC7us9pTkOVkEFza8Cf6D7cC/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cSuSuxO_WhLuRg_U4z-D7vYj1V9WAHY5/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GR_HNPdCPYyzeAMO8Ss_iDcqyAEMLECJ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Saderh/Bol.91/2026</t>
+  </si>
+  <si>
+    <t>Yazmín Leonardo</t>
+  </si>
+  <si>
+    <t>Locutor David Cárdenas destacó la labor de la Secretaría de Agricultura y Desarrollo Rural (Saderh) encabezada por Napoleón González Pérez, enfocada en dotar de herramientas e insumos a los productores del campo de Nopala para hacer más rentable y eficiente su labor. Asimismo, se enfatizó la necesidad de impulsar programas exclusivos para las nuevas generaciones de hijos de campesinos, buscando motivar el relevo generacional ante el abandono que el campo ha sufrido por parte de administraciones anteriores y brindarles mayores oportunidades de desarrollo productivo.</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>Nopala</t>
+  </si>
+  <si>
+    <t>Esto de la mano con lo que le informaba que llevó a cabo la Sader, la Secretaría de Agricultura en Nopala, con los insumos, pues también se va fortaleciendo en este caso, eh facilitar herramientas para hacer más rentable y eficiente el trabajo de la tierra. Cuando la tierra deja de generar productos, deja de generar productos por falta de herramientas, por falta de semillas, por falta de apoyo. En este caso, de lo que estamos hablando es que no solamente es al productor, está bien a su familia, a los hijos de campesinas y campesinos. La tierra es leal y siempre está dispuesta a brindar generosamente los frutos que en su vientre germinan, se procesan y nacen, pero requiere también la participación del ser humano. Por ello es que la Secretaría de Agricultura y Desarrollo Rural llevó a cabo la entrega en las manos de Napoleón González Pérez en esta estrategia que busca facilitar herramientas para hacer más rentable y eficiente el trabajo de la tierra. Escuchemos a Napoleón González.
+(...) De las actividades del campo deben haber oportunidades para los jóvenes y por eso estamos trabajando con el secretario con el director de Agricultura, Sergio Cortés, un programa para el siguiente año en favor de los jóvenes. Un programa exclusivo para jóvenes, hijos de campesinos, porque hay que motivar el campo, la gente, porque tenemos que ver en el relevo generacional que la mayoría de la gente que trabaja el campo son adultos mayores que merecen todo nuestro respeto y como lo decía en un principio, el campo necesita esfuerzo, necesita tiempo y es el ocio, hay que estar ahí y los jóvenes, por esa falta de atención que hubo para el campo, ese abandono que lo tuvieron los gobiernos anteriores se han alejado pero no porque no quieran trabajar el campo, porque el campo no produzca, no es porque no había oportunidades. Hoy tenemos que acercar más oportunidades, como este equipos para que les facilite ese trabajo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10aXvTpWxuH8l7U-F1TIsP_ZoKusdg3eS/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>Sebiso/Bol.702/2026</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso) llevó a cabo una gira de trabajo de dos días por municipios de la Huasteca y la Sierra Alta de Hidalgo, abarcando localidades como Xochiatipan, Huautla, Atlapexco, Huazalingo, Tlanchinol, Tepehuacán de Guerrero y Tianguistengo. Durante esta gira se entregaron 4,325 tarjetas de los programas Bienestar y Desarrollo y Madres Trabajadoras para evitar gastos de traslado a las familias beneficiarias. Asimismo, se distribuyeron paquetes de cacao y azúcar en Huazalingo y Tianguistengo para la elaboración de chocolate con motivo de las próximas festividades tradicionales y del Xantolo.</t>
+  </si>
+  <si>
+    <t>Bienestar</t>
+  </si>
+  <si>
+    <t>Programas Del Pueblo</t>
+  </si>
+  <si>
+    <t>Gracias, Rosa María. Fíjese que también la Sebiso llevó a cabo la entrega de 4,000 apoyos sociales en una gira por la Huasteca y la Sierra Alta de Hidalgo. La Secretaría de Bienestar e Inclusión Social concluyó una gira de trabajo de dos días por diversos municipios de la Huasteca y la Sierra Alta para la entrega directa de apoyos sociales. El despliegue territorial abarcó las localidades de Xochiatipan, Huautla, Atlapexco, Huazalingo, Tlanchinol, así como Chilijapa en Tepehuacán de Guerrero y Santa Mónica en Tianguistengo. En estas demarcaciones se distribuyeron un total de 4,325 tarjetas correspondientes a los programas Bienestar y Desarrollo, Madres Trabajadoras, todo ello con el propósito de evitar gastos de traslado a los beneficiarios. Adicionalmente, la dependencia estatal entregó paquetes de cacao y azúcar en comunidades de Huazalingo y Tianguistengo para la elaboración tradicional de chocolate, todo esto de cara a las próximas festividades, complementando así las acciones y asistencia social en las regiones indígenas del Estado. Ya estaremos comentando en torno al Xantolo porque en nuestros pueblos originarios, pueblos indígenas, la cultura, la tradición es algo constante, presente todos los días y desde luego en esto los apoyos que se entregan en cacao, desde luego en azúcar fortalece el desarrollo también de estos encuentros culturales de esta tradición familiar y recordar también siempre a los seres queridos que adelantaron en el camino.»</t>
+  </si>
+  <si>
+    <t>SEPH/Bol.1949/2026</t>
+  </si>
+  <si>
+    <t>SEPH promueve entornos escolares seguros, inclusivos y libres de violencia</t>
+  </si>
+  <si>
+    <t>Convivencia Escolar</t>
+  </si>
+  <si>
+    <t>Tepeji del Río</t>
+  </si>
+  <si>
+    <t>Y tenemos también información contigo, Rosa María, en torno a la Secretaría de Educación Pública. Vamos contigo, Rosa María, la SEP
+Con la participación de autoridades educativas, instancias gubernamentales y comunidad escolar, la Secretaría de Educación Pública de Hidalgo realizó la novena edición de la feria para la convivencia escolar en la escuela primaria de TEPG del Río, donde se impulsaron acciones preventivas para fortalecer la cultura de paz y promover ambientes escolares seguros. La jornada benefició a 594 estudiantes, 32 figuras educativas y 120 madres y padres de familia, mediante actividades interactivas orientadas a la prevención, la sana convivencia y la participación de niñas y niños en la construcción de entornos seguros</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cAb9Xe65wV7uViri6nx4JI-bIF_iD0OK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>La Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh) anunció un programa enfocado en apoyar a las nuevas generaciones de hijos de campesinos dedicados al sector agropecuario, con el fin de facilitar herramientas que hagan más rentable y eficiente el trabajo de la tierra. Este anuncio se dio durante una reunión en Nopala, donde se entregaron 2,918,088 pesos en insumos agrícolas y pecuarios —como semillas, aves, ganado porcino, herramientas y árboles frutales— a 481 productores de la región. En el evento estuvieron presentes alcaldes de Nopala de Villagrán, Huichapan, Tecozautla y Chapantongo para coordinar acciones en favor del desarrollo rural</t>
+  </si>
+  <si>
+    <t>La Saderh alista programa para jóvenes del campo y entrega 2.9 millones de pesos en insumos agrícolas. Estamos hablando de esta reunión en Nopala. La Secretaría de Agricultura y Desarrollo Rural de Hidalgo diseña un programa enfocado en respaldar a las nuevas generaciones dedicadas al sector agropecuario, particularmente a hijas e hijos de campesinos, así lo informó Napoleón González Pérez. La estrategia busca facilitar herramientas para hacer más rentable y eficiente el trabajo de la tierra. El anuncio se realizó durante la distribución de 2,918,088 pesos en apoyo directo a 481 productoras y productores de Nopala de Villagrán y municipios vecinos. Entre los insumos otorgados destacan semillas de maíz, avena y jitomate, aves de doble propósito, vientres porcinos, molinos picadores, rollos de alambre y plantas frutales como limón persa, manzana yala y nogal. Todo esto en apoyo, desde luego, en soporte para todas todas las personas que trabajan la tierra. Al evento acudieron alcaldes de Nopala de Villagrán, Huichapan, Tecozautla y Chapantongo, reflejando el trabajo coordinado entre los municipios de la región para atender el desarrollo rural</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1AEAa7-kPTotuj8hJEEfJYjgArRHABnVE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Tenemos información de lo que ha acontecido, está sucediendo en este momento y también el día de ayer le daba el adelanto del reconocimiento que hizo el gobernador Julio Menchaca a la trayectoria y vocación del personal médico. El gobernador comentaba el día de ayer en su mensaje en su familia, su hermano Andrés, es médico y evidentemente en la práctica familiar, pues va uno conociendo eh todo el desarrollo de una carrera, de una profesión y desde luego también los retos, el aprendizaje, la capacitación, el estar al día en el tema médico, pues evidentemente hay que estar todos los días eh la disposición del aprendizaje, del desarrollo y también del humanismo de brindar a los pacientes lo mejor de cada eh médica, médico para alcanzar desde luego la salud. En reconocimiento a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud, el gobernador de Hidalgo, Julio Menchaca Salazar, encabezó ayer la entrega de medallas y reconocimiento a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. Escuchemos lo que destacó el gobernador de Hidalgo:
+"Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber".
+De igual manera, Irvyn Asael Rangel Hernández, José Antonio Madrid Gómez, José Francisco Paredes Salazar, José Luis García León, Josefina Gutiérrez Castro, Luciano Ricardo Mendiola, eh son y participaron en estos reconocimientos, les fueron entregados a médicas y médicos cuya labor, reitero, ha contribuido al bienestar de las familias. A nombre de las y los galardonados, Guadalupe Ibarra Durán agradeció a las instituciones de salud por permitirles servir con vocación y humanidad al pueblo de Hidalgo, al tiempo que reafirmó la importancia de contar con el acompañamiento de sus seres queridos en esta elección de vida, dijo, "Gracias a nuestras familias que han soportado y experimentado sacrificios". 
+"Lo primero es no hacer daño", afirmó la secretaria de salud, Vanessa Escalante Arroyo, al reconocer la entrega, la vocación de servicio y profesionalismo del personal médico que día a día trabaja por el bienestar de quienes acuden a los servicios de salud en busca de atención y cuidado. Finalmente, el mandatario estatal recordó que durante su etapa como diputado local, trabajó de manera conjunta con el Colegio Médico Hidalguense en una iniciativa de reforma a la legislación, esto con el propósito de brindar certeza jurídica al personal médico mediante el reconocimiento de una excluyente de responsabilidad penal en aquellos casos en los que, pese a haber cumplido los protocolos de atención establecidos, se produjera alguna lesión o la pérdida de una vida. Parte de lo que se destacó el día de ayer.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nREwZdqLicrAEv1d5qkNspZ-Pk35UilF/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>SSPH/Bol.991/2026</t>
+  </si>
+  <si>
+    <t>La Policía en Hidalgo aseguró 29,000 litros de hidrocarburo y detuvo a una persona en Sempuala. Resulta que hubo un accidente, llegó la policía y detectaron durante la revisión que transportaba cerca de 30,000 litros de combustible»</t>
+  </si>
+  <si>
+    <t>SSPH</t>
+  </si>
+  <si>
+    <t>Combate al huachicol</t>
+  </si>
+  <si>
+    <t>Zempoala</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Wewip_vNhbdl2TJpjGrfPdHACc-Q-wTB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Fueron detenidas tres personas en posesión de narcóticos y armas de fuego, presentados ya están ante el Ministerio Público.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_Fb68Z8rmbTe9v7gisXl7e3eRxtXN59T/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Lleva Sebiso apoyos directos a comunidades de la Huasteca y la sierra</t>
+  </si>
+  <si>
+    <t>Bien, por otra parte, le comento acerca de estos apoyos que se brindan en comunidades de la Huasteca y de la Sierra. El objetivo es seguir llevando beneficios a las y los hidalguenses de diferentes regiones del Estado, así lo puntualizó Ricardo Gómez Moreno, el titular de la Secretaría de Bienestar e Inclusión Social, al realizar una gira de trabajo por comunidades de la Huasteca y de la Sierra Alta. En una jornada de dos días, el funcionario estatal visitó, perdón, las localidades de Xochiatipan, Huautla, Atlapexco y Huazalingo, así como Tlanchinol, la comunidad de Chilijapa, de Tepehuacán de Guerrero y Santa Mónica, en el municipio de Tianguistengo, esto en la Sierra Alta. En estos lugares se entregaron de manera directa las tarjetas de los programas Madres Trabajadoras, Bienestar y Desarrollo, garantizando que los recursos lleguen sin intermediarios a las familias que los necesitan. Con un alcance total de 4,325 apoyos entregados de mano en mano, el despliegue territorial benefició a miles de hogares hidalguenses, 3,590 apoyos asignados a través de Bienestar y Desarrollo y 735 del programa Madres Trabajadoras. Al acercar los apoyos hasta sus municipios, la Secretaría de Bienestar evita que las y los beneficiarios realicen gastos de traslado que afecten su economía familiar, además, claro, de ahorrarles tiempo, lo cual también redunda en recursos económicos, puesto que pueden seguir trabajando. Sobre este despliegue en la región, el titular de la dependencia destacó, Ricardo Gómez Moreno, destacó el compromiso de nuestro gobernador Julio Menchaca se demuestra en el territorio entregando las tarjetas de manera personal, informándoles de manera directa. Este recurso es para apoyar a cubrir sus necesidades y a través de él reafirmamos que seguimos trabajando a diario por quien más lo necesita. Así lo puntualizó Ricardo Gómez Moreno. Aunado a la entrega de las tarjetas de apoyo económico, la Sebiso fortalece su compromiso con la identidad cultural de los pueblos originarios mediante la distribución de paquetes con cacao y azúcar en Cocotla, Huazalingo, eh Cocotla, comunidad de Huazalingo y Santa Mónica, comunidad de Tianguistengo. Este insumo permitirá a las familias elaborar las tradicionales tablillas de chocolate para las próximas festividades. Bueno, ya ya están, ya están en curso estas festividades de de Día de Muertos. Hay personas que llevan pues no solo días, sino incluso meses de preparación para esta celebración de Día de Muertos, sobre todo en la Huasteca con el Xantolo y también pues el cultivo de las flores de Sempoaxúchitl tradicionales en esta época, su olor y su color característico llenan las casas, sobre todo de comunidades en la Sierra y en la Huasteca de Hidalgo. Por supuesto, en muchos otros municipios, incluso en las ciudades como Pachuca, como Tulancingo, también se puede apreciar esta festividad, sin embargo, tiene un sabor peculiar, especial en las comunidades, en los municipios al interior del Estado. Si usted tiene la posibilidad de visitar alguno de estos municipios, bueno, si ya ha acudido sabrá que que vale mucho la pena y si no, de verdad, es algo recomendable visitar los municipios de la entidad en el marco de estas celebraciones.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M2rYregTGEAAT6EYteDAsCZKngvF9FGI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Hidalgo apuesta por el futuro del campo con oportunidades para jóvenes</t>
+  </si>
+  <si>
+    <t>Y le recuerdo un dato que en su momento dio a conocer el Instituto Nacional de Estadística y Geografía, el INEGI, acerca de la Encuesta Nacional Agropecuaria de este instituto: el 82% de los productores del campo tiene 46 o más años, mientras que solo el 18% tiene menos de 45 años. Sin embargo, hay un dato también favorable, hay una mayor preparación entre las personas que sostienen la actividad agropecuaria del país, pues cada vez hay más productores con bachillerato, incluso con educación superior y más aún con educación especializada en tareas del campo, ingenieros agrónomos, entre otras especialidades que van permitiendo o van favoreciendo la tecnificación y una mejor producción del campo. Sin embargo, es un hecho que cada vez menos jóvenes se han interesado en la actividad agropecuaria. Y en este contexto, le comento que con el objetivo de abrir nuevas oportunidades para los jóvenes que trabajan en el campo, el gobierno del Estado trabaja en el diseño de un programa exclusivo para este sector. Así lo informó el secretario de Agricultura y Desarrollo Rural, Napoleón González Pérez. La iniciativa busca acercar herramientas y apoyos que faciliten las labores agropecuarias, particularmente a quienes son hijos de campesinos y conocen de primera mano el esfuerzo, el tiempo y la dedicación que requiere trabajar la tierra. El titular de esta secretaría destacó que impulsar a las nuevas generaciones es fundamental, sobrado, con alternativas que contribuyan a mejorar las condiciones de trabajo, con opciones que faciliten su labor y creando oportunidades que les permitan alcanzar una mejor calidad de vida. El anuncio se realizó durante la entrega de apoyos por 2,918,000 pesos en beneficio directo de 481 productoras y productores de Nopala, de Villagrán y municipios de la región. Los insumos entregados incluyen semillas de maíz, de avena, perdón, de jitomate, aves de doble propósito, rollos de alambre, molinos picadores y vientres porcinos. También se distribuyeron plantas de limón persa, manzana yala y nogal de cáscara de papel para promover la diversificación de cultivos y fortalecer la rentabilidad de las parcelas. Lo más importante, dijo el secretario de Agricultura, lo más importante para nosotros es saber y escuchar lo que la gente trabajadora del campo siente, porque sabemos perfectamente que la verdadera fuerza del Estado reside ahí, con nuestra gente. Hoy tenemos un gobierno del pueblo y para el pueblo, por eso les pido que sigan confiando en la transformación de Hidalgo. Así lo refirió Napoleón González. En la jornada participaron las presidentas municipales de Nopala, Diana Moreno Rea; la presidenta de Huichapan, Yeymi Solís Zavala; de Tecozautla, Marisol Prieto Avendaño; y el presidente municipal de Chapantongo, Eligio Figueroa Chávez, en una muestra de coordinación entre los distintos órdenes de gobierno para impulsar el desarrollo rural. Con el diseño de este nuevo programa y la entrega de apoyos productivos, la Secretaría de Agricultura busca ampliar las oportunidades para las familias del campo y favorecer que las nuevas generaciones cuenten con herramientas para continuar y fortalecer las actividades agropecuarias que se llevan a cabo en la entidad. Y bueno, pues este tipo de diseños de programas buscando justamente interesar a las y los jóvenes en la actividad del campo.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CEo1cHaygPdiufu_qR3769X961oqjGAv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Julio Menchaca, Diana Moreno Rea, Yeymi Solís Zavala, Marisol Prieto Avendaño, Eligio Figueroa Chávez</t>
+  </si>
+  <si>
+    <t>Locutor Jesús Riveros da lectura a comentario de radioescucha que reporta, la falta de suministro de agua potable en el fraccionamiento El Palmar, en la capital del estado de Hidalgo. Ante esta situación, se realizó un llamado de atención a la CAASIM para conocer las causas y la posible solución a esta problemática que afecta a los habitantes de la zona.</t>
+  </si>
+  <si>
+    <t>«Gracias a través de la línea telefónica nos informan que no tienen agua en el fraccionamiento El Palmar, perdón, allá en la capital hidalguense. Así que el llamado para la CAASIM, vamos a preguntar a ver qué qué nos puede señalar al respecto.»</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1R7u05pxcYqz4ue06nVFxpcsR2Gqon4bJ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo</t>
+  </si>
+  <si>
+    <t>Continuamos con información desde la capital del estado y le comparto acerca de este reconocimiento que hace el gobernador del estado a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud. En una ceremonia que encabezara por el mandatario estatal, se hizo la entrega de medallas y reconocimientos a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. En el marco de este reconocimiento, esto es parte de lo que dijo el gobernador Julio Menchaca:
+"Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber".
+Bien, en esta ceremonia fueron galardonadas y galardonados por su trayectoria y contribuciones al ámbito de la salud: Antonio Christian Oropeza Montemayor, Armando Robles Guzmán, Armando Sinco Ángeles, Elide Zitlali Vera Yañez, Elizabeth Gutiérrez Baltazar, Esteban Quevedo Moraila, Guadalupe Ibarra Durán, Gustavo Martín del Campo Olivares e Ignacio Trejo Borbolla. 
+De igual manera, Irving Asael Rangel Hernández, José Antonio Madrid Gómez Tagle, José Francisco Paredes Salazar, José Luis García León, Josefina Gutiérrez Castro, Luciano Ricardo Mendiola Figueroa, Noé Pérez González, Olga Jimena Torres Peón y Rafael Monroy Arias. 
+A nombre de las y los galardonados, Guadalupe Ibarra Durán agradeció a las instituciones de salud por permitirles servir con vocación y humanidad al pueblo de Hidalgo, al tiempo que reafirmó la importancia de contar con el acompañamiento de sus seres queridos en esta elección de vida, "gracias a nuestras familias que han soportado y experimentado sacrificios"puntualizó. 
+"Lo primero es no hacer daño", afirmó la Secretaria de Salud, Vanessa Escalante Arroyo, al reconocer la entrega vocación de servicio y profesionalismo del personal médico que día a día trabaja por el bienestar de quienes acuden a los servicios de salud en busca de atención y cuidado, es decir, lo primero es una atención justamente adecuada, una atención que haga sentir confianza a las personas que acuden por un servicio de salud.
+Al final de esta ceremonia, el gobernador Julio Menchaca recordó que durante su etapa como diputado local trabajó de manera conjunta con el Colegio Médico Hidalguense en una iniciativa de reforma a la legislación con el propósito de brindar certeza jurídica al personal médico mediante el reconocimiento de una excluyente de responsabilidad penal en aquellos casos en los que, pese haberse cumplido los protocolos de atención establecidos, se produjera alguna lesión o la pérdida de una vida. 
+Por supuesto que las médicas y los médicos, como cualquier otro trabajador, requiere de un sustento, más aún, por supuesto, en su caso, de un sustento legal de tener garantías en la realización de su trabajo que es sumamente delicado y por supuesto también que estas garantías se extiendan a las personas que atienden.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T8eU4k-ksM0rDnZkRmMd3Uw7tWksAWLR/view?usp=drivesdk</t>
   </si>
 </sst>
 </file>
@@ -1453,8 +1282,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X33" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
-  <autoFilter ref="A1:X33" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}" name="Tabla5" displayName="Tabla5" ref="A1:X27" tableType="xml" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+  <autoFilter ref="A1:X27" xr:uid="{F82FBE5C-075E-4603-B4C6-498D0CAE0A71}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{9F157467-DCCD-4AA5-A6ED-3B32726AEC51}" uniqueName="Numero" name="#" dataDxfId="23">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Numero" xmlDataType="string"/>
@@ -1850,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312D807-ACA9-4D2F-8621-44E65E11791E}">
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
@@ -1953,160 +1782,176 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D2" s="5"/>
+        <v>46323</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="E2" s="5" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S2" s="5">
-        <v>27</v>
+        <v>464</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
+      <c r="X2" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C3" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E3" s="3" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="3">
+        <v>204</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="3">
-        <v>128</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>15</v>
@@ -2115,134 +1960,134 @@
         <v>16</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S4" s="3">
-        <v>223</v>
+        <v>38</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E5" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S5" s="3">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="W5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>84</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C6" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D6" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E6" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>15</v>
@@ -2251,289 +2096,283 @@
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="R6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" s="3">
+        <v>69</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="W6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S6" s="3">
-        <v>94</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S7" s="3">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-      <c r="W7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D8" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S8" s="3">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-      <c r="W8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D9" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S9" s="3">
+        <v>7</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="C10" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E10" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>113</v>
@@ -2542,77 +2381,83 @@
         <v>114</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S10" s="3">
-        <v>484</v>
+        <v>8</v>
       </c>
       <c r="T10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C11" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D11" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E11" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" s="3">
+        <v>50</v>
+      </c>
+      <c r="T11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S11" s="3">
-        <v>43</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
@@ -2621,44 +2466,46 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E12" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>17</v>
@@ -2670,384 +2517,388 @@
         <v>121</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S12" s="3">
-        <v>242</v>
+        <v>1026</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="W12" s="3"/>
       <c r="X12" s="3" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="R13" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="S13" s="3">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
+      <c r="W13" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="X13" s="3"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E14" s="3" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S14" s="3">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="X14" s="3"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E15" s="3" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S15" s="3">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U15" s="3"/>
-      <c r="V15" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="X15" s="3"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="C16" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D16" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="E16" s="3" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S16" s="3">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="X16" s="3"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C17" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D17" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E17" s="3" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S17" s="3">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="X17" s="3"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="C18" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D18" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E18" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
@@ -3059,134 +2910,126 @@
         <v>16</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>154</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="Q18" s="3"/>
       <c r="R18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S18" s="3">
-        <v>28</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>45</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C19" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="R19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O19" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="S19" s="3">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="T19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-      <c r="W19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="X19" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="C20" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E20" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>15</v>
@@ -3195,132 +3038,138 @@
         <v>16</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S20" s="3">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U20" s="3"/>
-      <c r="V20" s="3" t="s">
-        <v>168</v>
-      </c>
+      <c r="V20" s="3"/>
       <c r="W20" s="3" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
+        <v>11</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="6">
+        <v>46323</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="S21" s="3">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="T21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X21" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="C22" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D22" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E22" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>15</v>
@@ -3329,64 +3178,64 @@
         <v>16</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S22" s="3">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C23" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D23" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E23" s="3" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>15</v>
@@ -3395,61 +3244,61 @@
         <v>16</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S23" s="3">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
-      <c r="W23" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D24" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E24" s="3" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>5</v>
@@ -3461,647 +3310,249 @@
         <v>16</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S24" s="3">
-        <v>47</v>
+        <v>224</v>
       </c>
       <c r="T24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="C25" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D25" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E25" s="3" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="R25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="S25" s="3">
-        <v>54</v>
+        <v>242</v>
       </c>
       <c r="T25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3" t="s">
-        <v>187</v>
-      </c>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D26" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E26" s="3" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="S26" s="3">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
-      <c r="W26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>192</v>
-      </c>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C27" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>46323</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E27" s="3" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S27" s="3">
+        <v>223</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S27" s="3">
-        <v>56</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X27" s="3"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>9</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S28" s="3">
-        <v>84</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="W28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="X28" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>8</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S29" s="3">
-        <v>77</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>4</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S30" s="3">
-        <v>5</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="X30" s="3"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>3</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S31" s="3">
-        <v>3</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="X31" s="3"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>2</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S32" s="3">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="X32" s="3"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>1</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="6">
-        <v>46322</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S33" s="3">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="X33" s="3"/>
+      <c r="X27" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tabla XML.xlsx
+++ b/Tabla XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\ReporteRadio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77A8B8A-109C-4B61-A230-CF6E189CEDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014EA3FA-170C-48DD-BFBD-EABB0D486385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A128845D-2150-4E78-84D7-156E8DB409E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="118">
   <si>
     <t>#</t>
   </si>
@@ -107,21 +107,9 @@
     <t>Opinión</t>
   </si>
   <si>
-    <t>Boletín</t>
-  </si>
-  <si>
     <t>NQ 90.1 FM</t>
   </si>
   <si>
-    <t>Ke Buena 106.7 FM</t>
-  </si>
-  <si>
-    <t>David Cárdenas</t>
-  </si>
-  <si>
-    <t>Noticias 106.7</t>
-  </si>
-  <si>
     <t>Juan Carlos Santamaría</t>
   </si>
   <si>
@@ -155,9 +143,6 @@
     <t>Contenido</t>
   </si>
   <si>
-    <t>Radioescucha</t>
-  </si>
-  <si>
     <t>Gobernador</t>
   </si>
   <si>
@@ -191,60 +176,27 @@
     <t>Enlace Noticias</t>
   </si>
   <si>
-    <t>SSH</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
     <t>Caasim</t>
   </si>
   <si>
-    <t>Abasto De Agua</t>
-  </si>
-  <si>
-    <t>Entrevista</t>
-  </si>
-  <si>
     <t>Positivo</t>
   </si>
   <si>
-    <t>Entrega de reconocimientos</t>
-  </si>
-  <si>
-    <t>PGJEH</t>
-  </si>
-  <si>
     <t>Súper Stéreo 100.5 FM</t>
   </si>
   <si>
-    <t>Jesús González</t>
-  </si>
-  <si>
-    <t>Enfoque Regional Meridiano</t>
-  </si>
-  <si>
-    <t>Hoy no circula</t>
-  </si>
-  <si>
-    <t>SDPEE-OCSAD/Bol.1337/2026</t>
-  </si>
-  <si>
     <t>Christian García</t>
   </si>
   <si>
     <t>Enfoque Regional Matutino</t>
   </si>
   <si>
-    <t>Vanesa Escalante Arroyo</t>
-  </si>
-  <si>
     <t>Acir 92.5 FM</t>
   </si>
   <si>
-    <t>Panorama Informativo</t>
-  </si>
-  <si>
     <t>Eulalio Larrieta</t>
   </si>
   <si>
@@ -260,9 +212,6 @@
     <t>Edith Balderas</t>
   </si>
   <si>
-    <t>Eulalio Larrieta agradece a Uriel Ramirez y Jair Martínez de la SEGOBH, porque esta al pendiente de lo que se necesite y los reportes.</t>
-  </si>
-  <si>
     <t>Eulalio Larrieta agradece a Cristian Yahir Castañeda supervisor de la región Pachuca quien nos va atender los reportes que correspondan a la SEMOT</t>
   </si>
   <si>
@@ -278,9 +227,6 @@
     <t>Izamara Quiroz</t>
   </si>
   <si>
-    <t>Vía telefónica a la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar con el tema: Día de muertos</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
@@ -290,294 +236,180 @@
     <t>Día De Muertos</t>
   </si>
   <si>
-    <t>Vía telefónica a la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar. Secretaria, ¿cómo está? Muy buena tarde.¿Qué tal, Jesús? Muy buena tarde. Muy bien, muchas gracias, gracias por este espacio.Secretaria, cada que platicamos con usted nos da mucho gusto hablar de la cultura de Hidalgo, de nuestra región, del trabajo que está haciendo en la Secretaría que usted encabeza, de verdad que es de mucho gusto, de mucha felicidad. Platíquenos lo que se viene del Día de Muertos, secretaria.Claro que sí, con mucho gusto. Fíjate que desde aquí, desde la Secretaría de Cultura, pues estamos muy contentos porque vamos a tener nuevamente el desfile Fiesta de las Almas, un desfile que convoca a más de 1,000 personas, Jesús. Vamos a hacer un recorrido de aproximadamente 90 minutos, más de 3 kilómetros, 3.4 kilómetros, exactamente, y vamos a partir del centro cultural del Ferrocarril para llegar al reloj de Pachuca.¿Cuándo va a ser este evento, secretaria?
-Sí, quisiera decirte que va a ser el día viernes 30 de octubre en punto de las 5:00 de la tarde. A las 5:00 de la tarde vamos a dar el banderazo y pues de ahí caminar juntos hacia el reloj monumental. Es algo que nos emociona mucho desde aquí, desde desde la Secretaría, porque, como tú sabes, es la celebración más grande pues de los mexicanos, de los hidalguenses y y recordar con con este evento, con este desfile, pues a las almas, a nuestras almas, a nuestros familiares que ya se han ido. Es una manera de de honrarlos, una representación eh pues donde estarán presentes varios municipios y pues también muchas instituciones.Una tradición que tenemos en el estado de Hidalgo, muy marcada, muy nuestra, secretaria, y que esto ha permitido que se lleve a otros países del mundo. Estuvo esta presencia de Hidalgo en Berlín. ¿Cómo les fue, secretaria?Así es, pues algo maravilloso, Jesús, porque es la primera vez que pues llevamos una muestra de nuestra identidad hidalguense, montar un un altar monumental allá en la Embajada de México en en Berlín, pues fue algo muy maravilloso eh visibilizar un un poco de nuestra cultura. En ese sentido eh pues nos acompañó maestras y maestros artesanos de de Huejutla para la elaboración, el presidente municipal también, eh hicimos una muestra también de de los Tenangos, una exposición ahí en la embajada, eh también una muestra de máscaras elaboradas por por madera de acá de la Sierra Baja y nos acompañó también la maestra Cindy, una maestra artesana que trabaja con con fibra del Valle del Mezquital. Eh muy significativo para para nosotros como como estado, te lo decía, porque es la primera vez que que mostramos eh esta riqueza cultural que tenemos. Y por otro lado, no solamente visibilizarlo, sino también abrir espacios para nuestros creadores hidalguenses.Qué emoción me imagino que usted, como secretaria de Cultura, estar en otro país y poder presumir toda la cultura que tenemos en nuestro estado de Hidalgo, secretaria.Así es. Eh tú sabes que bajo el liderazgo de nuestro gobernador Julio Menchaca, pues estamos visibilizando sí aquí en nuestro estado, en todas las regiones, también en otros estados, porque hemos sido invitados en otros estados, pero esta representación de de Hidalgo en en Berlín, pues ha sido muy maravillosa y aparte porque es el inicio de de trabajos que estaremos teniendo. Eh tenemos ya la invitación para dos festivales más eh pues en este eh en aquel bello país. De verdad que fue un momento muymuy significativo para nosotros, pero sobre todo el poder mostrar lo que siempre les digo, esto que nos hace ricos, que es nuestra identidad.¿Va a regresar entonces Hidalgo a Alemania? Eh, fíjate que ya ya tenemos eh pues las conversaciones también con Arenés, que fue quien nos vinculó, la red de investigación de las Américas, con su directora ejecutiva Greta de León y eh ya estamos eh también pues con con la agenda para para regresar a a dos festivales más y pues también que que no sea la la única vez que el Xantolo se visibiliza en en otro país. Se ha hablado también ya de poder montarlo el año siguiente en otro espacio, pero también allá en Alemania.Es un trabajo muy interesante el que viene realizando el gobierno de Hidalgo que encabeza el gobernador Julio Menchaca en el tema cultural y prueba de ello fue la entrega de apoyos al fortalecimiento artístico cultural 2026, que justo se acaba de llevar a cabo hace unas horas. Platíquenos un poco de ello para finalizar, secretaria.Con mucho gusto, Jesús. Fíjate que, efectivamente, hicimos entrega de de apoyos eh del programa eh conocido como PECDA y algo que quiero resaltar y siempre lo digo, tenemos hoy un gobernador que eh se preocupa y fortalece y ha puesto al centro de la transformación a la cultura. Eh desde su llegada, este programa ha incrementado en un 117%, que es algo muy significativo y algo que quiero destacar, Jesús, es que por primera vez se apoyan a espacios culturales independientes. Esto es algo muy muy bueno para la comunidad, porque por un lado se apoyan a los artistas de manera individual, a los colectivos, los proyectos, pero hoy también se les da este impulso a a los espacios, a los foros y y se apoyaron a 12 foros en esta emisión, eh un monto eh muy significativo, 130,000 pesos para cada uno de estos espacios. Eh realmente es un una gran fortaleza para la comunidad artística y cultural.Un gran trabajo el que se lleva a cabo en materia cultural en el estado de Hidalgo. Le agradecemos siempre, secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar, esta información que fortalece lo la información en torno a lo que se realiza en el estado de Hidalgo. Muchas gracias, secretaria.Muchas gracias, Jesús, y hacerles la invitación para que nos acompañen a este gran desfile Fiesta de las Almas, 30 de octubre en punto de las 5:00 de la tarde. Eh si no se han registrado, aún pueden acudir, pueden para para eh visibilizar toda todas las participaciones, pero también pueden acudir con su disfraz de Catrín o de Catrina. Nos va a dar mucho gusto recibirlos. Hasta luego.Al contrario, muchas gracias de poder platicar con usted.
-Gracias, Jesús.Ella es la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1YcTR4Apkz5nlGO-A9u1-9WQLvy4qf6mO/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Nos vamos hasta el estado de Hidalgo, reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo. Distinguió a 18 profesionales por su dedicación al cuidado de la salud, en reconocimiento a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud. El gobernador de Hidalgo, Julio Menchaca Salazar, encabezó la entrega de medallas y reconocimientos a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. Vamos a escuchar parte de lo que destaca el mandatario de allá del estado de Hidalgo, Julio Menchaca Salazar.</t>
-  </si>
-  <si>
-    <t>Nos vamos hasta el estado de Hidalgo, reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo. Distinguió a 18 profesionales por su dedicación al cuidado de la salud, en reconocimiento a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud. el gobernador de Hidalgo, Julio Menchaca Salazar, encabezó la entrega de medallas y reconocimientos a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. Vamos a escuchar parte de lo que destaca el mandatario de allá del estado de Hidalgo, Julio Menchaca Salazar. Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento, por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber. durante la ceremonia fueron galardonadas y galardonados por su trayectoria y contribuciones al ámbito de la salud Antonio Cristiano Ropeza Montemayor, Armando Robles Guzmán, Armando Cinco Ángeles, Elide Citlaly Vera Ñañez, Elizabeth Gutiérrez Baltazar, Esteban Quevedo Morayla, Guadalupe Ibarra Durán, Gustavo Martín del Campo Olivares e Ignacio Trejo Borboña, al igual de manera de igual manera Irving Azahel Rangel Hern Jos Antonio Madrid G Tagle Jos Francisco Paredes Salazar Jos Luis Garc Le Josefina Guti Castro Luciano Ricardo Mendiola Figueroa No P Gonz Olga Jimena Torres Pe y Rafael Monroy Arias A nombre de las y los galardonados, Guadalupe Ibarra Durán agradeció a las instituciones de salud por permitirle servir con vocación y humanidad al pueblo de Hidalgo, al tiempo que reafirmó la importancia de contar con el acompañamiento de sus seres queridos en esta elección de vida. Gracias a nuestras familias que han soportado y experimentado sacrificios en lo que puntualizó, lo primero es no hacer daño, afirmó la secretaria de Salud, Vanessa Escalante Arroyo, al reconocer la entrega y vocación de servicio profesionalismo del personal médico que día a día trabaja por el bienestar de quienes acuden a los servicios de salud en busca de atención y cuidado. Finalmente, el mandatario estatal recordó que durante su etapa como diputado local trabajó de manera conjunta con el Colegio Médico Hidalguense en una iniciativa de reforma a la legislación con el propósito de brindar certeza jurídica al personal médico mediante el reconocimiento de una excluyente de responsabilidad penal en aquellos casos en los que pese a haberse cumplido los protocolos de atención establecidos, se produjera alguna lesión o pérdida de una vida. Es lo que se destaca desde el estado de Hidalgo en torno a los galardonados médicas y médicos de allá de ese estado.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/13M8O54uZGskteflcKmq59p_Qf0M4VvEZ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>PGJEH/Bol.077/2026</t>
-  </si>
-  <si>
-    <t>La Agencia de Investigación Criminal detuvo a tres personas en la localidad de Xochitlán de las Flores, aquí en Tula de Allende, por su presunta posesión de narcóticos y armas de fuego. Se trata de dos mujeres y un hombre.</t>
-  </si>
-  <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>La Agencia de Investigación Criminal detuvo a tres personas en la localidad de Xochitlán de las Flores, aquí en Tula de Allende, por su presunta posesión de narcóticos y armas de fuego. Se trata de dos mujeres y un hombre. Durante el operativo, les aseguraron un arma de fuego corta y una larga, esta última con características de fusil tipo AK-47, un cargador abastecido con cartuchos útiles y 149 bolsas con hierba verde, cuya característica de marihuana. Las personas detenidas quedaron a disposición del Ministerio Público que determinará su situación jurídica.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/18LztBkWvJ8vhN6OGxSHV553zkGyJQtj-/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>También el gobernador de Hidalgo, Julio Menchaca Salazar, destacó el fortalecimiento de las finanzas estatales, con un incremento en la recaudación propia y una reducción de cuarenta y dos por ciento en la deuda pública. De acuerdo con cifras estatales, los ingresos propios pasaron de cuatro mil novecientos dieciséis millones de pesos en dos mil veintiuno, a más de nueve mil seiscientos treinta y seis millones en dos mil veinticinco, lo que representa un aumento del noventa y seis por ciento.</t>
-  </si>
-  <si>
-    <t>Disciplina financiera</t>
-  </si>
-  <si>
-    <t>También el gobernador de Hidalgo, Julio Menchaca Salazar, destacó el fortalecimiento de las finanzas estatales, con un incremento en la recaudación propia y una reducción de cuarenta y dos por ciento en la deuda pública. De acuerdo con cifras estatales, los ingresos propios pasaron de cuatro mil novecientos dieciséis millones de pesos en dos mil veintiuno, a más de nueve mil seiscientos treinta y seis millones en dos mil veinticinco, lo que representa un aumento del noventa y seis por ciento. El mandatario señaló que estos resultados permiten ampliar la capacidad financiera del Estado. La reducción de la deuda corresponde al periodo de dos mil veintidós a dos mil veintiséis.El gobernador Julio Menchaca Salazar enfatizó:"Hidalgo se está distinguiendo a nivel nacional por la recaudación. Acuérdense que en cuatro años superamos el noventa y seis por ciento de la recaudación. Eso implica que estamos recaudando más, que estamos invirtiendo más y que debemos menos, porque hemos también disminuido la deuda en un cuarenta y dos por ciento. Entonces, se está haciendo un gran trabajo por parte de la Secretaría de Hacienda Estatal, tiene el reconocimiento de Hacienda Federal y hoy organismos internacionales, como el evento que se dio el pasado fin de semana, están a la disposición de seguir participando con nosotros, incluso con proyectos que implican inversión, que implican recursos internacionales para ir mejorando y transparentando todo lo que significa la recaudación, no solamente la catastral, sino todo lo que implica la guerra."</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/11zUHnCb-GuILzWa0r2hNlfvoszRMMq7E/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>HACIENDA</t>
-  </si>
-  <si>
-    <t>Son ya las siete de la mañana con once minutos y vamos con la información porque hay muchas cosas que compartirle en este miércoles, en esta mitad de semana. Miren, el gobernador de Hidalgo, Julio Menchaca Salazar, entregó medallas y reconocimientos a diecinueve médicas y médicos por su trayectoria de aportaciones a la salud en la entidad.</t>
-  </si>
-  <si>
-    <t>Son ya las siete de la mañana con once minutos y vamos con la información porque hay muchas cosas que compartirle en este miércoles, en esta mitad de semana. Miren, el gobernador de Hidalgo, Julio Menchaca Salazar, entregó medallas y reconocimientos a diecinueve médicas y médicos por su trayectoria de aportaciones a la salud en la entidad. Durante la ceremonia destacó su compromiso con las comunidades y las familias hidalguenses.El gobernador Julio Menchaca Salazar señaló:"Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento, por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber."A nombre de las y los galardonados, la doctora Guadalupe Ibarra agradeció a las instituciones de salud y a sus familias por acompañarlos en su labor. La secretaria de Salud, Vanessa Escalante Arroyo, reconoció la vocación y profesionalismo del personal médico. En el acto, Menchaca recordó que cuando fue diputado local, impulsó junto con el Colegio Médico Hidalguense una reforma para dar certeza jurídica a quienes cumplen los protocolos de atención.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1HJ7A3sefgEEJhvZre1_aB4z7ATBdnNRe/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Radioescucha Lalo, saludos a todos de parte de tu amigo Gerardo Islas y toda la comunidad de Chavarría, La Calera, El Pedregal, comentando que hoy el «Hoy No Circula»... la realidad es que el gobierno y Semoth quier</t>
-  </si>
-  <si>
-    <t>Negativo</t>
-  </si>
-  <si>
-    <t>Radioescucha  Lalo, saludos a todos de parte de tu amigo Gerardo Islas y toda la comunidad de Chavarría, La Calera, El Pedregal, comentando que hoy el «Hoy No Circula»... la realidad es que el gobierno y Semoth quieren engañar a los hidalguenses. Eso sí yo no lo sé. Lo que sí les digo, que eso del «Hoy No Circula», para mí en lo personal... en lo personal, es una opinión personal, que quede bien claro, no funcionaría porque mucha gente, como se los digo, compraría un vehículo más. Entonces pues como que las cosas no serían iguales</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1euKmzVgTc2TVX_udN065xz_lXoUUJHYe/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Radioescucha Karen Zepeda. «Muy buenos días, licenciado Larrieta, para comentarte que en la colonia Juan C. Doria llevamos una semana sin agua...»</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/135gSO0B6TLpSE1vf3wyxLwDLnYYJ8_Qv/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Radioescucha dice: “Hola, muy buenos días, Lalo Larrieta. Disculpe la molestia, pero en Rinconadas de San Francisco, Mineral de la Reforma, tenemos tres días sin agua “</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nNJwVboMYO4G6c3l85tG6G2YuZO4E2Im/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Cultura/Bol.724/2026</t>
-  </si>
-  <si>
-    <t>Danza, música y una ofrenda integral es la jornada cultural gratuita en el Centro de las Artes por el Día de Muertos.</t>
-  </si>
-  <si>
-    <t>Danza, música y una ofrenda integral es la jornada cultural gratuita en el Centro de Artes por el Día de Muertos.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CJgNp9fQZ5-eL1xhOtaGzo1cWjhcF4aG/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Neyda Naranjo</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia del Estado de Hidalgo, a través de la Agencia de Investigación Criminal (AIC), detuvo a tres personas en posesión de sustancias con características de narcóticos, así como armas de fuego y cartuchos útiles.</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia del Estado de Hidalgo, a través de la Agencia de Investigación Criminal (AIC), detuvo a tres personas en posesión de sustancias con características de narcóticos, así como armas de fuego y cartuchos útiles.A los detenidos se les encontró en posesión de 60 bolsas de plástico con una sustancia sólida cristalina de color blanco, un arma de fuego corta y una larga, esta última con características de fusil tipo AK-47, un cargador abastecido con cartuchos útiles y 149 bolsas con hierba verde cuya apariencia es la de la mariguana.Las personas detenidas quedaron a disposición del Ministerio Público, autoridad que determinará su situación jurídica.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1z3RZYQnAcgELT0EWmlgUsBiliIcOt6uP/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Vía telefónica Jerusalem Kuri del Campo Directora General del Museo Interactivo El Rehilete con el tema: Noches de Terror. Este 29 de octubre tenemos el concurso de altares. En él hicimos la convocatoria en su momento dirigida a alumnos desde primaria, secundaria, media superior y superior. Ellos van a poner su altar en el Museo El Rehilete.</t>
-  </si>
-  <si>
-    <t>Ahora sí, Jerusalén, ¿cómo estás? Muy buenos días. Hola, hola. Bien, Lalo, gracias a Dios. Saludo con mucho cariño a toda la gente que nos hace favor de escuchar el día de hoy, aquí en tu programa. Perfecto. Pero yo, a ver, yo quiero que me presumas. ¿Son noches de terror? Sí, son noches de terror, pero también les queremos platicar que aquí en el Museo del Rehilete, pues como sabemos y estamos convencidos que no es un lugar solo para visitar, sino que es un lugar donde queremos que siempre despierte la curiosidad de chicos, de grandes, y bueno, pues aquí, amigos, les traemos noticias para este fin de semana. Ah, perfecto. A ver, a mí me interesa, yo soy bien chismoso, bien metiche, en verdad. A ver, ¿qué vamos a tener? En el Dinoparque va a estar sensacional, pero vamos a tener altares, Vamos a estar festejando el Xantolo, Día de Muertos, como lo quieran decir, y nada más en un solo lugar. Sí, en un solo lugar. Ya saben que aquí en el Museo del Reguilete nos encanta siempre la fiesta y preparar cosas increíbles para todos ustedes. Y bueno, esta vez tenemos actividades que integran ciencia, tecnología, arte, cultura, innovación, tradiciones y convivencia familiar. Esto es Lalo, todo lo que va a encerrar este fin de semana Que ustedes están pensando, me quiero disfrazar ¿A dónde voy? ¿Con toda mi familia o con mis amigos? Pues al Museo El Rehilete Pero déjenme les platico y vamos en orden Primero Dios, para este 29 de octubre Tenemos el concurso de altares El concurso de altares que vienen, bueno Vuelven nuestros muertos y vuelve la magia En ello hicimos la convocatoria en su tiempo, en su momento, y bueno, esto va dirigido para alumnos desde la primaria, secundaria, superior, media superior, todos ellos. Y ellos aquí van a poner su altar en el Museo del Rehiletey están todas las actividades. Si ustedes van desde hoy, ya prácticamente están puestos todos los altares de los que se inscribieron del interior del estado. Vamos a tener alrededor de 10 municipios participantes. Y bueno, esto está increíble, Lalo, porque aquí lo que hacemos son sus tradiciones, pero además la intención es ir mucho más allá de la decoración, ¿sí? Antes de construir este altar, los estudiantes investigan, se reúnen. Para nosotros esto es increíble porque lo que también tratamos de fomentar es el trabajo en equipo entre ellos, ¿sí? y que no nada más sea un altar por ponerlo, sino que descubran todo lo que hay detrás, todo lo que es la historia, todo lo que es conectar con los ancestros. Y bueno, el ver a los jóvenes ahí participar de esta manera para nosotros es increíble, es un paso gigantesco el que damos en el Museo del Rehiletepara mantener nuestras tradiciones aquí, sobre todo con esto que es Día de Muertos y de los altares. Esto es muy importante, en verdad, porque se han ido perdiendo nuestras tradiciones. Y si nosotros lo vamos inculcando con los jóvenes, con nuestros hijos, esto lo vamos impulsando y lo vamos a dejar ahí que vaya quedando, pues, en todo lo que nosotros sabemos de dónde venimos, quiénes somos, y creo que es muy importante y hacerlo con Museo del Rehilete, pues nos va a llevar a todo esto a tenerlo más grabado en nosotros cuando nuestros pequeños vayan creciendo. Sí, esto es muy importante porque el dejar en ellos que la cultura también se investiga, se comprende y se crea, y esto al compartirlo con todo el público, bueno, pues nos da esa magia increíble que es lo que tiene que hacer siempre el Museo del Rehilete, porque insisto, no es un lugar solo para visitar, sino es para divertirse, para aprender y para llevarse todos los que van ahí algo en el corazón, una experiencia increíble que les dure para siempre como un buen recuerdo. exactamente como un buen recuerdo y como una buena tradición sí porque lo trasladas a casa con la familia con los amigos y creo que las cosas son más positivas como lo hacíamos desde niños bueno yo ya yo yo jugaba con los picapedras yo les digo no es lo que les decía o sea yo no tengo ningún problema o sea yo pon los huesos de los dinosaurios ah en el altar y con las cosas por el estilo no les platicaba la historia que cuando llegaba el diario a casa pues lo aventaban y me descalabraban Entonces pues yo no ten ning problema en ese aspecto Si ustedes vieran a Lalo de verdad le digo que no diga esas cosas porque está tan joven, tan guapo, todo el rollo aquí, y dice eso, ya se van a imaginar a un señor muy, muy grande. Aunque usted no lo crea, señor Enrique. Bueno, Pedro, Juan, o ustedes que estén en los controles, no lo crean. Pero bueno, aquí lo importante es eso, ¿no? Que tengamos esas tradiciones Yo lo veía en casa con mi madre Que ponía su altar y todo ello Entonces te va quedando ese legado Vamos a poner, por ejemplo ayer Que aparentemente En todas estas experiencias Llegaron los animalitos, los perritos, los peludos, los gatitos Llegaron a los altares Entonces todo este proceso Luego los niños Los niños Y luego ya al final de todo esto Ya es cuando dicen las personas que se accidentaron Es todo un ritual Y si nosotros lo tenemos presente Y si el Museo Rehilete nos lo recuerda Con todos estos jóvenes, pues qué más Sí, tenerlo presente Y siempre nuestros corazones a las personas Que se han adelantado Y bueno, vamos a tener el concurso Y este viernes a las 3 de la tarde Va a ser la premiación Pero además lo muy padre de esto Es que se van a quedar todo el fin de semana Ahí en exposición Para que no solo visites el Museo Rehilete Sino también veas todos estos altares, cómo fueron hechos. Sí, siempre también prevalece aquí la ciencia, Lalo, porque esto fue dedicado a algún científico, a alguna personalidad que ya se adelantó y que, bueno, en honor a ellos, se están haciendo cada quien eligió a alguien, ahí lo descubriremos. Pero además hacen sus tapetes padrísimos. O sea, es una experiencia increíble ir, revivir todo esto en estas fechas tan maravillosas. Y yo les invito a todos los que nos están escuchando que no dejen de ir al Museo del Rehilete a ver esta maravilla de altares que hay. Perfecto, vamos a regresar, vamos a seguir con el programa, pero hoy Jerusalém va a estar con nosotros platicándonos más de todo lo que tenemos. Hacemos la pausa y regresamos en esta mañana y recuerda que asistir al Museo del Rehilete en este fin de semana que estará sensacional, ¿de acuerdo? Hay que ir con toda la familia. Seguimos con Jerusalén Kuri del Campo, está con nosotros en esta mañana del Museo del Rehilete y Dinoparque porque tenemos muchas festividades que están en grande y están sensacionales para que usted visite todo este fin de semana y los días subsecuentes también. ¡Cómo no! ¡Ay, gracias, Lalo! Pues aquí seguimos muy entretenidos viendo cómo se trabaja desde aquí adentro en cabina. Y la verdad que es una experiencia súper padre, así como la que queremos que vivan en el Museo del Rehilete Vamos a recapitular, si les parece. Mañana, primero Dios jueves En esto del concurso de los altares A las 3 de la tarde Va a ser la premiación Y van a estar en exposición Todo el fin de semana Para que no se pierdan nuestras tradiciones A ver, ¿por qué me cambiaste todo el juego? A ver, platícame ¿Qué más vas a tener? Sí, es que son muchas cosas Sí, la verdad que aquí no descansamos Para que ustedes puedan estar divertidos Entretenidos Y en familia o en amigos aquí en el Museo del Rehilete. Vamos, esto es mañana. Sí. Y se quedan ahí en exposición. Después, el viernes, tenemos nuestro tradicional viernes de consejo. Acuérdense que cuando los niños no tienen clases, aquí el Museo del Reguilete les abre las puertas para que ahí los papás estén muy tranquilos de que sus hijos están aprendiendo, divirtiéndose, y además súper, súper cuidaditos. El mensaje va bien para los niños. No son los papás, son los papases. Porque así dicen los niños, ¿no? Para que los papás y las mamás, ahí está, perfecto, para que los papás y las mamás se padrien con los niños al Museo del Rehilete. Pero es súper interesante, de verdad, Lalo, lo que aquí se esmeran todos los que trabajamos aquí en el Museo del Rehilete, porque es el tema cada viernes de consejo, acorde a la época que estamos viviendo, ¿no? Ahorita, en época, en momento, en tradiciones, nos corresponde al México antiguo y vivo. La ciencia ilumina la memoria Aqu todos los ni queremos que aprendan y descubran los s y significados de las ofrendas y del chantolo tambi mientras experimentan con fen relacionados con el color la luz los pigmentos las sombras y la electricidad Entonces aquí todo esto es donde queremos que ellos muestren todo lo que pueden aprender a través de la ciencia y que también la ciencia es la que está presente en nuestra historia, nuestros colores, nuestros materiales, nuestras costumbres y hasta en nuestra manera de recordar. Aquí como hace rato te decía que lo de los alzares iba para personas de niños de primaria, secundaria y también de media superior y superior. Esto va de niños los viernes de consejo de 6 a 14 años y se realiza el viernes, este próximo viernes de 9 a 3 horas. Ahí en el Museo del Rehilete van a estar las inscripciones abiertas hasta ese día también Por si quieren llegar y se deciden a la mera hora Pues esta vez va a tener el plus de los altares Y ellos también todo esto que van a aprender lo van a cerrar haciendo su propio altar A ver, Gerro, también, todo esto de las noches de terror y todo ¿El Museo del Rehilete está en todas sus áreas abiertas? ¿O nada más es un sector el que está abierto funcionando para la noche de terror? Ah, no, pero a las noches de terror, ahí venimos, entonces ya pasamos el 29, el 30. Ah, no, no, pero ahora me explica. ¿Está abierto o está abierto a todos o no está abierto? Las noches de terror son exclusivamente en el Dinoparque. Ah, ok, perfecto. ¿Sí? Y esas noches de terror van a ser, este año les tenemos la noticia de que vamos a hacer tres. Iniciamos en esta nueva administración, bueno, ya nueva, ya son cuatro años en esta administración, Con el gobernador Julio Menchaca Es donde implementamos Estas noches de terror ¿Por qué? Porque bueno, se nos hizo padre la idea De abrir el Dinoparque en la noche Y que vayan con su linterna Que vayan todos disfrazados Y la verdad, la primera vez Hubo muy buena reacción de la gente Pero nos quedamos con ganas de más Nos pidieron otra noche Entonces aumentamos Al siguiente año dos noches de terror Y este año les tenemos la gran noticia de que van a ser tres, el 30, 31 de octubre y 1 de noviembre. Aquí te explico. El museo y el parque, el Dinoparque, están abiertos todo el día, solo que se cierra la taquilla a 5 de la tarde normalmente, y el Dinoparque y el museo a las 7. ¿Qué va a pasar? Que esta vez se abre la taquilla, después de que cierre a las 5 normal del día, A las 6 de la tarde se abre Escuchen bien, amigos, amigas 6 de la tarde se abre Para el Dinoparque exclusivamente Para estas noches de terror Y entonces, aquí va a estar Bueno, increíble Porque ya tenemos Dinosaurios mecatrónicos Mucha gente aún no lo sabe Entonces vayan, conózcanlos Y ahorita en la noche nos lucen Muchísimo más Por todo lo que se están esmerando también quiero decirles los guías que trabajan aquí en el Museo del Rehilete ahorita nos platicas todo eso porque vamos a la pausa ya nos alargamos, vamos a una pausa Jero, seguimos platicando más de todo lo que tenemos precisamente para este fin de semana en el Museo del Rehilete y también Dinoparque todos apúntense para la diversión por favor aquí que ahora ya les vamos a hablar de nuestras super noches de terror en el Dinopark en serio si son de terror mucho, si Ah, bueno, pues entonces, vamos. Y además, mira, es que para cerrar estas actividades especiales de esta temporada, el Dinoparque se transformará en un recorrido nocturno con ambientaciones, personajes y muchas sorpresas. Las Noches de Terror, a todos los que nos están escuchando, ojo, se llevarán a cabo este viernes, sábado y domingo, o sea 30 31 y 1 de noviembre de 6 de la tarde a 9 Muchas personas piensan que nos ha pasado y si quiero aclararlo que a las seis si no llego a las seis entonces ya no llegu No no no Est abierto de seis a nueve. O sea, tú puedes llegar a las seis, seis y media, siete, así. En adelante, hasta las nueve de la noche que se cierra. Y bueno, vamos a tener aquí una entrada general que es de cincuenta pesos por persona y los boletos pueden adquirirse en taquilla el día del evento. Tú llegas, te preparas con tu disfraz, con tu linterna, con todos tus amigos, tus amigas, con la familia, y se lanzan al Dinoparque de ahí del Museo del Rehilete para poder pasar una noche espectacular, una experiencia increíble y diferente sobre todo. Esto es importante. Diferente, diferente, porque de momento queremos buscar algo. ¿A dónde? ¿A dónde? Y si es diferente, pues ya lo hicimos. Y si te van a espantar, pues ya le decimos también En este fin de semana Si en este fin de semana nos vamos a espantar Y nos vamos a espantar de lo lindo En el Dinoparque y el Museo del Rehilete Pues ahí estamos, ¿a poco no? Sí, sí, sí, y a todos los que ya vayan a llegar Medio tarde, bueno, lo más tarde Así para que adquieran sus boletos Es a las ocho, para que tengan todavía Ese recorrido, porque se cierra a las nueve Y todavía puedan una hora Disfrutar de ello Y fíjate que quiero platicarles cómo va a estar esta experiencia, porque contará con cuatro pasajes temáticos diferentes, como el circo del terror, que ya fue todo un éxito en años pasados, y nos lo volvieron a pedir, que esto es con una atmósfera de circo y payasos. ¡Anden! El laboratorio zombie, que recaerá en un espacio invadido por zombies, y también el mundo de Coco, que está inspirado en el color y las tradiciones del Día de Muertos. También vamos a tener otro, que es el Bosque de las Brujas, lleno de misterio y hechicería. ¿Cómo ves, Lalo? Ay, no, hombre, no, está bien. Va a haber diferentes espacios también, amigos, para que puedan sacarse fotografías, ambientaciones especiales a lo largo de este recorrido. Y al último lo que hacemos es rompes Ahí en lo que es el paseo arqueológico Ahí rompemos con una gran verbena Estamos ahí con un DJ, hay baile, hay antojitos Ahí se pueden quedar a ver unas proyecciones Y hacer este momento mágico Para que puedan vivirlo con nosotros en el Museo del Reguilete en el Dinoparque Dije, las brujas, dije, no, si a mis hermanas las tengo encerradas ¡Qué pacho! ¡Qué pacho! Hermanas, ya se van a escapar. Porque no están aquí para pegarle las hermanas, pero sí. Se me van a escapar mis hermanas y se van a ir al Dinopark. Noche de brujas, dicen, pues, ¿cómo? Está bien. Que se disfrace toda la familia. No, ya no es así nada. Prepárense con sus amigos. Saludos de hermanas. Vayan, diviértanse, no olviden su linterna. Lalo, te queremos, por favor, tener ahí presente para que vivas esta experiencia. De todo este gran esfuerzo que hacemos todos los que trabajamos en el Museo del Rehilete, porque ahí van los guías, ¿Sí? Que ellos están preparando también todo esto con nosotros, somos un gran equipo, una gran familia, que que estamos con todo cariño, cada día preparando cosas muy hermosas para ustedes, también modernizando el Museo del Rehilete, tiene ya a partir de esta administración, estos dinosaurios mecatrónicos que han causado sensación, y que no en todos lados están, la verdad que es un privilegio, Muchas cosas que se han venido renovando Y por más que vamos Unos proyectos muy ambiciosos Con todo el apoyo que hemos tenido Del gobernador Julio Menchaca Salazar Así es que vamos adelante con ello No dejen de divertirse Está padrísimo Vengan y encuéntrense con estas noches de terror Gracias Ya aquí apartó su lugar mi hermana Ya me mandó un mensaje Dice ¿Qué pasa? No, está bien, no me paso La verdad que pasó hermana Nada más emocionate Ahí está. Nada más queríamos ver si los estados te escuchan. Ah, no, sí. Perfecto. Vámonos. Son las nueve de la mañana con treinta y un minutos. Vamos a resumen rápidamente en Panorama.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1sc3UwJd4sg6ntyF0Iq464eOI5rGkSX0t/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1p9GedDLvB1XhWYbRLhyz65ikgAUqQqu3/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Uriel Ramirez,  Jair Martínez</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14nPg7LVKbC7us9pTkOVkEFza8Cf6D7cC/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1cSuSuxO_WhLuRg_U4z-D7vYj1V9WAHY5/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1GR_HNPdCPYyzeAMO8Ss_iDcqyAEMLECJ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Saderh/Bol.91/2026</t>
-  </si>
-  <si>
-    <t>Yazmín Leonardo</t>
-  </si>
-  <si>
-    <t>Locutor David Cárdenas destacó la labor de la Secretaría de Agricultura y Desarrollo Rural (Saderh) encabezada por Napoleón González Pérez, enfocada en dotar de herramientas e insumos a los productores del campo de Nopala para hacer más rentable y eficiente su labor. Asimismo, se enfatizó la necesidad de impulsar programas exclusivos para las nuevas generaciones de hijos de campesinos, buscando motivar el relevo generacional ante el abandono que el campo ha sufrido por parte de administraciones anteriores y brindarles mayores oportunidades de desarrollo productivo.</t>
-  </si>
-  <si>
-    <t>Saderh</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>Nopala</t>
-  </si>
-  <si>
-    <t>Esto de la mano con lo que le informaba que llevó a cabo la Sader, la Secretaría de Agricultura en Nopala, con los insumos, pues también se va fortaleciendo en este caso, eh facilitar herramientas para hacer más rentable y eficiente el trabajo de la tierra. Cuando la tierra deja de generar productos, deja de generar productos por falta de herramientas, por falta de semillas, por falta de apoyo. En este caso, de lo que estamos hablando es que no solamente es al productor, está bien a su familia, a los hijos de campesinas y campesinos. La tierra es leal y siempre está dispuesta a brindar generosamente los frutos que en su vientre germinan, se procesan y nacen, pero requiere también la participación del ser humano. Por ello es que la Secretaría de Agricultura y Desarrollo Rural llevó a cabo la entrega en las manos de Napoleón González Pérez en esta estrategia que busca facilitar herramientas para hacer más rentable y eficiente el trabajo de la tierra. Escuchemos a Napoleón González.
-(...) De las actividades del campo deben haber oportunidades para los jóvenes y por eso estamos trabajando con el secretario con el director de Agricultura, Sergio Cortés, un programa para el siguiente año en favor de los jóvenes. Un programa exclusivo para jóvenes, hijos de campesinos, porque hay que motivar el campo, la gente, porque tenemos que ver en el relevo generacional que la mayoría de la gente que trabaja el campo son adultos mayores que merecen todo nuestro respeto y como lo decía en un principio, el campo necesita esfuerzo, necesita tiempo y es el ocio, hay que estar ahí y los jóvenes, por esa falta de atención que hubo para el campo, ese abandono que lo tuvieron los gobiernos anteriores se han alejado pero no porque no quieran trabajar el campo, porque el campo no produzca, no es porque no había oportunidades. Hoy tenemos que acercar más oportunidades, como este equipos para que les facilite ese trabajo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10aXvTpWxuH8l7U-F1TIsP_ZoKusdg3eS/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez</t>
-  </si>
-  <si>
-    <t>Sebiso/Bol.702/2026</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso) llevó a cabo una gira de trabajo de dos días por municipios de la Huasteca y la Sierra Alta de Hidalgo, abarcando localidades como Xochiatipan, Huautla, Atlapexco, Huazalingo, Tlanchinol, Tepehuacán de Guerrero y Tianguistengo. Durante esta gira se entregaron 4,325 tarjetas de los programas Bienestar y Desarrollo y Madres Trabajadoras para evitar gastos de traslado a las familias beneficiarias. Asimismo, se distribuyeron paquetes de cacao y azúcar en Huazalingo y Tianguistengo para la elaboración de chocolate con motivo de las próximas festividades tradicionales y del Xantolo.</t>
-  </si>
-  <si>
-    <t>Bienestar</t>
-  </si>
-  <si>
-    <t>Programas Del Pueblo</t>
-  </si>
-  <si>
-    <t>Gracias, Rosa María. Fíjese que también la Sebiso llevó a cabo la entrega de 4,000 apoyos sociales en una gira por la Huasteca y la Sierra Alta de Hidalgo. La Secretaría de Bienestar e Inclusión Social concluyó una gira de trabajo de dos días por diversos municipios de la Huasteca y la Sierra Alta para la entrega directa de apoyos sociales. El despliegue territorial abarcó las localidades de Xochiatipan, Huautla, Atlapexco, Huazalingo, Tlanchinol, así como Chilijapa en Tepehuacán de Guerrero y Santa Mónica en Tianguistengo. En estas demarcaciones se distribuyeron un total de 4,325 tarjetas correspondientes a los programas Bienestar y Desarrollo, Madres Trabajadoras, todo ello con el propósito de evitar gastos de traslado a los beneficiarios. Adicionalmente, la dependencia estatal entregó paquetes de cacao y azúcar en comunidades de Huazalingo y Tianguistengo para la elaboración tradicional de chocolate, todo esto de cara a las próximas festividades, complementando así las acciones y asistencia social en las regiones indígenas del Estado. Ya estaremos comentando en torno al Xantolo porque en nuestros pueblos originarios, pueblos indígenas, la cultura, la tradición es algo constante, presente todos los días y desde luego en esto los apoyos que se entregan en cacao, desde luego en azúcar fortalece el desarrollo también de estos encuentros culturales de esta tradición familiar y recordar también siempre a los seres queridos que adelantaron en el camino.»</t>
-  </si>
-  <si>
-    <t>SEPH/Bol.1949/2026</t>
-  </si>
-  <si>
-    <t>SEPH promueve entornos escolares seguros, inclusivos y libres de violencia</t>
-  </si>
-  <si>
-    <t>Convivencia Escolar</t>
-  </si>
-  <si>
-    <t>Tepeji del Río</t>
-  </si>
-  <si>
-    <t>Y tenemos también información contigo, Rosa María, en torno a la Secretaría de Educación Pública. Vamos contigo, Rosa María, la SEP
-Con la participación de autoridades educativas, instancias gubernamentales y comunidad escolar, la Secretaría de Educación Pública de Hidalgo realizó la novena edición de la feria para la convivencia escolar en la escuela primaria de TEPG del Río, donde se impulsaron acciones preventivas para fortalecer la cultura de paz y promover ambientes escolares seguros. La jornada benefició a 594 estudiantes, 32 figuras educativas y 120 madres y padres de familia, mediante actividades interactivas orientadas a la prevención, la sana convivencia y la participación de niñas y niños en la construcción de entornos seguros</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1cAb9Xe65wV7uViri6nx4JI-bIF_iD0OK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>La Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh) anunció un programa enfocado en apoyar a las nuevas generaciones de hijos de campesinos dedicados al sector agropecuario, con el fin de facilitar herramientas que hagan más rentable y eficiente el trabajo de la tierra. Este anuncio se dio durante una reunión en Nopala, donde se entregaron 2,918,088 pesos en insumos agrícolas y pecuarios —como semillas, aves, ganado porcino, herramientas y árboles frutales— a 481 productores de la región. En el evento estuvieron presentes alcaldes de Nopala de Villagrán, Huichapan, Tecozautla y Chapantongo para coordinar acciones en favor del desarrollo rural</t>
-  </si>
-  <si>
-    <t>La Saderh alista programa para jóvenes del campo y entrega 2.9 millones de pesos en insumos agrícolas. Estamos hablando de esta reunión en Nopala. La Secretaría de Agricultura y Desarrollo Rural de Hidalgo diseña un programa enfocado en respaldar a las nuevas generaciones dedicadas al sector agropecuario, particularmente a hijas e hijos de campesinos, así lo informó Napoleón González Pérez. La estrategia busca facilitar herramientas para hacer más rentable y eficiente el trabajo de la tierra. El anuncio se realizó durante la distribución de 2,918,088 pesos en apoyo directo a 481 productoras y productores de Nopala de Villagrán y municipios vecinos. Entre los insumos otorgados destacan semillas de maíz, avena y jitomate, aves de doble propósito, vientres porcinos, molinos picadores, rollos de alambre y plantas frutales como limón persa, manzana yala y nogal. Todo esto en apoyo, desde luego, en soporte para todas todas las personas que trabajan la tierra. Al evento acudieron alcaldes de Nopala de Villagrán, Huichapan, Tecozautla y Chapantongo, reflejando el trabajo coordinado entre los municipios de la región para atender el desarrollo rural</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1AEAa7-kPTotuj8hJEEfJYjgArRHABnVE/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Tenemos información de lo que ha acontecido, está sucediendo en este momento y también el día de ayer le daba el adelanto del reconocimiento que hizo el gobernador Julio Menchaca a la trayectoria y vocación del personal médico. El gobernador comentaba el día de ayer en su mensaje en su familia, su hermano Andrés, es médico y evidentemente en la práctica familiar, pues va uno conociendo eh todo el desarrollo de una carrera, de una profesión y desde luego también los retos, el aprendizaje, la capacitación, el estar al día en el tema médico, pues evidentemente hay que estar todos los días eh la disposición del aprendizaje, del desarrollo y también del humanismo de brindar a los pacientes lo mejor de cada eh médica, médico para alcanzar desde luego la salud. En reconocimiento a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud, el gobernador de Hidalgo, Julio Menchaca Salazar, encabezó ayer la entrega de medallas y reconocimiento a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. Escuchemos lo que destacó el gobernador de Hidalgo:
-"Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber".
-De igual manera, Irvyn Asael Rangel Hernández, José Antonio Madrid Gómez, José Francisco Paredes Salazar, José Luis García León, Josefina Gutiérrez Castro, Luciano Ricardo Mendiola, eh son y participaron en estos reconocimientos, les fueron entregados a médicas y médicos cuya labor, reitero, ha contribuido al bienestar de las familias. A nombre de las y los galardonados, Guadalupe Ibarra Durán agradeció a las instituciones de salud por permitirles servir con vocación y humanidad al pueblo de Hidalgo, al tiempo que reafirmó la importancia de contar con el acompañamiento de sus seres queridos en esta elección de vida, dijo, "Gracias a nuestras familias que han soportado y experimentado sacrificios". 
-"Lo primero es no hacer daño", afirmó la secretaria de salud, Vanessa Escalante Arroyo, al reconocer la entrega, la vocación de servicio y profesionalismo del personal médico que día a día trabaja por el bienestar de quienes acuden a los servicios de salud en busca de atención y cuidado. Finalmente, el mandatario estatal recordó que durante su etapa como diputado local, trabajó de manera conjunta con el Colegio Médico Hidalguense en una iniciativa de reforma a la legislación, esto con el propósito de brindar certeza jurídica al personal médico mediante el reconocimiento de una excluyente de responsabilidad penal en aquellos casos en los que, pese a haber cumplido los protocolos de atención establecidos, se produjera alguna lesión o la pérdida de una vida. Parte de lo que se destacó el día de ayer.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nREwZdqLicrAEv1d5qkNspZ-Pk35UilF/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>SSPH/Bol.991/2026</t>
-  </si>
-  <si>
-    <t>La Policía en Hidalgo aseguró 29,000 litros de hidrocarburo y detuvo a una persona en Sempuala. Resulta que hubo un accidente, llegó la policía y detectaron durante la revisión que transportaba cerca de 30,000 litros de combustible»</t>
-  </si>
-  <si>
-    <t>SSPH</t>
-  </si>
-  <si>
-    <t>Combate al huachicol</t>
-  </si>
-  <si>
-    <t>Zempoala</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Wewip_vNhbdl2TJpjGrfPdHACc-Q-wTB/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Fueron detenidas tres personas en posesión de narcóticos y armas de fuego, presentados ya están ante el Ministerio Público.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1_Fb68Z8rmbTe9v7gisXl7e3eRxtXN59T/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Lleva Sebiso apoyos directos a comunidades de la Huasteca y la sierra</t>
-  </si>
-  <si>
-    <t>Bien, por otra parte, le comento acerca de estos apoyos que se brindan en comunidades de la Huasteca y de la Sierra. El objetivo es seguir llevando beneficios a las y los hidalguenses de diferentes regiones del Estado, así lo puntualizó Ricardo Gómez Moreno, el titular de la Secretaría de Bienestar e Inclusión Social, al realizar una gira de trabajo por comunidades de la Huasteca y de la Sierra Alta. En una jornada de dos días, el funcionario estatal visitó, perdón, las localidades de Xochiatipan, Huautla, Atlapexco y Huazalingo, así como Tlanchinol, la comunidad de Chilijapa, de Tepehuacán de Guerrero y Santa Mónica, en el municipio de Tianguistengo, esto en la Sierra Alta. En estos lugares se entregaron de manera directa las tarjetas de los programas Madres Trabajadoras, Bienestar y Desarrollo, garantizando que los recursos lleguen sin intermediarios a las familias que los necesitan. Con un alcance total de 4,325 apoyos entregados de mano en mano, el despliegue territorial benefició a miles de hogares hidalguenses, 3,590 apoyos asignados a través de Bienestar y Desarrollo y 735 del programa Madres Trabajadoras. Al acercar los apoyos hasta sus municipios, la Secretaría de Bienestar evita que las y los beneficiarios realicen gastos de traslado que afecten su economía familiar, además, claro, de ahorrarles tiempo, lo cual también redunda en recursos económicos, puesto que pueden seguir trabajando. Sobre este despliegue en la región, el titular de la dependencia destacó, Ricardo Gómez Moreno, destacó el compromiso de nuestro gobernador Julio Menchaca se demuestra en el territorio entregando las tarjetas de manera personal, informándoles de manera directa. Este recurso es para apoyar a cubrir sus necesidades y a través de él reafirmamos que seguimos trabajando a diario por quien más lo necesita. Así lo puntualizó Ricardo Gómez Moreno. Aunado a la entrega de las tarjetas de apoyo económico, la Sebiso fortalece su compromiso con la identidad cultural de los pueblos originarios mediante la distribución de paquetes con cacao y azúcar en Cocotla, Huazalingo, eh Cocotla, comunidad de Huazalingo y Santa Mónica, comunidad de Tianguistengo. Este insumo permitirá a las familias elaborar las tradicionales tablillas de chocolate para las próximas festividades. Bueno, ya ya están, ya están en curso estas festividades de de Día de Muertos. Hay personas que llevan pues no solo días, sino incluso meses de preparación para esta celebración de Día de Muertos, sobre todo en la Huasteca con el Xantolo y también pues el cultivo de las flores de Sempoaxúchitl tradicionales en esta época, su olor y su color característico llenan las casas, sobre todo de comunidades en la Sierra y en la Huasteca de Hidalgo. Por supuesto, en muchos otros municipios, incluso en las ciudades como Pachuca, como Tulancingo, también se puede apreciar esta festividad, sin embargo, tiene un sabor peculiar, especial en las comunidades, en los municipios al interior del Estado. Si usted tiene la posibilidad de visitar alguno de estos municipios, bueno, si ya ha acudido sabrá que que vale mucho la pena y si no, de verdad, es algo recomendable visitar los municipios de la entidad en el marco de estas celebraciones.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1M2rYregTGEAAT6EYteDAsCZKngvF9FGI/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Hidalgo apuesta por el futuro del campo con oportunidades para jóvenes</t>
-  </si>
-  <si>
-    <t>Y le recuerdo un dato que en su momento dio a conocer el Instituto Nacional de Estadística y Geografía, el INEGI, acerca de la Encuesta Nacional Agropecuaria de este instituto: el 82% de los productores del campo tiene 46 o más años, mientras que solo el 18% tiene menos de 45 años. Sin embargo, hay un dato también favorable, hay una mayor preparación entre las personas que sostienen la actividad agropecuaria del país, pues cada vez hay más productores con bachillerato, incluso con educación superior y más aún con educación especializada en tareas del campo, ingenieros agrónomos, entre otras especialidades que van permitiendo o van favoreciendo la tecnificación y una mejor producción del campo. Sin embargo, es un hecho que cada vez menos jóvenes se han interesado en la actividad agropecuaria. Y en este contexto, le comento que con el objetivo de abrir nuevas oportunidades para los jóvenes que trabajan en el campo, el gobierno del Estado trabaja en el diseño de un programa exclusivo para este sector. Así lo informó el secretario de Agricultura y Desarrollo Rural, Napoleón González Pérez. La iniciativa busca acercar herramientas y apoyos que faciliten las labores agropecuarias, particularmente a quienes son hijos de campesinos y conocen de primera mano el esfuerzo, el tiempo y la dedicación que requiere trabajar la tierra. El titular de esta secretaría destacó que impulsar a las nuevas generaciones es fundamental, sobrado, con alternativas que contribuyan a mejorar las condiciones de trabajo, con opciones que faciliten su labor y creando oportunidades que les permitan alcanzar una mejor calidad de vida. El anuncio se realizó durante la entrega de apoyos por 2,918,000 pesos en beneficio directo de 481 productoras y productores de Nopala, de Villagrán y municipios de la región. Los insumos entregados incluyen semillas de maíz, de avena, perdón, de jitomate, aves de doble propósito, rollos de alambre, molinos picadores y vientres porcinos. También se distribuyeron plantas de limón persa, manzana yala y nogal de cáscara de papel para promover la diversificación de cultivos y fortalecer la rentabilidad de las parcelas. Lo más importante, dijo el secretario de Agricultura, lo más importante para nosotros es saber y escuchar lo que la gente trabajadora del campo siente, porque sabemos perfectamente que la verdadera fuerza del Estado reside ahí, con nuestra gente. Hoy tenemos un gobierno del pueblo y para el pueblo, por eso les pido que sigan confiando en la transformación de Hidalgo. Así lo refirió Napoleón González. En la jornada participaron las presidentas municipales de Nopala, Diana Moreno Rea; la presidenta de Huichapan, Yeymi Solís Zavala; de Tecozautla, Marisol Prieto Avendaño; y el presidente municipal de Chapantongo, Eligio Figueroa Chávez, en una muestra de coordinación entre los distintos órdenes de gobierno para impulsar el desarrollo rural. Con el diseño de este nuevo programa y la entrega de apoyos productivos, la Secretaría de Agricultura busca ampliar las oportunidades para las familias del campo y favorecer que las nuevas generaciones cuenten con herramientas para continuar y fortalecer las actividades agropecuarias que se llevan a cabo en la entidad. Y bueno, pues este tipo de diseños de programas buscando justamente interesar a las y los jóvenes en la actividad del campo.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CEo1cHaygPdiufu_qR3769X961oqjGAv/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Julio Menchaca, Diana Moreno Rea, Yeymi Solís Zavala, Marisol Prieto Avendaño, Eligio Figueroa Chávez</t>
-  </si>
-  <si>
-    <t>Locutor Jesús Riveros da lectura a comentario de radioescucha que reporta, la falta de suministro de agua potable en el fraccionamiento El Palmar, en la capital del estado de Hidalgo. Ante esta situación, se realizó un llamado de atención a la CAASIM para conocer las causas y la posible solución a esta problemática que afecta a los habitantes de la zona.</t>
-  </si>
-  <si>
-    <t>«Gracias a través de la línea telefónica nos informan que no tienen agua en el fraccionamiento El Palmar, perdón, allá en la capital hidalguense. Así que el llamado para la CAASIM, vamos a preguntar a ver qué qué nos puede señalar al respecto.»</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1R7u05pxcYqz4ue06nVFxpcsR2Gqon4bJ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Reconoce Julio Menchaca la trayectoria y vocación del personal médico de Hidalgo</t>
-  </si>
-  <si>
-    <t>Continuamos con información desde la capital del estado y le comparto acerca de este reconocimiento que hace el gobernador del estado a la experiencia, profesionalismo y compromiso social de quienes dedican su vida al cuidado de la salud. En una ceremonia que encabezara por el mandatario estatal, se hizo la entrega de medallas y reconocimientos a 18 médicas y médicos cuya labor ha contribuido al bienestar de las familias hidalguenses. En el marco de este reconocimiento, esto es parte de lo que dijo el gobernador Julio Menchaca:
-"Y hoy estamos reconociendo a médicas, a médicos con una trayectoria profesional que es para presumir, porque son hidalguenses por nacimiento o por adopción, pero que llevan ese cariño profundo a su comunidad, a su municipio, al estado de Hidalgo y a México, proyectándolo con su saber".
-Bien, en esta ceremonia fueron galardonadas y galardonados por su trayectoria y contribuciones al ámbito de la salud: Antonio Christian Oropeza Montemayor, Armando Robles Guzmán, Armando Sinco Ángeles, Elide Zitlali Vera Yañez, Elizabeth Gutiérrez Baltazar, Esteban Quevedo Moraila, Guadalupe Ibarra Durán, Gustavo Martín del Campo Olivares e Ignacio Trejo Borbolla. 
-De igual manera, Irving Asael Rangel Hernández, José Antonio Madrid Gómez Tagle, José Francisco Paredes Salazar, José Luis García León, Josefina Gutiérrez Castro, Luciano Ricardo Mendiola Figueroa, Noé Pérez González, Olga Jimena Torres Peón y Rafael Monroy Arias. 
-A nombre de las y los galardonados, Guadalupe Ibarra Durán agradeció a las instituciones de salud por permitirles servir con vocación y humanidad al pueblo de Hidalgo, al tiempo que reafirmó la importancia de contar con el acompañamiento de sus seres queridos en esta elección de vida, "gracias a nuestras familias que han soportado y experimentado sacrificios"puntualizó. 
-"Lo primero es no hacer daño", afirmó la Secretaria de Salud, Vanessa Escalante Arroyo, al reconocer la entrega vocación de servicio y profesionalismo del personal médico que día a día trabaja por el bienestar de quienes acuden a los servicios de salud en busca de atención y cuidado, es decir, lo primero es una atención justamente adecuada, una atención que haga sentir confianza a las personas que acuden por un servicio de salud.
-Al final de esta ceremonia, el gobernador Julio Menchaca recordó que durante su etapa como diputado local trabajó de manera conjunta con el Colegio Médico Hidalguense en una iniciativa de reforma a la legislación con el propósito de brindar certeza jurídica al personal médico mediante el reconocimiento de una excluyente de responsabilidad penal en aquellos casos en los que, pese haberse cumplido los protocolos de atención establecidos, se produjera alguna lesión o la pérdida de una vida. 
-Por supuesto que las médicas y los médicos, como cualquier otro trabajador, requiere de un sustento, más aún, por supuesto, en su caso, de un sustento legal de tener garantías en la realización de su trabajo que es sumamente delicado y por supuesto también que estas garantías se extiendan a las personas que atienden.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1T8eU4k-ksM0rDnZkRmMd3Uw7tWksAWLR/view?usp=drivesdk</t>
+    <t>Canal 12 Huejutla</t>
+  </si>
+  <si>
+    <t>Vía telefónica a la secretaria de Cultura del Gobierno de Hidalgo, Neyda Naranjo Baltazar con el tema: Celebración del Día de Muertos, Celebración del De muertos: Presencia de Hidalgo en Berlín y Desfile alusivo al día de Muertos.</t>
+  </si>
+  <si>
+    <t>Rubén Juárez</t>
+  </si>
+  <si>
+    <t>Contacto Informativo N</t>
+  </si>
+  <si>
+    <t>Bueno, ya regresamos con más información aquí a Contacto Informativo, tenemos en la línea telefónica a la secretaria de Cultura del Gobierno del Estado de Hidalgo, a Neyda Naranjo Baltazar, secretaria, buenas noches. ¿Qué tal Rubén? Buenas noches, te saludo con mucho gusto a ti, a tu auditorio, muchas gracias por este espacio. Secretaria, bueno, para que nos comparta el tema de el Día de Muertos, y bueno, la la presencia de Hidalgo allá en Berlín, Alemania, secretaria. Claro que sí, mira, pues te voy a platicar que la semana pasada, pues gracias al liderazgo de nuestro gobernador Julio Menchaca Salazar y a la coordinación con la Red de Investigación de las Américas, fue posible llegar a la Embajada de Berlín junto con el presidente municipal Alfredo San Román de Huejutla de Reyes y su equipo, maestras y maestros artesanos, para poder elaborar un altar monumental justamente ahí en la Embajada de México en Berlín. Mostrar un poco de lo que hacemos aquí, de cómo recordamos a nuestros difuntos, de toda la fiesta, porque así lo vivimos nosotros como una fiesta, para recordar a quienes nunca salen de nuestro corazón. también decirte que lo acompañamos con una exposición de máscaras de madera de San Agustín Mezquititlán, y por otro lado nos acompa una maestra artesana del Valle del Mezquital espec del municipio de Chilcuautla con una exposici de artesan de isla Tuvimos también ahí mismo en la embajada una exposición de tenangos que forma parte del acervo de aquí de Secretaría de Cultura, relatos, mitos, esa exposición permanece allá en la embajada y también se montó otro altar en el Hotel Meliá. Esto es la primera ocasión que se lleva a cabo, la primera ocasión que el Xantolo sale a otro país visibilizando nuestra cultura y por otro lado abriendo puertas para nuestros artistas y portadores de cultura. Secretaria, también en otro tema, coméntenos y compártanos el desfile del Día de Muertos. Sí, claro, fíjate que estamos muy emocionados porque por segunda ocasión llevaremos a cabo el desfile Fiesta de las Almas, donde vamos a llevarlo a cabo este viernes 30 de octubre en punto de las 5 de la tarde. la cita es frente al Centro Cultural del Ferrocarril, aquí en Pachuca, y vamos a caminar juntas y juntos hacia el Reloj Monumental hacia el centro de Pachuca Decirte que tenemos la participaci de varios municipios un contingente de m de 1 personas 25 carros aleg una participaci de algunas secretarías, de varias escuelas, también nos acompañan ballets y bueno, será un desfile muy bonito y aprovecho para invitar a la gente para que estén al pendiente porque esta es una oportunidad también de recordar, te decía, a nuestros difuntos, también mostrar un poco de nuestra identidad y este desfile van disfrazados de catrinas, catrines, cuidando mucho Rubén esta parte, la parte de nuestra identidad y decirte que varias regiones van a estar participando en este gran desfile. Secretaria, también para finalizar, bueno, ya este viernes va a ser la inauguración oficial del escenario aquí del Chantolo dos mil veintiséis aquí en el municipio de Bojuta, la invitación, secretaria, si nos hace favor a, bueno, a la gente, no solo de otras regiones, sino de otras partes del país para que asistan a esta parte del estado de Hidalgo. S por supuesto hacerles la invitaci a todas las personas que nos escuchen no se pueden perder este 30 de octubre punto de las 9 de la noche ah en Huejutla la capital cultural la inauguraci del altar monumental Queremos que todos acudan para poder disfrutar de todo lo que se ha preparado para la gente que se acerque el presidente municipal junto con su equipo trabajan est con las puertas abiertas y pues hacerles la invitaci tambi aqu a las personas que no son de nuestro estado a que visiten y que será una gran ruta visitar Huejutla, los demás municipios, Atlapexco, San Felipe, Orizatlán, Yahualica, todos los municipios, porque debemos recordar, Rubén, que el chantolo se vive en los hogares, en la música, en las danzas, y pues queremos juntos y juntas celebrar y recordar a quienes ya se nos han adelantado y que en estas fechas regresan en una visita y recordarlos con estos altares. Ok, secretaria, bueno, agradecerle que nos haya tomado la llamada y bueno, informar de todas las actividades que viene realizando la Secretaría de Cultura del Gobierno del Estado de Hidalgo. Muchas gracias Rubén, invitarlos a todos a que nos sigan en la página de Facebook Secretaría de Cultura de Hidalgo y pues con mucho gusto volver a hacer la invitación. nos vemos en el desfile de Fiesta de las Almas o nos encontramos por allá en la Huasteca en los municipios que así se va a celebrar Ok, secretaria, agradezco mucho y muy amable Buenas noches Buenas noches, hasta luego</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XK7lwCjPLMPqsHy4nclNVbpHTd2hYx_-/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo</t>
+  </si>
+  <si>
+    <t>Vía telefónica Prentice Escamilla. dir de vinculación de la secretaria de cultura del Gobierno de Hidalgo, con el tema: Celebración del Día de Muertos, Celebración del De muertos: Presencia de Hidalgo en Berlín y Desfile alusivo al día de Muertos.</t>
+  </si>
+  <si>
+    <t>Locutor (Juan Carlos Santamaría)]: ...información desde la capital hidalguense. E iniciamos con con buenas noticias, porque sin duda lo son estas eh celebraciones, el estar eh pues recordando la tradición mexicana y eh por supuesto tener actividades al respecto. Y eh tengo el gusto de saludar a René Escamilla Fernández, el director general de Vinculación, Programación y Difusión Cultural de la Secretaría de C